--- a/5_筆記/閱讀數據.xlsx
+++ b/5_筆記/閱讀數據.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="513" uniqueCount="507">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="514" uniqueCount="508">
   <si>
     <t xml:space="preserve">索引號</t>
   </si>
@@ -829,6 +829,9 @@
   </si>
   <si>
     <t xml:space="preserve">晉紀一</t>
+  </si>
+  <si>
+    <t xml:space="preserve">曹奐6年至7年、司馬炎至7年</t>
   </si>
   <si>
     <t xml:space="preserve">晉紀二</t>
@@ -1677,16 +1680,12 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="15">
+  <cellXfs count="12">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -1699,14 +1698,6 @@
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="165" fontId="4" fillId="3" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -1810,7 +1801,7 @@
 </styleSheet>
 </file>
 
-<file path=xl/charts/chart4.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/charts/chart3.xml><?xml version="1.0" encoding="utf-8"?>
 <c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <c:lang val="en-US"/>
   <c:roundedCorners val="0"/>
@@ -1844,7 +1835,7 @@
       <c:overlay val="0"/>
       <c:spPr>
         <a:noFill/>
-        <a:ln w="0">
+        <a:ln>
           <a:noFill/>
         </a:ln>
       </c:spPr>
@@ -1872,7 +1863,7 @@
             <a:solidFill>
               <a:srgbClr val="4f81bd"/>
             </a:solidFill>
-            <a:ln cap="rnd" w="19080">
+            <a:ln w="19080">
               <a:solidFill>
                 <a:srgbClr val="4f81bd"/>
               </a:solidFill>
@@ -1890,7 +1881,7 @@
           </c:marker>
           <c:dLbls>
             <c:txPr>
-              <a:bodyPr wrap="square"/>
+              <a:bodyPr/>
               <a:lstStyle/>
               <a:p>
                 <a:pPr>
@@ -1910,12 +1901,7 @@
             <c:showSerName val="0"/>
             <c:showPercent val="0"/>
             <c:separator>; </c:separator>
-            <c:showLeaderLines val="1"/>
-            <c:extLst>
-              <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
-                <c15:showLeaderLines val="1"/>
-              </c:ext>
-            </c:extLst>
+            <c:showLeaderLines val="0"/>
           </c:dLbls>
           <c:xVal>
             <c:numRef>
@@ -2166,16 +2152,22 @@
                 <c:pt idx="77">
                   <c:v>2.33333333333333</c:v>
                 </c:pt>
+                <c:pt idx="78">
+                  <c:v>1.25</c:v>
+                </c:pt>
+                <c:pt idx="79">
+                  <c:v>164.775735294118</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:yVal>
           <c:smooth val="1"/>
         </c:ser>
-        <c:axId val="98971055"/>
-        <c:axId val="67073672"/>
+        <c:axId val="37135447"/>
+        <c:axId val="47779490"/>
       </c:scatterChart>
       <c:valAx>
-        <c:axId val="98971055"/>
+        <c:axId val="37135447"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -2220,12 +2212,12 @@
           <c:overlay val="0"/>
           <c:spPr>
             <a:noFill/>
-            <a:ln w="0">
+            <a:ln>
               <a:noFill/>
             </a:ln>
           </c:spPr>
         </c:title>
-        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:numFmt formatCode="General" sourceLinked="0"/>
         <c:majorTickMark val="none"/>
         <c:minorTickMark val="none"/>
         <c:tickLblPos val="nextTo"/>
@@ -2251,12 +2243,12 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="67073672"/>
+        <c:crossAx val="47779490"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="midCat"/>
       </c:valAx>
       <c:valAx>
-        <c:axId val="67073672"/>
+        <c:axId val="47779490"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -2301,7 +2293,7 @@
           <c:overlay val="0"/>
           <c:spPr>
             <a:noFill/>
-            <a:ln w="0">
+            <a:ln>
               <a:noFill/>
             </a:ln>
           </c:spPr>
@@ -2332,13 +2324,13 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="98971055"/>
+        <c:crossAx val="37135447"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="midCat"/>
       </c:valAx>
       <c:spPr>
         <a:noFill/>
-        <a:ln w="0">
+        <a:ln>
           <a:noFill/>
         </a:ln>
       </c:spPr>
@@ -2371,9 +2363,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>15</xdr:col>
-      <xdr:colOff>671040</xdr:colOff>
+      <xdr:colOff>670680</xdr:colOff>
       <xdr:row>27</xdr:row>
-      <xdr:rowOff>109080</xdr:rowOff>
+      <xdr:rowOff>108720</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame>
       <xdr:nvGraphicFramePr>
@@ -2381,8 +2373,8 @@
         <xdr:cNvGraphicFramePr/>
       </xdr:nvGraphicFramePr>
       <xdr:xfrm>
-        <a:off x="6835320" y="1995480"/>
-        <a:ext cx="4150080" cy="2742840"/>
+        <a:off x="6835320" y="1995120"/>
+        <a:ext cx="4150080" cy="2742480"/>
       </xdr:xfrm>
       <a:graphic>
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
@@ -2400,72 +2392,71 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:R79"/>
+  <dimension ref="A1:R81"/>
   <sheetFormatPr defaultColWidth="8.68359375" defaultRowHeight="13.5" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="7.76"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="5.76"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="3" style="1" width="11.62"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="2" width="9.76"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="6" style="0" width="9.76"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="5" style="0" width="9.76"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="0" width="7.76"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="9" style="0" width="14.12"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="15" min="15" style="0" width="16.38"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="15" min="15" style="0" width="16.39"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="16" min="16" style="0" width="18.62"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="17" min="17" style="0" width="16.38"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="17" min="17" style="0" width="16.39"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="18" min="18" style="0" width="18.62"/>
   </cols>
   <sheetData>
-    <row r="1" s="7" customFormat="true" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1" s="3" t="s">
+    <row r="1" s="3" customFormat="true" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="4" t="s">
+      <c r="B1" s="3" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="5" t="s">
+      <c r="C1" s="4" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="5" t="s">
+      <c r="D1" s="4" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="6" t="s">
+      <c r="E1" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="4" t="s">
+      <c r="F1" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="3" t="s">
+      <c r="G1" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="7" t="s">
+      <c r="H1" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="I1" s="7" t="s">
+      <c r="I1" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="K1" s="7" t="s">
+      <c r="K1" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="L1" s="7" t="s">
+      <c r="L1" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="M1" s="7" t="s">
+      <c r="M1" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="N1" s="7" t="s">
+      <c r="N1" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="O1" s="7" t="s">
+      <c r="O1" s="3" t="s">
         <v>13</v>
       </c>
-      <c r="P1" s="8" t="s">
+      <c r="P1" s="5" t="s">
         <v>14</v>
       </c>
-      <c r="Q1" s="7" t="s">
+      <c r="Q1" s="3" t="s">
         <v>15</v>
       </c>
-      <c r="R1" s="8" t="s">
+      <c r="R1" s="5" t="s">
         <v>16</v>
       </c>
     </row>
@@ -2483,7 +2474,7 @@
       <c r="D2" s="1" t="n">
         <v>44042</v>
       </c>
-      <c r="E2" s="2" t="n">
+      <c r="E2" s="0" t="n">
         <f aca="false">D2-C2+1</f>
         <v>24</v>
       </c>
@@ -2516,19 +2507,19 @@
       </c>
       <c r="O2" s="0" t="n">
         <f aca="false">L2*$L$10</f>
-        <v>611.128205128205</v>
+        <v>-37491.8</v>
       </c>
       <c r="P2" s="1" t="n">
         <f aca="false">$C$2+O2</f>
-        <v>44630.1282051282</v>
+        <v>6527.2</v>
       </c>
       <c r="Q2" s="0" t="n">
         <f aca="false">(M2-$F$2)*$L$11</f>
-        <v>507.627375782915</v>
+        <v>2601.65360470217</v>
       </c>
       <c r="R2" s="1" t="n">
         <f aca="false">$C$2+Q2</f>
-        <v>44526.6273757829</v>
+        <v>46620.6536047022</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2545,7 +2536,7 @@
       <c r="D3" s="1" t="n">
         <v>44071</v>
       </c>
-      <c r="E3" s="2" t="n">
+      <c r="E3" s="0" t="n">
         <f aca="false">D3-C3+1</f>
         <v>30</v>
       </c>
@@ -2579,19 +2570,19 @@
       </c>
       <c r="O3" s="0" t="n">
         <f aca="false">L3*$L$10</f>
-        <v>701</v>
+        <v>-43005.3</v>
       </c>
       <c r="P3" s="1" t="n">
         <f aca="false">$C$2+O3</f>
-        <v>44720</v>
+        <v>1013.7</v>
       </c>
       <c r="Q3" s="0" t="n">
         <f aca="false">(M3-$F$2)*$L$11</f>
-        <v>556.516047607915</v>
+        <v>2852.21414448087</v>
       </c>
       <c r="R3" s="1" t="n">
         <f aca="false">$C$2+Q3</f>
-        <v>44575.5160476079</v>
+        <v>46871.2141444809</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2608,7 +2599,7 @@
       <c r="D4" s="1" t="n">
         <v>44099</v>
       </c>
-      <c r="E4" s="2" t="n">
+      <c r="E4" s="0" t="n">
         <f aca="false">D4-C4+1</f>
         <v>28</v>
       </c>
@@ -2642,19 +2633,19 @@
       </c>
       <c r="O4" s="0" t="n">
         <f aca="false">L4*$L$10</f>
-        <v>1060.48717948718</v>
+        <v>-65059.3</v>
       </c>
       <c r="P4" s="1" t="n">
         <f aca="false">$C$2+O4</f>
-        <v>45079.4871794872</v>
+        <v>-21040.3</v>
       </c>
       <c r="Q4" s="0" t="n">
         <f aca="false">(M4-$F$2)*$L$11</f>
-        <v>670.589615199581</v>
+        <v>3436.8554039645</v>
       </c>
       <c r="R4" s="1" t="n">
         <f aca="false">$C$2+Q4</f>
-        <v>44689.5896151996</v>
+        <v>47455.8554039645</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2671,7 +2662,7 @@
       <c r="D5" s="1" t="n">
         <v>44121</v>
       </c>
-      <c r="E5" s="2" t="n">
+      <c r="E5" s="0" t="n">
         <f aca="false">D5-C5+1</f>
         <v>23</v>
       </c>
@@ -2705,19 +2696,19 @@
       </c>
       <c r="O5" s="0" t="n">
         <f aca="false">L5*$L$10</f>
-        <v>1581.74358974359</v>
+        <v>-97037.6</v>
       </c>
       <c r="P5" s="1" t="n">
         <f aca="false">$C$2+O5</f>
-        <v>45600.7435897436</v>
+        <v>-53018.6</v>
       </c>
       <c r="Q5" s="0" t="n">
         <f aca="false">(M5-$F$2)*$L$11</f>
-        <v>808.292707506664</v>
+        <v>4142.60092434117</v>
       </c>
       <c r="R5" s="1" t="n">
         <f aca="false">$C$2+Q5</f>
-        <v>44827.2927075067</v>
+        <v>48161.6009243412</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2734,7 +2725,7 @@
       <c r="D6" s="1" t="n">
         <v>44145</v>
       </c>
-      <c r="E6" s="2" t="n">
+      <c r="E6" s="0" t="n">
         <f aca="false">D6-C6+1</f>
         <v>24</v>
       </c>
@@ -2768,19 +2759,19 @@
       </c>
       <c r="O6" s="0" t="n">
         <f aca="false">L6*$L$10</f>
-        <v>2381.60256410256</v>
+        <v>-146107.75</v>
       </c>
       <c r="P6" s="1" t="n">
         <f aca="false">$C$2+O6</f>
-        <v>46400.6025641026</v>
+        <v>-102088.75</v>
       </c>
       <c r="Q6" s="0" t="n">
         <f aca="false">(M6-$F$2)*$L$11</f>
-        <v>1067.40266817916</v>
+        <v>5470.57178516829</v>
       </c>
       <c r="R6" s="1" t="n">
         <f aca="false">$C$2+Q6</f>
-        <v>45086.4026681792</v>
+        <v>49489.5717851683</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2797,7 +2788,7 @@
       <c r="D7" s="1" t="n">
         <v>44171</v>
       </c>
-      <c r="E7" s="2" t="n">
+      <c r="E7" s="0" t="n">
         <f aca="false">D7-C7+1</f>
         <v>26</v>
       </c>
@@ -2831,19 +2822,19 @@
       </c>
       <c r="O7" s="0" t="n">
         <f aca="false">L7*$L$10</f>
-        <v>2642.23076923077</v>
+        <v>-162096.9</v>
       </c>
       <c r="P7" s="1" t="n">
         <f aca="false">$C$2+O7</f>
-        <v>46661.2307692308</v>
+        <v>-118077.9</v>
       </c>
       <c r="Q7" s="0" t="n">
         <f aca="false">(M7-$F$2)*$L$11</f>
-        <v>1109.7728504275</v>
+        <v>5687.72425297649</v>
       </c>
       <c r="R7" s="1" t="n">
         <f aca="false">$C$2+Q7</f>
-        <v>45128.7728504275</v>
+        <v>49706.7242529765</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2860,7 +2851,7 @@
       <c r="D8" s="1" t="n">
         <v>44187</v>
       </c>
-      <c r="E8" s="2" t="n">
+      <c r="E8" s="0" t="n">
         <f aca="false">D8-C8+1</f>
         <v>16</v>
       </c>
@@ -2882,10 +2873,10 @@
       <c r="K8" s="0" t="s">
         <v>23</v>
       </c>
-      <c r="L8" s="9" t="n">
+      <c r="L8" s="6" t="n">
         <v>294</v>
       </c>
-      <c r="M8" s="9" t="n">
+      <c r="M8" s="6" t="n">
         <v>959</v>
       </c>
       <c r="N8" s="0" t="n">
@@ -2894,19 +2885,19 @@
       </c>
       <c r="O8" s="0" t="n">
         <f aca="false">L8*$L$10</f>
-        <v>2642.23076923077</v>
+        <v>-162096.9</v>
       </c>
       <c r="P8" s="1" t="n">
         <f aca="false">$C$2+O8</f>
-        <v>46661.2307692308</v>
+        <v>-118077.9</v>
       </c>
       <c r="Q8" s="0" t="n">
         <f aca="false">(M8-$F$2)*$L$11</f>
-        <v>1109.7728504275</v>
+        <v>5687.72425297649</v>
       </c>
       <c r="R8" s="1" t="n">
         <f aca="false">$C$2+Q8</f>
-        <v>45128.7728504275</v>
+        <v>49706.7242529765</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2923,7 +2914,7 @@
       <c r="D9" s="1" t="n">
         <v>44202</v>
       </c>
-      <c r="E9" s="2" t="n">
+      <c r="E9" s="0" t="n">
         <f aca="false">D9-C9+1</f>
         <v>15</v>
       </c>
@@ -2957,7 +2948,7 @@
       <c r="D10" s="1" t="n">
         <v>44207</v>
       </c>
-      <c r="E10" s="2" t="n">
+      <c r="E10" s="0" t="n">
         <f aca="false">D10-C10+1</f>
         <v>5</v>
       </c>
@@ -2981,7 +2972,7 @@
       </c>
       <c r="L10" s="0" t="n">
         <f aca="false">AVERAGE(E:E)</f>
-        <v>8.98717948717949</v>
+        <v>-551.35</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2998,7 +2989,7 @@
       <c r="D11" s="1" t="n">
         <v>44212</v>
       </c>
-      <c r="E11" s="2" t="n">
+      <c r="E11" s="0" t="n">
         <f aca="false">D11-C11+1</f>
         <v>6</v>
       </c>
@@ -3022,7 +3013,7 @@
       </c>
       <c r="L11" s="0" t="n">
         <f aca="false">AVEDEV(I:I)</f>
-        <v>0.814811197083331</v>
+        <v>4.17600899631167</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3039,7 +3030,7 @@
       <c r="D12" s="1" t="n">
         <v>44220</v>
       </c>
-      <c r="E12" s="2" t="n">
+      <c r="E12" s="0" t="n">
         <f aca="false">D12-C12+1</f>
         <v>8</v>
       </c>
@@ -3073,7 +3064,7 @@
       <c r="D13" s="1" t="n">
         <v>44229</v>
       </c>
-      <c r="E13" s="2" t="n">
+      <c r="E13" s="0" t="n">
         <f aca="false">D13-C13+1</f>
         <v>9</v>
       </c>
@@ -3107,7 +3098,7 @@
       <c r="D14" s="1" t="n">
         <v>44238</v>
       </c>
-      <c r="E14" s="2" t="n">
+      <c r="E14" s="0" t="n">
         <f aca="false">D14-C14+1</f>
         <v>10</v>
       </c>
@@ -3141,7 +3132,7 @@
       <c r="D15" s="1" t="n">
         <v>44247</v>
       </c>
-      <c r="E15" s="2" t="n">
+      <c r="E15" s="0" t="n">
         <f aca="false">D15-C15+1</f>
         <v>9</v>
       </c>
@@ -3175,7 +3166,7 @@
       <c r="D16" s="1" t="n">
         <v>44255</v>
       </c>
-      <c r="E16" s="2" t="n">
+      <c r="E16" s="0" t="n">
         <f aca="false">D16-C16+1</f>
         <v>8</v>
       </c>
@@ -3209,7 +3200,7 @@
       <c r="D17" s="1" t="n">
         <v>44264</v>
       </c>
-      <c r="E17" s="2" t="n">
+      <c r="E17" s="0" t="n">
         <f aca="false">D17-C17+1</f>
         <v>9</v>
       </c>
@@ -3243,7 +3234,7 @@
       <c r="D18" s="1" t="n">
         <v>44271</v>
       </c>
-      <c r="E18" s="2" t="n">
+      <c r="E18" s="0" t="n">
         <f aca="false">D18-C18+1</f>
         <v>7</v>
       </c>
@@ -3277,7 +3268,7 @@
       <c r="D19" s="1" t="n">
         <v>44278</v>
       </c>
-      <c r="E19" s="2" t="n">
+      <c r="E19" s="0" t="n">
         <f aca="false">D19-C19+1</f>
         <v>7</v>
       </c>
@@ -3285,7 +3276,7 @@
         <f aca="false">G18+1</f>
         <v>-133</v>
       </c>
-      <c r="G19" s="2" t="n">
+      <c r="G19" s="0" t="n">
         <v>-125</v>
       </c>
       <c r="H19" s="0" t="n">
@@ -3311,7 +3302,7 @@
       <c r="D20" s="1" t="n">
         <v>44287</v>
       </c>
-      <c r="E20" s="2" t="n">
+      <c r="E20" s="0" t="n">
         <f aca="false">D20-C20+1</f>
         <v>9</v>
       </c>
@@ -3319,7 +3310,7 @@
         <f aca="false">G19+1</f>
         <v>-124</v>
       </c>
-      <c r="G20" s="2" t="n">
+      <c r="G20" s="0" t="n">
         <v>-119</v>
       </c>
       <c r="H20" s="0" t="n">
@@ -3345,7 +3336,7 @@
       <c r="D21" s="1" t="n">
         <v>44293</v>
       </c>
-      <c r="E21" s="2" t="n">
+      <c r="E21" s="0" t="n">
         <f aca="false">D21-C21+1</f>
         <v>7</v>
       </c>
@@ -3353,7 +3344,7 @@
         <f aca="false">G20+1</f>
         <v>-118</v>
       </c>
-      <c r="G21" s="2" t="n">
+      <c r="G21" s="0" t="n">
         <v>-110</v>
       </c>
       <c r="H21" s="0" t="n">
@@ -3379,7 +3370,7 @@
       <c r="D22" s="1" t="n">
         <v>44300</v>
       </c>
-      <c r="E22" s="2" t="n">
+      <c r="E22" s="0" t="n">
         <f aca="false">D22-C22+1</f>
         <v>7</v>
       </c>
@@ -3413,7 +3404,7 @@
       <c r="D23" s="1" t="n">
         <v>44307</v>
       </c>
-      <c r="E23" s="2" t="n">
+      <c r="E23" s="0" t="n">
         <f aca="false">D23-C23+1</f>
         <v>8</v>
       </c>
@@ -3421,7 +3412,7 @@
         <f aca="false">G22+1</f>
         <v>-98</v>
       </c>
-      <c r="G23" s="2" t="n">
+      <c r="G23" s="0" t="n">
         <v>-87</v>
       </c>
       <c r="H23" s="0" t="n">
@@ -3447,7 +3438,7 @@
       <c r="D24" s="1" t="n">
         <v>44316</v>
       </c>
-      <c r="E24" s="2" t="n">
+      <c r="E24" s="0" t="n">
         <f aca="false">D24-C24+1</f>
         <v>10</v>
       </c>
@@ -3481,7 +3472,7 @@
       <c r="D25" s="1" t="n">
         <v>44325</v>
       </c>
-      <c r="E25" s="2" t="n">
+      <c r="E25" s="0" t="n">
         <f aca="false">D25-C25+1</f>
         <v>9</v>
       </c>
@@ -3515,7 +3506,7 @@
       <c r="D26" s="1" t="n">
         <v>44330</v>
       </c>
-      <c r="E26" s="2" t="n">
+      <c r="E26" s="0" t="n">
         <f aca="false">D26-C26+1</f>
         <v>6</v>
       </c>
@@ -3549,7 +3540,7 @@
       <c r="D27" s="1" t="n">
         <v>44333</v>
       </c>
-      <c r="E27" s="2" t="n">
+      <c r="E27" s="0" t="n">
         <f aca="false">D27-C27+1</f>
         <v>3</v>
       </c>
@@ -3583,7 +3574,7 @@
       <c r="D28" s="1" t="n">
         <v>44340</v>
       </c>
-      <c r="E28" s="2" t="n">
+      <c r="E28" s="0" t="n">
         <f aca="false">D28-C28+1</f>
         <v>7</v>
       </c>
@@ -3591,7 +3582,7 @@
         <f aca="false">G27+1</f>
         <v>-58</v>
       </c>
-      <c r="G28" s="2" t="n">
+      <c r="G28" s="0" t="n">
         <v>-49</v>
       </c>
       <c r="H28" s="0" t="n">
@@ -3617,7 +3608,7 @@
       <c r="D29" s="1" t="n">
         <v>44345</v>
       </c>
-      <c r="E29" s="2" t="n">
+      <c r="E29" s="0" t="n">
         <f aca="false">D29-C29+1</f>
         <v>5</v>
       </c>
@@ -3625,7 +3616,7 @@
         <f aca="false">G28+1</f>
         <v>-48</v>
       </c>
-      <c r="G29" s="2" t="n">
+      <c r="G29" s="0" t="n">
         <v>-42</v>
       </c>
       <c r="H29" s="0" t="n">
@@ -3651,7 +3642,7 @@
       <c r="D30" s="1" t="n">
         <v>44352</v>
       </c>
-      <c r="E30" s="2" t="n">
+      <c r="E30" s="0" t="n">
         <f aca="false">D30-C30+1</f>
         <v>7</v>
       </c>
@@ -3659,7 +3650,7 @@
         <f aca="false">G29+1</f>
         <v>-41</v>
       </c>
-      <c r="G30" s="2" t="n">
+      <c r="G30" s="0" t="n">
         <v>-33</v>
       </c>
       <c r="H30" s="0" t="n">
@@ -3685,7 +3676,7 @@
       <c r="D31" s="1" t="n">
         <v>44361</v>
       </c>
-      <c r="E31" s="2" t="n">
+      <c r="E31" s="0" t="n">
         <f aca="false">D31-C31+1</f>
         <v>9</v>
       </c>
@@ -3693,7 +3684,7 @@
         <f aca="false">G30+1</f>
         <v>-32</v>
       </c>
-      <c r="G31" s="2" t="n">
+      <c r="G31" s="0" t="n">
         <v>-23</v>
       </c>
       <c r="H31" s="0" t="n">
@@ -3719,7 +3710,7 @@
       <c r="D32" s="1" t="n">
         <v>44368</v>
       </c>
-      <c r="E32" s="2" t="n">
+      <c r="E32" s="0" t="n">
         <f aca="false">D32-C32+1</f>
         <v>8</v>
       </c>
@@ -3727,7 +3718,7 @@
         <f aca="false">G31+1</f>
         <v>-22</v>
       </c>
-      <c r="G32" s="2" t="n">
+      <c r="G32" s="0" t="n">
         <v>-14</v>
       </c>
       <c r="H32" s="0" t="n">
@@ -3753,7 +3744,7 @@
       <c r="D33" s="1" t="n">
         <v>44373</v>
       </c>
-      <c r="E33" s="2" t="n">
+      <c r="E33" s="0" t="n">
         <f aca="false">D33-C33+1</f>
         <v>5</v>
       </c>
@@ -3761,7 +3752,7 @@
         <f aca="false">G32+1</f>
         <v>-13</v>
       </c>
-      <c r="G33" s="2" t="n">
+      <c r="G33" s="0" t="n">
         <v>-8</v>
       </c>
       <c r="H33" s="0" t="n">
@@ -3787,7 +3778,7 @@
       <c r="D34" s="1" t="n">
         <v>44377</v>
       </c>
-      <c r="E34" s="2" t="n">
+      <c r="E34" s="0" t="n">
         <f aca="false">D34-C34+1</f>
         <v>5</v>
       </c>
@@ -3795,7 +3786,7 @@
         <f aca="false">G33+1</f>
         <v>-7</v>
       </c>
-      <c r="G34" s="2" t="n">
+      <c r="G34" s="0" t="n">
         <v>-6</v>
       </c>
       <c r="H34" s="0" t="n">
@@ -3821,7 +3812,7 @@
       <c r="D35" s="1" t="n">
         <v>44380</v>
       </c>
-      <c r="E35" s="2" t="n">
+      <c r="E35" s="0" t="n">
         <f aca="false">D35-C35+1</f>
         <v>3</v>
       </c>
@@ -3829,7 +3820,7 @@
         <f aca="false">G34+1</f>
         <v>-5</v>
       </c>
-      <c r="G35" s="2" t="n">
+      <c r="G35" s="0" t="n">
         <v>-3</v>
       </c>
       <c r="H35" s="0" t="n">
@@ -3855,7 +3846,7 @@
       <c r="D36" s="1" t="n">
         <v>44385</v>
       </c>
-      <c r="E36" s="2" t="n">
+      <c r="E36" s="0" t="n">
         <f aca="false">D36-C36+1</f>
         <v>5</v>
       </c>
@@ -3863,7 +3854,7 @@
         <f aca="false">G35+1</f>
         <v>-2</v>
       </c>
-      <c r="G36" s="2" t="n">
+      <c r="G36" s="0" t="n">
         <v>2</v>
       </c>
       <c r="H36" s="0" t="n">
@@ -3889,7 +3880,7 @@
       <c r="D37" s="1" t="n">
         <v>44390</v>
       </c>
-      <c r="E37" s="2" t="n">
+      <c r="E37" s="0" t="n">
         <f aca="false">D37-C37+1</f>
         <v>5</v>
       </c>
@@ -3897,7 +3888,7 @@
         <f aca="false">G36+1</f>
         <v>3</v>
       </c>
-      <c r="G37" s="2" t="n">
+      <c r="G37" s="0" t="n">
         <v>8</v>
       </c>
       <c r="H37" s="0" t="n">
@@ -3923,7 +3914,7 @@
       <c r="D38" s="1" t="n">
         <v>44396</v>
       </c>
-      <c r="E38" s="2" t="n">
+      <c r="E38" s="0" t="n">
         <f aca="false">D38-C38+1</f>
         <v>6</v>
       </c>
@@ -3931,7 +3922,7 @@
         <f aca="false">G37+1</f>
         <v>9</v>
       </c>
-      <c r="G38" s="2" t="n">
+      <c r="G38" s="0" t="n">
         <v>14</v>
       </c>
       <c r="H38" s="0" t="n">
@@ -3957,7 +3948,7 @@
       <c r="D39" s="1" t="n">
         <v>44403</v>
       </c>
-      <c r="E39" s="2" t="n">
+      <c r="E39" s="0" t="n">
         <f aca="false">D39-C39+1</f>
         <v>7</v>
       </c>
@@ -3965,7 +3956,7 @@
         <f aca="false">G38+1</f>
         <v>15</v>
       </c>
-      <c r="G39" s="2" t="n">
+      <c r="G39" s="0" t="n">
         <v>22</v>
       </c>
       <c r="H39" s="0" t="n">
@@ -3991,7 +3982,7 @@
       <c r="D40" s="1" t="n">
         <v>44409</v>
       </c>
-      <c r="E40" s="2" t="n">
+      <c r="E40" s="0" t="n">
         <f aca="false">D40-C40+1</f>
         <v>6</v>
       </c>
@@ -3999,7 +3990,7 @@
         <f aca="false">G39+1</f>
         <v>23</v>
       </c>
-      <c r="G40" s="2" t="n">
+      <c r="G40" s="0" t="n">
         <v>24</v>
       </c>
       <c r="H40" s="0" t="n">
@@ -4025,7 +4016,7 @@
       <c r="D41" s="1" t="n">
         <v>44416</v>
       </c>
-      <c r="E41" s="2" t="n">
+      <c r="E41" s="0" t="n">
         <f aca="false">D41-C41+1</f>
         <v>7</v>
       </c>
@@ -4033,7 +4024,7 @@
         <f aca="false">G40+1</f>
         <v>25</v>
       </c>
-      <c r="G41" s="2" t="n">
+      <c r="G41" s="0" t="n">
         <v>26</v>
       </c>
       <c r="H41" s="0" t="n">
@@ -4059,7 +4050,7 @@
       <c r="D42" s="1" t="n">
         <v>44424</v>
       </c>
-      <c r="E42" s="2" t="n">
+      <c r="E42" s="0" t="n">
         <f aca="false">D42-C42+1</f>
         <v>8</v>
       </c>
@@ -4067,7 +4058,7 @@
         <f aca="false">G41+1</f>
         <v>27</v>
       </c>
-      <c r="G42" s="2" t="n">
+      <c r="G42" s="0" t="n">
         <v>29</v>
       </c>
       <c r="H42" s="0" t="n">
@@ -4093,7 +4084,7 @@
       <c r="D43" s="1" t="n">
         <v>44430</v>
       </c>
-      <c r="E43" s="2" t="n">
+      <c r="E43" s="0" t="n">
         <f aca="false">D43-C43+1</f>
         <v>6</v>
       </c>
@@ -4101,7 +4092,7 @@
         <f aca="false">G42+1</f>
         <v>30</v>
       </c>
-      <c r="G43" s="2" t="n">
+      <c r="G43" s="0" t="n">
         <v>35</v>
       </c>
       <c r="H43" s="0" t="n">
@@ -4127,7 +4118,7 @@
       <c r="D44" s="1" t="n">
         <v>44438</v>
       </c>
-      <c r="E44" s="2" t="n">
+      <c r="E44" s="0" t="n">
         <f aca="false">D44-C44+1</f>
         <v>8</v>
       </c>
@@ -4135,7 +4126,7 @@
         <f aca="false">G43+1</f>
         <v>36</v>
       </c>
-      <c r="G44" s="2" t="n">
+      <c r="G44" s="0" t="n">
         <v>46</v>
       </c>
       <c r="H44" s="0" t="n">
@@ -4161,7 +4152,7 @@
       <c r="D45" s="1" t="n">
         <v>44446</v>
       </c>
-      <c r="E45" s="2" t="n">
+      <c r="E45" s="0" t="n">
         <f aca="false">D45-C45+1</f>
         <v>8</v>
       </c>
@@ -4169,7 +4160,7 @@
         <f aca="false">G44+1</f>
         <v>47</v>
       </c>
-      <c r="G45" s="2" t="n">
+      <c r="G45" s="0" t="n">
         <v>60</v>
       </c>
       <c r="H45" s="0" t="n">
@@ -4195,7 +4186,7 @@
       <c r="D46" s="1" t="n">
         <v>44455</v>
       </c>
-      <c r="E46" s="2" t="n">
+      <c r="E46" s="0" t="n">
         <f aca="false">D46-C46+1</f>
         <v>9</v>
       </c>
@@ -4203,7 +4194,7 @@
         <f aca="false">G45+1</f>
         <v>61</v>
       </c>
-      <c r="G46" s="2" t="n">
+      <c r="G46" s="0" t="n">
         <v>75</v>
       </c>
       <c r="H46" s="0" t="n">
@@ -4230,7 +4221,7 @@
       <c r="D47" s="1" t="n">
         <v>44462</v>
       </c>
-      <c r="E47" s="2" t="n">
+      <c r="E47" s="0" t="n">
         <f aca="false">D47-C47+1</f>
         <v>7</v>
       </c>
@@ -4238,7 +4229,7 @@
         <f aca="false">G46+1</f>
         <v>76</v>
       </c>
-      <c r="G47" s="2" t="n">
+      <c r="G47" s="0" t="n">
         <v>84</v>
       </c>
       <c r="H47" s="0" t="n">
@@ -4265,7 +4256,7 @@
       <c r="D48" s="1" t="n">
         <v>44469</v>
       </c>
-      <c r="E48" s="2" t="n">
+      <c r="E48" s="0" t="n">
         <f aca="false">D48-C48+1</f>
         <v>7</v>
       </c>
@@ -4273,7 +4264,7 @@
         <f aca="false">G47+1</f>
         <v>85</v>
       </c>
-      <c r="G48" s="2" t="n">
+      <c r="G48" s="0" t="n">
         <v>91</v>
       </c>
       <c r="H48" s="0" t="n">
@@ -4300,7 +4291,7 @@
       <c r="D49" s="1" t="n">
         <v>44477</v>
       </c>
-      <c r="E49" s="2" t="n">
+      <c r="E49" s="0" t="n">
         <f aca="false">D49-C49+1</f>
         <v>8</v>
       </c>
@@ -4308,7 +4299,7 @@
         <f aca="false">G48+1</f>
         <v>92</v>
       </c>
-      <c r="G49" s="2" t="n">
+      <c r="G49" s="0" t="n">
         <v>105</v>
       </c>
       <c r="H49" s="0" t="n">
@@ -4335,7 +4326,7 @@
       <c r="D50" s="1" t="n">
         <v>44486</v>
       </c>
-      <c r="E50" s="2" t="n">
+      <c r="E50" s="0" t="n">
         <f aca="false">D50-C50+1</f>
         <v>9</v>
       </c>
@@ -4343,7 +4334,7 @@
         <f aca="false">G49+1</f>
         <v>106</v>
       </c>
-      <c r="G50" s="2" t="n">
+      <c r="G50" s="0" t="n">
         <v>115</v>
       </c>
       <c r="H50" s="0" t="n">
@@ -4370,7 +4361,7 @@
       <c r="D51" s="1" t="n">
         <v>44496</v>
       </c>
-      <c r="E51" s="2" t="n">
+      <c r="E51" s="0" t="n">
         <f aca="false">D51-C51+1</f>
         <v>10</v>
       </c>
@@ -4378,7 +4369,7 @@
         <f aca="false">G50+1</f>
         <v>116</v>
       </c>
-      <c r="G51" s="2" t="n">
+      <c r="G51" s="0" t="n">
         <v>124</v>
       </c>
       <c r="H51" s="0" t="n">
@@ -4405,7 +4396,7 @@
       <c r="D52" s="1" t="n">
         <v>44504</v>
       </c>
-      <c r="E52" s="2" t="n">
+      <c r="E52" s="0" t="n">
         <f aca="false">D52-C52+1</f>
         <v>8</v>
       </c>
@@ -4413,7 +4404,7 @@
         <f aca="false">G51+1</f>
         <v>125</v>
       </c>
-      <c r="G52" s="2" t="n">
+      <c r="G52" s="0" t="n">
         <v>133</v>
       </c>
       <c r="H52" s="0" t="n">
@@ -4440,7 +4431,7 @@
       <c r="D53" s="1" t="n">
         <v>44513</v>
       </c>
-      <c r="E53" s="2" t="n">
+      <c r="E53" s="0" t="n">
         <f aca="false">D53-C53+1</f>
         <v>9</v>
       </c>
@@ -4448,7 +4439,7 @@
         <f aca="false">G52+1</f>
         <v>134</v>
       </c>
-      <c r="G53" s="2" t="n">
+      <c r="G53" s="0" t="n">
         <v>145</v>
       </c>
       <c r="H53" s="0" t="n">
@@ -4475,7 +4466,7 @@
       <c r="D54" s="1" t="n">
         <v>44521</v>
       </c>
-      <c r="E54" s="2" t="n">
+      <c r="E54" s="0" t="n">
         <f aca="false">D54-C54+1</f>
         <v>8</v>
       </c>
@@ -4483,7 +4474,7 @@
         <f aca="false">G53+1</f>
         <v>146</v>
       </c>
-      <c r="G54" s="2" t="n">
+      <c r="G54" s="0" t="n">
         <v>156</v>
       </c>
       <c r="H54" s="0" t="n">
@@ -4510,7 +4501,7 @@
       <c r="D55" s="1" t="n">
         <v>44529</v>
       </c>
-      <c r="E55" s="2" t="n">
+      <c r="E55" s="0" t="n">
         <f aca="false">D55-C55+1</f>
         <v>8</v>
       </c>
@@ -4518,7 +4509,7 @@
         <f aca="false">G54+1</f>
         <v>157</v>
       </c>
-      <c r="G55" s="2" t="n">
+      <c r="G55" s="0" t="n">
         <v>163</v>
       </c>
       <c r="H55" s="0" t="n">
@@ -4545,7 +4536,7 @@
       <c r="D56" s="1" t="n">
         <v>44535</v>
       </c>
-      <c r="E56" s="2" t="n">
+      <c r="E56" s="0" t="n">
         <f aca="false">D56-C56+1</f>
         <v>6</v>
       </c>
@@ -4553,7 +4544,7 @@
         <f aca="false">G55+1</f>
         <v>164</v>
       </c>
-      <c r="G56" s="2" t="n">
+      <c r="G56" s="0" t="n">
         <v>166</v>
       </c>
       <c r="H56" s="0" t="n">
@@ -4580,7 +4571,7 @@
       <c r="D57" s="1" t="n">
         <v>44542</v>
       </c>
-      <c r="E57" s="2" t="n">
+      <c r="E57" s="0" t="n">
         <f aca="false">D57-C57+1</f>
         <v>7</v>
       </c>
@@ -4588,7 +4579,7 @@
         <f aca="false">G56+1</f>
         <v>167</v>
       </c>
-      <c r="G57" s="2" t="n">
+      <c r="G57" s="0" t="n">
         <v>171</v>
       </c>
       <c r="H57" s="0" t="n">
@@ -4615,7 +4606,7 @@
       <c r="D58" s="1" t="n">
         <v>44550</v>
       </c>
-      <c r="E58" s="2" t="n">
+      <c r="E58" s="0" t="n">
         <f aca="false">D58-C58+1</f>
         <v>8</v>
       </c>
@@ -4623,7 +4614,7 @@
         <f aca="false">G57+1</f>
         <v>172</v>
       </c>
-      <c r="G58" s="2" t="n">
+      <c r="G58" s="0" t="n">
         <v>180</v>
       </c>
       <c r="H58" s="0" t="n">
@@ -4650,7 +4641,7 @@
       <c r="D59" s="1" t="n">
         <v>44557</v>
       </c>
-      <c r="E59" s="2" t="n">
+      <c r="E59" s="0" t="n">
         <f aca="false">D59-C59+1</f>
         <v>7</v>
       </c>
@@ -4658,7 +4649,7 @@
         <f aca="false">G58+1</f>
         <v>181</v>
       </c>
-      <c r="G59" s="2" t="n">
+      <c r="G59" s="0" t="n">
         <v>187</v>
       </c>
       <c r="H59" s="0" t="n">
@@ -4685,7 +4676,7 @@
       <c r="D60" s="1" t="n">
         <v>44565</v>
       </c>
-      <c r="E60" s="2" t="n">
+      <c r="E60" s="0" t="n">
         <f aca="false">D60-C60+1</f>
         <v>8</v>
       </c>
@@ -4693,7 +4684,7 @@
         <f aca="false">G59+1</f>
         <v>188</v>
       </c>
-      <c r="G60" s="2" t="n">
+      <c r="G60" s="0" t="n">
         <v>190</v>
       </c>
       <c r="H60" s="0" t="n">
@@ -4720,7 +4711,7 @@
       <c r="D61" s="1" t="n">
         <v>44574</v>
       </c>
-      <c r="E61" s="2" t="n">
+      <c r="E61" s="0" t="n">
         <f aca="false">D61-C61+1</f>
         <v>9</v>
       </c>
@@ -4728,7 +4719,7 @@
         <f aca="false">G60+1</f>
         <v>191</v>
       </c>
-      <c r="G61" s="2" t="n">
+      <c r="G61" s="0" t="n">
         <v>193</v>
       </c>
       <c r="H61" s="0" t="n">
@@ -4755,7 +4746,7 @@
       <c r="D62" s="1" t="n">
         <v>44584</v>
       </c>
-      <c r="E62" s="2" t="n">
+      <c r="E62" s="0" t="n">
         <f aca="false">D62-C62+1</f>
         <v>10</v>
       </c>
@@ -4763,7 +4754,7 @@
         <f aca="false">G61+1</f>
         <v>194</v>
       </c>
-      <c r="G62" s="2" t="n">
+      <c r="G62" s="0" t="n">
         <v>195</v>
       </c>
       <c r="H62" s="0" t="n">
@@ -4790,7 +4781,7 @@
       <c r="D63" s="1" t="n">
         <v>44592</v>
       </c>
-      <c r="E63" s="2" t="n">
+      <c r="E63" s="0" t="n">
         <f aca="false">D63-C63+1</f>
         <v>8</v>
       </c>
@@ -4798,7 +4789,7 @@
         <f aca="false">G62+1</f>
         <v>196</v>
       </c>
-      <c r="G63" s="2" t="n">
+      <c r="G63" s="0" t="n">
         <v>198</v>
       </c>
       <c r="H63" s="0" t="n">
@@ -4825,7 +4816,7 @@
       <c r="D64" s="1" t="n">
         <v>44600</v>
       </c>
-      <c r="E64" s="2" t="n">
+      <c r="E64" s="0" t="n">
         <f aca="false">D64-C64+1</f>
         <v>8</v>
       </c>
@@ -4833,7 +4824,7 @@
         <f aca="false">G63+1</f>
         <v>199</v>
       </c>
-      <c r="G64" s="2" t="n">
+      <c r="G64" s="0" t="n">
         <v>200</v>
       </c>
       <c r="H64" s="0" t="n">
@@ -4860,7 +4851,7 @@
       <c r="D65" s="1" t="n">
         <v>44608</v>
       </c>
-      <c r="E65" s="2" t="n">
+      <c r="E65" s="0" t="n">
         <f aca="false">D65-C65+1</f>
         <v>8</v>
       </c>
@@ -4868,7 +4859,7 @@
         <f aca="false">G64+1</f>
         <v>201</v>
       </c>
-      <c r="G65" s="2" t="n">
+      <c r="G65" s="0" t="n">
         <v>205</v>
       </c>
       <c r="H65" s="0" t="n">
@@ -4895,7 +4886,7 @@
       <c r="D66" s="1" t="n">
         <v>44616</v>
       </c>
-      <c r="E66" s="2" t="n">
+      <c r="E66" s="0" t="n">
         <f aca="false">D66-C66+1</f>
         <v>8</v>
       </c>
@@ -4903,7 +4894,7 @@
         <f aca="false">G65+1</f>
         <v>206</v>
       </c>
-      <c r="G66" s="2" t="n">
+      <c r="G66" s="0" t="n">
         <v>208</v>
       </c>
       <c r="H66" s="0" t="n">
@@ -4930,7 +4921,7 @@
       <c r="D67" s="1" t="n">
         <v>44625</v>
       </c>
-      <c r="E67" s="2" t="n">
+      <c r="E67" s="0" t="n">
         <f aca="false">D67-C67+1</f>
         <v>9</v>
       </c>
@@ -4938,7 +4929,7 @@
         <f aca="false">G66+1</f>
         <v>209</v>
       </c>
-      <c r="G67" s="2" t="n">
+      <c r="G67" s="0" t="n">
         <v>213</v>
       </c>
       <c r="H67" s="0" t="n">
@@ -4965,7 +4956,7 @@
       <c r="D68" s="1" t="n">
         <v>44632</v>
       </c>
-      <c r="E68" s="2" t="n">
+      <c r="E68" s="0" t="n">
         <f aca="false">D68-C68+1</f>
         <v>7</v>
       </c>
@@ -4973,7 +4964,7 @@
         <f aca="false">G67+1</f>
         <v>214</v>
       </c>
-      <c r="G68" s="2" t="n">
+      <c r="G68" s="0" t="n">
         <v>216</v>
       </c>
       <c r="H68" s="0" t="n">
@@ -5000,7 +4991,7 @@
       <c r="D69" s="1" t="n">
         <v>44639</v>
       </c>
-      <c r="E69" s="2" t="n">
+      <c r="E69" s="0" t="n">
         <f aca="false">D69-C69+1</f>
         <v>7</v>
       </c>
@@ -5008,7 +4999,7 @@
         <f aca="false">G68+1</f>
         <v>217</v>
       </c>
-      <c r="G69" s="2" t="n">
+      <c r="G69" s="0" t="n">
         <v>219</v>
       </c>
       <c r="H69" s="0" t="n">
@@ -5034,7 +5025,7 @@
       <c r="D70" s="1" t="n">
         <v>44715</v>
       </c>
-      <c r="E70" s="2" t="n">
+      <c r="E70" s="0" t="n">
         <f aca="false">D70-C70+1</f>
         <v>7</v>
       </c>
@@ -5042,7 +5033,7 @@
         <f aca="false">G69+1</f>
         <v>220</v>
       </c>
-      <c r="G70" s="2" t="n">
+      <c r="G70" s="0" t="n">
         <v>222</v>
       </c>
       <c r="H70" s="0" t="n">
@@ -5069,7 +5060,7 @@
       <c r="D71" s="1" t="n">
         <v>44722</v>
       </c>
-      <c r="E71" s="2" t="n">
+      <c r="E71" s="0" t="n">
         <f aca="false">D71-C71+1</f>
         <v>7</v>
       </c>
@@ -5077,7 +5068,7 @@
         <f aca="false">G70+1</f>
         <v>223</v>
       </c>
-      <c r="G71" s="2" t="n">
+      <c r="G71" s="0" t="n">
         <v>227</v>
       </c>
       <c r="H71" s="0" t="n">
@@ -5104,7 +5095,7 @@
       <c r="D72" s="1" t="n">
         <v>44728</v>
       </c>
-      <c r="E72" s="2" t="n">
+      <c r="E72" s="0" t="n">
         <f aca="false">D72-C72+1</f>
         <v>6</v>
       </c>
@@ -5112,7 +5103,7 @@
         <f aca="false">G71+1</f>
         <v>228</v>
       </c>
-      <c r="G72" s="2" t="n">
+      <c r="G72" s="0" t="n">
         <v>230</v>
       </c>
       <c r="H72" s="0" t="n">
@@ -5139,7 +5130,7 @@
       <c r="D73" s="1" t="n">
         <v>44735</v>
       </c>
-      <c r="E73" s="2" t="n">
+      <c r="E73" s="0" t="n">
         <f aca="false">D73-C73+1</f>
         <v>7</v>
       </c>
@@ -5147,7 +5138,7 @@
         <f aca="false">G72+1</f>
         <v>231</v>
       </c>
-      <c r="G73" s="2" t="n">
+      <c r="G73" s="0" t="n">
         <v>234</v>
       </c>
       <c r="H73" s="0" t="n">
@@ -5174,7 +5165,7 @@
       <c r="D74" s="1" t="n">
         <v>44740</v>
       </c>
-      <c r="E74" s="2" t="n">
+      <c r="E74" s="0" t="n">
         <f aca="false">D74-C74+1</f>
         <v>5</v>
       </c>
@@ -5182,7 +5173,7 @@
         <f aca="false">G73+1</f>
         <v>235</v>
       </c>
-      <c r="G74" s="2" t="n">
+      <c r="G74" s="0" t="n">
         <v>237</v>
       </c>
       <c r="H74" s="0" t="n">
@@ -5209,7 +5200,7 @@
       <c r="D75" s="1" t="n">
         <v>44748</v>
       </c>
-      <c r="E75" s="2" t="n">
+      <c r="E75" s="0" t="n">
         <f aca="false">D75-C75+1</f>
         <v>8</v>
       </c>
@@ -5217,7 +5208,7 @@
         <f aca="false">G74+1</f>
         <v>238</v>
       </c>
-      <c r="G75" s="2" t="n">
+      <c r="G75" s="0" t="n">
         <v>245</v>
       </c>
       <c r="H75" s="0" t="n">
@@ -5244,7 +5235,7 @@
       <c r="D76" s="1" t="n">
         <v>44756</v>
       </c>
-      <c r="E76" s="2" t="n">
+      <c r="E76" s="0" t="n">
         <f aca="false">D76-C76+1</f>
         <v>8</v>
       </c>
@@ -5252,7 +5243,7 @@
         <f aca="false">G75+1</f>
         <v>246</v>
       </c>
-      <c r="G76" s="2" t="n">
+      <c r="G76" s="0" t="n">
         <v>252</v>
       </c>
       <c r="H76" s="0" t="n">
@@ -5279,7 +5270,7 @@
       <c r="D77" s="1" t="n">
         <v>44763</v>
       </c>
-      <c r="E77" s="2" t="n">
+      <c r="E77" s="0" t="n">
         <f aca="false">D77-C77+1</f>
         <v>7</v>
       </c>
@@ -5287,7 +5278,7 @@
         <f aca="false">G76+1</f>
         <v>253</v>
       </c>
-      <c r="G77" s="2" t="n">
+      <c r="G77" s="0" t="n">
         <v>255</v>
       </c>
       <c r="H77" s="0" t="n">
@@ -5314,7 +5305,7 @@
       <c r="D78" s="1" t="n">
         <v>44771</v>
       </c>
-      <c r="E78" s="2" t="n">
+      <c r="E78" s="0" t="n">
         <f aca="false">D78-C78+1</f>
         <v>8</v>
       </c>
@@ -5322,7 +5313,7 @@
         <f aca="false">G77+1</f>
         <v>256</v>
       </c>
-      <c r="G78" s="2" t="n">
+      <c r="G78" s="0" t="n">
         <v>261</v>
       </c>
       <c r="H78" s="0" t="n">
@@ -5349,7 +5340,7 @@
       <c r="D79" s="1" t="n">
         <v>44778</v>
       </c>
-      <c r="E79" s="2" t="n">
+      <c r="E79" s="0" t="n">
         <f aca="false">D79-C79+1</f>
         <v>7</v>
       </c>
@@ -5357,7 +5348,7 @@
         <f aca="false">G78+1</f>
         <v>262</v>
       </c>
-      <c r="G79" s="2" t="n">
+      <c r="G79" s="0" t="n">
         <v>264</v>
       </c>
       <c r="H79" s="0" t="n">
@@ -5369,10 +5360,72 @@
         <v>2.33333333333333</v>
       </c>
     </row>
+    <row r="80" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A80" s="0" t="n">
+        <v>701</v>
+      </c>
+      <c r="B80" s="0" t="str">
+        <f aca="false">"卷"&amp;ROW(B79)</f>
+        <v>卷79</v>
+      </c>
+      <c r="C80" s="1" t="n">
+        <v>44808</v>
+      </c>
+      <c r="D80" s="1" t="n">
+        <v>44817</v>
+      </c>
+      <c r="E80" s="0" t="n">
+        <f aca="false">D80-C80+1</f>
+        <v>10</v>
+      </c>
+      <c r="F80" s="0" t="n">
+        <f aca="false">G79+1</f>
+        <v>265</v>
+      </c>
+      <c r="G80" s="0" t="n">
+        <v>272</v>
+      </c>
+      <c r="H80" s="0" t="n">
+        <f aca="false">IF(F80*G80&lt;0,ABS(F80)+ABS(G80),G80-F80+1)</f>
+        <v>8</v>
+      </c>
+      <c r="I80" s="0" t="n">
+        <f aca="false">E80/H80</f>
+        <v>1.25</v>
+      </c>
+    </row>
+    <row r="81" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A81" s="0" t="n">
+        <v>702</v>
+      </c>
+      <c r="B81" s="0" t="str">
+        <f aca="false">"卷"&amp;ROW(B80)</f>
+        <v>卷80</v>
+      </c>
+      <c r="C81" s="1" t="n">
+        <v>44820</v>
+      </c>
+      <c r="E81" s="0" t="n">
+        <f aca="false">D81-C81+1</f>
+        <v>-44819</v>
+      </c>
+      <c r="F81" s="0" t="n">
+        <f aca="false">G80+1</f>
+        <v>273</v>
+      </c>
+      <c r="H81" s="0" t="n">
+        <f aca="false">IF(F81*G81&lt;0,ABS(F81)+ABS(G81),G81-F81+1)</f>
+        <v>-272</v>
+      </c>
+      <c r="I81" s="0" t="n">
+        <f aca="false">E81/H81</f>
+        <v>164.775735294118</v>
+      </c>
+    </row>
   </sheetData>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.511811023622047" footer="0.511811023622047"/>
-  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.511805555555555" footer="0.511805555555555"/>
+  <pageSetup paperSize="9" scale="100" firstPageNumber="0" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" useFirstPageNumber="false" horizontalDpi="300" verticalDpi="300" copies="1"/>
   <headerFooter differentFirst="false" differentOddEven="false">
     <oddHeader/>
     <oddFooter/>
@@ -5391,35 +5444,35 @@
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="0" width="33.38"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="0" width="22.12"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="10" width="9"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="7" width="9"/>
   </cols>
   <sheetData>
-    <row r="1" s="7" customFormat="true" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1" s="7" t="s">
+    <row r="1" s="3" customFormat="true" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A1" s="3" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="7" t="s">
+      <c r="B1" s="3" t="s">
         <v>25</v>
       </c>
-      <c r="C1" s="3" t="s">
+      <c r="C1" s="2" t="s">
         <v>26</v>
       </c>
-      <c r="D1" s="7" t="s">
+      <c r="D1" s="3" t="s">
         <v>27</v>
       </c>
-      <c r="E1" s="7" t="s">
+      <c r="E1" s="3" t="s">
         <v>28</v>
       </c>
-      <c r="F1" s="9" t="s">
+      <c r="F1" s="6" t="s">
         <v>29</v>
       </c>
-      <c r="G1" s="9" t="s">
+      <c r="G1" s="6" t="s">
         <v>30</v>
       </c>
-      <c r="H1" s="11" t="s">
+      <c r="H1" s="8" t="s">
         <v>31</v>
       </c>
-      <c r="I1" s="8" t="s">
+      <c r="I1" s="5" t="s">
         <v>32</v>
       </c>
     </row>
@@ -5445,7 +5498,7 @@
       <c r="F2" s="0" t="s">
         <v>34</v>
       </c>
-      <c r="H2" s="10" t="s">
+      <c r="H2" s="7" t="s">
         <v>35</v>
       </c>
       <c r="I2" s="0" t="str">
@@ -5478,7 +5531,7 @@
       <c r="G3" s="0" t="s">
         <v>38</v>
       </c>
-      <c r="H3" s="10" t="s">
+      <c r="H3" s="7" t="s">
         <v>39</v>
       </c>
       <c r="I3" s="0" t="str">
@@ -5508,7 +5561,7 @@
       <c r="G4" s="0" t="s">
         <v>41</v>
       </c>
-      <c r="H4" s="10" t="s">
+      <c r="H4" s="7" t="s">
         <v>42</v>
       </c>
       <c r="I4" s="0" t="str">
@@ -5538,7 +5591,7 @@
       <c r="G5" s="0" t="s">
         <v>44</v>
       </c>
-      <c r="H5" s="10" t="s">
+      <c r="H5" s="7" t="s">
         <v>45</v>
       </c>
       <c r="I5" s="0" t="str">
@@ -5568,7 +5621,7 @@
       <c r="F6" s="0" t="s">
         <v>47</v>
       </c>
-      <c r="H6" s="10" t="s">
+      <c r="H6" s="7" t="s">
         <v>48</v>
       </c>
       <c r="I6" s="0" t="str">
@@ -5598,7 +5651,7 @@
       <c r="G7" s="0" t="s">
         <v>50</v>
       </c>
-      <c r="H7" s="10" t="s">
+      <c r="H7" s="7" t="s">
         <v>51</v>
       </c>
       <c r="I7" s="0" t="str">
@@ -5628,7 +5681,7 @@
       <c r="F8" s="0" t="s">
         <v>53</v>
       </c>
-      <c r="H8" s="10" t="s">
+      <c r="H8" s="7" t="s">
         <v>54</v>
       </c>
       <c r="I8" s="0" t="str">
@@ -5655,7 +5708,7 @@
         <f aca="false">VLOOKUP($A9,統計!$A:$G,7,)</f>
         <v>-207</v>
       </c>
-      <c r="H9" s="10" t="s">
+      <c r="H9" s="7" t="s">
         <v>56</v>
       </c>
       <c r="I9" s="0" t="str">
@@ -5688,7 +5741,7 @@
       <c r="G10" s="0" t="s">
         <v>59</v>
       </c>
-      <c r="H10" s="10" t="s">
+      <c r="H10" s="7" t="s">
         <v>60</v>
       </c>
       <c r="I10" s="0" t="str">
@@ -5718,7 +5771,7 @@
       <c r="G11" s="0" t="s">
         <v>62</v>
       </c>
-      <c r="H11" s="10" t="s">
+      <c r="H11" s="7" t="s">
         <v>63</v>
       </c>
       <c r="I11" s="0" t="str">
@@ -5748,7 +5801,7 @@
       <c r="G12" s="0" t="s">
         <v>65</v>
       </c>
-      <c r="H12" s="10" t="s">
+      <c r="H12" s="7" t="s">
         <v>66</v>
       </c>
       <c r="I12" s="0" t="str">
@@ -5775,7 +5828,7 @@
         <f aca="false">VLOOKUP($A13,統計!$A:$G,7,)</f>
         <v>-188</v>
       </c>
-      <c r="H13" s="10" t="s">
+      <c r="H13" s="7" t="s">
         <v>68</v>
       </c>
       <c r="I13" s="0" t="str">
@@ -5808,7 +5861,7 @@
       <c r="G14" s="0" t="s">
         <v>71</v>
       </c>
-      <c r="H14" s="10" t="s">
+      <c r="H14" s="7" t="s">
         <v>72</v>
       </c>
       <c r="I14" s="0" t="str">
@@ -5838,7 +5891,7 @@
       <c r="G15" s="0" t="s">
         <v>74</v>
       </c>
-      <c r="H15" s="10" t="s">
+      <c r="H15" s="7" t="s">
         <v>75</v>
       </c>
       <c r="I15" s="0" t="str">
@@ -5868,7 +5921,7 @@
       <c r="G16" s="0" t="s">
         <v>77</v>
       </c>
-      <c r="H16" s="10" t="s">
+      <c r="H16" s="7" t="s">
         <v>78</v>
       </c>
       <c r="I16" s="0" t="str">
@@ -5901,7 +5954,7 @@
       <c r="G17" s="0" t="s">
         <v>81</v>
       </c>
-      <c r="H17" s="10" t="s">
+      <c r="H17" s="7" t="s">
         <v>82</v>
       </c>
       <c r="I17" s="0" t="str">
@@ -5934,7 +5987,7 @@
       <c r="G18" s="0" t="s">
         <v>85</v>
       </c>
-      <c r="H18" s="10" t="s">
+      <c r="H18" s="7" t="s">
         <v>86</v>
       </c>
       <c r="I18" s="0" t="str">
@@ -5964,7 +6017,7 @@
       <c r="G19" s="0" t="s">
         <v>88</v>
       </c>
-      <c r="H19" s="10" t="s">
+      <c r="H19" s="7" t="s">
         <v>89</v>
       </c>
       <c r="I19" s="0" t="str">
@@ -5997,7 +6050,7 @@
       <c r="G20" s="0" t="s">
         <v>92</v>
       </c>
-      <c r="H20" s="10" t="s">
+      <c r="H20" s="7" t="s">
         <v>93</v>
       </c>
       <c r="I20" s="0" t="str">
@@ -6027,7 +6080,7 @@
       <c r="G21" s="0" t="s">
         <v>95</v>
       </c>
-      <c r="H21" s="10" t="s">
+      <c r="H21" s="7" t="s">
         <v>96</v>
       </c>
       <c r="I21" s="0" t="str">
@@ -6054,7 +6107,7 @@
         <f aca="false">VLOOKUP($A22,統計!$A:$G,7,)</f>
         <v>-99</v>
       </c>
-      <c r="H22" s="10" t="s">
+      <c r="H22" s="7" t="s">
         <v>98</v>
       </c>
       <c r="I22" s="0" t="str">
@@ -6084,7 +6137,7 @@
       <c r="G23" s="0" t="s">
         <v>100</v>
       </c>
-      <c r="H23" s="10" t="s">
+      <c r="H23" s="7" t="s">
         <v>101</v>
       </c>
       <c r="I23" s="0" t="str">
@@ -6114,7 +6167,7 @@
       <c r="F24" s="0" t="s">
         <v>103</v>
       </c>
-      <c r="H24" s="10" t="s">
+      <c r="H24" s="7" t="s">
         <v>104</v>
       </c>
       <c r="I24" s="0" t="str">
@@ -6147,7 +6200,7 @@
       <c r="G25" s="0" t="s">
         <v>107</v>
       </c>
-      <c r="H25" s="10" t="s">
+      <c r="H25" s="7" t="s">
         <v>108</v>
       </c>
       <c r="I25" s="0" t="str">
@@ -6177,7 +6230,7 @@
       <c r="G26" s="0" t="s">
         <v>110</v>
       </c>
-      <c r="H26" s="10" t="s">
+      <c r="H26" s="7" t="s">
         <v>111</v>
       </c>
       <c r="I26" s="0" t="str">
@@ -6204,7 +6257,7 @@
         <f aca="false">VLOOKUP($A27,統計!$A:$G,7,)</f>
         <v>-59</v>
       </c>
-      <c r="H27" s="10" t="s">
+      <c r="H27" s="7" t="s">
         <v>113</v>
       </c>
       <c r="I27" s="0" t="str">
@@ -6237,7 +6290,7 @@
       <c r="G28" s="0" t="s">
         <v>116</v>
       </c>
-      <c r="H28" s="10" t="s">
+      <c r="H28" s="7" t="s">
         <v>117</v>
       </c>
       <c r="I28" s="0" t="str">
@@ -6267,7 +6320,7 @@
       <c r="G29" s="0" t="s">
         <v>119</v>
       </c>
-      <c r="H29" s="10" t="s">
+      <c r="H29" s="7" t="s">
         <v>120</v>
       </c>
       <c r="I29" s="0" t="str">
@@ -6297,7 +6350,7 @@
       <c r="F30" s="0" t="s">
         <v>122</v>
       </c>
-      <c r="H30" s="10" t="s">
+      <c r="H30" s="7" t="s">
         <v>123</v>
       </c>
       <c r="I30" s="0" t="str">
@@ -6327,7 +6380,7 @@
       <c r="F31" s="0" t="s">
         <v>125</v>
       </c>
-      <c r="H31" s="10" t="s">
+      <c r="H31" s="7" t="s">
         <v>126</v>
       </c>
       <c r="I31" s="0" t="str">
@@ -6360,7 +6413,7 @@
       <c r="G32" s="0" t="s">
         <v>129</v>
       </c>
-      <c r="H32" s="10" t="s">
+      <c r="H32" s="7" t="s">
         <v>130</v>
       </c>
       <c r="I32" s="0" t="str">
@@ -6390,7 +6443,7 @@
       <c r="F33" s="0" t="s">
         <v>132</v>
       </c>
-      <c r="H33" s="10" t="s">
+      <c r="H33" s="7" t="s">
         <v>133</v>
       </c>
       <c r="I33" s="0" t="str">
@@ -6420,7 +6473,7 @@
       <c r="F34" s="0" t="s">
         <v>135</v>
       </c>
-      <c r="H34" s="10" t="s">
+      <c r="H34" s="7" t="s">
         <v>136</v>
       </c>
       <c r="I34" s="0" t="str">
@@ -6450,7 +6503,7 @@
       <c r="G35" s="0" t="s">
         <v>138</v>
       </c>
-      <c r="H35" s="10" t="s">
+      <c r="H35" s="7" t="s">
         <v>139</v>
       </c>
       <c r="I35" s="0" t="str">
@@ -6483,7 +6536,7 @@
       <c r="G36" s="0" t="s">
         <v>142</v>
       </c>
-      <c r="H36" s="10" t="s">
+      <c r="H36" s="7" t="s">
         <v>143</v>
       </c>
       <c r="I36" s="0" t="str">
@@ -6513,7 +6566,7 @@
       <c r="G37" s="0" t="s">
         <v>145</v>
       </c>
-      <c r="H37" s="10" t="s">
+      <c r="H37" s="7" t="s">
         <v>146</v>
       </c>
       <c r="I37" s="0" t="str">
@@ -6543,7 +6596,7 @@
       <c r="G38" s="0" t="s">
         <v>148</v>
       </c>
-      <c r="H38" s="10" t="s">
+      <c r="H38" s="7" t="s">
         <v>149</v>
       </c>
       <c r="I38" s="0" t="str">
@@ -6573,7 +6626,7 @@
       <c r="G39" s="0" t="s">
         <v>151</v>
       </c>
-      <c r="H39" s="10" t="s">
+      <c r="H39" s="7" t="s">
         <v>152</v>
       </c>
       <c r="I39" s="0" t="str">
@@ -6603,7 +6656,7 @@
       <c r="G40" s="0" t="s">
         <v>154</v>
       </c>
-      <c r="H40" s="10" t="s">
+      <c r="H40" s="7" t="s">
         <v>155</v>
       </c>
       <c r="I40" s="0" t="str">
@@ -6630,7 +6683,7 @@
         <f aca="false">VLOOKUP($A41,統計!$A:$G,7,)</f>
         <v>26</v>
       </c>
-      <c r="H41" s="10" t="s">
+      <c r="H41" s="7" t="s">
         <v>157</v>
       </c>
       <c r="I41" s="0" t="str">
@@ -6660,7 +6713,7 @@
       <c r="F42" s="0" t="s">
         <v>159</v>
       </c>
-      <c r="H42" s="10" t="s">
+      <c r="H42" s="7" t="s">
         <v>160</v>
       </c>
       <c r="I42" s="0" t="str">
@@ -6690,7 +6743,7 @@
       <c r="F43" s="0" t="s">
         <v>162</v>
       </c>
-      <c r="H43" s="10" t="s">
+      <c r="H43" s="7" t="s">
         <v>163</v>
       </c>
       <c r="I43" s="0" t="str">
@@ -6720,7 +6773,7 @@
       <c r="G44" s="0" t="s">
         <v>165</v>
       </c>
-      <c r="H44" s="10" t="s">
+      <c r="H44" s="7" t="s">
         <v>166</v>
       </c>
       <c r="I44" s="0" t="str">
@@ -6750,7 +6803,7 @@
       <c r="G45" s="0" t="s">
         <v>168</v>
       </c>
-      <c r="H45" s="10" t="s">
+      <c r="H45" s="7" t="s">
         <v>169</v>
       </c>
       <c r="I45" s="0" t="str">
@@ -6783,7 +6836,7 @@
       <c r="G46" s="0" t="s">
         <v>172</v>
       </c>
-      <c r="H46" s="10" t="s">
+      <c r="H46" s="7" t="s">
         <v>173</v>
       </c>
       <c r="I46" s="0" t="str">
@@ -6813,7 +6866,7 @@
       <c r="F47" s="0" t="s">
         <v>175</v>
       </c>
-      <c r="H47" s="10" t="s">
+      <c r="H47" s="7" t="s">
         <v>176</v>
       </c>
       <c r="I47" s="0" t="str">
@@ -6846,7 +6899,7 @@
       <c r="G48" s="0" t="s">
         <v>179</v>
       </c>
-      <c r="H48" s="10" t="s">
+      <c r="H48" s="7" t="s">
         <v>180</v>
       </c>
       <c r="I48" s="0" t="str">
@@ -6876,7 +6929,7 @@
       <c r="G49" s="0" t="s">
         <v>182</v>
       </c>
-      <c r="H49" s="10" t="s">
+      <c r="H49" s="7" t="s">
         <v>183</v>
       </c>
       <c r="I49" s="0" t="str">
@@ -6903,7 +6956,7 @@
         <f aca="false">VLOOKUP($A50,統計!$A:$G,7,)</f>
         <v>115</v>
       </c>
-      <c r="H50" s="12" t="s">
+      <c r="H50" s="9" t="s">
         <v>185</v>
       </c>
       <c r="I50" s="0" t="str">
@@ -6936,7 +6989,7 @@
       <c r="G51" s="0" t="s">
         <v>188</v>
       </c>
-      <c r="H51" s="12" t="s">
+      <c r="H51" s="9" t="s">
         <v>189</v>
       </c>
       <c r="I51" s="0" t="str">
@@ -6966,7 +7019,7 @@
       <c r="G52" s="0" t="s">
         <v>191</v>
       </c>
-      <c r="H52" s="10" t="s">
+      <c r="H52" s="7" t="s">
         <v>192</v>
       </c>
       <c r="I52" s="0" t="str">
@@ -6993,7 +7046,7 @@
         <f aca="false">VLOOKUP($A53,統計!$A:$G,7,)</f>
         <v>145</v>
       </c>
-      <c r="H53" s="10" t="s">
+      <c r="H53" s="7" t="s">
         <v>194</v>
       </c>
       <c r="I53" s="0" t="str">
@@ -7023,7 +7076,7 @@
       <c r="F54" s="0" t="s">
         <v>196</v>
       </c>
-      <c r="H54" s="10" t="s">
+      <c r="H54" s="7" t="s">
         <v>197</v>
       </c>
       <c r="I54" s="0" t="str">
@@ -7056,7 +7109,7 @@
       <c r="G55" s="0" t="s">
         <v>200</v>
       </c>
-      <c r="H55" s="10" t="s">
+      <c r="H55" s="7" t="s">
         <v>201</v>
       </c>
       <c r="I55" s="0" t="str">
@@ -7083,7 +7136,7 @@
         <f aca="false">VLOOKUP($A56,統計!$A:$G,7,)</f>
         <v>166</v>
       </c>
-      <c r="H56" s="10" t="s">
+      <c r="H56" s="7" t="s">
         <v>203</v>
       </c>
       <c r="I56" s="0" t="str">
@@ -7113,7 +7166,7 @@
       <c r="F57" s="0" t="s">
         <v>205</v>
       </c>
-      <c r="H57" s="10" t="s">
+      <c r="H57" s="7" t="s">
         <v>206</v>
       </c>
       <c r="I57" s="0" t="str">
@@ -7140,7 +7193,7 @@
         <f aca="false">VLOOKUP($A58,統計!$A:$G,7,)</f>
         <v>180</v>
       </c>
-      <c r="H58" s="10" t="s">
+      <c r="H58" s="7" t="s">
         <v>208</v>
       </c>
       <c r="I58" s="0" t="str">
@@ -7170,7 +7223,7 @@
       <c r="F59" s="0" t="s">
         <v>210</v>
       </c>
-      <c r="H59" s="10" t="s">
+      <c r="H59" s="7" t="s">
         <v>211</v>
       </c>
       <c r="I59" s="0" t="str">
@@ -7200,7 +7253,7 @@
       <c r="G60" s="0" t="s">
         <v>213</v>
       </c>
-      <c r="H60" s="10" t="s">
+      <c r="H60" s="7" t="s">
         <v>214</v>
       </c>
       <c r="I60" s="0" t="str">
@@ -7230,7 +7283,7 @@
       <c r="F61" s="0" t="s">
         <v>216</v>
       </c>
-      <c r="H61" s="10" t="s">
+      <c r="H61" s="7" t="s">
         <v>217</v>
       </c>
       <c r="I61" s="0" t="str">
@@ -7260,7 +7313,7 @@
       <c r="F62" s="0" t="s">
         <v>219</v>
       </c>
-      <c r="H62" s="10" t="s">
+      <c r="H62" s="7" t="s">
         <v>220</v>
       </c>
       <c r="I62" s="0" t="str">
@@ -7293,7 +7346,7 @@
       <c r="G63" s="0" t="s">
         <v>223</v>
       </c>
-      <c r="H63" s="13" t="s">
+      <c r="H63" s="10" t="s">
         <v>224</v>
       </c>
       <c r="I63" s="0" t="str">
@@ -7320,7 +7373,7 @@
         <f aca="false">VLOOKUP($A64,統計!$A:$G,7,)</f>
         <v>200</v>
       </c>
-      <c r="H64" s="13" t="s">
+      <c r="H64" s="10" t="s">
         <v>226</v>
       </c>
       <c r="I64" s="0" t="str">
@@ -7350,7 +7403,7 @@
       <c r="F65" s="0" t="s">
         <v>228</v>
       </c>
-      <c r="H65" s="10" t="s">
+      <c r="H65" s="7" t="s">
         <v>229</v>
       </c>
       <c r="I65" s="0" t="str">
@@ -7377,7 +7430,7 @@
         <f aca="false">VLOOKUP($A66,統計!$A:$G,7,)</f>
         <v>208</v>
       </c>
-      <c r="H66" s="10" t="s">
+      <c r="H66" s="7" t="s">
         <v>231</v>
       </c>
       <c r="I66" s="0" t="str">
@@ -7404,7 +7457,7 @@
         <f aca="false">VLOOKUP($A67,統計!$A:$G,7,)</f>
         <v>213</v>
       </c>
-      <c r="H67" s="10" t="s">
+      <c r="H67" s="7" t="s">
         <v>233</v>
       </c>
       <c r="I67" s="0" t="str">
@@ -7434,7 +7487,7 @@
       <c r="G68" s="0" t="s">
         <v>235</v>
       </c>
-      <c r="H68" s="10" t="s">
+      <c r="H68" s="7" t="s">
         <v>236</v>
       </c>
       <c r="I68" s="0" t="str">
@@ -7461,7 +7514,7 @@
         <f aca="false">VLOOKUP($A69,統計!$A:$G,7,)</f>
         <v>219</v>
       </c>
-      <c r="H69" s="10" t="s">
+      <c r="H69" s="7" t="s">
         <v>238</v>
       </c>
       <c r="I69" s="0" t="str">
@@ -7488,7 +7541,7 @@
         <f aca="false">VLOOKUP($A70,統計!$A:$G,7,)</f>
         <v>222</v>
       </c>
-      <c r="H70" s="10" t="s">
+      <c r="H70" s="7" t="s">
         <v>240</v>
       </c>
       <c r="I70" s="0" t="str">
@@ -7518,7 +7571,7 @@
       <c r="G71" s="0" t="s">
         <v>242</v>
       </c>
-      <c r="H71" s="10" t="s">
+      <c r="H71" s="7" t="s">
         <v>243</v>
       </c>
       <c r="I71" s="0" t="str">
@@ -7545,7 +7598,7 @@
         <f aca="false">VLOOKUP($A72,統計!$A:$G,7,)</f>
         <v>230</v>
       </c>
-      <c r="H72" s="10" t="s">
+      <c r="H72" s="7" t="s">
         <v>245</v>
       </c>
       <c r="I72" s="0" t="str">
@@ -7575,7 +7628,7 @@
       <c r="G73" s="0" t="s">
         <v>247</v>
       </c>
-      <c r="H73" s="10" t="s">
+      <c r="H73" s="7" t="s">
         <v>248</v>
       </c>
       <c r="I73" s="0" t="str">
@@ -7605,7 +7658,7 @@
       <c r="G74" s="0" t="s">
         <v>250</v>
       </c>
-      <c r="H74" s="10" t="s">
+      <c r="H74" s="7" t="s">
         <v>251</v>
       </c>
       <c r="I74" s="0" t="str">
@@ -7635,7 +7688,7 @@
       <c r="F75" s="0" t="s">
         <v>253</v>
       </c>
-      <c r="H75" s="10" t="s">
+      <c r="H75" s="7" t="s">
         <v>254</v>
       </c>
       <c r="I75" s="0" t="str">
@@ -7668,7 +7721,7 @@
       <c r="G76" s="0" t="s">
         <v>257</v>
       </c>
-      <c r="H76" s="10" t="s">
+      <c r="H76" s="7" t="s">
         <v>258</v>
       </c>
       <c r="I76" s="0" t="str">
@@ -7698,7 +7751,7 @@
       <c r="F77" s="0" t="s">
         <v>260</v>
       </c>
-      <c r="H77" s="10" t="s">
+      <c r="H77" s="7" t="s">
         <v>261</v>
       </c>
       <c r="I77" s="0" t="str">
@@ -7728,7 +7781,7 @@
       <c r="F78" s="0" t="s">
         <v>263</v>
       </c>
-      <c r="H78" s="10" t="s">
+      <c r="H78" s="7" t="s">
         <v>264</v>
       </c>
       <c r="I78" s="0" t="str">
@@ -7766,52 +7819,55 @@
         <v>610|[卷78](5_筆記/资治通鉴78.html)|魏紀十|262|264|陳留阮氏世系、三卞皇后圖||曹奐3年至5年</v>
       </c>
     </row>
-    <row r="80" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="80" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A80" s="0" t="n">
         <v>701</v>
       </c>
-      <c r="B80" s="0" t="e">
+      <c r="B80" s="0" t="str">
         <f aca="false">VLOOKUP($A80,統計!$A:$G,2,)</f>
-        <v>#N/A</v>
+        <v>卷79</v>
       </c>
       <c r="C80" s="0" t="s">
         <v>268</v>
       </c>
-      <c r="D80" s="0" t="e">
+      <c r="D80" s="0" t="n">
         <f aca="false">VLOOKUP($A80,統計!$A:$G,6,)</f>
-        <v>#N/A</v>
-      </c>
-      <c r="E80" s="0" t="e">
+        <v>265</v>
+      </c>
+      <c r="E80" s="0" t="n">
         <f aca="false">VLOOKUP($A80,統計!$A:$G,7,)</f>
-        <v>#N/A</v>
-      </c>
-      <c r="I80" s="0" t="e">
+        <v>272</v>
+      </c>
+      <c r="H80" s="0" t="s">
+        <v>269</v>
+      </c>
+      <c r="I80" s="0" t="str">
         <f aca="false">A80&amp;"|"&amp;"["&amp;B80&amp;"](5_筆記/资治通鉴"&amp;SUBSTITUTE(B80,"卷","")&amp;".html)|"&amp;C80&amp;"|"&amp;D80&amp;"|"&amp;E80&amp;"|"&amp;F80&amp;"|"&amp;G80&amp;"|"&amp;H80</f>
-        <v>#N/A</v>
+        <v>701|[卷79](5_筆記/资治通鉴79.html)|晉紀一|265|272|||曹奐6年至7年、司馬炎至7年</v>
       </c>
     </row>
     <row r="81" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A81" s="0" t="n">
         <v>702</v>
       </c>
-      <c r="B81" s="0" t="e">
+      <c r="B81" s="0" t="str">
         <f aca="false">VLOOKUP($A81,統計!$A:$G,2,)</f>
-        <v>#N/A</v>
+        <v>卷80</v>
       </c>
       <c r="C81" s="0" t="s">
-        <v>269</v>
-      </c>
-      <c r="D81" s="0" t="e">
+        <v>270</v>
+      </c>
+      <c r="D81" s="0" t="n">
         <f aca="false">VLOOKUP($A81,統計!$A:$G,6,)</f>
-        <v>#N/A</v>
-      </c>
-      <c r="E81" s="0" t="e">
+        <v>273</v>
+      </c>
+      <c r="E81" s="0" t="n">
         <f aca="false">VLOOKUP($A81,統計!$A:$G,7,)</f>
-        <v>#N/A</v>
-      </c>
-      <c r="I81" s="0" t="e">
+        <v>0</v>
+      </c>
+      <c r="I81" s="0" t="str">
         <f aca="false">A81&amp;"|"&amp;"["&amp;B81&amp;"](5_筆記/资治通鉴"&amp;SUBSTITUTE(B81,"卷","")&amp;".html)|"&amp;C81&amp;"|"&amp;D81&amp;"|"&amp;E81&amp;"|"&amp;F81&amp;"|"&amp;G81&amp;"|"&amp;H81</f>
-        <v>#N/A</v>
+        <v>702|[卷80](5_筆記/资治通鉴80.html)|晉紀二|273|0|||</v>
       </c>
     </row>
     <row r="82" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -7823,7 +7879,7 @@
         <v>#N/A</v>
       </c>
       <c r="C82" s="0" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="D82" s="0" t="e">
         <f aca="false">VLOOKUP($A82,統計!$A:$G,6,)</f>
@@ -7847,7 +7903,7 @@
         <v>#N/A</v>
       </c>
       <c r="C83" s="0" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="D83" s="0" t="e">
         <f aca="false">VLOOKUP($A83,統計!$A:$G,6,)</f>
@@ -7871,7 +7927,7 @@
         <v>#N/A</v>
       </c>
       <c r="C84" s="0" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="D84" s="0" t="e">
         <f aca="false">VLOOKUP($A84,統計!$A:$G,6,)</f>
@@ -7895,7 +7951,7 @@
         <v>#N/A</v>
       </c>
       <c r="C85" s="0" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="D85" s="0" t="e">
         <f aca="false">VLOOKUP($A85,統計!$A:$G,6,)</f>
@@ -7919,7 +7975,7 @@
         <v>#N/A</v>
       </c>
       <c r="C86" s="0" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="D86" s="0" t="e">
         <f aca="false">VLOOKUP($A86,統計!$A:$G,6,)</f>
@@ -7943,7 +7999,7 @@
         <v>#N/A</v>
       </c>
       <c r="C87" s="0" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="D87" s="0" t="e">
         <f aca="false">VLOOKUP($A87,統計!$A:$G,6,)</f>
@@ -7967,7 +8023,7 @@
         <v>#N/A</v>
       </c>
       <c r="C88" s="0" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="D88" s="0" t="e">
         <f aca="false">VLOOKUP($A88,統計!$A:$G,6,)</f>
@@ -7991,7 +8047,7 @@
         <v>#N/A</v>
       </c>
       <c r="C89" s="0" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="D89" s="0" t="e">
         <f aca="false">VLOOKUP($A89,統計!$A:$G,6,)</f>
@@ -8015,7 +8071,7 @@
         <v>#N/A</v>
       </c>
       <c r="C90" s="0" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="D90" s="0" t="e">
         <f aca="false">VLOOKUP($A90,統計!$A:$G,6,)</f>
@@ -8039,7 +8095,7 @@
         <v>#N/A</v>
       </c>
       <c r="C91" s="0" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="D91" s="0" t="e">
         <f aca="false">VLOOKUP($A91,統計!$A:$G,6,)</f>
@@ -8063,7 +8119,7 @@
         <v>#N/A</v>
       </c>
       <c r="C92" s="0" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="D92" s="0" t="e">
         <f aca="false">VLOOKUP($A92,統計!$A:$G,6,)</f>
@@ -8087,7 +8143,7 @@
         <v>#N/A</v>
       </c>
       <c r="C93" s="0" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="D93" s="0" t="e">
         <f aca="false">VLOOKUP($A93,統計!$A:$G,6,)</f>
@@ -8111,7 +8167,7 @@
         <v>#N/A</v>
       </c>
       <c r="C94" s="0" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="D94" s="0" t="e">
         <f aca="false">VLOOKUP($A94,統計!$A:$G,6,)</f>
@@ -8135,7 +8191,7 @@
         <v>#N/A</v>
       </c>
       <c r="C95" s="0" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="D95" s="0" t="e">
         <f aca="false">VLOOKUP($A95,統計!$A:$G,6,)</f>
@@ -8159,7 +8215,7 @@
         <v>#N/A</v>
       </c>
       <c r="C96" s="0" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="D96" s="0" t="e">
         <f aca="false">VLOOKUP($A96,統計!$A:$G,6,)</f>
@@ -8183,7 +8239,7 @@
         <v>#N/A</v>
       </c>
       <c r="C97" s="0" t="s">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="D97" s="0" t="e">
         <f aca="false">VLOOKUP($A97,統計!$A:$G,6,)</f>
@@ -8207,7 +8263,7 @@
         <v>#N/A</v>
       </c>
       <c r="C98" s="0" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="D98" s="0" t="e">
         <f aca="false">VLOOKUP($A98,統計!$A:$G,6,)</f>
@@ -8231,7 +8287,7 @@
         <v>#N/A</v>
       </c>
       <c r="C99" s="0" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="D99" s="0" t="e">
         <f aca="false">VLOOKUP($A99,統計!$A:$G,6,)</f>
@@ -8255,7 +8311,7 @@
         <v>#N/A</v>
       </c>
       <c r="C100" s="0" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="D100" s="0" t="e">
         <f aca="false">VLOOKUP($A100,統計!$A:$G,6,)</f>
@@ -8279,7 +8335,7 @@
         <v>#N/A</v>
       </c>
       <c r="C101" s="0" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="D101" s="0" t="e">
         <f aca="false">VLOOKUP($A101,統計!$A:$G,6,)</f>
@@ -8303,7 +8359,7 @@
         <v>#N/A</v>
       </c>
       <c r="C102" s="0" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="D102" s="0" t="e">
         <f aca="false">VLOOKUP($A102,統計!$A:$G,6,)</f>
@@ -8327,7 +8383,7 @@
         <v>#N/A</v>
       </c>
       <c r="C103" s="0" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="D103" s="0" t="e">
         <f aca="false">VLOOKUP($A103,統計!$A:$G,6,)</f>
@@ -8351,7 +8407,7 @@
         <v>#N/A</v>
       </c>
       <c r="C104" s="0" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="D104" s="0" t="e">
         <f aca="false">VLOOKUP($A104,統計!$A:$G,6,)</f>
@@ -8375,7 +8431,7 @@
         <v>#N/A</v>
       </c>
       <c r="C105" s="0" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="D105" s="0" t="e">
         <f aca="false">VLOOKUP($A105,統計!$A:$G,6,)</f>
@@ -8399,7 +8455,7 @@
         <v>#N/A</v>
       </c>
       <c r="C106" s="0" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="D106" s="0" t="e">
         <f aca="false">VLOOKUP($A106,統計!$A:$G,6,)</f>
@@ -8423,7 +8479,7 @@
         <v>#N/A</v>
       </c>
       <c r="C107" s="0" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="D107" s="0" t="e">
         <f aca="false">VLOOKUP($A107,統計!$A:$G,6,)</f>
@@ -8447,7 +8503,7 @@
         <v>#N/A</v>
       </c>
       <c r="C108" s="0" t="s">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="D108" s="0" t="e">
         <f aca="false">VLOOKUP($A108,統計!$A:$G,6,)</f>
@@ -8471,7 +8527,7 @@
         <v>#N/A</v>
       </c>
       <c r="C109" s="0" t="s">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="D109" s="0" t="e">
         <f aca="false">VLOOKUP($A109,統計!$A:$G,6,)</f>
@@ -8495,7 +8551,7 @@
         <v>#N/A</v>
       </c>
       <c r="C110" s="0" t="s">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="D110" s="0" t="e">
         <f aca="false">VLOOKUP($A110,統計!$A:$G,6,)</f>
@@ -8519,7 +8575,7 @@
         <v>#N/A</v>
       </c>
       <c r="C111" s="0" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="D111" s="0" t="e">
         <f aca="false">VLOOKUP($A111,統計!$A:$G,6,)</f>
@@ -8543,7 +8599,7 @@
         <v>#N/A</v>
       </c>
       <c r="C112" s="0" t="s">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="D112" s="0" t="e">
         <f aca="false">VLOOKUP($A112,統計!$A:$G,6,)</f>
@@ -8567,7 +8623,7 @@
         <v>#N/A</v>
       </c>
       <c r="C113" s="0" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="D113" s="0" t="e">
         <f aca="false">VLOOKUP($A113,統計!$A:$G,6,)</f>
@@ -8591,7 +8647,7 @@
         <v>#N/A</v>
       </c>
       <c r="C114" s="0" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="D114" s="0" t="e">
         <f aca="false">VLOOKUP($A114,統計!$A:$G,6,)</f>
@@ -8615,7 +8671,7 @@
         <v>#N/A</v>
       </c>
       <c r="C115" s="0" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="D115" s="0" t="e">
         <f aca="false">VLOOKUP($A115,統計!$A:$G,6,)</f>
@@ -8639,7 +8695,7 @@
         <v>#N/A</v>
       </c>
       <c r="C116" s="0" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="D116" s="0" t="e">
         <f aca="false">VLOOKUP($A116,統計!$A:$G,6,)</f>
@@ -8663,7 +8719,7 @@
         <v>#N/A</v>
       </c>
       <c r="C117" s="0" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="D117" s="0" t="e">
         <f aca="false">VLOOKUP($A117,統計!$A:$G,6,)</f>
@@ -8687,7 +8743,7 @@
         <v>#N/A</v>
       </c>
       <c r="C118" s="0" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="D118" s="0" t="e">
         <f aca="false">VLOOKUP($A118,統計!$A:$G,6,)</f>
@@ -8711,7 +8767,7 @@
         <v>#N/A</v>
       </c>
       <c r="C119" s="0" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="D119" s="0" t="e">
         <f aca="false">VLOOKUP($A119,統計!$A:$G,6,)</f>
@@ -8735,7 +8791,7 @@
         <v>#N/A</v>
       </c>
       <c r="C120" s="0" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="D120" s="0" t="e">
         <f aca="false">VLOOKUP($A120,統計!$A:$G,6,)</f>
@@ -8759,7 +8815,7 @@
         <v>#N/A</v>
       </c>
       <c r="C121" s="0" t="s">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="D121" s="0" t="e">
         <f aca="false">VLOOKUP($A121,統計!$A:$G,6,)</f>
@@ -8783,7 +8839,7 @@
         <v>#N/A</v>
       </c>
       <c r="C122" s="0" t="s">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="D122" s="0" t="e">
         <f aca="false">VLOOKUP($A122,統計!$A:$G,6,)</f>
@@ -8807,7 +8863,7 @@
         <v>#N/A</v>
       </c>
       <c r="C123" s="0" t="s">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="D123" s="0" t="e">
         <f aca="false">VLOOKUP($A123,統計!$A:$G,6,)</f>
@@ -8831,7 +8887,7 @@
         <v>#N/A</v>
       </c>
       <c r="C124" s="0" t="s">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="D124" s="0" t="e">
         <f aca="false">VLOOKUP($A124,統計!$A:$G,6,)</f>
@@ -8855,7 +8911,7 @@
         <v>#N/A</v>
       </c>
       <c r="C125" s="0" t="s">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="D125" s="0" t="e">
         <f aca="false">VLOOKUP($A125,統計!$A:$G,6,)</f>
@@ -8879,7 +8935,7 @@
         <v>#N/A</v>
       </c>
       <c r="C126" s="0" t="s">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="D126" s="0" t="e">
         <f aca="false">VLOOKUP($A126,統計!$A:$G,6,)</f>
@@ -8903,7 +8959,7 @@
         <v>#N/A</v>
       </c>
       <c r="C127" s="0" t="s">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="D127" s="0" t="e">
         <f aca="false">VLOOKUP($A127,統計!$A:$G,6,)</f>
@@ -8927,7 +8983,7 @@
         <v>#N/A</v>
       </c>
       <c r="C128" s="0" t="s">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="D128" s="0" t="e">
         <f aca="false">VLOOKUP($A128,統計!$A:$G,6,)</f>
@@ -8951,7 +9007,7 @@
         <v>#N/A</v>
       </c>
       <c r="C129" s="0" t="s">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="D129" s="0" t="e">
         <f aca="false">VLOOKUP($A129,統計!$A:$G,6,)</f>
@@ -8975,7 +9031,7 @@
         <v>#N/A</v>
       </c>
       <c r="C130" s="0" t="s">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="D130" s="0" t="e">
         <f aca="false">VLOOKUP($A130,統計!$A:$G,6,)</f>
@@ -8999,7 +9055,7 @@
         <v>#N/A</v>
       </c>
       <c r="C131" s="0" t="s">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="D131" s="0" t="e">
         <f aca="false">VLOOKUP($A131,統計!$A:$G,6,)</f>
@@ -9023,7 +9079,7 @@
         <v>#N/A</v>
       </c>
       <c r="C132" s="0" t="s">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="D132" s="0" t="e">
         <f aca="false">VLOOKUP($A132,統計!$A:$G,6,)</f>
@@ -9047,7 +9103,7 @@
         <v>#N/A</v>
       </c>
       <c r="C133" s="0" t="s">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="D133" s="0" t="e">
         <f aca="false">VLOOKUP($A133,統計!$A:$G,6,)</f>
@@ -9071,7 +9127,7 @@
         <v>#N/A</v>
       </c>
       <c r="C134" s="0" t="s">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="D134" s="0" t="e">
         <f aca="false">VLOOKUP($A134,統計!$A:$G,6,)</f>
@@ -9095,7 +9151,7 @@
         <v>#N/A</v>
       </c>
       <c r="C135" s="0" t="s">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="D135" s="0" t="e">
         <f aca="false">VLOOKUP($A135,統計!$A:$G,6,)</f>
@@ -9119,7 +9175,7 @@
         <v>#N/A</v>
       </c>
       <c r="C136" s="0" t="s">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="D136" s="0" t="e">
         <f aca="false">VLOOKUP($A136,統計!$A:$G,6,)</f>
@@ -9143,7 +9199,7 @@
         <v>#N/A</v>
       </c>
       <c r="C137" s="0" t="s">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="D137" s="0" t="e">
         <f aca="false">VLOOKUP($A137,統計!$A:$G,6,)</f>
@@ -9167,7 +9223,7 @@
         <v>#N/A</v>
       </c>
       <c r="C138" s="0" t="s">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="D138" s="0" t="e">
         <f aca="false">VLOOKUP($A138,統計!$A:$G,6,)</f>
@@ -9191,7 +9247,7 @@
         <v>#N/A</v>
       </c>
       <c r="C139" s="0" t="s">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="D139" s="0" t="e">
         <f aca="false">VLOOKUP($A139,統計!$A:$G,6,)</f>
@@ -9215,7 +9271,7 @@
         <v>#N/A</v>
       </c>
       <c r="C140" s="0" t="s">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="D140" s="0" t="e">
         <f aca="false">VLOOKUP($A140,統計!$A:$G,6,)</f>
@@ -9239,7 +9295,7 @@
         <v>#N/A</v>
       </c>
       <c r="C141" s="0" t="s">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="D141" s="0" t="e">
         <f aca="false">VLOOKUP($A141,統計!$A:$G,6,)</f>
@@ -9263,7 +9319,7 @@
         <v>#N/A</v>
       </c>
       <c r="C142" s="0" t="s">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="D142" s="0" t="e">
         <f aca="false">VLOOKUP($A142,統計!$A:$G,6,)</f>
@@ -9287,7 +9343,7 @@
         <v>#N/A</v>
       </c>
       <c r="C143" s="0" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="D143" s="0" t="e">
         <f aca="false">VLOOKUP($A143,統計!$A:$G,6,)</f>
@@ -9311,7 +9367,7 @@
         <v>#N/A</v>
       </c>
       <c r="C144" s="0" t="s">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="D144" s="0" t="e">
         <f aca="false">VLOOKUP($A144,統計!$A:$G,6,)</f>
@@ -9335,7 +9391,7 @@
         <v>#N/A</v>
       </c>
       <c r="C145" s="0" t="s">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="D145" s="0" t="e">
         <f aca="false">VLOOKUP($A145,統計!$A:$G,6,)</f>
@@ -9359,7 +9415,7 @@
         <v>#N/A</v>
       </c>
       <c r="C146" s="0" t="s">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="D146" s="0" t="e">
         <f aca="false">VLOOKUP($A146,統計!$A:$G,6,)</f>
@@ -9383,7 +9439,7 @@
         <v>#N/A</v>
       </c>
       <c r="C147" s="0" t="s">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="D147" s="0" t="e">
         <f aca="false">VLOOKUP($A147,統計!$A:$G,6,)</f>
@@ -9407,7 +9463,7 @@
         <v>#N/A</v>
       </c>
       <c r="C148" s="0" t="s">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="D148" s="0" t="e">
         <f aca="false">VLOOKUP($A148,統計!$A:$G,6,)</f>
@@ -9431,7 +9487,7 @@
         <v>#N/A</v>
       </c>
       <c r="C149" s="0" t="s">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="D149" s="0" t="e">
         <f aca="false">VLOOKUP($A149,統計!$A:$G,6,)</f>
@@ -9455,7 +9511,7 @@
         <v>#N/A</v>
       </c>
       <c r="C150" s="0" t="s">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="D150" s="0" t="e">
         <f aca="false">VLOOKUP($A150,統計!$A:$G,6,)</f>
@@ -9479,7 +9535,7 @@
         <v>#N/A</v>
       </c>
       <c r="C151" s="0" t="s">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="D151" s="0" t="e">
         <f aca="false">VLOOKUP($A151,統計!$A:$G,6,)</f>
@@ -9503,7 +9559,7 @@
         <v>#N/A</v>
       </c>
       <c r="C152" s="0" t="s">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="D152" s="0" t="e">
         <f aca="false">VLOOKUP($A152,統計!$A:$G,6,)</f>
@@ -9527,7 +9583,7 @@
         <v>#N/A</v>
       </c>
       <c r="C153" s="0" t="s">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="D153" s="0" t="e">
         <f aca="false">VLOOKUP($A153,統計!$A:$G,6,)</f>
@@ -9551,7 +9607,7 @@
         <v>#N/A</v>
       </c>
       <c r="C154" s="0" t="s">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="D154" s="0" t="e">
         <f aca="false">VLOOKUP($A154,統計!$A:$G,6,)</f>
@@ -9575,7 +9631,7 @@
         <v>#N/A</v>
       </c>
       <c r="C155" s="0" t="s">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="D155" s="0" t="e">
         <f aca="false">VLOOKUP($A155,統計!$A:$G,6,)</f>
@@ -9599,7 +9655,7 @@
         <v>#N/A</v>
       </c>
       <c r="C156" s="0" t="s">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="D156" s="0" t="e">
         <f aca="false">VLOOKUP($A156,統計!$A:$G,6,)</f>
@@ -9623,7 +9679,7 @@
         <v>#N/A</v>
       </c>
       <c r="C157" s="0" t="s">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="D157" s="0" t="e">
         <f aca="false">VLOOKUP($A157,統計!$A:$G,6,)</f>
@@ -9647,7 +9703,7 @@
         <v>#N/A</v>
       </c>
       <c r="C158" s="0" t="s">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="D158" s="0" t="e">
         <f aca="false">VLOOKUP($A158,統計!$A:$G,6,)</f>
@@ -9671,7 +9727,7 @@
         <v>#N/A</v>
       </c>
       <c r="C159" s="0" t="s">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="D159" s="0" t="e">
         <f aca="false">VLOOKUP($A159,統計!$A:$G,6,)</f>
@@ -9695,7 +9751,7 @@
         <v>#N/A</v>
       </c>
       <c r="C160" s="0" t="s">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="D160" s="0" t="e">
         <f aca="false">VLOOKUP($A160,統計!$A:$G,6,)</f>
@@ -9719,7 +9775,7 @@
         <v>#N/A</v>
       </c>
       <c r="C161" s="0" t="s">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="D161" s="0" t="e">
         <f aca="false">VLOOKUP($A161,統計!$A:$G,6,)</f>
@@ -9743,7 +9799,7 @@
         <v>#N/A</v>
       </c>
       <c r="C162" s="0" t="s">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="D162" s="0" t="e">
         <f aca="false">VLOOKUP($A162,統計!$A:$G,6,)</f>
@@ -9767,7 +9823,7 @@
         <v>#N/A</v>
       </c>
       <c r="C163" s="0" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="D163" s="0" t="e">
         <f aca="false">VLOOKUP($A163,統計!$A:$G,6,)</f>
@@ -9791,7 +9847,7 @@
         <v>#N/A</v>
       </c>
       <c r="C164" s="0" t="s">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="D164" s="0" t="e">
         <f aca="false">VLOOKUP($A164,統計!$A:$G,6,)</f>
@@ -9815,7 +9871,7 @@
         <v>#N/A</v>
       </c>
       <c r="C165" s="0" t="s">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="D165" s="0" t="e">
         <f aca="false">VLOOKUP($A165,統計!$A:$G,6,)</f>
@@ -9839,7 +9895,7 @@
         <v>#N/A</v>
       </c>
       <c r="C166" s="0" t="s">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="D166" s="0" t="e">
         <f aca="false">VLOOKUP($A166,統計!$A:$G,6,)</f>
@@ -9863,7 +9919,7 @@
         <v>#N/A</v>
       </c>
       <c r="C167" s="0" t="s">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="D167" s="0" t="e">
         <f aca="false">VLOOKUP($A167,統計!$A:$G,6,)</f>
@@ -9887,7 +9943,7 @@
         <v>#N/A</v>
       </c>
       <c r="C168" s="0" t="s">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="D168" s="0" t="e">
         <f aca="false">VLOOKUP($A168,統計!$A:$G,6,)</f>
@@ -9911,7 +9967,7 @@
         <v>#N/A</v>
       </c>
       <c r="C169" s="0" t="s">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="D169" s="0" t="e">
         <f aca="false">VLOOKUP($A169,統計!$A:$G,6,)</f>
@@ -9935,7 +9991,7 @@
         <v>#N/A</v>
       </c>
       <c r="C170" s="0" t="s">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="D170" s="0" t="e">
         <f aca="false">VLOOKUP($A170,統計!$A:$G,6,)</f>
@@ -9959,7 +10015,7 @@
         <v>#N/A</v>
       </c>
       <c r="C171" s="0" t="s">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="D171" s="0" t="e">
         <f aca="false">VLOOKUP($A171,統計!$A:$G,6,)</f>
@@ -9983,7 +10039,7 @@
         <v>#N/A</v>
       </c>
       <c r="C172" s="0" t="s">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="D172" s="0" t="e">
         <f aca="false">VLOOKUP($A172,統計!$A:$G,6,)</f>
@@ -10007,7 +10063,7 @@
         <v>#N/A</v>
       </c>
       <c r="C173" s="0" t="s">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="D173" s="0" t="e">
         <f aca="false">VLOOKUP($A173,統計!$A:$G,6,)</f>
@@ -10031,7 +10087,7 @@
         <v>#N/A</v>
       </c>
       <c r="C174" s="0" t="s">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="D174" s="0" t="e">
         <f aca="false">VLOOKUP($A174,統計!$A:$G,6,)</f>
@@ -10055,7 +10111,7 @@
         <v>#N/A</v>
       </c>
       <c r="C175" s="0" t="s">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="D175" s="0" t="e">
         <f aca="false">VLOOKUP($A175,統計!$A:$G,6,)</f>
@@ -10079,7 +10135,7 @@
         <v>#N/A</v>
       </c>
       <c r="C176" s="0" t="s">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="D176" s="0" t="e">
         <f aca="false">VLOOKUP($A176,統計!$A:$G,6,)</f>
@@ -10103,7 +10159,7 @@
         <v>#N/A</v>
       </c>
       <c r="C177" s="0" t="s">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="D177" s="0" t="e">
         <f aca="false">VLOOKUP($A177,統計!$A:$G,6,)</f>
@@ -10127,7 +10183,7 @@
         <v>#N/A</v>
       </c>
       <c r="C178" s="0" t="s">
-        <v>366</v>
+        <v>367</v>
       </c>
       <c r="D178" s="0" t="e">
         <f aca="false">VLOOKUP($A178,統計!$A:$G,6,)</f>
@@ -10151,7 +10207,7 @@
         <v>#N/A</v>
       </c>
       <c r="C179" s="0" t="s">
-        <v>367</v>
+        <v>368</v>
       </c>
       <c r="D179" s="0" t="e">
         <f aca="false">VLOOKUP($A179,統計!$A:$G,6,)</f>
@@ -10175,7 +10231,7 @@
         <v>#N/A</v>
       </c>
       <c r="C180" s="0" t="s">
-        <v>368</v>
+        <v>369</v>
       </c>
       <c r="D180" s="0" t="e">
         <f aca="false">VLOOKUP($A180,統計!$A:$G,6,)</f>
@@ -10199,7 +10255,7 @@
         <v>#N/A</v>
       </c>
       <c r="C181" s="0" t="s">
-        <v>369</v>
+        <v>370</v>
       </c>
       <c r="D181" s="0" t="e">
         <f aca="false">VLOOKUP($A181,統計!$A:$G,6,)</f>
@@ -10223,7 +10279,7 @@
         <v>#N/A</v>
       </c>
       <c r="C182" s="0" t="s">
-        <v>370</v>
+        <v>371</v>
       </c>
       <c r="D182" s="0" t="e">
         <f aca="false">VLOOKUP($A182,統計!$A:$G,6,)</f>
@@ -10247,7 +10303,7 @@
         <v>#N/A</v>
       </c>
       <c r="C183" s="0" t="s">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="D183" s="0" t="e">
         <f aca="false">VLOOKUP($A183,統計!$A:$G,6,)</f>
@@ -10271,7 +10327,7 @@
         <v>#N/A</v>
       </c>
       <c r="C184" s="0" t="s">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="D184" s="0" t="e">
         <f aca="false">VLOOKUP($A184,統計!$A:$G,6,)</f>
@@ -10295,7 +10351,7 @@
         <v>#N/A</v>
       </c>
       <c r="C185" s="0" t="s">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c r="D185" s="0" t="e">
         <f aca="false">VLOOKUP($A185,統計!$A:$G,6,)</f>
@@ -10319,7 +10375,7 @@
         <v>#N/A</v>
       </c>
       <c r="C186" s="0" t="s">
-        <v>374</v>
+        <v>375</v>
       </c>
       <c r="D186" s="0" t="e">
         <f aca="false">VLOOKUP($A186,統計!$A:$G,6,)</f>
@@ -10343,7 +10399,7 @@
         <v>#N/A</v>
       </c>
       <c r="C187" s="0" t="s">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="D187" s="0" t="e">
         <f aca="false">VLOOKUP($A187,統計!$A:$G,6,)</f>
@@ -10367,7 +10423,7 @@
         <v>#N/A</v>
       </c>
       <c r="C188" s="0" t="s">
-        <v>376</v>
+        <v>377</v>
       </c>
       <c r="D188" s="0" t="e">
         <f aca="false">VLOOKUP($A188,統計!$A:$G,6,)</f>
@@ -10391,7 +10447,7 @@
         <v>#N/A</v>
       </c>
       <c r="C189" s="0" t="s">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="D189" s="0" t="e">
         <f aca="false">VLOOKUP($A189,統計!$A:$G,6,)</f>
@@ -10415,7 +10471,7 @@
         <v>#N/A</v>
       </c>
       <c r="C190" s="0" t="s">
-        <v>378</v>
+        <v>379</v>
       </c>
       <c r="D190" s="0" t="e">
         <f aca="false">VLOOKUP($A190,統計!$A:$G,6,)</f>
@@ -10439,7 +10495,7 @@
         <v>#N/A</v>
       </c>
       <c r="C191" s="0" t="s">
-        <v>379</v>
+        <v>380</v>
       </c>
       <c r="D191" s="0" t="e">
         <f aca="false">VLOOKUP($A191,統計!$A:$G,6,)</f>
@@ -10463,7 +10519,7 @@
         <v>#N/A</v>
       </c>
       <c r="C192" s="0" t="s">
-        <v>380</v>
+        <v>381</v>
       </c>
       <c r="D192" s="0" t="e">
         <f aca="false">VLOOKUP($A192,統計!$A:$G,6,)</f>
@@ -10487,7 +10543,7 @@
         <v>#N/A</v>
       </c>
       <c r="C193" s="0" t="s">
-        <v>381</v>
+        <v>382</v>
       </c>
       <c r="D193" s="0" t="e">
         <f aca="false">VLOOKUP($A193,統計!$A:$G,6,)</f>
@@ -10511,7 +10567,7 @@
         <v>#N/A</v>
       </c>
       <c r="C194" s="0" t="s">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="D194" s="0" t="e">
         <f aca="false">VLOOKUP($A194,統計!$A:$G,6,)</f>
@@ -10535,7 +10591,7 @@
         <v>#N/A</v>
       </c>
       <c r="C195" s="0" t="s">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="D195" s="0" t="e">
         <f aca="false">VLOOKUP($A195,統計!$A:$G,6,)</f>
@@ -10559,7 +10615,7 @@
         <v>#N/A</v>
       </c>
       <c r="C196" s="0" t="s">
-        <v>384</v>
+        <v>385</v>
       </c>
       <c r="D196" s="0" t="e">
         <f aca="false">VLOOKUP($A196,統計!$A:$G,6,)</f>
@@ -10583,7 +10639,7 @@
         <v>#N/A</v>
       </c>
       <c r="C197" s="0" t="s">
-        <v>385</v>
+        <v>386</v>
       </c>
       <c r="D197" s="0" t="e">
         <f aca="false">VLOOKUP($A197,統計!$A:$G,6,)</f>
@@ -10607,7 +10663,7 @@
         <v>#N/A</v>
       </c>
       <c r="C198" s="0" t="s">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="D198" s="0" t="e">
         <f aca="false">VLOOKUP($A198,統計!$A:$G,6,)</f>
@@ -10631,7 +10687,7 @@
         <v>#N/A</v>
       </c>
       <c r="C199" s="0" t="s">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="D199" s="0" t="e">
         <f aca="false">VLOOKUP($A199,統計!$A:$G,6,)</f>
@@ -10655,7 +10711,7 @@
         <v>#N/A</v>
       </c>
       <c r="C200" s="0" t="s">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c r="D200" s="0" t="e">
         <f aca="false">VLOOKUP($A200,統計!$A:$G,6,)</f>
@@ -10679,7 +10735,7 @@
         <v>#N/A</v>
       </c>
       <c r="C201" s="0" t="s">
-        <v>389</v>
+        <v>390</v>
       </c>
       <c r="D201" s="0" t="e">
         <f aca="false">VLOOKUP($A201,統計!$A:$G,6,)</f>
@@ -10703,7 +10759,7 @@
         <v>#N/A</v>
       </c>
       <c r="C202" s="0" t="s">
-        <v>390</v>
+        <v>391</v>
       </c>
       <c r="D202" s="0" t="e">
         <f aca="false">VLOOKUP($A202,統計!$A:$G,6,)</f>
@@ -10727,7 +10783,7 @@
         <v>#N/A</v>
       </c>
       <c r="C203" s="0" t="s">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="D203" s="0" t="e">
         <f aca="false">VLOOKUP($A203,統計!$A:$G,6,)</f>
@@ -10751,7 +10807,7 @@
         <v>#N/A</v>
       </c>
       <c r="C204" s="0" t="s">
-        <v>392</v>
+        <v>393</v>
       </c>
       <c r="D204" s="0" t="e">
         <f aca="false">VLOOKUP($A204,統計!$A:$G,6,)</f>
@@ -10775,7 +10831,7 @@
         <v>#N/A</v>
       </c>
       <c r="C205" s="0" t="s">
-        <v>393</v>
+        <v>394</v>
       </c>
       <c r="D205" s="0" t="e">
         <f aca="false">VLOOKUP($A205,統計!$A:$G,6,)</f>
@@ -10799,7 +10855,7 @@
         <v>#N/A</v>
       </c>
       <c r="C206" s="0" t="s">
-        <v>394</v>
+        <v>395</v>
       </c>
       <c r="D206" s="0" t="e">
         <f aca="false">VLOOKUP($A206,統計!$A:$G,6,)</f>
@@ -10823,7 +10879,7 @@
         <v>#N/A</v>
       </c>
       <c r="C207" s="0" t="s">
-        <v>395</v>
+        <v>396</v>
       </c>
       <c r="D207" s="0" t="e">
         <f aca="false">VLOOKUP($A207,統計!$A:$G,6,)</f>
@@ -10847,7 +10903,7 @@
         <v>#N/A</v>
       </c>
       <c r="C208" s="0" t="s">
-        <v>396</v>
+        <v>397</v>
       </c>
       <c r="D208" s="0" t="e">
         <f aca="false">VLOOKUP($A208,統計!$A:$G,6,)</f>
@@ -10871,7 +10927,7 @@
         <v>#N/A</v>
       </c>
       <c r="C209" s="0" t="s">
-        <v>397</v>
+        <v>398</v>
       </c>
       <c r="D209" s="0" t="e">
         <f aca="false">VLOOKUP($A209,統計!$A:$G,6,)</f>
@@ -10895,7 +10951,7 @@
         <v>#N/A</v>
       </c>
       <c r="C210" s="0" t="s">
-        <v>398</v>
+        <v>399</v>
       </c>
       <c r="D210" s="0" t="e">
         <f aca="false">VLOOKUP($A210,統計!$A:$G,6,)</f>
@@ -10919,7 +10975,7 @@
         <v>#N/A</v>
       </c>
       <c r="C211" s="0" t="s">
-        <v>399</v>
+        <v>400</v>
       </c>
       <c r="D211" s="0" t="e">
         <f aca="false">VLOOKUP($A211,統計!$A:$G,6,)</f>
@@ -10943,7 +10999,7 @@
         <v>#N/A</v>
       </c>
       <c r="C212" s="0" t="s">
-        <v>400</v>
+        <v>401</v>
       </c>
       <c r="D212" s="0" t="e">
         <f aca="false">VLOOKUP($A212,統計!$A:$G,6,)</f>
@@ -10967,7 +11023,7 @@
         <v>#N/A</v>
       </c>
       <c r="C213" s="0" t="s">
-        <v>401</v>
+        <v>402</v>
       </c>
       <c r="D213" s="0" t="e">
         <f aca="false">VLOOKUP($A213,統計!$A:$G,6,)</f>
@@ -10991,7 +11047,7 @@
         <v>#N/A</v>
       </c>
       <c r="C214" s="0" t="s">
-        <v>402</v>
+        <v>403</v>
       </c>
       <c r="D214" s="0" t="e">
         <f aca="false">VLOOKUP($A214,統計!$A:$G,6,)</f>
@@ -11015,7 +11071,7 @@
         <v>#N/A</v>
       </c>
       <c r="C215" s="0" t="s">
-        <v>403</v>
+        <v>404</v>
       </c>
       <c r="D215" s="0" t="e">
         <f aca="false">VLOOKUP($A215,統計!$A:$G,6,)</f>
@@ -11039,7 +11095,7 @@
         <v>#N/A</v>
       </c>
       <c r="C216" s="0" t="s">
-        <v>404</v>
+        <v>405</v>
       </c>
       <c r="D216" s="0" t="e">
         <f aca="false">VLOOKUP($A216,統計!$A:$G,6,)</f>
@@ -11063,7 +11119,7 @@
         <v>#N/A</v>
       </c>
       <c r="C217" s="0" t="s">
-        <v>405</v>
+        <v>406</v>
       </c>
       <c r="D217" s="0" t="e">
         <f aca="false">VLOOKUP($A217,統計!$A:$G,6,)</f>
@@ -11087,7 +11143,7 @@
         <v>#N/A</v>
       </c>
       <c r="C218" s="0" t="s">
-        <v>406</v>
+        <v>407</v>
       </c>
       <c r="D218" s="0" t="e">
         <f aca="false">VLOOKUP($A218,統計!$A:$G,6,)</f>
@@ -11111,7 +11167,7 @@
         <v>#N/A</v>
       </c>
       <c r="C219" s="0" t="s">
-        <v>407</v>
+        <v>408</v>
       </c>
       <c r="D219" s="0" t="e">
         <f aca="false">VLOOKUP($A219,統計!$A:$G,6,)</f>
@@ -11135,7 +11191,7 @@
         <v>#N/A</v>
       </c>
       <c r="C220" s="0" t="s">
-        <v>408</v>
+        <v>409</v>
       </c>
       <c r="D220" s="0" t="e">
         <f aca="false">VLOOKUP($A220,統計!$A:$G,6,)</f>
@@ -11159,7 +11215,7 @@
         <v>#N/A</v>
       </c>
       <c r="C221" s="0" t="s">
-        <v>409</v>
+        <v>410</v>
       </c>
       <c r="D221" s="0" t="e">
         <f aca="false">VLOOKUP($A221,統計!$A:$G,6,)</f>
@@ -11183,7 +11239,7 @@
         <v>#N/A</v>
       </c>
       <c r="C222" s="0" t="s">
-        <v>410</v>
+        <v>411</v>
       </c>
       <c r="D222" s="0" t="e">
         <f aca="false">VLOOKUP($A222,統計!$A:$G,6,)</f>
@@ -11207,7 +11263,7 @@
         <v>#N/A</v>
       </c>
       <c r="C223" s="0" t="s">
-        <v>411</v>
+        <v>412</v>
       </c>
       <c r="D223" s="0" t="e">
         <f aca="false">VLOOKUP($A223,統計!$A:$G,6,)</f>
@@ -11231,7 +11287,7 @@
         <v>#N/A</v>
       </c>
       <c r="C224" s="0" t="s">
-        <v>412</v>
+        <v>413</v>
       </c>
       <c r="D224" s="0" t="e">
         <f aca="false">VLOOKUP($A224,統計!$A:$G,6,)</f>
@@ -11255,7 +11311,7 @@
         <v>#N/A</v>
       </c>
       <c r="C225" s="0" t="s">
-        <v>413</v>
+        <v>414</v>
       </c>
       <c r="D225" s="0" t="e">
         <f aca="false">VLOOKUP($A225,統計!$A:$G,6,)</f>
@@ -11279,7 +11335,7 @@
         <v>#N/A</v>
       </c>
       <c r="C226" s="0" t="s">
-        <v>414</v>
+        <v>415</v>
       </c>
       <c r="D226" s="0" t="e">
         <f aca="false">VLOOKUP($A226,統計!$A:$G,6,)</f>
@@ -11303,7 +11359,7 @@
         <v>#N/A</v>
       </c>
       <c r="C227" s="0" t="s">
-        <v>415</v>
+        <v>416</v>
       </c>
       <c r="D227" s="0" t="e">
         <f aca="false">VLOOKUP($A227,統計!$A:$G,6,)</f>
@@ -11327,7 +11383,7 @@
         <v>#N/A</v>
       </c>
       <c r="C228" s="0" t="s">
-        <v>416</v>
+        <v>417</v>
       </c>
       <c r="D228" s="0" t="e">
         <f aca="false">VLOOKUP($A228,統計!$A:$G,6,)</f>
@@ -11351,7 +11407,7 @@
         <v>#N/A</v>
       </c>
       <c r="C229" s="0" t="s">
-        <v>417</v>
+        <v>418</v>
       </c>
       <c r="D229" s="0" t="e">
         <f aca="false">VLOOKUP($A229,統計!$A:$G,6,)</f>
@@ -11375,7 +11431,7 @@
         <v>#N/A</v>
       </c>
       <c r="C230" s="0" t="s">
-        <v>418</v>
+        <v>419</v>
       </c>
       <c r="D230" s="0" t="e">
         <f aca="false">VLOOKUP($A230,統計!$A:$G,6,)</f>
@@ -11399,7 +11455,7 @@
         <v>#N/A</v>
       </c>
       <c r="C231" s="0" t="s">
-        <v>419</v>
+        <v>420</v>
       </c>
       <c r="D231" s="0" t="e">
         <f aca="false">VLOOKUP($A231,統計!$A:$G,6,)</f>
@@ -11423,7 +11479,7 @@
         <v>#N/A</v>
       </c>
       <c r="C232" s="0" t="s">
-        <v>420</v>
+        <v>421</v>
       </c>
       <c r="D232" s="0" t="e">
         <f aca="false">VLOOKUP($A232,統計!$A:$G,6,)</f>
@@ -11447,7 +11503,7 @@
         <v>#N/A</v>
       </c>
       <c r="C233" s="0" t="s">
-        <v>421</v>
+        <v>422</v>
       </c>
       <c r="D233" s="0" t="e">
         <f aca="false">VLOOKUP($A233,統計!$A:$G,6,)</f>
@@ -11471,7 +11527,7 @@
         <v>#N/A</v>
       </c>
       <c r="C234" s="0" t="s">
-        <v>422</v>
+        <v>423</v>
       </c>
       <c r="D234" s="0" t="e">
         <f aca="false">VLOOKUP($A234,統計!$A:$G,6,)</f>
@@ -11495,7 +11551,7 @@
         <v>#N/A</v>
       </c>
       <c r="C235" s="0" t="s">
-        <v>423</v>
+        <v>424</v>
       </c>
       <c r="D235" s="0" t="e">
         <f aca="false">VLOOKUP($A235,統計!$A:$G,6,)</f>
@@ -11519,7 +11575,7 @@
         <v>#N/A</v>
       </c>
       <c r="C236" s="0" t="s">
-        <v>424</v>
+        <v>425</v>
       </c>
       <c r="D236" s="0" t="e">
         <f aca="false">VLOOKUP($A236,統計!$A:$G,6,)</f>
@@ -11543,7 +11599,7 @@
         <v>#N/A</v>
       </c>
       <c r="C237" s="0" t="s">
-        <v>425</v>
+        <v>426</v>
       </c>
       <c r="D237" s="0" t="e">
         <f aca="false">VLOOKUP($A237,統計!$A:$G,6,)</f>
@@ -11567,7 +11623,7 @@
         <v>#N/A</v>
       </c>
       <c r="C238" s="0" t="s">
-        <v>426</v>
+        <v>427</v>
       </c>
       <c r="D238" s="0" t="e">
         <f aca="false">VLOOKUP($A238,統計!$A:$G,6,)</f>
@@ -11591,7 +11647,7 @@
         <v>#N/A</v>
       </c>
       <c r="C239" s="0" t="s">
-        <v>427</v>
+        <v>428</v>
       </c>
       <c r="D239" s="0" t="e">
         <f aca="false">VLOOKUP($A239,統計!$A:$G,6,)</f>
@@ -11615,7 +11671,7 @@
         <v>#N/A</v>
       </c>
       <c r="C240" s="0" t="s">
-        <v>428</v>
+        <v>429</v>
       </c>
       <c r="D240" s="0" t="e">
         <f aca="false">VLOOKUP($A240,統計!$A:$G,6,)</f>
@@ -11639,7 +11695,7 @@
         <v>#N/A</v>
       </c>
       <c r="C241" s="0" t="s">
-        <v>429</v>
+        <v>430</v>
       </c>
       <c r="D241" s="0" t="e">
         <f aca="false">VLOOKUP($A241,統計!$A:$G,6,)</f>
@@ -11663,7 +11719,7 @@
         <v>#N/A</v>
       </c>
       <c r="C242" s="0" t="s">
-        <v>430</v>
+        <v>431</v>
       </c>
       <c r="D242" s="0" t="e">
         <f aca="false">VLOOKUP($A242,統計!$A:$G,6,)</f>
@@ -11687,7 +11743,7 @@
         <v>#N/A</v>
       </c>
       <c r="C243" s="0" t="s">
-        <v>431</v>
+        <v>432</v>
       </c>
       <c r="D243" s="0" t="e">
         <f aca="false">VLOOKUP($A243,統計!$A:$G,6,)</f>
@@ -11711,7 +11767,7 @@
         <v>#N/A</v>
       </c>
       <c r="C244" s="0" t="s">
-        <v>432</v>
+        <v>433</v>
       </c>
       <c r="D244" s="0" t="e">
         <f aca="false">VLOOKUP($A244,統計!$A:$G,6,)</f>
@@ -11735,7 +11791,7 @@
         <v>#N/A</v>
       </c>
       <c r="C245" s="0" t="s">
-        <v>433</v>
+        <v>434</v>
       </c>
       <c r="D245" s="0" t="e">
         <f aca="false">VLOOKUP($A245,統計!$A:$G,6,)</f>
@@ -11759,7 +11815,7 @@
         <v>#N/A</v>
       </c>
       <c r="C246" s="0" t="s">
-        <v>434</v>
+        <v>435</v>
       </c>
       <c r="D246" s="0" t="e">
         <f aca="false">VLOOKUP($A246,統計!$A:$G,6,)</f>
@@ -11783,7 +11839,7 @@
         <v>#N/A</v>
       </c>
       <c r="C247" s="0" t="s">
-        <v>435</v>
+        <v>436</v>
       </c>
       <c r="D247" s="0" t="e">
         <f aca="false">VLOOKUP($A247,統計!$A:$G,6,)</f>
@@ -11807,7 +11863,7 @@
         <v>#N/A</v>
       </c>
       <c r="C248" s="0" t="s">
-        <v>436</v>
+        <v>437</v>
       </c>
       <c r="D248" s="0" t="e">
         <f aca="false">VLOOKUP($A248,統計!$A:$G,6,)</f>
@@ -11831,7 +11887,7 @@
         <v>#N/A</v>
       </c>
       <c r="C249" s="0" t="s">
-        <v>437</v>
+        <v>438</v>
       </c>
       <c r="D249" s="0" t="e">
         <f aca="false">VLOOKUP($A249,統計!$A:$G,6,)</f>
@@ -11855,7 +11911,7 @@
         <v>#N/A</v>
       </c>
       <c r="C250" s="0" t="s">
-        <v>438</v>
+        <v>439</v>
       </c>
       <c r="D250" s="0" t="e">
         <f aca="false">VLOOKUP($A250,統計!$A:$G,6,)</f>
@@ -11879,7 +11935,7 @@
         <v>#N/A</v>
       </c>
       <c r="C251" s="0" t="s">
-        <v>439</v>
+        <v>440</v>
       </c>
       <c r="D251" s="0" t="e">
         <f aca="false">VLOOKUP($A251,統計!$A:$G,6,)</f>
@@ -11903,7 +11959,7 @@
         <v>#N/A</v>
       </c>
       <c r="C252" s="0" t="s">
-        <v>440</v>
+        <v>441</v>
       </c>
       <c r="D252" s="0" t="e">
         <f aca="false">VLOOKUP($A252,統計!$A:$G,6,)</f>
@@ -11927,7 +11983,7 @@
         <v>#N/A</v>
       </c>
       <c r="C253" s="0" t="s">
-        <v>441</v>
+        <v>442</v>
       </c>
       <c r="D253" s="0" t="e">
         <f aca="false">VLOOKUP($A253,統計!$A:$G,6,)</f>
@@ -11951,7 +12007,7 @@
         <v>#N/A</v>
       </c>
       <c r="C254" s="0" t="s">
-        <v>442</v>
+        <v>443</v>
       </c>
       <c r="D254" s="0" t="e">
         <f aca="false">VLOOKUP($A254,統計!$A:$G,6,)</f>
@@ -11975,7 +12031,7 @@
         <v>#N/A</v>
       </c>
       <c r="C255" s="0" t="s">
-        <v>443</v>
+        <v>444</v>
       </c>
       <c r="D255" s="0" t="e">
         <f aca="false">VLOOKUP($A255,統計!$A:$G,6,)</f>
@@ -11999,7 +12055,7 @@
         <v>#N/A</v>
       </c>
       <c r="C256" s="0" t="s">
-        <v>444</v>
+        <v>445</v>
       </c>
       <c r="D256" s="0" t="e">
         <f aca="false">VLOOKUP($A256,統計!$A:$G,6,)</f>
@@ -12023,7 +12079,7 @@
         <v>#N/A</v>
       </c>
       <c r="C257" s="0" t="s">
-        <v>445</v>
+        <v>446</v>
       </c>
       <c r="D257" s="0" t="e">
         <f aca="false">VLOOKUP($A257,統計!$A:$G,6,)</f>
@@ -12047,7 +12103,7 @@
         <v>#N/A</v>
       </c>
       <c r="C258" s="0" t="s">
-        <v>446</v>
+        <v>447</v>
       </c>
       <c r="D258" s="0" t="e">
         <f aca="false">VLOOKUP($A258,統計!$A:$G,6,)</f>
@@ -12071,7 +12127,7 @@
         <v>#N/A</v>
       </c>
       <c r="C259" s="0" t="s">
-        <v>447</v>
+        <v>448</v>
       </c>
       <c r="D259" s="0" t="e">
         <f aca="false">VLOOKUP($A259,統計!$A:$G,6,)</f>
@@ -12095,7 +12151,7 @@
         <v>#N/A</v>
       </c>
       <c r="C260" s="0" t="s">
-        <v>448</v>
+        <v>449</v>
       </c>
       <c r="D260" s="0" t="e">
         <f aca="false">VLOOKUP($A260,統計!$A:$G,6,)</f>
@@ -12119,7 +12175,7 @@
         <v>#N/A</v>
       </c>
       <c r="C261" s="0" t="s">
-        <v>449</v>
+        <v>450</v>
       </c>
       <c r="D261" s="0" t="e">
         <f aca="false">VLOOKUP($A261,統計!$A:$G,6,)</f>
@@ -12143,7 +12199,7 @@
         <v>#N/A</v>
       </c>
       <c r="C262" s="0" t="s">
-        <v>450</v>
+        <v>451</v>
       </c>
       <c r="D262" s="0" t="e">
         <f aca="false">VLOOKUP($A262,統計!$A:$G,6,)</f>
@@ -12167,7 +12223,7 @@
         <v>#N/A</v>
       </c>
       <c r="C263" s="0" t="s">
-        <v>451</v>
+        <v>452</v>
       </c>
       <c r="D263" s="0" t="e">
         <f aca="false">VLOOKUP($A263,統計!$A:$G,6,)</f>
@@ -12191,7 +12247,7 @@
         <v>#N/A</v>
       </c>
       <c r="C264" s="0" t="s">
-        <v>452</v>
+        <v>453</v>
       </c>
       <c r="D264" s="0" t="e">
         <f aca="false">VLOOKUP($A264,統計!$A:$G,6,)</f>
@@ -12215,7 +12271,7 @@
         <v>#N/A</v>
       </c>
       <c r="C265" s="0" t="s">
-        <v>453</v>
+        <v>454</v>
       </c>
       <c r="D265" s="0" t="e">
         <f aca="false">VLOOKUP($A265,統計!$A:$G,6,)</f>
@@ -12239,7 +12295,7 @@
         <v>#N/A</v>
       </c>
       <c r="C266" s="0" t="s">
-        <v>454</v>
+        <v>455</v>
       </c>
       <c r="D266" s="0" t="e">
         <f aca="false">VLOOKUP($A266,統計!$A:$G,6,)</f>
@@ -12263,7 +12319,7 @@
         <v>#N/A</v>
       </c>
       <c r="C267" s="0" t="s">
-        <v>455</v>
+        <v>456</v>
       </c>
       <c r="D267" s="0" t="e">
         <f aca="false">VLOOKUP($A267,統計!$A:$G,6,)</f>
@@ -12287,7 +12343,7 @@
         <v>#N/A</v>
       </c>
       <c r="C268" s="0" t="s">
-        <v>456</v>
+        <v>457</v>
       </c>
       <c r="D268" s="0" t="e">
         <f aca="false">VLOOKUP($A268,統計!$A:$G,6,)</f>
@@ -12311,7 +12367,7 @@
         <v>#N/A</v>
       </c>
       <c r="C269" s="0" t="s">
-        <v>457</v>
+        <v>458</v>
       </c>
       <c r="D269" s="0" t="e">
         <f aca="false">VLOOKUP($A269,統計!$A:$G,6,)</f>
@@ -12335,7 +12391,7 @@
         <v>#N/A</v>
       </c>
       <c r="C270" s="0" t="s">
-        <v>458</v>
+        <v>459</v>
       </c>
       <c r="D270" s="0" t="e">
         <f aca="false">VLOOKUP($A270,統計!$A:$G,6,)</f>
@@ -12359,7 +12415,7 @@
         <v>#N/A</v>
       </c>
       <c r="C271" s="0" t="s">
-        <v>459</v>
+        <v>460</v>
       </c>
       <c r="D271" s="0" t="e">
         <f aca="false">VLOOKUP($A271,統計!$A:$G,6,)</f>
@@ -12383,7 +12439,7 @@
         <v>#N/A</v>
       </c>
       <c r="C272" s="0" t="s">
-        <v>460</v>
+        <v>461</v>
       </c>
       <c r="D272" s="0" t="e">
         <f aca="false">VLOOKUP($A272,統計!$A:$G,6,)</f>
@@ -12407,7 +12463,7 @@
         <v>#N/A</v>
       </c>
       <c r="C273" s="0" t="s">
-        <v>461</v>
+        <v>462</v>
       </c>
       <c r="D273" s="0" t="e">
         <f aca="false">VLOOKUP($A273,統計!$A:$G,6,)</f>
@@ -12431,7 +12487,7 @@
         <v>#N/A</v>
       </c>
       <c r="C274" s="0" t="s">
-        <v>462</v>
+        <v>463</v>
       </c>
       <c r="D274" s="0" t="e">
         <f aca="false">VLOOKUP($A274,統計!$A:$G,6,)</f>
@@ -12455,7 +12511,7 @@
         <v>#N/A</v>
       </c>
       <c r="C275" s="0" t="s">
-        <v>463</v>
+        <v>464</v>
       </c>
       <c r="D275" s="0" t="e">
         <f aca="false">VLOOKUP($A275,統計!$A:$G,6,)</f>
@@ -12479,7 +12535,7 @@
         <v>#N/A</v>
       </c>
       <c r="C276" s="0" t="s">
-        <v>464</v>
+        <v>465</v>
       </c>
       <c r="D276" s="0" t="e">
         <f aca="false">VLOOKUP($A276,統計!$A:$G,6,)</f>
@@ -12503,7 +12559,7 @@
         <v>#N/A</v>
       </c>
       <c r="C277" s="0" t="s">
-        <v>465</v>
+        <v>466</v>
       </c>
       <c r="D277" s="0" t="e">
         <f aca="false">VLOOKUP($A277,統計!$A:$G,6,)</f>
@@ -12527,7 +12583,7 @@
         <v>#N/A</v>
       </c>
       <c r="C278" s="0" t="s">
-        <v>466</v>
+        <v>467</v>
       </c>
       <c r="D278" s="0" t="e">
         <f aca="false">VLOOKUP($A278,統計!$A:$G,6,)</f>
@@ -12551,7 +12607,7 @@
         <v>#N/A</v>
       </c>
       <c r="C279" s="0" t="s">
-        <v>467</v>
+        <v>468</v>
       </c>
       <c r="D279" s="0" t="e">
         <f aca="false">VLOOKUP($A279,統計!$A:$G,6,)</f>
@@ -12575,7 +12631,7 @@
         <v>#N/A</v>
       </c>
       <c r="C280" s="0" t="s">
-        <v>468</v>
+        <v>469</v>
       </c>
       <c r="D280" s="0" t="e">
         <f aca="false">VLOOKUP($A280,統計!$A:$G,6,)</f>
@@ -12599,7 +12655,7 @@
         <v>#N/A</v>
       </c>
       <c r="C281" s="0" t="s">
-        <v>469</v>
+        <v>470</v>
       </c>
       <c r="D281" s="0" t="e">
         <f aca="false">VLOOKUP($A281,統計!$A:$G,6,)</f>
@@ -12623,7 +12679,7 @@
         <v>#N/A</v>
       </c>
       <c r="C282" s="0" t="s">
-        <v>470</v>
+        <v>471</v>
       </c>
       <c r="D282" s="0" t="e">
         <f aca="false">VLOOKUP($A282,統計!$A:$G,6,)</f>
@@ -12647,7 +12703,7 @@
         <v>#N/A</v>
       </c>
       <c r="C283" s="0" t="s">
-        <v>471</v>
+        <v>472</v>
       </c>
       <c r="D283" s="0" t="e">
         <f aca="false">VLOOKUP($A283,統計!$A:$G,6,)</f>
@@ -12671,7 +12727,7 @@
         <v>#N/A</v>
       </c>
       <c r="C284" s="0" t="s">
-        <v>472</v>
+        <v>473</v>
       </c>
       <c r="D284" s="0" t="e">
         <f aca="false">VLOOKUP($A284,統計!$A:$G,6,)</f>
@@ -12695,7 +12751,7 @@
         <v>#N/A</v>
       </c>
       <c r="C285" s="0" t="s">
-        <v>473</v>
+        <v>474</v>
       </c>
       <c r="D285" s="0" t="e">
         <f aca="false">VLOOKUP($A285,統計!$A:$G,6,)</f>
@@ -12719,7 +12775,7 @@
         <v>#N/A</v>
       </c>
       <c r="C286" s="0" t="s">
-        <v>474</v>
+        <v>475</v>
       </c>
       <c r="D286" s="0" t="e">
         <f aca="false">VLOOKUP($A286,統計!$A:$G,6,)</f>
@@ -12743,7 +12799,7 @@
         <v>#N/A</v>
       </c>
       <c r="C287" s="0" t="s">
-        <v>475</v>
+        <v>476</v>
       </c>
       <c r="D287" s="0" t="e">
         <f aca="false">VLOOKUP($A287,統計!$A:$G,6,)</f>
@@ -12767,7 +12823,7 @@
         <v>#N/A</v>
       </c>
       <c r="C288" s="0" t="s">
-        <v>476</v>
+        <v>477</v>
       </c>
       <c r="D288" s="0" t="e">
         <f aca="false">VLOOKUP($A288,統計!$A:$G,6,)</f>
@@ -12791,7 +12847,7 @@
         <v>#N/A</v>
       </c>
       <c r="C289" s="0" t="s">
-        <v>477</v>
+        <v>478</v>
       </c>
       <c r="D289" s="0" t="e">
         <f aca="false">VLOOKUP($A289,統計!$A:$G,6,)</f>
@@ -12815,7 +12871,7 @@
         <v>#N/A</v>
       </c>
       <c r="C290" s="0" t="s">
-        <v>478</v>
+        <v>479</v>
       </c>
       <c r="D290" s="0" t="e">
         <f aca="false">VLOOKUP($A290,統計!$A:$G,6,)</f>
@@ -12839,7 +12895,7 @@
         <v>#N/A</v>
       </c>
       <c r="C291" s="0" t="s">
-        <v>479</v>
+        <v>480</v>
       </c>
       <c r="D291" s="0" t="e">
         <f aca="false">VLOOKUP($A291,統計!$A:$G,6,)</f>
@@ -12863,7 +12919,7 @@
         <v>#N/A</v>
       </c>
       <c r="C292" s="0" t="s">
-        <v>480</v>
+        <v>481</v>
       </c>
       <c r="D292" s="0" t="e">
         <f aca="false">VLOOKUP($A292,統計!$A:$G,6,)</f>
@@ -12887,7 +12943,7 @@
         <v>#N/A</v>
       </c>
       <c r="C293" s="0" t="s">
-        <v>481</v>
+        <v>482</v>
       </c>
       <c r="D293" s="0" t="e">
         <f aca="false">VLOOKUP($A293,統計!$A:$G,6,)</f>
@@ -12911,7 +12967,7 @@
         <v>#N/A</v>
       </c>
       <c r="C294" s="0" t="s">
-        <v>482</v>
+        <v>483</v>
       </c>
       <c r="D294" s="0" t="e">
         <f aca="false">VLOOKUP($A294,統計!$A:$G,6,)</f>
@@ -12935,7 +12991,7 @@
         <v>#N/A</v>
       </c>
       <c r="C295" s="0" t="s">
-        <v>483</v>
+        <v>484</v>
       </c>
       <c r="D295" s="0" t="e">
         <f aca="false">VLOOKUP($A295,統計!$A:$G,6,)</f>
@@ -12952,8 +13008,8 @@
     </row>
   </sheetData>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.511811023622047" footer="0.511811023622047"/>
-  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.511805555555555" footer="0.511805555555555"/>
+  <pageSetup paperSize="9" scale="100" firstPageNumber="0" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" useFirstPageNumber="false" horizontalDpi="300" verticalDpi="300" copies="1"/>
   <headerFooter differentFirst="false" differentOddEven="false">
     <oddHeader/>
     <oddFooter/>
@@ -12971,13 +13027,13 @@
   <sheetData>
     <row r="1" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B1" s="0" t="s">
-        <v>484</v>
+        <v>485</v>
       </c>
       <c r="C1" s="0" t="s">
-        <v>485</v>
+        <v>486</v>
       </c>
       <c r="D1" s="0" t="s">
-        <v>486</v>
+        <v>487</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -12991,30 +13047,30 @@
         <v>1173</v>
       </c>
       <c r="E2" s="0" t="s">
-        <v>487</v>
+        <v>488</v>
       </c>
       <c r="G2" s="0" t="n">
         <f aca="false">C2/B2</f>
         <v>2.41791044776119</v>
       </c>
       <c r="H2" s="0" t="s">
-        <v>488</v>
+        <v>489</v>
       </c>
       <c r="K2" s="0" t="n">
         <f aca="false">D2/C2</f>
         <v>1.81018518518519</v>
       </c>
       <c r="L2" s="0" t="s">
-        <v>489</v>
+        <v>490</v>
       </c>
       <c r="N2" s="0" t="s">
-        <v>490</v>
+        <v>491</v>
       </c>
       <c r="O2" s="0" t="n">
         <v>80</v>
       </c>
       <c r="P2" s="0" t="s">
-        <v>491</v>
+        <v>492</v>
       </c>
       <c r="Q2" s="0" t="n">
         <f aca="false">O2/D2</f>
@@ -13026,7 +13082,7 @@
         <v>1239</v>
       </c>
       <c r="E3" s="0" t="s">
-        <v>492</v>
+        <v>493</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -13034,7 +13090,7 @@
         <v>2175</v>
       </c>
       <c r="E4" s="0" t="s">
-        <v>493</v>
+        <v>494</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -13045,19 +13101,19 @@
         <v>18</v>
       </c>
       <c r="G5" s="0" t="s">
-        <v>494</v>
+        <v>495</v>
       </c>
       <c r="H5" s="0" t="s">
-        <v>495</v>
+        <v>496</v>
       </c>
       <c r="I5" s="0" t="s">
-        <v>496</v>
+        <v>497</v>
       </c>
       <c r="K5" s="0" t="s">
-        <v>497</v>
+        <v>498</v>
       </c>
       <c r="L5" s="0" t="s">
-        <v>498</v>
+        <v>499</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -13065,7 +13121,7 @@
         <v>3732</v>
       </c>
       <c r="E6" s="0" t="s">
-        <v>499</v>
+        <v>500</v>
       </c>
       <c r="G6" s="0" t="n">
         <f aca="false">C6-C2</f>
@@ -13096,27 +13152,27 @@
         <v>22</v>
       </c>
       <c r="G7" s="0" t="s">
-        <v>500</v>
+        <v>501</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="G8" s="14" t="n">
+      <c r="G8" s="11" t="n">
         <f aca="false">C2/C7</f>
         <v>0.0674157303370787</v>
       </c>
       <c r="O8" s="0" t="s">
-        <v>501</v>
+        <v>502</v>
       </c>
       <c r="P8" s="0" t="s">
-        <v>502</v>
+        <v>503</v>
       </c>
       <c r="Q8" s="0" t="s">
-        <v>503</v>
+        <v>504</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="N9" s="0" t="s">
-        <v>504</v>
+        <v>505</v>
       </c>
       <c r="O9" s="0" t="n">
         <v>1</v>
@@ -13132,7 +13188,7 @@
     </row>
     <row r="10" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="N10" s="0" t="s">
-        <v>504</v>
+        <v>505</v>
       </c>
       <c r="O10" s="0" t="n">
         <v>2</v>
@@ -13148,7 +13204,7 @@
     </row>
     <row r="11" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="N11" s="0" t="s">
-        <v>504</v>
+        <v>505</v>
       </c>
       <c r="O11" s="0" t="n">
         <v>294</v>
@@ -13164,7 +13220,7 @@
     </row>
     <row r="13" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="N13" s="0" t="s">
-        <v>505</v>
+        <v>506</v>
       </c>
       <c r="O13" s="0" t="n">
         <v>200</v>
@@ -13172,7 +13228,7 @@
     </row>
     <row r="14" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="N14" s="0" t="s">
-        <v>506</v>
+        <v>507</v>
       </c>
       <c r="O14" s="0" t="n">
         <v>118</v>
@@ -13180,8 +13236,8 @@
     </row>
   </sheetData>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.511811023622047" footer="0.511811023622047"/>
-  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.511805555555555" footer="0.511805555555555"/>
+  <pageSetup paperSize="9" scale="100" firstPageNumber="0" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" useFirstPageNumber="false" horizontalDpi="300" verticalDpi="300" copies="1"/>
   <headerFooter differentFirst="false" differentOddEven="false">
     <oddHeader/>
     <oddFooter/>

--- a/5_筆記/閱讀數據.xlsx
+++ b/5_筆記/閱讀數據.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="514" uniqueCount="508">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="516" uniqueCount="510">
   <si>
     <t xml:space="preserve">索引號</t>
   </si>
@@ -835,6 +835,12 @@
   </si>
   <si>
     <t xml:space="preserve">晉紀二</t>
+  </si>
+  <si>
+    <t xml:space="preserve">諸王就國情況(西晉大小國)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">司馬炎8年至14年</t>
   </si>
   <si>
     <t xml:space="preserve">晉紀三</t>
@@ -1801,7 +1807,7 @@
 </styleSheet>
 </file>
 
-<file path=xl/charts/chart3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/charts/chart2.xml><?xml version="1.0" encoding="utf-8"?>
 <c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <c:lang val="en-US"/>
   <c:roundedCorners val="0"/>
@@ -2156,18 +2162,21 @@
                   <c:v>1.25</c:v>
                 </c:pt>
                 <c:pt idx="79">
-                  <c:v>164.775735294118</c:v>
+                  <c:v>1.28571428571429</c:v>
+                </c:pt>
+                <c:pt idx="80">
+                  <c:v>160.673835125448</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
           </c:yVal>
           <c:smooth val="1"/>
         </c:ser>
-        <c:axId val="37135447"/>
-        <c:axId val="47779490"/>
+        <c:axId val="77021377"/>
+        <c:axId val="65069290"/>
       </c:scatterChart>
       <c:valAx>
-        <c:axId val="37135447"/>
+        <c:axId val="77021377"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -2243,12 +2252,12 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="47779490"/>
+        <c:crossAx val="65069290"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="midCat"/>
       </c:valAx>
       <c:valAx>
-        <c:axId val="47779490"/>
+        <c:axId val="65069290"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -2324,7 +2333,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="37135447"/>
+        <c:crossAx val="77021377"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="midCat"/>
       </c:valAx>
@@ -2363,9 +2372,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>15</xdr:col>
-      <xdr:colOff>670680</xdr:colOff>
+      <xdr:colOff>670320</xdr:colOff>
       <xdr:row>27</xdr:row>
-      <xdr:rowOff>108720</xdr:rowOff>
+      <xdr:rowOff>108360</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame>
       <xdr:nvGraphicFramePr>
@@ -2374,7 +2383,7 @@
       </xdr:nvGraphicFramePr>
       <xdr:xfrm>
         <a:off x="6835320" y="1995120"/>
-        <a:ext cx="4150080" cy="2742480"/>
+        <a:ext cx="4150440" cy="2742120"/>
       </xdr:xfrm>
       <a:graphic>
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
@@ -2392,7 +2401,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:R81"/>
+  <dimension ref="A1:R82"/>
   <sheetFormatPr defaultColWidth="8.68359375" defaultRowHeight="13.5" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="7.76"/>
@@ -2507,19 +2516,19 @@
       </c>
       <c r="O2" s="0" t="n">
         <f aca="false">L2*$L$10</f>
-        <v>-37491.8</v>
+        <v>-37028.9382716049</v>
       </c>
       <c r="P2" s="1" t="n">
         <f aca="false">$C$2+O2</f>
-        <v>6527.2</v>
+        <v>6990.06172839506</v>
       </c>
       <c r="Q2" s="0" t="n">
         <f aca="false">(M2-$F$2)*$L$11</f>
-        <v>2601.65360470217</v>
+        <v>2511.58429231704</v>
       </c>
       <c r="R2" s="1" t="n">
         <f aca="false">$C$2+Q2</f>
-        <v>46620.6536047022</v>
+        <v>46530.584292317</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2570,19 +2579,19 @@
       </c>
       <c r="O3" s="0" t="n">
         <f aca="false">L3*$L$10</f>
-        <v>-43005.3</v>
+        <v>-42474.3703703704</v>
       </c>
       <c r="P3" s="1" t="n">
         <f aca="false">$C$2+O3</f>
-        <v>1013.7</v>
+        <v>1544.62962962964</v>
       </c>
       <c r="Q3" s="0" t="n">
         <f aca="false">(M3-$F$2)*$L$11</f>
-        <v>2852.21414448087</v>
+        <v>2753.47041998802</v>
       </c>
       <c r="R3" s="1" t="n">
         <f aca="false">$C$2+Q3</f>
-        <v>46871.2141444809</v>
+        <v>46772.470419988</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2633,19 +2642,19 @@
       </c>
       <c r="O4" s="0" t="n">
         <f aca="false">L4*$L$10</f>
-        <v>-65059.3</v>
+        <v>-64256.0987654321</v>
       </c>
       <c r="P4" s="1" t="n">
         <f aca="false">$C$2+O4</f>
-        <v>-21040.3</v>
+        <v>-20237.0987654321</v>
       </c>
       <c r="Q4" s="0" t="n">
         <f aca="false">(M4-$F$2)*$L$11</f>
-        <v>3436.8554039645</v>
+        <v>3317.87138455364</v>
       </c>
       <c r="R4" s="1" t="n">
         <f aca="false">$C$2+Q4</f>
-        <v>47455.8554039645</v>
+        <v>47336.8713845537</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2696,19 +2705,19 @@
       </c>
       <c r="O5" s="0" t="n">
         <f aca="false">L5*$L$10</f>
-        <v>-97037.6</v>
+        <v>-95839.6049382716</v>
       </c>
       <c r="P5" s="1" t="n">
         <f aca="false">$C$2+O5</f>
-        <v>-53018.6</v>
+        <v>-51820.6049382716</v>
       </c>
       <c r="Q5" s="0" t="n">
         <f aca="false">(M5-$F$2)*$L$11</f>
-        <v>4142.60092434117</v>
+        <v>3999.18397749358</v>
       </c>
       <c r="R5" s="1" t="n">
         <f aca="false">$C$2+Q5</f>
-        <v>48161.6009243412</v>
+        <v>48018.1839774936</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2759,19 +2768,19 @@
       </c>
       <c r="O6" s="0" t="n">
         <f aca="false">L6*$L$10</f>
-        <v>-146107.75</v>
+        <v>-144303.950617284</v>
       </c>
       <c r="P6" s="1" t="n">
         <f aca="false">$C$2+O6</f>
-        <v>-102088.75</v>
+        <v>-100284.950617284</v>
       </c>
       <c r="Q6" s="0" t="n">
         <f aca="false">(M6-$F$2)*$L$11</f>
-        <v>5470.57178516829</v>
+        <v>5281.18045414979</v>
       </c>
       <c r="R6" s="1" t="n">
         <f aca="false">$C$2+Q6</f>
-        <v>49489.5717851683</v>
+        <v>49300.1804541498</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2822,19 +2831,19 @@
       </c>
       <c r="O7" s="0" t="n">
         <f aca="false">L7*$L$10</f>
-        <v>-162096.9</v>
+        <v>-160095.703703704</v>
       </c>
       <c r="P7" s="1" t="n">
         <f aca="false">$C$2+O7</f>
-        <v>-118077.9</v>
+        <v>-116076.703703704</v>
       </c>
       <c r="Q7" s="0" t="n">
         <f aca="false">(M7-$F$2)*$L$11</f>
-        <v>5687.72425297649</v>
+        <v>5490.81509813131</v>
       </c>
       <c r="R7" s="1" t="n">
         <f aca="false">$C$2+Q7</f>
-        <v>49706.7242529765</v>
+        <v>49509.8150981313</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2885,19 +2894,19 @@
       </c>
       <c r="O8" s="0" t="n">
         <f aca="false">L8*$L$10</f>
-        <v>-162096.9</v>
+        <v>-160095.703703704</v>
       </c>
       <c r="P8" s="1" t="n">
         <f aca="false">$C$2+O8</f>
-        <v>-118077.9</v>
+        <v>-116076.703703704</v>
       </c>
       <c r="Q8" s="0" t="n">
         <f aca="false">(M8-$F$2)*$L$11</f>
-        <v>5687.72425297649</v>
+        <v>5490.81509813131</v>
       </c>
       <c r="R8" s="1" t="n">
         <f aca="false">$C$2+Q8</f>
-        <v>49706.7242529765</v>
+        <v>49509.8150981313</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2972,7 +2981,7 @@
       </c>
       <c r="L10" s="0" t="n">
         <f aca="false">AVERAGE(E:E)</f>
-        <v>-551.35</v>
+        <v>-544.543209876543</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3013,7 +3022,7 @@
       </c>
       <c r="L11" s="0" t="n">
         <f aca="false">AVEDEV(I:I)</f>
-        <v>4.17600899631167</v>
+        <v>4.03143546118304</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5405,21 +5414,55 @@
       <c r="C81" s="1" t="n">
         <v>44820</v>
       </c>
+      <c r="D81" s="1" t="n">
+        <v>44828</v>
+      </c>
       <c r="E81" s="0" t="n">
         <f aca="false">D81-C81+1</f>
-        <v>-44819</v>
+        <v>9</v>
       </c>
       <c r="F81" s="0" t="n">
         <f aca="false">G80+1</f>
         <v>273</v>
       </c>
+      <c r="G81" s="0" t="n">
+        <v>279</v>
+      </c>
       <c r="H81" s="0" t="n">
         <f aca="false">IF(F81*G81&lt;0,ABS(F81)+ABS(G81),G81-F81+1)</f>
-        <v>-272</v>
+        <v>7</v>
       </c>
       <c r="I81" s="0" t="n">
         <f aca="false">E81/H81</f>
-        <v>164.775735294118</v>
+        <v>1.28571428571429</v>
+      </c>
+    </row>
+    <row r="82" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A82" s="0" t="n">
+        <v>703</v>
+      </c>
+      <c r="B82" s="0" t="str">
+        <f aca="false">"卷"&amp;ROW(B81)</f>
+        <v>卷81</v>
+      </c>
+      <c r="C82" s="1" t="n">
+        <v>44829</v>
+      </c>
+      <c r="E82" s="0" t="n">
+        <f aca="false">D82-C82+1</f>
+        <v>-44828</v>
+      </c>
+      <c r="F82" s="0" t="n">
+        <f aca="false">G81+1</f>
+        <v>280</v>
+      </c>
+      <c r="H82" s="0" t="n">
+        <f aca="false">IF(F82*G82&lt;0,ABS(F82)+ABS(G82),G82-F82+1)</f>
+        <v>-279</v>
+      </c>
+      <c r="I82" s="0" t="n">
+        <f aca="false">E82/H82</f>
+        <v>160.673835125448</v>
       </c>
     </row>
   </sheetData>
@@ -7846,7 +7889,7 @@
         <v>701|[卷79](5_筆記/资治通鉴79.html)|晉紀一|265|272|||曹奐6年至7年、司馬炎至7年</v>
       </c>
     </row>
-    <row r="81" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="81" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A81" s="0" t="n">
         <v>702</v>
       </c>
@@ -7863,35 +7906,41 @@
       </c>
       <c r="E81" s="0" t="n">
         <f aca="false">VLOOKUP($A81,統計!$A:$G,7,)</f>
-        <v>0</v>
+        <v>279</v>
+      </c>
+      <c r="G81" s="0" t="s">
+        <v>271</v>
+      </c>
+      <c r="H81" s="0" t="s">
+        <v>272</v>
       </c>
       <c r="I81" s="0" t="str">
         <f aca="false">A81&amp;"|"&amp;"["&amp;B81&amp;"](5_筆記/资治通鉴"&amp;SUBSTITUTE(B81,"卷","")&amp;".html)|"&amp;C81&amp;"|"&amp;D81&amp;"|"&amp;E81&amp;"|"&amp;F81&amp;"|"&amp;G81&amp;"|"&amp;H81</f>
-        <v>702|[卷80](5_筆記/资治通鉴80.html)|晉紀二|273|0|||</v>
+        <v>702|[卷80](5_筆記/资治通鉴80.html)|晉紀二|273|279||諸王就國情況(西晉大小國)|司馬炎8年至14年</v>
       </c>
     </row>
     <row r="82" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A82" s="0" t="n">
         <v>703</v>
       </c>
-      <c r="B82" s="0" t="e">
+      <c r="B82" s="0" t="str">
         <f aca="false">VLOOKUP($A82,統計!$A:$G,2,)</f>
-        <v>#N/A</v>
+        <v>卷81</v>
       </c>
       <c r="C82" s="0" t="s">
-        <v>271</v>
-      </c>
-      <c r="D82" s="0" t="e">
+        <v>273</v>
+      </c>
+      <c r="D82" s="0" t="n">
         <f aca="false">VLOOKUP($A82,統計!$A:$G,6,)</f>
-        <v>#N/A</v>
-      </c>
-      <c r="E82" s="0" t="e">
+        <v>280</v>
+      </c>
+      <c r="E82" s="0" t="n">
         <f aca="false">VLOOKUP($A82,統計!$A:$G,7,)</f>
-        <v>#N/A</v>
-      </c>
-      <c r="I82" s="0" t="e">
+        <v>0</v>
+      </c>
+      <c r="I82" s="0" t="str">
         <f aca="false">A82&amp;"|"&amp;"["&amp;B82&amp;"](5_筆記/资治通鉴"&amp;SUBSTITUTE(B82,"卷","")&amp;".html)|"&amp;C82&amp;"|"&amp;D82&amp;"|"&amp;E82&amp;"|"&amp;F82&amp;"|"&amp;G82&amp;"|"&amp;H82</f>
-        <v>#N/A</v>
+        <v>703|[卷81](5_筆記/资治通鉴81.html)|晉紀三|280|0|||</v>
       </c>
     </row>
     <row r="83" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -7903,7 +7952,7 @@
         <v>#N/A</v>
       </c>
       <c r="C83" s="0" t="s">
-        <v>272</v>
+        <v>274</v>
       </c>
       <c r="D83" s="0" t="e">
         <f aca="false">VLOOKUP($A83,統計!$A:$G,6,)</f>
@@ -7927,7 +7976,7 @@
         <v>#N/A</v>
       </c>
       <c r="C84" s="0" t="s">
-        <v>273</v>
+        <v>275</v>
       </c>
       <c r="D84" s="0" t="e">
         <f aca="false">VLOOKUP($A84,統計!$A:$G,6,)</f>
@@ -7951,7 +8000,7 @@
         <v>#N/A</v>
       </c>
       <c r="C85" s="0" t="s">
-        <v>274</v>
+        <v>276</v>
       </c>
       <c r="D85" s="0" t="e">
         <f aca="false">VLOOKUP($A85,統計!$A:$G,6,)</f>
@@ -7975,7 +8024,7 @@
         <v>#N/A</v>
       </c>
       <c r="C86" s="0" t="s">
-        <v>275</v>
+        <v>277</v>
       </c>
       <c r="D86" s="0" t="e">
         <f aca="false">VLOOKUP($A86,統計!$A:$G,6,)</f>
@@ -7999,7 +8048,7 @@
         <v>#N/A</v>
       </c>
       <c r="C87" s="0" t="s">
-        <v>276</v>
+        <v>278</v>
       </c>
       <c r="D87" s="0" t="e">
         <f aca="false">VLOOKUP($A87,統計!$A:$G,6,)</f>
@@ -8023,7 +8072,7 @@
         <v>#N/A</v>
       </c>
       <c r="C88" s="0" t="s">
-        <v>277</v>
+        <v>279</v>
       </c>
       <c r="D88" s="0" t="e">
         <f aca="false">VLOOKUP($A88,統計!$A:$G,6,)</f>
@@ -8047,7 +8096,7 @@
         <v>#N/A</v>
       </c>
       <c r="C89" s="0" t="s">
-        <v>278</v>
+        <v>280</v>
       </c>
       <c r="D89" s="0" t="e">
         <f aca="false">VLOOKUP($A89,統計!$A:$G,6,)</f>
@@ -8071,7 +8120,7 @@
         <v>#N/A</v>
       </c>
       <c r="C90" s="0" t="s">
-        <v>279</v>
+        <v>281</v>
       </c>
       <c r="D90" s="0" t="e">
         <f aca="false">VLOOKUP($A90,統計!$A:$G,6,)</f>
@@ -8095,7 +8144,7 @@
         <v>#N/A</v>
       </c>
       <c r="C91" s="0" t="s">
-        <v>280</v>
+        <v>282</v>
       </c>
       <c r="D91" s="0" t="e">
         <f aca="false">VLOOKUP($A91,統計!$A:$G,6,)</f>
@@ -8119,7 +8168,7 @@
         <v>#N/A</v>
       </c>
       <c r="C92" s="0" t="s">
-        <v>281</v>
+        <v>283</v>
       </c>
       <c r="D92" s="0" t="e">
         <f aca="false">VLOOKUP($A92,統計!$A:$G,6,)</f>
@@ -8143,7 +8192,7 @@
         <v>#N/A</v>
       </c>
       <c r="C93" s="0" t="s">
-        <v>282</v>
+        <v>284</v>
       </c>
       <c r="D93" s="0" t="e">
         <f aca="false">VLOOKUP($A93,統計!$A:$G,6,)</f>
@@ -8167,7 +8216,7 @@
         <v>#N/A</v>
       </c>
       <c r="C94" s="0" t="s">
-        <v>283</v>
+        <v>285</v>
       </c>
       <c r="D94" s="0" t="e">
         <f aca="false">VLOOKUP($A94,統計!$A:$G,6,)</f>
@@ -8191,7 +8240,7 @@
         <v>#N/A</v>
       </c>
       <c r="C95" s="0" t="s">
-        <v>284</v>
+        <v>286</v>
       </c>
       <c r="D95" s="0" t="e">
         <f aca="false">VLOOKUP($A95,統計!$A:$G,6,)</f>
@@ -8215,7 +8264,7 @@
         <v>#N/A</v>
       </c>
       <c r="C96" s="0" t="s">
-        <v>285</v>
+        <v>287</v>
       </c>
       <c r="D96" s="0" t="e">
         <f aca="false">VLOOKUP($A96,統計!$A:$G,6,)</f>
@@ -8239,7 +8288,7 @@
         <v>#N/A</v>
       </c>
       <c r="C97" s="0" t="s">
-        <v>286</v>
+        <v>288</v>
       </c>
       <c r="D97" s="0" t="e">
         <f aca="false">VLOOKUP($A97,統計!$A:$G,6,)</f>
@@ -8263,7 +8312,7 @@
         <v>#N/A</v>
       </c>
       <c r="C98" s="0" t="s">
-        <v>287</v>
+        <v>289</v>
       </c>
       <c r="D98" s="0" t="e">
         <f aca="false">VLOOKUP($A98,統計!$A:$G,6,)</f>
@@ -8287,7 +8336,7 @@
         <v>#N/A</v>
       </c>
       <c r="C99" s="0" t="s">
-        <v>288</v>
+        <v>290</v>
       </c>
       <c r="D99" s="0" t="e">
         <f aca="false">VLOOKUP($A99,統計!$A:$G,6,)</f>
@@ -8311,7 +8360,7 @@
         <v>#N/A</v>
       </c>
       <c r="C100" s="0" t="s">
-        <v>289</v>
+        <v>291</v>
       </c>
       <c r="D100" s="0" t="e">
         <f aca="false">VLOOKUP($A100,統計!$A:$G,6,)</f>
@@ -8335,7 +8384,7 @@
         <v>#N/A</v>
       </c>
       <c r="C101" s="0" t="s">
-        <v>290</v>
+        <v>292</v>
       </c>
       <c r="D101" s="0" t="e">
         <f aca="false">VLOOKUP($A101,統計!$A:$G,6,)</f>
@@ -8359,7 +8408,7 @@
         <v>#N/A</v>
       </c>
       <c r="C102" s="0" t="s">
-        <v>291</v>
+        <v>293</v>
       </c>
       <c r="D102" s="0" t="e">
         <f aca="false">VLOOKUP($A102,統計!$A:$G,6,)</f>
@@ -8383,7 +8432,7 @@
         <v>#N/A</v>
       </c>
       <c r="C103" s="0" t="s">
-        <v>292</v>
+        <v>294</v>
       </c>
       <c r="D103" s="0" t="e">
         <f aca="false">VLOOKUP($A103,統計!$A:$G,6,)</f>
@@ -8407,7 +8456,7 @@
         <v>#N/A</v>
       </c>
       <c r="C104" s="0" t="s">
-        <v>293</v>
+        <v>295</v>
       </c>
       <c r="D104" s="0" t="e">
         <f aca="false">VLOOKUP($A104,統計!$A:$G,6,)</f>
@@ -8431,7 +8480,7 @@
         <v>#N/A</v>
       </c>
       <c r="C105" s="0" t="s">
-        <v>294</v>
+        <v>296</v>
       </c>
       <c r="D105" s="0" t="e">
         <f aca="false">VLOOKUP($A105,統計!$A:$G,6,)</f>
@@ -8455,7 +8504,7 @@
         <v>#N/A</v>
       </c>
       <c r="C106" s="0" t="s">
-        <v>295</v>
+        <v>297</v>
       </c>
       <c r="D106" s="0" t="e">
         <f aca="false">VLOOKUP($A106,統計!$A:$G,6,)</f>
@@ -8479,7 +8528,7 @@
         <v>#N/A</v>
       </c>
       <c r="C107" s="0" t="s">
-        <v>296</v>
+        <v>298</v>
       </c>
       <c r="D107" s="0" t="e">
         <f aca="false">VLOOKUP($A107,統計!$A:$G,6,)</f>
@@ -8503,7 +8552,7 @@
         <v>#N/A</v>
       </c>
       <c r="C108" s="0" t="s">
-        <v>297</v>
+        <v>299</v>
       </c>
       <c r="D108" s="0" t="e">
         <f aca="false">VLOOKUP($A108,統計!$A:$G,6,)</f>
@@ -8527,7 +8576,7 @@
         <v>#N/A</v>
       </c>
       <c r="C109" s="0" t="s">
-        <v>298</v>
+        <v>300</v>
       </c>
       <c r="D109" s="0" t="e">
         <f aca="false">VLOOKUP($A109,統計!$A:$G,6,)</f>
@@ -8551,7 +8600,7 @@
         <v>#N/A</v>
       </c>
       <c r="C110" s="0" t="s">
-        <v>299</v>
+        <v>301</v>
       </c>
       <c r="D110" s="0" t="e">
         <f aca="false">VLOOKUP($A110,統計!$A:$G,6,)</f>
@@ -8575,7 +8624,7 @@
         <v>#N/A</v>
       </c>
       <c r="C111" s="0" t="s">
-        <v>300</v>
+        <v>302</v>
       </c>
       <c r="D111" s="0" t="e">
         <f aca="false">VLOOKUP($A111,統計!$A:$G,6,)</f>
@@ -8599,7 +8648,7 @@
         <v>#N/A</v>
       </c>
       <c r="C112" s="0" t="s">
-        <v>301</v>
+        <v>303</v>
       </c>
       <c r="D112" s="0" t="e">
         <f aca="false">VLOOKUP($A112,統計!$A:$G,6,)</f>
@@ -8623,7 +8672,7 @@
         <v>#N/A</v>
       </c>
       <c r="C113" s="0" t="s">
-        <v>302</v>
+        <v>304</v>
       </c>
       <c r="D113" s="0" t="e">
         <f aca="false">VLOOKUP($A113,統計!$A:$G,6,)</f>
@@ -8647,7 +8696,7 @@
         <v>#N/A</v>
       </c>
       <c r="C114" s="0" t="s">
-        <v>303</v>
+        <v>305</v>
       </c>
       <c r="D114" s="0" t="e">
         <f aca="false">VLOOKUP($A114,統計!$A:$G,6,)</f>
@@ -8671,7 +8720,7 @@
         <v>#N/A</v>
       </c>
       <c r="C115" s="0" t="s">
-        <v>304</v>
+        <v>306</v>
       </c>
       <c r="D115" s="0" t="e">
         <f aca="false">VLOOKUP($A115,統計!$A:$G,6,)</f>
@@ -8695,7 +8744,7 @@
         <v>#N/A</v>
       </c>
       <c r="C116" s="0" t="s">
-        <v>305</v>
+        <v>307</v>
       </c>
       <c r="D116" s="0" t="e">
         <f aca="false">VLOOKUP($A116,統計!$A:$G,6,)</f>
@@ -8719,7 +8768,7 @@
         <v>#N/A</v>
       </c>
       <c r="C117" s="0" t="s">
-        <v>306</v>
+        <v>308</v>
       </c>
       <c r="D117" s="0" t="e">
         <f aca="false">VLOOKUP($A117,統計!$A:$G,6,)</f>
@@ -8743,7 +8792,7 @@
         <v>#N/A</v>
       </c>
       <c r="C118" s="0" t="s">
-        <v>307</v>
+        <v>309</v>
       </c>
       <c r="D118" s="0" t="e">
         <f aca="false">VLOOKUP($A118,統計!$A:$G,6,)</f>
@@ -8767,7 +8816,7 @@
         <v>#N/A</v>
       </c>
       <c r="C119" s="0" t="s">
-        <v>308</v>
+        <v>310</v>
       </c>
       <c r="D119" s="0" t="e">
         <f aca="false">VLOOKUP($A119,統計!$A:$G,6,)</f>
@@ -8791,7 +8840,7 @@
         <v>#N/A</v>
       </c>
       <c r="C120" s="0" t="s">
-        <v>309</v>
+        <v>311</v>
       </c>
       <c r="D120" s="0" t="e">
         <f aca="false">VLOOKUP($A120,統計!$A:$G,6,)</f>
@@ -8815,7 +8864,7 @@
         <v>#N/A</v>
       </c>
       <c r="C121" s="0" t="s">
-        <v>310</v>
+        <v>312</v>
       </c>
       <c r="D121" s="0" t="e">
         <f aca="false">VLOOKUP($A121,統計!$A:$G,6,)</f>
@@ -8839,7 +8888,7 @@
         <v>#N/A</v>
       </c>
       <c r="C122" s="0" t="s">
-        <v>311</v>
+        <v>313</v>
       </c>
       <c r="D122" s="0" t="e">
         <f aca="false">VLOOKUP($A122,統計!$A:$G,6,)</f>
@@ -8863,7 +8912,7 @@
         <v>#N/A</v>
       </c>
       <c r="C123" s="0" t="s">
-        <v>312</v>
+        <v>314</v>
       </c>
       <c r="D123" s="0" t="e">
         <f aca="false">VLOOKUP($A123,統計!$A:$G,6,)</f>
@@ -8887,7 +8936,7 @@
         <v>#N/A</v>
       </c>
       <c r="C124" s="0" t="s">
-        <v>313</v>
+        <v>315</v>
       </c>
       <c r="D124" s="0" t="e">
         <f aca="false">VLOOKUP($A124,統計!$A:$G,6,)</f>
@@ -8911,7 +8960,7 @@
         <v>#N/A</v>
       </c>
       <c r="C125" s="0" t="s">
-        <v>314</v>
+        <v>316</v>
       </c>
       <c r="D125" s="0" t="e">
         <f aca="false">VLOOKUP($A125,統計!$A:$G,6,)</f>
@@ -8935,7 +8984,7 @@
         <v>#N/A</v>
       </c>
       <c r="C126" s="0" t="s">
-        <v>315</v>
+        <v>317</v>
       </c>
       <c r="D126" s="0" t="e">
         <f aca="false">VLOOKUP($A126,統計!$A:$G,6,)</f>
@@ -8959,7 +9008,7 @@
         <v>#N/A</v>
       </c>
       <c r="C127" s="0" t="s">
-        <v>316</v>
+        <v>318</v>
       </c>
       <c r="D127" s="0" t="e">
         <f aca="false">VLOOKUP($A127,統計!$A:$G,6,)</f>
@@ -8983,7 +9032,7 @@
         <v>#N/A</v>
       </c>
       <c r="C128" s="0" t="s">
-        <v>317</v>
+        <v>319</v>
       </c>
       <c r="D128" s="0" t="e">
         <f aca="false">VLOOKUP($A128,統計!$A:$G,6,)</f>
@@ -9007,7 +9056,7 @@
         <v>#N/A</v>
       </c>
       <c r="C129" s="0" t="s">
-        <v>318</v>
+        <v>320</v>
       </c>
       <c r="D129" s="0" t="e">
         <f aca="false">VLOOKUP($A129,統計!$A:$G,6,)</f>
@@ -9031,7 +9080,7 @@
         <v>#N/A</v>
       </c>
       <c r="C130" s="0" t="s">
-        <v>319</v>
+        <v>321</v>
       </c>
       <c r="D130" s="0" t="e">
         <f aca="false">VLOOKUP($A130,統計!$A:$G,6,)</f>
@@ -9055,7 +9104,7 @@
         <v>#N/A</v>
       </c>
       <c r="C131" s="0" t="s">
-        <v>320</v>
+        <v>322</v>
       </c>
       <c r="D131" s="0" t="e">
         <f aca="false">VLOOKUP($A131,統計!$A:$G,6,)</f>
@@ -9079,7 +9128,7 @@
         <v>#N/A</v>
       </c>
       <c r="C132" s="0" t="s">
-        <v>321</v>
+        <v>323</v>
       </c>
       <c r="D132" s="0" t="e">
         <f aca="false">VLOOKUP($A132,統計!$A:$G,6,)</f>
@@ -9103,7 +9152,7 @@
         <v>#N/A</v>
       </c>
       <c r="C133" s="0" t="s">
-        <v>322</v>
+        <v>324</v>
       </c>
       <c r="D133" s="0" t="e">
         <f aca="false">VLOOKUP($A133,統計!$A:$G,6,)</f>
@@ -9127,7 +9176,7 @@
         <v>#N/A</v>
       </c>
       <c r="C134" s="0" t="s">
-        <v>323</v>
+        <v>325</v>
       </c>
       <c r="D134" s="0" t="e">
         <f aca="false">VLOOKUP($A134,統計!$A:$G,6,)</f>
@@ -9151,7 +9200,7 @@
         <v>#N/A</v>
       </c>
       <c r="C135" s="0" t="s">
-        <v>324</v>
+        <v>326</v>
       </c>
       <c r="D135" s="0" t="e">
         <f aca="false">VLOOKUP($A135,統計!$A:$G,6,)</f>
@@ -9175,7 +9224,7 @@
         <v>#N/A</v>
       </c>
       <c r="C136" s="0" t="s">
-        <v>325</v>
+        <v>327</v>
       </c>
       <c r="D136" s="0" t="e">
         <f aca="false">VLOOKUP($A136,統計!$A:$G,6,)</f>
@@ -9199,7 +9248,7 @@
         <v>#N/A</v>
       </c>
       <c r="C137" s="0" t="s">
-        <v>326</v>
+        <v>328</v>
       </c>
       <c r="D137" s="0" t="e">
         <f aca="false">VLOOKUP($A137,統計!$A:$G,6,)</f>
@@ -9223,7 +9272,7 @@
         <v>#N/A</v>
       </c>
       <c r="C138" s="0" t="s">
-        <v>327</v>
+        <v>329</v>
       </c>
       <c r="D138" s="0" t="e">
         <f aca="false">VLOOKUP($A138,統計!$A:$G,6,)</f>
@@ -9247,7 +9296,7 @@
         <v>#N/A</v>
       </c>
       <c r="C139" s="0" t="s">
-        <v>328</v>
+        <v>330</v>
       </c>
       <c r="D139" s="0" t="e">
         <f aca="false">VLOOKUP($A139,統計!$A:$G,6,)</f>
@@ -9271,7 +9320,7 @@
         <v>#N/A</v>
       </c>
       <c r="C140" s="0" t="s">
-        <v>329</v>
+        <v>331</v>
       </c>
       <c r="D140" s="0" t="e">
         <f aca="false">VLOOKUP($A140,統計!$A:$G,6,)</f>
@@ -9295,7 +9344,7 @@
         <v>#N/A</v>
       </c>
       <c r="C141" s="0" t="s">
-        <v>330</v>
+        <v>332</v>
       </c>
       <c r="D141" s="0" t="e">
         <f aca="false">VLOOKUP($A141,統計!$A:$G,6,)</f>
@@ -9319,7 +9368,7 @@
         <v>#N/A</v>
       </c>
       <c r="C142" s="0" t="s">
-        <v>331</v>
+        <v>333</v>
       </c>
       <c r="D142" s="0" t="e">
         <f aca="false">VLOOKUP($A142,統計!$A:$G,6,)</f>
@@ -9343,7 +9392,7 @@
         <v>#N/A</v>
       </c>
       <c r="C143" s="0" t="s">
-        <v>332</v>
+        <v>334</v>
       </c>
       <c r="D143" s="0" t="e">
         <f aca="false">VLOOKUP($A143,統計!$A:$G,6,)</f>
@@ -9367,7 +9416,7 @@
         <v>#N/A</v>
       </c>
       <c r="C144" s="0" t="s">
-        <v>333</v>
+        <v>335</v>
       </c>
       <c r="D144" s="0" t="e">
         <f aca="false">VLOOKUP($A144,統計!$A:$G,6,)</f>
@@ -9391,7 +9440,7 @@
         <v>#N/A</v>
       </c>
       <c r="C145" s="0" t="s">
-        <v>334</v>
+        <v>336</v>
       </c>
       <c r="D145" s="0" t="e">
         <f aca="false">VLOOKUP($A145,統計!$A:$G,6,)</f>
@@ -9415,7 +9464,7 @@
         <v>#N/A</v>
       </c>
       <c r="C146" s="0" t="s">
-        <v>335</v>
+        <v>337</v>
       </c>
       <c r="D146" s="0" t="e">
         <f aca="false">VLOOKUP($A146,統計!$A:$G,6,)</f>
@@ -9439,7 +9488,7 @@
         <v>#N/A</v>
       </c>
       <c r="C147" s="0" t="s">
-        <v>336</v>
+        <v>338</v>
       </c>
       <c r="D147" s="0" t="e">
         <f aca="false">VLOOKUP($A147,統計!$A:$G,6,)</f>
@@ -9463,7 +9512,7 @@
         <v>#N/A</v>
       </c>
       <c r="C148" s="0" t="s">
-        <v>337</v>
+        <v>339</v>
       </c>
       <c r="D148" s="0" t="e">
         <f aca="false">VLOOKUP($A148,統計!$A:$G,6,)</f>
@@ -9487,7 +9536,7 @@
         <v>#N/A</v>
       </c>
       <c r="C149" s="0" t="s">
-        <v>338</v>
+        <v>340</v>
       </c>
       <c r="D149" s="0" t="e">
         <f aca="false">VLOOKUP($A149,統計!$A:$G,6,)</f>
@@ -9511,7 +9560,7 @@
         <v>#N/A</v>
       </c>
       <c r="C150" s="0" t="s">
-        <v>339</v>
+        <v>341</v>
       </c>
       <c r="D150" s="0" t="e">
         <f aca="false">VLOOKUP($A150,統計!$A:$G,6,)</f>
@@ -9535,7 +9584,7 @@
         <v>#N/A</v>
       </c>
       <c r="C151" s="0" t="s">
-        <v>340</v>
+        <v>342</v>
       </c>
       <c r="D151" s="0" t="e">
         <f aca="false">VLOOKUP($A151,統計!$A:$G,6,)</f>
@@ -9559,7 +9608,7 @@
         <v>#N/A</v>
       </c>
       <c r="C152" s="0" t="s">
-        <v>341</v>
+        <v>343</v>
       </c>
       <c r="D152" s="0" t="e">
         <f aca="false">VLOOKUP($A152,統計!$A:$G,6,)</f>
@@ -9583,7 +9632,7 @@
         <v>#N/A</v>
       </c>
       <c r="C153" s="0" t="s">
-        <v>342</v>
+        <v>344</v>
       </c>
       <c r="D153" s="0" t="e">
         <f aca="false">VLOOKUP($A153,統計!$A:$G,6,)</f>
@@ -9607,7 +9656,7 @@
         <v>#N/A</v>
       </c>
       <c r="C154" s="0" t="s">
-        <v>343</v>
+        <v>345</v>
       </c>
       <c r="D154" s="0" t="e">
         <f aca="false">VLOOKUP($A154,統計!$A:$G,6,)</f>
@@ -9631,7 +9680,7 @@
         <v>#N/A</v>
       </c>
       <c r="C155" s="0" t="s">
-        <v>344</v>
+        <v>346</v>
       </c>
       <c r="D155" s="0" t="e">
         <f aca="false">VLOOKUP($A155,統計!$A:$G,6,)</f>
@@ -9655,7 +9704,7 @@
         <v>#N/A</v>
       </c>
       <c r="C156" s="0" t="s">
-        <v>345</v>
+        <v>347</v>
       </c>
       <c r="D156" s="0" t="e">
         <f aca="false">VLOOKUP($A156,統計!$A:$G,6,)</f>
@@ -9679,7 +9728,7 @@
         <v>#N/A</v>
       </c>
       <c r="C157" s="0" t="s">
-        <v>346</v>
+        <v>348</v>
       </c>
       <c r="D157" s="0" t="e">
         <f aca="false">VLOOKUP($A157,統計!$A:$G,6,)</f>
@@ -9703,7 +9752,7 @@
         <v>#N/A</v>
       </c>
       <c r="C158" s="0" t="s">
-        <v>347</v>
+        <v>349</v>
       </c>
       <c r="D158" s="0" t="e">
         <f aca="false">VLOOKUP($A158,統計!$A:$G,6,)</f>
@@ -9727,7 +9776,7 @@
         <v>#N/A</v>
       </c>
       <c r="C159" s="0" t="s">
-        <v>348</v>
+        <v>350</v>
       </c>
       <c r="D159" s="0" t="e">
         <f aca="false">VLOOKUP($A159,統計!$A:$G,6,)</f>
@@ -9751,7 +9800,7 @@
         <v>#N/A</v>
       </c>
       <c r="C160" s="0" t="s">
-        <v>349</v>
+        <v>351</v>
       </c>
       <c r="D160" s="0" t="e">
         <f aca="false">VLOOKUP($A160,統計!$A:$G,6,)</f>
@@ -9775,7 +9824,7 @@
         <v>#N/A</v>
       </c>
       <c r="C161" s="0" t="s">
-        <v>350</v>
+        <v>352</v>
       </c>
       <c r="D161" s="0" t="e">
         <f aca="false">VLOOKUP($A161,統計!$A:$G,6,)</f>
@@ -9799,7 +9848,7 @@
         <v>#N/A</v>
       </c>
       <c r="C162" s="0" t="s">
-        <v>351</v>
+        <v>353</v>
       </c>
       <c r="D162" s="0" t="e">
         <f aca="false">VLOOKUP($A162,統計!$A:$G,6,)</f>
@@ -9823,7 +9872,7 @@
         <v>#N/A</v>
       </c>
       <c r="C163" s="0" t="s">
-        <v>352</v>
+        <v>354</v>
       </c>
       <c r="D163" s="0" t="e">
         <f aca="false">VLOOKUP($A163,統計!$A:$G,6,)</f>
@@ -9847,7 +9896,7 @@
         <v>#N/A</v>
       </c>
       <c r="C164" s="0" t="s">
-        <v>353</v>
+        <v>355</v>
       </c>
       <c r="D164" s="0" t="e">
         <f aca="false">VLOOKUP($A164,統計!$A:$G,6,)</f>
@@ -9871,7 +9920,7 @@
         <v>#N/A</v>
       </c>
       <c r="C165" s="0" t="s">
-        <v>354</v>
+        <v>356</v>
       </c>
       <c r="D165" s="0" t="e">
         <f aca="false">VLOOKUP($A165,統計!$A:$G,6,)</f>
@@ -9895,7 +9944,7 @@
         <v>#N/A</v>
       </c>
       <c r="C166" s="0" t="s">
-        <v>355</v>
+        <v>357</v>
       </c>
       <c r="D166" s="0" t="e">
         <f aca="false">VLOOKUP($A166,統計!$A:$G,6,)</f>
@@ -9919,7 +9968,7 @@
         <v>#N/A</v>
       </c>
       <c r="C167" s="0" t="s">
-        <v>356</v>
+        <v>358</v>
       </c>
       <c r="D167" s="0" t="e">
         <f aca="false">VLOOKUP($A167,統計!$A:$G,6,)</f>
@@ -9943,7 +9992,7 @@
         <v>#N/A</v>
       </c>
       <c r="C168" s="0" t="s">
-        <v>357</v>
+        <v>359</v>
       </c>
       <c r="D168" s="0" t="e">
         <f aca="false">VLOOKUP($A168,統計!$A:$G,6,)</f>
@@ -9967,7 +10016,7 @@
         <v>#N/A</v>
       </c>
       <c r="C169" s="0" t="s">
-        <v>358</v>
+        <v>360</v>
       </c>
       <c r="D169" s="0" t="e">
         <f aca="false">VLOOKUP($A169,統計!$A:$G,6,)</f>
@@ -9991,7 +10040,7 @@
         <v>#N/A</v>
       </c>
       <c r="C170" s="0" t="s">
-        <v>359</v>
+        <v>361</v>
       </c>
       <c r="D170" s="0" t="e">
         <f aca="false">VLOOKUP($A170,統計!$A:$G,6,)</f>
@@ -10015,7 +10064,7 @@
         <v>#N/A</v>
       </c>
       <c r="C171" s="0" t="s">
-        <v>360</v>
+        <v>362</v>
       </c>
       <c r="D171" s="0" t="e">
         <f aca="false">VLOOKUP($A171,統計!$A:$G,6,)</f>
@@ -10039,7 +10088,7 @@
         <v>#N/A</v>
       </c>
       <c r="C172" s="0" t="s">
-        <v>361</v>
+        <v>363</v>
       </c>
       <c r="D172" s="0" t="e">
         <f aca="false">VLOOKUP($A172,統計!$A:$G,6,)</f>
@@ -10063,7 +10112,7 @@
         <v>#N/A</v>
       </c>
       <c r="C173" s="0" t="s">
-        <v>362</v>
+        <v>364</v>
       </c>
       <c r="D173" s="0" t="e">
         <f aca="false">VLOOKUP($A173,統計!$A:$G,6,)</f>
@@ -10087,7 +10136,7 @@
         <v>#N/A</v>
       </c>
       <c r="C174" s="0" t="s">
-        <v>363</v>
+        <v>365</v>
       </c>
       <c r="D174" s="0" t="e">
         <f aca="false">VLOOKUP($A174,統計!$A:$G,6,)</f>
@@ -10111,7 +10160,7 @@
         <v>#N/A</v>
       </c>
       <c r="C175" s="0" t="s">
-        <v>364</v>
+        <v>366</v>
       </c>
       <c r="D175" s="0" t="e">
         <f aca="false">VLOOKUP($A175,統計!$A:$G,6,)</f>
@@ -10135,7 +10184,7 @@
         <v>#N/A</v>
       </c>
       <c r="C176" s="0" t="s">
-        <v>365</v>
+        <v>367</v>
       </c>
       <c r="D176" s="0" t="e">
         <f aca="false">VLOOKUP($A176,統計!$A:$G,6,)</f>
@@ -10159,7 +10208,7 @@
         <v>#N/A</v>
       </c>
       <c r="C177" s="0" t="s">
-        <v>366</v>
+        <v>368</v>
       </c>
       <c r="D177" s="0" t="e">
         <f aca="false">VLOOKUP($A177,統計!$A:$G,6,)</f>
@@ -10183,7 +10232,7 @@
         <v>#N/A</v>
       </c>
       <c r="C178" s="0" t="s">
-        <v>367</v>
+        <v>369</v>
       </c>
       <c r="D178" s="0" t="e">
         <f aca="false">VLOOKUP($A178,統計!$A:$G,6,)</f>
@@ -10207,7 +10256,7 @@
         <v>#N/A</v>
       </c>
       <c r="C179" s="0" t="s">
-        <v>368</v>
+        <v>370</v>
       </c>
       <c r="D179" s="0" t="e">
         <f aca="false">VLOOKUP($A179,統計!$A:$G,6,)</f>
@@ -10231,7 +10280,7 @@
         <v>#N/A</v>
       </c>
       <c r="C180" s="0" t="s">
-        <v>369</v>
+        <v>371</v>
       </c>
       <c r="D180" s="0" t="e">
         <f aca="false">VLOOKUP($A180,統計!$A:$G,6,)</f>
@@ -10255,7 +10304,7 @@
         <v>#N/A</v>
       </c>
       <c r="C181" s="0" t="s">
-        <v>370</v>
+        <v>372</v>
       </c>
       <c r="D181" s="0" t="e">
         <f aca="false">VLOOKUP($A181,統計!$A:$G,6,)</f>
@@ -10279,7 +10328,7 @@
         <v>#N/A</v>
       </c>
       <c r="C182" s="0" t="s">
-        <v>371</v>
+        <v>373</v>
       </c>
       <c r="D182" s="0" t="e">
         <f aca="false">VLOOKUP($A182,統計!$A:$G,6,)</f>
@@ -10303,7 +10352,7 @@
         <v>#N/A</v>
       </c>
       <c r="C183" s="0" t="s">
-        <v>372</v>
+        <v>374</v>
       </c>
       <c r="D183" s="0" t="e">
         <f aca="false">VLOOKUP($A183,統計!$A:$G,6,)</f>
@@ -10327,7 +10376,7 @@
         <v>#N/A</v>
       </c>
       <c r="C184" s="0" t="s">
-        <v>373</v>
+        <v>375</v>
       </c>
       <c r="D184" s="0" t="e">
         <f aca="false">VLOOKUP($A184,統計!$A:$G,6,)</f>
@@ -10351,7 +10400,7 @@
         <v>#N/A</v>
       </c>
       <c r="C185" s="0" t="s">
-        <v>374</v>
+        <v>376</v>
       </c>
       <c r="D185" s="0" t="e">
         <f aca="false">VLOOKUP($A185,統計!$A:$G,6,)</f>
@@ -10375,7 +10424,7 @@
         <v>#N/A</v>
       </c>
       <c r="C186" s="0" t="s">
-        <v>375</v>
+        <v>377</v>
       </c>
       <c r="D186" s="0" t="e">
         <f aca="false">VLOOKUP($A186,統計!$A:$G,6,)</f>
@@ -10399,7 +10448,7 @@
         <v>#N/A</v>
       </c>
       <c r="C187" s="0" t="s">
-        <v>376</v>
+        <v>378</v>
       </c>
       <c r="D187" s="0" t="e">
         <f aca="false">VLOOKUP($A187,統計!$A:$G,6,)</f>
@@ -10423,7 +10472,7 @@
         <v>#N/A</v>
       </c>
       <c r="C188" s="0" t="s">
-        <v>377</v>
+        <v>379</v>
       </c>
       <c r="D188" s="0" t="e">
         <f aca="false">VLOOKUP($A188,統計!$A:$G,6,)</f>
@@ -10447,7 +10496,7 @@
         <v>#N/A</v>
       </c>
       <c r="C189" s="0" t="s">
-        <v>378</v>
+        <v>380</v>
       </c>
       <c r="D189" s="0" t="e">
         <f aca="false">VLOOKUP($A189,統計!$A:$G,6,)</f>
@@ -10471,7 +10520,7 @@
         <v>#N/A</v>
       </c>
       <c r="C190" s="0" t="s">
-        <v>379</v>
+        <v>381</v>
       </c>
       <c r="D190" s="0" t="e">
         <f aca="false">VLOOKUP($A190,統計!$A:$G,6,)</f>
@@ -10495,7 +10544,7 @@
         <v>#N/A</v>
       </c>
       <c r="C191" s="0" t="s">
-        <v>380</v>
+        <v>382</v>
       </c>
       <c r="D191" s="0" t="e">
         <f aca="false">VLOOKUP($A191,統計!$A:$G,6,)</f>
@@ -10519,7 +10568,7 @@
         <v>#N/A</v>
       </c>
       <c r="C192" s="0" t="s">
-        <v>381</v>
+        <v>383</v>
       </c>
       <c r="D192" s="0" t="e">
         <f aca="false">VLOOKUP($A192,統計!$A:$G,6,)</f>
@@ -10543,7 +10592,7 @@
         <v>#N/A</v>
       </c>
       <c r="C193" s="0" t="s">
-        <v>382</v>
+        <v>384</v>
       </c>
       <c r="D193" s="0" t="e">
         <f aca="false">VLOOKUP($A193,統計!$A:$G,6,)</f>
@@ -10567,7 +10616,7 @@
         <v>#N/A</v>
       </c>
       <c r="C194" s="0" t="s">
-        <v>383</v>
+        <v>385</v>
       </c>
       <c r="D194" s="0" t="e">
         <f aca="false">VLOOKUP($A194,統計!$A:$G,6,)</f>
@@ -10591,7 +10640,7 @@
         <v>#N/A</v>
       </c>
       <c r="C195" s="0" t="s">
-        <v>384</v>
+        <v>386</v>
       </c>
       <c r="D195" s="0" t="e">
         <f aca="false">VLOOKUP($A195,統計!$A:$G,6,)</f>
@@ -10615,7 +10664,7 @@
         <v>#N/A</v>
       </c>
       <c r="C196" s="0" t="s">
-        <v>385</v>
+        <v>387</v>
       </c>
       <c r="D196" s="0" t="e">
         <f aca="false">VLOOKUP($A196,統計!$A:$G,6,)</f>
@@ -10639,7 +10688,7 @@
         <v>#N/A</v>
       </c>
       <c r="C197" s="0" t="s">
-        <v>386</v>
+        <v>388</v>
       </c>
       <c r="D197" s="0" t="e">
         <f aca="false">VLOOKUP($A197,統計!$A:$G,6,)</f>
@@ -10663,7 +10712,7 @@
         <v>#N/A</v>
       </c>
       <c r="C198" s="0" t="s">
-        <v>387</v>
+        <v>389</v>
       </c>
       <c r="D198" s="0" t="e">
         <f aca="false">VLOOKUP($A198,統計!$A:$G,6,)</f>
@@ -10687,7 +10736,7 @@
         <v>#N/A</v>
       </c>
       <c r="C199" s="0" t="s">
-        <v>388</v>
+        <v>390</v>
       </c>
       <c r="D199" s="0" t="e">
         <f aca="false">VLOOKUP($A199,統計!$A:$G,6,)</f>
@@ -10711,7 +10760,7 @@
         <v>#N/A</v>
       </c>
       <c r="C200" s="0" t="s">
-        <v>389</v>
+        <v>391</v>
       </c>
       <c r="D200" s="0" t="e">
         <f aca="false">VLOOKUP($A200,統計!$A:$G,6,)</f>
@@ -10735,7 +10784,7 @@
         <v>#N/A</v>
       </c>
       <c r="C201" s="0" t="s">
-        <v>390</v>
+        <v>392</v>
       </c>
       <c r="D201" s="0" t="e">
         <f aca="false">VLOOKUP($A201,統計!$A:$G,6,)</f>
@@ -10759,7 +10808,7 @@
         <v>#N/A</v>
       </c>
       <c r="C202" s="0" t="s">
-        <v>391</v>
+        <v>393</v>
       </c>
       <c r="D202" s="0" t="e">
         <f aca="false">VLOOKUP($A202,統計!$A:$G,6,)</f>
@@ -10783,7 +10832,7 @@
         <v>#N/A</v>
       </c>
       <c r="C203" s="0" t="s">
-        <v>392</v>
+        <v>394</v>
       </c>
       <c r="D203" s="0" t="e">
         <f aca="false">VLOOKUP($A203,統計!$A:$G,6,)</f>
@@ -10807,7 +10856,7 @@
         <v>#N/A</v>
       </c>
       <c r="C204" s="0" t="s">
-        <v>393</v>
+        <v>395</v>
       </c>
       <c r="D204" s="0" t="e">
         <f aca="false">VLOOKUP($A204,統計!$A:$G,6,)</f>
@@ -10831,7 +10880,7 @@
         <v>#N/A</v>
       </c>
       <c r="C205" s="0" t="s">
-        <v>394</v>
+        <v>396</v>
       </c>
       <c r="D205" s="0" t="e">
         <f aca="false">VLOOKUP($A205,統計!$A:$G,6,)</f>
@@ -10855,7 +10904,7 @@
         <v>#N/A</v>
       </c>
       <c r="C206" s="0" t="s">
-        <v>395</v>
+        <v>397</v>
       </c>
       <c r="D206" s="0" t="e">
         <f aca="false">VLOOKUP($A206,統計!$A:$G,6,)</f>
@@ -10879,7 +10928,7 @@
         <v>#N/A</v>
       </c>
       <c r="C207" s="0" t="s">
-        <v>396</v>
+        <v>398</v>
       </c>
       <c r="D207" s="0" t="e">
         <f aca="false">VLOOKUP($A207,統計!$A:$G,6,)</f>
@@ -10903,7 +10952,7 @@
         <v>#N/A</v>
       </c>
       <c r="C208" s="0" t="s">
-        <v>397</v>
+        <v>399</v>
       </c>
       <c r="D208" s="0" t="e">
         <f aca="false">VLOOKUP($A208,統計!$A:$G,6,)</f>
@@ -10927,7 +10976,7 @@
         <v>#N/A</v>
       </c>
       <c r="C209" s="0" t="s">
-        <v>398</v>
+        <v>400</v>
       </c>
       <c r="D209" s="0" t="e">
         <f aca="false">VLOOKUP($A209,統計!$A:$G,6,)</f>
@@ -10951,7 +11000,7 @@
         <v>#N/A</v>
       </c>
       <c r="C210" s="0" t="s">
-        <v>399</v>
+        <v>401</v>
       </c>
       <c r="D210" s="0" t="e">
         <f aca="false">VLOOKUP($A210,統計!$A:$G,6,)</f>
@@ -10975,7 +11024,7 @@
         <v>#N/A</v>
       </c>
       <c r="C211" s="0" t="s">
-        <v>400</v>
+        <v>402</v>
       </c>
       <c r="D211" s="0" t="e">
         <f aca="false">VLOOKUP($A211,統計!$A:$G,6,)</f>
@@ -10999,7 +11048,7 @@
         <v>#N/A</v>
       </c>
       <c r="C212" s="0" t="s">
-        <v>401</v>
+        <v>403</v>
       </c>
       <c r="D212" s="0" t="e">
         <f aca="false">VLOOKUP($A212,統計!$A:$G,6,)</f>
@@ -11023,7 +11072,7 @@
         <v>#N/A</v>
       </c>
       <c r="C213" s="0" t="s">
-        <v>402</v>
+        <v>404</v>
       </c>
       <c r="D213" s="0" t="e">
         <f aca="false">VLOOKUP($A213,統計!$A:$G,6,)</f>
@@ -11047,7 +11096,7 @@
         <v>#N/A</v>
       </c>
       <c r="C214" s="0" t="s">
-        <v>403</v>
+        <v>405</v>
       </c>
       <c r="D214" s="0" t="e">
         <f aca="false">VLOOKUP($A214,統計!$A:$G,6,)</f>
@@ -11071,7 +11120,7 @@
         <v>#N/A</v>
       </c>
       <c r="C215" s="0" t="s">
-        <v>404</v>
+        <v>406</v>
       </c>
       <c r="D215" s="0" t="e">
         <f aca="false">VLOOKUP($A215,統計!$A:$G,6,)</f>
@@ -11095,7 +11144,7 @@
         <v>#N/A</v>
       </c>
       <c r="C216" s="0" t="s">
-        <v>405</v>
+        <v>407</v>
       </c>
       <c r="D216" s="0" t="e">
         <f aca="false">VLOOKUP($A216,統計!$A:$G,6,)</f>
@@ -11119,7 +11168,7 @@
         <v>#N/A</v>
       </c>
       <c r="C217" s="0" t="s">
-        <v>406</v>
+        <v>408</v>
       </c>
       <c r="D217" s="0" t="e">
         <f aca="false">VLOOKUP($A217,統計!$A:$G,6,)</f>
@@ -11143,7 +11192,7 @@
         <v>#N/A</v>
       </c>
       <c r="C218" s="0" t="s">
-        <v>407</v>
+        <v>409</v>
       </c>
       <c r="D218" s="0" t="e">
         <f aca="false">VLOOKUP($A218,統計!$A:$G,6,)</f>
@@ -11167,7 +11216,7 @@
         <v>#N/A</v>
       </c>
       <c r="C219" s="0" t="s">
-        <v>408</v>
+        <v>410</v>
       </c>
       <c r="D219" s="0" t="e">
         <f aca="false">VLOOKUP($A219,統計!$A:$G,6,)</f>
@@ -11191,7 +11240,7 @@
         <v>#N/A</v>
       </c>
       <c r="C220" s="0" t="s">
-        <v>409</v>
+        <v>411</v>
       </c>
       <c r="D220" s="0" t="e">
         <f aca="false">VLOOKUP($A220,統計!$A:$G,6,)</f>
@@ -11215,7 +11264,7 @@
         <v>#N/A</v>
       </c>
       <c r="C221" s="0" t="s">
-        <v>410</v>
+        <v>412</v>
       </c>
       <c r="D221" s="0" t="e">
         <f aca="false">VLOOKUP($A221,統計!$A:$G,6,)</f>
@@ -11239,7 +11288,7 @@
         <v>#N/A</v>
       </c>
       <c r="C222" s="0" t="s">
-        <v>411</v>
+        <v>413</v>
       </c>
       <c r="D222" s="0" t="e">
         <f aca="false">VLOOKUP($A222,統計!$A:$G,6,)</f>
@@ -11263,7 +11312,7 @@
         <v>#N/A</v>
       </c>
       <c r="C223" s="0" t="s">
-        <v>412</v>
+        <v>414</v>
       </c>
       <c r="D223" s="0" t="e">
         <f aca="false">VLOOKUP($A223,統計!$A:$G,6,)</f>
@@ -11287,7 +11336,7 @@
         <v>#N/A</v>
       </c>
       <c r="C224" s="0" t="s">
-        <v>413</v>
+        <v>415</v>
       </c>
       <c r="D224" s="0" t="e">
         <f aca="false">VLOOKUP($A224,統計!$A:$G,6,)</f>
@@ -11311,7 +11360,7 @@
         <v>#N/A</v>
       </c>
       <c r="C225" s="0" t="s">
-        <v>414</v>
+        <v>416</v>
       </c>
       <c r="D225" s="0" t="e">
         <f aca="false">VLOOKUP($A225,統計!$A:$G,6,)</f>
@@ -11335,7 +11384,7 @@
         <v>#N/A</v>
       </c>
       <c r="C226" s="0" t="s">
-        <v>415</v>
+        <v>417</v>
       </c>
       <c r="D226" s="0" t="e">
         <f aca="false">VLOOKUP($A226,統計!$A:$G,6,)</f>
@@ -11359,7 +11408,7 @@
         <v>#N/A</v>
       </c>
       <c r="C227" s="0" t="s">
-        <v>416</v>
+        <v>418</v>
       </c>
       <c r="D227" s="0" t="e">
         <f aca="false">VLOOKUP($A227,統計!$A:$G,6,)</f>
@@ -11383,7 +11432,7 @@
         <v>#N/A</v>
       </c>
       <c r="C228" s="0" t="s">
-        <v>417</v>
+        <v>419</v>
       </c>
       <c r="D228" s="0" t="e">
         <f aca="false">VLOOKUP($A228,統計!$A:$G,6,)</f>
@@ -11407,7 +11456,7 @@
         <v>#N/A</v>
       </c>
       <c r="C229" s="0" t="s">
-        <v>418</v>
+        <v>420</v>
       </c>
       <c r="D229" s="0" t="e">
         <f aca="false">VLOOKUP($A229,統計!$A:$G,6,)</f>
@@ -11431,7 +11480,7 @@
         <v>#N/A</v>
       </c>
       <c r="C230" s="0" t="s">
-        <v>419</v>
+        <v>421</v>
       </c>
       <c r="D230" s="0" t="e">
         <f aca="false">VLOOKUP($A230,統計!$A:$G,6,)</f>
@@ -11455,7 +11504,7 @@
         <v>#N/A</v>
       </c>
       <c r="C231" s="0" t="s">
-        <v>420</v>
+        <v>422</v>
       </c>
       <c r="D231" s="0" t="e">
         <f aca="false">VLOOKUP($A231,統計!$A:$G,6,)</f>
@@ -11479,7 +11528,7 @@
         <v>#N/A</v>
       </c>
       <c r="C232" s="0" t="s">
-        <v>421</v>
+        <v>423</v>
       </c>
       <c r="D232" s="0" t="e">
         <f aca="false">VLOOKUP($A232,統計!$A:$G,6,)</f>
@@ -11503,7 +11552,7 @@
         <v>#N/A</v>
       </c>
       <c r="C233" s="0" t="s">
-        <v>422</v>
+        <v>424</v>
       </c>
       <c r="D233" s="0" t="e">
         <f aca="false">VLOOKUP($A233,統計!$A:$G,6,)</f>
@@ -11527,7 +11576,7 @@
         <v>#N/A</v>
       </c>
       <c r="C234" s="0" t="s">
-        <v>423</v>
+        <v>425</v>
       </c>
       <c r="D234" s="0" t="e">
         <f aca="false">VLOOKUP($A234,統計!$A:$G,6,)</f>
@@ -11551,7 +11600,7 @@
         <v>#N/A</v>
       </c>
       <c r="C235" s="0" t="s">
-        <v>424</v>
+        <v>426</v>
       </c>
       <c r="D235" s="0" t="e">
         <f aca="false">VLOOKUP($A235,統計!$A:$G,6,)</f>
@@ -11575,7 +11624,7 @@
         <v>#N/A</v>
       </c>
       <c r="C236" s="0" t="s">
-        <v>425</v>
+        <v>427</v>
       </c>
       <c r="D236" s="0" t="e">
         <f aca="false">VLOOKUP($A236,統計!$A:$G,6,)</f>
@@ -11599,7 +11648,7 @@
         <v>#N/A</v>
       </c>
       <c r="C237" s="0" t="s">
-        <v>426</v>
+        <v>428</v>
       </c>
       <c r="D237" s="0" t="e">
         <f aca="false">VLOOKUP($A237,統計!$A:$G,6,)</f>
@@ -11623,7 +11672,7 @@
         <v>#N/A</v>
       </c>
       <c r="C238" s="0" t="s">
-        <v>427</v>
+        <v>429</v>
       </c>
       <c r="D238" s="0" t="e">
         <f aca="false">VLOOKUP($A238,統計!$A:$G,6,)</f>
@@ -11647,7 +11696,7 @@
         <v>#N/A</v>
       </c>
       <c r="C239" s="0" t="s">
-        <v>428</v>
+        <v>430</v>
       </c>
       <c r="D239" s="0" t="e">
         <f aca="false">VLOOKUP($A239,統計!$A:$G,6,)</f>
@@ -11671,7 +11720,7 @@
         <v>#N/A</v>
       </c>
       <c r="C240" s="0" t="s">
-        <v>429</v>
+        <v>431</v>
       </c>
       <c r="D240" s="0" t="e">
         <f aca="false">VLOOKUP($A240,統計!$A:$G,6,)</f>
@@ -11695,7 +11744,7 @@
         <v>#N/A</v>
       </c>
       <c r="C241" s="0" t="s">
-        <v>430</v>
+        <v>432</v>
       </c>
       <c r="D241" s="0" t="e">
         <f aca="false">VLOOKUP($A241,統計!$A:$G,6,)</f>
@@ -11719,7 +11768,7 @@
         <v>#N/A</v>
       </c>
       <c r="C242" s="0" t="s">
-        <v>431</v>
+        <v>433</v>
       </c>
       <c r="D242" s="0" t="e">
         <f aca="false">VLOOKUP($A242,統計!$A:$G,6,)</f>
@@ -11743,7 +11792,7 @@
         <v>#N/A</v>
       </c>
       <c r="C243" s="0" t="s">
-        <v>432</v>
+        <v>434</v>
       </c>
       <c r="D243" s="0" t="e">
         <f aca="false">VLOOKUP($A243,統計!$A:$G,6,)</f>
@@ -11767,7 +11816,7 @@
         <v>#N/A</v>
       </c>
       <c r="C244" s="0" t="s">
-        <v>433</v>
+        <v>435</v>
       </c>
       <c r="D244" s="0" t="e">
         <f aca="false">VLOOKUP($A244,統計!$A:$G,6,)</f>
@@ -11791,7 +11840,7 @@
         <v>#N/A</v>
       </c>
       <c r="C245" s="0" t="s">
-        <v>434</v>
+        <v>436</v>
       </c>
       <c r="D245" s="0" t="e">
         <f aca="false">VLOOKUP($A245,統計!$A:$G,6,)</f>
@@ -11815,7 +11864,7 @@
         <v>#N/A</v>
       </c>
       <c r="C246" s="0" t="s">
-        <v>435</v>
+        <v>437</v>
       </c>
       <c r="D246" s="0" t="e">
         <f aca="false">VLOOKUP($A246,統計!$A:$G,6,)</f>
@@ -11839,7 +11888,7 @@
         <v>#N/A</v>
       </c>
       <c r="C247" s="0" t="s">
-        <v>436</v>
+        <v>438</v>
       </c>
       <c r="D247" s="0" t="e">
         <f aca="false">VLOOKUP($A247,統計!$A:$G,6,)</f>
@@ -11863,7 +11912,7 @@
         <v>#N/A</v>
       </c>
       <c r="C248" s="0" t="s">
-        <v>437</v>
+        <v>439</v>
       </c>
       <c r="D248" s="0" t="e">
         <f aca="false">VLOOKUP($A248,統計!$A:$G,6,)</f>
@@ -11887,7 +11936,7 @@
         <v>#N/A</v>
       </c>
       <c r="C249" s="0" t="s">
-        <v>438</v>
+        <v>440</v>
       </c>
       <c r="D249" s="0" t="e">
         <f aca="false">VLOOKUP($A249,統計!$A:$G,6,)</f>
@@ -11911,7 +11960,7 @@
         <v>#N/A</v>
       </c>
       <c r="C250" s="0" t="s">
-        <v>439</v>
+        <v>441</v>
       </c>
       <c r="D250" s="0" t="e">
         <f aca="false">VLOOKUP($A250,統計!$A:$G,6,)</f>
@@ -11935,7 +11984,7 @@
         <v>#N/A</v>
       </c>
       <c r="C251" s="0" t="s">
-        <v>440</v>
+        <v>442</v>
       </c>
       <c r="D251" s="0" t="e">
         <f aca="false">VLOOKUP($A251,統計!$A:$G,6,)</f>
@@ -11959,7 +12008,7 @@
         <v>#N/A</v>
       </c>
       <c r="C252" s="0" t="s">
-        <v>441</v>
+        <v>443</v>
       </c>
       <c r="D252" s="0" t="e">
         <f aca="false">VLOOKUP($A252,統計!$A:$G,6,)</f>
@@ -11983,7 +12032,7 @@
         <v>#N/A</v>
       </c>
       <c r="C253" s="0" t="s">
-        <v>442</v>
+        <v>444</v>
       </c>
       <c r="D253" s="0" t="e">
         <f aca="false">VLOOKUP($A253,統計!$A:$G,6,)</f>
@@ -12007,7 +12056,7 @@
         <v>#N/A</v>
       </c>
       <c r="C254" s="0" t="s">
-        <v>443</v>
+        <v>445</v>
       </c>
       <c r="D254" s="0" t="e">
         <f aca="false">VLOOKUP($A254,統計!$A:$G,6,)</f>
@@ -12031,7 +12080,7 @@
         <v>#N/A</v>
       </c>
       <c r="C255" s="0" t="s">
-        <v>444</v>
+        <v>446</v>
       </c>
       <c r="D255" s="0" t="e">
         <f aca="false">VLOOKUP($A255,統計!$A:$G,6,)</f>
@@ -12055,7 +12104,7 @@
         <v>#N/A</v>
       </c>
       <c r="C256" s="0" t="s">
-        <v>445</v>
+        <v>447</v>
       </c>
       <c r="D256" s="0" t="e">
         <f aca="false">VLOOKUP($A256,統計!$A:$G,6,)</f>
@@ -12079,7 +12128,7 @@
         <v>#N/A</v>
       </c>
       <c r="C257" s="0" t="s">
-        <v>446</v>
+        <v>448</v>
       </c>
       <c r="D257" s="0" t="e">
         <f aca="false">VLOOKUP($A257,統計!$A:$G,6,)</f>
@@ -12103,7 +12152,7 @@
         <v>#N/A</v>
       </c>
       <c r="C258" s="0" t="s">
-        <v>447</v>
+        <v>449</v>
       </c>
       <c r="D258" s="0" t="e">
         <f aca="false">VLOOKUP($A258,統計!$A:$G,6,)</f>
@@ -12127,7 +12176,7 @@
         <v>#N/A</v>
       </c>
       <c r="C259" s="0" t="s">
-        <v>448</v>
+        <v>450</v>
       </c>
       <c r="D259" s="0" t="e">
         <f aca="false">VLOOKUP($A259,統計!$A:$G,6,)</f>
@@ -12151,7 +12200,7 @@
         <v>#N/A</v>
       </c>
       <c r="C260" s="0" t="s">
-        <v>449</v>
+        <v>451</v>
       </c>
       <c r="D260" s="0" t="e">
         <f aca="false">VLOOKUP($A260,統計!$A:$G,6,)</f>
@@ -12175,7 +12224,7 @@
         <v>#N/A</v>
       </c>
       <c r="C261" s="0" t="s">
-        <v>450</v>
+        <v>452</v>
       </c>
       <c r="D261" s="0" t="e">
         <f aca="false">VLOOKUP($A261,統計!$A:$G,6,)</f>
@@ -12199,7 +12248,7 @@
         <v>#N/A</v>
       </c>
       <c r="C262" s="0" t="s">
-        <v>451</v>
+        <v>453</v>
       </c>
       <c r="D262" s="0" t="e">
         <f aca="false">VLOOKUP($A262,統計!$A:$G,6,)</f>
@@ -12223,7 +12272,7 @@
         <v>#N/A</v>
       </c>
       <c r="C263" s="0" t="s">
-        <v>452</v>
+        <v>454</v>
       </c>
       <c r="D263" s="0" t="e">
         <f aca="false">VLOOKUP($A263,統計!$A:$G,6,)</f>
@@ -12247,7 +12296,7 @@
         <v>#N/A</v>
       </c>
       <c r="C264" s="0" t="s">
-        <v>453</v>
+        <v>455</v>
       </c>
       <c r="D264" s="0" t="e">
         <f aca="false">VLOOKUP($A264,統計!$A:$G,6,)</f>
@@ -12271,7 +12320,7 @@
         <v>#N/A</v>
       </c>
       <c r="C265" s="0" t="s">
-        <v>454</v>
+        <v>456</v>
       </c>
       <c r="D265" s="0" t="e">
         <f aca="false">VLOOKUP($A265,統計!$A:$G,6,)</f>
@@ -12295,7 +12344,7 @@
         <v>#N/A</v>
       </c>
       <c r="C266" s="0" t="s">
-        <v>455</v>
+        <v>457</v>
       </c>
       <c r="D266" s="0" t="e">
         <f aca="false">VLOOKUP($A266,統計!$A:$G,6,)</f>
@@ -12319,7 +12368,7 @@
         <v>#N/A</v>
       </c>
       <c r="C267" s="0" t="s">
-        <v>456</v>
+        <v>458</v>
       </c>
       <c r="D267" s="0" t="e">
         <f aca="false">VLOOKUP($A267,統計!$A:$G,6,)</f>
@@ -12343,7 +12392,7 @@
         <v>#N/A</v>
       </c>
       <c r="C268" s="0" t="s">
-        <v>457</v>
+        <v>459</v>
       </c>
       <c r="D268" s="0" t="e">
         <f aca="false">VLOOKUP($A268,統計!$A:$G,6,)</f>
@@ -12367,7 +12416,7 @@
         <v>#N/A</v>
       </c>
       <c r="C269" s="0" t="s">
-        <v>458</v>
+        <v>460</v>
       </c>
       <c r="D269" s="0" t="e">
         <f aca="false">VLOOKUP($A269,統計!$A:$G,6,)</f>
@@ -12391,7 +12440,7 @@
         <v>#N/A</v>
       </c>
       <c r="C270" s="0" t="s">
-        <v>459</v>
+        <v>461</v>
       </c>
       <c r="D270" s="0" t="e">
         <f aca="false">VLOOKUP($A270,統計!$A:$G,6,)</f>
@@ -12415,7 +12464,7 @@
         <v>#N/A</v>
       </c>
       <c r="C271" s="0" t="s">
-        <v>460</v>
+        <v>462</v>
       </c>
       <c r="D271" s="0" t="e">
         <f aca="false">VLOOKUP($A271,統計!$A:$G,6,)</f>
@@ -12439,7 +12488,7 @@
         <v>#N/A</v>
       </c>
       <c r="C272" s="0" t="s">
-        <v>461</v>
+        <v>463</v>
       </c>
       <c r="D272" s="0" t="e">
         <f aca="false">VLOOKUP($A272,統計!$A:$G,6,)</f>
@@ -12463,7 +12512,7 @@
         <v>#N/A</v>
       </c>
       <c r="C273" s="0" t="s">
-        <v>462</v>
+        <v>464</v>
       </c>
       <c r="D273" s="0" t="e">
         <f aca="false">VLOOKUP($A273,統計!$A:$G,6,)</f>
@@ -12487,7 +12536,7 @@
         <v>#N/A</v>
       </c>
       <c r="C274" s="0" t="s">
-        <v>463</v>
+        <v>465</v>
       </c>
       <c r="D274" s="0" t="e">
         <f aca="false">VLOOKUP($A274,統計!$A:$G,6,)</f>
@@ -12511,7 +12560,7 @@
         <v>#N/A</v>
       </c>
       <c r="C275" s="0" t="s">
-        <v>464</v>
+        <v>466</v>
       </c>
       <c r="D275" s="0" t="e">
         <f aca="false">VLOOKUP($A275,統計!$A:$G,6,)</f>
@@ -12535,7 +12584,7 @@
         <v>#N/A</v>
       </c>
       <c r="C276" s="0" t="s">
-        <v>465</v>
+        <v>467</v>
       </c>
       <c r="D276" s="0" t="e">
         <f aca="false">VLOOKUP($A276,統計!$A:$G,6,)</f>
@@ -12559,7 +12608,7 @@
         <v>#N/A</v>
       </c>
       <c r="C277" s="0" t="s">
-        <v>466</v>
+        <v>468</v>
       </c>
       <c r="D277" s="0" t="e">
         <f aca="false">VLOOKUP($A277,統計!$A:$G,6,)</f>
@@ -12583,7 +12632,7 @@
         <v>#N/A</v>
       </c>
       <c r="C278" s="0" t="s">
-        <v>467</v>
+        <v>469</v>
       </c>
       <c r="D278" s="0" t="e">
         <f aca="false">VLOOKUP($A278,統計!$A:$G,6,)</f>
@@ -12607,7 +12656,7 @@
         <v>#N/A</v>
       </c>
       <c r="C279" s="0" t="s">
-        <v>468</v>
+        <v>470</v>
       </c>
       <c r="D279" s="0" t="e">
         <f aca="false">VLOOKUP($A279,統計!$A:$G,6,)</f>
@@ -12631,7 +12680,7 @@
         <v>#N/A</v>
       </c>
       <c r="C280" s="0" t="s">
-        <v>469</v>
+        <v>471</v>
       </c>
       <c r="D280" s="0" t="e">
         <f aca="false">VLOOKUP($A280,統計!$A:$G,6,)</f>
@@ -12655,7 +12704,7 @@
         <v>#N/A</v>
       </c>
       <c r="C281" s="0" t="s">
-        <v>470</v>
+        <v>472</v>
       </c>
       <c r="D281" s="0" t="e">
         <f aca="false">VLOOKUP($A281,統計!$A:$G,6,)</f>
@@ -12679,7 +12728,7 @@
         <v>#N/A</v>
       </c>
       <c r="C282" s="0" t="s">
-        <v>471</v>
+        <v>473</v>
       </c>
       <c r="D282" s="0" t="e">
         <f aca="false">VLOOKUP($A282,統計!$A:$G,6,)</f>
@@ -12703,7 +12752,7 @@
         <v>#N/A</v>
       </c>
       <c r="C283" s="0" t="s">
-        <v>472</v>
+        <v>474</v>
       </c>
       <c r="D283" s="0" t="e">
         <f aca="false">VLOOKUP($A283,統計!$A:$G,6,)</f>
@@ -12727,7 +12776,7 @@
         <v>#N/A</v>
       </c>
       <c r="C284" s="0" t="s">
-        <v>473</v>
+        <v>475</v>
       </c>
       <c r="D284" s="0" t="e">
         <f aca="false">VLOOKUP($A284,統計!$A:$G,6,)</f>
@@ -12751,7 +12800,7 @@
         <v>#N/A</v>
       </c>
       <c r="C285" s="0" t="s">
-        <v>474</v>
+        <v>476</v>
       </c>
       <c r="D285" s="0" t="e">
         <f aca="false">VLOOKUP($A285,統計!$A:$G,6,)</f>
@@ -12775,7 +12824,7 @@
         <v>#N/A</v>
       </c>
       <c r="C286" s="0" t="s">
-        <v>475</v>
+        <v>477</v>
       </c>
       <c r="D286" s="0" t="e">
         <f aca="false">VLOOKUP($A286,統計!$A:$G,6,)</f>
@@ -12799,7 +12848,7 @@
         <v>#N/A</v>
       </c>
       <c r="C287" s="0" t="s">
-        <v>476</v>
+        <v>478</v>
       </c>
       <c r="D287" s="0" t="e">
         <f aca="false">VLOOKUP($A287,統計!$A:$G,6,)</f>
@@ -12823,7 +12872,7 @@
         <v>#N/A</v>
       </c>
       <c r="C288" s="0" t="s">
-        <v>477</v>
+        <v>479</v>
       </c>
       <c r="D288" s="0" t="e">
         <f aca="false">VLOOKUP($A288,統計!$A:$G,6,)</f>
@@ -12847,7 +12896,7 @@
         <v>#N/A</v>
       </c>
       <c r="C289" s="0" t="s">
-        <v>478</v>
+        <v>480</v>
       </c>
       <c r="D289" s="0" t="e">
         <f aca="false">VLOOKUP($A289,統計!$A:$G,6,)</f>
@@ -12871,7 +12920,7 @@
         <v>#N/A</v>
       </c>
       <c r="C290" s="0" t="s">
-        <v>479</v>
+        <v>481</v>
       </c>
       <c r="D290" s="0" t="e">
         <f aca="false">VLOOKUP($A290,統計!$A:$G,6,)</f>
@@ -12895,7 +12944,7 @@
         <v>#N/A</v>
       </c>
       <c r="C291" s="0" t="s">
-        <v>480</v>
+        <v>482</v>
       </c>
       <c r="D291" s="0" t="e">
         <f aca="false">VLOOKUP($A291,統計!$A:$G,6,)</f>
@@ -12919,7 +12968,7 @@
         <v>#N/A</v>
       </c>
       <c r="C292" s="0" t="s">
-        <v>481</v>
+        <v>483</v>
       </c>
       <c r="D292" s="0" t="e">
         <f aca="false">VLOOKUP($A292,統計!$A:$G,6,)</f>
@@ -12943,7 +12992,7 @@
         <v>#N/A</v>
       </c>
       <c r="C293" s="0" t="s">
-        <v>482</v>
+        <v>484</v>
       </c>
       <c r="D293" s="0" t="e">
         <f aca="false">VLOOKUP($A293,統計!$A:$G,6,)</f>
@@ -12967,7 +13016,7 @@
         <v>#N/A</v>
       </c>
       <c r="C294" s="0" t="s">
-        <v>483</v>
+        <v>485</v>
       </c>
       <c r="D294" s="0" t="e">
         <f aca="false">VLOOKUP($A294,統計!$A:$G,6,)</f>
@@ -12991,7 +13040,7 @@
         <v>#N/A</v>
       </c>
       <c r="C295" s="0" t="s">
-        <v>484</v>
+        <v>486</v>
       </c>
       <c r="D295" s="0" t="e">
         <f aca="false">VLOOKUP($A295,統計!$A:$G,6,)</f>
@@ -13027,13 +13076,13 @@
   <sheetData>
     <row r="1" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B1" s="0" t="s">
-        <v>485</v>
+        <v>487</v>
       </c>
       <c r="C1" s="0" t="s">
-        <v>486</v>
+        <v>488</v>
       </c>
       <c r="D1" s="0" t="s">
-        <v>487</v>
+        <v>489</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -13047,30 +13096,30 @@
         <v>1173</v>
       </c>
       <c r="E2" s="0" t="s">
-        <v>488</v>
+        <v>490</v>
       </c>
       <c r="G2" s="0" t="n">
         <f aca="false">C2/B2</f>
         <v>2.41791044776119</v>
       </c>
       <c r="H2" s="0" t="s">
-        <v>489</v>
+        <v>491</v>
       </c>
       <c r="K2" s="0" t="n">
         <f aca="false">D2/C2</f>
         <v>1.81018518518519</v>
       </c>
       <c r="L2" s="0" t="s">
-        <v>490</v>
+        <v>492</v>
       </c>
       <c r="N2" s="0" t="s">
-        <v>491</v>
+        <v>493</v>
       </c>
       <c r="O2" s="0" t="n">
         <v>80</v>
       </c>
       <c r="P2" s="0" t="s">
-        <v>492</v>
+        <v>494</v>
       </c>
       <c r="Q2" s="0" t="n">
         <f aca="false">O2/D2</f>
@@ -13082,7 +13131,7 @@
         <v>1239</v>
       </c>
       <c r="E3" s="0" t="s">
-        <v>493</v>
+        <v>495</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -13090,7 +13139,7 @@
         <v>2175</v>
       </c>
       <c r="E4" s="0" t="s">
-        <v>494</v>
+        <v>496</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -13101,19 +13150,19 @@
         <v>18</v>
       </c>
       <c r="G5" s="0" t="s">
-        <v>495</v>
+        <v>497</v>
       </c>
       <c r="H5" s="0" t="s">
-        <v>496</v>
+        <v>498</v>
       </c>
       <c r="I5" s="0" t="s">
-        <v>497</v>
+        <v>499</v>
       </c>
       <c r="K5" s="0" t="s">
-        <v>498</v>
+        <v>500</v>
       </c>
       <c r="L5" s="0" t="s">
-        <v>499</v>
+        <v>501</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -13121,7 +13170,7 @@
         <v>3732</v>
       </c>
       <c r="E6" s="0" t="s">
-        <v>500</v>
+        <v>502</v>
       </c>
       <c r="G6" s="0" t="n">
         <f aca="false">C6-C2</f>
@@ -13152,7 +13201,7 @@
         <v>22</v>
       </c>
       <c r="G7" s="0" t="s">
-        <v>501</v>
+        <v>503</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -13161,18 +13210,18 @@
         <v>0.0674157303370787</v>
       </c>
       <c r="O8" s="0" t="s">
-        <v>502</v>
+        <v>504</v>
       </c>
       <c r="P8" s="0" t="s">
-        <v>503</v>
+        <v>505</v>
       </c>
       <c r="Q8" s="0" t="s">
-        <v>504</v>
+        <v>506</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="N9" s="0" t="s">
-        <v>505</v>
+        <v>507</v>
       </c>
       <c r="O9" s="0" t="n">
         <v>1</v>
@@ -13188,7 +13237,7 @@
     </row>
     <row r="10" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="N10" s="0" t="s">
-        <v>505</v>
+        <v>507</v>
       </c>
       <c r="O10" s="0" t="n">
         <v>2</v>
@@ -13204,7 +13253,7 @@
     </row>
     <row r="11" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="N11" s="0" t="s">
-        <v>505</v>
+        <v>507</v>
       </c>
       <c r="O11" s="0" t="n">
         <v>294</v>
@@ -13220,7 +13269,7 @@
     </row>
     <row r="13" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="N13" s="0" t="s">
-        <v>506</v>
+        <v>508</v>
       </c>
       <c r="O13" s="0" t="n">
         <v>200</v>
@@ -13228,7 +13277,7 @@
     </row>
     <row r="14" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="N14" s="0" t="s">
-        <v>507</v>
+        <v>509</v>
       </c>
       <c r="O14" s="0" t="n">
         <v>118</v>

--- a/5_筆記/閱讀數據.xlsx
+++ b/5_筆記/閱讀數據.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="516" uniqueCount="510">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="518" uniqueCount="512">
   <si>
     <t xml:space="preserve">索引號</t>
   </si>
@@ -844,6 +844,12 @@
   </si>
   <si>
     <t xml:space="preserve">晉紀三</t>
+  </si>
+  <si>
+    <t xml:space="preserve">弘農楊氏名人世系</t>
+  </si>
+  <si>
+    <t xml:space="preserve">司馬炎15年至23年</t>
   </si>
   <si>
     <t xml:space="preserve">晉紀四</t>
@@ -1807,7 +1813,7 @@
 </styleSheet>
 </file>
 
-<file path=xl/charts/chart2.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/charts/chart3.xml><?xml version="1.0" encoding="utf-8"?>
 <c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <c:lang val="en-US"/>
   <c:roundedCorners val="0"/>
@@ -2165,18 +2171,18 @@
                   <c:v>1.28571428571429</c:v>
                 </c:pt>
                 <c:pt idx="80">
-                  <c:v>160.673835125448</c:v>
+                  <c:v>0.888888888888889</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
           </c:yVal>
           <c:smooth val="1"/>
         </c:ser>
-        <c:axId val="77021377"/>
-        <c:axId val="65069290"/>
+        <c:axId val="57524932"/>
+        <c:axId val="83774724"/>
       </c:scatterChart>
       <c:valAx>
-        <c:axId val="77021377"/>
+        <c:axId val="57524932"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -2252,12 +2258,12 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="65069290"/>
+        <c:crossAx val="83774724"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="midCat"/>
       </c:valAx>
       <c:valAx>
-        <c:axId val="65069290"/>
+        <c:axId val="83774724"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -2333,7 +2339,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="77021377"/>
+        <c:crossAx val="57524932"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="midCat"/>
       </c:valAx>
@@ -2372,9 +2378,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>15</xdr:col>
-      <xdr:colOff>670320</xdr:colOff>
+      <xdr:colOff>669600</xdr:colOff>
       <xdr:row>27</xdr:row>
-      <xdr:rowOff>108360</xdr:rowOff>
+      <xdr:rowOff>107640</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame>
       <xdr:nvGraphicFramePr>
@@ -2383,7 +2389,7 @@
       </xdr:nvGraphicFramePr>
       <xdr:xfrm>
         <a:off x="6835320" y="1995120"/>
-        <a:ext cx="4150440" cy="2742120"/>
+        <a:ext cx="4149720" cy="2741400"/>
       </xdr:xfrm>
       <a:graphic>
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
@@ -2516,19 +2522,19 @@
       </c>
       <c r="O2" s="0" t="n">
         <f aca="false">L2*$L$10</f>
-        <v>-37028.9382716049</v>
+        <v>611.160493827161</v>
       </c>
       <c r="P2" s="1" t="n">
         <f aca="false">$C$2+O2</f>
-        <v>6990.06172839506</v>
+        <v>44630.1604938272</v>
       </c>
       <c r="Q2" s="0" t="n">
         <f aca="false">(M2-$F$2)*$L$11</f>
-        <v>2511.58429231704</v>
+        <v>494.239180822187</v>
       </c>
       <c r="R2" s="1" t="n">
         <f aca="false">$C$2+Q2</f>
-        <v>46530.584292317</v>
+        <v>44513.2391808222</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2579,19 +2585,19 @@
       </c>
       <c r="O3" s="0" t="n">
         <f aca="false">L3*$L$10</f>
-        <v>-42474.3703703704</v>
+        <v>701.037037037037</v>
       </c>
       <c r="P3" s="1" t="n">
         <f aca="false">$C$2+O3</f>
-        <v>1544.62962962964</v>
+        <v>44720.037037037</v>
       </c>
       <c r="Q3" s="0" t="n">
         <f aca="false">(M3-$F$2)*$L$11</f>
-        <v>2753.47041998802</v>
+        <v>541.838459874083</v>
       </c>
       <c r="R3" s="1" t="n">
         <f aca="false">$C$2+Q3</f>
-        <v>46772.470419988</v>
+        <v>44560.8384598741</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2642,19 +2648,19 @@
       </c>
       <c r="O4" s="0" t="n">
         <f aca="false">L4*$L$10</f>
-        <v>-64256.0987654321</v>
+        <v>1060.54320987654</v>
       </c>
       <c r="P4" s="1" t="n">
         <f aca="false">$C$2+O4</f>
-        <v>-20237.0987654321</v>
+        <v>45079.5432098766</v>
       </c>
       <c r="Q4" s="0" t="n">
         <f aca="false">(M4-$F$2)*$L$11</f>
-        <v>3317.87138455364</v>
+        <v>652.903444328507</v>
       </c>
       <c r="R4" s="1" t="n">
         <f aca="false">$C$2+Q4</f>
-        <v>47336.8713845537</v>
+        <v>44671.9034443285</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2705,19 +2711,19 @@
       </c>
       <c r="O5" s="0" t="n">
         <f aca="false">L5*$L$10</f>
-        <v>-95839.6049382716</v>
+        <v>1581.82716049383</v>
       </c>
       <c r="P5" s="1" t="n">
         <f aca="false">$C$2+O5</f>
-        <v>-51820.6049382716</v>
+        <v>45600.8271604938</v>
       </c>
       <c r="Q5" s="0" t="n">
         <f aca="false">(M5-$F$2)*$L$11</f>
-        <v>3999.18397749358</v>
+        <v>786.974746991347</v>
       </c>
       <c r="R5" s="1" t="n">
         <f aca="false">$C$2+Q5</f>
-        <v>48018.1839774936</v>
+        <v>44805.9747469913</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2768,19 +2774,19 @@
       </c>
       <c r="O6" s="0" t="n">
         <f aca="false">L6*$L$10</f>
-        <v>-144303.950617284</v>
+        <v>2381.72839506173</v>
       </c>
       <c r="P6" s="1" t="n">
         <f aca="false">$C$2+O6</f>
-        <v>-100284.950617284</v>
+        <v>46400.7283950617</v>
       </c>
       <c r="Q6" s="0" t="n">
         <f aca="false">(M6-$F$2)*$L$11</f>
-        <v>5281.18045414979</v>
+        <v>1039.2509259664</v>
       </c>
       <c r="R6" s="1" t="n">
         <f aca="false">$C$2+Q6</f>
-        <v>49300.1804541498</v>
+        <v>45058.2509259664</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2831,19 +2837,19 @@
       </c>
       <c r="O7" s="0" t="n">
         <f aca="false">L7*$L$10</f>
-        <v>-160095.703703704</v>
+        <v>2642.37037037037</v>
       </c>
       <c r="P7" s="1" t="n">
         <f aca="false">$C$2+O7</f>
-        <v>-116076.703703704</v>
+        <v>46661.3703703704</v>
       </c>
       <c r="Q7" s="0" t="n">
         <f aca="false">(M7-$F$2)*$L$11</f>
-        <v>5490.81509813131</v>
+        <v>1080.50363447804</v>
       </c>
       <c r="R7" s="1" t="n">
         <f aca="false">$C$2+Q7</f>
-        <v>49509.8150981313</v>
+        <v>45099.503634478</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2894,19 +2900,19 @@
       </c>
       <c r="O8" s="0" t="n">
         <f aca="false">L8*$L$10</f>
-        <v>-160095.703703704</v>
+        <v>2642.37037037037</v>
       </c>
       <c r="P8" s="1" t="n">
         <f aca="false">$C$2+O8</f>
-        <v>-116076.703703704</v>
+        <v>46661.3703703704</v>
       </c>
       <c r="Q8" s="0" t="n">
         <f aca="false">(M8-$F$2)*$L$11</f>
-        <v>5490.81509813131</v>
+        <v>1080.50363447804</v>
       </c>
       <c r="R8" s="1" t="n">
         <f aca="false">$C$2+Q8</f>
-        <v>49509.8150981313</v>
+        <v>45099.503634478</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2981,7 +2987,7 @@
       </c>
       <c r="L10" s="0" t="n">
         <f aca="false">AVERAGE(E:E)</f>
-        <v>-544.543209876543</v>
+        <v>8.98765432098766</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3022,7 +3028,7 @@
       </c>
       <c r="L11" s="0" t="n">
         <f aca="false">AVEDEV(I:I)</f>
-        <v>4.03143546118304</v>
+        <v>0.7933213175316</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5448,21 +5454,27 @@
       <c r="C82" s="1" t="n">
         <v>44829</v>
       </c>
+      <c r="D82" s="1" t="n">
+        <v>44836</v>
+      </c>
       <c r="E82" s="0" t="n">
         <f aca="false">D82-C82+1</f>
-        <v>-44828</v>
+        <v>8</v>
       </c>
       <c r="F82" s="0" t="n">
         <f aca="false">G81+1</f>
         <v>280</v>
       </c>
+      <c r="G82" s="0" t="n">
+        <v>288</v>
+      </c>
       <c r="H82" s="0" t="n">
         <f aca="false">IF(F82*G82&lt;0,ABS(F82)+ABS(G82),G82-F82+1)</f>
-        <v>-279</v>
+        <v>9</v>
       </c>
       <c r="I82" s="0" t="n">
         <f aca="false">E82/H82</f>
-        <v>160.673835125448</v>
+        <v>0.888888888888889</v>
       </c>
     </row>
   </sheetData>
@@ -5487,7 +5499,7 @@
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="0" width="33.38"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="0" width="22.12"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="7" width="9"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="7" width="22.03"/>
   </cols>
   <sheetData>
     <row r="1" s="3" customFormat="true" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -7919,7 +7931,7 @@
         <v>702|[卷80](5_筆記/资治通鉴80.html)|晉紀二|273|279||諸王就國情況(西晉大小國)|司馬炎8年至14年</v>
       </c>
     </row>
-    <row r="82" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="82" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A82" s="0" t="n">
         <v>703</v>
       </c>
@@ -7936,14 +7948,20 @@
       </c>
       <c r="E82" s="0" t="n">
         <f aca="false">VLOOKUP($A82,統計!$A:$G,7,)</f>
-        <v>0</v>
+        <v>288</v>
+      </c>
+      <c r="F82" s="0" t="s">
+        <v>274</v>
+      </c>
+      <c r="H82" s="0" t="s">
+        <v>275</v>
       </c>
       <c r="I82" s="0" t="str">
         <f aca="false">A82&amp;"|"&amp;"["&amp;B82&amp;"](5_筆記/资治通鉴"&amp;SUBSTITUTE(B82,"卷","")&amp;".html)|"&amp;C82&amp;"|"&amp;D82&amp;"|"&amp;E82&amp;"|"&amp;F82&amp;"|"&amp;G82&amp;"|"&amp;H82</f>
-        <v>703|[卷81](5_筆記/资治通鉴81.html)|晉紀三|280|0|||</v>
-      </c>
-    </row>
-    <row r="83" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>703|[卷81](5_筆記/资治通鉴81.html)|晉紀三|280|288|弘農楊氏名人世系||司馬炎15年至23年</v>
+      </c>
+    </row>
+    <row r="83" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A83" s="0" t="n">
         <v>704</v>
       </c>
@@ -7952,7 +7970,7 @@
         <v>#N/A</v>
       </c>
       <c r="C83" s="0" t="s">
-        <v>274</v>
+        <v>276</v>
       </c>
       <c r="D83" s="0" t="e">
         <f aca="false">VLOOKUP($A83,統計!$A:$G,6,)</f>
@@ -7962,6 +7980,7 @@
         <f aca="false">VLOOKUP($A83,統計!$A:$G,7,)</f>
         <v>#N/A</v>
       </c>
+      <c r="H83" s="0"/>
       <c r="I83" s="0" t="e">
         <f aca="false">A83&amp;"|"&amp;"["&amp;B83&amp;"](5_筆記/资治通鉴"&amp;SUBSTITUTE(B83,"卷","")&amp;".html)|"&amp;C83&amp;"|"&amp;D83&amp;"|"&amp;E83&amp;"|"&amp;F83&amp;"|"&amp;G83&amp;"|"&amp;H83</f>
         <v>#N/A</v>
@@ -7976,7 +7995,7 @@
         <v>#N/A</v>
       </c>
       <c r="C84" s="0" t="s">
-        <v>275</v>
+        <v>277</v>
       </c>
       <c r="D84" s="0" t="e">
         <f aca="false">VLOOKUP($A84,統計!$A:$G,6,)</f>
@@ -8000,7 +8019,7 @@
         <v>#N/A</v>
       </c>
       <c r="C85" s="0" t="s">
-        <v>276</v>
+        <v>278</v>
       </c>
       <c r="D85" s="0" t="e">
         <f aca="false">VLOOKUP($A85,統計!$A:$G,6,)</f>
@@ -8024,7 +8043,7 @@
         <v>#N/A</v>
       </c>
       <c r="C86" s="0" t="s">
-        <v>277</v>
+        <v>279</v>
       </c>
       <c r="D86" s="0" t="e">
         <f aca="false">VLOOKUP($A86,統計!$A:$G,6,)</f>
@@ -8048,7 +8067,7 @@
         <v>#N/A</v>
       </c>
       <c r="C87" s="0" t="s">
-        <v>278</v>
+        <v>280</v>
       </c>
       <c r="D87" s="0" t="e">
         <f aca="false">VLOOKUP($A87,統計!$A:$G,6,)</f>
@@ -8072,7 +8091,7 @@
         <v>#N/A</v>
       </c>
       <c r="C88" s="0" t="s">
-        <v>279</v>
+        <v>281</v>
       </c>
       <c r="D88" s="0" t="e">
         <f aca="false">VLOOKUP($A88,統計!$A:$G,6,)</f>
@@ -8096,7 +8115,7 @@
         <v>#N/A</v>
       </c>
       <c r="C89" s="0" t="s">
-        <v>280</v>
+        <v>282</v>
       </c>
       <c r="D89" s="0" t="e">
         <f aca="false">VLOOKUP($A89,統計!$A:$G,6,)</f>
@@ -8120,7 +8139,7 @@
         <v>#N/A</v>
       </c>
       <c r="C90" s="0" t="s">
-        <v>281</v>
+        <v>283</v>
       </c>
       <c r="D90" s="0" t="e">
         <f aca="false">VLOOKUP($A90,統計!$A:$G,6,)</f>
@@ -8144,7 +8163,7 @@
         <v>#N/A</v>
       </c>
       <c r="C91" s="0" t="s">
-        <v>282</v>
+        <v>284</v>
       </c>
       <c r="D91" s="0" t="e">
         <f aca="false">VLOOKUP($A91,統計!$A:$G,6,)</f>
@@ -8168,7 +8187,7 @@
         <v>#N/A</v>
       </c>
       <c r="C92" s="0" t="s">
-        <v>283</v>
+        <v>285</v>
       </c>
       <c r="D92" s="0" t="e">
         <f aca="false">VLOOKUP($A92,統計!$A:$G,6,)</f>
@@ -8192,7 +8211,7 @@
         <v>#N/A</v>
       </c>
       <c r="C93" s="0" t="s">
-        <v>284</v>
+        <v>286</v>
       </c>
       <c r="D93" s="0" t="e">
         <f aca="false">VLOOKUP($A93,統計!$A:$G,6,)</f>
@@ -8216,7 +8235,7 @@
         <v>#N/A</v>
       </c>
       <c r="C94" s="0" t="s">
-        <v>285</v>
+        <v>287</v>
       </c>
       <c r="D94" s="0" t="e">
         <f aca="false">VLOOKUP($A94,統計!$A:$G,6,)</f>
@@ -8240,7 +8259,7 @@
         <v>#N/A</v>
       </c>
       <c r="C95" s="0" t="s">
-        <v>286</v>
+        <v>288</v>
       </c>
       <c r="D95" s="0" t="e">
         <f aca="false">VLOOKUP($A95,統計!$A:$G,6,)</f>
@@ -8264,7 +8283,7 @@
         <v>#N/A</v>
       </c>
       <c r="C96" s="0" t="s">
-        <v>287</v>
+        <v>289</v>
       </c>
       <c r="D96" s="0" t="e">
         <f aca="false">VLOOKUP($A96,統計!$A:$G,6,)</f>
@@ -8288,7 +8307,7 @@
         <v>#N/A</v>
       </c>
       <c r="C97" s="0" t="s">
-        <v>288</v>
+        <v>290</v>
       </c>
       <c r="D97" s="0" t="e">
         <f aca="false">VLOOKUP($A97,統計!$A:$G,6,)</f>
@@ -8312,7 +8331,7 @@
         <v>#N/A</v>
       </c>
       <c r="C98" s="0" t="s">
-        <v>289</v>
+        <v>291</v>
       </c>
       <c r="D98" s="0" t="e">
         <f aca="false">VLOOKUP($A98,統計!$A:$G,6,)</f>
@@ -8336,7 +8355,7 @@
         <v>#N/A</v>
       </c>
       <c r="C99" s="0" t="s">
-        <v>290</v>
+        <v>292</v>
       </c>
       <c r="D99" s="0" t="e">
         <f aca="false">VLOOKUP($A99,統計!$A:$G,6,)</f>
@@ -8360,7 +8379,7 @@
         <v>#N/A</v>
       </c>
       <c r="C100" s="0" t="s">
-        <v>291</v>
+        <v>293</v>
       </c>
       <c r="D100" s="0" t="e">
         <f aca="false">VLOOKUP($A100,統計!$A:$G,6,)</f>
@@ -8384,7 +8403,7 @@
         <v>#N/A</v>
       </c>
       <c r="C101" s="0" t="s">
-        <v>292</v>
+        <v>294</v>
       </c>
       <c r="D101" s="0" t="e">
         <f aca="false">VLOOKUP($A101,統計!$A:$G,6,)</f>
@@ -8408,7 +8427,7 @@
         <v>#N/A</v>
       </c>
       <c r="C102" s="0" t="s">
-        <v>293</v>
+        <v>295</v>
       </c>
       <c r="D102" s="0" t="e">
         <f aca="false">VLOOKUP($A102,統計!$A:$G,6,)</f>
@@ -8432,7 +8451,7 @@
         <v>#N/A</v>
       </c>
       <c r="C103" s="0" t="s">
-        <v>294</v>
+        <v>296</v>
       </c>
       <c r="D103" s="0" t="e">
         <f aca="false">VLOOKUP($A103,統計!$A:$G,6,)</f>
@@ -8456,7 +8475,7 @@
         <v>#N/A</v>
       </c>
       <c r="C104" s="0" t="s">
-        <v>295</v>
+        <v>297</v>
       </c>
       <c r="D104" s="0" t="e">
         <f aca="false">VLOOKUP($A104,統計!$A:$G,6,)</f>
@@ -8480,7 +8499,7 @@
         <v>#N/A</v>
       </c>
       <c r="C105" s="0" t="s">
-        <v>296</v>
+        <v>298</v>
       </c>
       <c r="D105" s="0" t="e">
         <f aca="false">VLOOKUP($A105,統計!$A:$G,6,)</f>
@@ -8504,7 +8523,7 @@
         <v>#N/A</v>
       </c>
       <c r="C106" s="0" t="s">
-        <v>297</v>
+        <v>299</v>
       </c>
       <c r="D106" s="0" t="e">
         <f aca="false">VLOOKUP($A106,統計!$A:$G,6,)</f>
@@ -8528,7 +8547,7 @@
         <v>#N/A</v>
       </c>
       <c r="C107" s="0" t="s">
-        <v>298</v>
+        <v>300</v>
       </c>
       <c r="D107" s="0" t="e">
         <f aca="false">VLOOKUP($A107,統計!$A:$G,6,)</f>
@@ -8552,7 +8571,7 @@
         <v>#N/A</v>
       </c>
       <c r="C108" s="0" t="s">
-        <v>299</v>
+        <v>301</v>
       </c>
       <c r="D108" s="0" t="e">
         <f aca="false">VLOOKUP($A108,統計!$A:$G,6,)</f>
@@ -8576,7 +8595,7 @@
         <v>#N/A</v>
       </c>
       <c r="C109" s="0" t="s">
-        <v>300</v>
+        <v>302</v>
       </c>
       <c r="D109" s="0" t="e">
         <f aca="false">VLOOKUP($A109,統計!$A:$G,6,)</f>
@@ -8600,7 +8619,7 @@
         <v>#N/A</v>
       </c>
       <c r="C110" s="0" t="s">
-        <v>301</v>
+        <v>303</v>
       </c>
       <c r="D110" s="0" t="e">
         <f aca="false">VLOOKUP($A110,統計!$A:$G,6,)</f>
@@ -8624,7 +8643,7 @@
         <v>#N/A</v>
       </c>
       <c r="C111" s="0" t="s">
-        <v>302</v>
+        <v>304</v>
       </c>
       <c r="D111" s="0" t="e">
         <f aca="false">VLOOKUP($A111,統計!$A:$G,6,)</f>
@@ -8648,7 +8667,7 @@
         <v>#N/A</v>
       </c>
       <c r="C112" s="0" t="s">
-        <v>303</v>
+        <v>305</v>
       </c>
       <c r="D112" s="0" t="e">
         <f aca="false">VLOOKUP($A112,統計!$A:$G,6,)</f>
@@ -8672,7 +8691,7 @@
         <v>#N/A</v>
       </c>
       <c r="C113" s="0" t="s">
-        <v>304</v>
+        <v>306</v>
       </c>
       <c r="D113" s="0" t="e">
         <f aca="false">VLOOKUP($A113,統計!$A:$G,6,)</f>
@@ -8696,7 +8715,7 @@
         <v>#N/A</v>
       </c>
       <c r="C114" s="0" t="s">
-        <v>305</v>
+        <v>307</v>
       </c>
       <c r="D114" s="0" t="e">
         <f aca="false">VLOOKUP($A114,統計!$A:$G,6,)</f>
@@ -8720,7 +8739,7 @@
         <v>#N/A</v>
       </c>
       <c r="C115" s="0" t="s">
-        <v>306</v>
+        <v>308</v>
       </c>
       <c r="D115" s="0" t="e">
         <f aca="false">VLOOKUP($A115,統計!$A:$G,6,)</f>
@@ -8744,7 +8763,7 @@
         <v>#N/A</v>
       </c>
       <c r="C116" s="0" t="s">
-        <v>307</v>
+        <v>309</v>
       </c>
       <c r="D116" s="0" t="e">
         <f aca="false">VLOOKUP($A116,統計!$A:$G,6,)</f>
@@ -8768,7 +8787,7 @@
         <v>#N/A</v>
       </c>
       <c r="C117" s="0" t="s">
-        <v>308</v>
+        <v>310</v>
       </c>
       <c r="D117" s="0" t="e">
         <f aca="false">VLOOKUP($A117,統計!$A:$G,6,)</f>
@@ -8792,7 +8811,7 @@
         <v>#N/A</v>
       </c>
       <c r="C118" s="0" t="s">
-        <v>309</v>
+        <v>311</v>
       </c>
       <c r="D118" s="0" t="e">
         <f aca="false">VLOOKUP($A118,統計!$A:$G,6,)</f>
@@ -8816,7 +8835,7 @@
         <v>#N/A</v>
       </c>
       <c r="C119" s="0" t="s">
-        <v>310</v>
+        <v>312</v>
       </c>
       <c r="D119" s="0" t="e">
         <f aca="false">VLOOKUP($A119,統計!$A:$G,6,)</f>
@@ -8840,7 +8859,7 @@
         <v>#N/A</v>
       </c>
       <c r="C120" s="0" t="s">
-        <v>311</v>
+        <v>313</v>
       </c>
       <c r="D120" s="0" t="e">
         <f aca="false">VLOOKUP($A120,統計!$A:$G,6,)</f>
@@ -8864,7 +8883,7 @@
         <v>#N/A</v>
       </c>
       <c r="C121" s="0" t="s">
-        <v>312</v>
+        <v>314</v>
       </c>
       <c r="D121" s="0" t="e">
         <f aca="false">VLOOKUP($A121,統計!$A:$G,6,)</f>
@@ -8888,7 +8907,7 @@
         <v>#N/A</v>
       </c>
       <c r="C122" s="0" t="s">
-        <v>313</v>
+        <v>315</v>
       </c>
       <c r="D122" s="0" t="e">
         <f aca="false">VLOOKUP($A122,統計!$A:$G,6,)</f>
@@ -8912,7 +8931,7 @@
         <v>#N/A</v>
       </c>
       <c r="C123" s="0" t="s">
-        <v>314</v>
+        <v>316</v>
       </c>
       <c r="D123" s="0" t="e">
         <f aca="false">VLOOKUP($A123,統計!$A:$G,6,)</f>
@@ -8936,7 +8955,7 @@
         <v>#N/A</v>
       </c>
       <c r="C124" s="0" t="s">
-        <v>315</v>
+        <v>317</v>
       </c>
       <c r="D124" s="0" t="e">
         <f aca="false">VLOOKUP($A124,統計!$A:$G,6,)</f>
@@ -8960,7 +8979,7 @@
         <v>#N/A</v>
       </c>
       <c r="C125" s="0" t="s">
-        <v>316</v>
+        <v>318</v>
       </c>
       <c r="D125" s="0" t="e">
         <f aca="false">VLOOKUP($A125,統計!$A:$G,6,)</f>
@@ -8984,7 +9003,7 @@
         <v>#N/A</v>
       </c>
       <c r="C126" s="0" t="s">
-        <v>317</v>
+        <v>319</v>
       </c>
       <c r="D126" s="0" t="e">
         <f aca="false">VLOOKUP($A126,統計!$A:$G,6,)</f>
@@ -9008,7 +9027,7 @@
         <v>#N/A</v>
       </c>
       <c r="C127" s="0" t="s">
-        <v>318</v>
+        <v>320</v>
       </c>
       <c r="D127" s="0" t="e">
         <f aca="false">VLOOKUP($A127,統計!$A:$G,6,)</f>
@@ -9032,7 +9051,7 @@
         <v>#N/A</v>
       </c>
       <c r="C128" s="0" t="s">
-        <v>319</v>
+        <v>321</v>
       </c>
       <c r="D128" s="0" t="e">
         <f aca="false">VLOOKUP($A128,統計!$A:$G,6,)</f>
@@ -9056,7 +9075,7 @@
         <v>#N/A</v>
       </c>
       <c r="C129" s="0" t="s">
-        <v>320</v>
+        <v>322</v>
       </c>
       <c r="D129" s="0" t="e">
         <f aca="false">VLOOKUP($A129,統計!$A:$G,6,)</f>
@@ -9080,7 +9099,7 @@
         <v>#N/A</v>
       </c>
       <c r="C130" s="0" t="s">
-        <v>321</v>
+        <v>323</v>
       </c>
       <c r="D130" s="0" t="e">
         <f aca="false">VLOOKUP($A130,統計!$A:$G,6,)</f>
@@ -9104,7 +9123,7 @@
         <v>#N/A</v>
       </c>
       <c r="C131" s="0" t="s">
-        <v>322</v>
+        <v>324</v>
       </c>
       <c r="D131" s="0" t="e">
         <f aca="false">VLOOKUP($A131,統計!$A:$G,6,)</f>
@@ -9128,7 +9147,7 @@
         <v>#N/A</v>
       </c>
       <c r="C132" s="0" t="s">
-        <v>323</v>
+        <v>325</v>
       </c>
       <c r="D132" s="0" t="e">
         <f aca="false">VLOOKUP($A132,統計!$A:$G,6,)</f>
@@ -9152,7 +9171,7 @@
         <v>#N/A</v>
       </c>
       <c r="C133" s="0" t="s">
-        <v>324</v>
+        <v>326</v>
       </c>
       <c r="D133" s="0" t="e">
         <f aca="false">VLOOKUP($A133,統計!$A:$G,6,)</f>
@@ -9176,7 +9195,7 @@
         <v>#N/A</v>
       </c>
       <c r="C134" s="0" t="s">
-        <v>325</v>
+        <v>327</v>
       </c>
       <c r="D134" s="0" t="e">
         <f aca="false">VLOOKUP($A134,統計!$A:$G,6,)</f>
@@ -9200,7 +9219,7 @@
         <v>#N/A</v>
       </c>
       <c r="C135" s="0" t="s">
-        <v>326</v>
+        <v>328</v>
       </c>
       <c r="D135" s="0" t="e">
         <f aca="false">VLOOKUP($A135,統計!$A:$G,6,)</f>
@@ -9224,7 +9243,7 @@
         <v>#N/A</v>
       </c>
       <c r="C136" s="0" t="s">
-        <v>327</v>
+        <v>329</v>
       </c>
       <c r="D136" s="0" t="e">
         <f aca="false">VLOOKUP($A136,統計!$A:$G,6,)</f>
@@ -9248,7 +9267,7 @@
         <v>#N/A</v>
       </c>
       <c r="C137" s="0" t="s">
-        <v>328</v>
+        <v>330</v>
       </c>
       <c r="D137" s="0" t="e">
         <f aca="false">VLOOKUP($A137,統計!$A:$G,6,)</f>
@@ -9272,7 +9291,7 @@
         <v>#N/A</v>
       </c>
       <c r="C138" s="0" t="s">
-        <v>329</v>
+        <v>331</v>
       </c>
       <c r="D138" s="0" t="e">
         <f aca="false">VLOOKUP($A138,統計!$A:$G,6,)</f>
@@ -9296,7 +9315,7 @@
         <v>#N/A</v>
       </c>
       <c r="C139" s="0" t="s">
-        <v>330</v>
+        <v>332</v>
       </c>
       <c r="D139" s="0" t="e">
         <f aca="false">VLOOKUP($A139,統計!$A:$G,6,)</f>
@@ -9320,7 +9339,7 @@
         <v>#N/A</v>
       </c>
       <c r="C140" s="0" t="s">
-        <v>331</v>
+        <v>333</v>
       </c>
       <c r="D140" s="0" t="e">
         <f aca="false">VLOOKUP($A140,統計!$A:$G,6,)</f>
@@ -9344,7 +9363,7 @@
         <v>#N/A</v>
       </c>
       <c r="C141" s="0" t="s">
-        <v>332</v>
+        <v>334</v>
       </c>
       <c r="D141" s="0" t="e">
         <f aca="false">VLOOKUP($A141,統計!$A:$G,6,)</f>
@@ -9368,7 +9387,7 @@
         <v>#N/A</v>
       </c>
       <c r="C142" s="0" t="s">
-        <v>333</v>
+        <v>335</v>
       </c>
       <c r="D142" s="0" t="e">
         <f aca="false">VLOOKUP($A142,統計!$A:$G,6,)</f>
@@ -9392,7 +9411,7 @@
         <v>#N/A</v>
       </c>
       <c r="C143" s="0" t="s">
-        <v>334</v>
+        <v>336</v>
       </c>
       <c r="D143" s="0" t="e">
         <f aca="false">VLOOKUP($A143,統計!$A:$G,6,)</f>
@@ -9416,7 +9435,7 @@
         <v>#N/A</v>
       </c>
       <c r="C144" s="0" t="s">
-        <v>335</v>
+        <v>337</v>
       </c>
       <c r="D144" s="0" t="e">
         <f aca="false">VLOOKUP($A144,統計!$A:$G,6,)</f>
@@ -9440,7 +9459,7 @@
         <v>#N/A</v>
       </c>
       <c r="C145" s="0" t="s">
-        <v>336</v>
+        <v>338</v>
       </c>
       <c r="D145" s="0" t="e">
         <f aca="false">VLOOKUP($A145,統計!$A:$G,6,)</f>
@@ -9464,7 +9483,7 @@
         <v>#N/A</v>
       </c>
       <c r="C146" s="0" t="s">
-        <v>337</v>
+        <v>339</v>
       </c>
       <c r="D146" s="0" t="e">
         <f aca="false">VLOOKUP($A146,統計!$A:$G,6,)</f>
@@ -9488,7 +9507,7 @@
         <v>#N/A</v>
       </c>
       <c r="C147" s="0" t="s">
-        <v>338</v>
+        <v>340</v>
       </c>
       <c r="D147" s="0" t="e">
         <f aca="false">VLOOKUP($A147,統計!$A:$G,6,)</f>
@@ -9512,7 +9531,7 @@
         <v>#N/A</v>
       </c>
       <c r="C148" s="0" t="s">
-        <v>339</v>
+        <v>341</v>
       </c>
       <c r="D148" s="0" t="e">
         <f aca="false">VLOOKUP($A148,統計!$A:$G,6,)</f>
@@ -9536,7 +9555,7 @@
         <v>#N/A</v>
       </c>
       <c r="C149" s="0" t="s">
-        <v>340</v>
+        <v>342</v>
       </c>
       <c r="D149" s="0" t="e">
         <f aca="false">VLOOKUP($A149,統計!$A:$G,6,)</f>
@@ -9560,7 +9579,7 @@
         <v>#N/A</v>
       </c>
       <c r="C150" s="0" t="s">
-        <v>341</v>
+        <v>343</v>
       </c>
       <c r="D150" s="0" t="e">
         <f aca="false">VLOOKUP($A150,統計!$A:$G,6,)</f>
@@ -9584,7 +9603,7 @@
         <v>#N/A</v>
       </c>
       <c r="C151" s="0" t="s">
-        <v>342</v>
+        <v>344</v>
       </c>
       <c r="D151" s="0" t="e">
         <f aca="false">VLOOKUP($A151,統計!$A:$G,6,)</f>
@@ -9608,7 +9627,7 @@
         <v>#N/A</v>
       </c>
       <c r="C152" s="0" t="s">
-        <v>343</v>
+        <v>345</v>
       </c>
       <c r="D152" s="0" t="e">
         <f aca="false">VLOOKUP($A152,統計!$A:$G,6,)</f>
@@ -9632,7 +9651,7 @@
         <v>#N/A</v>
       </c>
       <c r="C153" s="0" t="s">
-        <v>344</v>
+        <v>346</v>
       </c>
       <c r="D153" s="0" t="e">
         <f aca="false">VLOOKUP($A153,統計!$A:$G,6,)</f>
@@ -9656,7 +9675,7 @@
         <v>#N/A</v>
       </c>
       <c r="C154" s="0" t="s">
-        <v>345</v>
+        <v>347</v>
       </c>
       <c r="D154" s="0" t="e">
         <f aca="false">VLOOKUP($A154,統計!$A:$G,6,)</f>
@@ -9680,7 +9699,7 @@
         <v>#N/A</v>
       </c>
       <c r="C155" s="0" t="s">
-        <v>346</v>
+        <v>348</v>
       </c>
       <c r="D155" s="0" t="e">
         <f aca="false">VLOOKUP($A155,統計!$A:$G,6,)</f>
@@ -9704,7 +9723,7 @@
         <v>#N/A</v>
       </c>
       <c r="C156" s="0" t="s">
-        <v>347</v>
+        <v>349</v>
       </c>
       <c r="D156" s="0" t="e">
         <f aca="false">VLOOKUP($A156,統計!$A:$G,6,)</f>
@@ -9728,7 +9747,7 @@
         <v>#N/A</v>
       </c>
       <c r="C157" s="0" t="s">
-        <v>348</v>
+        <v>350</v>
       </c>
       <c r="D157" s="0" t="e">
         <f aca="false">VLOOKUP($A157,統計!$A:$G,6,)</f>
@@ -9752,7 +9771,7 @@
         <v>#N/A</v>
       </c>
       <c r="C158" s="0" t="s">
-        <v>349</v>
+        <v>351</v>
       </c>
       <c r="D158" s="0" t="e">
         <f aca="false">VLOOKUP($A158,統計!$A:$G,6,)</f>
@@ -9776,7 +9795,7 @@
         <v>#N/A</v>
       </c>
       <c r="C159" s="0" t="s">
-        <v>350</v>
+        <v>352</v>
       </c>
       <c r="D159" s="0" t="e">
         <f aca="false">VLOOKUP($A159,統計!$A:$G,6,)</f>
@@ -9800,7 +9819,7 @@
         <v>#N/A</v>
       </c>
       <c r="C160" s="0" t="s">
-        <v>351</v>
+        <v>353</v>
       </c>
       <c r="D160" s="0" t="e">
         <f aca="false">VLOOKUP($A160,統計!$A:$G,6,)</f>
@@ -9824,7 +9843,7 @@
         <v>#N/A</v>
       </c>
       <c r="C161" s="0" t="s">
-        <v>352</v>
+        <v>354</v>
       </c>
       <c r="D161" s="0" t="e">
         <f aca="false">VLOOKUP($A161,統計!$A:$G,6,)</f>
@@ -9848,7 +9867,7 @@
         <v>#N/A</v>
       </c>
       <c r="C162" s="0" t="s">
-        <v>353</v>
+        <v>355</v>
       </c>
       <c r="D162" s="0" t="e">
         <f aca="false">VLOOKUP($A162,統計!$A:$G,6,)</f>
@@ -9872,7 +9891,7 @@
         <v>#N/A</v>
       </c>
       <c r="C163" s="0" t="s">
-        <v>354</v>
+        <v>356</v>
       </c>
       <c r="D163" s="0" t="e">
         <f aca="false">VLOOKUP($A163,統計!$A:$G,6,)</f>
@@ -9896,7 +9915,7 @@
         <v>#N/A</v>
       </c>
       <c r="C164" s="0" t="s">
-        <v>355</v>
+        <v>357</v>
       </c>
       <c r="D164" s="0" t="e">
         <f aca="false">VLOOKUP($A164,統計!$A:$G,6,)</f>
@@ -9920,7 +9939,7 @@
         <v>#N/A</v>
       </c>
       <c r="C165" s="0" t="s">
-        <v>356</v>
+        <v>358</v>
       </c>
       <c r="D165" s="0" t="e">
         <f aca="false">VLOOKUP($A165,統計!$A:$G,6,)</f>
@@ -9944,7 +9963,7 @@
         <v>#N/A</v>
       </c>
       <c r="C166" s="0" t="s">
-        <v>357</v>
+        <v>359</v>
       </c>
       <c r="D166" s="0" t="e">
         <f aca="false">VLOOKUP($A166,統計!$A:$G,6,)</f>
@@ -9968,7 +9987,7 @@
         <v>#N/A</v>
       </c>
       <c r="C167" s="0" t="s">
-        <v>358</v>
+        <v>360</v>
       </c>
       <c r="D167" s="0" t="e">
         <f aca="false">VLOOKUP($A167,統計!$A:$G,6,)</f>
@@ -9992,7 +10011,7 @@
         <v>#N/A</v>
       </c>
       <c r="C168" s="0" t="s">
-        <v>359</v>
+        <v>361</v>
       </c>
       <c r="D168" s="0" t="e">
         <f aca="false">VLOOKUP($A168,統計!$A:$G,6,)</f>
@@ -10016,7 +10035,7 @@
         <v>#N/A</v>
       </c>
       <c r="C169" s="0" t="s">
-        <v>360</v>
+        <v>362</v>
       </c>
       <c r="D169" s="0" t="e">
         <f aca="false">VLOOKUP($A169,統計!$A:$G,6,)</f>
@@ -10040,7 +10059,7 @@
         <v>#N/A</v>
       </c>
       <c r="C170" s="0" t="s">
-        <v>361</v>
+        <v>363</v>
       </c>
       <c r="D170" s="0" t="e">
         <f aca="false">VLOOKUP($A170,統計!$A:$G,6,)</f>
@@ -10064,7 +10083,7 @@
         <v>#N/A</v>
       </c>
       <c r="C171" s="0" t="s">
-        <v>362</v>
+        <v>364</v>
       </c>
       <c r="D171" s="0" t="e">
         <f aca="false">VLOOKUP($A171,統計!$A:$G,6,)</f>
@@ -10088,7 +10107,7 @@
         <v>#N/A</v>
       </c>
       <c r="C172" s="0" t="s">
-        <v>363</v>
+        <v>365</v>
       </c>
       <c r="D172" s="0" t="e">
         <f aca="false">VLOOKUP($A172,統計!$A:$G,6,)</f>
@@ -10112,7 +10131,7 @@
         <v>#N/A</v>
       </c>
       <c r="C173" s="0" t="s">
-        <v>364</v>
+        <v>366</v>
       </c>
       <c r="D173" s="0" t="e">
         <f aca="false">VLOOKUP($A173,統計!$A:$G,6,)</f>
@@ -10136,7 +10155,7 @@
         <v>#N/A</v>
       </c>
       <c r="C174" s="0" t="s">
-        <v>365</v>
+        <v>367</v>
       </c>
       <c r="D174" s="0" t="e">
         <f aca="false">VLOOKUP($A174,統計!$A:$G,6,)</f>
@@ -10160,7 +10179,7 @@
         <v>#N/A</v>
       </c>
       <c r="C175" s="0" t="s">
-        <v>366</v>
+        <v>368</v>
       </c>
       <c r="D175" s="0" t="e">
         <f aca="false">VLOOKUP($A175,統計!$A:$G,6,)</f>
@@ -10184,7 +10203,7 @@
         <v>#N/A</v>
       </c>
       <c r="C176" s="0" t="s">
-        <v>367</v>
+        <v>369</v>
       </c>
       <c r="D176" s="0" t="e">
         <f aca="false">VLOOKUP($A176,統計!$A:$G,6,)</f>
@@ -10208,7 +10227,7 @@
         <v>#N/A</v>
       </c>
       <c r="C177" s="0" t="s">
-        <v>368</v>
+        <v>370</v>
       </c>
       <c r="D177" s="0" t="e">
         <f aca="false">VLOOKUP($A177,統計!$A:$G,6,)</f>
@@ -10232,7 +10251,7 @@
         <v>#N/A</v>
       </c>
       <c r="C178" s="0" t="s">
-        <v>369</v>
+        <v>371</v>
       </c>
       <c r="D178" s="0" t="e">
         <f aca="false">VLOOKUP($A178,統計!$A:$G,6,)</f>
@@ -10256,7 +10275,7 @@
         <v>#N/A</v>
       </c>
       <c r="C179" s="0" t="s">
-        <v>370</v>
+        <v>372</v>
       </c>
       <c r="D179" s="0" t="e">
         <f aca="false">VLOOKUP($A179,統計!$A:$G,6,)</f>
@@ -10280,7 +10299,7 @@
         <v>#N/A</v>
       </c>
       <c r="C180" s="0" t="s">
-        <v>371</v>
+        <v>373</v>
       </c>
       <c r="D180" s="0" t="e">
         <f aca="false">VLOOKUP($A180,統計!$A:$G,6,)</f>
@@ -10304,7 +10323,7 @@
         <v>#N/A</v>
       </c>
       <c r="C181" s="0" t="s">
-        <v>372</v>
+        <v>374</v>
       </c>
       <c r="D181" s="0" t="e">
         <f aca="false">VLOOKUP($A181,統計!$A:$G,6,)</f>
@@ -10328,7 +10347,7 @@
         <v>#N/A</v>
       </c>
       <c r="C182" s="0" t="s">
-        <v>373</v>
+        <v>375</v>
       </c>
       <c r="D182" s="0" t="e">
         <f aca="false">VLOOKUP($A182,統計!$A:$G,6,)</f>
@@ -10352,7 +10371,7 @@
         <v>#N/A</v>
       </c>
       <c r="C183" s="0" t="s">
-        <v>374</v>
+        <v>376</v>
       </c>
       <c r="D183" s="0" t="e">
         <f aca="false">VLOOKUP($A183,統計!$A:$G,6,)</f>
@@ -10376,7 +10395,7 @@
         <v>#N/A</v>
       </c>
       <c r="C184" s="0" t="s">
-        <v>375</v>
+        <v>377</v>
       </c>
       <c r="D184" s="0" t="e">
         <f aca="false">VLOOKUP($A184,統計!$A:$G,6,)</f>
@@ -10400,7 +10419,7 @@
         <v>#N/A</v>
       </c>
       <c r="C185" s="0" t="s">
-        <v>376</v>
+        <v>378</v>
       </c>
       <c r="D185" s="0" t="e">
         <f aca="false">VLOOKUP($A185,統計!$A:$G,6,)</f>
@@ -10424,7 +10443,7 @@
         <v>#N/A</v>
       </c>
       <c r="C186" s="0" t="s">
-        <v>377</v>
+        <v>379</v>
       </c>
       <c r="D186" s="0" t="e">
         <f aca="false">VLOOKUP($A186,統計!$A:$G,6,)</f>
@@ -10448,7 +10467,7 @@
         <v>#N/A</v>
       </c>
       <c r="C187" s="0" t="s">
-        <v>378</v>
+        <v>380</v>
       </c>
       <c r="D187" s="0" t="e">
         <f aca="false">VLOOKUP($A187,統計!$A:$G,6,)</f>
@@ -10472,7 +10491,7 @@
         <v>#N/A</v>
       </c>
       <c r="C188" s="0" t="s">
-        <v>379</v>
+        <v>381</v>
       </c>
       <c r="D188" s="0" t="e">
         <f aca="false">VLOOKUP($A188,統計!$A:$G,6,)</f>
@@ -10496,7 +10515,7 @@
         <v>#N/A</v>
       </c>
       <c r="C189" s="0" t="s">
-        <v>380</v>
+        <v>382</v>
       </c>
       <c r="D189" s="0" t="e">
         <f aca="false">VLOOKUP($A189,統計!$A:$G,6,)</f>
@@ -10520,7 +10539,7 @@
         <v>#N/A</v>
       </c>
       <c r="C190" s="0" t="s">
-        <v>381</v>
+        <v>383</v>
       </c>
       <c r="D190" s="0" t="e">
         <f aca="false">VLOOKUP($A190,統計!$A:$G,6,)</f>
@@ -10544,7 +10563,7 @@
         <v>#N/A</v>
       </c>
       <c r="C191" s="0" t="s">
-        <v>382</v>
+        <v>384</v>
       </c>
       <c r="D191" s="0" t="e">
         <f aca="false">VLOOKUP($A191,統計!$A:$G,6,)</f>
@@ -10568,7 +10587,7 @@
         <v>#N/A</v>
       </c>
       <c r="C192" s="0" t="s">
-        <v>383</v>
+        <v>385</v>
       </c>
       <c r="D192" s="0" t="e">
         <f aca="false">VLOOKUP($A192,統計!$A:$G,6,)</f>
@@ -10592,7 +10611,7 @@
         <v>#N/A</v>
       </c>
       <c r="C193" s="0" t="s">
-        <v>384</v>
+        <v>386</v>
       </c>
       <c r="D193" s="0" t="e">
         <f aca="false">VLOOKUP($A193,統計!$A:$G,6,)</f>
@@ -10616,7 +10635,7 @@
         <v>#N/A</v>
       </c>
       <c r="C194" s="0" t="s">
-        <v>385</v>
+        <v>387</v>
       </c>
       <c r="D194" s="0" t="e">
         <f aca="false">VLOOKUP($A194,統計!$A:$G,6,)</f>
@@ -10640,7 +10659,7 @@
         <v>#N/A</v>
       </c>
       <c r="C195" s="0" t="s">
-        <v>386</v>
+        <v>388</v>
       </c>
       <c r="D195" s="0" t="e">
         <f aca="false">VLOOKUP($A195,統計!$A:$G,6,)</f>
@@ -10664,7 +10683,7 @@
         <v>#N/A</v>
       </c>
       <c r="C196" s="0" t="s">
-        <v>387</v>
+        <v>389</v>
       </c>
       <c r="D196" s="0" t="e">
         <f aca="false">VLOOKUP($A196,統計!$A:$G,6,)</f>
@@ -10688,7 +10707,7 @@
         <v>#N/A</v>
       </c>
       <c r="C197" s="0" t="s">
-        <v>388</v>
+        <v>390</v>
       </c>
       <c r="D197" s="0" t="e">
         <f aca="false">VLOOKUP($A197,統計!$A:$G,6,)</f>
@@ -10712,7 +10731,7 @@
         <v>#N/A</v>
       </c>
       <c r="C198" s="0" t="s">
-        <v>389</v>
+        <v>391</v>
       </c>
       <c r="D198" s="0" t="e">
         <f aca="false">VLOOKUP($A198,統計!$A:$G,6,)</f>
@@ -10736,7 +10755,7 @@
         <v>#N/A</v>
       </c>
       <c r="C199" s="0" t="s">
-        <v>390</v>
+        <v>392</v>
       </c>
       <c r="D199" s="0" t="e">
         <f aca="false">VLOOKUP($A199,統計!$A:$G,6,)</f>
@@ -10760,7 +10779,7 @@
         <v>#N/A</v>
       </c>
       <c r="C200" s="0" t="s">
-        <v>391</v>
+        <v>393</v>
       </c>
       <c r="D200" s="0" t="e">
         <f aca="false">VLOOKUP($A200,統計!$A:$G,6,)</f>
@@ -10784,7 +10803,7 @@
         <v>#N/A</v>
       </c>
       <c r="C201" s="0" t="s">
-        <v>392</v>
+        <v>394</v>
       </c>
       <c r="D201" s="0" t="e">
         <f aca="false">VLOOKUP($A201,統計!$A:$G,6,)</f>
@@ -10808,7 +10827,7 @@
         <v>#N/A</v>
       </c>
       <c r="C202" s="0" t="s">
-        <v>393</v>
+        <v>395</v>
       </c>
       <c r="D202" s="0" t="e">
         <f aca="false">VLOOKUP($A202,統計!$A:$G,6,)</f>
@@ -10832,7 +10851,7 @@
         <v>#N/A</v>
       </c>
       <c r="C203" s="0" t="s">
-        <v>394</v>
+        <v>396</v>
       </c>
       <c r="D203" s="0" t="e">
         <f aca="false">VLOOKUP($A203,統計!$A:$G,6,)</f>
@@ -10856,7 +10875,7 @@
         <v>#N/A</v>
       </c>
       <c r="C204" s="0" t="s">
-        <v>395</v>
+        <v>397</v>
       </c>
       <c r="D204" s="0" t="e">
         <f aca="false">VLOOKUP($A204,統計!$A:$G,6,)</f>
@@ -10880,7 +10899,7 @@
         <v>#N/A</v>
       </c>
       <c r="C205" s="0" t="s">
-        <v>396</v>
+        <v>398</v>
       </c>
       <c r="D205" s="0" t="e">
         <f aca="false">VLOOKUP($A205,統計!$A:$G,6,)</f>
@@ -10904,7 +10923,7 @@
         <v>#N/A</v>
       </c>
       <c r="C206" s="0" t="s">
-        <v>397</v>
+        <v>399</v>
       </c>
       <c r="D206" s="0" t="e">
         <f aca="false">VLOOKUP($A206,統計!$A:$G,6,)</f>
@@ -10928,7 +10947,7 @@
         <v>#N/A</v>
       </c>
       <c r="C207" s="0" t="s">
-        <v>398</v>
+        <v>400</v>
       </c>
       <c r="D207" s="0" t="e">
         <f aca="false">VLOOKUP($A207,統計!$A:$G,6,)</f>
@@ -10952,7 +10971,7 @@
         <v>#N/A</v>
       </c>
       <c r="C208" s="0" t="s">
-        <v>399</v>
+        <v>401</v>
       </c>
       <c r="D208" s="0" t="e">
         <f aca="false">VLOOKUP($A208,統計!$A:$G,6,)</f>
@@ -10976,7 +10995,7 @@
         <v>#N/A</v>
       </c>
       <c r="C209" s="0" t="s">
-        <v>400</v>
+        <v>402</v>
       </c>
       <c r="D209" s="0" t="e">
         <f aca="false">VLOOKUP($A209,統計!$A:$G,6,)</f>
@@ -11000,7 +11019,7 @@
         <v>#N/A</v>
       </c>
       <c r="C210" s="0" t="s">
-        <v>401</v>
+        <v>403</v>
       </c>
       <c r="D210" s="0" t="e">
         <f aca="false">VLOOKUP($A210,統計!$A:$G,6,)</f>
@@ -11024,7 +11043,7 @@
         <v>#N/A</v>
       </c>
       <c r="C211" s="0" t="s">
-        <v>402</v>
+        <v>404</v>
       </c>
       <c r="D211" s="0" t="e">
         <f aca="false">VLOOKUP($A211,統計!$A:$G,6,)</f>
@@ -11048,7 +11067,7 @@
         <v>#N/A</v>
       </c>
       <c r="C212" s="0" t="s">
-        <v>403</v>
+        <v>405</v>
       </c>
       <c r="D212" s="0" t="e">
         <f aca="false">VLOOKUP($A212,統計!$A:$G,6,)</f>
@@ -11072,7 +11091,7 @@
         <v>#N/A</v>
       </c>
       <c r="C213" s="0" t="s">
-        <v>404</v>
+        <v>406</v>
       </c>
       <c r="D213" s="0" t="e">
         <f aca="false">VLOOKUP($A213,統計!$A:$G,6,)</f>
@@ -11096,7 +11115,7 @@
         <v>#N/A</v>
       </c>
       <c r="C214" s="0" t="s">
-        <v>405</v>
+        <v>407</v>
       </c>
       <c r="D214" s="0" t="e">
         <f aca="false">VLOOKUP($A214,統計!$A:$G,6,)</f>
@@ -11120,7 +11139,7 @@
         <v>#N/A</v>
       </c>
       <c r="C215" s="0" t="s">
-        <v>406</v>
+        <v>408</v>
       </c>
       <c r="D215" s="0" t="e">
         <f aca="false">VLOOKUP($A215,統計!$A:$G,6,)</f>
@@ -11144,7 +11163,7 @@
         <v>#N/A</v>
       </c>
       <c r="C216" s="0" t="s">
-        <v>407</v>
+        <v>409</v>
       </c>
       <c r="D216" s="0" t="e">
         <f aca="false">VLOOKUP($A216,統計!$A:$G,6,)</f>
@@ -11168,7 +11187,7 @@
         <v>#N/A</v>
       </c>
       <c r="C217" s="0" t="s">
-        <v>408</v>
+        <v>410</v>
       </c>
       <c r="D217" s="0" t="e">
         <f aca="false">VLOOKUP($A217,統計!$A:$G,6,)</f>
@@ -11192,7 +11211,7 @@
         <v>#N/A</v>
       </c>
       <c r="C218" s="0" t="s">
-        <v>409</v>
+        <v>411</v>
       </c>
       <c r="D218" s="0" t="e">
         <f aca="false">VLOOKUP($A218,統計!$A:$G,6,)</f>
@@ -11216,7 +11235,7 @@
         <v>#N/A</v>
       </c>
       <c r="C219" s="0" t="s">
-        <v>410</v>
+        <v>412</v>
       </c>
       <c r="D219" s="0" t="e">
         <f aca="false">VLOOKUP($A219,統計!$A:$G,6,)</f>
@@ -11240,7 +11259,7 @@
         <v>#N/A</v>
       </c>
       <c r="C220" s="0" t="s">
-        <v>411</v>
+        <v>413</v>
       </c>
       <c r="D220" s="0" t="e">
         <f aca="false">VLOOKUP($A220,統計!$A:$G,6,)</f>
@@ -11264,7 +11283,7 @@
         <v>#N/A</v>
       </c>
       <c r="C221" s="0" t="s">
-        <v>412</v>
+        <v>414</v>
       </c>
       <c r="D221" s="0" t="e">
         <f aca="false">VLOOKUP($A221,統計!$A:$G,6,)</f>
@@ -11288,7 +11307,7 @@
         <v>#N/A</v>
       </c>
       <c r="C222" s="0" t="s">
-        <v>413</v>
+        <v>415</v>
       </c>
       <c r="D222" s="0" t="e">
         <f aca="false">VLOOKUP($A222,統計!$A:$G,6,)</f>
@@ -11312,7 +11331,7 @@
         <v>#N/A</v>
       </c>
       <c r="C223" s="0" t="s">
-        <v>414</v>
+        <v>416</v>
       </c>
       <c r="D223" s="0" t="e">
         <f aca="false">VLOOKUP($A223,統計!$A:$G,6,)</f>
@@ -11336,7 +11355,7 @@
         <v>#N/A</v>
       </c>
       <c r="C224" s="0" t="s">
-        <v>415</v>
+        <v>417</v>
       </c>
       <c r="D224" s="0" t="e">
         <f aca="false">VLOOKUP($A224,統計!$A:$G,6,)</f>
@@ -11360,7 +11379,7 @@
         <v>#N/A</v>
       </c>
       <c r="C225" s="0" t="s">
-        <v>416</v>
+        <v>418</v>
       </c>
       <c r="D225" s="0" t="e">
         <f aca="false">VLOOKUP($A225,統計!$A:$G,6,)</f>
@@ -11384,7 +11403,7 @@
         <v>#N/A</v>
       </c>
       <c r="C226" s="0" t="s">
-        <v>417</v>
+        <v>419</v>
       </c>
       <c r="D226" s="0" t="e">
         <f aca="false">VLOOKUP($A226,統計!$A:$G,6,)</f>
@@ -11408,7 +11427,7 @@
         <v>#N/A</v>
       </c>
       <c r="C227" s="0" t="s">
-        <v>418</v>
+        <v>420</v>
       </c>
       <c r="D227" s="0" t="e">
         <f aca="false">VLOOKUP($A227,統計!$A:$G,6,)</f>
@@ -11432,7 +11451,7 @@
         <v>#N/A</v>
       </c>
       <c r="C228" s="0" t="s">
-        <v>419</v>
+        <v>421</v>
       </c>
       <c r="D228" s="0" t="e">
         <f aca="false">VLOOKUP($A228,統計!$A:$G,6,)</f>
@@ -11456,7 +11475,7 @@
         <v>#N/A</v>
       </c>
       <c r="C229" s="0" t="s">
-        <v>420</v>
+        <v>422</v>
       </c>
       <c r="D229" s="0" t="e">
         <f aca="false">VLOOKUP($A229,統計!$A:$G,6,)</f>
@@ -11480,7 +11499,7 @@
         <v>#N/A</v>
       </c>
       <c r="C230" s="0" t="s">
-        <v>421</v>
+        <v>423</v>
       </c>
       <c r="D230" s="0" t="e">
         <f aca="false">VLOOKUP($A230,統計!$A:$G,6,)</f>
@@ -11504,7 +11523,7 @@
         <v>#N/A</v>
       </c>
       <c r="C231" s="0" t="s">
-        <v>422</v>
+        <v>424</v>
       </c>
       <c r="D231" s="0" t="e">
         <f aca="false">VLOOKUP($A231,統計!$A:$G,6,)</f>
@@ -11528,7 +11547,7 @@
         <v>#N/A</v>
       </c>
       <c r="C232" s="0" t="s">
-        <v>423</v>
+        <v>425</v>
       </c>
       <c r="D232" s="0" t="e">
         <f aca="false">VLOOKUP($A232,統計!$A:$G,6,)</f>
@@ -11552,7 +11571,7 @@
         <v>#N/A</v>
       </c>
       <c r="C233" s="0" t="s">
-        <v>424</v>
+        <v>426</v>
       </c>
       <c r="D233" s="0" t="e">
         <f aca="false">VLOOKUP($A233,統計!$A:$G,6,)</f>
@@ -11576,7 +11595,7 @@
         <v>#N/A</v>
       </c>
       <c r="C234" s="0" t="s">
-        <v>425</v>
+        <v>427</v>
       </c>
       <c r="D234" s="0" t="e">
         <f aca="false">VLOOKUP($A234,統計!$A:$G,6,)</f>
@@ -11600,7 +11619,7 @@
         <v>#N/A</v>
       </c>
       <c r="C235" s="0" t="s">
-        <v>426</v>
+        <v>428</v>
       </c>
       <c r="D235" s="0" t="e">
         <f aca="false">VLOOKUP($A235,統計!$A:$G,6,)</f>
@@ -11624,7 +11643,7 @@
         <v>#N/A</v>
       </c>
       <c r="C236" s="0" t="s">
-        <v>427</v>
+        <v>429</v>
       </c>
       <c r="D236" s="0" t="e">
         <f aca="false">VLOOKUP($A236,統計!$A:$G,6,)</f>
@@ -11648,7 +11667,7 @@
         <v>#N/A</v>
       </c>
       <c r="C237" s="0" t="s">
-        <v>428</v>
+        <v>430</v>
       </c>
       <c r="D237" s="0" t="e">
         <f aca="false">VLOOKUP($A237,統計!$A:$G,6,)</f>
@@ -11672,7 +11691,7 @@
         <v>#N/A</v>
       </c>
       <c r="C238" s="0" t="s">
-        <v>429</v>
+        <v>431</v>
       </c>
       <c r="D238" s="0" t="e">
         <f aca="false">VLOOKUP($A238,統計!$A:$G,6,)</f>
@@ -11696,7 +11715,7 @@
         <v>#N/A</v>
       </c>
       <c r="C239" s="0" t="s">
-        <v>430</v>
+        <v>432</v>
       </c>
       <c r="D239" s="0" t="e">
         <f aca="false">VLOOKUP($A239,統計!$A:$G,6,)</f>
@@ -11720,7 +11739,7 @@
         <v>#N/A</v>
       </c>
       <c r="C240" s="0" t="s">
-        <v>431</v>
+        <v>433</v>
       </c>
       <c r="D240" s="0" t="e">
         <f aca="false">VLOOKUP($A240,統計!$A:$G,6,)</f>
@@ -11744,7 +11763,7 @@
         <v>#N/A</v>
       </c>
       <c r="C241" s="0" t="s">
-        <v>432</v>
+        <v>434</v>
       </c>
       <c r="D241" s="0" t="e">
         <f aca="false">VLOOKUP($A241,統計!$A:$G,6,)</f>
@@ -11768,7 +11787,7 @@
         <v>#N/A</v>
       </c>
       <c r="C242" s="0" t="s">
-        <v>433</v>
+        <v>435</v>
       </c>
       <c r="D242" s="0" t="e">
         <f aca="false">VLOOKUP($A242,統計!$A:$G,6,)</f>
@@ -11792,7 +11811,7 @@
         <v>#N/A</v>
       </c>
       <c r="C243" s="0" t="s">
-        <v>434</v>
+        <v>436</v>
       </c>
       <c r="D243" s="0" t="e">
         <f aca="false">VLOOKUP($A243,統計!$A:$G,6,)</f>
@@ -11816,7 +11835,7 @@
         <v>#N/A</v>
       </c>
       <c r="C244" s="0" t="s">
-        <v>435</v>
+        <v>437</v>
       </c>
       <c r="D244" s="0" t="e">
         <f aca="false">VLOOKUP($A244,統計!$A:$G,6,)</f>
@@ -11840,7 +11859,7 @@
         <v>#N/A</v>
       </c>
       <c r="C245" s="0" t="s">
-        <v>436</v>
+        <v>438</v>
       </c>
       <c r="D245" s="0" t="e">
         <f aca="false">VLOOKUP($A245,統計!$A:$G,6,)</f>
@@ -11864,7 +11883,7 @@
         <v>#N/A</v>
       </c>
       <c r="C246" s="0" t="s">
-        <v>437</v>
+        <v>439</v>
       </c>
       <c r="D246" s="0" t="e">
         <f aca="false">VLOOKUP($A246,統計!$A:$G,6,)</f>
@@ -11888,7 +11907,7 @@
         <v>#N/A</v>
       </c>
       <c r="C247" s="0" t="s">
-        <v>438</v>
+        <v>440</v>
       </c>
       <c r="D247" s="0" t="e">
         <f aca="false">VLOOKUP($A247,統計!$A:$G,6,)</f>
@@ -11912,7 +11931,7 @@
         <v>#N/A</v>
       </c>
       <c r="C248" s="0" t="s">
-        <v>439</v>
+        <v>441</v>
       </c>
       <c r="D248" s="0" t="e">
         <f aca="false">VLOOKUP($A248,統計!$A:$G,6,)</f>
@@ -11936,7 +11955,7 @@
         <v>#N/A</v>
       </c>
       <c r="C249" s="0" t="s">
-        <v>440</v>
+        <v>442</v>
       </c>
       <c r="D249" s="0" t="e">
         <f aca="false">VLOOKUP($A249,統計!$A:$G,6,)</f>
@@ -11960,7 +11979,7 @@
         <v>#N/A</v>
       </c>
       <c r="C250" s="0" t="s">
-        <v>441</v>
+        <v>443</v>
       </c>
       <c r="D250" s="0" t="e">
         <f aca="false">VLOOKUP($A250,統計!$A:$G,6,)</f>
@@ -11984,7 +12003,7 @@
         <v>#N/A</v>
       </c>
       <c r="C251" s="0" t="s">
-        <v>442</v>
+        <v>444</v>
       </c>
       <c r="D251" s="0" t="e">
         <f aca="false">VLOOKUP($A251,統計!$A:$G,6,)</f>
@@ -12008,7 +12027,7 @@
         <v>#N/A</v>
       </c>
       <c r="C252" s="0" t="s">
-        <v>443</v>
+        <v>445</v>
       </c>
       <c r="D252" s="0" t="e">
         <f aca="false">VLOOKUP($A252,統計!$A:$G,6,)</f>
@@ -12032,7 +12051,7 @@
         <v>#N/A</v>
       </c>
       <c r="C253" s="0" t="s">
-        <v>444</v>
+        <v>446</v>
       </c>
       <c r="D253" s="0" t="e">
         <f aca="false">VLOOKUP($A253,統計!$A:$G,6,)</f>
@@ -12056,7 +12075,7 @@
         <v>#N/A</v>
       </c>
       <c r="C254" s="0" t="s">
-        <v>445</v>
+        <v>447</v>
       </c>
       <c r="D254" s="0" t="e">
         <f aca="false">VLOOKUP($A254,統計!$A:$G,6,)</f>
@@ -12080,7 +12099,7 @@
         <v>#N/A</v>
       </c>
       <c r="C255" s="0" t="s">
-        <v>446</v>
+        <v>448</v>
       </c>
       <c r="D255" s="0" t="e">
         <f aca="false">VLOOKUP($A255,統計!$A:$G,6,)</f>
@@ -12104,7 +12123,7 @@
         <v>#N/A</v>
       </c>
       <c r="C256" s="0" t="s">
-        <v>447</v>
+        <v>449</v>
       </c>
       <c r="D256" s="0" t="e">
         <f aca="false">VLOOKUP($A256,統計!$A:$G,6,)</f>
@@ -12128,7 +12147,7 @@
         <v>#N/A</v>
       </c>
       <c r="C257" s="0" t="s">
-        <v>448</v>
+        <v>450</v>
       </c>
       <c r="D257" s="0" t="e">
         <f aca="false">VLOOKUP($A257,統計!$A:$G,6,)</f>
@@ -12152,7 +12171,7 @@
         <v>#N/A</v>
       </c>
       <c r="C258" s="0" t="s">
-        <v>449</v>
+        <v>451</v>
       </c>
       <c r="D258" s="0" t="e">
         <f aca="false">VLOOKUP($A258,統計!$A:$G,6,)</f>
@@ -12176,7 +12195,7 @@
         <v>#N/A</v>
       </c>
       <c r="C259" s="0" t="s">
-        <v>450</v>
+        <v>452</v>
       </c>
       <c r="D259" s="0" t="e">
         <f aca="false">VLOOKUP($A259,統計!$A:$G,6,)</f>
@@ -12200,7 +12219,7 @@
         <v>#N/A</v>
       </c>
       <c r="C260" s="0" t="s">
-        <v>451</v>
+        <v>453</v>
       </c>
       <c r="D260" s="0" t="e">
         <f aca="false">VLOOKUP($A260,統計!$A:$G,6,)</f>
@@ -12224,7 +12243,7 @@
         <v>#N/A</v>
       </c>
       <c r="C261" s="0" t="s">
-        <v>452</v>
+        <v>454</v>
       </c>
       <c r="D261" s="0" t="e">
         <f aca="false">VLOOKUP($A261,統計!$A:$G,6,)</f>
@@ -12248,7 +12267,7 @@
         <v>#N/A</v>
       </c>
       <c r="C262" s="0" t="s">
-        <v>453</v>
+        <v>455</v>
       </c>
       <c r="D262" s="0" t="e">
         <f aca="false">VLOOKUP($A262,統計!$A:$G,6,)</f>
@@ -12272,7 +12291,7 @@
         <v>#N/A</v>
       </c>
       <c r="C263" s="0" t="s">
-        <v>454</v>
+        <v>456</v>
       </c>
       <c r="D263" s="0" t="e">
         <f aca="false">VLOOKUP($A263,統計!$A:$G,6,)</f>
@@ -12296,7 +12315,7 @@
         <v>#N/A</v>
       </c>
       <c r="C264" s="0" t="s">
-        <v>455</v>
+        <v>457</v>
       </c>
       <c r="D264" s="0" t="e">
         <f aca="false">VLOOKUP($A264,統計!$A:$G,6,)</f>
@@ -12320,7 +12339,7 @@
         <v>#N/A</v>
       </c>
       <c r="C265" s="0" t="s">
-        <v>456</v>
+        <v>458</v>
       </c>
       <c r="D265" s="0" t="e">
         <f aca="false">VLOOKUP($A265,統計!$A:$G,6,)</f>
@@ -12344,7 +12363,7 @@
         <v>#N/A</v>
       </c>
       <c r="C266" s="0" t="s">
-        <v>457</v>
+        <v>459</v>
       </c>
       <c r="D266" s="0" t="e">
         <f aca="false">VLOOKUP($A266,統計!$A:$G,6,)</f>
@@ -12368,7 +12387,7 @@
         <v>#N/A</v>
       </c>
       <c r="C267" s="0" t="s">
-        <v>458</v>
+        <v>460</v>
       </c>
       <c r="D267" s="0" t="e">
         <f aca="false">VLOOKUP($A267,統計!$A:$G,6,)</f>
@@ -12392,7 +12411,7 @@
         <v>#N/A</v>
       </c>
       <c r="C268" s="0" t="s">
-        <v>459</v>
+        <v>461</v>
       </c>
       <c r="D268" s="0" t="e">
         <f aca="false">VLOOKUP($A268,統計!$A:$G,6,)</f>
@@ -12416,7 +12435,7 @@
         <v>#N/A</v>
       </c>
       <c r="C269" s="0" t="s">
-        <v>460</v>
+        <v>462</v>
       </c>
       <c r="D269" s="0" t="e">
         <f aca="false">VLOOKUP($A269,統計!$A:$G,6,)</f>
@@ -12440,7 +12459,7 @@
         <v>#N/A</v>
       </c>
       <c r="C270" s="0" t="s">
-        <v>461</v>
+        <v>463</v>
       </c>
       <c r="D270" s="0" t="e">
         <f aca="false">VLOOKUP($A270,統計!$A:$G,6,)</f>
@@ -12464,7 +12483,7 @@
         <v>#N/A</v>
       </c>
       <c r="C271" s="0" t="s">
-        <v>462</v>
+        <v>464</v>
       </c>
       <c r="D271" s="0" t="e">
         <f aca="false">VLOOKUP($A271,統計!$A:$G,6,)</f>
@@ -12488,7 +12507,7 @@
         <v>#N/A</v>
       </c>
       <c r="C272" s="0" t="s">
-        <v>463</v>
+        <v>465</v>
       </c>
       <c r="D272" s="0" t="e">
         <f aca="false">VLOOKUP($A272,統計!$A:$G,6,)</f>
@@ -12512,7 +12531,7 @@
         <v>#N/A</v>
       </c>
       <c r="C273" s="0" t="s">
-        <v>464</v>
+        <v>466</v>
       </c>
       <c r="D273" s="0" t="e">
         <f aca="false">VLOOKUP($A273,統計!$A:$G,6,)</f>
@@ -12536,7 +12555,7 @@
         <v>#N/A</v>
       </c>
       <c r="C274" s="0" t="s">
-        <v>465</v>
+        <v>467</v>
       </c>
       <c r="D274" s="0" t="e">
         <f aca="false">VLOOKUP($A274,統計!$A:$G,6,)</f>
@@ -12560,7 +12579,7 @@
         <v>#N/A</v>
       </c>
       <c r="C275" s="0" t="s">
-        <v>466</v>
+        <v>468</v>
       </c>
       <c r="D275" s="0" t="e">
         <f aca="false">VLOOKUP($A275,統計!$A:$G,6,)</f>
@@ -12584,7 +12603,7 @@
         <v>#N/A</v>
       </c>
       <c r="C276" s="0" t="s">
-        <v>467</v>
+        <v>469</v>
       </c>
       <c r="D276" s="0" t="e">
         <f aca="false">VLOOKUP($A276,統計!$A:$G,6,)</f>
@@ -12608,7 +12627,7 @@
         <v>#N/A</v>
       </c>
       <c r="C277" s="0" t="s">
-        <v>468</v>
+        <v>470</v>
       </c>
       <c r="D277" s="0" t="e">
         <f aca="false">VLOOKUP($A277,統計!$A:$G,6,)</f>
@@ -12632,7 +12651,7 @@
         <v>#N/A</v>
       </c>
       <c r="C278" s="0" t="s">
-        <v>469</v>
+        <v>471</v>
       </c>
       <c r="D278" s="0" t="e">
         <f aca="false">VLOOKUP($A278,統計!$A:$G,6,)</f>
@@ -12656,7 +12675,7 @@
         <v>#N/A</v>
       </c>
       <c r="C279" s="0" t="s">
-        <v>470</v>
+        <v>472</v>
       </c>
       <c r="D279" s="0" t="e">
         <f aca="false">VLOOKUP($A279,統計!$A:$G,6,)</f>
@@ -12680,7 +12699,7 @@
         <v>#N/A</v>
       </c>
       <c r="C280" s="0" t="s">
-        <v>471</v>
+        <v>473</v>
       </c>
       <c r="D280" s="0" t="e">
         <f aca="false">VLOOKUP($A280,統計!$A:$G,6,)</f>
@@ -12704,7 +12723,7 @@
         <v>#N/A</v>
       </c>
       <c r="C281" s="0" t="s">
-        <v>472</v>
+        <v>474</v>
       </c>
       <c r="D281" s="0" t="e">
         <f aca="false">VLOOKUP($A281,統計!$A:$G,6,)</f>
@@ -12728,7 +12747,7 @@
         <v>#N/A</v>
       </c>
       <c r="C282" s="0" t="s">
-        <v>473</v>
+        <v>475</v>
       </c>
       <c r="D282" s="0" t="e">
         <f aca="false">VLOOKUP($A282,統計!$A:$G,6,)</f>
@@ -12752,7 +12771,7 @@
         <v>#N/A</v>
       </c>
       <c r="C283" s="0" t="s">
-        <v>474</v>
+        <v>476</v>
       </c>
       <c r="D283" s="0" t="e">
         <f aca="false">VLOOKUP($A283,統計!$A:$G,6,)</f>
@@ -12776,7 +12795,7 @@
         <v>#N/A</v>
       </c>
       <c r="C284" s="0" t="s">
-        <v>475</v>
+        <v>477</v>
       </c>
       <c r="D284" s="0" t="e">
         <f aca="false">VLOOKUP($A284,統計!$A:$G,6,)</f>
@@ -12800,7 +12819,7 @@
         <v>#N/A</v>
       </c>
       <c r="C285" s="0" t="s">
-        <v>476</v>
+        <v>478</v>
       </c>
       <c r="D285" s="0" t="e">
         <f aca="false">VLOOKUP($A285,統計!$A:$G,6,)</f>
@@ -12824,7 +12843,7 @@
         <v>#N/A</v>
       </c>
       <c r="C286" s="0" t="s">
-        <v>477</v>
+        <v>479</v>
       </c>
       <c r="D286" s="0" t="e">
         <f aca="false">VLOOKUP($A286,統計!$A:$G,6,)</f>
@@ -12848,7 +12867,7 @@
         <v>#N/A</v>
       </c>
       <c r="C287" s="0" t="s">
-        <v>478</v>
+        <v>480</v>
       </c>
       <c r="D287" s="0" t="e">
         <f aca="false">VLOOKUP($A287,統計!$A:$G,6,)</f>
@@ -12872,7 +12891,7 @@
         <v>#N/A</v>
       </c>
       <c r="C288" s="0" t="s">
-        <v>479</v>
+        <v>481</v>
       </c>
       <c r="D288" s="0" t="e">
         <f aca="false">VLOOKUP($A288,統計!$A:$G,6,)</f>
@@ -12896,7 +12915,7 @@
         <v>#N/A</v>
       </c>
       <c r="C289" s="0" t="s">
-        <v>480</v>
+        <v>482</v>
       </c>
       <c r="D289" s="0" t="e">
         <f aca="false">VLOOKUP($A289,統計!$A:$G,6,)</f>
@@ -12920,7 +12939,7 @@
         <v>#N/A</v>
       </c>
       <c r="C290" s="0" t="s">
-        <v>481</v>
+        <v>483</v>
       </c>
       <c r="D290" s="0" t="e">
         <f aca="false">VLOOKUP($A290,統計!$A:$G,6,)</f>
@@ -12944,7 +12963,7 @@
         <v>#N/A</v>
       </c>
       <c r="C291" s="0" t="s">
-        <v>482</v>
+        <v>484</v>
       </c>
       <c r="D291" s="0" t="e">
         <f aca="false">VLOOKUP($A291,統計!$A:$G,6,)</f>
@@ -12968,7 +12987,7 @@
         <v>#N/A</v>
       </c>
       <c r="C292" s="0" t="s">
-        <v>483</v>
+        <v>485</v>
       </c>
       <c r="D292" s="0" t="e">
         <f aca="false">VLOOKUP($A292,統計!$A:$G,6,)</f>
@@ -12992,7 +13011,7 @@
         <v>#N/A</v>
       </c>
       <c r="C293" s="0" t="s">
-        <v>484</v>
+        <v>486</v>
       </c>
       <c r="D293" s="0" t="e">
         <f aca="false">VLOOKUP($A293,統計!$A:$G,6,)</f>
@@ -13016,7 +13035,7 @@
         <v>#N/A</v>
       </c>
       <c r="C294" s="0" t="s">
-        <v>485</v>
+        <v>487</v>
       </c>
       <c r="D294" s="0" t="e">
         <f aca="false">VLOOKUP($A294,統計!$A:$G,6,)</f>
@@ -13040,7 +13059,7 @@
         <v>#N/A</v>
       </c>
       <c r="C295" s="0" t="s">
-        <v>486</v>
+        <v>488</v>
       </c>
       <c r="D295" s="0" t="e">
         <f aca="false">VLOOKUP($A295,統計!$A:$G,6,)</f>
@@ -13076,13 +13095,13 @@
   <sheetData>
     <row r="1" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B1" s="0" t="s">
-        <v>487</v>
+        <v>489</v>
       </c>
       <c r="C1" s="0" t="s">
-        <v>488</v>
+        <v>490</v>
       </c>
       <c r="D1" s="0" t="s">
-        <v>489</v>
+        <v>491</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -13096,30 +13115,30 @@
         <v>1173</v>
       </c>
       <c r="E2" s="0" t="s">
-        <v>490</v>
+        <v>492</v>
       </c>
       <c r="G2" s="0" t="n">
         <f aca="false">C2/B2</f>
         <v>2.41791044776119</v>
       </c>
       <c r="H2" s="0" t="s">
-        <v>491</v>
+        <v>493</v>
       </c>
       <c r="K2" s="0" t="n">
         <f aca="false">D2/C2</f>
         <v>1.81018518518519</v>
       </c>
       <c r="L2" s="0" t="s">
-        <v>492</v>
+        <v>494</v>
       </c>
       <c r="N2" s="0" t="s">
-        <v>493</v>
+        <v>495</v>
       </c>
       <c r="O2" s="0" t="n">
         <v>80</v>
       </c>
       <c r="P2" s="0" t="s">
-        <v>494</v>
+        <v>496</v>
       </c>
       <c r="Q2" s="0" t="n">
         <f aca="false">O2/D2</f>
@@ -13131,7 +13150,7 @@
         <v>1239</v>
       </c>
       <c r="E3" s="0" t="s">
-        <v>495</v>
+        <v>497</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -13139,7 +13158,7 @@
         <v>2175</v>
       </c>
       <c r="E4" s="0" t="s">
-        <v>496</v>
+        <v>498</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -13150,19 +13169,19 @@
         <v>18</v>
       </c>
       <c r="G5" s="0" t="s">
-        <v>497</v>
+        <v>499</v>
       </c>
       <c r="H5" s="0" t="s">
-        <v>498</v>
+        <v>500</v>
       </c>
       <c r="I5" s="0" t="s">
-        <v>499</v>
+        <v>501</v>
       </c>
       <c r="K5" s="0" t="s">
-        <v>500</v>
+        <v>502</v>
       </c>
       <c r="L5" s="0" t="s">
-        <v>501</v>
+        <v>503</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -13170,7 +13189,7 @@
         <v>3732</v>
       </c>
       <c r="E6" s="0" t="s">
-        <v>502</v>
+        <v>504</v>
       </c>
       <c r="G6" s="0" t="n">
         <f aca="false">C6-C2</f>
@@ -13201,7 +13220,7 @@
         <v>22</v>
       </c>
       <c r="G7" s="0" t="s">
-        <v>503</v>
+        <v>505</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -13210,18 +13229,18 @@
         <v>0.0674157303370787</v>
       </c>
       <c r="O8" s="0" t="s">
-        <v>504</v>
+        <v>506</v>
       </c>
       <c r="P8" s="0" t="s">
-        <v>505</v>
+        <v>507</v>
       </c>
       <c r="Q8" s="0" t="s">
-        <v>506</v>
+        <v>508</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="N9" s="0" t="s">
-        <v>507</v>
+        <v>509</v>
       </c>
       <c r="O9" s="0" t="n">
         <v>1</v>
@@ -13237,7 +13256,7 @@
     </row>
     <row r="10" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="N10" s="0" t="s">
-        <v>507</v>
+        <v>509</v>
       </c>
       <c r="O10" s="0" t="n">
         <v>2</v>
@@ -13253,7 +13272,7 @@
     </row>
     <row r="11" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="N11" s="0" t="s">
-        <v>507</v>
+        <v>509</v>
       </c>
       <c r="O11" s="0" t="n">
         <v>294</v>
@@ -13269,7 +13288,7 @@
     </row>
     <row r="13" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="N13" s="0" t="s">
-        <v>508</v>
+        <v>510</v>
       </c>
       <c r="O13" s="0" t="n">
         <v>200</v>
@@ -13277,7 +13296,7 @@
     </row>
     <row r="14" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="N14" s="0" t="s">
-        <v>509</v>
+        <v>511</v>
       </c>
       <c r="O14" s="0" t="n">
         <v>118</v>

--- a/5_筆記/閱讀數據.xlsx
+++ b/5_筆記/閱讀數據.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="518" uniqueCount="512">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="520" uniqueCount="514">
   <si>
     <t xml:space="preserve">索引號</t>
   </si>
@@ -853,6 +853,12 @@
   </si>
   <si>
     <t xml:space="preserve">晉紀四</t>
+  </si>
+  <si>
+    <t xml:space="preserve">八王之亂人物表</t>
+  </si>
+  <si>
+    <t xml:space="preserve">司馬炎24年至25年、晉惠帝至9年</t>
   </si>
   <si>
     <t xml:space="preserve">晉紀五</t>
@@ -1564,11 +1570,12 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="4">
+  <numFmts count="5">
     <numFmt numFmtId="164" formatCode="General"/>
     <numFmt numFmtId="165" formatCode="yyyy\-m\-d"/>
-    <numFmt numFmtId="166" formatCode="0%"/>
-    <numFmt numFmtId="167" formatCode="0.00%"/>
+    <numFmt numFmtId="166" formatCode="yyyy\-mm\-dd"/>
+    <numFmt numFmtId="167" formatCode="0%"/>
+    <numFmt numFmtId="168" formatCode="0.00%"/>
   </numFmts>
   <fonts count="9">
     <font>
@@ -1688,11 +1695,11 @@
     <xf numFmtId="41" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="44" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="166" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="167" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="12">
+  <cellXfs count="13">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -1721,6 +1728,10 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
+    <xf numFmtId="166" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -1737,7 +1748,7 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="167" fontId="0" fillId="0" borderId="0" xfId="19" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="168" fontId="0" fillId="0" borderId="0" xfId="19" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -1813,7 +1824,7 @@
 </styleSheet>
 </file>
 
-<file path=xl/charts/chart3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/charts/chart4.xml><?xml version="1.0" encoding="utf-8"?>
 <c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <c:lang val="en-US"/>
   <c:roundedCorners val="0"/>
@@ -2173,16 +2184,19 @@
                 <c:pt idx="80">
                   <c:v>0.888888888888889</c:v>
                 </c:pt>
+                <c:pt idx="81">
+                  <c:v>1.5</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:yVal>
           <c:smooth val="1"/>
         </c:ser>
-        <c:axId val="57524932"/>
-        <c:axId val="83774724"/>
+        <c:axId val="38421606"/>
+        <c:axId val="95797626"/>
       </c:scatterChart>
       <c:valAx>
-        <c:axId val="57524932"/>
+        <c:axId val="38421606"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -2258,12 +2272,12 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="83774724"/>
+        <c:crossAx val="95797626"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="midCat"/>
       </c:valAx>
       <c:valAx>
-        <c:axId val="83774724"/>
+        <c:axId val="95797626"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -2339,7 +2353,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="57524932"/>
+        <c:crossAx val="38421606"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="midCat"/>
       </c:valAx>
@@ -2374,11 +2388,11 @@
       <xdr:col>10</xdr:col>
       <xdr:colOff>90360</xdr:colOff>
       <xdr:row>11</xdr:row>
-      <xdr:rowOff>109440</xdr:rowOff>
+      <xdr:rowOff>109800</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>15</xdr:col>
-      <xdr:colOff>669600</xdr:colOff>
+      <xdr:colOff>669240</xdr:colOff>
       <xdr:row>27</xdr:row>
       <xdr:rowOff>107640</xdr:rowOff>
     </xdr:to>
@@ -2388,8 +2402,8 @@
         <xdr:cNvGraphicFramePr/>
       </xdr:nvGraphicFramePr>
       <xdr:xfrm>
-        <a:off x="6835320" y="1995120"/>
-        <a:ext cx="4149720" cy="2741400"/>
+        <a:off x="6918480" y="1995480"/>
+        <a:ext cx="4149360" cy="2741040"/>
       </xdr:xfrm>
       <a:graphic>
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
@@ -2407,12 +2421,13 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:R82"/>
+  <dimension ref="A1:R83"/>
   <sheetFormatPr defaultColWidth="8.68359375" defaultRowHeight="13.5" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="7.76"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="5.76"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="3" style="1" width="11.62"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="1" width="12.81"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="1" width="11.62"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="5" style="0" width="9.76"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="0" width="7.76"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="9" style="0" width="14.12"/>
@@ -2522,19 +2537,19 @@
       </c>
       <c r="O2" s="0" t="n">
         <f aca="false">L2*$L$10</f>
-        <v>611.160493827161</v>
+        <v>616.146341463415</v>
       </c>
       <c r="P2" s="1" t="n">
         <f aca="false">$C$2+O2</f>
-        <v>44630.1604938272</v>
+        <v>44635.1463414634</v>
       </c>
       <c r="Q2" s="0" t="n">
         <f aca="false">(M2-$F$2)*$L$11</f>
-        <v>494.239180822187</v>
+        <v>488.246554437988</v>
       </c>
       <c r="R2" s="1" t="n">
         <f aca="false">$C$2+Q2</f>
-        <v>44513.2391808222</v>
+        <v>44507.246554438</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2585,19 +2600,19 @@
       </c>
       <c r="O3" s="0" t="n">
         <f aca="false">L3*$L$10</f>
-        <v>701.037037037037</v>
+        <v>706.756097560976</v>
       </c>
       <c r="P3" s="1" t="n">
         <f aca="false">$C$2+O3</f>
-        <v>44720.037037037</v>
+        <v>44725.756097561</v>
       </c>
       <c r="Q3" s="0" t="n">
         <f aca="false">(M3-$F$2)*$L$11</f>
-        <v>541.838459874083</v>
+        <v>535.268694512273</v>
       </c>
       <c r="R3" s="1" t="n">
         <f aca="false">$C$2+Q3</f>
-        <v>44560.8384598741</v>
+        <v>44554.2686945123</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2648,19 +2663,19 @@
       </c>
       <c r="O4" s="0" t="n">
         <f aca="false">L4*$L$10</f>
-        <v>1060.54320987654</v>
+        <v>1069.19512195122</v>
       </c>
       <c r="P4" s="1" t="n">
         <f aca="false">$C$2+O4</f>
-        <v>45079.5432098766</v>
+        <v>45088.1951219512</v>
       </c>
       <c r="Q4" s="0" t="n">
         <f aca="false">(M4-$F$2)*$L$11</f>
-        <v>652.903444328507</v>
+        <v>644.98702135227</v>
       </c>
       <c r="R4" s="1" t="n">
         <f aca="false">$C$2+Q4</f>
-        <v>44671.9034443285</v>
+        <v>44663.9870213523</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2711,19 +2726,19 @@
       </c>
       <c r="O5" s="0" t="n">
         <f aca="false">L5*$L$10</f>
-        <v>1581.82716049383</v>
+        <v>1594.73170731707</v>
       </c>
       <c r="P5" s="1" t="n">
         <f aca="false">$C$2+O5</f>
-        <v>45600.8271604938</v>
+        <v>45613.7317073171</v>
       </c>
       <c r="Q5" s="0" t="n">
         <f aca="false">(M5-$F$2)*$L$11</f>
-        <v>786.974746991347</v>
+        <v>777.432715894838</v>
       </c>
       <c r="R5" s="1" t="n">
         <f aca="false">$C$2+Q5</f>
-        <v>44805.9747469913</v>
+        <v>44796.4327158948</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2774,19 +2789,19 @@
       </c>
       <c r="O6" s="0" t="n">
         <f aca="false">L6*$L$10</f>
-        <v>2381.72839506173</v>
+        <v>2401.15853658537</v>
       </c>
       <c r="P6" s="1" t="n">
         <f aca="false">$C$2+O6</f>
-        <v>46400.7283950617</v>
+        <v>46420.1585365854</v>
       </c>
       <c r="Q6" s="0" t="n">
         <f aca="false">(M6-$F$2)*$L$11</f>
-        <v>1039.2509259664</v>
+        <v>1026.65005828855</v>
       </c>
       <c r="R6" s="1" t="n">
         <f aca="false">$C$2+Q6</f>
-        <v>45058.2509259664</v>
+        <v>45045.6500582886</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2837,19 +2852,19 @@
       </c>
       <c r="O7" s="0" t="n">
         <f aca="false">L7*$L$10</f>
-        <v>2642.37037037037</v>
+        <v>2663.92682926829</v>
       </c>
       <c r="P7" s="1" t="n">
         <f aca="false">$C$2+O7</f>
-        <v>46661.3703703704</v>
+        <v>46682.9268292683</v>
       </c>
       <c r="Q7" s="0" t="n">
         <f aca="false">(M7-$F$2)*$L$11</f>
-        <v>1080.50363447804</v>
+        <v>1067.40257968626</v>
       </c>
       <c r="R7" s="1" t="n">
         <f aca="false">$C$2+Q7</f>
-        <v>45099.503634478</v>
+        <v>45086.4025796863</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2900,19 +2915,19 @@
       </c>
       <c r="O8" s="0" t="n">
         <f aca="false">L8*$L$10</f>
-        <v>2642.37037037037</v>
+        <v>2663.92682926829</v>
       </c>
       <c r="P8" s="1" t="n">
         <f aca="false">$C$2+O8</f>
-        <v>46661.3703703704</v>
+        <v>46682.9268292683</v>
       </c>
       <c r="Q8" s="0" t="n">
         <f aca="false">(M8-$F$2)*$L$11</f>
-        <v>1080.50363447804</v>
+        <v>1067.40257968626</v>
       </c>
       <c r="R8" s="1" t="n">
         <f aca="false">$C$2+Q8</f>
-        <v>45099.503634478</v>
+        <v>45086.4025796863</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2987,7 +3002,7 @@
       </c>
       <c r="L10" s="0" t="n">
         <f aca="false">AVERAGE(E:E)</f>
-        <v>8.98765432098766</v>
+        <v>9.0609756097561</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3028,7 +3043,7 @@
       </c>
       <c r="L11" s="0" t="n">
         <f aca="false">AVEDEV(I:I)</f>
-        <v>0.7933213175316</v>
+        <v>0.78370233457141</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5475,6 +5490,40 @@
       <c r="I82" s="0" t="n">
         <f aca="false">E82/H82</f>
         <v>0.888888888888889</v>
+      </c>
+    </row>
+    <row r="83" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A83" s="0" t="n">
+        <v>704</v>
+      </c>
+      <c r="B83" s="0" t="str">
+        <f aca="false">"卷"&amp;ROW(B82)</f>
+        <v>卷82</v>
+      </c>
+      <c r="C83" s="7" t="n">
+        <v>44853</v>
+      </c>
+      <c r="D83" s="1" t="n">
+        <v>44867</v>
+      </c>
+      <c r="E83" s="0" t="n">
+        <f aca="false">D83-C83+1</f>
+        <v>15</v>
+      </c>
+      <c r="F83" s="0" t="n">
+        <f aca="false">G82+1</f>
+        <v>289</v>
+      </c>
+      <c r="G83" s="0" t="n">
+        <v>298</v>
+      </c>
+      <c r="H83" s="0" t="n">
+        <f aca="false">IF(F83*G83&lt;0,ABS(F83)+ABS(G83),G83-F83+1)</f>
+        <v>10</v>
+      </c>
+      <c r="I83" s="0" t="n">
+        <f aca="false">E83/H83</f>
+        <v>1.5</v>
       </c>
     </row>
   </sheetData>
@@ -5499,7 +5548,7 @@
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="0" width="33.38"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="0" width="22.12"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="7" width="22.03"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="8" width="22.03"/>
   </cols>
   <sheetData>
     <row r="1" s="3" customFormat="true" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5524,7 +5573,7 @@
       <c r="G1" s="6" t="s">
         <v>30</v>
       </c>
-      <c r="H1" s="8" t="s">
+      <c r="H1" s="9" t="s">
         <v>31</v>
       </c>
       <c r="I1" s="5" t="s">
@@ -5553,7 +5602,7 @@
       <c r="F2" s="0" t="s">
         <v>34</v>
       </c>
-      <c r="H2" s="7" t="s">
+      <c r="H2" s="8" t="s">
         <v>35</v>
       </c>
       <c r="I2" s="0" t="str">
@@ -5586,7 +5635,7 @@
       <c r="G3" s="0" t="s">
         <v>38</v>
       </c>
-      <c r="H3" s="7" t="s">
+      <c r="H3" s="8" t="s">
         <v>39</v>
       </c>
       <c r="I3" s="0" t="str">
@@ -5616,7 +5665,7 @@
       <c r="G4" s="0" t="s">
         <v>41</v>
       </c>
-      <c r="H4" s="7" t="s">
+      <c r="H4" s="8" t="s">
         <v>42</v>
       </c>
       <c r="I4" s="0" t="str">
@@ -5646,7 +5695,7 @@
       <c r="G5" s="0" t="s">
         <v>44</v>
       </c>
-      <c r="H5" s="7" t="s">
+      <c r="H5" s="8" t="s">
         <v>45</v>
       </c>
       <c r="I5" s="0" t="str">
@@ -5676,7 +5725,7 @@
       <c r="F6" s="0" t="s">
         <v>47</v>
       </c>
-      <c r="H6" s="7" t="s">
+      <c r="H6" s="8" t="s">
         <v>48</v>
       </c>
       <c r="I6" s="0" t="str">
@@ -5706,7 +5755,7 @@
       <c r="G7" s="0" t="s">
         <v>50</v>
       </c>
-      <c r="H7" s="7" t="s">
+      <c r="H7" s="8" t="s">
         <v>51</v>
       </c>
       <c r="I7" s="0" t="str">
@@ -5736,7 +5785,7 @@
       <c r="F8" s="0" t="s">
         <v>53</v>
       </c>
-      <c r="H8" s="7" t="s">
+      <c r="H8" s="8" t="s">
         <v>54</v>
       </c>
       <c r="I8" s="0" t="str">
@@ -5763,7 +5812,7 @@
         <f aca="false">VLOOKUP($A9,統計!$A:$G,7,)</f>
         <v>-207</v>
       </c>
-      <c r="H9" s="7" t="s">
+      <c r="H9" s="8" t="s">
         <v>56</v>
       </c>
       <c r="I9" s="0" t="str">
@@ -5796,7 +5845,7 @@
       <c r="G10" s="0" t="s">
         <v>59</v>
       </c>
-      <c r="H10" s="7" t="s">
+      <c r="H10" s="8" t="s">
         <v>60</v>
       </c>
       <c r="I10" s="0" t="str">
@@ -5826,7 +5875,7 @@
       <c r="G11" s="0" t="s">
         <v>62</v>
       </c>
-      <c r="H11" s="7" t="s">
+      <c r="H11" s="8" t="s">
         <v>63</v>
       </c>
       <c r="I11" s="0" t="str">
@@ -5856,7 +5905,7 @@
       <c r="G12" s="0" t="s">
         <v>65</v>
       </c>
-      <c r="H12" s="7" t="s">
+      <c r="H12" s="8" t="s">
         <v>66</v>
       </c>
       <c r="I12" s="0" t="str">
@@ -5883,7 +5932,7 @@
         <f aca="false">VLOOKUP($A13,統計!$A:$G,7,)</f>
         <v>-188</v>
       </c>
-      <c r="H13" s="7" t="s">
+      <c r="H13" s="8" t="s">
         <v>68</v>
       </c>
       <c r="I13" s="0" t="str">
@@ -5916,7 +5965,7 @@
       <c r="G14" s="0" t="s">
         <v>71</v>
       </c>
-      <c r="H14" s="7" t="s">
+      <c r="H14" s="8" t="s">
         <v>72</v>
       </c>
       <c r="I14" s="0" t="str">
@@ -5946,7 +5995,7 @@
       <c r="G15" s="0" t="s">
         <v>74</v>
       </c>
-      <c r="H15" s="7" t="s">
+      <c r="H15" s="8" t="s">
         <v>75</v>
       </c>
       <c r="I15" s="0" t="str">
@@ -5976,7 +6025,7 @@
       <c r="G16" s="0" t="s">
         <v>77</v>
       </c>
-      <c r="H16" s="7" t="s">
+      <c r="H16" s="8" t="s">
         <v>78</v>
       </c>
       <c r="I16" s="0" t="str">
@@ -6009,7 +6058,7 @@
       <c r="G17" s="0" t="s">
         <v>81</v>
       </c>
-      <c r="H17" s="7" t="s">
+      <c r="H17" s="8" t="s">
         <v>82</v>
       </c>
       <c r="I17" s="0" t="str">
@@ -6042,7 +6091,7 @@
       <c r="G18" s="0" t="s">
         <v>85</v>
       </c>
-      <c r="H18" s="7" t="s">
+      <c r="H18" s="8" t="s">
         <v>86</v>
       </c>
       <c r="I18" s="0" t="str">
@@ -6072,7 +6121,7 @@
       <c r="G19" s="0" t="s">
         <v>88</v>
       </c>
-      <c r="H19" s="7" t="s">
+      <c r="H19" s="8" t="s">
         <v>89</v>
       </c>
       <c r="I19" s="0" t="str">
@@ -6105,7 +6154,7 @@
       <c r="G20" s="0" t="s">
         <v>92</v>
       </c>
-      <c r="H20" s="7" t="s">
+      <c r="H20" s="8" t="s">
         <v>93</v>
       </c>
       <c r="I20" s="0" t="str">
@@ -6135,7 +6184,7 @@
       <c r="G21" s="0" t="s">
         <v>95</v>
       </c>
-      <c r="H21" s="7" t="s">
+      <c r="H21" s="8" t="s">
         <v>96</v>
       </c>
       <c r="I21" s="0" t="str">
@@ -6162,7 +6211,7 @@
         <f aca="false">VLOOKUP($A22,統計!$A:$G,7,)</f>
         <v>-99</v>
       </c>
-      <c r="H22" s="7" t="s">
+      <c r="H22" s="8" t="s">
         <v>98</v>
       </c>
       <c r="I22" s="0" t="str">
@@ -6192,7 +6241,7 @@
       <c r="G23" s="0" t="s">
         <v>100</v>
       </c>
-      <c r="H23" s="7" t="s">
+      <c r="H23" s="8" t="s">
         <v>101</v>
       </c>
       <c r="I23" s="0" t="str">
@@ -6222,7 +6271,7 @@
       <c r="F24" s="0" t="s">
         <v>103</v>
       </c>
-      <c r="H24" s="7" t="s">
+      <c r="H24" s="8" t="s">
         <v>104</v>
       </c>
       <c r="I24" s="0" t="str">
@@ -6255,7 +6304,7 @@
       <c r="G25" s="0" t="s">
         <v>107</v>
       </c>
-      <c r="H25" s="7" t="s">
+      <c r="H25" s="8" t="s">
         <v>108</v>
       </c>
       <c r="I25" s="0" t="str">
@@ -6285,7 +6334,7 @@
       <c r="G26" s="0" t="s">
         <v>110</v>
       </c>
-      <c r="H26" s="7" t="s">
+      <c r="H26" s="8" t="s">
         <v>111</v>
       </c>
       <c r="I26" s="0" t="str">
@@ -6312,7 +6361,7 @@
         <f aca="false">VLOOKUP($A27,統計!$A:$G,7,)</f>
         <v>-59</v>
       </c>
-      <c r="H27" s="7" t="s">
+      <c r="H27" s="8" t="s">
         <v>113</v>
       </c>
       <c r="I27" s="0" t="str">
@@ -6345,7 +6394,7 @@
       <c r="G28" s="0" t="s">
         <v>116</v>
       </c>
-      <c r="H28" s="7" t="s">
+      <c r="H28" s="8" t="s">
         <v>117</v>
       </c>
       <c r="I28" s="0" t="str">
@@ -6375,7 +6424,7 @@
       <c r="G29" s="0" t="s">
         <v>119</v>
       </c>
-      <c r="H29" s="7" t="s">
+      <c r="H29" s="8" t="s">
         <v>120</v>
       </c>
       <c r="I29" s="0" t="str">
@@ -6405,7 +6454,7 @@
       <c r="F30" s="0" t="s">
         <v>122</v>
       </c>
-      <c r="H30" s="7" t="s">
+      <c r="H30" s="8" t="s">
         <v>123</v>
       </c>
       <c r="I30" s="0" t="str">
@@ -6435,7 +6484,7 @@
       <c r="F31" s="0" t="s">
         <v>125</v>
       </c>
-      <c r="H31" s="7" t="s">
+      <c r="H31" s="8" t="s">
         <v>126</v>
       </c>
       <c r="I31" s="0" t="str">
@@ -6468,7 +6517,7 @@
       <c r="G32" s="0" t="s">
         <v>129</v>
       </c>
-      <c r="H32" s="7" t="s">
+      <c r="H32" s="8" t="s">
         <v>130</v>
       </c>
       <c r="I32" s="0" t="str">
@@ -6498,7 +6547,7 @@
       <c r="F33" s="0" t="s">
         <v>132</v>
       </c>
-      <c r="H33" s="7" t="s">
+      <c r="H33" s="8" t="s">
         <v>133</v>
       </c>
       <c r="I33" s="0" t="str">
@@ -6528,7 +6577,7 @@
       <c r="F34" s="0" t="s">
         <v>135</v>
       </c>
-      <c r="H34" s="7" t="s">
+      <c r="H34" s="8" t="s">
         <v>136</v>
       </c>
       <c r="I34" s="0" t="str">
@@ -6558,7 +6607,7 @@
       <c r="G35" s="0" t="s">
         <v>138</v>
       </c>
-      <c r="H35" s="7" t="s">
+      <c r="H35" s="8" t="s">
         <v>139</v>
       </c>
       <c r="I35" s="0" t="str">
@@ -6591,7 +6640,7 @@
       <c r="G36" s="0" t="s">
         <v>142</v>
       </c>
-      <c r="H36" s="7" t="s">
+      <c r="H36" s="8" t="s">
         <v>143</v>
       </c>
       <c r="I36" s="0" t="str">
@@ -6621,7 +6670,7 @@
       <c r="G37" s="0" t="s">
         <v>145</v>
       </c>
-      <c r="H37" s="7" t="s">
+      <c r="H37" s="8" t="s">
         <v>146</v>
       </c>
       <c r="I37" s="0" t="str">
@@ -6651,7 +6700,7 @@
       <c r="G38" s="0" t="s">
         <v>148</v>
       </c>
-      <c r="H38" s="7" t="s">
+      <c r="H38" s="8" t="s">
         <v>149</v>
       </c>
       <c r="I38" s="0" t="str">
@@ -6681,7 +6730,7 @@
       <c r="G39" s="0" t="s">
         <v>151</v>
       </c>
-      <c r="H39" s="7" t="s">
+      <c r="H39" s="8" t="s">
         <v>152</v>
       </c>
       <c r="I39" s="0" t="str">
@@ -6711,7 +6760,7 @@
       <c r="G40" s="0" t="s">
         <v>154</v>
       </c>
-      <c r="H40" s="7" t="s">
+      <c r="H40" s="8" t="s">
         <v>155</v>
       </c>
       <c r="I40" s="0" t="str">
@@ -6738,7 +6787,7 @@
         <f aca="false">VLOOKUP($A41,統計!$A:$G,7,)</f>
         <v>26</v>
       </c>
-      <c r="H41" s="7" t="s">
+      <c r="H41" s="8" t="s">
         <v>157</v>
       </c>
       <c r="I41" s="0" t="str">
@@ -6768,7 +6817,7 @@
       <c r="F42" s="0" t="s">
         <v>159</v>
       </c>
-      <c r="H42" s="7" t="s">
+      <c r="H42" s="8" t="s">
         <v>160</v>
       </c>
       <c r="I42" s="0" t="str">
@@ -6798,7 +6847,7 @@
       <c r="F43" s="0" t="s">
         <v>162</v>
       </c>
-      <c r="H43" s="7" t="s">
+      <c r="H43" s="8" t="s">
         <v>163</v>
       </c>
       <c r="I43" s="0" t="str">
@@ -6828,7 +6877,7 @@
       <c r="G44" s="0" t="s">
         <v>165</v>
       </c>
-      <c r="H44" s="7" t="s">
+      <c r="H44" s="8" t="s">
         <v>166</v>
       </c>
       <c r="I44" s="0" t="str">
@@ -6858,7 +6907,7 @@
       <c r="G45" s="0" t="s">
         <v>168</v>
       </c>
-      <c r="H45" s="7" t="s">
+      <c r="H45" s="8" t="s">
         <v>169</v>
       </c>
       <c r="I45" s="0" t="str">
@@ -6891,7 +6940,7 @@
       <c r="G46" s="0" t="s">
         <v>172</v>
       </c>
-      <c r="H46" s="7" t="s">
+      <c r="H46" s="8" t="s">
         <v>173</v>
       </c>
       <c r="I46" s="0" t="str">
@@ -6921,7 +6970,7 @@
       <c r="F47" s="0" t="s">
         <v>175</v>
       </c>
-      <c r="H47" s="7" t="s">
+      <c r="H47" s="8" t="s">
         <v>176</v>
       </c>
       <c r="I47" s="0" t="str">
@@ -6954,7 +7003,7 @@
       <c r="G48" s="0" t="s">
         <v>179</v>
       </c>
-      <c r="H48" s="7" t="s">
+      <c r="H48" s="8" t="s">
         <v>180</v>
       </c>
       <c r="I48" s="0" t="str">
@@ -6984,7 +7033,7 @@
       <c r="G49" s="0" t="s">
         <v>182</v>
       </c>
-      <c r="H49" s="7" t="s">
+      <c r="H49" s="8" t="s">
         <v>183</v>
       </c>
       <c r="I49" s="0" t="str">
@@ -7011,7 +7060,7 @@
         <f aca="false">VLOOKUP($A50,統計!$A:$G,7,)</f>
         <v>115</v>
       </c>
-      <c r="H50" s="9" t="s">
+      <c r="H50" s="10" t="s">
         <v>185</v>
       </c>
       <c r="I50" s="0" t="str">
@@ -7044,7 +7093,7 @@
       <c r="G51" s="0" t="s">
         <v>188</v>
       </c>
-      <c r="H51" s="9" t="s">
+      <c r="H51" s="10" t="s">
         <v>189</v>
       </c>
       <c r="I51" s="0" t="str">
@@ -7074,7 +7123,7 @@
       <c r="G52" s="0" t="s">
         <v>191</v>
       </c>
-      <c r="H52" s="7" t="s">
+      <c r="H52" s="8" t="s">
         <v>192</v>
       </c>
       <c r="I52" s="0" t="str">
@@ -7101,7 +7150,7 @@
         <f aca="false">VLOOKUP($A53,統計!$A:$G,7,)</f>
         <v>145</v>
       </c>
-      <c r="H53" s="7" t="s">
+      <c r="H53" s="8" t="s">
         <v>194</v>
       </c>
       <c r="I53" s="0" t="str">
@@ -7131,7 +7180,7 @@
       <c r="F54" s="0" t="s">
         <v>196</v>
       </c>
-      <c r="H54" s="7" t="s">
+      <c r="H54" s="8" t="s">
         <v>197</v>
       </c>
       <c r="I54" s="0" t="str">
@@ -7164,7 +7213,7 @@
       <c r="G55" s="0" t="s">
         <v>200</v>
       </c>
-      <c r="H55" s="7" t="s">
+      <c r="H55" s="8" t="s">
         <v>201</v>
       </c>
       <c r="I55" s="0" t="str">
@@ -7191,7 +7240,7 @@
         <f aca="false">VLOOKUP($A56,統計!$A:$G,7,)</f>
         <v>166</v>
       </c>
-      <c r="H56" s="7" t="s">
+      <c r="H56" s="8" t="s">
         <v>203</v>
       </c>
       <c r="I56" s="0" t="str">
@@ -7221,7 +7270,7 @@
       <c r="F57" s="0" t="s">
         <v>205</v>
       </c>
-      <c r="H57" s="7" t="s">
+      <c r="H57" s="8" t="s">
         <v>206</v>
       </c>
       <c r="I57" s="0" t="str">
@@ -7248,7 +7297,7 @@
         <f aca="false">VLOOKUP($A58,統計!$A:$G,7,)</f>
         <v>180</v>
       </c>
-      <c r="H58" s="7" t="s">
+      <c r="H58" s="8" t="s">
         <v>208</v>
       </c>
       <c r="I58" s="0" t="str">
@@ -7278,7 +7327,7 @@
       <c r="F59" s="0" t="s">
         <v>210</v>
       </c>
-      <c r="H59" s="7" t="s">
+      <c r="H59" s="8" t="s">
         <v>211</v>
       </c>
       <c r="I59" s="0" t="str">
@@ -7308,7 +7357,7 @@
       <c r="G60" s="0" t="s">
         <v>213</v>
       </c>
-      <c r="H60" s="7" t="s">
+      <c r="H60" s="8" t="s">
         <v>214</v>
       </c>
       <c r="I60" s="0" t="str">
@@ -7338,7 +7387,7 @@
       <c r="F61" s="0" t="s">
         <v>216</v>
       </c>
-      <c r="H61" s="7" t="s">
+      <c r="H61" s="8" t="s">
         <v>217</v>
       </c>
       <c r="I61" s="0" t="str">
@@ -7368,7 +7417,7 @@
       <c r="F62" s="0" t="s">
         <v>219</v>
       </c>
-      <c r="H62" s="7" t="s">
+      <c r="H62" s="8" t="s">
         <v>220</v>
       </c>
       <c r="I62" s="0" t="str">
@@ -7401,7 +7450,7 @@
       <c r="G63" s="0" t="s">
         <v>223</v>
       </c>
-      <c r="H63" s="10" t="s">
+      <c r="H63" s="11" t="s">
         <v>224</v>
       </c>
       <c r="I63" s="0" t="str">
@@ -7428,7 +7477,7 @@
         <f aca="false">VLOOKUP($A64,統計!$A:$G,7,)</f>
         <v>200</v>
       </c>
-      <c r="H64" s="10" t="s">
+      <c r="H64" s="11" t="s">
         <v>226</v>
       </c>
       <c r="I64" s="0" t="str">
@@ -7458,7 +7507,7 @@
       <c r="F65" s="0" t="s">
         <v>228</v>
       </c>
-      <c r="H65" s="7" t="s">
+      <c r="H65" s="8" t="s">
         <v>229</v>
       </c>
       <c r="I65" s="0" t="str">
@@ -7485,7 +7534,7 @@
         <f aca="false">VLOOKUP($A66,統計!$A:$G,7,)</f>
         <v>208</v>
       </c>
-      <c r="H66" s="7" t="s">
+      <c r="H66" s="8" t="s">
         <v>231</v>
       </c>
       <c r="I66" s="0" t="str">
@@ -7512,7 +7561,7 @@
         <f aca="false">VLOOKUP($A67,統計!$A:$G,7,)</f>
         <v>213</v>
       </c>
-      <c r="H67" s="7" t="s">
+      <c r="H67" s="8" t="s">
         <v>233</v>
       </c>
       <c r="I67" s="0" t="str">
@@ -7542,7 +7591,7 @@
       <c r="G68" s="0" t="s">
         <v>235</v>
       </c>
-      <c r="H68" s="7" t="s">
+      <c r="H68" s="8" t="s">
         <v>236</v>
       </c>
       <c r="I68" s="0" t="str">
@@ -7569,7 +7618,7 @@
         <f aca="false">VLOOKUP($A69,統計!$A:$G,7,)</f>
         <v>219</v>
       </c>
-      <c r="H69" s="7" t="s">
+      <c r="H69" s="8" t="s">
         <v>238</v>
       </c>
       <c r="I69" s="0" t="str">
@@ -7596,7 +7645,7 @@
         <f aca="false">VLOOKUP($A70,統計!$A:$G,7,)</f>
         <v>222</v>
       </c>
-      <c r="H70" s="7" t="s">
+      <c r="H70" s="8" t="s">
         <v>240</v>
       </c>
       <c r="I70" s="0" t="str">
@@ -7626,7 +7675,7 @@
       <c r="G71" s="0" t="s">
         <v>242</v>
       </c>
-      <c r="H71" s="7" t="s">
+      <c r="H71" s="8" t="s">
         <v>243</v>
       </c>
       <c r="I71" s="0" t="str">
@@ -7653,7 +7702,7 @@
         <f aca="false">VLOOKUP($A72,統計!$A:$G,7,)</f>
         <v>230</v>
       </c>
-      <c r="H72" s="7" t="s">
+      <c r="H72" s="8" t="s">
         <v>245</v>
       </c>
       <c r="I72" s="0" t="str">
@@ -7683,7 +7732,7 @@
       <c r="G73" s="0" t="s">
         <v>247</v>
       </c>
-      <c r="H73" s="7" t="s">
+      <c r="H73" s="8" t="s">
         <v>248</v>
       </c>
       <c r="I73" s="0" t="str">
@@ -7713,7 +7762,7 @@
       <c r="G74" s="0" t="s">
         <v>250</v>
       </c>
-      <c r="H74" s="7" t="s">
+      <c r="H74" s="8" t="s">
         <v>251</v>
       </c>
       <c r="I74" s="0" t="str">
@@ -7743,7 +7792,7 @@
       <c r="F75" s="0" t="s">
         <v>253</v>
       </c>
-      <c r="H75" s="7" t="s">
+      <c r="H75" s="8" t="s">
         <v>254</v>
       </c>
       <c r="I75" s="0" t="str">
@@ -7776,7 +7825,7 @@
       <c r="G76" s="0" t="s">
         <v>257</v>
       </c>
-      <c r="H76" s="7" t="s">
+      <c r="H76" s="8" t="s">
         <v>258</v>
       </c>
       <c r="I76" s="0" t="str">
@@ -7806,7 +7855,7 @@
       <c r="F77" s="0" t="s">
         <v>260</v>
       </c>
-      <c r="H77" s="7" t="s">
+      <c r="H77" s="8" t="s">
         <v>261</v>
       </c>
       <c r="I77" s="0" t="str">
@@ -7836,7 +7885,7 @@
       <c r="F78" s="0" t="s">
         <v>263</v>
       </c>
-      <c r="H78" s="7" t="s">
+      <c r="H78" s="8" t="s">
         <v>264</v>
       </c>
       <c r="I78" s="0" t="str">
@@ -7965,28 +8014,33 @@
       <c r="A83" s="0" t="n">
         <v>704</v>
       </c>
-      <c r="B83" s="0" t="e">
+      <c r="B83" s="0" t="str">
         <f aca="false">VLOOKUP($A83,統計!$A:$G,2,)</f>
-        <v>#N/A</v>
+        <v>卷82</v>
       </c>
       <c r="C83" s="0" t="s">
         <v>276</v>
       </c>
-      <c r="D83" s="0" t="e">
+      <c r="D83" s="0" t="n">
         <f aca="false">VLOOKUP($A83,統計!$A:$G,6,)</f>
-        <v>#N/A</v>
-      </c>
-      <c r="E83" s="0" t="e">
+        <v>289</v>
+      </c>
+      <c r="E83" s="0" t="n">
         <f aca="false">VLOOKUP($A83,統計!$A:$G,7,)</f>
-        <v>#N/A</v>
-      </c>
-      <c r="H83" s="0"/>
-      <c r="I83" s="0" t="e">
+        <v>298</v>
+      </c>
+      <c r="G83" s="0" t="s">
+        <v>277</v>
+      </c>
+      <c r="H83" s="0" t="s">
+        <v>278</v>
+      </c>
+      <c r="I83" s="0" t="str">
         <f aca="false">A83&amp;"|"&amp;"["&amp;B83&amp;"](5_筆記/资治通鉴"&amp;SUBSTITUTE(B83,"卷","")&amp;".html)|"&amp;C83&amp;"|"&amp;D83&amp;"|"&amp;E83&amp;"|"&amp;F83&amp;"|"&amp;G83&amp;"|"&amp;H83</f>
-        <v>#N/A</v>
-      </c>
-    </row>
-    <row r="84" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>704|[卷82](5_筆記/资治通鉴82.html)|晉紀四|289|298||八王之亂人物表|司馬炎24年至25年、晉惠帝至9年</v>
+      </c>
+    </row>
+    <row r="84" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A84" s="0" t="n">
         <v>705</v>
       </c>
@@ -7995,7 +8049,7 @@
         <v>#N/A</v>
       </c>
       <c r="C84" s="0" t="s">
-        <v>277</v>
+        <v>279</v>
       </c>
       <c r="D84" s="0" t="e">
         <f aca="false">VLOOKUP($A84,統計!$A:$G,6,)</f>
@@ -8005,6 +8059,7 @@
         <f aca="false">VLOOKUP($A84,統計!$A:$G,7,)</f>
         <v>#N/A</v>
       </c>
+      <c r="H84" s="0"/>
       <c r="I84" s="0" t="e">
         <f aca="false">A84&amp;"|"&amp;"["&amp;B84&amp;"](5_筆記/资治通鉴"&amp;SUBSTITUTE(B84,"卷","")&amp;".html)|"&amp;C84&amp;"|"&amp;D84&amp;"|"&amp;E84&amp;"|"&amp;F84&amp;"|"&amp;G84&amp;"|"&amp;H84</f>
         <v>#N/A</v>
@@ -8019,7 +8074,7 @@
         <v>#N/A</v>
       </c>
       <c r="C85" s="0" t="s">
-        <v>278</v>
+        <v>280</v>
       </c>
       <c r="D85" s="0" t="e">
         <f aca="false">VLOOKUP($A85,統計!$A:$G,6,)</f>
@@ -8043,7 +8098,7 @@
         <v>#N/A</v>
       </c>
       <c r="C86" s="0" t="s">
-        <v>279</v>
+        <v>281</v>
       </c>
       <c r="D86" s="0" t="e">
         <f aca="false">VLOOKUP($A86,統計!$A:$G,6,)</f>
@@ -8067,7 +8122,7 @@
         <v>#N/A</v>
       </c>
       <c r="C87" s="0" t="s">
-        <v>280</v>
+        <v>282</v>
       </c>
       <c r="D87" s="0" t="e">
         <f aca="false">VLOOKUP($A87,統計!$A:$G,6,)</f>
@@ -8091,7 +8146,7 @@
         <v>#N/A</v>
       </c>
       <c r="C88" s="0" t="s">
-        <v>281</v>
+        <v>283</v>
       </c>
       <c r="D88" s="0" t="e">
         <f aca="false">VLOOKUP($A88,統計!$A:$G,6,)</f>
@@ -8115,7 +8170,7 @@
         <v>#N/A</v>
       </c>
       <c r="C89" s="0" t="s">
-        <v>282</v>
+        <v>284</v>
       </c>
       <c r="D89" s="0" t="e">
         <f aca="false">VLOOKUP($A89,統計!$A:$G,6,)</f>
@@ -8139,7 +8194,7 @@
         <v>#N/A</v>
       </c>
       <c r="C90" s="0" t="s">
-        <v>283</v>
+        <v>285</v>
       </c>
       <c r="D90" s="0" t="e">
         <f aca="false">VLOOKUP($A90,統計!$A:$G,6,)</f>
@@ -8163,7 +8218,7 @@
         <v>#N/A</v>
       </c>
       <c r="C91" s="0" t="s">
-        <v>284</v>
+        <v>286</v>
       </c>
       <c r="D91" s="0" t="e">
         <f aca="false">VLOOKUP($A91,統計!$A:$G,6,)</f>
@@ -8187,7 +8242,7 @@
         <v>#N/A</v>
       </c>
       <c r="C92" s="0" t="s">
-        <v>285</v>
+        <v>287</v>
       </c>
       <c r="D92" s="0" t="e">
         <f aca="false">VLOOKUP($A92,統計!$A:$G,6,)</f>
@@ -8211,7 +8266,7 @@
         <v>#N/A</v>
       </c>
       <c r="C93" s="0" t="s">
-        <v>286</v>
+        <v>288</v>
       </c>
       <c r="D93" s="0" t="e">
         <f aca="false">VLOOKUP($A93,統計!$A:$G,6,)</f>
@@ -8235,7 +8290,7 @@
         <v>#N/A</v>
       </c>
       <c r="C94" s="0" t="s">
-        <v>287</v>
+        <v>289</v>
       </c>
       <c r="D94" s="0" t="e">
         <f aca="false">VLOOKUP($A94,統計!$A:$G,6,)</f>
@@ -8259,7 +8314,7 @@
         <v>#N/A</v>
       </c>
       <c r="C95" s="0" t="s">
-        <v>288</v>
+        <v>290</v>
       </c>
       <c r="D95" s="0" t="e">
         <f aca="false">VLOOKUP($A95,統計!$A:$G,6,)</f>
@@ -8283,7 +8338,7 @@
         <v>#N/A</v>
       </c>
       <c r="C96" s="0" t="s">
-        <v>289</v>
+        <v>291</v>
       </c>
       <c r="D96" s="0" t="e">
         <f aca="false">VLOOKUP($A96,統計!$A:$G,6,)</f>
@@ -8307,7 +8362,7 @@
         <v>#N/A</v>
       </c>
       <c r="C97" s="0" t="s">
-        <v>290</v>
+        <v>292</v>
       </c>
       <c r="D97" s="0" t="e">
         <f aca="false">VLOOKUP($A97,統計!$A:$G,6,)</f>
@@ -8331,7 +8386,7 @@
         <v>#N/A</v>
       </c>
       <c r="C98" s="0" t="s">
-        <v>291</v>
+        <v>293</v>
       </c>
       <c r="D98" s="0" t="e">
         <f aca="false">VLOOKUP($A98,統計!$A:$G,6,)</f>
@@ -8355,7 +8410,7 @@
         <v>#N/A</v>
       </c>
       <c r="C99" s="0" t="s">
-        <v>292</v>
+        <v>294</v>
       </c>
       <c r="D99" s="0" t="e">
         <f aca="false">VLOOKUP($A99,統計!$A:$G,6,)</f>
@@ -8379,7 +8434,7 @@
         <v>#N/A</v>
       </c>
       <c r="C100" s="0" t="s">
-        <v>293</v>
+        <v>295</v>
       </c>
       <c r="D100" s="0" t="e">
         <f aca="false">VLOOKUP($A100,統計!$A:$G,6,)</f>
@@ -8403,7 +8458,7 @@
         <v>#N/A</v>
       </c>
       <c r="C101" s="0" t="s">
-        <v>294</v>
+        <v>296</v>
       </c>
       <c r="D101" s="0" t="e">
         <f aca="false">VLOOKUP($A101,統計!$A:$G,6,)</f>
@@ -8427,7 +8482,7 @@
         <v>#N/A</v>
       </c>
       <c r="C102" s="0" t="s">
-        <v>295</v>
+        <v>297</v>
       </c>
       <c r="D102" s="0" t="e">
         <f aca="false">VLOOKUP($A102,統計!$A:$G,6,)</f>
@@ -8451,7 +8506,7 @@
         <v>#N/A</v>
       </c>
       <c r="C103" s="0" t="s">
-        <v>296</v>
+        <v>298</v>
       </c>
       <c r="D103" s="0" t="e">
         <f aca="false">VLOOKUP($A103,統計!$A:$G,6,)</f>
@@ -8475,7 +8530,7 @@
         <v>#N/A</v>
       </c>
       <c r="C104" s="0" t="s">
-        <v>297</v>
+        <v>299</v>
       </c>
       <c r="D104" s="0" t="e">
         <f aca="false">VLOOKUP($A104,統計!$A:$G,6,)</f>
@@ -8499,7 +8554,7 @@
         <v>#N/A</v>
       </c>
       <c r="C105" s="0" t="s">
-        <v>298</v>
+        <v>300</v>
       </c>
       <c r="D105" s="0" t="e">
         <f aca="false">VLOOKUP($A105,統計!$A:$G,6,)</f>
@@ -8523,7 +8578,7 @@
         <v>#N/A</v>
       </c>
       <c r="C106" s="0" t="s">
-        <v>299</v>
+        <v>301</v>
       </c>
       <c r="D106" s="0" t="e">
         <f aca="false">VLOOKUP($A106,統計!$A:$G,6,)</f>
@@ -8547,7 +8602,7 @@
         <v>#N/A</v>
       </c>
       <c r="C107" s="0" t="s">
-        <v>300</v>
+        <v>302</v>
       </c>
       <c r="D107" s="0" t="e">
         <f aca="false">VLOOKUP($A107,統計!$A:$G,6,)</f>
@@ -8571,7 +8626,7 @@
         <v>#N/A</v>
       </c>
       <c r="C108" s="0" t="s">
-        <v>301</v>
+        <v>303</v>
       </c>
       <c r="D108" s="0" t="e">
         <f aca="false">VLOOKUP($A108,統計!$A:$G,6,)</f>
@@ -8595,7 +8650,7 @@
         <v>#N/A</v>
       </c>
       <c r="C109" s="0" t="s">
-        <v>302</v>
+        <v>304</v>
       </c>
       <c r="D109" s="0" t="e">
         <f aca="false">VLOOKUP($A109,統計!$A:$G,6,)</f>
@@ -8619,7 +8674,7 @@
         <v>#N/A</v>
       </c>
       <c r="C110" s="0" t="s">
-        <v>303</v>
+        <v>305</v>
       </c>
       <c r="D110" s="0" t="e">
         <f aca="false">VLOOKUP($A110,統計!$A:$G,6,)</f>
@@ -8643,7 +8698,7 @@
         <v>#N/A</v>
       </c>
       <c r="C111" s="0" t="s">
-        <v>304</v>
+        <v>306</v>
       </c>
       <c r="D111" s="0" t="e">
         <f aca="false">VLOOKUP($A111,統計!$A:$G,6,)</f>
@@ -8667,7 +8722,7 @@
         <v>#N/A</v>
       </c>
       <c r="C112" s="0" t="s">
-        <v>305</v>
+        <v>307</v>
       </c>
       <c r="D112" s="0" t="e">
         <f aca="false">VLOOKUP($A112,統計!$A:$G,6,)</f>
@@ -8691,7 +8746,7 @@
         <v>#N/A</v>
       </c>
       <c r="C113" s="0" t="s">
-        <v>306</v>
+        <v>308</v>
       </c>
       <c r="D113" s="0" t="e">
         <f aca="false">VLOOKUP($A113,統計!$A:$G,6,)</f>
@@ -8715,7 +8770,7 @@
         <v>#N/A</v>
       </c>
       <c r="C114" s="0" t="s">
-        <v>307</v>
+        <v>309</v>
       </c>
       <c r="D114" s="0" t="e">
         <f aca="false">VLOOKUP($A114,統計!$A:$G,6,)</f>
@@ -8739,7 +8794,7 @@
         <v>#N/A</v>
       </c>
       <c r="C115" s="0" t="s">
-        <v>308</v>
+        <v>310</v>
       </c>
       <c r="D115" s="0" t="e">
         <f aca="false">VLOOKUP($A115,統計!$A:$G,6,)</f>
@@ -8763,7 +8818,7 @@
         <v>#N/A</v>
       </c>
       <c r="C116" s="0" t="s">
-        <v>309</v>
+        <v>311</v>
       </c>
       <c r="D116" s="0" t="e">
         <f aca="false">VLOOKUP($A116,統計!$A:$G,6,)</f>
@@ -8787,7 +8842,7 @@
         <v>#N/A</v>
       </c>
       <c r="C117" s="0" t="s">
-        <v>310</v>
+        <v>312</v>
       </c>
       <c r="D117" s="0" t="e">
         <f aca="false">VLOOKUP($A117,統計!$A:$G,6,)</f>
@@ -8811,7 +8866,7 @@
         <v>#N/A</v>
       </c>
       <c r="C118" s="0" t="s">
-        <v>311</v>
+        <v>313</v>
       </c>
       <c r="D118" s="0" t="e">
         <f aca="false">VLOOKUP($A118,統計!$A:$G,6,)</f>
@@ -8835,7 +8890,7 @@
         <v>#N/A</v>
       </c>
       <c r="C119" s="0" t="s">
-        <v>312</v>
+        <v>314</v>
       </c>
       <c r="D119" s="0" t="e">
         <f aca="false">VLOOKUP($A119,統計!$A:$G,6,)</f>
@@ -8859,7 +8914,7 @@
         <v>#N/A</v>
       </c>
       <c r="C120" s="0" t="s">
-        <v>313</v>
+        <v>315</v>
       </c>
       <c r="D120" s="0" t="e">
         <f aca="false">VLOOKUP($A120,統計!$A:$G,6,)</f>
@@ -8883,7 +8938,7 @@
         <v>#N/A</v>
       </c>
       <c r="C121" s="0" t="s">
-        <v>314</v>
+        <v>316</v>
       </c>
       <c r="D121" s="0" t="e">
         <f aca="false">VLOOKUP($A121,統計!$A:$G,6,)</f>
@@ -8907,7 +8962,7 @@
         <v>#N/A</v>
       </c>
       <c r="C122" s="0" t="s">
-        <v>315</v>
+        <v>317</v>
       </c>
       <c r="D122" s="0" t="e">
         <f aca="false">VLOOKUP($A122,統計!$A:$G,6,)</f>
@@ -8931,7 +8986,7 @@
         <v>#N/A</v>
       </c>
       <c r="C123" s="0" t="s">
-        <v>316</v>
+        <v>318</v>
       </c>
       <c r="D123" s="0" t="e">
         <f aca="false">VLOOKUP($A123,統計!$A:$G,6,)</f>
@@ -8955,7 +9010,7 @@
         <v>#N/A</v>
       </c>
       <c r="C124" s="0" t="s">
-        <v>317</v>
+        <v>319</v>
       </c>
       <c r="D124" s="0" t="e">
         <f aca="false">VLOOKUP($A124,統計!$A:$G,6,)</f>
@@ -8979,7 +9034,7 @@
         <v>#N/A</v>
       </c>
       <c r="C125" s="0" t="s">
-        <v>318</v>
+        <v>320</v>
       </c>
       <c r="D125" s="0" t="e">
         <f aca="false">VLOOKUP($A125,統計!$A:$G,6,)</f>
@@ -9003,7 +9058,7 @@
         <v>#N/A</v>
       </c>
       <c r="C126" s="0" t="s">
-        <v>319</v>
+        <v>321</v>
       </c>
       <c r="D126" s="0" t="e">
         <f aca="false">VLOOKUP($A126,統計!$A:$G,6,)</f>
@@ -9027,7 +9082,7 @@
         <v>#N/A</v>
       </c>
       <c r="C127" s="0" t="s">
-        <v>320</v>
+        <v>322</v>
       </c>
       <c r="D127" s="0" t="e">
         <f aca="false">VLOOKUP($A127,統計!$A:$G,6,)</f>
@@ -9051,7 +9106,7 @@
         <v>#N/A</v>
       </c>
       <c r="C128" s="0" t="s">
-        <v>321</v>
+        <v>323</v>
       </c>
       <c r="D128" s="0" t="e">
         <f aca="false">VLOOKUP($A128,統計!$A:$G,6,)</f>
@@ -9075,7 +9130,7 @@
         <v>#N/A</v>
       </c>
       <c r="C129" s="0" t="s">
-        <v>322</v>
+        <v>324</v>
       </c>
       <c r="D129" s="0" t="e">
         <f aca="false">VLOOKUP($A129,統計!$A:$G,6,)</f>
@@ -9099,7 +9154,7 @@
         <v>#N/A</v>
       </c>
       <c r="C130" s="0" t="s">
-        <v>323</v>
+        <v>325</v>
       </c>
       <c r="D130" s="0" t="e">
         <f aca="false">VLOOKUP($A130,統計!$A:$G,6,)</f>
@@ -9123,7 +9178,7 @@
         <v>#N/A</v>
       </c>
       <c r="C131" s="0" t="s">
-        <v>324</v>
+        <v>326</v>
       </c>
       <c r="D131" s="0" t="e">
         <f aca="false">VLOOKUP($A131,統計!$A:$G,6,)</f>
@@ -9147,7 +9202,7 @@
         <v>#N/A</v>
       </c>
       <c r="C132" s="0" t="s">
-        <v>325</v>
+        <v>327</v>
       </c>
       <c r="D132" s="0" t="e">
         <f aca="false">VLOOKUP($A132,統計!$A:$G,6,)</f>
@@ -9171,7 +9226,7 @@
         <v>#N/A</v>
       </c>
       <c r="C133" s="0" t="s">
-        <v>326</v>
+        <v>328</v>
       </c>
       <c r="D133" s="0" t="e">
         <f aca="false">VLOOKUP($A133,統計!$A:$G,6,)</f>
@@ -9195,7 +9250,7 @@
         <v>#N/A</v>
       </c>
       <c r="C134" s="0" t="s">
-        <v>327</v>
+        <v>329</v>
       </c>
       <c r="D134" s="0" t="e">
         <f aca="false">VLOOKUP($A134,統計!$A:$G,6,)</f>
@@ -9219,7 +9274,7 @@
         <v>#N/A</v>
       </c>
       <c r="C135" s="0" t="s">
-        <v>328</v>
+        <v>330</v>
       </c>
       <c r="D135" s="0" t="e">
         <f aca="false">VLOOKUP($A135,統計!$A:$G,6,)</f>
@@ -9243,7 +9298,7 @@
         <v>#N/A</v>
       </c>
       <c r="C136" s="0" t="s">
-        <v>329</v>
+        <v>331</v>
       </c>
       <c r="D136" s="0" t="e">
         <f aca="false">VLOOKUP($A136,統計!$A:$G,6,)</f>
@@ -9267,7 +9322,7 @@
         <v>#N/A</v>
       </c>
       <c r="C137" s="0" t="s">
-        <v>330</v>
+        <v>332</v>
       </c>
       <c r="D137" s="0" t="e">
         <f aca="false">VLOOKUP($A137,統計!$A:$G,6,)</f>
@@ -9291,7 +9346,7 @@
         <v>#N/A</v>
       </c>
       <c r="C138" s="0" t="s">
-        <v>331</v>
+        <v>333</v>
       </c>
       <c r="D138" s="0" t="e">
         <f aca="false">VLOOKUP($A138,統計!$A:$G,6,)</f>
@@ -9315,7 +9370,7 @@
         <v>#N/A</v>
       </c>
       <c r="C139" s="0" t="s">
-        <v>332</v>
+        <v>334</v>
       </c>
       <c r="D139" s="0" t="e">
         <f aca="false">VLOOKUP($A139,統計!$A:$G,6,)</f>
@@ -9339,7 +9394,7 @@
         <v>#N/A</v>
       </c>
       <c r="C140" s="0" t="s">
-        <v>333</v>
+        <v>335</v>
       </c>
       <c r="D140" s="0" t="e">
         <f aca="false">VLOOKUP($A140,統計!$A:$G,6,)</f>
@@ -9363,7 +9418,7 @@
         <v>#N/A</v>
       </c>
       <c r="C141" s="0" t="s">
-        <v>334</v>
+        <v>336</v>
       </c>
       <c r="D141" s="0" t="e">
         <f aca="false">VLOOKUP($A141,統計!$A:$G,6,)</f>
@@ -9387,7 +9442,7 @@
         <v>#N/A</v>
       </c>
       <c r="C142" s="0" t="s">
-        <v>335</v>
+        <v>337</v>
       </c>
       <c r="D142" s="0" t="e">
         <f aca="false">VLOOKUP($A142,統計!$A:$G,6,)</f>
@@ -9411,7 +9466,7 @@
         <v>#N/A</v>
       </c>
       <c r="C143" s="0" t="s">
-        <v>336</v>
+        <v>338</v>
       </c>
       <c r="D143" s="0" t="e">
         <f aca="false">VLOOKUP($A143,統計!$A:$G,6,)</f>
@@ -9435,7 +9490,7 @@
         <v>#N/A</v>
       </c>
       <c r="C144" s="0" t="s">
-        <v>337</v>
+        <v>339</v>
       </c>
       <c r="D144" s="0" t="e">
         <f aca="false">VLOOKUP($A144,統計!$A:$G,6,)</f>
@@ -9459,7 +9514,7 @@
         <v>#N/A</v>
       </c>
       <c r="C145" s="0" t="s">
-        <v>338</v>
+        <v>340</v>
       </c>
       <c r="D145" s="0" t="e">
         <f aca="false">VLOOKUP($A145,統計!$A:$G,6,)</f>
@@ -9483,7 +9538,7 @@
         <v>#N/A</v>
       </c>
       <c r="C146" s="0" t="s">
-        <v>339</v>
+        <v>341</v>
       </c>
       <c r="D146" s="0" t="e">
         <f aca="false">VLOOKUP($A146,統計!$A:$G,6,)</f>
@@ -9507,7 +9562,7 @@
         <v>#N/A</v>
       </c>
       <c r="C147" s="0" t="s">
-        <v>340</v>
+        <v>342</v>
       </c>
       <c r="D147" s="0" t="e">
         <f aca="false">VLOOKUP($A147,統計!$A:$G,6,)</f>
@@ -9531,7 +9586,7 @@
         <v>#N/A</v>
       </c>
       <c r="C148" s="0" t="s">
-        <v>341</v>
+        <v>343</v>
       </c>
       <c r="D148" s="0" t="e">
         <f aca="false">VLOOKUP($A148,統計!$A:$G,6,)</f>
@@ -9555,7 +9610,7 @@
         <v>#N/A</v>
       </c>
       <c r="C149" s="0" t="s">
-        <v>342</v>
+        <v>344</v>
       </c>
       <c r="D149" s="0" t="e">
         <f aca="false">VLOOKUP($A149,統計!$A:$G,6,)</f>
@@ -9579,7 +9634,7 @@
         <v>#N/A</v>
       </c>
       <c r="C150" s="0" t="s">
-        <v>343</v>
+        <v>345</v>
       </c>
       <c r="D150" s="0" t="e">
         <f aca="false">VLOOKUP($A150,統計!$A:$G,6,)</f>
@@ -9603,7 +9658,7 @@
         <v>#N/A</v>
       </c>
       <c r="C151" s="0" t="s">
-        <v>344</v>
+        <v>346</v>
       </c>
       <c r="D151" s="0" t="e">
         <f aca="false">VLOOKUP($A151,統計!$A:$G,6,)</f>
@@ -9627,7 +9682,7 @@
         <v>#N/A</v>
       </c>
       <c r="C152" s="0" t="s">
-        <v>345</v>
+        <v>347</v>
       </c>
       <c r="D152" s="0" t="e">
         <f aca="false">VLOOKUP($A152,統計!$A:$G,6,)</f>
@@ -9651,7 +9706,7 @@
         <v>#N/A</v>
       </c>
       <c r="C153" s="0" t="s">
-        <v>346</v>
+        <v>348</v>
       </c>
       <c r="D153" s="0" t="e">
         <f aca="false">VLOOKUP($A153,統計!$A:$G,6,)</f>
@@ -9675,7 +9730,7 @@
         <v>#N/A</v>
       </c>
       <c r="C154" s="0" t="s">
-        <v>347</v>
+        <v>349</v>
       </c>
       <c r="D154" s="0" t="e">
         <f aca="false">VLOOKUP($A154,統計!$A:$G,6,)</f>
@@ -9699,7 +9754,7 @@
         <v>#N/A</v>
       </c>
       <c r="C155" s="0" t="s">
-        <v>348</v>
+        <v>350</v>
       </c>
       <c r="D155" s="0" t="e">
         <f aca="false">VLOOKUP($A155,統計!$A:$G,6,)</f>
@@ -9723,7 +9778,7 @@
         <v>#N/A</v>
       </c>
       <c r="C156" s="0" t="s">
-        <v>349</v>
+        <v>351</v>
       </c>
       <c r="D156" s="0" t="e">
         <f aca="false">VLOOKUP($A156,統計!$A:$G,6,)</f>
@@ -9747,7 +9802,7 @@
         <v>#N/A</v>
       </c>
       <c r="C157" s="0" t="s">
-        <v>350</v>
+        <v>352</v>
       </c>
       <c r="D157" s="0" t="e">
         <f aca="false">VLOOKUP($A157,統計!$A:$G,6,)</f>
@@ -9771,7 +9826,7 @@
         <v>#N/A</v>
       </c>
       <c r="C158" s="0" t="s">
-        <v>351</v>
+        <v>353</v>
       </c>
       <c r="D158" s="0" t="e">
         <f aca="false">VLOOKUP($A158,統計!$A:$G,6,)</f>
@@ -9795,7 +9850,7 @@
         <v>#N/A</v>
       </c>
       <c r="C159" s="0" t="s">
-        <v>352</v>
+        <v>354</v>
       </c>
       <c r="D159" s="0" t="e">
         <f aca="false">VLOOKUP($A159,統計!$A:$G,6,)</f>
@@ -9819,7 +9874,7 @@
         <v>#N/A</v>
       </c>
       <c r="C160" s="0" t="s">
-        <v>353</v>
+        <v>355</v>
       </c>
       <c r="D160" s="0" t="e">
         <f aca="false">VLOOKUP($A160,統計!$A:$G,6,)</f>
@@ -9843,7 +9898,7 @@
         <v>#N/A</v>
       </c>
       <c r="C161" s="0" t="s">
-        <v>354</v>
+        <v>356</v>
       </c>
       <c r="D161" s="0" t="e">
         <f aca="false">VLOOKUP($A161,統計!$A:$G,6,)</f>
@@ -9867,7 +9922,7 @@
         <v>#N/A</v>
       </c>
       <c r="C162" s="0" t="s">
-        <v>355</v>
+        <v>357</v>
       </c>
       <c r="D162" s="0" t="e">
         <f aca="false">VLOOKUP($A162,統計!$A:$G,6,)</f>
@@ -9891,7 +9946,7 @@
         <v>#N/A</v>
       </c>
       <c r="C163" s="0" t="s">
-        <v>356</v>
+        <v>358</v>
       </c>
       <c r="D163" s="0" t="e">
         <f aca="false">VLOOKUP($A163,統計!$A:$G,6,)</f>
@@ -9915,7 +9970,7 @@
         <v>#N/A</v>
       </c>
       <c r="C164" s="0" t="s">
-        <v>357</v>
+        <v>359</v>
       </c>
       <c r="D164" s="0" t="e">
         <f aca="false">VLOOKUP($A164,統計!$A:$G,6,)</f>
@@ -9939,7 +9994,7 @@
         <v>#N/A</v>
       </c>
       <c r="C165" s="0" t="s">
-        <v>358</v>
+        <v>360</v>
       </c>
       <c r="D165" s="0" t="e">
         <f aca="false">VLOOKUP($A165,統計!$A:$G,6,)</f>
@@ -9963,7 +10018,7 @@
         <v>#N/A</v>
       </c>
       <c r="C166" s="0" t="s">
-        <v>359</v>
+        <v>361</v>
       </c>
       <c r="D166" s="0" t="e">
         <f aca="false">VLOOKUP($A166,統計!$A:$G,6,)</f>
@@ -9987,7 +10042,7 @@
         <v>#N/A</v>
       </c>
       <c r="C167" s="0" t="s">
-        <v>360</v>
+        <v>362</v>
       </c>
       <c r="D167" s="0" t="e">
         <f aca="false">VLOOKUP($A167,統計!$A:$G,6,)</f>
@@ -10011,7 +10066,7 @@
         <v>#N/A</v>
       </c>
       <c r="C168" s="0" t="s">
-        <v>361</v>
+        <v>363</v>
       </c>
       <c r="D168" s="0" t="e">
         <f aca="false">VLOOKUP($A168,統計!$A:$G,6,)</f>
@@ -10035,7 +10090,7 @@
         <v>#N/A</v>
       </c>
       <c r="C169" s="0" t="s">
-        <v>362</v>
+        <v>364</v>
       </c>
       <c r="D169" s="0" t="e">
         <f aca="false">VLOOKUP($A169,統計!$A:$G,6,)</f>
@@ -10059,7 +10114,7 @@
         <v>#N/A</v>
       </c>
       <c r="C170" s="0" t="s">
-        <v>363</v>
+        <v>365</v>
       </c>
       <c r="D170" s="0" t="e">
         <f aca="false">VLOOKUP($A170,統計!$A:$G,6,)</f>
@@ -10083,7 +10138,7 @@
         <v>#N/A</v>
       </c>
       <c r="C171" s="0" t="s">
-        <v>364</v>
+        <v>366</v>
       </c>
       <c r="D171" s="0" t="e">
         <f aca="false">VLOOKUP($A171,統計!$A:$G,6,)</f>
@@ -10107,7 +10162,7 @@
         <v>#N/A</v>
       </c>
       <c r="C172" s="0" t="s">
-        <v>365</v>
+        <v>367</v>
       </c>
       <c r="D172" s="0" t="e">
         <f aca="false">VLOOKUP($A172,統計!$A:$G,6,)</f>
@@ -10131,7 +10186,7 @@
         <v>#N/A</v>
       </c>
       <c r="C173" s="0" t="s">
-        <v>366</v>
+        <v>368</v>
       </c>
       <c r="D173" s="0" t="e">
         <f aca="false">VLOOKUP($A173,統計!$A:$G,6,)</f>
@@ -10155,7 +10210,7 @@
         <v>#N/A</v>
       </c>
       <c r="C174" s="0" t="s">
-        <v>367</v>
+        <v>369</v>
       </c>
       <c r="D174" s="0" t="e">
         <f aca="false">VLOOKUP($A174,統計!$A:$G,6,)</f>
@@ -10179,7 +10234,7 @@
         <v>#N/A</v>
       </c>
       <c r="C175" s="0" t="s">
-        <v>368</v>
+        <v>370</v>
       </c>
       <c r="D175" s="0" t="e">
         <f aca="false">VLOOKUP($A175,統計!$A:$G,6,)</f>
@@ -10203,7 +10258,7 @@
         <v>#N/A</v>
       </c>
       <c r="C176" s="0" t="s">
-        <v>369</v>
+        <v>371</v>
       </c>
       <c r="D176" s="0" t="e">
         <f aca="false">VLOOKUP($A176,統計!$A:$G,6,)</f>
@@ -10227,7 +10282,7 @@
         <v>#N/A</v>
       </c>
       <c r="C177" s="0" t="s">
-        <v>370</v>
+        <v>372</v>
       </c>
       <c r="D177" s="0" t="e">
         <f aca="false">VLOOKUP($A177,統計!$A:$G,6,)</f>
@@ -10251,7 +10306,7 @@
         <v>#N/A</v>
       </c>
       <c r="C178" s="0" t="s">
-        <v>371</v>
+        <v>373</v>
       </c>
       <c r="D178" s="0" t="e">
         <f aca="false">VLOOKUP($A178,統計!$A:$G,6,)</f>
@@ -10275,7 +10330,7 @@
         <v>#N/A</v>
       </c>
       <c r="C179" s="0" t="s">
-        <v>372</v>
+        <v>374</v>
       </c>
       <c r="D179" s="0" t="e">
         <f aca="false">VLOOKUP($A179,統計!$A:$G,6,)</f>
@@ -10299,7 +10354,7 @@
         <v>#N/A</v>
       </c>
       <c r="C180" s="0" t="s">
-        <v>373</v>
+        <v>375</v>
       </c>
       <c r="D180" s="0" t="e">
         <f aca="false">VLOOKUP($A180,統計!$A:$G,6,)</f>
@@ -10323,7 +10378,7 @@
         <v>#N/A</v>
       </c>
       <c r="C181" s="0" t="s">
-        <v>374</v>
+        <v>376</v>
       </c>
       <c r="D181" s="0" t="e">
         <f aca="false">VLOOKUP($A181,統計!$A:$G,6,)</f>
@@ -10347,7 +10402,7 @@
         <v>#N/A</v>
       </c>
       <c r="C182" s="0" t="s">
-        <v>375</v>
+        <v>377</v>
       </c>
       <c r="D182" s="0" t="e">
         <f aca="false">VLOOKUP($A182,統計!$A:$G,6,)</f>
@@ -10371,7 +10426,7 @@
         <v>#N/A</v>
       </c>
       <c r="C183" s="0" t="s">
-        <v>376</v>
+        <v>378</v>
       </c>
       <c r="D183" s="0" t="e">
         <f aca="false">VLOOKUP($A183,統計!$A:$G,6,)</f>
@@ -10395,7 +10450,7 @@
         <v>#N/A</v>
       </c>
       <c r="C184" s="0" t="s">
-        <v>377</v>
+        <v>379</v>
       </c>
       <c r="D184" s="0" t="e">
         <f aca="false">VLOOKUP($A184,統計!$A:$G,6,)</f>
@@ -10419,7 +10474,7 @@
         <v>#N/A</v>
       </c>
       <c r="C185" s="0" t="s">
-        <v>378</v>
+        <v>380</v>
       </c>
       <c r="D185" s="0" t="e">
         <f aca="false">VLOOKUP($A185,統計!$A:$G,6,)</f>
@@ -10443,7 +10498,7 @@
         <v>#N/A</v>
       </c>
       <c r="C186" s="0" t="s">
-        <v>379</v>
+        <v>381</v>
       </c>
       <c r="D186" s="0" t="e">
         <f aca="false">VLOOKUP($A186,統計!$A:$G,6,)</f>
@@ -10467,7 +10522,7 @@
         <v>#N/A</v>
       </c>
       <c r="C187" s="0" t="s">
-        <v>380</v>
+        <v>382</v>
       </c>
       <c r="D187" s="0" t="e">
         <f aca="false">VLOOKUP($A187,統計!$A:$G,6,)</f>
@@ -10491,7 +10546,7 @@
         <v>#N/A</v>
       </c>
       <c r="C188" s="0" t="s">
-        <v>381</v>
+        <v>383</v>
       </c>
       <c r="D188" s="0" t="e">
         <f aca="false">VLOOKUP($A188,統計!$A:$G,6,)</f>
@@ -10515,7 +10570,7 @@
         <v>#N/A</v>
       </c>
       <c r="C189" s="0" t="s">
-        <v>382</v>
+        <v>384</v>
       </c>
       <c r="D189" s="0" t="e">
         <f aca="false">VLOOKUP($A189,統計!$A:$G,6,)</f>
@@ -10539,7 +10594,7 @@
         <v>#N/A</v>
       </c>
       <c r="C190" s="0" t="s">
-        <v>383</v>
+        <v>385</v>
       </c>
       <c r="D190" s="0" t="e">
         <f aca="false">VLOOKUP($A190,統計!$A:$G,6,)</f>
@@ -10563,7 +10618,7 @@
         <v>#N/A</v>
       </c>
       <c r="C191" s="0" t="s">
-        <v>384</v>
+        <v>386</v>
       </c>
       <c r="D191" s="0" t="e">
         <f aca="false">VLOOKUP($A191,統計!$A:$G,6,)</f>
@@ -10587,7 +10642,7 @@
         <v>#N/A</v>
       </c>
       <c r="C192" s="0" t="s">
-        <v>385</v>
+        <v>387</v>
       </c>
       <c r="D192" s="0" t="e">
         <f aca="false">VLOOKUP($A192,統計!$A:$G,6,)</f>
@@ -10611,7 +10666,7 @@
         <v>#N/A</v>
       </c>
       <c r="C193" s="0" t="s">
-        <v>386</v>
+        <v>388</v>
       </c>
       <c r="D193" s="0" t="e">
         <f aca="false">VLOOKUP($A193,統計!$A:$G,6,)</f>
@@ -10635,7 +10690,7 @@
         <v>#N/A</v>
       </c>
       <c r="C194" s="0" t="s">
-        <v>387</v>
+        <v>389</v>
       </c>
       <c r="D194" s="0" t="e">
         <f aca="false">VLOOKUP($A194,統計!$A:$G,6,)</f>
@@ -10659,7 +10714,7 @@
         <v>#N/A</v>
       </c>
       <c r="C195" s="0" t="s">
-        <v>388</v>
+        <v>390</v>
       </c>
       <c r="D195" s="0" t="e">
         <f aca="false">VLOOKUP($A195,統計!$A:$G,6,)</f>
@@ -10683,7 +10738,7 @@
         <v>#N/A</v>
       </c>
       <c r="C196" s="0" t="s">
-        <v>389</v>
+        <v>391</v>
       </c>
       <c r="D196" s="0" t="e">
         <f aca="false">VLOOKUP($A196,統計!$A:$G,6,)</f>
@@ -10707,7 +10762,7 @@
         <v>#N/A</v>
       </c>
       <c r="C197" s="0" t="s">
-        <v>390</v>
+        <v>392</v>
       </c>
       <c r="D197" s="0" t="e">
         <f aca="false">VLOOKUP($A197,統計!$A:$G,6,)</f>
@@ -10731,7 +10786,7 @@
         <v>#N/A</v>
       </c>
       <c r="C198" s="0" t="s">
-        <v>391</v>
+        <v>393</v>
       </c>
       <c r="D198" s="0" t="e">
         <f aca="false">VLOOKUP($A198,統計!$A:$G,6,)</f>
@@ -10755,7 +10810,7 @@
         <v>#N/A</v>
       </c>
       <c r="C199" s="0" t="s">
-        <v>392</v>
+        <v>394</v>
       </c>
       <c r="D199" s="0" t="e">
         <f aca="false">VLOOKUP($A199,統計!$A:$G,6,)</f>
@@ -10779,7 +10834,7 @@
         <v>#N/A</v>
       </c>
       <c r="C200" s="0" t="s">
-        <v>393</v>
+        <v>395</v>
       </c>
       <c r="D200" s="0" t="e">
         <f aca="false">VLOOKUP($A200,統計!$A:$G,6,)</f>
@@ -10803,7 +10858,7 @@
         <v>#N/A</v>
       </c>
       <c r="C201" s="0" t="s">
-        <v>394</v>
+        <v>396</v>
       </c>
       <c r="D201" s="0" t="e">
         <f aca="false">VLOOKUP($A201,統計!$A:$G,6,)</f>
@@ -10827,7 +10882,7 @@
         <v>#N/A</v>
       </c>
       <c r="C202" s="0" t="s">
-        <v>395</v>
+        <v>397</v>
       </c>
       <c r="D202" s="0" t="e">
         <f aca="false">VLOOKUP($A202,統計!$A:$G,6,)</f>
@@ -10851,7 +10906,7 @@
         <v>#N/A</v>
       </c>
       <c r="C203" s="0" t="s">
-        <v>396</v>
+        <v>398</v>
       </c>
       <c r="D203" s="0" t="e">
         <f aca="false">VLOOKUP($A203,統計!$A:$G,6,)</f>
@@ -10875,7 +10930,7 @@
         <v>#N/A</v>
       </c>
       <c r="C204" s="0" t="s">
-        <v>397</v>
+        <v>399</v>
       </c>
       <c r="D204" s="0" t="e">
         <f aca="false">VLOOKUP($A204,統計!$A:$G,6,)</f>
@@ -10899,7 +10954,7 @@
         <v>#N/A</v>
       </c>
       <c r="C205" s="0" t="s">
-        <v>398</v>
+        <v>400</v>
       </c>
       <c r="D205" s="0" t="e">
         <f aca="false">VLOOKUP($A205,統計!$A:$G,6,)</f>
@@ -10923,7 +10978,7 @@
         <v>#N/A</v>
       </c>
       <c r="C206" s="0" t="s">
-        <v>399</v>
+        <v>401</v>
       </c>
       <c r="D206" s="0" t="e">
         <f aca="false">VLOOKUP($A206,統計!$A:$G,6,)</f>
@@ -10947,7 +11002,7 @@
         <v>#N/A</v>
       </c>
       <c r="C207" s="0" t="s">
-        <v>400</v>
+        <v>402</v>
       </c>
       <c r="D207" s="0" t="e">
         <f aca="false">VLOOKUP($A207,統計!$A:$G,6,)</f>
@@ -10971,7 +11026,7 @@
         <v>#N/A</v>
       </c>
       <c r="C208" s="0" t="s">
-        <v>401</v>
+        <v>403</v>
       </c>
       <c r="D208" s="0" t="e">
         <f aca="false">VLOOKUP($A208,統計!$A:$G,6,)</f>
@@ -10995,7 +11050,7 @@
         <v>#N/A</v>
       </c>
       <c r="C209" s="0" t="s">
-        <v>402</v>
+        <v>404</v>
       </c>
       <c r="D209" s="0" t="e">
         <f aca="false">VLOOKUP($A209,統計!$A:$G,6,)</f>
@@ -11019,7 +11074,7 @@
         <v>#N/A</v>
       </c>
       <c r="C210" s="0" t="s">
-        <v>403</v>
+        <v>405</v>
       </c>
       <c r="D210" s="0" t="e">
         <f aca="false">VLOOKUP($A210,統計!$A:$G,6,)</f>
@@ -11043,7 +11098,7 @@
         <v>#N/A</v>
       </c>
       <c r="C211" s="0" t="s">
-        <v>404</v>
+        <v>406</v>
       </c>
       <c r="D211" s="0" t="e">
         <f aca="false">VLOOKUP($A211,統計!$A:$G,6,)</f>
@@ -11067,7 +11122,7 @@
         <v>#N/A</v>
       </c>
       <c r="C212" s="0" t="s">
-        <v>405</v>
+        <v>407</v>
       </c>
       <c r="D212" s="0" t="e">
         <f aca="false">VLOOKUP($A212,統計!$A:$G,6,)</f>
@@ -11091,7 +11146,7 @@
         <v>#N/A</v>
       </c>
       <c r="C213" s="0" t="s">
-        <v>406</v>
+        <v>408</v>
       </c>
       <c r="D213" s="0" t="e">
         <f aca="false">VLOOKUP($A213,統計!$A:$G,6,)</f>
@@ -11115,7 +11170,7 @@
         <v>#N/A</v>
       </c>
       <c r="C214" s="0" t="s">
-        <v>407</v>
+        <v>409</v>
       </c>
       <c r="D214" s="0" t="e">
         <f aca="false">VLOOKUP($A214,統計!$A:$G,6,)</f>
@@ -11139,7 +11194,7 @@
         <v>#N/A</v>
       </c>
       <c r="C215" s="0" t="s">
-        <v>408</v>
+        <v>410</v>
       </c>
       <c r="D215" s="0" t="e">
         <f aca="false">VLOOKUP($A215,統計!$A:$G,6,)</f>
@@ -11163,7 +11218,7 @@
         <v>#N/A</v>
       </c>
       <c r="C216" s="0" t="s">
-        <v>409</v>
+        <v>411</v>
       </c>
       <c r="D216" s="0" t="e">
         <f aca="false">VLOOKUP($A216,統計!$A:$G,6,)</f>
@@ -11187,7 +11242,7 @@
         <v>#N/A</v>
       </c>
       <c r="C217" s="0" t="s">
-        <v>410</v>
+        <v>412</v>
       </c>
       <c r="D217" s="0" t="e">
         <f aca="false">VLOOKUP($A217,統計!$A:$G,6,)</f>
@@ -11211,7 +11266,7 @@
         <v>#N/A</v>
       </c>
       <c r="C218" s="0" t="s">
-        <v>411</v>
+        <v>413</v>
       </c>
       <c r="D218" s="0" t="e">
         <f aca="false">VLOOKUP($A218,統計!$A:$G,6,)</f>
@@ -11235,7 +11290,7 @@
         <v>#N/A</v>
       </c>
       <c r="C219" s="0" t="s">
-        <v>412</v>
+        <v>414</v>
       </c>
       <c r="D219" s="0" t="e">
         <f aca="false">VLOOKUP($A219,統計!$A:$G,6,)</f>
@@ -11259,7 +11314,7 @@
         <v>#N/A</v>
       </c>
       <c r="C220" s="0" t="s">
-        <v>413</v>
+        <v>415</v>
       </c>
       <c r="D220" s="0" t="e">
         <f aca="false">VLOOKUP($A220,統計!$A:$G,6,)</f>
@@ -11283,7 +11338,7 @@
         <v>#N/A</v>
       </c>
       <c r="C221" s="0" t="s">
-        <v>414</v>
+        <v>416</v>
       </c>
       <c r="D221" s="0" t="e">
         <f aca="false">VLOOKUP($A221,統計!$A:$G,6,)</f>
@@ -11307,7 +11362,7 @@
         <v>#N/A</v>
       </c>
       <c r="C222" s="0" t="s">
-        <v>415</v>
+        <v>417</v>
       </c>
       <c r="D222" s="0" t="e">
         <f aca="false">VLOOKUP($A222,統計!$A:$G,6,)</f>
@@ -11331,7 +11386,7 @@
         <v>#N/A</v>
       </c>
       <c r="C223" s="0" t="s">
-        <v>416</v>
+        <v>418</v>
       </c>
       <c r="D223" s="0" t="e">
         <f aca="false">VLOOKUP($A223,統計!$A:$G,6,)</f>
@@ -11355,7 +11410,7 @@
         <v>#N/A</v>
       </c>
       <c r="C224" s="0" t="s">
-        <v>417</v>
+        <v>419</v>
       </c>
       <c r="D224" s="0" t="e">
         <f aca="false">VLOOKUP($A224,統計!$A:$G,6,)</f>
@@ -11379,7 +11434,7 @@
         <v>#N/A</v>
       </c>
       <c r="C225" s="0" t="s">
-        <v>418</v>
+        <v>420</v>
       </c>
       <c r="D225" s="0" t="e">
         <f aca="false">VLOOKUP($A225,統計!$A:$G,6,)</f>
@@ -11403,7 +11458,7 @@
         <v>#N/A</v>
       </c>
       <c r="C226" s="0" t="s">
-        <v>419</v>
+        <v>421</v>
       </c>
       <c r="D226" s="0" t="e">
         <f aca="false">VLOOKUP($A226,統計!$A:$G,6,)</f>
@@ -11427,7 +11482,7 @@
         <v>#N/A</v>
       </c>
       <c r="C227" s="0" t="s">
-        <v>420</v>
+        <v>422</v>
       </c>
       <c r="D227" s="0" t="e">
         <f aca="false">VLOOKUP($A227,統計!$A:$G,6,)</f>
@@ -11451,7 +11506,7 @@
         <v>#N/A</v>
       </c>
       <c r="C228" s="0" t="s">
-        <v>421</v>
+        <v>423</v>
       </c>
       <c r="D228" s="0" t="e">
         <f aca="false">VLOOKUP($A228,統計!$A:$G,6,)</f>
@@ -11475,7 +11530,7 @@
         <v>#N/A</v>
       </c>
       <c r="C229" s="0" t="s">
-        <v>422</v>
+        <v>424</v>
       </c>
       <c r="D229" s="0" t="e">
         <f aca="false">VLOOKUP($A229,統計!$A:$G,6,)</f>
@@ -11499,7 +11554,7 @@
         <v>#N/A</v>
       </c>
       <c r="C230" s="0" t="s">
-        <v>423</v>
+        <v>425</v>
       </c>
       <c r="D230" s="0" t="e">
         <f aca="false">VLOOKUP($A230,統計!$A:$G,6,)</f>
@@ -11523,7 +11578,7 @@
         <v>#N/A</v>
       </c>
       <c r="C231" s="0" t="s">
-        <v>424</v>
+        <v>426</v>
       </c>
       <c r="D231" s="0" t="e">
         <f aca="false">VLOOKUP($A231,統計!$A:$G,6,)</f>
@@ -11547,7 +11602,7 @@
         <v>#N/A</v>
       </c>
       <c r="C232" s="0" t="s">
-        <v>425</v>
+        <v>427</v>
       </c>
       <c r="D232" s="0" t="e">
         <f aca="false">VLOOKUP($A232,統計!$A:$G,6,)</f>
@@ -11571,7 +11626,7 @@
         <v>#N/A</v>
       </c>
       <c r="C233" s="0" t="s">
-        <v>426</v>
+        <v>428</v>
       </c>
       <c r="D233" s="0" t="e">
         <f aca="false">VLOOKUP($A233,統計!$A:$G,6,)</f>
@@ -11595,7 +11650,7 @@
         <v>#N/A</v>
       </c>
       <c r="C234" s="0" t="s">
-        <v>427</v>
+        <v>429</v>
       </c>
       <c r="D234" s="0" t="e">
         <f aca="false">VLOOKUP($A234,統計!$A:$G,6,)</f>
@@ -11619,7 +11674,7 @@
         <v>#N/A</v>
       </c>
       <c r="C235" s="0" t="s">
-        <v>428</v>
+        <v>430</v>
       </c>
       <c r="D235" s="0" t="e">
         <f aca="false">VLOOKUP($A235,統計!$A:$G,6,)</f>
@@ -11643,7 +11698,7 @@
         <v>#N/A</v>
       </c>
       <c r="C236" s="0" t="s">
-        <v>429</v>
+        <v>431</v>
       </c>
       <c r="D236" s="0" t="e">
         <f aca="false">VLOOKUP($A236,統計!$A:$G,6,)</f>
@@ -11667,7 +11722,7 @@
         <v>#N/A</v>
       </c>
       <c r="C237" s="0" t="s">
-        <v>430</v>
+        <v>432</v>
       </c>
       <c r="D237" s="0" t="e">
         <f aca="false">VLOOKUP($A237,統計!$A:$G,6,)</f>
@@ -11691,7 +11746,7 @@
         <v>#N/A</v>
       </c>
       <c r="C238" s="0" t="s">
-        <v>431</v>
+        <v>433</v>
       </c>
       <c r="D238" s="0" t="e">
         <f aca="false">VLOOKUP($A238,統計!$A:$G,6,)</f>
@@ -11715,7 +11770,7 @@
         <v>#N/A</v>
       </c>
       <c r="C239" s="0" t="s">
-        <v>432</v>
+        <v>434</v>
       </c>
       <c r="D239" s="0" t="e">
         <f aca="false">VLOOKUP($A239,統計!$A:$G,6,)</f>
@@ -11739,7 +11794,7 @@
         <v>#N/A</v>
       </c>
       <c r="C240" s="0" t="s">
-        <v>433</v>
+        <v>435</v>
       </c>
       <c r="D240" s="0" t="e">
         <f aca="false">VLOOKUP($A240,統計!$A:$G,6,)</f>
@@ -11763,7 +11818,7 @@
         <v>#N/A</v>
       </c>
       <c r="C241" s="0" t="s">
-        <v>434</v>
+        <v>436</v>
       </c>
       <c r="D241" s="0" t="e">
         <f aca="false">VLOOKUP($A241,統計!$A:$G,6,)</f>
@@ -11787,7 +11842,7 @@
         <v>#N/A</v>
       </c>
       <c r="C242" s="0" t="s">
-        <v>435</v>
+        <v>437</v>
       </c>
       <c r="D242" s="0" t="e">
         <f aca="false">VLOOKUP($A242,統計!$A:$G,6,)</f>
@@ -11811,7 +11866,7 @@
         <v>#N/A</v>
       </c>
       <c r="C243" s="0" t="s">
-        <v>436</v>
+        <v>438</v>
       </c>
       <c r="D243" s="0" t="e">
         <f aca="false">VLOOKUP($A243,統計!$A:$G,6,)</f>
@@ -11835,7 +11890,7 @@
         <v>#N/A</v>
       </c>
       <c r="C244" s="0" t="s">
-        <v>437</v>
+        <v>439</v>
       </c>
       <c r="D244" s="0" t="e">
         <f aca="false">VLOOKUP($A244,統計!$A:$G,6,)</f>
@@ -11859,7 +11914,7 @@
         <v>#N/A</v>
       </c>
       <c r="C245" s="0" t="s">
-        <v>438</v>
+        <v>440</v>
       </c>
       <c r="D245" s="0" t="e">
         <f aca="false">VLOOKUP($A245,統計!$A:$G,6,)</f>
@@ -11883,7 +11938,7 @@
         <v>#N/A</v>
       </c>
       <c r="C246" s="0" t="s">
-        <v>439</v>
+        <v>441</v>
       </c>
       <c r="D246" s="0" t="e">
         <f aca="false">VLOOKUP($A246,統計!$A:$G,6,)</f>
@@ -11907,7 +11962,7 @@
         <v>#N/A</v>
       </c>
       <c r="C247" s="0" t="s">
-        <v>440</v>
+        <v>442</v>
       </c>
       <c r="D247" s="0" t="e">
         <f aca="false">VLOOKUP($A247,統計!$A:$G,6,)</f>
@@ -11931,7 +11986,7 @@
         <v>#N/A</v>
       </c>
       <c r="C248" s="0" t="s">
-        <v>441</v>
+        <v>443</v>
       </c>
       <c r="D248" s="0" t="e">
         <f aca="false">VLOOKUP($A248,統計!$A:$G,6,)</f>
@@ -11955,7 +12010,7 @@
         <v>#N/A</v>
       </c>
       <c r="C249" s="0" t="s">
-        <v>442</v>
+        <v>444</v>
       </c>
       <c r="D249" s="0" t="e">
         <f aca="false">VLOOKUP($A249,統計!$A:$G,6,)</f>
@@ -11979,7 +12034,7 @@
         <v>#N/A</v>
       </c>
       <c r="C250" s="0" t="s">
-        <v>443</v>
+        <v>445</v>
       </c>
       <c r="D250" s="0" t="e">
         <f aca="false">VLOOKUP($A250,統計!$A:$G,6,)</f>
@@ -12003,7 +12058,7 @@
         <v>#N/A</v>
       </c>
       <c r="C251" s="0" t="s">
-        <v>444</v>
+        <v>446</v>
       </c>
       <c r="D251" s="0" t="e">
         <f aca="false">VLOOKUP($A251,統計!$A:$G,6,)</f>
@@ -12027,7 +12082,7 @@
         <v>#N/A</v>
       </c>
       <c r="C252" s="0" t="s">
-        <v>445</v>
+        <v>447</v>
       </c>
       <c r="D252" s="0" t="e">
         <f aca="false">VLOOKUP($A252,統計!$A:$G,6,)</f>
@@ -12051,7 +12106,7 @@
         <v>#N/A</v>
       </c>
       <c r="C253" s="0" t="s">
-        <v>446</v>
+        <v>448</v>
       </c>
       <c r="D253" s="0" t="e">
         <f aca="false">VLOOKUP($A253,統計!$A:$G,6,)</f>
@@ -12075,7 +12130,7 @@
         <v>#N/A</v>
       </c>
       <c r="C254" s="0" t="s">
-        <v>447</v>
+        <v>449</v>
       </c>
       <c r="D254" s="0" t="e">
         <f aca="false">VLOOKUP($A254,統計!$A:$G,6,)</f>
@@ -12099,7 +12154,7 @@
         <v>#N/A</v>
       </c>
       <c r="C255" s="0" t="s">
-        <v>448</v>
+        <v>450</v>
       </c>
       <c r="D255" s="0" t="e">
         <f aca="false">VLOOKUP($A255,統計!$A:$G,6,)</f>
@@ -12123,7 +12178,7 @@
         <v>#N/A</v>
       </c>
       <c r="C256" s="0" t="s">
-        <v>449</v>
+        <v>451</v>
       </c>
       <c r="D256" s="0" t="e">
         <f aca="false">VLOOKUP($A256,統計!$A:$G,6,)</f>
@@ -12147,7 +12202,7 @@
         <v>#N/A</v>
       </c>
       <c r="C257" s="0" t="s">
-        <v>450</v>
+        <v>452</v>
       </c>
       <c r="D257" s="0" t="e">
         <f aca="false">VLOOKUP($A257,統計!$A:$G,6,)</f>
@@ -12171,7 +12226,7 @@
         <v>#N/A</v>
       </c>
       <c r="C258" s="0" t="s">
-        <v>451</v>
+        <v>453</v>
       </c>
       <c r="D258" s="0" t="e">
         <f aca="false">VLOOKUP($A258,統計!$A:$G,6,)</f>
@@ -12195,7 +12250,7 @@
         <v>#N/A</v>
       </c>
       <c r="C259" s="0" t="s">
-        <v>452</v>
+        <v>454</v>
       </c>
       <c r="D259" s="0" t="e">
         <f aca="false">VLOOKUP($A259,統計!$A:$G,6,)</f>
@@ -12219,7 +12274,7 @@
         <v>#N/A</v>
       </c>
       <c r="C260" s="0" t="s">
-        <v>453</v>
+        <v>455</v>
       </c>
       <c r="D260" s="0" t="e">
         <f aca="false">VLOOKUP($A260,統計!$A:$G,6,)</f>
@@ -12243,7 +12298,7 @@
         <v>#N/A</v>
       </c>
       <c r="C261" s="0" t="s">
-        <v>454</v>
+        <v>456</v>
       </c>
       <c r="D261" s="0" t="e">
         <f aca="false">VLOOKUP($A261,統計!$A:$G,6,)</f>
@@ -12267,7 +12322,7 @@
         <v>#N/A</v>
       </c>
       <c r="C262" s="0" t="s">
-        <v>455</v>
+        <v>457</v>
       </c>
       <c r="D262" s="0" t="e">
         <f aca="false">VLOOKUP($A262,統計!$A:$G,6,)</f>
@@ -12291,7 +12346,7 @@
         <v>#N/A</v>
       </c>
       <c r="C263" s="0" t="s">
-        <v>456</v>
+        <v>458</v>
       </c>
       <c r="D263" s="0" t="e">
         <f aca="false">VLOOKUP($A263,統計!$A:$G,6,)</f>
@@ -12315,7 +12370,7 @@
         <v>#N/A</v>
       </c>
       <c r="C264" s="0" t="s">
-        <v>457</v>
+        <v>459</v>
       </c>
       <c r="D264" s="0" t="e">
         <f aca="false">VLOOKUP($A264,統計!$A:$G,6,)</f>
@@ -12339,7 +12394,7 @@
         <v>#N/A</v>
       </c>
       <c r="C265" s="0" t="s">
-        <v>458</v>
+        <v>460</v>
       </c>
       <c r="D265" s="0" t="e">
         <f aca="false">VLOOKUP($A265,統計!$A:$G,6,)</f>
@@ -12363,7 +12418,7 @@
         <v>#N/A</v>
       </c>
       <c r="C266" s="0" t="s">
-        <v>459</v>
+        <v>461</v>
       </c>
       <c r="D266" s="0" t="e">
         <f aca="false">VLOOKUP($A266,統計!$A:$G,6,)</f>
@@ -12387,7 +12442,7 @@
         <v>#N/A</v>
       </c>
       <c r="C267" s="0" t="s">
-        <v>460</v>
+        <v>462</v>
       </c>
       <c r="D267" s="0" t="e">
         <f aca="false">VLOOKUP($A267,統計!$A:$G,6,)</f>
@@ -12411,7 +12466,7 @@
         <v>#N/A</v>
       </c>
       <c r="C268" s="0" t="s">
-        <v>461</v>
+        <v>463</v>
       </c>
       <c r="D268" s="0" t="e">
         <f aca="false">VLOOKUP($A268,統計!$A:$G,6,)</f>
@@ -12435,7 +12490,7 @@
         <v>#N/A</v>
       </c>
       <c r="C269" s="0" t="s">
-        <v>462</v>
+        <v>464</v>
       </c>
       <c r="D269" s="0" t="e">
         <f aca="false">VLOOKUP($A269,統計!$A:$G,6,)</f>
@@ -12459,7 +12514,7 @@
         <v>#N/A</v>
       </c>
       <c r="C270" s="0" t="s">
-        <v>463</v>
+        <v>465</v>
       </c>
       <c r="D270" s="0" t="e">
         <f aca="false">VLOOKUP($A270,統計!$A:$G,6,)</f>
@@ -12483,7 +12538,7 @@
         <v>#N/A</v>
       </c>
       <c r="C271" s="0" t="s">
-        <v>464</v>
+        <v>466</v>
       </c>
       <c r="D271" s="0" t="e">
         <f aca="false">VLOOKUP($A271,統計!$A:$G,6,)</f>
@@ -12507,7 +12562,7 @@
         <v>#N/A</v>
       </c>
       <c r="C272" s="0" t="s">
-        <v>465</v>
+        <v>467</v>
       </c>
       <c r="D272" s="0" t="e">
         <f aca="false">VLOOKUP($A272,統計!$A:$G,6,)</f>
@@ -12531,7 +12586,7 @@
         <v>#N/A</v>
       </c>
       <c r="C273" s="0" t="s">
-        <v>466</v>
+        <v>468</v>
       </c>
       <c r="D273" s="0" t="e">
         <f aca="false">VLOOKUP($A273,統計!$A:$G,6,)</f>
@@ -12555,7 +12610,7 @@
         <v>#N/A</v>
       </c>
       <c r="C274" s="0" t="s">
-        <v>467</v>
+        <v>469</v>
       </c>
       <c r="D274" s="0" t="e">
         <f aca="false">VLOOKUP($A274,統計!$A:$G,6,)</f>
@@ -12579,7 +12634,7 @@
         <v>#N/A</v>
       </c>
       <c r="C275" s="0" t="s">
-        <v>468</v>
+        <v>470</v>
       </c>
       <c r="D275" s="0" t="e">
         <f aca="false">VLOOKUP($A275,統計!$A:$G,6,)</f>
@@ -12603,7 +12658,7 @@
         <v>#N/A</v>
       </c>
       <c r="C276" s="0" t="s">
-        <v>469</v>
+        <v>471</v>
       </c>
       <c r="D276" s="0" t="e">
         <f aca="false">VLOOKUP($A276,統計!$A:$G,6,)</f>
@@ -12627,7 +12682,7 @@
         <v>#N/A</v>
       </c>
       <c r="C277" s="0" t="s">
-        <v>470</v>
+        <v>472</v>
       </c>
       <c r="D277" s="0" t="e">
         <f aca="false">VLOOKUP($A277,統計!$A:$G,6,)</f>
@@ -12651,7 +12706,7 @@
         <v>#N/A</v>
       </c>
       <c r="C278" s="0" t="s">
-        <v>471</v>
+        <v>473</v>
       </c>
       <c r="D278" s="0" t="e">
         <f aca="false">VLOOKUP($A278,統計!$A:$G,6,)</f>
@@ -12675,7 +12730,7 @@
         <v>#N/A</v>
       </c>
       <c r="C279" s="0" t="s">
-        <v>472</v>
+        <v>474</v>
       </c>
       <c r="D279" s="0" t="e">
         <f aca="false">VLOOKUP($A279,統計!$A:$G,6,)</f>
@@ -12699,7 +12754,7 @@
         <v>#N/A</v>
       </c>
       <c r="C280" s="0" t="s">
-        <v>473</v>
+        <v>475</v>
       </c>
       <c r="D280" s="0" t="e">
         <f aca="false">VLOOKUP($A280,統計!$A:$G,6,)</f>
@@ -12723,7 +12778,7 @@
         <v>#N/A</v>
       </c>
       <c r="C281" s="0" t="s">
-        <v>474</v>
+        <v>476</v>
       </c>
       <c r="D281" s="0" t="e">
         <f aca="false">VLOOKUP($A281,統計!$A:$G,6,)</f>
@@ -12747,7 +12802,7 @@
         <v>#N/A</v>
       </c>
       <c r="C282" s="0" t="s">
-        <v>475</v>
+        <v>477</v>
       </c>
       <c r="D282" s="0" t="e">
         <f aca="false">VLOOKUP($A282,統計!$A:$G,6,)</f>
@@ -12771,7 +12826,7 @@
         <v>#N/A</v>
       </c>
       <c r="C283" s="0" t="s">
-        <v>476</v>
+        <v>478</v>
       </c>
       <c r="D283" s="0" t="e">
         <f aca="false">VLOOKUP($A283,統計!$A:$G,6,)</f>
@@ -12795,7 +12850,7 @@
         <v>#N/A</v>
       </c>
       <c r="C284" s="0" t="s">
-        <v>477</v>
+        <v>479</v>
       </c>
       <c r="D284" s="0" t="e">
         <f aca="false">VLOOKUP($A284,統計!$A:$G,6,)</f>
@@ -12819,7 +12874,7 @@
         <v>#N/A</v>
       </c>
       <c r="C285" s="0" t="s">
-        <v>478</v>
+        <v>480</v>
       </c>
       <c r="D285" s="0" t="e">
         <f aca="false">VLOOKUP($A285,統計!$A:$G,6,)</f>
@@ -12843,7 +12898,7 @@
         <v>#N/A</v>
       </c>
       <c r="C286" s="0" t="s">
-        <v>479</v>
+        <v>481</v>
       </c>
       <c r="D286" s="0" t="e">
         <f aca="false">VLOOKUP($A286,統計!$A:$G,6,)</f>
@@ -12867,7 +12922,7 @@
         <v>#N/A</v>
       </c>
       <c r="C287" s="0" t="s">
-        <v>480</v>
+        <v>482</v>
       </c>
       <c r="D287" s="0" t="e">
         <f aca="false">VLOOKUP($A287,統計!$A:$G,6,)</f>
@@ -12891,7 +12946,7 @@
         <v>#N/A</v>
       </c>
       <c r="C288" s="0" t="s">
-        <v>481</v>
+        <v>483</v>
       </c>
       <c r="D288" s="0" t="e">
         <f aca="false">VLOOKUP($A288,統計!$A:$G,6,)</f>
@@ -12915,7 +12970,7 @@
         <v>#N/A</v>
       </c>
       <c r="C289" s="0" t="s">
-        <v>482</v>
+        <v>484</v>
       </c>
       <c r="D289" s="0" t="e">
         <f aca="false">VLOOKUP($A289,統計!$A:$G,6,)</f>
@@ -12939,7 +12994,7 @@
         <v>#N/A</v>
       </c>
       <c r="C290" s="0" t="s">
-        <v>483</v>
+        <v>485</v>
       </c>
       <c r="D290" s="0" t="e">
         <f aca="false">VLOOKUP($A290,統計!$A:$G,6,)</f>
@@ -12963,7 +13018,7 @@
         <v>#N/A</v>
       </c>
       <c r="C291" s="0" t="s">
-        <v>484</v>
+        <v>486</v>
       </c>
       <c r="D291" s="0" t="e">
         <f aca="false">VLOOKUP($A291,統計!$A:$G,6,)</f>
@@ -12987,7 +13042,7 @@
         <v>#N/A</v>
       </c>
       <c r="C292" s="0" t="s">
-        <v>485</v>
+        <v>487</v>
       </c>
       <c r="D292" s="0" t="e">
         <f aca="false">VLOOKUP($A292,統計!$A:$G,6,)</f>
@@ -13011,7 +13066,7 @@
         <v>#N/A</v>
       </c>
       <c r="C293" s="0" t="s">
-        <v>486</v>
+        <v>488</v>
       </c>
       <c r="D293" s="0" t="e">
         <f aca="false">VLOOKUP($A293,統計!$A:$G,6,)</f>
@@ -13035,7 +13090,7 @@
         <v>#N/A</v>
       </c>
       <c r="C294" s="0" t="s">
-        <v>487</v>
+        <v>489</v>
       </c>
       <c r="D294" s="0" t="e">
         <f aca="false">VLOOKUP($A294,統計!$A:$G,6,)</f>
@@ -13059,7 +13114,7 @@
         <v>#N/A</v>
       </c>
       <c r="C295" s="0" t="s">
-        <v>488</v>
+        <v>490</v>
       </c>
       <c r="D295" s="0" t="e">
         <f aca="false">VLOOKUP($A295,統計!$A:$G,6,)</f>
@@ -13095,13 +13150,13 @@
   <sheetData>
     <row r="1" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B1" s="0" t="s">
-        <v>489</v>
+        <v>491</v>
       </c>
       <c r="C1" s="0" t="s">
-        <v>490</v>
+        <v>492</v>
       </c>
       <c r="D1" s="0" t="s">
-        <v>491</v>
+        <v>493</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -13115,30 +13170,30 @@
         <v>1173</v>
       </c>
       <c r="E2" s="0" t="s">
-        <v>492</v>
+        <v>494</v>
       </c>
       <c r="G2" s="0" t="n">
         <f aca="false">C2/B2</f>
         <v>2.41791044776119</v>
       </c>
       <c r="H2" s="0" t="s">
-        <v>493</v>
+        <v>495</v>
       </c>
       <c r="K2" s="0" t="n">
         <f aca="false">D2/C2</f>
         <v>1.81018518518519</v>
       </c>
       <c r="L2" s="0" t="s">
-        <v>494</v>
+        <v>496</v>
       </c>
       <c r="N2" s="0" t="s">
-        <v>495</v>
+        <v>497</v>
       </c>
       <c r="O2" s="0" t="n">
         <v>80</v>
       </c>
       <c r="P2" s="0" t="s">
-        <v>496</v>
+        <v>498</v>
       </c>
       <c r="Q2" s="0" t="n">
         <f aca="false">O2/D2</f>
@@ -13150,7 +13205,7 @@
         <v>1239</v>
       </c>
       <c r="E3" s="0" t="s">
-        <v>497</v>
+        <v>499</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -13158,7 +13213,7 @@
         <v>2175</v>
       </c>
       <c r="E4" s="0" t="s">
-        <v>498</v>
+        <v>500</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -13169,19 +13224,19 @@
         <v>18</v>
       </c>
       <c r="G5" s="0" t="s">
-        <v>499</v>
+        <v>501</v>
       </c>
       <c r="H5" s="0" t="s">
-        <v>500</v>
+        <v>502</v>
       </c>
       <c r="I5" s="0" t="s">
-        <v>501</v>
+        <v>503</v>
       </c>
       <c r="K5" s="0" t="s">
-        <v>502</v>
+        <v>504</v>
       </c>
       <c r="L5" s="0" t="s">
-        <v>503</v>
+        <v>505</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -13189,7 +13244,7 @@
         <v>3732</v>
       </c>
       <c r="E6" s="0" t="s">
-        <v>504</v>
+        <v>506</v>
       </c>
       <c r="G6" s="0" t="n">
         <f aca="false">C6-C2</f>
@@ -13220,27 +13275,27 @@
         <v>22</v>
       </c>
       <c r="G7" s="0" t="s">
-        <v>505</v>
+        <v>507</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="G8" s="11" t="n">
+      <c r="G8" s="12" t="n">
         <f aca="false">C2/C7</f>
         <v>0.0674157303370787</v>
       </c>
       <c r="O8" s="0" t="s">
-        <v>506</v>
+        <v>508</v>
       </c>
       <c r="P8" s="0" t="s">
-        <v>507</v>
+        <v>509</v>
       </c>
       <c r="Q8" s="0" t="s">
-        <v>508</v>
+        <v>510</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="N9" s="0" t="s">
-        <v>509</v>
+        <v>511</v>
       </c>
       <c r="O9" s="0" t="n">
         <v>1</v>
@@ -13256,7 +13311,7 @@
     </row>
     <row r="10" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="N10" s="0" t="s">
-        <v>509</v>
+        <v>511</v>
       </c>
       <c r="O10" s="0" t="n">
         <v>2</v>
@@ -13272,7 +13327,7 @@
     </row>
     <row r="11" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="N11" s="0" t="s">
-        <v>509</v>
+        <v>511</v>
       </c>
       <c r="O11" s="0" t="n">
         <v>294</v>
@@ -13288,7 +13343,7 @@
     </row>
     <row r="13" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="N13" s="0" t="s">
-        <v>510</v>
+        <v>512</v>
       </c>
       <c r="O13" s="0" t="n">
         <v>200</v>
@@ -13296,7 +13351,7 @@
     </row>
     <row r="14" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="N14" s="0" t="s">
-        <v>511</v>
+        <v>513</v>
       </c>
       <c r="O14" s="0" t="n">
         <v>118</v>

--- a/5_筆記/閱讀數據.xlsx
+++ b/5_筆記/閱讀數據.xlsx
@@ -855,13 +855,13 @@
     <t xml:space="preserve">晉紀四</t>
   </si>
   <si>
-    <t xml:space="preserve">八王之亂人物表</t>
-  </si>
-  <si>
     <t xml:space="preserve">司馬炎24年至25年、晉惠帝至9年</t>
   </si>
   <si>
     <t xml:space="preserve">晉紀五</t>
+  </si>
+  <si>
+    <t xml:space="preserve">晉惠帝10年至11年</t>
   </si>
   <si>
     <t xml:space="preserve">晉紀六</t>
@@ -2187,16 +2187,22 @@
                 <c:pt idx="81">
                   <c:v>1.5</c:v>
                 </c:pt>
+                <c:pt idx="82">
+                  <c:v>4.5</c:v>
+                </c:pt>
+                <c:pt idx="83">
+                  <c:v>-22438</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:yVal>
           <c:smooth val="1"/>
         </c:ser>
-        <c:axId val="38421606"/>
-        <c:axId val="95797626"/>
+        <c:axId val="882462"/>
+        <c:axId val="13861728"/>
       </c:scatterChart>
       <c:valAx>
-        <c:axId val="38421606"/>
+        <c:axId val="882462"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -2272,12 +2278,12 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="95797626"/>
+        <c:crossAx val="13861728"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="midCat"/>
       </c:valAx>
       <c:valAx>
-        <c:axId val="95797626"/>
+        <c:axId val="13861728"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -2353,7 +2359,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="38421606"/>
+        <c:crossAx val="882462"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="midCat"/>
       </c:valAx>
@@ -2388,11 +2394,11 @@
       <xdr:col>10</xdr:col>
       <xdr:colOff>90360</xdr:colOff>
       <xdr:row>11</xdr:row>
-      <xdr:rowOff>109800</xdr:rowOff>
+      <xdr:rowOff>110160</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>15</xdr:col>
-      <xdr:colOff>669240</xdr:colOff>
+      <xdr:colOff>668880</xdr:colOff>
       <xdr:row>27</xdr:row>
       <xdr:rowOff>107640</xdr:rowOff>
     </xdr:to>
@@ -2402,8 +2408,8 @@
         <xdr:cNvGraphicFramePr/>
       </xdr:nvGraphicFramePr>
       <xdr:xfrm>
-        <a:off x="6918480" y="1995480"/>
-        <a:ext cx="4149360" cy="2741040"/>
+        <a:off x="7001640" y="1995840"/>
+        <a:ext cx="4149000" cy="2740680"/>
       </xdr:xfrm>
       <a:graphic>
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
@@ -2421,13 +2427,12 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:R83"/>
+  <dimension ref="A1:R85"/>
   <sheetFormatPr defaultColWidth="8.68359375" defaultRowHeight="13.5" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="7.76"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="5.76"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="1" width="12.81"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="1" width="11.62"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="3" style="1" width="12.81"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="5" style="0" width="9.76"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="0" width="7.76"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="9" style="0" width="14.12"/>
@@ -2537,19 +2542,19 @@
       </c>
       <c r="O2" s="0" t="n">
         <f aca="false">L2*$L$10</f>
-        <v>616.146341463415</v>
+        <v>-35719.4285714286</v>
       </c>
       <c r="P2" s="1" t="n">
         <f aca="false">$C$2+O2</f>
-        <v>44635.1463414634</v>
+        <v>8299.57142857143</v>
       </c>
       <c r="Q2" s="0" t="n">
         <f aca="false">(M2-$F$2)*$L$11</f>
-        <v>488.246554437988</v>
+        <v>328890.689419697</v>
       </c>
       <c r="R2" s="1" t="n">
         <f aca="false">$C$2+Q2</f>
-        <v>44507.246554438</v>
+        <v>372909.689419697</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2600,19 +2605,19 @@
       </c>
       <c r="O3" s="0" t="n">
         <f aca="false">L3*$L$10</f>
-        <v>706.756097560976</v>
+        <v>-40972.2857142857</v>
       </c>
       <c r="P3" s="1" t="n">
         <f aca="false">$C$2+O3</f>
-        <v>44725.756097561</v>
+        <v>3046.71428571428</v>
       </c>
       <c r="Q3" s="0" t="n">
         <f aca="false">(M3-$F$2)*$L$11</f>
-        <v>535.268694512273</v>
+        <v>360565.555174403</v>
       </c>
       <c r="R3" s="1" t="n">
         <f aca="false">$C$2+Q3</f>
-        <v>44554.2686945123</v>
+        <v>404584.555174403</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2663,19 +2668,19 @@
       </c>
       <c r="O4" s="0" t="n">
         <f aca="false">L4*$L$10</f>
-        <v>1069.19512195122</v>
+        <v>-61983.7142857143</v>
       </c>
       <c r="P4" s="1" t="n">
         <f aca="false">$C$2+O4</f>
-        <v>45088.1951219512</v>
+        <v>-17964.7142857143</v>
       </c>
       <c r="Q4" s="0" t="n">
         <f aca="false">(M4-$F$2)*$L$11</f>
-        <v>644.98702135227</v>
+        <v>434473.575268718</v>
       </c>
       <c r="R4" s="1" t="n">
         <f aca="false">$C$2+Q4</f>
-        <v>44663.9870213523</v>
+        <v>478492.575268718</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2726,19 +2731,19 @@
       </c>
       <c r="O5" s="0" t="n">
         <f aca="false">L5*$L$10</f>
-        <v>1594.73170731707</v>
+        <v>-92450.2857142857</v>
       </c>
       <c r="P5" s="1" t="n">
         <f aca="false">$C$2+O5</f>
-        <v>45613.7317073171</v>
+        <v>-48431.2857142857</v>
       </c>
       <c r="Q5" s="0" t="n">
         <f aca="false">(M5-$F$2)*$L$11</f>
-        <v>777.432715894838</v>
+        <v>523691.113811139</v>
       </c>
       <c r="R5" s="1" t="n">
         <f aca="false">$C$2+Q5</f>
-        <v>44796.4327158948</v>
+        <v>567710.11381114</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2789,19 +2794,19 @@
       </c>
       <c r="O6" s="0" t="n">
         <f aca="false">L6*$L$10</f>
-        <v>2401.15853658537</v>
+        <v>-139200.714285714</v>
       </c>
       <c r="P6" s="1" t="n">
         <f aca="false">$C$2+O6</f>
-        <v>46420.1585365854</v>
+        <v>-95181.7142857143</v>
       </c>
       <c r="Q6" s="0" t="n">
         <f aca="false">(M6-$F$2)*$L$11</f>
-        <v>1026.65005828855</v>
+        <v>691567.902311081</v>
       </c>
       <c r="R6" s="1" t="n">
         <f aca="false">$C$2+Q6</f>
-        <v>45045.6500582886</v>
+        <v>735586.902311081</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2852,19 +2857,19 @@
       </c>
       <c r="O7" s="0" t="n">
         <f aca="false">L7*$L$10</f>
-        <v>2663.92682926829</v>
+        <v>-154434</v>
       </c>
       <c r="P7" s="1" t="n">
         <f aca="false">$C$2+O7</f>
-        <v>46682.9268292683</v>
+        <v>-110415</v>
       </c>
       <c r="Q7" s="0" t="n">
         <f aca="false">(M7-$F$2)*$L$11</f>
-        <v>1067.40257968626</v>
+        <v>719019.452631827</v>
       </c>
       <c r="R7" s="1" t="n">
         <f aca="false">$C$2+Q7</f>
-        <v>45086.4025796863</v>
+        <v>763038.452631827</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2915,19 +2920,19 @@
       </c>
       <c r="O8" s="0" t="n">
         <f aca="false">L8*$L$10</f>
-        <v>2663.92682926829</v>
+        <v>-154434</v>
       </c>
       <c r="P8" s="1" t="n">
         <f aca="false">$C$2+O8</f>
-        <v>46682.9268292683</v>
+        <v>-110415</v>
       </c>
       <c r="Q8" s="0" t="n">
         <f aca="false">(M8-$F$2)*$L$11</f>
-        <v>1067.40257968626</v>
+        <v>719019.452631827</v>
       </c>
       <c r="R8" s="1" t="n">
         <f aca="false">$C$2+Q8</f>
-        <v>45086.4025796863</v>
+        <v>763038.452631827</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3002,7 +3007,7 @@
       </c>
       <c r="L10" s="0" t="n">
         <f aca="false">AVERAGE(E:E)</f>
-        <v>9.0609756097561</v>
+        <v>-525.285714285714</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3043,7 +3048,7 @@
       </c>
       <c r="L11" s="0" t="n">
         <f aca="false">AVEDEV(I:I)</f>
-        <v>0.78370233457141</v>
+        <v>527.9144292451</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5524,6 +5529,71 @@
       <c r="I83" s="0" t="n">
         <f aca="false">E83/H83</f>
         <v>1.5</v>
+      </c>
+    </row>
+    <row r="84" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A84" s="0" t="n">
+        <v>705</v>
+      </c>
+      <c r="B84" s="0" t="str">
+        <f aca="false">"卷"&amp;ROW(B83)</f>
+        <v>卷83</v>
+      </c>
+      <c r="C84" s="7" t="n">
+        <v>44868</v>
+      </c>
+      <c r="D84" s="1" t="n">
+        <v>44876</v>
+      </c>
+      <c r="E84" s="0" t="n">
+        <f aca="false">D84-C84+1</f>
+        <v>9</v>
+      </c>
+      <c r="F84" s="0" t="n">
+        <f aca="false">G83+1</f>
+        <v>299</v>
+      </c>
+      <c r="G84" s="0" t="n">
+        <v>300</v>
+      </c>
+      <c r="H84" s="0" t="n">
+        <f aca="false">IF(F84*G84&lt;0,ABS(F84)+ABS(G84),G84-F84+1)</f>
+        <v>2</v>
+      </c>
+      <c r="I84" s="0" t="n">
+        <f aca="false">E84/H84</f>
+        <v>4.5</v>
+      </c>
+    </row>
+    <row r="85" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A85" s="0" t="n">
+        <v>706</v>
+      </c>
+      <c r="B85" s="0" t="str">
+        <f aca="false">"卷"&amp;ROW(B84)</f>
+        <v>卷84</v>
+      </c>
+      <c r="C85" s="7" t="n">
+        <v>44877</v>
+      </c>
+      <c r="E85" s="0" t="n">
+        <f aca="false">D85-C85+1</f>
+        <v>-44876</v>
+      </c>
+      <c r="F85" s="0" t="n">
+        <f aca="false">G84+1</f>
+        <v>301</v>
+      </c>
+      <c r="G85" s="0" t="n">
+        <v>302</v>
+      </c>
+      <c r="H85" s="0" t="n">
+        <f aca="false">IF(F85*G85&lt;0,ABS(F85)+ABS(G85),G85-F85+1)</f>
+        <v>2</v>
+      </c>
+      <c r="I85" s="0" t="n">
+        <f aca="false">E85/H85</f>
+        <v>-22438</v>
       </c>
     </row>
   </sheetData>
@@ -8029,64 +8099,63 @@
         <f aca="false">VLOOKUP($A83,統計!$A:$G,7,)</f>
         <v>298</v>
       </c>
-      <c r="G83" s="0" t="s">
+      <c r="H83" s="0" t="s">
         <v>277</v>
-      </c>
-      <c r="H83" s="0" t="s">
-        <v>278</v>
       </c>
       <c r="I83" s="0" t="str">
         <f aca="false">A83&amp;"|"&amp;"["&amp;B83&amp;"](5_筆記/资治通鉴"&amp;SUBSTITUTE(B83,"卷","")&amp;".html)|"&amp;C83&amp;"|"&amp;D83&amp;"|"&amp;E83&amp;"|"&amp;F83&amp;"|"&amp;G83&amp;"|"&amp;H83</f>
-        <v>704|[卷82](5_筆記/资治通鉴82.html)|晉紀四|289|298||八王之亂人物表|司馬炎24年至25年、晉惠帝至9年</v>
+        <v>704|[卷82](5_筆記/资治通鉴82.html)|晉紀四|289|298|||司馬炎24年至25年、晉惠帝至9年</v>
       </c>
     </row>
     <row r="84" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A84" s="0" t="n">
         <v>705</v>
       </c>
-      <c r="B84" s="0" t="e">
+      <c r="B84" s="0" t="str">
         <f aca="false">VLOOKUP($A84,統計!$A:$G,2,)</f>
-        <v>#N/A</v>
+        <v>卷83</v>
       </c>
       <c r="C84" s="0" t="s">
+        <v>278</v>
+      </c>
+      <c r="D84" s="0" t="n">
+        <f aca="false">VLOOKUP($A84,統計!$A:$G,6,)</f>
+        <v>299</v>
+      </c>
+      <c r="E84" s="0" t="n">
+        <f aca="false">VLOOKUP($A84,統計!$A:$G,7,)</f>
+        <v>300</v>
+      </c>
+      <c r="H84" s="0" t="s">
         <v>279</v>
       </c>
-      <c r="D84" s="0" t="e">
-        <f aca="false">VLOOKUP($A84,統計!$A:$G,6,)</f>
-        <v>#N/A</v>
-      </c>
-      <c r="E84" s="0" t="e">
-        <f aca="false">VLOOKUP($A84,統計!$A:$G,7,)</f>
-        <v>#N/A</v>
-      </c>
-      <c r="H84" s="0"/>
-      <c r="I84" s="0" t="e">
+      <c r="I84" s="0" t="str">
         <f aca="false">A84&amp;"|"&amp;"["&amp;B84&amp;"](5_筆記/资治通鉴"&amp;SUBSTITUTE(B84,"卷","")&amp;".html)|"&amp;C84&amp;"|"&amp;D84&amp;"|"&amp;E84&amp;"|"&amp;F84&amp;"|"&amp;G84&amp;"|"&amp;H84</f>
-        <v>#N/A</v>
+        <v>705|[卷83](5_筆記/资治通鉴83.html)|晉紀五|299|300|||晉惠帝10年至11年</v>
       </c>
     </row>
     <row r="85" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A85" s="0" t="n">
         <v>706</v>
       </c>
-      <c r="B85" s="0" t="e">
+      <c r="B85" s="0" t="str">
         <f aca="false">VLOOKUP($A85,統計!$A:$G,2,)</f>
-        <v>#N/A</v>
+        <v>卷84</v>
       </c>
       <c r="C85" s="0" t="s">
         <v>280</v>
       </c>
-      <c r="D85" s="0" t="e">
+      <c r="D85" s="0" t="n">
         <f aca="false">VLOOKUP($A85,統計!$A:$G,6,)</f>
-        <v>#N/A</v>
-      </c>
-      <c r="E85" s="0" t="e">
+        <v>301</v>
+      </c>
+      <c r="E85" s="0" t="n">
         <f aca="false">VLOOKUP($A85,統計!$A:$G,7,)</f>
-        <v>#N/A</v>
-      </c>
-      <c r="I85" s="0" t="e">
+        <v>302</v>
+      </c>
+      <c r="I85" s="0" t="str">
         <f aca="false">A85&amp;"|"&amp;"["&amp;B85&amp;"](5_筆記/资治通鉴"&amp;SUBSTITUTE(B85,"卷","")&amp;".html)|"&amp;C85&amp;"|"&amp;D85&amp;"|"&amp;E85&amp;"|"&amp;F85&amp;"|"&amp;G85&amp;"|"&amp;H85</f>
-        <v>#N/A</v>
+        <v>706|[卷84](5_筆記/资治通鉴84.html)|晉紀六|301|302|||</v>
       </c>
     </row>
     <row r="86" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">

--- a/5_筆記/閱讀數據.xlsx
+++ b/5_筆記/閱讀數據.xlsx
@@ -8,16 +8,16 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\self\study\zizhitongjian\5_筆記\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E9F3C742-A31E-4DCE-8B3F-037BB642A2DF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{82623B25-C67E-4B56-BCE2-60553B13210F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-24120" yWindow="2415" windowWidth="24240" windowHeight="13740" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="統計" sheetId="1" r:id="rId1"/>
     <sheet name="目錄生成" sheetId="2" r:id="rId2"/>
     <sheet name="Sheet2" sheetId="3" r:id="rId3"/>
   </sheets>
-  <calcPr calcId="181029"/>
+  <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:loext="http://schemas.libreoffice.org/" uri="{7626C862-2A13-11E5-B345-FEFF819CDC9F}">
       <loext:extCalcPr stringRefSyntax="ExcelA1"/>
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="521" uniqueCount="515">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="523" uniqueCount="517">
   <si>
     <t>索引號</t>
   </si>
@@ -1572,6 +1572,14 @@
   </si>
   <si>
     <t>晉惠帝12年、司馬倫、晉惠帝13年</t>
+  </si>
+  <si>
+    <t>羊獻容廢立表</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>晉惠帝14年至15年</t>
+    <phoneticPr fontId="4" type="noConversion"/>
   </si>
 </sst>
 </file>
@@ -1878,7 +1886,7 @@
             <c:strRef>
               <c:f>統計!$B$2:$B$115</c:f>
               <c:strCache>
-                <c:ptCount val="84"/>
+                <c:ptCount val="85"/>
                 <c:pt idx="0">
                   <c:v>卷1</c:v>
                 </c:pt>
@@ -2130,6 +2138,9 @@
                 </c:pt>
                 <c:pt idx="83">
                   <c:v>卷84</c:v>
+                </c:pt>
+                <c:pt idx="84">
+                  <c:v>卷85</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
@@ -2391,6 +2402,9 @@
                 </c:pt>
                 <c:pt idx="83">
                   <c:v>6.5</c:v>
+                </c:pt>
+                <c:pt idx="84">
+                  <c:v>5</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -2945,7 +2959,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:R85"/>
+  <dimension ref="A1:R86"/>
   <sheetFormatPr defaultColWidth="8.625" defaultRowHeight="13.5" x14ac:dyDescent="0.15"/>
   <cols>
     <col min="1" max="1" width="7.75" customWidth="1"/>
@@ -3060,19 +3074,19 @@
       </c>
       <c r="O2">
         <f t="shared" ref="O2:O8" si="5">L2*$L$10</f>
-        <v>619.28571428571433</v>
+        <v>620</v>
       </c>
       <c r="P2" s="1">
         <f t="shared" ref="P2:P8" si="6">$C$2+O2</f>
-        <v>44638.285714285717</v>
+        <v>44639</v>
       </c>
       <c r="Q2">
         <f t="shared" ref="Q2:Q8" si="7">(M2-$F$2)*$L$11</f>
-        <v>557.0330243749064</v>
+        <v>584.46359048733302</v>
       </c>
       <c r="R2" s="1">
         <f t="shared" ref="R2:R8" si="8">$C$2+Q2</f>
-        <v>44576.033024374905</v>
+        <v>44603.463590487336</v>
       </c>
     </row>
     <row r="3" spans="1:18" x14ac:dyDescent="0.15">
@@ -3123,19 +3137,19 @@
       </c>
       <c r="O3">
         <f t="shared" si="5"/>
-        <v>710.35714285714289</v>
+        <v>711.17647058823525</v>
       </c>
       <c r="P3" s="1">
         <f t="shared" si="6"/>
-        <v>44729.357142857145</v>
+        <v>44730.176470588238</v>
       </c>
       <c r="Q3">
         <f t="shared" si="7"/>
-        <v>610.67986460362943</v>
+        <v>640.75221878466857</v>
       </c>
       <c r="R3" s="1">
         <f t="shared" si="8"/>
-        <v>44629.679864603626</v>
+        <v>44659.75221878467</v>
       </c>
     </row>
     <row r="4" spans="1:18" x14ac:dyDescent="0.15">
@@ -3186,19 +3200,19 @@
       </c>
       <c r="O4">
         <f t="shared" si="5"/>
-        <v>1074.6428571428571</v>
+        <v>1075.8823529411764</v>
       </c>
       <c r="P4" s="1">
         <f t="shared" si="6"/>
-        <v>45093.642857142855</v>
+        <v>45094.882352941175</v>
       </c>
       <c r="Q4">
         <f t="shared" si="7"/>
-        <v>735.85582513731617</v>
+        <v>772.09235147845118</v>
       </c>
       <c r="R4" s="1">
         <f t="shared" si="8"/>
-        <v>44754.855825137318</v>
+        <v>44791.092351478452</v>
       </c>
     </row>
     <row r="5" spans="1:18" x14ac:dyDescent="0.15">
@@ -3249,19 +3263,19 @@
       </c>
       <c r="O5">
         <f t="shared" si="5"/>
-        <v>1602.8571428571429</v>
+        <v>1604.705882352941</v>
       </c>
       <c r="P5" s="1">
         <f t="shared" si="6"/>
-        <v>45621.857142857145</v>
+        <v>45623.705882352944</v>
       </c>
       <c r="Q5">
         <f t="shared" si="7"/>
-        <v>886.96109178155245</v>
+        <v>930.63865451594609</v>
       </c>
       <c r="R5" s="1">
         <f t="shared" si="8"/>
-        <v>44905.961091781552</v>
+        <v>44949.638654515948</v>
       </c>
     </row>
     <row r="6" spans="1:18" x14ac:dyDescent="0.15">
@@ -3312,19 +3326,19 @@
       </c>
       <c r="O6">
         <f t="shared" si="5"/>
-        <v>2413.3928571428573</v>
+        <v>2416.1764705882351</v>
       </c>
       <c r="P6" s="1">
         <f t="shared" si="6"/>
-        <v>46432.392857142855</v>
+        <v>46435.176470588238</v>
       </c>
       <c r="Q6">
         <f t="shared" si="7"/>
-        <v>1171.289344993784</v>
+        <v>1228.9683844918241</v>
       </c>
       <c r="R6" s="1">
         <f t="shared" si="8"/>
-        <v>45190.289344993784</v>
+        <v>45247.968384491825</v>
       </c>
     </row>
     <row r="7" spans="1:18" x14ac:dyDescent="0.15">
@@ -3375,19 +3389,19 @@
       </c>
       <c r="O7">
         <f t="shared" si="5"/>
-        <v>2677.5</v>
+        <v>2680.5882352941176</v>
       </c>
       <c r="P7" s="1">
         <f t="shared" si="6"/>
-        <v>46696.5</v>
+        <v>46699.588235294119</v>
       </c>
       <c r="Q7">
         <f t="shared" si="7"/>
-        <v>1217.7832731920105</v>
+        <v>1277.7518623495146</v>
       </c>
       <c r="R7" s="1">
         <f t="shared" si="8"/>
-        <v>45236.783273192013</v>
+        <v>45296.751862349513</v>
       </c>
     </row>
     <row r="8" spans="1:18" x14ac:dyDescent="0.15">
@@ -3438,19 +3452,19 @@
       </c>
       <c r="O8">
         <f t="shared" si="5"/>
-        <v>2677.5</v>
+        <v>2680.5882352941176</v>
       </c>
       <c r="P8" s="1">
         <f t="shared" si="6"/>
-        <v>46696.5</v>
+        <v>46699.588235294119</v>
       </c>
       <c r="Q8">
         <f t="shared" si="7"/>
-        <v>1217.7832731920105</v>
+        <v>1277.7518623495146</v>
       </c>
       <c r="R8" s="1">
         <f t="shared" si="8"/>
-        <v>45236.783273192013</v>
+        <v>45296.751862349513</v>
       </c>
     </row>
     <row r="9" spans="1:18" x14ac:dyDescent="0.15">
@@ -3525,7 +3539,7 @@
       </c>
       <c r="L10">
         <f>AVERAGE(E:E)</f>
-        <v>9.1071428571428577</v>
+        <v>9.117647058823529</v>
       </c>
     </row>
     <row r="11" spans="1:18" x14ac:dyDescent="0.15">
@@ -3566,7 +3580,7 @@
       </c>
       <c r="L11">
         <f>AVEDEV(I:I)</f>
-        <v>0.89411400381204886</v>
+        <v>0.9381438049555908</v>
       </c>
     </row>
     <row r="12" spans="1:18" x14ac:dyDescent="0.15">
@@ -5429,7 +5443,7 @@
         <v>526</v>
       </c>
       <c r="B66" t="str">
-        <f t="shared" ref="B66:B85" si="16">"卷"&amp;ROW(B65)</f>
+        <f t="shared" ref="B66:B86" si="16">"卷"&amp;ROW(B65)</f>
         <v>卷65</v>
       </c>
       <c r="C66" s="1">
@@ -6115,6 +6129,40 @@
       <c r="I85">
         <f t="shared" si="19"/>
         <v>6.5</v>
+      </c>
+    </row>
+    <row r="86" spans="1:9" x14ac:dyDescent="0.15">
+      <c r="A86">
+        <v>707</v>
+      </c>
+      <c r="B86" t="str">
+        <f t="shared" si="16"/>
+        <v>卷85</v>
+      </c>
+      <c r="C86" s="7">
+        <v>44891</v>
+      </c>
+      <c r="D86" s="1">
+        <v>44900</v>
+      </c>
+      <c r="E86">
+        <f t="shared" ref="E86" si="22">D86-C86+1</f>
+        <v>10</v>
+      </c>
+      <c r="F86">
+        <f t="shared" ref="F86" si="23">G85+1</f>
+        <v>303</v>
+      </c>
+      <c r="G86">
+        <v>304</v>
+      </c>
+      <c r="H86">
+        <f t="shared" ref="H86" si="24">IF(F86*G86&lt;0,ABS(F86)+ABS(G86),G86-F86+1)</f>
+        <v>2</v>
+      </c>
+      <c r="I86">
+        <f t="shared" ref="I86" si="25">E86/H86</f>
+        <v>5</v>
       </c>
     </row>
   </sheetData>
@@ -8679,24 +8727,30 @@
       <c r="A86">
         <v>707</v>
       </c>
-      <c r="B86" t="e">
+      <c r="B86" t="str">
         <f>VLOOKUP($A86,統計!$A:$G,2,)</f>
-        <v>#N/A</v>
+        <v>卷85</v>
       </c>
       <c r="C86" t="s">
         <v>281</v>
       </c>
-      <c r="D86" t="e">
+      <c r="D86">
         <f>VLOOKUP($A86,統計!$A:$G,6,)</f>
-        <v>#N/A</v>
-      </c>
-      <c r="E86" t="e">
+        <v>303</v>
+      </c>
+      <c r="E86">
         <f>VLOOKUP($A86,統計!$A:$G,7,)</f>
-        <v>#N/A</v>
-      </c>
-      <c r="I86" t="e">
+        <v>304</v>
+      </c>
+      <c r="G86" t="s">
+        <v>515</v>
+      </c>
+      <c r="H86" s="8" t="s">
+        <v>516</v>
+      </c>
+      <c r="I86" t="str">
         <f t="shared" si="1"/>
-        <v>#N/A</v>
+        <v>707|[卷85](5_筆記/资治通鉴85.html)|晉紀七|303|304||羊獻容廢立表|晉惠帝14年至15年</v>
       </c>
     </row>
     <row r="87" spans="1:9" x14ac:dyDescent="0.15">

--- a/5_筆記/閱讀數據.xlsx
+++ b/5_筆記/閱讀數據.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="25726"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="25831"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\self\study\zizhitongjian\5_筆記\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{82623B25-C67E-4B56-BCE2-60553B13210F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3C9DC5E1-4EE8-4241-94DB-8594506179B7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-24120" yWindow="2415" windowWidth="24240" windowHeight="13740" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="523" uniqueCount="517">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="524" uniqueCount="518">
   <si>
     <t>索引號</t>
   </si>
@@ -1579,6 +1579,10 @@
   </si>
   <si>
     <t>晉惠帝14年至15年</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>晉惠帝16年至18年、晉懷帝至2年</t>
     <phoneticPr fontId="4" type="noConversion"/>
   </si>
 </sst>
@@ -1666,7 +1670,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="9" fontId="3" fillId="0" borderId="0" applyBorder="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="13">
+  <cellXfs count="10">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="176" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
@@ -1675,11 +1679,8 @@
     <xf numFmtId="0" fontId="1" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="1" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="177" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="10" fontId="0" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="10" fontId="0" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyProtection="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="百分比" xfId="1" builtinId="5"/>
@@ -1886,7 +1887,7 @@
             <c:strRef>
               <c:f>統計!$B$2:$B$115</c:f>
               <c:strCache>
-                <c:ptCount val="85"/>
+                <c:ptCount val="86"/>
                 <c:pt idx="0">
                   <c:v>卷1</c:v>
                 </c:pt>
@@ -2141,6 +2142,9 @@
                 </c:pt>
                 <c:pt idx="84">
                   <c:v>卷85</c:v>
+                </c:pt>
+                <c:pt idx="85">
+                  <c:v>卷86</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
@@ -2405,6 +2409,9 @@
                 </c:pt>
                 <c:pt idx="84">
                   <c:v>5</c:v>
+                </c:pt>
+                <c:pt idx="85">
+                  <c:v>3.75</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -2959,7 +2966,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:R86"/>
+  <dimension ref="A1:R87"/>
   <sheetFormatPr defaultColWidth="8.625" defaultRowHeight="13.5" x14ac:dyDescent="0.15"/>
   <cols>
     <col min="1" max="1" width="7.75" customWidth="1"/>
@@ -3074,19 +3081,19 @@
       </c>
       <c r="O2">
         <f t="shared" ref="O2:O8" si="5">L2*$L$10</f>
-        <v>620</v>
+        <v>624.65116279069775</v>
       </c>
       <c r="P2" s="1">
         <f t="shared" ref="P2:P8" si="6">$C$2+O2</f>
-        <v>44639</v>
+        <v>44643.651162790695</v>
       </c>
       <c r="Q2">
         <f t="shared" ref="Q2:Q8" si="7">(M2-$F$2)*$L$11</f>
-        <v>584.46359048733302</v>
+        <v>598.2649505954995</v>
       </c>
       <c r="R2" s="1">
         <f t="shared" ref="R2:R8" si="8">$C$2+Q2</f>
-        <v>44603.463590487336</v>
+        <v>44617.264950595498</v>
       </c>
     </row>
     <row r="3" spans="1:18" x14ac:dyDescent="0.15">
@@ -3137,19 +3144,19 @@
       </c>
       <c r="O3">
         <f t="shared" si="5"/>
-        <v>711.17647058823525</v>
+        <v>716.51162790697674</v>
       </c>
       <c r="P3" s="1">
         <f t="shared" si="6"/>
-        <v>44730.176470588238</v>
+        <v>44735.511627906977</v>
       </c>
       <c r="Q3">
         <f t="shared" si="7"/>
-        <v>640.75221878466857</v>
+        <v>655.88276285188795</v>
       </c>
       <c r="R3" s="1">
         <f t="shared" si="8"/>
-        <v>44659.75221878467</v>
+        <v>44674.882762851885</v>
       </c>
     </row>
     <row r="4" spans="1:18" x14ac:dyDescent="0.15">
@@ -3200,19 +3207,19 @@
       </c>
       <c r="O4">
         <f t="shared" si="5"/>
-        <v>1075.8823529411764</v>
+        <v>1083.953488372093</v>
       </c>
       <c r="P4" s="1">
         <f t="shared" si="6"/>
-        <v>45094.882352941175</v>
+        <v>45102.953488372092</v>
       </c>
       <c r="Q4">
         <f t="shared" si="7"/>
-        <v>772.09235147845118</v>
+        <v>790.32432478346084</v>
       </c>
       <c r="R4" s="1">
         <f t="shared" si="8"/>
-        <v>44791.092351478452</v>
+        <v>44809.324324783462</v>
       </c>
     </row>
     <row r="5" spans="1:18" x14ac:dyDescent="0.15">
@@ -3263,19 +3270,19 @@
       </c>
       <c r="O5">
         <f t="shared" si="5"/>
-        <v>1604.705882352941</v>
+        <v>1616.7441860465117</v>
       </c>
       <c r="P5" s="1">
         <f t="shared" si="6"/>
-        <v>45623.705882352944</v>
+        <v>45635.744186046511</v>
       </c>
       <c r="Q5">
         <f t="shared" si="7"/>
-        <v>930.63865451594609</v>
+        <v>952.61449597228818</v>
       </c>
       <c r="R5" s="1">
         <f t="shared" si="8"/>
-        <v>44949.638654515948</v>
+        <v>44971.614495972288</v>
       </c>
     </row>
     <row r="6" spans="1:18" x14ac:dyDescent="0.15">
@@ -3326,19 +3333,19 @@
       </c>
       <c r="O6">
         <f t="shared" si="5"/>
-        <v>2416.1764705882351</v>
+        <v>2434.3023255813955</v>
       </c>
       <c r="P6" s="1">
         <f t="shared" si="6"/>
-        <v>46435.176470588238</v>
+        <v>46453.302325581397</v>
       </c>
       <c r="Q6">
         <f t="shared" si="7"/>
-        <v>1228.9683844918241</v>
+        <v>1257.9889009311466</v>
       </c>
       <c r="R6" s="1">
         <f t="shared" si="8"/>
-        <v>45247.968384491825</v>
+        <v>45276.988900931145</v>
       </c>
     </row>
     <row r="7" spans="1:18" x14ac:dyDescent="0.15">
@@ -3389,19 +3396,19 @@
       </c>
       <c r="O7">
         <f t="shared" si="5"/>
-        <v>2680.5882352941176</v>
+        <v>2700.6976744186049</v>
       </c>
       <c r="P7" s="1">
         <f t="shared" si="6"/>
-        <v>46699.588235294119</v>
+        <v>46719.697674418603</v>
       </c>
       <c r="Q7">
         <f t="shared" si="7"/>
-        <v>1277.7518623495146</v>
+        <v>1307.9243382200166</v>
       </c>
       <c r="R7" s="1">
         <f t="shared" si="8"/>
-        <v>45296.751862349513</v>
+        <v>45326.924338220015</v>
       </c>
     </row>
     <row r="8" spans="1:18" x14ac:dyDescent="0.15">
@@ -3452,19 +3459,19 @@
       </c>
       <c r="O8">
         <f t="shared" si="5"/>
-        <v>2680.5882352941176</v>
+        <v>2700.6976744186049</v>
       </c>
       <c r="P8" s="1">
         <f t="shared" si="6"/>
-        <v>46699.588235294119</v>
+        <v>46719.697674418603</v>
       </c>
       <c r="Q8">
         <f t="shared" si="7"/>
-        <v>1277.7518623495146</v>
+        <v>1307.9243382200166</v>
       </c>
       <c r="R8" s="1">
         <f t="shared" si="8"/>
-        <v>45296.751862349513</v>
+        <v>45326.924338220015</v>
       </c>
     </row>
     <row r="9" spans="1:18" x14ac:dyDescent="0.15">
@@ -3539,7 +3546,7 @@
       </c>
       <c r="L10">
         <f>AVERAGE(E:E)</f>
-        <v>9.117647058823529</v>
+        <v>9.1860465116279073</v>
       </c>
     </row>
     <row r="11" spans="1:18" x14ac:dyDescent="0.15">
@@ -3580,7 +3587,7 @@
       </c>
       <c r="L11">
         <f>AVEDEV(I:I)</f>
-        <v>0.9381438049555908</v>
+        <v>0.96029687093980665</v>
       </c>
     </row>
     <row r="12" spans="1:18" x14ac:dyDescent="0.15">
@@ -5443,7 +5450,7 @@
         <v>526</v>
       </c>
       <c r="B66" t="str">
-        <f t="shared" ref="B66:B86" si="16">"卷"&amp;ROW(B65)</f>
+        <f t="shared" ref="B66:B87" si="16">"卷"&amp;ROW(B65)</f>
         <v>卷65</v>
       </c>
       <c r="C66" s="1">
@@ -6163,6 +6170,40 @@
       <c r="I86">
         <f t="shared" ref="I86" si="25">E86/H86</f>
         <v>5</v>
+      </c>
+    </row>
+    <row r="87" spans="1:9" x14ac:dyDescent="0.15">
+      <c r="A87">
+        <v>708</v>
+      </c>
+      <c r="B87" t="str">
+        <f t="shared" si="16"/>
+        <v>卷86</v>
+      </c>
+      <c r="C87" s="7">
+        <v>44902</v>
+      </c>
+      <c r="D87" s="1">
+        <v>44916</v>
+      </c>
+      <c r="E87">
+        <f t="shared" ref="E87" si="26">D87-C87+1</f>
+        <v>15</v>
+      </c>
+      <c r="F87">
+        <f t="shared" ref="F87" si="27">G86+1</f>
+        <v>305</v>
+      </c>
+      <c r="G87">
+        <v>308</v>
+      </c>
+      <c r="H87">
+        <f t="shared" ref="H87" si="28">IF(F87*G87&lt;0,ABS(F87)+ABS(G87),G87-F87+1)</f>
+        <v>4</v>
+      </c>
+      <c r="I87">
+        <f t="shared" ref="I87" si="29">E87/H87</f>
+        <v>3.75</v>
       </c>
     </row>
   </sheetData>
@@ -6180,7 +6221,7 @@
   <cols>
     <col min="6" max="6" width="33.375" customWidth="1"/>
     <col min="7" max="7" width="22.125" customWidth="1"/>
-    <col min="8" max="8" width="22" style="8" customWidth="1"/>
+    <col min="8" max="8" width="22" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:9" s="3" customFormat="1" x14ac:dyDescent="0.15">
@@ -6205,7 +6246,7 @@
       <c r="G1" s="6" t="s">
         <v>30</v>
       </c>
-      <c r="H1" s="9" t="s">
+      <c r="H1" s="2" t="s">
         <v>31</v>
       </c>
       <c r="I1" s="5" t="s">
@@ -6234,7 +6275,7 @@
       <c r="F2" t="s">
         <v>34</v>
       </c>
-      <c r="H2" s="8" t="s">
+      <c r="H2" t="s">
         <v>35</v>
       </c>
       <c r="I2" t="str">
@@ -6267,7 +6308,7 @@
       <c r="G3" t="s">
         <v>38</v>
       </c>
-      <c r="H3" s="8" t="s">
+      <c r="H3" t="s">
         <v>39</v>
       </c>
       <c r="I3" t="str">
@@ -6297,7 +6338,7 @@
       <c r="G4" t="s">
         <v>41</v>
       </c>
-      <c r="H4" s="8" t="s">
+      <c r="H4" t="s">
         <v>42</v>
       </c>
       <c r="I4" t="str">
@@ -6327,7 +6368,7 @@
       <c r="G5" t="s">
         <v>44</v>
       </c>
-      <c r="H5" s="8" t="s">
+      <c r="H5" t="s">
         <v>45</v>
       </c>
       <c r="I5" t="str">
@@ -6357,7 +6398,7 @@
       <c r="F6" t="s">
         <v>47</v>
       </c>
-      <c r="H6" s="8" t="s">
+      <c r="H6" t="s">
         <v>48</v>
       </c>
       <c r="I6" t="str">
@@ -6387,7 +6428,7 @@
       <c r="G7" t="s">
         <v>50</v>
       </c>
-      <c r="H7" s="8" t="s">
+      <c r="H7" t="s">
         <v>51</v>
       </c>
       <c r="I7" t="str">
@@ -6417,7 +6458,7 @@
       <c r="F8" t="s">
         <v>53</v>
       </c>
-      <c r="H8" s="8" t="s">
+      <c r="H8" t="s">
         <v>54</v>
       </c>
       <c r="I8" t="str">
@@ -6444,7 +6485,7 @@
         <f>VLOOKUP($A9,統計!$A:$G,7,)</f>
         <v>-207</v>
       </c>
-      <c r="H9" s="8" t="s">
+      <c r="H9" t="s">
         <v>56</v>
       </c>
       <c r="I9" t="str">
@@ -6477,7 +6518,7 @@
       <c r="G10" t="s">
         <v>59</v>
       </c>
-      <c r="H10" s="8" t="s">
+      <c r="H10" t="s">
         <v>60</v>
       </c>
       <c r="I10" t="str">
@@ -6507,7 +6548,7 @@
       <c r="G11" t="s">
         <v>62</v>
       </c>
-      <c r="H11" s="8" t="s">
+      <c r="H11" t="s">
         <v>63</v>
       </c>
       <c r="I11" t="str">
@@ -6537,7 +6578,7 @@
       <c r="G12" t="s">
         <v>65</v>
       </c>
-      <c r="H12" s="8" t="s">
+      <c r="H12" t="s">
         <v>66</v>
       </c>
       <c r="I12" t="str">
@@ -6564,7 +6605,7 @@
         <f>VLOOKUP($A13,統計!$A:$G,7,)</f>
         <v>-188</v>
       </c>
-      <c r="H13" s="8" t="s">
+      <c r="H13" t="s">
         <v>68</v>
       </c>
       <c r="I13" t="str">
@@ -6597,7 +6638,7 @@
       <c r="G14" t="s">
         <v>71</v>
       </c>
-      <c r="H14" s="8" t="s">
+      <c r="H14" t="s">
         <v>72</v>
       </c>
       <c r="I14" t="str">
@@ -6627,7 +6668,7 @@
       <c r="G15" t="s">
         <v>74</v>
       </c>
-      <c r="H15" s="8" t="s">
+      <c r="H15" t="s">
         <v>75</v>
       </c>
       <c r="I15" t="str">
@@ -6657,7 +6698,7 @@
       <c r="G16" t="s">
         <v>77</v>
       </c>
-      <c r="H16" s="8" t="s">
+      <c r="H16" t="s">
         <v>78</v>
       </c>
       <c r="I16" t="str">
@@ -6690,7 +6731,7 @@
       <c r="G17" t="s">
         <v>81</v>
       </c>
-      <c r="H17" s="8" t="s">
+      <c r="H17" t="s">
         <v>82</v>
       </c>
       <c r="I17" t="str">
@@ -6723,7 +6764,7 @@
       <c r="G18" t="s">
         <v>85</v>
       </c>
-      <c r="H18" s="8" t="s">
+      <c r="H18" t="s">
         <v>86</v>
       </c>
       <c r="I18" t="str">
@@ -6753,7 +6794,7 @@
       <c r="G19" t="s">
         <v>88</v>
       </c>
-      <c r="H19" s="8" t="s">
+      <c r="H19" t="s">
         <v>89</v>
       </c>
       <c r="I19" t="str">
@@ -6786,7 +6827,7 @@
       <c r="G20" t="s">
         <v>92</v>
       </c>
-      <c r="H20" s="8" t="s">
+      <c r="H20" t="s">
         <v>93</v>
       </c>
       <c r="I20" t="str">
@@ -6816,7 +6857,7 @@
       <c r="G21" t="s">
         <v>95</v>
       </c>
-      <c r="H21" s="8" t="s">
+      <c r="H21" t="s">
         <v>96</v>
       </c>
       <c r="I21" t="str">
@@ -6843,7 +6884,7 @@
         <f>VLOOKUP($A22,統計!$A:$G,7,)</f>
         <v>-99</v>
       </c>
-      <c r="H22" s="8" t="s">
+      <c r="H22" t="s">
         <v>98</v>
       </c>
       <c r="I22" t="str">
@@ -6873,7 +6914,7 @@
       <c r="G23" t="s">
         <v>100</v>
       </c>
-      <c r="H23" s="8" t="s">
+      <c r="H23" t="s">
         <v>101</v>
       </c>
       <c r="I23" t="str">
@@ -6903,7 +6944,7 @@
       <c r="F24" t="s">
         <v>103</v>
       </c>
-      <c r="H24" s="8" t="s">
+      <c r="H24" t="s">
         <v>104</v>
       </c>
       <c r="I24" t="str">
@@ -6936,7 +6977,7 @@
       <c r="G25" t="s">
         <v>107</v>
       </c>
-      <c r="H25" s="8" t="s">
+      <c r="H25" t="s">
         <v>108</v>
       </c>
       <c r="I25" t="str">
@@ -6966,7 +7007,7 @@
       <c r="G26" t="s">
         <v>110</v>
       </c>
-      <c r="H26" s="8" t="s">
+      <c r="H26" t="s">
         <v>111</v>
       </c>
       <c r="I26" t="str">
@@ -6993,7 +7034,7 @@
         <f>VLOOKUP($A27,統計!$A:$G,7,)</f>
         <v>-59</v>
       </c>
-      <c r="H27" s="8" t="s">
+      <c r="H27" t="s">
         <v>113</v>
       </c>
       <c r="I27" t="str">
@@ -7026,7 +7067,7 @@
       <c r="G28" t="s">
         <v>116</v>
       </c>
-      <c r="H28" s="8" t="s">
+      <c r="H28" t="s">
         <v>117</v>
       </c>
       <c r="I28" t="str">
@@ -7056,7 +7097,7 @@
       <c r="G29" t="s">
         <v>119</v>
       </c>
-      <c r="H29" s="8" t="s">
+      <c r="H29" t="s">
         <v>120</v>
       </c>
       <c r="I29" t="str">
@@ -7086,7 +7127,7 @@
       <c r="F30" t="s">
         <v>122</v>
       </c>
-      <c r="H30" s="8" t="s">
+      <c r="H30" t="s">
         <v>123</v>
       </c>
       <c r="I30" t="str">
@@ -7116,7 +7157,7 @@
       <c r="F31" t="s">
         <v>125</v>
       </c>
-      <c r="H31" s="8" t="s">
+      <c r="H31" t="s">
         <v>126</v>
       </c>
       <c r="I31" t="str">
@@ -7149,7 +7190,7 @@
       <c r="G32" t="s">
         <v>129</v>
       </c>
-      <c r="H32" s="8" t="s">
+      <c r="H32" t="s">
         <v>130</v>
       </c>
       <c r="I32" t="str">
@@ -7179,7 +7220,7 @@
       <c r="F33" t="s">
         <v>132</v>
       </c>
-      <c r="H33" s="8" t="s">
+      <c r="H33" t="s">
         <v>133</v>
       </c>
       <c r="I33" t="str">
@@ -7209,7 +7250,7 @@
       <c r="F34" t="s">
         <v>135</v>
       </c>
-      <c r="H34" s="8" t="s">
+      <c r="H34" t="s">
         <v>136</v>
       </c>
       <c r="I34" t="str">
@@ -7239,7 +7280,7 @@
       <c r="G35" t="s">
         <v>138</v>
       </c>
-      <c r="H35" s="8" t="s">
+      <c r="H35" t="s">
         <v>139</v>
       </c>
       <c r="I35" t="str">
@@ -7272,7 +7313,7 @@
       <c r="G36" t="s">
         <v>142</v>
       </c>
-      <c r="H36" s="8" t="s">
+      <c r="H36" t="s">
         <v>143</v>
       </c>
       <c r="I36" t="str">
@@ -7302,7 +7343,7 @@
       <c r="G37" t="s">
         <v>145</v>
       </c>
-      <c r="H37" s="8" t="s">
+      <c r="H37" t="s">
         <v>146</v>
       </c>
       <c r="I37" t="str">
@@ -7332,7 +7373,7 @@
       <c r="G38" t="s">
         <v>148</v>
       </c>
-      <c r="H38" s="8" t="s">
+      <c r="H38" t="s">
         <v>149</v>
       </c>
       <c r="I38" t="str">
@@ -7362,7 +7403,7 @@
       <c r="G39" t="s">
         <v>151</v>
       </c>
-      <c r="H39" s="8" t="s">
+      <c r="H39" t="s">
         <v>152</v>
       </c>
       <c r="I39" t="str">
@@ -7392,7 +7433,7 @@
       <c r="G40" t="s">
         <v>154</v>
       </c>
-      <c r="H40" s="8" t="s">
+      <c r="H40" t="s">
         <v>155</v>
       </c>
       <c r="I40" t="str">
@@ -7419,7 +7460,7 @@
         <f>VLOOKUP($A41,統計!$A:$G,7,)</f>
         <v>26</v>
       </c>
-      <c r="H41" s="8" t="s">
+      <c r="H41" t="s">
         <v>157</v>
       </c>
       <c r="I41" t="str">
@@ -7449,7 +7490,7 @@
       <c r="F42" t="s">
         <v>159</v>
       </c>
-      <c r="H42" s="8" t="s">
+      <c r="H42" t="s">
         <v>160</v>
       </c>
       <c r="I42" t="str">
@@ -7479,7 +7520,7 @@
       <c r="F43" t="s">
         <v>162</v>
       </c>
-      <c r="H43" s="8" t="s">
+      <c r="H43" t="s">
         <v>163</v>
       </c>
       <c r="I43" t="str">
@@ -7509,7 +7550,7 @@
       <c r="G44" t="s">
         <v>165</v>
       </c>
-      <c r="H44" s="8" t="s">
+      <c r="H44" t="s">
         <v>166</v>
       </c>
       <c r="I44" t="str">
@@ -7539,7 +7580,7 @@
       <c r="G45" t="s">
         <v>168</v>
       </c>
-      <c r="H45" s="8" t="s">
+      <c r="H45" t="s">
         <v>169</v>
       </c>
       <c r="I45" t="str">
@@ -7572,7 +7613,7 @@
       <c r="G46" t="s">
         <v>172</v>
       </c>
-      <c r="H46" s="8" t="s">
+      <c r="H46" t="s">
         <v>173</v>
       </c>
       <c r="I46" t="str">
@@ -7602,7 +7643,7 @@
       <c r="F47" t="s">
         <v>175</v>
       </c>
-      <c r="H47" s="8" t="s">
+      <c r="H47" t="s">
         <v>176</v>
       </c>
       <c r="I47" t="str">
@@ -7635,7 +7676,7 @@
       <c r="G48" t="s">
         <v>179</v>
       </c>
-      <c r="H48" s="8" t="s">
+      <c r="H48" t="s">
         <v>180</v>
       </c>
       <c r="I48" t="str">
@@ -7665,7 +7706,7 @@
       <c r="G49" t="s">
         <v>182</v>
       </c>
-      <c r="H49" s="8" t="s">
+      <c r="H49" t="s">
         <v>183</v>
       </c>
       <c r="I49" t="str">
@@ -7692,7 +7733,7 @@
         <f>VLOOKUP($A50,統計!$A:$G,7,)</f>
         <v>115</v>
       </c>
-      <c r="H50" s="10" t="s">
+      <c r="H50" s="8" t="s">
         <v>185</v>
       </c>
       <c r="I50" t="str">
@@ -7725,7 +7766,7 @@
       <c r="G51" t="s">
         <v>188</v>
       </c>
-      <c r="H51" s="10" t="s">
+      <c r="H51" s="8" t="s">
         <v>189</v>
       </c>
       <c r="I51" t="str">
@@ -7755,7 +7796,7 @@
       <c r="G52" t="s">
         <v>191</v>
       </c>
-      <c r="H52" s="8" t="s">
+      <c r="H52" t="s">
         <v>192</v>
       </c>
       <c r="I52" t="str">
@@ -7782,7 +7823,7 @@
         <f>VLOOKUP($A53,統計!$A:$G,7,)</f>
         <v>145</v>
       </c>
-      <c r="H53" s="8" t="s">
+      <c r="H53" t="s">
         <v>194</v>
       </c>
       <c r="I53" t="str">
@@ -7812,7 +7853,7 @@
       <c r="F54" t="s">
         <v>196</v>
       </c>
-      <c r="H54" s="8" t="s">
+      <c r="H54" t="s">
         <v>197</v>
       </c>
       <c r="I54" t="str">
@@ -7845,7 +7886,7 @@
       <c r="G55" t="s">
         <v>200</v>
       </c>
-      <c r="H55" s="8" t="s">
+      <c r="H55" t="s">
         <v>201</v>
       </c>
       <c r="I55" t="str">
@@ -7872,7 +7913,7 @@
         <f>VLOOKUP($A56,統計!$A:$G,7,)</f>
         <v>166</v>
       </c>
-      <c r="H56" s="8" t="s">
+      <c r="H56" t="s">
         <v>203</v>
       </c>
       <c r="I56" t="str">
@@ -7902,7 +7943,7 @@
       <c r="F57" t="s">
         <v>205</v>
       </c>
-      <c r="H57" s="8" t="s">
+      <c r="H57" t="s">
         <v>206</v>
       </c>
       <c r="I57" t="str">
@@ -7929,7 +7970,7 @@
         <f>VLOOKUP($A58,統計!$A:$G,7,)</f>
         <v>180</v>
       </c>
-      <c r="H58" s="8" t="s">
+      <c r="H58" t="s">
         <v>208</v>
       </c>
       <c r="I58" t="str">
@@ -7959,7 +8000,7 @@
       <c r="F59" t="s">
         <v>210</v>
       </c>
-      <c r="H59" s="8" t="s">
+      <c r="H59" t="s">
         <v>211</v>
       </c>
       <c r="I59" t="str">
@@ -7989,7 +8030,7 @@
       <c r="G60" t="s">
         <v>213</v>
       </c>
-      <c r="H60" s="8" t="s">
+      <c r="H60" t="s">
         <v>214</v>
       </c>
       <c r="I60" t="str">
@@ -8019,7 +8060,7 @@
       <c r="F61" t="s">
         <v>216</v>
       </c>
-      <c r="H61" s="8" t="s">
+      <c r="H61" t="s">
         <v>217</v>
       </c>
       <c r="I61" t="str">
@@ -8049,7 +8090,7 @@
       <c r="F62" t="s">
         <v>219</v>
       </c>
-      <c r="H62" s="8" t="s">
+      <c r="H62" t="s">
         <v>220</v>
       </c>
       <c r="I62" t="str">
@@ -8082,7 +8123,7 @@
       <c r="G63" t="s">
         <v>223</v>
       </c>
-      <c r="H63" s="11" t="s">
+      <c r="H63" t="s">
         <v>224</v>
       </c>
       <c r="I63" t="str">
@@ -8109,7 +8150,7 @@
         <f>VLOOKUP($A64,統計!$A:$G,7,)</f>
         <v>200</v>
       </c>
-      <c r="H64" s="11" t="s">
+      <c r="H64" t="s">
         <v>226</v>
       </c>
       <c r="I64" t="str">
@@ -8139,7 +8180,7 @@
       <c r="F65" t="s">
         <v>228</v>
       </c>
-      <c r="H65" s="8" t="s">
+      <c r="H65" t="s">
         <v>229</v>
       </c>
       <c r="I65" t="str">
@@ -8166,7 +8207,7 @@
         <f>VLOOKUP($A66,統計!$A:$G,7,)</f>
         <v>208</v>
       </c>
-      <c r="H66" s="8" t="s">
+      <c r="H66" t="s">
         <v>231</v>
       </c>
       <c r="I66" t="str">
@@ -8193,7 +8234,7 @@
         <f>VLOOKUP($A67,統計!$A:$G,7,)</f>
         <v>213</v>
       </c>
-      <c r="H67" s="8" t="s">
+      <c r="H67" t="s">
         <v>233</v>
       </c>
       <c r="I67" t="str">
@@ -8223,7 +8264,7 @@
       <c r="G68" t="s">
         <v>235</v>
       </c>
-      <c r="H68" s="8" t="s">
+      <c r="H68" t="s">
         <v>236</v>
       </c>
       <c r="I68" t="str">
@@ -8250,7 +8291,7 @@
         <f>VLOOKUP($A69,統計!$A:$G,7,)</f>
         <v>219</v>
       </c>
-      <c r="H69" s="8" t="s">
+      <c r="H69" t="s">
         <v>238</v>
       </c>
       <c r="I69" t="str">
@@ -8277,7 +8318,7 @@
         <f>VLOOKUP($A70,統計!$A:$G,7,)</f>
         <v>222</v>
       </c>
-      <c r="H70" s="8" t="s">
+      <c r="H70" t="s">
         <v>240</v>
       </c>
       <c r="I70" t="str">
@@ -8307,7 +8348,7 @@
       <c r="G71" t="s">
         <v>242</v>
       </c>
-      <c r="H71" s="8" t="s">
+      <c r="H71" t="s">
         <v>243</v>
       </c>
       <c r="I71" t="str">
@@ -8334,7 +8375,7 @@
         <f>VLOOKUP($A72,統計!$A:$G,7,)</f>
         <v>230</v>
       </c>
-      <c r="H72" s="8" t="s">
+      <c r="H72" t="s">
         <v>245</v>
       </c>
       <c r="I72" t="str">
@@ -8364,7 +8405,7 @@
       <c r="G73" t="s">
         <v>247</v>
       </c>
-      <c r="H73" s="8" t="s">
+      <c r="H73" t="s">
         <v>248</v>
       </c>
       <c r="I73" t="str">
@@ -8394,7 +8435,7 @@
       <c r="G74" t="s">
         <v>250</v>
       </c>
-      <c r="H74" s="8" t="s">
+      <c r="H74" t="s">
         <v>251</v>
       </c>
       <c r="I74" t="str">
@@ -8424,7 +8465,7 @@
       <c r="F75" t="s">
         <v>253</v>
       </c>
-      <c r="H75" s="8" t="s">
+      <c r="H75" t="s">
         <v>254</v>
       </c>
       <c r="I75" t="str">
@@ -8457,7 +8498,7 @@
       <c r="G76" t="s">
         <v>257</v>
       </c>
-      <c r="H76" s="8" t="s">
+      <c r="H76" t="s">
         <v>258</v>
       </c>
       <c r="I76" t="str">
@@ -8487,7 +8528,7 @@
       <c r="F77" t="s">
         <v>260</v>
       </c>
-      <c r="H77" s="8" t="s">
+      <c r="H77" t="s">
         <v>261</v>
       </c>
       <c r="I77" t="str">
@@ -8517,7 +8558,7 @@
       <c r="F78" t="s">
         <v>263</v>
       </c>
-      <c r="H78" s="8" t="s">
+      <c r="H78" t="s">
         <v>264</v>
       </c>
       <c r="I78" t="str">
@@ -8715,7 +8756,7 @@
         <f>VLOOKUP($A85,統計!$A:$G,7,)</f>
         <v>302</v>
       </c>
-      <c r="H85" s="8" t="s">
+      <c r="H85" t="s">
         <v>514</v>
       </c>
       <c r="I85" t="str">
@@ -8745,7 +8786,7 @@
       <c r="G86" t="s">
         <v>515</v>
       </c>
-      <c r="H86" s="8" t="s">
+      <c r="H86" t="s">
         <v>516</v>
       </c>
       <c r="I86" t="str">
@@ -8757,24 +8798,27 @@
       <c r="A87">
         <v>708</v>
       </c>
-      <c r="B87" t="e">
+      <c r="B87" t="str">
         <f>VLOOKUP($A87,統計!$A:$G,2,)</f>
-        <v>#N/A</v>
+        <v>卷86</v>
       </c>
       <c r="C87" t="s">
         <v>282</v>
       </c>
-      <c r="D87" t="e">
+      <c r="D87">
         <f>VLOOKUP($A87,統計!$A:$G,6,)</f>
-        <v>#N/A</v>
-      </c>
-      <c r="E87" t="e">
+        <v>305</v>
+      </c>
+      <c r="E87">
         <f>VLOOKUP($A87,統計!$A:$G,7,)</f>
-        <v>#N/A</v>
-      </c>
-      <c r="I87" t="e">
+        <v>308</v>
+      </c>
+      <c r="H87" t="s">
+        <v>517</v>
+      </c>
+      <c r="I87" t="str">
         <f t="shared" si="1"/>
-        <v>#N/A</v>
+        <v>708|[卷86](5_筆記/资治通鉴86.html)|晉紀八|305|308|||晉惠帝16年至18年、晉懷帝至2年</v>
       </c>
     </row>
     <row r="88" spans="1:9" x14ac:dyDescent="0.15">
@@ -13772,7 +13816,7 @@
   </sheetData>
   <phoneticPr fontId="4" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.51180555555555496" footer="0.51180555555555496"/>
-  <pageSetup paperSize="9" firstPageNumber="0" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
+  <pageSetup paperSize="9" firstPageNumber="0" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId1"/>
 </worksheet>
 </file>
 
@@ -13912,7 +13956,7 @@
       </c>
     </row>
     <row r="8" spans="2:17" x14ac:dyDescent="0.15">
-      <c r="G8" s="12">
+      <c r="G8" s="9">
         <f>C2/C7</f>
         <v>6.741573033707865E-2</v>
       </c>

--- a/5_筆記/閱讀數據.xlsx
+++ b/5_筆記/閱讀數據.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\self\study\zizhitongjian\5_筆記\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3C9DC5E1-4EE8-4241-94DB-8594506179B7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D4B9EE8A-E235-4B68-835B-DC0C3B5904A1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-24120" yWindow="2415" windowWidth="24240" windowHeight="13740" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="統計" sheetId="1" r:id="rId1"/>
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="524" uniqueCount="518">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="525" uniqueCount="519">
   <si>
     <t>索引號</t>
   </si>
@@ -1584,6 +1584,9 @@
   <si>
     <t>晉惠帝16年至18年、晉懷帝至2年</t>
     <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>晉懷帝3年至5年</t>
   </si>
 </sst>
 </file>
@@ -1887,7 +1890,7 @@
             <c:strRef>
               <c:f>統計!$B$2:$B$115</c:f>
               <c:strCache>
-                <c:ptCount val="86"/>
+                <c:ptCount val="87"/>
                 <c:pt idx="0">
                   <c:v>卷1</c:v>
                 </c:pt>
@@ -2145,6 +2148,9 @@
                 </c:pt>
                 <c:pt idx="85">
                   <c:v>卷86</c:v>
+                </c:pt>
+                <c:pt idx="86">
+                  <c:v>卷87</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
@@ -2412,6 +2418,9 @@
                 </c:pt>
                 <c:pt idx="85">
                   <c:v>3.75</c:v>
+                </c:pt>
+                <c:pt idx="86">
+                  <c:v>5.333333333333333</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -2966,7 +2975,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:R87"/>
+  <dimension ref="A1:R88"/>
   <sheetFormatPr defaultColWidth="8.625" defaultRowHeight="13.5" x14ac:dyDescent="0.15"/>
   <cols>
     <col min="1" max="1" width="7.75" customWidth="1"/>
@@ -3081,19 +3090,19 @@
       </c>
       <c r="O2">
         <f t="shared" ref="O2:O8" si="5">L2*$L$10</f>
-        <v>624.65116279069775</v>
+        <v>629.97701149425279</v>
       </c>
       <c r="P2" s="1">
         <f t="shared" ref="P2:P8" si="6">$C$2+O2</f>
-        <v>44643.651162790695</v>
+        <v>44648.977011494251</v>
       </c>
       <c r="Q2">
         <f t="shared" ref="Q2:Q8" si="7">(M2-$F$2)*$L$11</f>
-        <v>598.2649505954995</v>
+        <v>626.99828192442305</v>
       </c>
       <c r="R2" s="1">
         <f t="shared" ref="R2:R8" si="8">$C$2+Q2</f>
-        <v>44617.264950595498</v>
+        <v>44645.998281924425</v>
       </c>
     </row>
     <row r="3" spans="1:18" x14ac:dyDescent="0.15">
@@ -3144,19 +3153,19 @@
       </c>
       <c r="O3">
         <f t="shared" si="5"/>
-        <v>716.51162790697674</v>
+        <v>722.62068965517233</v>
       </c>
       <c r="P3" s="1">
         <f t="shared" si="6"/>
-        <v>44735.511627906977</v>
+        <v>44741.620689655174</v>
       </c>
       <c r="Q3">
         <f t="shared" si="7"/>
-        <v>655.88276285188795</v>
+        <v>687.3833492044638</v>
       </c>
       <c r="R3" s="1">
         <f t="shared" si="8"/>
-        <v>44674.882762851885</v>
+        <v>44706.383349204465</v>
       </c>
     </row>
     <row r="4" spans="1:18" x14ac:dyDescent="0.15">
@@ -3207,19 +3216,19 @@
       </c>
       <c r="O4">
         <f t="shared" si="5"/>
-        <v>1083.953488372093</v>
+        <v>1093.1954022988505</v>
       </c>
       <c r="P4" s="1">
         <f t="shared" si="6"/>
-        <v>45102.953488372092</v>
+        <v>45112.19540229885</v>
       </c>
       <c r="Q4">
         <f t="shared" si="7"/>
-        <v>790.32432478346084</v>
+        <v>828.2818395245589</v>
       </c>
       <c r="R4" s="1">
         <f t="shared" si="8"/>
-        <v>44809.324324783462</v>
+        <v>44847.281839524556</v>
       </c>
     </row>
     <row r="5" spans="1:18" x14ac:dyDescent="0.15">
@@ -3270,19 +3279,19 @@
       </c>
       <c r="O5">
         <f t="shared" si="5"/>
-        <v>1616.7441860465117</v>
+        <v>1630.5287356321837</v>
       </c>
       <c r="P5" s="1">
         <f t="shared" si="6"/>
-        <v>45635.744186046511</v>
+        <v>45649.528735632186</v>
       </c>
       <c r="Q5">
         <f t="shared" si="7"/>
-        <v>952.61449597228818</v>
+        <v>998.36644569667362</v>
       </c>
       <c r="R5" s="1">
         <f t="shared" si="8"/>
-        <v>44971.614495972288</v>
+        <v>45017.366445696673</v>
       </c>
     </row>
     <row r="6" spans="1:18" x14ac:dyDescent="0.15">
@@ -3333,19 +3342,19 @@
       </c>
       <c r="O6">
         <f t="shared" si="5"/>
-        <v>2434.3023255813955</v>
+        <v>2455.0574712643675</v>
       </c>
       <c r="P6" s="1">
         <f t="shared" si="6"/>
-        <v>46453.302325581397</v>
+        <v>46474.057471264365</v>
       </c>
       <c r="Q6">
         <f t="shared" si="7"/>
-        <v>1257.9889009311466</v>
+        <v>1318.4073022808896</v>
       </c>
       <c r="R6" s="1">
         <f t="shared" si="8"/>
-        <v>45276.988900931145</v>
+        <v>45337.407302280888</v>
       </c>
     </row>
     <row r="7" spans="1:18" x14ac:dyDescent="0.15">
@@ -3396,19 +3405,19 @@
       </c>
       <c r="O7">
         <f t="shared" si="5"/>
-        <v>2700.6976744186049</v>
+        <v>2723.7241379310344</v>
       </c>
       <c r="P7" s="1">
         <f t="shared" si="6"/>
-        <v>46719.697674418603</v>
+        <v>46742.724137931036</v>
       </c>
       <c r="Q7">
         <f t="shared" si="7"/>
-        <v>1307.9243382200166</v>
+        <v>1370.7410272569248</v>
       </c>
       <c r="R7" s="1">
         <f t="shared" si="8"/>
-        <v>45326.924338220015</v>
+        <v>45389.741027256925</v>
       </c>
     </row>
     <row r="8" spans="1:18" x14ac:dyDescent="0.15">
@@ -3459,19 +3468,19 @@
       </c>
       <c r="O8">
         <f t="shared" si="5"/>
-        <v>2700.6976744186049</v>
+        <v>2723.7241379310344</v>
       </c>
       <c r="P8" s="1">
         <f t="shared" si="6"/>
-        <v>46719.697674418603</v>
+        <v>46742.724137931036</v>
       </c>
       <c r="Q8">
         <f t="shared" si="7"/>
-        <v>1307.9243382200166</v>
+        <v>1370.7410272569248</v>
       </c>
       <c r="R8" s="1">
         <f t="shared" si="8"/>
-        <v>45326.924338220015</v>
+        <v>45389.741027256925</v>
       </c>
     </row>
     <row r="9" spans="1:18" x14ac:dyDescent="0.15">
@@ -3546,7 +3555,7 @@
       </c>
       <c r="L10">
         <f>AVERAGE(E:E)</f>
-        <v>9.1860465116279073</v>
+        <v>9.2643678160919531</v>
       </c>
     </row>
     <row r="11" spans="1:18" x14ac:dyDescent="0.15">
@@ -3587,7 +3596,7 @@
       </c>
       <c r="L11">
         <f>AVEDEV(I:I)</f>
-        <v>0.96029687093980665</v>
+        <v>1.006417788000679</v>
       </c>
     </row>
     <row r="12" spans="1:18" x14ac:dyDescent="0.15">
@@ -5450,7 +5459,7 @@
         <v>526</v>
       </c>
       <c r="B66" t="str">
-        <f t="shared" ref="B66:B87" si="16">"卷"&amp;ROW(B65)</f>
+        <f t="shared" ref="B66:B88" si="16">"卷"&amp;ROW(B65)</f>
         <v>卷65</v>
       </c>
       <c r="C66" s="1">
@@ -6204,6 +6213,41 @@
       <c r="I87">
         <f t="shared" ref="I87" si="29">E87/H87</f>
         <v>3.75</v>
+      </c>
+    </row>
+    <row r="88" spans="1:9" x14ac:dyDescent="0.15">
+      <c r="A88">
+        <v>709</v>
+      </c>
+      <c r="B88" t="str">
+        <f t="shared" si="16"/>
+        <v>卷87</v>
+      </c>
+      <c r="C88" s="1">
+        <f t="shared" ref="C88" si="30">D87+1</f>
+        <v>44917</v>
+      </c>
+      <c r="D88" s="1">
+        <v>44932</v>
+      </c>
+      <c r="E88">
+        <f t="shared" ref="E88" si="31">D88-C88+1</f>
+        <v>16</v>
+      </c>
+      <c r="F88">
+        <f t="shared" ref="F88" si="32">G87+1</f>
+        <v>309</v>
+      </c>
+      <c r="G88">
+        <v>311</v>
+      </c>
+      <c r="H88">
+        <f t="shared" ref="H88" si="33">IF(F88*G88&lt;0,ABS(F88)+ABS(G88),G88-F88+1)</f>
+        <v>3</v>
+      </c>
+      <c r="I88">
+        <f t="shared" ref="I88" si="34">E88/H88</f>
+        <v>5.333333333333333</v>
       </c>
     </row>
   </sheetData>
@@ -8825,24 +8869,27 @@
       <c r="A88">
         <v>709</v>
       </c>
-      <c r="B88" t="e">
+      <c r="B88" t="str">
         <f>VLOOKUP($A88,統計!$A:$G,2,)</f>
-        <v>#N/A</v>
+        <v>卷87</v>
       </c>
       <c r="C88" t="s">
         <v>283</v>
       </c>
-      <c r="D88" t="e">
+      <c r="D88">
         <f>VLOOKUP($A88,統計!$A:$G,6,)</f>
-        <v>#N/A</v>
-      </c>
-      <c r="E88" t="e">
+        <v>309</v>
+      </c>
+      <c r="E88">
         <f>VLOOKUP($A88,統計!$A:$G,7,)</f>
-        <v>#N/A</v>
-      </c>
-      <c r="I88" t="e">
+        <v>311</v>
+      </c>
+      <c r="H88" t="s">
+        <v>518</v>
+      </c>
+      <c r="I88" t="str">
         <f t="shared" si="1"/>
-        <v>#N/A</v>
+        <v>709|[卷87](5_筆記/资治通鉴87.html)|晉紀九|309|311|||晉懷帝3年至5年</v>
       </c>
     </row>
     <row r="89" spans="1:9" x14ac:dyDescent="0.15">

--- a/5_筆記/閱讀數據.xlsx
+++ b/5_筆記/閱讀數據.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\self\study\zizhitongjian\5_筆記\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D4B9EE8A-E235-4B68-835B-DC0C3B5904A1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BD5564E7-3029-43DD-BC56-319FC94D993A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-24120" yWindow="2415" windowWidth="24240" windowHeight="13740" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="統計" sheetId="1" r:id="rId1"/>
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="525" uniqueCount="519">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="526" uniqueCount="520">
   <si>
     <t>索引號</t>
   </si>
@@ -1587,6 +1587,10 @@
   </si>
   <si>
     <t>晉懷帝3年至5年</t>
+  </si>
+  <si>
+    <t>晉懷帝6年至7年、晉愍帝元年</t>
+    <phoneticPr fontId="4" type="noConversion"/>
   </si>
 </sst>
 </file>
@@ -1890,7 +1894,7 @@
             <c:strRef>
               <c:f>統計!$B$2:$B$115</c:f>
               <c:strCache>
-                <c:ptCount val="87"/>
+                <c:ptCount val="88"/>
                 <c:pt idx="0">
                   <c:v>卷1</c:v>
                 </c:pt>
@@ -2151,6 +2155,9 @@
                 </c:pt>
                 <c:pt idx="86">
                   <c:v>卷87</c:v>
+                </c:pt>
+                <c:pt idx="87">
+                  <c:v>卷88</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
@@ -2421,6 +2428,9 @@
                 </c:pt>
                 <c:pt idx="86">
                   <c:v>5.333333333333333</c:v>
+                </c:pt>
+                <c:pt idx="87">
+                  <c:v>5.5</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -2975,7 +2985,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:R88"/>
+  <dimension ref="A1:R89"/>
   <sheetFormatPr defaultColWidth="8.625" defaultRowHeight="13.5" x14ac:dyDescent="0.15"/>
   <cols>
     <col min="1" max="1" width="7.75" customWidth="1"/>
@@ -3090,19 +3100,19 @@
       </c>
       <c r="O2">
         <f t="shared" ref="O2:O8" si="5">L2*$L$10</f>
-        <v>629.97701149425279</v>
+        <v>631.31818181818176</v>
       </c>
       <c r="P2" s="1">
         <f t="shared" ref="P2:P8" si="6">$C$2+O2</f>
-        <v>44648.977011494251</v>
+        <v>44650.318181818184</v>
       </c>
       <c r="Q2">
         <f t="shared" ref="Q2:Q8" si="7">(M2-$F$2)*$L$11</f>
-        <v>626.99828192442305</v>
+        <v>655.89115821530072</v>
       </c>
       <c r="R2" s="1">
         <f t="shared" ref="R2:R8" si="8">$C$2+Q2</f>
-        <v>44645.998281924425</v>
+        <v>44674.891158215301</v>
       </c>
     </row>
     <row r="3" spans="1:18" x14ac:dyDescent="0.15">
@@ -3153,19 +3163,19 @@
       </c>
       <c r="O3">
         <f t="shared" si="5"/>
-        <v>722.62068965517233</v>
+        <v>724.15909090909088</v>
       </c>
       <c r="P3" s="1">
         <f t="shared" si="6"/>
-        <v>44741.620689655174</v>
+        <v>44743.159090909088</v>
       </c>
       <c r="Q3">
         <f t="shared" si="7"/>
-        <v>687.3833492044638</v>
+        <v>719.05884600489628</v>
       </c>
       <c r="R3" s="1">
         <f t="shared" si="8"/>
-        <v>44706.383349204465</v>
+        <v>44738.058846004897</v>
       </c>
     </row>
     <row r="4" spans="1:18" x14ac:dyDescent="0.15">
@@ -3216,19 +3226,19 @@
       </c>
       <c r="O4">
         <f t="shared" si="5"/>
-        <v>1093.1954022988505</v>
+        <v>1095.5227272727273</v>
       </c>
       <c r="P4" s="1">
         <f t="shared" si="6"/>
-        <v>45112.19540229885</v>
+        <v>45114.522727272728</v>
       </c>
       <c r="Q4">
         <f t="shared" si="7"/>
-        <v>828.2818395245589</v>
+        <v>866.45011751395259</v>
       </c>
       <c r="R4" s="1">
         <f t="shared" si="8"/>
-        <v>44847.281839524556</v>
+        <v>44885.450117513952</v>
       </c>
     </row>
     <row r="5" spans="1:18" x14ac:dyDescent="0.15">
@@ -3279,19 +3289,19 @@
       </c>
       <c r="O5">
         <f t="shared" si="5"/>
-        <v>1630.5287356321837</v>
+        <v>1633.9999999999998</v>
       </c>
       <c r="P5" s="1">
         <f t="shared" si="6"/>
-        <v>45649.528735632186</v>
+        <v>45653</v>
       </c>
       <c r="Q5">
         <f t="shared" si="7"/>
-        <v>998.36644569667362</v>
+        <v>1044.3724381213135</v>
       </c>
       <c r="R5" s="1">
         <f t="shared" si="8"/>
-        <v>45017.366445696673</v>
+        <v>45063.372438121311</v>
       </c>
     </row>
     <row r="6" spans="1:18" x14ac:dyDescent="0.15">
@@ -3342,19 +3352,19 @@
       </c>
       <c r="O6">
         <f t="shared" si="5"/>
-        <v>2455.0574712643675</v>
+        <v>2460.2840909090905</v>
       </c>
       <c r="P6" s="1">
         <f t="shared" si="6"/>
-        <v>46474.057471264365</v>
+        <v>46479.284090909088</v>
       </c>
       <c r="Q6">
         <f t="shared" si="7"/>
-        <v>1318.4073022808896</v>
+        <v>1379.16118340617</v>
       </c>
       <c r="R6" s="1">
         <f t="shared" si="8"/>
-        <v>45337.407302280888</v>
+        <v>45398.16118340617</v>
       </c>
     </row>
     <row r="7" spans="1:18" x14ac:dyDescent="0.15">
@@ -3405,19 +3415,19 @@
       </c>
       <c r="O7">
         <f t="shared" si="5"/>
-        <v>2723.7241379310344</v>
+        <v>2729.522727272727</v>
       </c>
       <c r="P7" s="1">
         <f t="shared" si="6"/>
-        <v>46742.724137931036</v>
+        <v>46748.522727272728</v>
       </c>
       <c r="Q7">
         <f t="shared" si="7"/>
-        <v>1370.7410272569248</v>
+        <v>1433.9065128238196</v>
       </c>
       <c r="R7" s="1">
         <f t="shared" si="8"/>
-        <v>45389.741027256925</v>
+        <v>45452.906512823822</v>
       </c>
     </row>
     <row r="8" spans="1:18" x14ac:dyDescent="0.15">
@@ -3468,19 +3478,19 @@
       </c>
       <c r="O8">
         <f t="shared" si="5"/>
-        <v>2723.7241379310344</v>
+        <v>2729.522727272727</v>
       </c>
       <c r="P8" s="1">
         <f t="shared" si="6"/>
-        <v>46742.724137931036</v>
+        <v>46748.522727272728</v>
       </c>
       <c r="Q8">
         <f t="shared" si="7"/>
-        <v>1370.7410272569248</v>
+        <v>1433.9065128238196</v>
       </c>
       <c r="R8" s="1">
         <f t="shared" si="8"/>
-        <v>45389.741027256925</v>
+        <v>45452.906512823822</v>
       </c>
     </row>
     <row r="9" spans="1:18" x14ac:dyDescent="0.15">
@@ -3555,7 +3565,7 @@
       </c>
       <c r="L10">
         <f>AVERAGE(E:E)</f>
-        <v>9.2643678160919531</v>
+        <v>9.2840909090909083</v>
       </c>
     </row>
     <row r="11" spans="1:18" x14ac:dyDescent="0.15">
@@ -3596,7 +3606,7 @@
       </c>
       <c r="L11">
         <f>AVEDEV(I:I)</f>
-        <v>1.006417788000679</v>
+        <v>1.0527947964932596</v>
       </c>
     </row>
     <row r="12" spans="1:18" x14ac:dyDescent="0.15">
@@ -5459,7 +5469,7 @@
         <v>526</v>
       </c>
       <c r="B66" t="str">
-        <f t="shared" ref="B66:B88" si="16">"卷"&amp;ROW(B65)</f>
+        <f t="shared" ref="B66:B89" si="16">"卷"&amp;ROW(B65)</f>
         <v>卷65</v>
       </c>
       <c r="C66" s="1">
@@ -6248,6 +6258,41 @@
       <c r="I88">
         <f t="shared" ref="I88" si="34">E88/H88</f>
         <v>5.333333333333333</v>
+      </c>
+    </row>
+    <row r="89" spans="1:9" x14ac:dyDescent="0.15">
+      <c r="A89">
+        <v>710</v>
+      </c>
+      <c r="B89" t="str">
+        <f t="shared" si="16"/>
+        <v>卷88</v>
+      </c>
+      <c r="C89" s="1">
+        <f t="shared" ref="C89" si="35">D88+1</f>
+        <v>44933</v>
+      </c>
+      <c r="D89" s="1">
+        <v>44943</v>
+      </c>
+      <c r="E89">
+        <f t="shared" ref="E89" si="36">D89-C89+1</f>
+        <v>11</v>
+      </c>
+      <c r="F89">
+        <f t="shared" ref="F89" si="37">G88+1</f>
+        <v>312</v>
+      </c>
+      <c r="G89">
+        <v>313</v>
+      </c>
+      <c r="H89">
+        <f t="shared" ref="H89" si="38">IF(F89*G89&lt;0,ABS(F89)+ABS(G89),G89-F89+1)</f>
+        <v>2</v>
+      </c>
+      <c r="I89">
+        <f t="shared" ref="I89" si="39">E89/H89</f>
+        <v>5.5</v>
       </c>
     </row>
   </sheetData>
@@ -8896,24 +8941,27 @@
       <c r="A89">
         <v>710</v>
       </c>
-      <c r="B89" t="e">
+      <c r="B89" t="str">
         <f>VLOOKUP($A89,統計!$A:$G,2,)</f>
-        <v>#N/A</v>
+        <v>卷88</v>
       </c>
       <c r="C89" t="s">
         <v>284</v>
       </c>
-      <c r="D89" t="e">
+      <c r="D89">
         <f>VLOOKUP($A89,統計!$A:$G,6,)</f>
-        <v>#N/A</v>
-      </c>
-      <c r="E89" t="e">
+        <v>312</v>
+      </c>
+      <c r="E89">
         <f>VLOOKUP($A89,統計!$A:$G,7,)</f>
-        <v>#N/A</v>
-      </c>
-      <c r="I89" t="e">
+        <v>313</v>
+      </c>
+      <c r="H89" t="s">
+        <v>519</v>
+      </c>
+      <c r="I89" t="str">
         <f t="shared" si="1"/>
-        <v>#N/A</v>
+        <v>710|[卷88](5_筆記/资治通鉴88.html)|晉紀十|312|313|||晉懷帝6年至7年、晉愍帝元年</v>
       </c>
     </row>
     <row r="90" spans="1:9" x14ac:dyDescent="0.15">

--- a/5_筆記/閱讀數據.xlsx
+++ b/5_筆記/閱讀數據.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="25831"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="25928"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\self\study\zizhitongjian\5_筆記\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BD5564E7-3029-43DD-BC56-319FC94D993A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3799E1F8-8B34-4E0B-B1F5-1F86562079F8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-24120" yWindow="2415" windowWidth="24240" windowHeight="13740" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="統計" sheetId="1" r:id="rId1"/>
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="526" uniqueCount="520">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="527" uniqueCount="521">
   <si>
     <t>索引號</t>
   </si>
@@ -1590,6 +1590,10 @@
   </si>
   <si>
     <t>晉懷帝6年至7年、晉愍帝元年</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>晉愍帝2年至4年</t>
     <phoneticPr fontId="4" type="noConversion"/>
   </si>
 </sst>
@@ -1894,7 +1898,7 @@
             <c:strRef>
               <c:f>統計!$B$2:$B$115</c:f>
               <c:strCache>
-                <c:ptCount val="88"/>
+                <c:ptCount val="89"/>
                 <c:pt idx="0">
                   <c:v>卷1</c:v>
                 </c:pt>
@@ -2158,6 +2162,9 @@
                 </c:pt>
                 <c:pt idx="87">
                   <c:v>卷88</c:v>
+                </c:pt>
+                <c:pt idx="88">
+                  <c:v>卷89</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
@@ -2431,6 +2438,9 @@
                 </c:pt>
                 <c:pt idx="87">
                   <c:v>5.5</c:v>
+                </c:pt>
+                <c:pt idx="88">
+                  <c:v>3.6666666666666665</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -2977,7 +2987,7 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme 2013 - 2022" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
@@ -2985,7 +2995,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:R89"/>
+  <dimension ref="A1:R90"/>
   <sheetFormatPr defaultColWidth="8.625" defaultRowHeight="13.5" x14ac:dyDescent="0.15"/>
   <cols>
     <col min="1" max="1" width="7.75" customWidth="1"/>
@@ -3100,19 +3110,19 @@
       </c>
       <c r="O2">
         <f t="shared" ref="O2:O8" si="5">L2*$L$10</f>
-        <v>631.31818181818176</v>
+        <v>632.62921348314615</v>
       </c>
       <c r="P2" s="1">
         <f t="shared" ref="P2:P8" si="6">$C$2+O2</f>
-        <v>44650.318181818184</v>
+        <v>44651.629213483146</v>
       </c>
       <c r="Q2">
         <f t="shared" ref="Q2:Q8" si="7">(M2-$F$2)*$L$11</f>
-        <v>655.89115821530072</v>
+        <v>666.59113544177046</v>
       </c>
       <c r="R2" s="1">
         <f t="shared" ref="R2:R8" si="8">$C$2+Q2</f>
-        <v>44674.891158215301</v>
+        <v>44685.591135441769</v>
       </c>
     </row>
     <row r="3" spans="1:18" x14ac:dyDescent="0.15">
@@ -3163,19 +3173,19 @@
       </c>
       <c r="O3">
         <f t="shared" si="5"/>
-        <v>724.15909090909088</v>
+        <v>725.66292134831463</v>
       </c>
       <c r="P3" s="1">
         <f t="shared" si="6"/>
-        <v>44743.159090909088</v>
+        <v>44744.662921348317</v>
       </c>
       <c r="Q3">
         <f t="shared" si="7"/>
-        <v>719.05884600489628</v>
+        <v>730.78931863038395</v>
       </c>
       <c r="R3" s="1">
         <f t="shared" si="8"/>
-        <v>44738.058846004897</v>
+        <v>44749.789318630385</v>
       </c>
     </row>
     <row r="4" spans="1:18" x14ac:dyDescent="0.15">
@@ -3226,19 +3236,19 @@
       </c>
       <c r="O4">
         <f t="shared" si="5"/>
-        <v>1095.5227272727273</v>
+        <v>1097.7977528089889</v>
       </c>
       <c r="P4" s="1">
         <f t="shared" si="6"/>
-        <v>45114.522727272728</v>
+        <v>45116.79775280899</v>
       </c>
       <c r="Q4">
         <f t="shared" si="7"/>
-        <v>866.45011751395259</v>
+        <v>880.58507940381548</v>
       </c>
       <c r="R4" s="1">
         <f t="shared" si="8"/>
-        <v>44885.450117513952</v>
+        <v>44899.585079403812</v>
       </c>
     </row>
     <row r="5" spans="1:18" x14ac:dyDescent="0.15">
@@ -3289,19 +3299,19 @@
       </c>
       <c r="O5">
         <f t="shared" si="5"/>
-        <v>1633.9999999999998</v>
+        <v>1637.3932584269664</v>
       </c>
       <c r="P5" s="1">
         <f t="shared" si="6"/>
-        <v>45653</v>
+        <v>45656.393258426964</v>
       </c>
       <c r="Q5">
         <f t="shared" si="7"/>
-        <v>1044.3724381213135</v>
+        <v>1061.4099620517436</v>
       </c>
       <c r="R5" s="1">
         <f t="shared" si="8"/>
-        <v>45063.372438121311</v>
+        <v>45080.409962051745</v>
       </c>
     </row>
     <row r="6" spans="1:18" x14ac:dyDescent="0.15">
@@ -3352,19 +3362,19 @@
       </c>
       <c r="O6">
         <f t="shared" si="5"/>
-        <v>2460.2840909090905</v>
+        <v>2465.3932584269664</v>
       </c>
       <c r="P6" s="1">
         <f t="shared" si="6"/>
-        <v>46479.284090909088</v>
+        <v>46484.393258426964</v>
       </c>
       <c r="Q6">
         <f t="shared" si="7"/>
-        <v>1379.16118340617</v>
+        <v>1401.6603329513953</v>
       </c>
       <c r="R6" s="1">
         <f t="shared" si="8"/>
-        <v>45398.16118340617</v>
+        <v>45420.660332951396</v>
       </c>
     </row>
     <row r="7" spans="1:18" x14ac:dyDescent="0.15">
@@ -3415,19 +3425,19 @@
       </c>
       <c r="O7">
         <f t="shared" si="5"/>
-        <v>2729.522727272727</v>
+        <v>2735.1910112359551</v>
       </c>
       <c r="P7" s="1">
         <f t="shared" si="6"/>
-        <v>46748.522727272728</v>
+        <v>46754.191011235955</v>
       </c>
       <c r="Q7">
         <f t="shared" si="7"/>
-        <v>1433.9065128238196</v>
+        <v>1457.298758381527</v>
       </c>
       <c r="R7" s="1">
         <f t="shared" si="8"/>
-        <v>45452.906512823822</v>
+        <v>45476.298758381527</v>
       </c>
     </row>
     <row r="8" spans="1:18" x14ac:dyDescent="0.15">
@@ -3478,19 +3488,19 @@
       </c>
       <c r="O8">
         <f t="shared" si="5"/>
-        <v>2729.522727272727</v>
+        <v>2735.1910112359551</v>
       </c>
       <c r="P8" s="1">
         <f t="shared" si="6"/>
-        <v>46748.522727272728</v>
+        <v>46754.191011235955</v>
       </c>
       <c r="Q8">
         <f t="shared" si="7"/>
-        <v>1433.9065128238196</v>
+        <v>1457.298758381527</v>
       </c>
       <c r="R8" s="1">
         <f t="shared" si="8"/>
-        <v>45452.906512823822</v>
+        <v>45476.298758381527</v>
       </c>
     </row>
     <row r="9" spans="1:18" x14ac:dyDescent="0.15">
@@ -3565,7 +3575,7 @@
       </c>
       <c r="L10">
         <f>AVERAGE(E:E)</f>
-        <v>9.2840909090909083</v>
+        <v>9.3033707865168545</v>
       </c>
     </row>
     <row r="11" spans="1:18" x14ac:dyDescent="0.15">
@@ -3606,7 +3616,7 @@
       </c>
       <c r="L11">
         <f>AVEDEV(I:I)</f>
-        <v>1.0527947964932596</v>
+        <v>1.0699697198102254</v>
       </c>
     </row>
     <row r="12" spans="1:18" x14ac:dyDescent="0.15">
@@ -5469,7 +5479,7 @@
         <v>526</v>
       </c>
       <c r="B66" t="str">
-        <f t="shared" ref="B66:B89" si="16">"卷"&amp;ROW(B65)</f>
+        <f t="shared" ref="B66:B90" si="16">"卷"&amp;ROW(B65)</f>
         <v>卷65</v>
       </c>
       <c r="C66" s="1">
@@ -6293,6 +6303,41 @@
       <c r="I89">
         <f t="shared" ref="I89" si="39">E89/H89</f>
         <v>5.5</v>
+      </c>
+    </row>
+    <row r="90" spans="1:9" x14ac:dyDescent="0.15">
+      <c r="A90">
+        <v>711</v>
+      </c>
+      <c r="B90" t="str">
+        <f t="shared" si="16"/>
+        <v>卷89</v>
+      </c>
+      <c r="C90" s="1">
+        <f t="shared" ref="C90" si="40">D89+1</f>
+        <v>44944</v>
+      </c>
+      <c r="D90" s="1">
+        <v>44954</v>
+      </c>
+      <c r="E90">
+        <f t="shared" ref="E90" si="41">D90-C90+1</f>
+        <v>11</v>
+      </c>
+      <c r="F90">
+        <f t="shared" ref="F90" si="42">G89+1</f>
+        <v>314</v>
+      </c>
+      <c r="G90">
+        <v>316</v>
+      </c>
+      <c r="H90">
+        <f t="shared" ref="H90" si="43">IF(F90*G90&lt;0,ABS(F90)+ABS(G90),G90-F90+1)</f>
+        <v>3</v>
+      </c>
+      <c r="I90">
+        <f t="shared" ref="I90" si="44">E90/H90</f>
+        <v>3.6666666666666665</v>
       </c>
     </row>
   </sheetData>
@@ -8968,29 +9013,32 @@
       <c r="A90">
         <v>711</v>
       </c>
-      <c r="B90" t="e">
+      <c r="B90" t="str">
         <f>VLOOKUP($A90,統計!$A:$G,2,)</f>
-        <v>#N/A</v>
+        <v>卷89</v>
       </c>
       <c r="C90" t="s">
         <v>285</v>
       </c>
-      <c r="D90" t="e">
+      <c r="D90">
         <f>VLOOKUP($A90,統計!$A:$G,6,)</f>
-        <v>#N/A</v>
-      </c>
-      <c r="E90" t="e">
+        <v>314</v>
+      </c>
+      <c r="E90">
         <f>VLOOKUP($A90,統計!$A:$G,7,)</f>
-        <v>#N/A</v>
-      </c>
-      <c r="I90" t="e">
+        <v>316</v>
+      </c>
+      <c r="H90" t="s">
+        <v>520</v>
+      </c>
+      <c r="I90" t="str">
         <f t="shared" si="1"/>
-        <v>#N/A</v>
+        <v>711|[卷89](5_筆記/资治通鉴89.html)|晉紀十一|314|316|||晉愍帝2年至4年</v>
       </c>
     </row>
     <row r="91" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A91">
-        <v>712</v>
+        <v>801</v>
       </c>
       <c r="B91" t="e">
         <f>VLOOKUP($A91,統計!$A:$G,2,)</f>
@@ -9014,7 +9062,7 @@
     </row>
     <row r="92" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A92">
-        <v>713</v>
+        <v>802</v>
       </c>
       <c r="B92" t="e">
         <f>VLOOKUP($A92,統計!$A:$G,2,)</f>
@@ -9038,7 +9086,7 @@
     </row>
     <row r="93" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A93">
-        <v>714</v>
+        <v>803</v>
       </c>
       <c r="B93" t="e">
         <f>VLOOKUP($A93,統計!$A:$G,2,)</f>
@@ -9062,7 +9110,7 @@
     </row>
     <row r="94" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A94">
-        <v>715</v>
+        <v>804</v>
       </c>
       <c r="B94" t="e">
         <f>VLOOKUP($A94,統計!$A:$G,2,)</f>
@@ -9086,7 +9134,7 @@
     </row>
     <row r="95" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A95">
-        <v>716</v>
+        <v>805</v>
       </c>
       <c r="B95" t="e">
         <f>VLOOKUP($A95,統計!$A:$G,2,)</f>
@@ -9110,7 +9158,7 @@
     </row>
     <row r="96" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A96">
-        <v>717</v>
+        <v>806</v>
       </c>
       <c r="B96" t="e">
         <f>VLOOKUP($A96,統計!$A:$G,2,)</f>
@@ -9134,7 +9182,7 @@
     </row>
     <row r="97" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A97">
-        <v>718</v>
+        <v>807</v>
       </c>
       <c r="B97" t="e">
         <f>VLOOKUP($A97,統計!$A:$G,2,)</f>
@@ -9158,7 +9206,7 @@
     </row>
     <row r="98" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A98">
-        <v>719</v>
+        <v>808</v>
       </c>
       <c r="B98" t="e">
         <f>VLOOKUP($A98,統計!$A:$G,2,)</f>
@@ -9182,7 +9230,7 @@
     </row>
     <row r="99" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A99">
-        <v>720</v>
+        <v>809</v>
       </c>
       <c r="B99" t="e">
         <f>VLOOKUP($A99,統計!$A:$G,2,)</f>
@@ -9206,7 +9254,7 @@
     </row>
     <row r="100" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A100">
-        <v>721</v>
+        <v>810</v>
       </c>
       <c r="B100" t="e">
         <f>VLOOKUP($A100,統計!$A:$G,2,)</f>
@@ -9230,7 +9278,7 @@
     </row>
     <row r="101" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A101">
-        <v>722</v>
+        <v>811</v>
       </c>
       <c r="B101" t="e">
         <f>VLOOKUP($A101,統計!$A:$G,2,)</f>
@@ -9254,7 +9302,7 @@
     </row>
     <row r="102" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A102">
-        <v>723</v>
+        <v>812</v>
       </c>
       <c r="B102" t="e">
         <f>VLOOKUP($A102,統計!$A:$G,2,)</f>
@@ -9278,7 +9326,7 @@
     </row>
     <row r="103" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A103">
-        <v>724</v>
+        <v>813</v>
       </c>
       <c r="B103" t="e">
         <f>VLOOKUP($A103,統計!$A:$G,2,)</f>
@@ -9302,7 +9350,7 @@
     </row>
     <row r="104" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A104">
-        <v>725</v>
+        <v>814</v>
       </c>
       <c r="B104" t="e">
         <f>VLOOKUP($A104,統計!$A:$G,2,)</f>
@@ -9326,7 +9374,7 @@
     </row>
     <row r="105" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A105">
-        <v>726</v>
+        <v>815</v>
       </c>
       <c r="B105" t="e">
         <f>VLOOKUP($A105,統計!$A:$G,2,)</f>
@@ -9350,7 +9398,7 @@
     </row>
     <row r="106" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A106">
-        <v>727</v>
+        <v>816</v>
       </c>
       <c r="B106" t="e">
         <f>VLOOKUP($A106,統計!$A:$G,2,)</f>
@@ -9374,7 +9422,7 @@
     </row>
     <row r="107" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A107">
-        <v>728</v>
+        <v>817</v>
       </c>
       <c r="B107" t="e">
         <f>VLOOKUP($A107,統計!$A:$G,2,)</f>
@@ -9398,7 +9446,7 @@
     </row>
     <row r="108" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A108">
-        <v>729</v>
+        <v>818</v>
       </c>
       <c r="B108" t="e">
         <f>VLOOKUP($A108,統計!$A:$G,2,)</f>
@@ -9422,7 +9470,7 @@
     </row>
     <row r="109" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A109">
-        <v>730</v>
+        <v>819</v>
       </c>
       <c r="B109" t="e">
         <f>VLOOKUP($A109,統計!$A:$G,2,)</f>
@@ -9446,7 +9494,7 @@
     </row>
     <row r="110" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A110">
-        <v>731</v>
+        <v>820</v>
       </c>
       <c r="B110" t="e">
         <f>VLOOKUP($A110,統計!$A:$G,2,)</f>
@@ -9470,7 +9518,7 @@
     </row>
     <row r="111" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A111">
-        <v>732</v>
+        <v>821</v>
       </c>
       <c r="B111" t="e">
         <f>VLOOKUP($A111,統計!$A:$G,2,)</f>
@@ -9494,7 +9542,7 @@
     </row>
     <row r="112" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A112">
-        <v>733</v>
+        <v>822</v>
       </c>
       <c r="B112" t="e">
         <f>VLOOKUP($A112,統計!$A:$G,2,)</f>
@@ -9518,7 +9566,7 @@
     </row>
     <row r="113" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A113">
-        <v>734</v>
+        <v>823</v>
       </c>
       <c r="B113" t="e">
         <f>VLOOKUP($A113,統計!$A:$G,2,)</f>
@@ -9542,7 +9590,7 @@
     </row>
     <row r="114" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A114">
-        <v>735</v>
+        <v>824</v>
       </c>
       <c r="B114" t="e">
         <f>VLOOKUP($A114,統計!$A:$G,2,)</f>
@@ -9566,7 +9614,7 @@
     </row>
     <row r="115" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A115">
-        <v>736</v>
+        <v>825</v>
       </c>
       <c r="B115" t="e">
         <f>VLOOKUP($A115,統計!$A:$G,2,)</f>
@@ -9590,7 +9638,7 @@
     </row>
     <row r="116" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A116">
-        <v>737</v>
+        <v>826</v>
       </c>
       <c r="B116" t="e">
         <f>VLOOKUP($A116,統計!$A:$G,2,)</f>
@@ -9614,7 +9662,7 @@
     </row>
     <row r="117" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A117">
-        <v>738</v>
+        <v>827</v>
       </c>
       <c r="B117" t="e">
         <f>VLOOKUP($A117,統計!$A:$G,2,)</f>
@@ -9638,7 +9686,7 @@
     </row>
     <row r="118" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A118">
-        <v>739</v>
+        <v>828</v>
       </c>
       <c r="B118" t="e">
         <f>VLOOKUP($A118,統計!$A:$G,2,)</f>
@@ -9662,7 +9710,7 @@
     </row>
     <row r="119" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A119">
-        <v>740</v>
+        <v>829</v>
       </c>
       <c r="B119" t="e">
         <f>VLOOKUP($A119,統計!$A:$G,2,)</f>
@@ -9686,7 +9734,7 @@
     </row>
     <row r="120" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A120">
-        <v>801</v>
+        <v>901</v>
       </c>
       <c r="B120" t="e">
         <f>VLOOKUP($A120,統計!$A:$G,2,)</f>
@@ -9710,7 +9758,7 @@
     </row>
     <row r="121" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A121">
-        <v>802</v>
+        <v>902</v>
       </c>
       <c r="B121" t="e">
         <f>VLOOKUP($A121,統計!$A:$G,2,)</f>
@@ -9734,7 +9782,7 @@
     </row>
     <row r="122" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A122">
-        <v>803</v>
+        <v>903</v>
       </c>
       <c r="B122" t="e">
         <f>VLOOKUP($A122,統計!$A:$G,2,)</f>
@@ -9758,7 +9806,7 @@
     </row>
     <row r="123" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A123">
-        <v>804</v>
+        <v>904</v>
       </c>
       <c r="B123" t="e">
         <f>VLOOKUP($A123,統計!$A:$G,2,)</f>
@@ -9782,7 +9830,7 @@
     </row>
     <row r="124" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A124">
-        <v>805</v>
+        <v>905</v>
       </c>
       <c r="B124" t="e">
         <f>VLOOKUP($A124,統計!$A:$G,2,)</f>
@@ -9806,7 +9854,7 @@
     </row>
     <row r="125" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A125">
-        <v>806</v>
+        <v>906</v>
       </c>
       <c r="B125" t="e">
         <f>VLOOKUP($A125,統計!$A:$G,2,)</f>
@@ -9830,7 +9878,7 @@
     </row>
     <row r="126" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A126">
-        <v>807</v>
+        <v>907</v>
       </c>
       <c r="B126" t="e">
         <f>VLOOKUP($A126,統計!$A:$G,2,)</f>
@@ -9854,7 +9902,7 @@
     </row>
     <row r="127" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A127">
-        <v>808</v>
+        <v>908</v>
       </c>
       <c r="B127" t="e">
         <f>VLOOKUP($A127,統計!$A:$G,2,)</f>
@@ -9878,7 +9926,7 @@
     </row>
     <row r="128" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A128">
-        <v>809</v>
+        <v>909</v>
       </c>
       <c r="B128" t="e">
         <f>VLOOKUP($A128,統計!$A:$G,2,)</f>
@@ -9902,7 +9950,7 @@
     </row>
     <row r="129" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A129">
-        <v>810</v>
+        <v>910</v>
       </c>
       <c r="B129" t="e">
         <f>VLOOKUP($A129,統計!$A:$G,2,)</f>
@@ -9926,7 +9974,7 @@
     </row>
     <row r="130" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A130">
-        <v>811</v>
+        <v>911</v>
       </c>
       <c r="B130" t="e">
         <f>VLOOKUP($A130,統計!$A:$G,2,)</f>
@@ -9950,7 +9998,7 @@
     </row>
     <row r="131" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A131">
-        <v>812</v>
+        <v>912</v>
       </c>
       <c r="B131" t="e">
         <f>VLOOKUP($A131,統計!$A:$G,2,)</f>
@@ -9974,7 +10022,7 @@
     </row>
     <row r="132" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A132">
-        <v>813</v>
+        <v>913</v>
       </c>
       <c r="B132" t="e">
         <f>VLOOKUP($A132,統計!$A:$G,2,)</f>
@@ -9998,7 +10046,7 @@
     </row>
     <row r="133" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A133">
-        <v>814</v>
+        <v>914</v>
       </c>
       <c r="B133" t="e">
         <f>VLOOKUP($A133,統計!$A:$G,2,)</f>
@@ -10022,7 +10070,7 @@
     </row>
     <row r="134" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A134">
-        <v>815</v>
+        <v>915</v>
       </c>
       <c r="B134" t="e">
         <f>VLOOKUP($A134,統計!$A:$G,2,)</f>
@@ -10046,7 +10094,7 @@
     </row>
     <row r="135" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A135">
-        <v>816</v>
+        <v>916</v>
       </c>
       <c r="B135" t="e">
         <f>VLOOKUP($A135,統計!$A:$G,2,)</f>
@@ -10070,7 +10118,7 @@
     </row>
     <row r="136" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A136">
-        <v>901</v>
+        <v>1001</v>
       </c>
       <c r="B136" t="e">
         <f>VLOOKUP($A136,統計!$A:$G,2,)</f>
@@ -10094,7 +10142,7 @@
     </row>
     <row r="137" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A137">
-        <v>902</v>
+        <v>1002</v>
       </c>
       <c r="B137" t="e">
         <f>VLOOKUP($A137,統計!$A:$G,2,)</f>
@@ -10118,7 +10166,7 @@
     </row>
     <row r="138" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A138">
-        <v>903</v>
+        <v>1003</v>
       </c>
       <c r="B138" t="e">
         <f>VLOOKUP($A138,統計!$A:$G,2,)</f>
@@ -10142,7 +10190,7 @@
     </row>
     <row r="139" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A139">
-        <v>904</v>
+        <v>1004</v>
       </c>
       <c r="B139" t="e">
         <f>VLOOKUP($A139,統計!$A:$G,2,)</f>
@@ -10166,7 +10214,7 @@
     </row>
     <row r="140" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A140">
-        <v>905</v>
+        <v>1005</v>
       </c>
       <c r="B140" t="e">
         <f>VLOOKUP($A140,統計!$A:$G,2,)</f>
@@ -10190,7 +10238,7 @@
     </row>
     <row r="141" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A141">
-        <v>906</v>
+        <v>1006</v>
       </c>
       <c r="B141" t="e">
         <f>VLOOKUP($A141,統計!$A:$G,2,)</f>
@@ -10214,7 +10262,7 @@
     </row>
     <row r="142" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A142">
-        <v>907</v>
+        <v>1007</v>
       </c>
       <c r="B142" t="e">
         <f>VLOOKUP($A142,統計!$A:$G,2,)</f>
@@ -10238,7 +10286,7 @@
     </row>
     <row r="143" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A143">
-        <v>908</v>
+        <v>1008</v>
       </c>
       <c r="B143" t="e">
         <f>VLOOKUP($A143,統計!$A:$G,2,)</f>
@@ -10262,7 +10310,7 @@
     </row>
     <row r="144" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A144">
-        <v>909</v>
+        <v>1009</v>
       </c>
       <c r="B144" t="e">
         <f>VLOOKUP($A144,統計!$A:$G,2,)</f>
@@ -10286,7 +10334,7 @@
     </row>
     <row r="145" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A145">
-        <v>910</v>
+        <v>1010</v>
       </c>
       <c r="B145" t="e">
         <f>VLOOKUP($A145,統計!$A:$G,2,)</f>
@@ -10310,7 +10358,7 @@
     </row>
     <row r="146" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A146">
-        <v>1001</v>
+        <v>1101</v>
       </c>
       <c r="B146" t="e">
         <f>VLOOKUP($A146,統計!$A:$G,2,)</f>
@@ -10334,7 +10382,7 @@
     </row>
     <row r="147" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A147">
-        <v>1002</v>
+        <v>1102</v>
       </c>
       <c r="B147" t="e">
         <f>VLOOKUP($A147,統計!$A:$G,2,)</f>
@@ -10358,7 +10406,7 @@
     </row>
     <row r="148" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A148">
-        <v>1003</v>
+        <v>1103</v>
       </c>
       <c r="B148" t="e">
         <f>VLOOKUP($A148,統計!$A:$G,2,)</f>
@@ -10382,7 +10430,7 @@
     </row>
     <row r="149" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A149">
-        <v>1004</v>
+        <v>1104</v>
       </c>
       <c r="B149" t="e">
         <f>VLOOKUP($A149,統計!$A:$G,2,)</f>
@@ -10406,7 +10454,7 @@
     </row>
     <row r="150" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A150">
-        <v>1005</v>
+        <v>1105</v>
       </c>
       <c r="B150" t="e">
         <f>VLOOKUP($A150,統計!$A:$G,2,)</f>
@@ -10430,7 +10478,7 @@
     </row>
     <row r="151" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A151">
-        <v>1006</v>
+        <v>1106</v>
       </c>
       <c r="B151" t="e">
         <f>VLOOKUP($A151,統計!$A:$G,2,)</f>
@@ -10454,7 +10502,7 @@
     </row>
     <row r="152" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A152">
-        <v>1007</v>
+        <v>1107</v>
       </c>
       <c r="B152" t="e">
         <f>VLOOKUP($A152,統計!$A:$G,2,)</f>
@@ -10478,7 +10526,7 @@
     </row>
     <row r="153" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A153">
-        <v>1008</v>
+        <v>1108</v>
       </c>
       <c r="B153" t="e">
         <f>VLOOKUP($A153,統計!$A:$G,2,)</f>
@@ -10502,7 +10550,7 @@
     </row>
     <row r="154" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A154">
-        <v>1009</v>
+        <v>1109</v>
       </c>
       <c r="B154" t="e">
         <f>VLOOKUP($A154,統計!$A:$G,2,)</f>
@@ -10526,7 +10574,7 @@
     </row>
     <row r="155" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A155">
-        <v>1010</v>
+        <v>1110</v>
       </c>
       <c r="B155" t="e">
         <f>VLOOKUP($A155,統計!$A:$G,2,)</f>
@@ -10550,7 +10598,7 @@
     </row>
     <row r="156" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A156">
-        <v>1011</v>
+        <v>1111</v>
       </c>
       <c r="B156" t="e">
         <f>VLOOKUP($A156,統計!$A:$G,2,)</f>
@@ -10574,7 +10622,7 @@
     </row>
     <row r="157" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A157">
-        <v>1012</v>
+        <v>1112</v>
       </c>
       <c r="B157" t="e">
         <f>VLOOKUP($A157,統計!$A:$G,2,)</f>
@@ -10598,7 +10646,7 @@
     </row>
     <row r="158" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A158">
-        <v>1013</v>
+        <v>1113</v>
       </c>
       <c r="B158" t="e">
         <f>VLOOKUP($A158,統計!$A:$G,2,)</f>
@@ -10622,7 +10670,7 @@
     </row>
     <row r="159" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A159">
-        <v>1014</v>
+        <v>1114</v>
       </c>
       <c r="B159" t="e">
         <f>VLOOKUP($A159,統計!$A:$G,2,)</f>
@@ -10646,7 +10694,7 @@
     </row>
     <row r="160" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A160">
-        <v>1015</v>
+        <v>1115</v>
       </c>
       <c r="B160" t="e">
         <f>VLOOKUP($A160,統計!$A:$G,2,)</f>
@@ -10670,7 +10718,7 @@
     </row>
     <row r="161" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A161">
-        <v>1016</v>
+        <v>1116</v>
       </c>
       <c r="B161" t="e">
         <f>VLOOKUP($A161,統計!$A:$G,2,)</f>
@@ -10694,7 +10742,7 @@
     </row>
     <row r="162" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A162">
-        <v>1017</v>
+        <v>1117</v>
       </c>
       <c r="B162" t="e">
         <f>VLOOKUP($A162,統計!$A:$G,2,)</f>
@@ -10718,7 +10766,7 @@
     </row>
     <row r="163" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A163">
-        <v>1018</v>
+        <v>1118</v>
       </c>
       <c r="B163" t="e">
         <f>VLOOKUP($A163,統計!$A:$G,2,)</f>
@@ -10742,7 +10790,7 @@
     </row>
     <row r="164" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A164">
-        <v>1019</v>
+        <v>1119</v>
       </c>
       <c r="B164" t="e">
         <f>VLOOKUP($A164,統計!$A:$G,2,)</f>
@@ -10766,7 +10814,7 @@
     </row>
     <row r="165" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A165">
-        <v>1020</v>
+        <v>1120</v>
       </c>
       <c r="B165" t="e">
         <f>VLOOKUP($A165,統計!$A:$G,2,)</f>
@@ -10790,7 +10838,7 @@
     </row>
     <row r="166" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A166">
-        <v>1021</v>
+        <v>1121</v>
       </c>
       <c r="B166" t="e">
         <f>VLOOKUP($A166,統計!$A:$G,2,)</f>
@@ -10814,7 +10862,7 @@
     </row>
     <row r="167" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A167">
-        <v>1022</v>
+        <v>1122</v>
       </c>
       <c r="B167" t="e">
         <f>VLOOKUP($A167,統計!$A:$G,2,)</f>
@@ -10838,7 +10886,7 @@
     </row>
     <row r="168" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A168">
-        <v>1101</v>
+        <v>1201</v>
       </c>
       <c r="B168" t="e">
         <f>VLOOKUP($A168,統計!$A:$G,2,)</f>
@@ -10862,7 +10910,7 @@
     </row>
     <row r="169" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A169">
-        <v>1102</v>
+        <v>1202</v>
       </c>
       <c r="B169" t="e">
         <f>VLOOKUP($A169,統計!$A:$G,2,)</f>
@@ -10886,7 +10934,7 @@
     </row>
     <row r="170" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A170">
-        <v>1103</v>
+        <v>1203</v>
       </c>
       <c r="B170" t="e">
         <f>VLOOKUP($A170,統計!$A:$G,2,)</f>
@@ -10910,7 +10958,7 @@
     </row>
     <row r="171" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A171">
-        <v>1104</v>
+        <v>1204</v>
       </c>
       <c r="B171" t="e">
         <f>VLOOKUP($A171,統計!$A:$G,2,)</f>
@@ -10934,7 +10982,7 @@
     </row>
     <row r="172" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A172">
-        <v>1105</v>
+        <v>1205</v>
       </c>
       <c r="B172" t="e">
         <f>VLOOKUP($A172,統計!$A:$G,2,)</f>
@@ -10958,7 +11006,7 @@
     </row>
     <row r="173" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A173">
-        <v>1106</v>
+        <v>1206</v>
       </c>
       <c r="B173" t="e">
         <f>VLOOKUP($A173,統計!$A:$G,2,)</f>
@@ -10982,7 +11030,7 @@
     </row>
     <row r="174" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A174">
-        <v>1107</v>
+        <v>1207</v>
       </c>
       <c r="B174" t="e">
         <f>VLOOKUP($A174,統計!$A:$G,2,)</f>
@@ -11006,7 +11054,7 @@
     </row>
     <row r="175" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A175">
-        <v>1108</v>
+        <v>1208</v>
       </c>
       <c r="B175" t="e">
         <f>VLOOKUP($A175,統計!$A:$G,2,)</f>
@@ -11030,7 +11078,7 @@
     </row>
     <row r="176" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A176">
-        <v>1109</v>
+        <v>1209</v>
       </c>
       <c r="B176" t="e">
         <f>VLOOKUP($A176,統計!$A:$G,2,)</f>
@@ -11054,7 +11102,7 @@
     </row>
     <row r="177" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A177">
-        <v>1110</v>
+        <v>1210</v>
       </c>
       <c r="B177" t="e">
         <f>VLOOKUP($A177,統計!$A:$G,2,)</f>
@@ -11078,7 +11126,7 @@
     </row>
     <row r="178" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A178">
-        <v>1201</v>
+        <v>1301</v>
       </c>
       <c r="B178" t="e">
         <f>VLOOKUP($A178,統計!$A:$G,2,)</f>
@@ -11102,7 +11150,7 @@
     </row>
     <row r="179" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A179">
-        <v>1202</v>
+        <v>1302</v>
       </c>
       <c r="B179" t="e">
         <f>VLOOKUP($A179,統計!$A:$G,2,)</f>
@@ -11126,7 +11174,7 @@
     </row>
     <row r="180" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A180">
-        <v>1203</v>
+        <v>1303</v>
       </c>
       <c r="B180" t="e">
         <f>VLOOKUP($A180,統計!$A:$G,2,)</f>
@@ -11150,7 +11198,7 @@
     </row>
     <row r="181" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A181">
-        <v>1204</v>
+        <v>1304</v>
       </c>
       <c r="B181" t="e">
         <f>VLOOKUP($A181,統計!$A:$G,2,)</f>
@@ -11174,7 +11222,7 @@
     </row>
     <row r="182" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A182">
-        <v>1205</v>
+        <v>1305</v>
       </c>
       <c r="B182" t="e">
         <f>VLOOKUP($A182,統計!$A:$G,2,)</f>
@@ -11198,7 +11246,7 @@
     </row>
     <row r="183" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A183">
-        <v>1206</v>
+        <v>1306</v>
       </c>
       <c r="B183" t="e">
         <f>VLOOKUP($A183,統計!$A:$G,2,)</f>
@@ -11222,7 +11270,7 @@
     </row>
     <row r="184" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A184">
-        <v>1207</v>
+        <v>1307</v>
       </c>
       <c r="B184" t="e">
         <f>VLOOKUP($A184,統計!$A:$G,2,)</f>
@@ -11246,7 +11294,7 @@
     </row>
     <row r="185" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A185">
-        <v>1208</v>
+        <v>1308</v>
       </c>
       <c r="B185" t="e">
         <f>VLOOKUP($A185,統計!$A:$G,2,)</f>
@@ -11270,7 +11318,7 @@
     </row>
     <row r="186" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A186">
-        <v>1301</v>
+        <v>1401</v>
       </c>
       <c r="B186" t="e">
         <f>VLOOKUP($A186,統計!$A:$G,2,)</f>
@@ -11294,7 +11342,7 @@
     </row>
     <row r="187" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A187">
-        <v>1302</v>
+        <v>1402</v>
       </c>
       <c r="B187" t="e">
         <f>VLOOKUP($A187,統計!$A:$G,2,)</f>
@@ -11318,7 +11366,7 @@
     </row>
     <row r="188" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A188">
-        <v>1303</v>
+        <v>1403</v>
       </c>
       <c r="B188" t="e">
         <f>VLOOKUP($A188,統計!$A:$G,2,)</f>
@@ -11342,7 +11390,7 @@
     </row>
     <row r="189" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A189">
-        <v>1304</v>
+        <v>1404</v>
       </c>
       <c r="B189" t="e">
         <f>VLOOKUP($A189,統計!$A:$G,2,)</f>
@@ -11366,7 +11414,7 @@
     </row>
     <row r="190" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A190">
-        <v>1305</v>
+        <v>1405</v>
       </c>
       <c r="B190" t="e">
         <f>VLOOKUP($A190,統計!$A:$G,2,)</f>
@@ -11390,7 +11438,7 @@
     </row>
     <row r="191" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A191">
-        <v>1306</v>
+        <v>1406</v>
       </c>
       <c r="B191" t="e">
         <f>VLOOKUP($A191,統計!$A:$G,2,)</f>
@@ -11414,7 +11462,7 @@
     </row>
     <row r="192" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A192">
-        <v>1307</v>
+        <v>1407</v>
       </c>
       <c r="B192" t="e">
         <f>VLOOKUP($A192,統計!$A:$G,2,)</f>
@@ -11438,7 +11486,7 @@
     </row>
     <row r="193" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A193">
-        <v>1308</v>
+        <v>1408</v>
       </c>
       <c r="B193" t="e">
         <f>VLOOKUP($A193,統計!$A:$G,2,)</f>
@@ -11462,7 +11510,7 @@
     </row>
     <row r="194" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A194">
-        <v>1309</v>
+        <v>1409</v>
       </c>
       <c r="B194" t="e">
         <f>VLOOKUP($A194,統計!$A:$G,2,)</f>
@@ -11486,7 +11534,7 @@
     </row>
     <row r="195" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A195">
-        <v>1310</v>
+        <v>1410</v>
       </c>
       <c r="B195" t="e">
         <f>VLOOKUP($A195,統計!$A:$G,2,)</f>
@@ -11510,7 +11558,7 @@
     </row>
     <row r="196" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A196">
-        <v>1311</v>
+        <v>1411</v>
       </c>
       <c r="B196" t="e">
         <f>VLOOKUP($A196,統計!$A:$G,2,)</f>
@@ -11534,7 +11582,7 @@
     </row>
     <row r="197" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A197">
-        <v>1312</v>
+        <v>1412</v>
       </c>
       <c r="B197" t="e">
         <f>VLOOKUP($A197,統計!$A:$G,2,)</f>
@@ -11558,7 +11606,7 @@
     </row>
     <row r="198" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A198">
-        <v>1313</v>
+        <v>1413</v>
       </c>
       <c r="B198" t="e">
         <f>VLOOKUP($A198,統計!$A:$G,2,)</f>
@@ -11582,7 +11630,7 @@
     </row>
     <row r="199" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A199">
-        <v>1314</v>
+        <v>1414</v>
       </c>
       <c r="B199" t="e">
         <f>VLOOKUP($A199,統計!$A:$G,2,)</f>
@@ -11606,7 +11654,7 @@
     </row>
     <row r="200" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A200">
-        <v>1315</v>
+        <v>1415</v>
       </c>
       <c r="B200" t="e">
         <f>VLOOKUP($A200,統計!$A:$G,2,)</f>
@@ -11630,7 +11678,7 @@
     </row>
     <row r="201" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A201">
-        <v>1316</v>
+        <v>1416</v>
       </c>
       <c r="B201" t="e">
         <f>VLOOKUP($A201,統計!$A:$G,2,)</f>
@@ -11654,7 +11702,7 @@
     </row>
     <row r="202" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A202">
-        <v>1317</v>
+        <v>1417</v>
       </c>
       <c r="B202" t="e">
         <f>VLOOKUP($A202,統計!$A:$G,2,)</f>
@@ -11678,7 +11726,7 @@
     </row>
     <row r="203" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A203">
-        <v>1318</v>
+        <v>1418</v>
       </c>
       <c r="B203" t="e">
         <f>VLOOKUP($A203,統計!$A:$G,2,)</f>
@@ -11702,7 +11750,7 @@
     </row>
     <row r="204" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A204">
-        <v>1319</v>
+        <v>1419</v>
       </c>
       <c r="B204" t="e">
         <f>VLOOKUP($A204,統計!$A:$G,2,)</f>
@@ -11726,7 +11774,7 @@
     </row>
     <row r="205" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A205">
-        <v>1320</v>
+        <v>1420</v>
       </c>
       <c r="B205" t="e">
         <f>VLOOKUP($A205,統計!$A:$G,2,)</f>
@@ -11750,7 +11798,7 @@
     </row>
     <row r="206" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A206">
-        <v>1321</v>
+        <v>1421</v>
       </c>
       <c r="B206" t="e">
         <f>VLOOKUP($A206,統計!$A:$G,2,)</f>
@@ -11774,7 +11822,7 @@
     </row>
     <row r="207" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A207">
-        <v>1322</v>
+        <v>1422</v>
       </c>
       <c r="B207" t="e">
         <f>VLOOKUP($A207,統計!$A:$G,2,)</f>
@@ -11798,7 +11846,7 @@
     </row>
     <row r="208" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A208">
-        <v>1323</v>
+        <v>1423</v>
       </c>
       <c r="B208" t="e">
         <f>VLOOKUP($A208,統計!$A:$G,2,)</f>
@@ -11822,7 +11870,7 @@
     </row>
     <row r="209" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A209">
-        <v>1324</v>
+        <v>1424</v>
       </c>
       <c r="B209" t="e">
         <f>VLOOKUP($A209,統計!$A:$G,2,)</f>
@@ -11846,7 +11894,7 @@
     </row>
     <row r="210" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A210">
-        <v>1325</v>
+        <v>1425</v>
       </c>
       <c r="B210" t="e">
         <f>VLOOKUP($A210,統計!$A:$G,2,)</f>
@@ -11870,7 +11918,7 @@
     </row>
     <row r="211" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A211">
-        <v>1326</v>
+        <v>1426</v>
       </c>
       <c r="B211" t="e">
         <f>VLOOKUP($A211,統計!$A:$G,2,)</f>
@@ -11894,7 +11942,7 @@
     </row>
     <row r="212" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A212">
-        <v>1327</v>
+        <v>1427</v>
       </c>
       <c r="B212" t="e">
         <f>VLOOKUP($A212,統計!$A:$G,2,)</f>
@@ -11918,7 +11966,7 @@
     </row>
     <row r="213" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A213">
-        <v>1328</v>
+        <v>1428</v>
       </c>
       <c r="B213" t="e">
         <f>VLOOKUP($A213,統計!$A:$G,2,)</f>
@@ -11942,7 +11990,7 @@
     </row>
     <row r="214" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A214">
-        <v>1329</v>
+        <v>1429</v>
       </c>
       <c r="B214" t="e">
         <f>VLOOKUP($A214,統計!$A:$G,2,)</f>
@@ -11966,7 +12014,7 @@
     </row>
     <row r="215" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A215">
-        <v>1330</v>
+        <v>1430</v>
       </c>
       <c r="B215" t="e">
         <f>VLOOKUP($A215,統計!$A:$G,2,)</f>
@@ -11990,7 +12038,7 @@
     </row>
     <row r="216" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A216">
-        <v>1331</v>
+        <v>1431</v>
       </c>
       <c r="B216" t="e">
         <f>VLOOKUP($A216,統計!$A:$G,2,)</f>
@@ -12014,7 +12062,7 @@
     </row>
     <row r="217" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A217">
-        <v>1332</v>
+        <v>1432</v>
       </c>
       <c r="B217" t="e">
         <f>VLOOKUP($A217,統計!$A:$G,2,)</f>
@@ -12038,7 +12086,7 @@
     </row>
     <row r="218" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A218">
-        <v>1333</v>
+        <v>1433</v>
       </c>
       <c r="B218" t="e">
         <f>VLOOKUP($A218,統計!$A:$G,2,)</f>
@@ -12062,7 +12110,7 @@
     </row>
     <row r="219" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A219">
-        <v>1334</v>
+        <v>1434</v>
       </c>
       <c r="B219" t="e">
         <f>VLOOKUP($A219,統計!$A:$G,2,)</f>
@@ -12086,7 +12134,7 @@
     </row>
     <row r="220" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A220">
-        <v>1335</v>
+        <v>1435</v>
       </c>
       <c r="B220" t="e">
         <f>VLOOKUP($A220,統計!$A:$G,2,)</f>
@@ -12110,7 +12158,7 @@
     </row>
     <row r="221" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A221">
-        <v>1336</v>
+        <v>1436</v>
       </c>
       <c r="B221" t="e">
         <f>VLOOKUP($A221,統計!$A:$G,2,)</f>
@@ -12134,7 +12182,7 @@
     </row>
     <row r="222" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A222">
-        <v>1337</v>
+        <v>1437</v>
       </c>
       <c r="B222" t="e">
         <f>VLOOKUP($A222,統計!$A:$G,2,)</f>
@@ -12158,7 +12206,7 @@
     </row>
     <row r="223" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A223">
-        <v>1338</v>
+        <v>1438</v>
       </c>
       <c r="B223" t="e">
         <f>VLOOKUP($A223,統計!$A:$G,2,)</f>
@@ -12182,7 +12230,7 @@
     </row>
     <row r="224" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A224">
-        <v>1339</v>
+        <v>1439</v>
       </c>
       <c r="B224" t="e">
         <f>VLOOKUP($A224,統計!$A:$G,2,)</f>
@@ -12206,7 +12254,7 @@
     </row>
     <row r="225" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A225">
-        <v>1340</v>
+        <v>1440</v>
       </c>
       <c r="B225" t="e">
         <f>VLOOKUP($A225,統計!$A:$G,2,)</f>
@@ -12230,7 +12278,7 @@
     </row>
     <row r="226" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A226">
-        <v>1341</v>
+        <v>1441</v>
       </c>
       <c r="B226" t="e">
         <f>VLOOKUP($A226,統計!$A:$G,2,)</f>
@@ -12254,7 +12302,7 @@
     </row>
     <row r="227" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A227">
-        <v>1342</v>
+        <v>1442</v>
       </c>
       <c r="B227" t="e">
         <f>VLOOKUP($A227,統計!$A:$G,2,)</f>
@@ -12278,7 +12326,7 @@
     </row>
     <row r="228" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A228">
-        <v>1343</v>
+        <v>1443</v>
       </c>
       <c r="B228" t="e">
         <f>VLOOKUP($A228,統計!$A:$G,2,)</f>
@@ -12302,7 +12350,7 @@
     </row>
     <row r="229" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A229">
-        <v>1344</v>
+        <v>1444</v>
       </c>
       <c r="B229" t="e">
         <f>VLOOKUP($A229,統計!$A:$G,2,)</f>
@@ -12326,7 +12374,7 @@
     </row>
     <row r="230" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A230">
-        <v>1345</v>
+        <v>1445</v>
       </c>
       <c r="B230" t="e">
         <f>VLOOKUP($A230,統計!$A:$G,2,)</f>
@@ -12350,7 +12398,7 @@
     </row>
     <row r="231" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A231">
-        <v>1346</v>
+        <v>1446</v>
       </c>
       <c r="B231" t="e">
         <f>VLOOKUP($A231,統計!$A:$G,2,)</f>
@@ -12374,7 +12422,7 @@
     </row>
     <row r="232" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A232">
-        <v>1347</v>
+        <v>1447</v>
       </c>
       <c r="B232" t="e">
         <f>VLOOKUP($A232,統計!$A:$G,2,)</f>
@@ -12398,7 +12446,7 @@
     </row>
     <row r="233" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A233">
-        <v>1348</v>
+        <v>1448</v>
       </c>
       <c r="B233" t="e">
         <f>VLOOKUP($A233,統計!$A:$G,2,)</f>
@@ -12422,7 +12470,7 @@
     </row>
     <row r="234" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A234">
-        <v>1349</v>
+        <v>1449</v>
       </c>
       <c r="B234" t="e">
         <f>VLOOKUP($A234,統計!$A:$G,2,)</f>
@@ -12446,7 +12494,7 @@
     </row>
     <row r="235" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A235">
-        <v>1350</v>
+        <v>1450</v>
       </c>
       <c r="B235" t="e">
         <f>VLOOKUP($A235,統計!$A:$G,2,)</f>
@@ -12470,7 +12518,7 @@
     </row>
     <row r="236" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A236">
-        <v>1351</v>
+        <v>1451</v>
       </c>
       <c r="B236" t="e">
         <f>VLOOKUP($A236,統計!$A:$G,2,)</f>
@@ -12494,7 +12542,7 @@
     </row>
     <row r="237" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A237">
-        <v>1352</v>
+        <v>1452</v>
       </c>
       <c r="B237" t="e">
         <f>VLOOKUP($A237,統計!$A:$G,2,)</f>
@@ -12518,7 +12566,7 @@
     </row>
     <row r="238" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A238">
-        <v>1353</v>
+        <v>1453</v>
       </c>
       <c r="B238" t="e">
         <f>VLOOKUP($A238,統計!$A:$G,2,)</f>
@@ -12542,7 +12590,7 @@
     </row>
     <row r="239" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A239">
-        <v>1354</v>
+        <v>1454</v>
       </c>
       <c r="B239" t="e">
         <f>VLOOKUP($A239,統計!$A:$G,2,)</f>
@@ -12566,7 +12614,7 @@
     </row>
     <row r="240" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A240">
-        <v>1355</v>
+        <v>1455</v>
       </c>
       <c r="B240" t="e">
         <f>VLOOKUP($A240,統計!$A:$G,2,)</f>
@@ -12590,7 +12638,7 @@
     </row>
     <row r="241" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A241">
-        <v>1356</v>
+        <v>1456</v>
       </c>
       <c r="B241" t="e">
         <f>VLOOKUP($A241,統計!$A:$G,2,)</f>
@@ -12614,7 +12662,7 @@
     </row>
     <row r="242" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A242">
-        <v>1357</v>
+        <v>1457</v>
       </c>
       <c r="B242" t="e">
         <f>VLOOKUP($A242,統計!$A:$G,2,)</f>
@@ -12638,7 +12686,7 @@
     </row>
     <row r="243" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A243">
-        <v>1358</v>
+        <v>1458</v>
       </c>
       <c r="B243" t="e">
         <f>VLOOKUP($A243,統計!$A:$G,2,)</f>
@@ -12662,7 +12710,7 @@
     </row>
     <row r="244" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A244">
-        <v>1359</v>
+        <v>1459</v>
       </c>
       <c r="B244" t="e">
         <f>VLOOKUP($A244,統計!$A:$G,2,)</f>
@@ -12686,7 +12734,7 @@
     </row>
     <row r="245" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A245">
-        <v>1360</v>
+        <v>1460</v>
       </c>
       <c r="B245" t="e">
         <f>VLOOKUP($A245,統計!$A:$G,2,)</f>
@@ -12710,7 +12758,7 @@
     </row>
     <row r="246" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A246">
-        <v>1361</v>
+        <v>1461</v>
       </c>
       <c r="B246" t="e">
         <f>VLOOKUP($A246,統計!$A:$G,2,)</f>
@@ -12734,7 +12782,7 @@
     </row>
     <row r="247" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A247">
-        <v>1362</v>
+        <v>1462</v>
       </c>
       <c r="B247" t="e">
         <f>VLOOKUP($A247,統計!$A:$G,2,)</f>
@@ -12758,7 +12806,7 @@
     </row>
     <row r="248" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A248">
-        <v>1363</v>
+        <v>1463</v>
       </c>
       <c r="B248" t="e">
         <f>VLOOKUP($A248,統計!$A:$G,2,)</f>
@@ -12782,7 +12830,7 @@
     </row>
     <row r="249" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A249">
-        <v>1364</v>
+        <v>1464</v>
       </c>
       <c r="B249" t="e">
         <f>VLOOKUP($A249,統計!$A:$G,2,)</f>
@@ -12806,7 +12854,7 @@
     </row>
     <row r="250" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A250">
-        <v>1365</v>
+        <v>1465</v>
       </c>
       <c r="B250" t="e">
         <f>VLOOKUP($A250,統計!$A:$G,2,)</f>
@@ -12830,7 +12878,7 @@
     </row>
     <row r="251" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A251">
-        <v>1366</v>
+        <v>1466</v>
       </c>
       <c r="B251" t="e">
         <f>VLOOKUP($A251,統計!$A:$G,2,)</f>
@@ -12854,7 +12902,7 @@
     </row>
     <row r="252" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A252">
-        <v>1367</v>
+        <v>1467</v>
       </c>
       <c r="B252" t="e">
         <f>VLOOKUP($A252,統計!$A:$G,2,)</f>
@@ -12878,7 +12926,7 @@
     </row>
     <row r="253" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A253">
-        <v>1368</v>
+        <v>1468</v>
       </c>
       <c r="B253" t="e">
         <f>VLOOKUP($A253,統計!$A:$G,2,)</f>
@@ -12902,7 +12950,7 @@
     </row>
     <row r="254" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A254">
-        <v>1369</v>
+        <v>1469</v>
       </c>
       <c r="B254" t="e">
         <f>VLOOKUP($A254,統計!$A:$G,2,)</f>
@@ -12926,7 +12974,7 @@
     </row>
     <row r="255" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A255">
-        <v>1370</v>
+        <v>1470</v>
       </c>
       <c r="B255" t="e">
         <f>VLOOKUP($A255,統計!$A:$G,2,)</f>
@@ -12950,7 +12998,7 @@
     </row>
     <row r="256" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A256">
-        <v>1371</v>
+        <v>1471</v>
       </c>
       <c r="B256" t="e">
         <f>VLOOKUP($A256,統計!$A:$G,2,)</f>
@@ -12974,7 +13022,7 @@
     </row>
     <row r="257" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A257">
-        <v>1372</v>
+        <v>1472</v>
       </c>
       <c r="B257" t="e">
         <f>VLOOKUP($A257,統計!$A:$G,2,)</f>
@@ -12998,7 +13046,7 @@
     </row>
     <row r="258" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A258">
-        <v>1373</v>
+        <v>1473</v>
       </c>
       <c r="B258" t="e">
         <f>VLOOKUP($A258,統計!$A:$G,2,)</f>
@@ -13022,7 +13070,7 @@
     </row>
     <row r="259" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A259">
-        <v>1374</v>
+        <v>1474</v>
       </c>
       <c r="B259" t="e">
         <f>VLOOKUP($A259,統計!$A:$G,2,)</f>
@@ -13046,7 +13094,7 @@
     </row>
     <row r="260" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A260">
-        <v>1375</v>
+        <v>1475</v>
       </c>
       <c r="B260" t="e">
         <f>VLOOKUP($A260,統計!$A:$G,2,)</f>
@@ -13070,7 +13118,7 @@
     </row>
     <row r="261" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A261">
-        <v>1376</v>
+        <v>1476</v>
       </c>
       <c r="B261" t="e">
         <f>VLOOKUP($A261,統計!$A:$G,2,)</f>
@@ -13094,7 +13142,7 @@
     </row>
     <row r="262" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A262">
-        <v>1377</v>
+        <v>1477</v>
       </c>
       <c r="B262" t="e">
         <f>VLOOKUP($A262,統計!$A:$G,2,)</f>
@@ -13118,7 +13166,7 @@
     </row>
     <row r="263" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A263">
-        <v>1378</v>
+        <v>1478</v>
       </c>
       <c r="B263" t="e">
         <f>VLOOKUP($A263,統計!$A:$G,2,)</f>
@@ -13142,7 +13190,7 @@
     </row>
     <row r="264" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A264">
-        <v>1379</v>
+        <v>1479</v>
       </c>
       <c r="B264" t="e">
         <f>VLOOKUP($A264,統計!$A:$G,2,)</f>
@@ -13166,7 +13214,7 @@
     </row>
     <row r="265" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A265">
-        <v>1380</v>
+        <v>1480</v>
       </c>
       <c r="B265" t="e">
         <f>VLOOKUP($A265,統計!$A:$G,2,)</f>
@@ -13190,7 +13238,7 @@
     </row>
     <row r="266" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A266">
-        <v>1381</v>
+        <v>1481</v>
       </c>
       <c r="B266" t="e">
         <f>VLOOKUP($A266,統計!$A:$G,2,)</f>
@@ -13214,7 +13262,7 @@
     </row>
     <row r="267" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A267">
-        <v>1401</v>
+        <v>1501</v>
       </c>
       <c r="B267" t="e">
         <f>VLOOKUP($A267,統計!$A:$G,2,)</f>
@@ -13238,7 +13286,7 @@
     </row>
     <row r="268" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A268">
-        <v>1402</v>
+        <v>1502</v>
       </c>
       <c r="B268" t="e">
         <f>VLOOKUP($A268,統計!$A:$G,2,)</f>
@@ -13262,7 +13310,7 @@
     </row>
     <row r="269" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A269">
-        <v>1403</v>
+        <v>1503</v>
       </c>
       <c r="B269" t="e">
         <f>VLOOKUP($A269,統計!$A:$G,2,)</f>
@@ -13286,7 +13334,7 @@
     </row>
     <row r="270" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A270">
-        <v>1404</v>
+        <v>1504</v>
       </c>
       <c r="B270" t="e">
         <f>VLOOKUP($A270,統計!$A:$G,2,)</f>
@@ -13310,7 +13358,7 @@
     </row>
     <row r="271" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A271">
-        <v>1405</v>
+        <v>1505</v>
       </c>
       <c r="B271" t="e">
         <f>VLOOKUP($A271,統計!$A:$G,2,)</f>
@@ -13334,7 +13382,7 @@
     </row>
     <row r="272" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A272">
-        <v>1406</v>
+        <v>1506</v>
       </c>
       <c r="B272" t="e">
         <f>VLOOKUP($A272,統計!$A:$G,2,)</f>
@@ -13358,7 +13406,7 @@
     </row>
     <row r="273" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A273">
-        <v>1501</v>
+        <v>1601</v>
       </c>
       <c r="B273" t="e">
         <f>VLOOKUP($A273,統計!$A:$G,2,)</f>
@@ -13382,7 +13430,7 @@
     </row>
     <row r="274" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A274">
-        <v>1502</v>
+        <v>1602</v>
       </c>
       <c r="B274" t="e">
         <f>VLOOKUP($A274,統計!$A:$G,2,)</f>
@@ -13406,7 +13454,7 @@
     </row>
     <row r="275" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A275">
-        <v>1503</v>
+        <v>1603</v>
       </c>
       <c r="B275" t="e">
         <f>VLOOKUP($A275,統計!$A:$G,2,)</f>
@@ -13430,7 +13478,7 @@
     </row>
     <row r="276" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A276">
-        <v>1504</v>
+        <v>1604</v>
       </c>
       <c r="B276" t="e">
         <f>VLOOKUP($A276,統計!$A:$G,2,)</f>
@@ -13454,7 +13502,7 @@
     </row>
     <row r="277" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A277">
-        <v>1505</v>
+        <v>1605</v>
       </c>
       <c r="B277" t="e">
         <f>VLOOKUP($A277,統計!$A:$G,2,)</f>
@@ -13478,7 +13526,7 @@
     </row>
     <row r="278" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A278">
-        <v>1506</v>
+        <v>1606</v>
       </c>
       <c r="B278" t="e">
         <f>VLOOKUP($A278,統計!$A:$G,2,)</f>
@@ -13502,7 +13550,7 @@
     </row>
     <row r="279" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A279">
-        <v>1507</v>
+        <v>1607</v>
       </c>
       <c r="B279" t="e">
         <f>VLOOKUP($A279,統計!$A:$G,2,)</f>
@@ -13526,7 +13574,7 @@
     </row>
     <row r="280" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A280">
-        <v>1508</v>
+        <v>1608</v>
       </c>
       <c r="B280" t="e">
         <f>VLOOKUP($A280,統計!$A:$G,2,)</f>
@@ -13550,7 +13598,7 @@
     </row>
     <row r="281" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A281">
-        <v>1601</v>
+        <v>1701</v>
       </c>
       <c r="B281" t="e">
         <f>VLOOKUP($A281,統計!$A:$G,2,)</f>
@@ -13574,7 +13622,7 @@
     </row>
     <row r="282" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A282">
-        <v>1602</v>
+        <v>1702</v>
       </c>
       <c r="B282" t="e">
         <f>VLOOKUP($A282,統計!$A:$G,2,)</f>
@@ -13598,7 +13646,7 @@
     </row>
     <row r="283" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A283">
-        <v>1603</v>
+        <v>1703</v>
       </c>
       <c r="B283" t="e">
         <f>VLOOKUP($A283,統計!$A:$G,2,)</f>
@@ -13622,7 +13670,7 @@
     </row>
     <row r="284" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A284">
-        <v>1604</v>
+        <v>1704</v>
       </c>
       <c r="B284" t="e">
         <f>VLOOKUP($A284,統計!$A:$G,2,)</f>
@@ -13646,7 +13694,7 @@
     </row>
     <row r="285" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A285">
-        <v>1605</v>
+        <v>1705</v>
       </c>
       <c r="B285" t="e">
         <f>VLOOKUP($A285,統計!$A:$G,2,)</f>
@@ -13670,7 +13718,7 @@
     </row>
     <row r="286" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A286">
-        <v>1606</v>
+        <v>1706</v>
       </c>
       <c r="B286" t="e">
         <f>VLOOKUP($A286,統計!$A:$G,2,)</f>
@@ -13694,7 +13742,7 @@
     </row>
     <row r="287" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A287">
-        <v>1701</v>
+        <v>1801</v>
       </c>
       <c r="B287" t="e">
         <f>VLOOKUP($A287,統計!$A:$G,2,)</f>
@@ -13718,7 +13766,7 @@
     </row>
     <row r="288" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A288">
-        <v>1702</v>
+        <v>1802</v>
       </c>
       <c r="B288" t="e">
         <f>VLOOKUP($A288,統計!$A:$G,2,)</f>
@@ -13742,7 +13790,7 @@
     </row>
     <row r="289" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A289">
-        <v>1703</v>
+        <v>1803</v>
       </c>
       <c r="B289" t="e">
         <f>VLOOKUP($A289,統計!$A:$G,2,)</f>
@@ -13766,7 +13814,7 @@
     </row>
     <row r="290" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A290">
-        <v>1704</v>
+        <v>1804</v>
       </c>
       <c r="B290" t="e">
         <f>VLOOKUP($A290,統計!$A:$G,2,)</f>
@@ -13790,7 +13838,7 @@
     </row>
     <row r="291" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A291">
-        <v>1801</v>
+        <v>1901</v>
       </c>
       <c r="B291" t="e">
         <f>VLOOKUP($A291,統計!$A:$G,2,)</f>
@@ -13814,7 +13862,7 @@
     </row>
     <row r="292" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A292">
-        <v>1802</v>
+        <v>1902</v>
       </c>
       <c r="B292" t="e">
         <f>VLOOKUP($A292,統計!$A:$G,2,)</f>
@@ -13838,7 +13886,7 @@
     </row>
     <row r="293" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A293">
-        <v>1803</v>
+        <v>1903</v>
       </c>
       <c r="B293" t="e">
         <f>VLOOKUP($A293,統計!$A:$G,2,)</f>
@@ -13862,7 +13910,7 @@
     </row>
     <row r="294" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A294">
-        <v>1804</v>
+        <v>1904</v>
       </c>
       <c r="B294" t="e">
         <f>VLOOKUP($A294,統計!$A:$G,2,)</f>
@@ -13886,7 +13934,7 @@
     </row>
     <row r="295" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A295">
-        <v>1805</v>
+        <v>1905</v>
       </c>
       <c r="B295" t="e">
         <f>VLOOKUP($A295,統計!$A:$G,2,)</f>

--- a/5_筆記/閱讀數據.xlsx
+++ b/5_筆記/閱讀數據.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="25928"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="26227"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\self\study\zizhitongjian\5_筆記\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3799E1F8-8B34-4E0B-B1F5-1F86562079F8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6ACF3720-862A-41EA-BB3A-6207F0770878}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="38620" windowHeight="21220" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="統計" sheetId="1" r:id="rId1"/>
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="527" uniqueCount="521">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="528" uniqueCount="522">
   <si>
     <t>索引號</t>
   </si>
@@ -1594,6 +1594,10 @@
   </si>
   <si>
     <t>晉愍帝2年至4年</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>晉元帝至2年</t>
     <phoneticPr fontId="4" type="noConversion"/>
   </si>
 </sst>
@@ -1898,7 +1902,7 @@
             <c:strRef>
               <c:f>統計!$B$2:$B$115</c:f>
               <c:strCache>
-                <c:ptCount val="89"/>
+                <c:ptCount val="90"/>
                 <c:pt idx="0">
                   <c:v>卷1</c:v>
                 </c:pt>
@@ -2165,6 +2169,9 @@
                 </c:pt>
                 <c:pt idx="88">
                   <c:v>卷89</c:v>
+                </c:pt>
+                <c:pt idx="89">
+                  <c:v>卷90</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
@@ -2441,6 +2448,9 @@
                 </c:pt>
                 <c:pt idx="88">
                   <c:v>3.6666666666666665</c:v>
+                </c:pt>
+                <c:pt idx="89">
+                  <c:v>5.5</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -2987,7 +2997,7 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme 2013 - 2022" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
@@ -2995,22 +3005,22 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:R90"/>
-  <sheetFormatPr defaultColWidth="8.625" defaultRowHeight="13.5" x14ac:dyDescent="0.15"/>
+  <dimension ref="A1:R91"/>
+  <sheetFormatPr defaultColWidth="8.6328125" defaultRowHeight="14" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="7.75" customWidth="1"/>
-    <col min="2" max="2" width="5.75" customWidth="1"/>
-    <col min="3" max="4" width="12.75" style="1" customWidth="1"/>
-    <col min="5" max="7" width="9.75" customWidth="1"/>
-    <col min="8" max="8" width="7.75" customWidth="1"/>
-    <col min="9" max="9" width="14.125" customWidth="1"/>
-    <col min="15" max="15" width="16.375" customWidth="1"/>
-    <col min="16" max="16" width="18.625" customWidth="1"/>
-    <col min="17" max="17" width="16.375" customWidth="1"/>
-    <col min="18" max="18" width="18.625" customWidth="1"/>
+    <col min="1" max="1" width="7.7265625" customWidth="1"/>
+    <col min="2" max="2" width="5.7265625" customWidth="1"/>
+    <col min="3" max="4" width="12.7265625" style="1" customWidth="1"/>
+    <col min="5" max="7" width="9.7265625" customWidth="1"/>
+    <col min="8" max="8" width="7.7265625" customWidth="1"/>
+    <col min="9" max="9" width="14.08984375" customWidth="1"/>
+    <col min="15" max="15" width="16.36328125" customWidth="1"/>
+    <col min="16" max="16" width="18.6328125" customWidth="1"/>
+    <col min="17" max="17" width="16.36328125" customWidth="1"/>
+    <col min="18" max="18" width="18.6328125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:18" s="3" customFormat="1" x14ac:dyDescent="0.15">
+    <row r="1" spans="1:18" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -3063,7 +3073,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="2" spans="1:18" x14ac:dyDescent="0.15">
+    <row r="2" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A2">
         <v>101</v>
       </c>
@@ -3110,22 +3120,22 @@
       </c>
       <c r="O2">
         <f t="shared" ref="O2:O8" si="5">L2*$L$10</f>
-        <v>632.62921348314615</v>
+        <v>633.91111111111115</v>
       </c>
       <c r="P2" s="1">
         <f t="shared" ref="P2:P8" si="6">$C$2+O2</f>
-        <v>44651.629213483146</v>
+        <v>44652.911111111112</v>
       </c>
       <c r="Q2">
         <f t="shared" ref="Q2:Q8" si="7">(M2-$F$2)*$L$11</f>
-        <v>666.59113544177046</v>
+        <v>693.78588689311891</v>
       </c>
       <c r="R2" s="1">
         <f t="shared" ref="R2:R8" si="8">$C$2+Q2</f>
-        <v>44685.591135441769</v>
-      </c>
-    </row>
-    <row r="3" spans="1:18" x14ac:dyDescent="0.15">
+        <v>44712.785886893122</v>
+      </c>
+    </row>
+    <row r="3" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A3">
         <v>102</v>
       </c>
@@ -3173,22 +3183,22 @@
       </c>
       <c r="O3">
         <f t="shared" si="5"/>
-        <v>725.66292134831463</v>
+        <v>727.13333333333344</v>
       </c>
       <c r="P3" s="1">
         <f t="shared" si="6"/>
-        <v>44744.662921348317</v>
+        <v>44746.133333333331</v>
       </c>
       <c r="Q3">
         <f t="shared" si="7"/>
-        <v>730.78931863038395</v>
+        <v>760.60314726805814</v>
       </c>
       <c r="R3" s="1">
         <f t="shared" si="8"/>
-        <v>44749.789318630385</v>
-      </c>
-    </row>
-    <row r="4" spans="1:18" x14ac:dyDescent="0.15">
+        <v>44779.603147268055</v>
+      </c>
+    </row>
+    <row r="4" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A4">
         <v>103</v>
       </c>
@@ -3236,22 +3246,22 @@
       </c>
       <c r="O4">
         <f t="shared" si="5"/>
-        <v>1097.7977528089889</v>
+        <v>1100.0222222222224</v>
       </c>
       <c r="P4" s="1">
         <f t="shared" si="6"/>
-        <v>45116.79775280899</v>
+        <v>45119.022222222222</v>
       </c>
       <c r="Q4">
         <f t="shared" si="7"/>
-        <v>880.58507940381548</v>
+        <v>916.5100881429164</v>
       </c>
       <c r="R4" s="1">
         <f t="shared" si="8"/>
-        <v>44899.585079403812</v>
-      </c>
-    </row>
-    <row r="5" spans="1:18" x14ac:dyDescent="0.15">
+        <v>44935.510088142917</v>
+      </c>
+    </row>
+    <row r="5" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A5">
         <v>104</v>
       </c>
@@ -3299,22 +3309,22 @@
       </c>
       <c r="O5">
         <f t="shared" si="5"/>
-        <v>1637.3932584269664</v>
+        <v>1640.7111111111112</v>
       </c>
       <c r="P5" s="1">
         <f t="shared" si="6"/>
-        <v>45656.393258426964</v>
+        <v>45659.711111111108</v>
       </c>
       <c r="Q5">
         <f t="shared" si="7"/>
-        <v>1061.4099620517436</v>
+        <v>1104.7120381989953</v>
       </c>
       <c r="R5" s="1">
         <f t="shared" si="8"/>
-        <v>45080.409962051745</v>
-      </c>
-    </row>
-    <row r="6" spans="1:18" x14ac:dyDescent="0.15">
+        <v>45123.712038198995</v>
+      </c>
+    </row>
+    <row r="6" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A6">
         <v>105</v>
       </c>
@@ -3362,22 +3372,22 @@
       </c>
       <c r="O6">
         <f t="shared" si="5"/>
-        <v>2465.3932584269664</v>
+        <v>2470.3888888888891</v>
       </c>
       <c r="P6" s="1">
         <f t="shared" si="6"/>
-        <v>46484.393258426964</v>
+        <v>46489.388888888891</v>
       </c>
       <c r="Q6">
         <f t="shared" si="7"/>
-        <v>1401.6603329513953</v>
+        <v>1458.843518186173</v>
       </c>
       <c r="R6" s="1">
         <f t="shared" si="8"/>
-        <v>45420.660332951396</v>
-      </c>
-    </row>
-    <row r="7" spans="1:18" x14ac:dyDescent="0.15">
+        <v>45477.843518186171</v>
+      </c>
+    </row>
+    <row r="7" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A7">
         <v>201</v>
       </c>
@@ -3425,22 +3435,22 @@
       </c>
       <c r="O7">
         <f t="shared" si="5"/>
-        <v>2735.1910112359551</v>
+        <v>2740.7333333333336</v>
       </c>
       <c r="P7" s="1">
         <f t="shared" si="6"/>
-        <v>46754.191011235955</v>
+        <v>46759.733333333337</v>
       </c>
       <c r="Q7">
         <f t="shared" si="7"/>
-        <v>1457.298758381527</v>
+        <v>1516.7518105111203</v>
       </c>
       <c r="R7" s="1">
         <f t="shared" si="8"/>
-        <v>45476.298758381527</v>
-      </c>
-    </row>
-    <row r="8" spans="1:18" x14ac:dyDescent="0.15">
+        <v>45535.751810511123</v>
+      </c>
+    </row>
+    <row r="8" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A8">
         <v>202</v>
       </c>
@@ -3488,22 +3498,22 @@
       </c>
       <c r="O8">
         <f t="shared" si="5"/>
-        <v>2735.1910112359551</v>
+        <v>2740.7333333333336</v>
       </c>
       <c r="P8" s="1">
         <f t="shared" si="6"/>
-        <v>46754.191011235955</v>
+        <v>46759.733333333337</v>
       </c>
       <c r="Q8">
         <f t="shared" si="7"/>
-        <v>1457.298758381527</v>
+        <v>1516.7518105111203</v>
       </c>
       <c r="R8" s="1">
         <f t="shared" si="8"/>
-        <v>45476.298758381527</v>
-      </c>
-    </row>
-    <row r="9" spans="1:18" x14ac:dyDescent="0.15">
+        <v>45535.751810511123</v>
+      </c>
+    </row>
+    <row r="9" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A9">
         <v>203</v>
       </c>
@@ -3537,7 +3547,7 @@
         <v>7.5</v>
       </c>
     </row>
-    <row r="10" spans="1:18" x14ac:dyDescent="0.15">
+    <row r="10" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A10">
         <v>301</v>
       </c>
@@ -3575,10 +3585,10 @@
       </c>
       <c r="L10">
         <f>AVERAGE(E:E)</f>
-        <v>9.3033707865168545</v>
-      </c>
-    </row>
-    <row r="11" spans="1:18" x14ac:dyDescent="0.15">
+        <v>9.3222222222222229</v>
+      </c>
+    </row>
+    <row r="11" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A11">
         <v>302</v>
       </c>
@@ -3616,10 +3626,10 @@
       </c>
       <c r="L11">
         <f>AVEDEV(I:I)</f>
-        <v>1.0699697198102254</v>
-      </c>
-    </row>
-    <row r="12" spans="1:18" x14ac:dyDescent="0.15">
+        <v>1.1136210062489871</v>
+      </c>
+    </row>
+    <row r="12" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A12">
         <v>303</v>
       </c>
@@ -3653,7 +3663,7 @@
         <v>2.6666666666666665</v>
       </c>
     </row>
-    <row r="13" spans="1:18" x14ac:dyDescent="0.15">
+    <row r="13" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A13">
         <v>304</v>
       </c>
@@ -3687,7 +3697,7 @@
         <v>0.75</v>
       </c>
     </row>
-    <row r="14" spans="1:18" x14ac:dyDescent="0.15">
+    <row r="14" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A14">
         <v>305</v>
       </c>
@@ -3721,7 +3731,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="15" spans="1:18" x14ac:dyDescent="0.15">
+    <row r="15" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A15">
         <v>306</v>
       </c>
@@ -3755,7 +3765,7 @@
         <v>1.125</v>
       </c>
     </row>
-    <row r="16" spans="1:18" x14ac:dyDescent="0.15">
+    <row r="16" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A16">
         <v>307</v>
       </c>
@@ -3789,7 +3799,7 @@
         <v>0.53333333333333333</v>
       </c>
     </row>
-    <row r="17" spans="1:9" x14ac:dyDescent="0.15">
+    <row r="17" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A17">
         <v>308</v>
       </c>
@@ -3823,7 +3833,7 @@
         <v>0.6428571428571429</v>
       </c>
     </row>
-    <row r="18" spans="1:9" x14ac:dyDescent="0.15">
+    <row r="18" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A18">
         <v>309</v>
       </c>
@@ -3857,7 +3867,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="19" spans="1:9" x14ac:dyDescent="0.15">
+    <row r="19" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A19">
         <v>310</v>
       </c>
@@ -3891,7 +3901,7 @@
         <v>0.77777777777777779</v>
       </c>
     </row>
-    <row r="20" spans="1:9" x14ac:dyDescent="0.15">
+    <row r="20" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A20">
         <v>311</v>
       </c>
@@ -3925,7 +3935,7 @@
         <v>1.5</v>
       </c>
     </row>
-    <row r="21" spans="1:9" x14ac:dyDescent="0.15">
+    <row r="21" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A21">
         <v>312</v>
       </c>
@@ -3959,7 +3969,7 @@
         <v>0.77777777777777779</v>
       </c>
     </row>
-    <row r="22" spans="1:9" x14ac:dyDescent="0.15">
+    <row r="22" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A22">
         <v>313</v>
       </c>
@@ -3993,7 +4003,7 @@
         <v>0.63636363636363635</v>
       </c>
     </row>
-    <row r="23" spans="1:9" x14ac:dyDescent="0.15">
+    <row r="23" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A23">
         <v>314</v>
       </c>
@@ -4027,7 +4037,7 @@
         <v>0.66666666666666663</v>
       </c>
     </row>
-    <row r="24" spans="1:9" x14ac:dyDescent="0.15">
+    <row r="24" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A24">
         <v>315</v>
       </c>
@@ -4061,7 +4071,7 @@
         <v>0.83333333333333337</v>
       </c>
     </row>
-    <row r="25" spans="1:9" x14ac:dyDescent="0.15">
+    <row r="25" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A25">
         <v>316</v>
       </c>
@@ -4095,7 +4105,7 @@
         <v>1.2857142857142858</v>
       </c>
     </row>
-    <row r="26" spans="1:9" x14ac:dyDescent="0.15">
+    <row r="26" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A26">
         <v>317</v>
       </c>
@@ -4129,7 +4139,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="27" spans="1:9" x14ac:dyDescent="0.15">
+    <row r="27" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A27">
         <v>318</v>
       </c>
@@ -4163,7 +4173,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="28" spans="1:9" x14ac:dyDescent="0.15">
+    <row r="28" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A28">
         <v>319</v>
       </c>
@@ -4197,7 +4207,7 @@
         <v>0.7</v>
       </c>
     </row>
-    <row r="29" spans="1:9" x14ac:dyDescent="0.15">
+    <row r="29" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A29">
         <v>320</v>
       </c>
@@ -4231,7 +4241,7 @@
         <v>0.7142857142857143</v>
       </c>
     </row>
-    <row r="30" spans="1:9" x14ac:dyDescent="0.15">
+    <row r="30" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A30">
         <v>321</v>
       </c>
@@ -4265,7 +4275,7 @@
         <v>0.77777777777777779</v>
       </c>
     </row>
-    <row r="31" spans="1:9" x14ac:dyDescent="0.15">
+    <row r="31" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A31">
         <v>322</v>
       </c>
@@ -4299,7 +4309,7 @@
         <v>0.9</v>
       </c>
     </row>
-    <row r="32" spans="1:9" x14ac:dyDescent="0.15">
+    <row r="32" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A32">
         <v>323</v>
       </c>
@@ -4333,7 +4343,7 @@
         <v>0.88888888888888884</v>
       </c>
     </row>
-    <row r="33" spans="1:9" x14ac:dyDescent="0.15">
+    <row r="33" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A33">
         <v>324</v>
       </c>
@@ -4367,7 +4377,7 @@
         <v>0.83333333333333337</v>
       </c>
     </row>
-    <row r="34" spans="1:9" x14ac:dyDescent="0.15">
+    <row r="34" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A34">
         <v>325</v>
       </c>
@@ -4401,7 +4411,7 @@
         <v>2.5</v>
       </c>
     </row>
-    <row r="35" spans="1:9" x14ac:dyDescent="0.15">
+    <row r="35" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A35">
         <v>326</v>
       </c>
@@ -4435,7 +4445,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="36" spans="1:9" x14ac:dyDescent="0.15">
+    <row r="36" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A36">
         <v>327</v>
       </c>
@@ -4469,7 +4479,7 @@
         <v>1.25</v>
       </c>
     </row>
-    <row r="37" spans="1:9" x14ac:dyDescent="0.15">
+    <row r="37" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A37">
         <v>328</v>
       </c>
@@ -4503,7 +4513,7 @@
         <v>0.83333333333333337</v>
       </c>
     </row>
-    <row r="38" spans="1:9" x14ac:dyDescent="0.15">
+    <row r="38" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A38">
         <v>401</v>
       </c>
@@ -4537,7 +4547,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="39" spans="1:9" x14ac:dyDescent="0.15">
+    <row r="39" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A39">
         <v>402</v>
       </c>
@@ -4571,7 +4581,7 @@
         <v>0.875</v>
       </c>
     </row>
-    <row r="40" spans="1:9" x14ac:dyDescent="0.15">
+    <row r="40" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A40">
         <v>403</v>
       </c>
@@ -4605,7 +4615,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="41" spans="1:9" x14ac:dyDescent="0.15">
+    <row r="41" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A41">
         <v>501</v>
       </c>
@@ -4639,7 +4649,7 @@
         <v>3.5</v>
       </c>
     </row>
-    <row r="42" spans="1:9" x14ac:dyDescent="0.15">
+    <row r="42" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A42">
         <v>502</v>
       </c>
@@ -4673,7 +4683,7 @@
         <v>2.6666666666666665</v>
       </c>
     </row>
-    <row r="43" spans="1:9" x14ac:dyDescent="0.15">
+    <row r="43" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A43">
         <v>503</v>
       </c>
@@ -4707,7 +4717,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="44" spans="1:9" x14ac:dyDescent="0.15">
+    <row r="44" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A44">
         <v>504</v>
       </c>
@@ -4741,7 +4751,7 @@
         <v>0.72727272727272729</v>
       </c>
     </row>
-    <row r="45" spans="1:9" x14ac:dyDescent="0.15">
+    <row r="45" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A45">
         <v>505</v>
       </c>
@@ -4775,7 +4785,7 @@
         <v>0.5714285714285714</v>
       </c>
     </row>
-    <row r="46" spans="1:9" x14ac:dyDescent="0.15">
+    <row r="46" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A46">
         <v>506</v>
       </c>
@@ -4809,7 +4819,7 @@
         <v>0.6</v>
       </c>
     </row>
-    <row r="47" spans="1:9" x14ac:dyDescent="0.15">
+    <row r="47" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A47">
         <v>507</v>
       </c>
@@ -4844,7 +4854,7 @@
         <v>0.77777777777777779</v>
       </c>
     </row>
-    <row r="48" spans="1:9" x14ac:dyDescent="0.15">
+    <row r="48" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A48">
         <v>508</v>
       </c>
@@ -4879,7 +4889,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="49" spans="1:9" x14ac:dyDescent="0.15">
+    <row r="49" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A49">
         <v>509</v>
       </c>
@@ -4914,7 +4924,7 @@
         <v>0.5714285714285714</v>
       </c>
     </row>
-    <row r="50" spans="1:9" x14ac:dyDescent="0.15">
+    <row r="50" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A50">
         <v>510</v>
       </c>
@@ -4949,7 +4959,7 @@
         <v>0.9</v>
       </c>
     </row>
-    <row r="51" spans="1:9" x14ac:dyDescent="0.15">
+    <row r="51" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A51">
         <v>511</v>
       </c>
@@ -4984,7 +4994,7 @@
         <v>1.1111111111111112</v>
       </c>
     </row>
-    <row r="52" spans="1:9" x14ac:dyDescent="0.15">
+    <row r="52" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A52">
         <v>512</v>
       </c>
@@ -5019,7 +5029,7 @@
         <v>0.88888888888888884</v>
       </c>
     </row>
-    <row r="53" spans="1:9" x14ac:dyDescent="0.15">
+    <row r="53" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A53">
         <v>513</v>
       </c>
@@ -5054,7 +5064,7 @@
         <v>0.75</v>
       </c>
     </row>
-    <row r="54" spans="1:9" x14ac:dyDescent="0.15">
+    <row r="54" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A54">
         <v>514</v>
       </c>
@@ -5089,7 +5099,7 @@
         <v>0.72727272727272729</v>
       </c>
     </row>
-    <row r="55" spans="1:9" x14ac:dyDescent="0.15">
+    <row r="55" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A55">
         <v>515</v>
       </c>
@@ -5124,7 +5134,7 @@
         <v>1.1428571428571428</v>
       </c>
     </row>
-    <row r="56" spans="1:9" x14ac:dyDescent="0.15">
+    <row r="56" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A56">
         <v>516</v>
       </c>
@@ -5159,7 +5169,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="57" spans="1:9" x14ac:dyDescent="0.15">
+    <row r="57" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A57">
         <v>517</v>
       </c>
@@ -5194,7 +5204,7 @@
         <v>1.4</v>
       </c>
     </row>
-    <row r="58" spans="1:9" x14ac:dyDescent="0.15">
+    <row r="58" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A58">
         <v>518</v>
       </c>
@@ -5229,7 +5239,7 @@
         <v>0.88888888888888884</v>
       </c>
     </row>
-    <row r="59" spans="1:9" x14ac:dyDescent="0.15">
+    <row r="59" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A59">
         <v>519</v>
       </c>
@@ -5264,7 +5274,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="60" spans="1:9" x14ac:dyDescent="0.15">
+    <row r="60" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A60">
         <v>520</v>
       </c>
@@ -5299,7 +5309,7 @@
         <v>2.6666666666666665</v>
       </c>
     </row>
-    <row r="61" spans="1:9" x14ac:dyDescent="0.15">
+    <row r="61" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A61">
         <v>521</v>
       </c>
@@ -5334,7 +5344,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="62" spans="1:9" x14ac:dyDescent="0.15">
+    <row r="62" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A62">
         <v>522</v>
       </c>
@@ -5369,7 +5379,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="63" spans="1:9" x14ac:dyDescent="0.15">
+    <row r="63" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A63">
         <v>523</v>
       </c>
@@ -5404,7 +5414,7 @@
         <v>2.6666666666666665</v>
       </c>
     </row>
-    <row r="64" spans="1:9" x14ac:dyDescent="0.15">
+    <row r="64" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A64">
         <v>524</v>
       </c>
@@ -5439,7 +5449,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="65" spans="1:9" x14ac:dyDescent="0.15">
+    <row r="65" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A65">
         <v>525</v>
       </c>
@@ -5474,12 +5484,12 @@
         <v>1.6</v>
       </c>
     </row>
-    <row r="66" spans="1:9" x14ac:dyDescent="0.15">
+    <row r="66" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A66">
         <v>526</v>
       </c>
       <c r="B66" t="str">
-        <f t="shared" ref="B66:B90" si="16">"卷"&amp;ROW(B65)</f>
+        <f t="shared" ref="B66:B91" si="16">"卷"&amp;ROW(B65)</f>
         <v>卷65</v>
       </c>
       <c r="C66" s="1">
@@ -5509,7 +5519,7 @@
         <v>2.6666666666666665</v>
       </c>
     </row>
-    <row r="67" spans="1:9" x14ac:dyDescent="0.15">
+    <row r="67" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A67">
         <v>527</v>
       </c>
@@ -5544,7 +5554,7 @@
         <v>1.8</v>
       </c>
     </row>
-    <row r="68" spans="1:9" x14ac:dyDescent="0.15">
+    <row r="68" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A68">
         <v>528</v>
       </c>
@@ -5579,7 +5589,7 @@
         <v>2.3333333333333335</v>
       </c>
     </row>
-    <row r="69" spans="1:9" x14ac:dyDescent="0.15">
+    <row r="69" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A69">
         <v>529</v>
       </c>
@@ -5614,7 +5624,7 @@
         <v>2.3333333333333335</v>
       </c>
     </row>
-    <row r="70" spans="1:9" x14ac:dyDescent="0.15">
+    <row r="70" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A70">
         <v>601</v>
       </c>
@@ -5648,7 +5658,7 @@
         <v>2.3333333333333335</v>
       </c>
     </row>
-    <row r="71" spans="1:9" x14ac:dyDescent="0.15">
+    <row r="71" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A71">
         <v>602</v>
       </c>
@@ -5683,7 +5693,7 @@
         <v>1.4</v>
       </c>
     </row>
-    <row r="72" spans="1:9" x14ac:dyDescent="0.15">
+    <row r="72" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A72">
         <v>603</v>
       </c>
@@ -5718,7 +5728,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="73" spans="1:9" x14ac:dyDescent="0.15">
+    <row r="73" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A73">
         <v>604</v>
       </c>
@@ -5753,7 +5763,7 @@
         <v>1.75</v>
       </c>
     </row>
-    <row r="74" spans="1:9" x14ac:dyDescent="0.15">
+    <row r="74" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A74">
         <v>605</v>
       </c>
@@ -5788,7 +5798,7 @@
         <v>1.6666666666666667</v>
       </c>
     </row>
-    <row r="75" spans="1:9" x14ac:dyDescent="0.15">
+    <row r="75" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A75">
         <v>606</v>
       </c>
@@ -5823,7 +5833,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="76" spans="1:9" x14ac:dyDescent="0.15">
+    <row r="76" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A76">
         <v>607</v>
       </c>
@@ -5858,7 +5868,7 @@
         <v>1.1428571428571428</v>
       </c>
     </row>
-    <row r="77" spans="1:9" x14ac:dyDescent="0.15">
+    <row r="77" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A77">
         <v>608</v>
       </c>
@@ -5893,7 +5903,7 @@
         <v>2.3333333333333335</v>
       </c>
     </row>
-    <row r="78" spans="1:9" x14ac:dyDescent="0.15">
+    <row r="78" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A78">
         <v>609</v>
       </c>
@@ -5928,7 +5938,7 @@
         <v>1.3333333333333333</v>
       </c>
     </row>
-    <row r="79" spans="1:9" x14ac:dyDescent="0.15">
+    <row r="79" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A79">
         <v>610</v>
       </c>
@@ -5963,7 +5973,7 @@
         <v>2.3333333333333335</v>
       </c>
     </row>
-    <row r="80" spans="1:9" x14ac:dyDescent="0.15">
+    <row r="80" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A80">
         <v>701</v>
       </c>
@@ -5997,7 +6007,7 @@
         <v>1.25</v>
       </c>
     </row>
-    <row r="81" spans="1:9" x14ac:dyDescent="0.15">
+    <row r="81" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A81">
         <v>702</v>
       </c>
@@ -6031,7 +6041,7 @@
         <v>1.2857142857142858</v>
       </c>
     </row>
-    <row r="82" spans="1:9" x14ac:dyDescent="0.15">
+    <row r="82" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A82">
         <v>703</v>
       </c>
@@ -6065,7 +6075,7 @@
         <v>0.88888888888888884</v>
       </c>
     </row>
-    <row r="83" spans="1:9" x14ac:dyDescent="0.15">
+    <row r="83" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A83">
         <v>704</v>
       </c>
@@ -6099,7 +6109,7 @@
         <v>1.5</v>
       </c>
     </row>
-    <row r="84" spans="1:9" x14ac:dyDescent="0.15">
+    <row r="84" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A84">
         <v>705</v>
       </c>
@@ -6133,7 +6143,7 @@
         <v>4.5</v>
       </c>
     </row>
-    <row r="85" spans="1:9" x14ac:dyDescent="0.15">
+    <row r="85" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A85">
         <v>706</v>
       </c>
@@ -6167,7 +6177,7 @@
         <v>6.5</v>
       </c>
     </row>
-    <row r="86" spans="1:9" x14ac:dyDescent="0.15">
+    <row r="86" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A86">
         <v>707</v>
       </c>
@@ -6201,7 +6211,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="87" spans="1:9" x14ac:dyDescent="0.15">
+    <row r="87" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A87">
         <v>708</v>
       </c>
@@ -6235,7 +6245,7 @@
         <v>3.75</v>
       </c>
     </row>
-    <row r="88" spans="1:9" x14ac:dyDescent="0.15">
+    <row r="88" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A88">
         <v>709</v>
       </c>
@@ -6270,7 +6280,7 @@
         <v>5.333333333333333</v>
       </c>
     </row>
-    <row r="89" spans="1:9" x14ac:dyDescent="0.15">
+    <row r="89" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A89">
         <v>710</v>
       </c>
@@ -6305,7 +6315,7 @@
         <v>5.5</v>
       </c>
     </row>
-    <row r="90" spans="1:9" x14ac:dyDescent="0.15">
+    <row r="90" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A90">
         <v>711</v>
       </c>
@@ -6336,8 +6346,42 @@
         <v>3</v>
       </c>
       <c r="I90">
-        <f t="shared" ref="I90" si="44">E90/H90</f>
+        <f t="shared" ref="I90:I91" si="44">E90/H90</f>
         <v>3.6666666666666665</v>
+      </c>
+    </row>
+    <row r="91" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A91">
+        <v>801</v>
+      </c>
+      <c r="B91" t="str">
+        <f t="shared" si="16"/>
+        <v>卷90</v>
+      </c>
+      <c r="C91" s="1">
+        <v>45019</v>
+      </c>
+      <c r="D91" s="1">
+        <v>45029</v>
+      </c>
+      <c r="E91">
+        <f t="shared" ref="E91" si="45">D91-C91+1</f>
+        <v>11</v>
+      </c>
+      <c r="F91">
+        <f t="shared" ref="F91" si="46">G90+1</f>
+        <v>317</v>
+      </c>
+      <c r="G91">
+        <v>318</v>
+      </c>
+      <c r="H91">
+        <f t="shared" ref="H91" si="47">IF(F91*G91&lt;0,ABS(F91)+ABS(G91),G91-F91+1)</f>
+        <v>2</v>
+      </c>
+      <c r="I91">
+        <f t="shared" si="44"/>
+        <v>5.5</v>
       </c>
     </row>
   </sheetData>
@@ -6351,14 +6395,14 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:I295"/>
-  <sheetFormatPr defaultColWidth="8.625" defaultRowHeight="13.5" x14ac:dyDescent="0.15"/>
+  <sheetFormatPr defaultColWidth="8.6328125" defaultRowHeight="14" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="6" max="6" width="33.375" customWidth="1"/>
-    <col min="7" max="7" width="22.125" customWidth="1"/>
+    <col min="6" max="6" width="33.36328125" customWidth="1"/>
+    <col min="7" max="7" width="22.08984375" customWidth="1"/>
     <col min="8" max="8" width="22" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9" s="3" customFormat="1" x14ac:dyDescent="0.15">
+    <row r="1" spans="1:9" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1" s="3" t="s">
         <v>0</v>
       </c>
@@ -6387,7 +6431,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="2" spans="1:9" x14ac:dyDescent="0.15">
+    <row r="2" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A2">
         <v>101</v>
       </c>
@@ -6417,7 +6461,7 @@
         <v>101|[卷1](5_筆記/资治通鉴1.html)|周紀一|-403|-369|趙建國前世系圖、趙建國前傳位圖、魏建國前傳位圖、韓建國前傳位圖、田氏代齊前傳位圖、秦四代亂政世系圖、秦四代亂政傳位圖||周威烈王23年至24年、周安王共26年、周烈王至7年</v>
       </c>
     </row>
-    <row r="3" spans="1:9" x14ac:dyDescent="0.15">
+    <row r="3" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A3">
         <v>102</v>
       </c>
@@ -6450,7 +6494,7 @@
         <v>102|[卷2](5_筆記/资治通鉴2.html)|周紀二|-368|-321|齊威王時期諸田譜系|商鞅二十等爵|周顯王共48年</v>
       </c>
     </row>
-    <row r="4" spans="1:9" x14ac:dyDescent="0.15">
+    <row r="4" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A4">
         <v>103</v>
       </c>
@@ -6480,7 +6524,7 @@
         <v>103|[卷3](5_筆記/资治通鉴3.html)|周紀三|-320|-298||古蜀國世系|周慎靚王共6年、周赧王至17年</v>
       </c>
     </row>
-    <row r="5" spans="1:9" x14ac:dyDescent="0.15">
+    <row r="5" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A5">
         <v>104</v>
       </c>
@@ -6510,7 +6554,7 @@
         <v>104|[卷4](5_筆記/资治通鉴4.html)|周紀四|-297|-273||楚国都城与各种郢都、西周國、東周國|周赧王18年至42年</v>
       </c>
     </row>
-    <row r="6" spans="1:9" x14ac:dyDescent="0.15">
+    <row r="6" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A6">
         <v>105</v>
       </c>
@@ -6540,7 +6584,7 @@
         <v>105|[卷5](5_筆記/资治通鉴5.html)|周紀五|-272|-256|孔子世系簡圖(至秦)、秦始皇關系圖||周赧王43年至59年</v>
       </c>
     </row>
-    <row r="7" spans="1:9" x14ac:dyDescent="0.15">
+    <row r="7" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A7">
         <v>201</v>
       </c>
@@ -6570,7 +6614,7 @@
         <v>201|[卷6](5_筆記/资治通鉴6.html)|秦紀一|-255|-228||韓國都城變遷史|秦昭襄王52年至56年、秦孝文王共1年、秦莊襄王共3年、秦王政至19年</v>
       </c>
     </row>
-    <row r="8" spans="1:9" x14ac:dyDescent="0.15">
+    <row r="8" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A8">
         <v>202</v>
       </c>
@@ -6600,7 +6644,7 @@
         <v>202|[卷7](5_筆記/资治通鉴7.html)|秦紀二|-227|-209|王翦家族、蒙驁家族、項燕家族||秦始皇20年至37年、秦二世元年</v>
       </c>
     </row>
-    <row r="9" spans="1:9" x14ac:dyDescent="0.15">
+    <row r="9" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A9">
         <v>203</v>
       </c>
@@ -6627,7 +6671,7 @@
         <v>203|[卷8](5_筆記/资治通鉴8.html)|秦紀三|-208|-207|||秦二世2年至3年</v>
       </c>
     </row>
-    <row r="10" spans="1:9" x14ac:dyDescent="0.15">
+    <row r="10" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A10">
         <v>301</v>
       </c>
@@ -6660,7 +6704,7 @@
         <v>301|[卷9](5_筆記/资治通鉴9.html)|漢紀一|-206|-205|秦末漢初政權逗逼分裂圖|歷代歲首表|楚漢至2年</v>
       </c>
     </row>
-    <row r="11" spans="1:9" x14ac:dyDescent="0.15">
+    <row r="11" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A11">
         <v>302</v>
       </c>
@@ -6690,7 +6734,7 @@
         <v>302|[卷10](5_筆記/资治通鉴10.html)|漢紀二|-204|-203||周禮宴請等級、韓信戰役表|楚漢3年至4年</v>
       </c>
     </row>
-    <row r="12" spans="1:9" x14ac:dyDescent="0.15">
+    <row r="12" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A12">
         <v>303</v>
       </c>
@@ -6720,7 +6764,7 @@
         <v>303|[卷11](5_筆記/资治通鉴11.html)|漢紀三|-202|-200||詔書形式、驛站交通規格、鞋類型|漢高祖5年至7年</v>
       </c>
     </row>
-    <row r="13" spans="1:9" x14ac:dyDescent="0.15">
+    <row r="13" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A13">
         <v>304</v>
       </c>
@@ -6747,7 +6791,7 @@
         <v>304|[卷12](5_筆記/资治通鉴12.html)|漢紀四|-199|-188|||漢高祖8年至12年、漢惠帝共7年</v>
       </c>
     </row>
-    <row r="14" spans="1:9" x14ac:dyDescent="0.15">
+    <row r="14" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A14">
         <v>305</v>
       </c>
@@ -6780,7 +6824,7 @@
         <v>305|[卷13](5_筆記/资治通鉴13.html)|漢紀五|-187|-178|諸呂世系圖|漢惠帝掛名子嗣表|漢高后共8年、漢文帝至2年</v>
       </c>
     </row>
-    <row r="15" spans="1:9" x14ac:dyDescent="0.15">
+    <row r="15" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A15">
         <v>306</v>
       </c>
@@ -6810,7 +6854,7 @@
         <v>306|[卷14](5_筆記/资治通鉴14.html)|漢紀六|-177|-170||漢歷代皇帝生前廟名、大夫罪名表、各類彗星|漢文帝3年至10年</v>
       </c>
     </row>
-    <row r="16" spans="1:9" x14ac:dyDescent="0.15">
+    <row r="16" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A16">
         <v>307</v>
       </c>
@@ -6840,7 +6884,7 @@
         <v>307|[卷15](5_筆記/资治通鉴15.html)|漢紀七|-169|-155||秦漢三公九卿概要|漢文帝11年至23年、漢景帝至2年</v>
       </c>
     </row>
-    <row r="17" spans="1:9" x14ac:dyDescent="0.15">
+    <row r="17" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A17">
         <v>308</v>
       </c>
@@ -6873,7 +6917,7 @@
         <v>308|[卷16](5_筆記/资治通鉴16.html)|漢紀八|-154|-141|七國之亂世系圖、臧兒田竇世系圖|漢兵役類型(昭帝紀注)|漢景帝3年至16年</v>
       </c>
     </row>
-    <row r="18" spans="1:9" x14ac:dyDescent="0.15">
+    <row r="18" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A18">
         <v>309</v>
       </c>
@@ -6906,7 +6950,7 @@
         <v>309|[卷17](5_筆記/资治通鉴17.html)|漢紀九|-140|-134|衛霍裙帶世系|牢獄別稱|漢武帝至7年</v>
       </c>
     </row>
-    <row r="19" spans="1:9" x14ac:dyDescent="0.15">
+    <row r="19" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A19">
         <v>310</v>
       </c>
@@ -6936,7 +6980,7 @@
         <v>310|[卷18](5_筆記/资治通鉴18.html)|漢紀十|-133|-125||武帝時期漢匈重要戰役|漢武帝8年至16年</v>
       </c>
     </row>
-    <row r="20" spans="1:9" x14ac:dyDescent="0.15">
+    <row r="20" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A20">
         <v>311</v>
       </c>
@@ -6969,7 +7013,7 @@
         <v>311|[卷19](5_筆記/资治通鉴19.html)|漢紀十一|-124|-119|淮南衡山謀反世系、死守外戚的平陽侯曹氏|武功爵表、張騫兩次探索各國紀要、白鹿皮幣|漢武帝17年至22年</v>
       </c>
     </row>
-    <row r="21" spans="1:9" x14ac:dyDescent="0.15">
+    <row r="21" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A21">
         <v>312</v>
       </c>
@@ -6999,7 +7043,7 @@
         <v>312|[卷20](5_筆記/资治通鉴20.html)|漢紀十二|-118|-110||西南諸夷|漢武帝23年至31年</v>
       </c>
     </row>
-    <row r="22" spans="1:9" x14ac:dyDescent="0.15">
+    <row r="22" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A22">
         <v>313</v>
       </c>
@@ -7026,7 +7070,7 @@
         <v>313|[卷21](5_筆記/资治通鉴21.html)|漢紀十三|-109|-99|||漢武帝32年至42年</v>
       </c>
     </row>
-    <row r="23" spans="1:9" x14ac:dyDescent="0.15">
+    <row r="23" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A23">
         <v>314</v>
       </c>
@@ -7056,7 +7100,7 @@
         <v>314|[卷22](5_筆記/资治通鉴22.html)|漢紀十四|-98|-87||漢朝匈奴官制、漢武帝子嗣、人臣功五品|漢武帝43年至54年</v>
       </c>
     </row>
-    <row r="24" spans="1:9" x14ac:dyDescent="0.15">
+    <row r="24" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A24">
         <v>315</v>
       </c>
@@ -7086,7 +7130,7 @@
         <v>315|[卷23](5_筆記/资治通鉴23.html)|漢紀十五|-86|-75|匈奴五單于爭立背景、假設蓋主嫁王充、上官皇后世系||漢昭帝至12年</v>
       </c>
     </row>
-    <row r="25" spans="1:9" x14ac:dyDescent="0.15">
+    <row r="25" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A25">
         <v>316</v>
       </c>
@@ -7119,7 +7163,7 @@
         <v>316|[卷24](5_筆記/资治通鉴24.html)|漢紀十六|-74|-68|漢武帝子嗣皇帝示意圖、霍光世系|西漢綬帶顏色、各時代盜墓信息|漢昭帝13年、漢廢帝、漢宣帝至6年</v>
       </c>
     </row>
-    <row r="26" spans="1:9" x14ac:dyDescent="0.15">
+    <row r="26" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A26">
         <v>317</v>
       </c>
@@ -7149,7 +7193,7 @@
         <v>317|[卷25](5_筆記/资治通鉴25.html)|漢紀十七|-67|-62||五爭車師|漢宣帝7年至12年</v>
       </c>
     </row>
-    <row r="27" spans="1:9" x14ac:dyDescent="0.15">
+    <row r="27" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A27">
         <v>318</v>
       </c>
@@ -7176,7 +7220,7 @@
         <v>318|[卷26](5_筆記/资治通鉴26.html)|漢紀十八|-61|-59|||漢宣帝13年至15年</v>
       </c>
     </row>
-    <row r="28" spans="1:9" x14ac:dyDescent="0.15">
+    <row r="28" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A28">
         <v>319</v>
       </c>
@@ -7209,7 +7253,7 @@
         <v>319|[卷27](5_筆記/资治通鉴27.html)|漢紀十九|-58|-49|麒麟閣十一功臣成分|五單于爭立表|漢宣帝16年至25年</v>
       </c>
     </row>
-    <row r="29" spans="1:9" x14ac:dyDescent="0.15">
+    <row r="29" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A29">
         <v>320</v>
       </c>
@@ -7239,7 +7283,7 @@
         <v>320|[卷28](5_筆記/资治通鉴28.html)|漢紀二十|-48|-42||蕭史黨爭表、舜命九官（尚書）|漢元帝至7年</v>
       </c>
     </row>
-    <row r="30" spans="1:9" x14ac:dyDescent="0.15">
+    <row r="30" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A30">
         <v>321</v>
       </c>
@@ -7269,7 +7313,7 @@
         <v>321|[卷29](5_筆記/资治通鉴29.html)|漢紀二十一|-41|-33|金日磾及班彪世系||漢元帝8年至16年</v>
       </c>
     </row>
-    <row r="31" spans="1:9" x14ac:dyDescent="0.15">
+    <row r="31" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A31">
         <v>322</v>
       </c>
@@ -7299,7 +7343,7 @@
         <v>322|[卷30](5_筆記/资治通鉴30.html)|漢紀二十二|-32|-23|呼韓邪世系||漢成帝至10年</v>
       </c>
     </row>
-    <row r="32" spans="1:9" x14ac:dyDescent="0.15">
+    <row r="32" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A32">
         <v>323</v>
       </c>
@@ -7332,7 +7376,7 @@
         <v>323|[卷31](5_筆記/资治通鉴31.html)|漢紀二十三|-22|-14|許平君世系、班氏世系|墳形製|漢成帝11年19年</v>
       </c>
     </row>
-    <row r="33" spans="1:9" x14ac:dyDescent="0.15">
+    <row r="33" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A33">
         <v>324</v>
       </c>
@@ -7362,7 +7406,7 @@
         <v>324|[卷32](5_筆記/资治通鉴32.html)|漢紀二十四|-13|-8|馮奉世世系||漢成帝20年至25年</v>
       </c>
     </row>
-    <row r="34" spans="1:9" x14ac:dyDescent="0.15">
+    <row r="34" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A34">
         <v>325</v>
       </c>
@@ -7392,7 +7436,7 @@
         <v>325|[卷33](5_筆記/资治通鉴33.html)|漢紀二十五|-7|-6|傅丁太后世系||漢成帝26年、漢哀帝元年</v>
       </c>
     </row>
-    <row r="35" spans="1:9" x14ac:dyDescent="0.15">
+    <row r="35" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A35">
         <v>326</v>
       </c>
@@ -7422,7 +7466,7 @@
         <v>326|[卷34](5_筆記/资治通鉴34.html)|漢紀二十六|-5|-3||西漢帝王男寵表|漢哀帝2年至4年</v>
       </c>
     </row>
-    <row r="36" spans="1:9" x14ac:dyDescent="0.15">
+    <row r="36" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A36">
         <v>327</v>
       </c>
@@ -7455,7 +7499,7 @@
         <v>327|[卷35](5_筆記/资治通鉴35.html)|漢紀二十七|-2|2|衛子夫後衛氏世系|新三公分職|漢哀帝5年至6年、漢平帝至2年</v>
       </c>
     </row>
-    <row r="37" spans="1:9" x14ac:dyDescent="0.15">
+    <row r="37" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A37">
         <v>328</v>
       </c>
@@ -7485,7 +7529,7 @@
         <v>328|[卷36](5_筆記/资治通鉴36.html)|漢紀二十八|3|8||九錫之法|漢平帝3年至6年、王莽居攝、始初至3年</v>
       </c>
     </row>
-    <row r="38" spans="1:9" x14ac:dyDescent="0.15">
+    <row r="38" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A38">
         <v>401</v>
       </c>
@@ -7515,7 +7559,7 @@
         <v>401|[卷37](5_筆記/资治通鉴37.html)|漢紀二十九|9|14||王莽十一公表、漢官儀印制|王莽至6年</v>
       </c>
     </row>
-    <row r="39" spans="1:9" x14ac:dyDescent="0.15">
+    <row r="39" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A39">
         <v>402</v>
       </c>
@@ -7545,7 +7589,7 @@
         <v>402|[卷38](5_筆記/资治通鉴38.html)|漢紀三十|15|22||王莽滅親表、周禮天子六宮制度、六宮安置表|王莽7年至14年</v>
       </c>
     </row>
-    <row r="40" spans="1:9" x14ac:dyDescent="0.15">
+    <row r="40" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A40">
         <v>403</v>
       </c>
@@ -7575,7 +7619,7 @@
         <v>403|[卷39](5_筆記/资治通鉴39.html)|漢紀三十一|23|24||東漢幽州十郡、銅馬諸賊表|王莽15年、玄漢至2年</v>
       </c>
     </row>
-    <row r="41" spans="1:9" x14ac:dyDescent="0.15">
+    <row r="41" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A41">
         <v>501</v>
       </c>
@@ -7602,7 +7646,7 @@
         <v>501|[卷40](5_筆記/资治通鉴40.html)|漢紀三十二|25|26|||漢光武帝至2年</v>
       </c>
     </row>
-    <row r="42" spans="1:9" x14ac:dyDescent="0.15">
+    <row r="42" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A42">
         <v>502</v>
       </c>
@@ -7632,7 +7676,7 @@
         <v>502|[卷41](5_筆記/资治通鉴41.html)|漢紀三十三|27|29|耿氏世系、莎車王世系||漢光武帝3年至5年</v>
       </c>
     </row>
-    <row r="43" spans="1:9" x14ac:dyDescent="0.15">
+    <row r="43" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A43">
         <v>503</v>
       </c>
@@ -7662,7 +7706,7 @@
         <v>503|[卷42](5_筆記/资治通鉴42.html)|漢紀三十四|30|35|陰氏世系||漢光武帝6年至11年</v>
       </c>
     </row>
-    <row r="44" spans="1:9" x14ac:dyDescent="0.15">
+    <row r="44" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A44">
         <v>504</v>
       </c>
@@ -7692,7 +7736,7 @@
         <v>504|[卷43](5_筆記/资治通鉴43.html)|漢紀三十五|36|46||羌人諸种、光武子嗣表|漢光武帝12年至22年</v>
       </c>
     </row>
-    <row r="45" spans="1:9" x14ac:dyDescent="0.15">
+    <row r="45" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A45">
         <v>505</v>
       </c>
@@ -7722,7 +7766,7 @@
         <v>505|[卷44](5_筆記/资治通鉴44.html)|漢紀三十六|47|60||光武官員俸祿表|漢光武帝23年至33年、漢明帝至3年</v>
       </c>
     </row>
-    <row r="46" spans="1:9" x14ac:dyDescent="0.15">
+    <row r="46" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A46">
         <v>506</v>
       </c>
@@ -7755,7 +7799,7 @@
         <v>506|[卷45](5_筆記/资治通鉴45.html)|漢紀三十七|61|75|南陽樊氏世系、扶風馬氏世系|西遊記人物原型、黃河改道概況|漢明帝4年至18年</v>
       </c>
     </row>
-    <row r="47" spans="1:9" x14ac:dyDescent="0.15">
+    <row r="47" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A47">
         <v>507</v>
       </c>
@@ -7785,7 +7829,7 @@
         <v>507|[卷46](5_筆記/资治通鉴46.html)|漢紀三十八|76|84|二宋二梁貴人世系||漢章帝至9年</v>
       </c>
     </row>
-    <row r="48" spans="1:9" x14ac:dyDescent="0.15">
+    <row r="48" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A48">
         <v>508</v>
       </c>
@@ -7818,7 +7862,7 @@
         <v>508|[卷47](5_筆記/资治通鉴47.html)|漢紀三十九|85|91|漢龜茲王世系|六代之樂、西漢皇后外戚結局表|漢章帝10年至13年、漢和帝至3年</v>
       </c>
     </row>
-    <row r="49" spans="1:9" x14ac:dyDescent="0.15">
+    <row r="49" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A49">
         <v>509</v>
       </c>
@@ -7848,7 +7892,7 @@
         <v>509|[卷48](5_筆記/资治通鉴48.html)|漢紀四十|92|105||東漢燒當羌鬥爭史|漢和帝4年至17年</v>
       </c>
     </row>
-    <row r="50" spans="1:9" x14ac:dyDescent="0.15">
+    <row r="50" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A50">
         <v>510</v>
       </c>
@@ -7875,7 +7919,7 @@
         <v>510|[卷49](5_筆記/资治通鉴49.html)|漢紀四十一|106|115|||漢殤帝元年、漢安帝至9年</v>
       </c>
     </row>
-    <row r="51" spans="1:9" x14ac:dyDescent="0.15">
+    <row r="51" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A51">
         <v>511</v>
       </c>
@@ -7908,7 +7952,7 @@
         <v>511|[卷50](5_筆記/资治通鉴50.html)|漢紀四十二|116|124|蔡諷蔡瑁世系圖|刺殺先零羌|漢安帝10年至18年</v>
       </c>
     </row>
-    <row r="52" spans="1:9" x14ac:dyDescent="0.15">
+    <row r="52" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A52">
         <v>512</v>
       </c>
@@ -7938,7 +7982,7 @@
         <v>512|[卷51](5_筆記/资治通鉴51.html)|漢紀四十三|125|133||漢群臣上書類型、天體學說三家|漢安帝19年、前少帝劉懿、漢順帝至8年</v>
       </c>
     </row>
-    <row r="53" spans="1:9" x14ac:dyDescent="0.15">
+    <row r="53" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A53">
         <v>513</v>
       </c>
@@ -7965,7 +8009,7 @@
         <v>513|[卷52](5_筆記/资治通鉴52.html)|漢紀四十四|134|145|||漢順帝9年至19年、漢沖帝、漢質帝</v>
       </c>
     </row>
-    <row r="54" spans="1:9" x14ac:dyDescent="0.15">
+    <row r="54" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A54">
         <v>514</v>
       </c>
@@ -7995,7 +8039,7 @@
         <v>514|[卷53](5_筆記/资治通鉴53.html)|漢紀四十五|146|156|梁氏世系圖、崔氏世系圖||漢桓帝至10年</v>
       </c>
     </row>
-    <row r="55" spans="1:9" x14ac:dyDescent="0.15">
+    <row r="55" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A55">
         <v>515</v>
       </c>
@@ -8028,7 +8072,7 @@
         <v>515|[卷54](5_筆記/资治通鉴54.html)|漢紀四十六|157|163|鄧猛女關系圖、李固世系|李杜組合匯總|漢桓帝11年至17年</v>
       </c>
     </row>
-    <row r="56" spans="1:9" x14ac:dyDescent="0.15">
+    <row r="56" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A56">
         <v>516</v>
       </c>
@@ -8055,7 +8099,7 @@
         <v>516|[卷55](5_筆記/资治通鉴55.html)|漢紀四十七|164|166|||漢桓帝18年至20年</v>
       </c>
     </row>
-    <row r="57" spans="1:9" x14ac:dyDescent="0.15">
+    <row r="57" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A57">
         <v>517</v>
       </c>
@@ -8085,7 +8129,7 @@
         <v>517|[卷56](5_筆記/资治通鉴56.html)|漢紀四十八|167|171|汝南袁氏世系||漢桓帝21年、漢靈帝至4年</v>
       </c>
     </row>
-    <row r="58" spans="1:9" x14ac:dyDescent="0.15">
+    <row r="58" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A58">
         <v>518</v>
       </c>
@@ -8112,7 +8156,7 @@
         <v>518|[卷57](5_筆記/资治通鉴57.html)|漢紀四十九|172|180|||漢靈帝5年至13年</v>
       </c>
     </row>
-    <row r="59" spans="1:9" x14ac:dyDescent="0.15">
+    <row r="59" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A59">
         <v>519</v>
       </c>
@@ -8142,7 +8186,7 @@
         <v>519|[卷58](5_筆記/资治通鉴58.html)|漢紀五十|181|187|檀石槐世系、何皇后世系||漢靈帝14年至20年</v>
       </c>
     </row>
-    <row r="60" spans="1:9" x14ac:dyDescent="0.15">
+    <row r="60" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A60">
         <v>520</v>
       </c>
@@ -8172,7 +8216,7 @@
         <v>520|[卷59](5_筆記/资治通鉴59.html)|漢紀五十一|188|190||十二分野表|漢靈帝21年、劉辯、漢獻帝至2年</v>
       </c>
     </row>
-    <row r="61" spans="1:9" x14ac:dyDescent="0.15">
+    <row r="61" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A61">
         <v>521</v>
       </c>
@@ -8202,7 +8246,7 @@
         <v>521|[卷60](5_筆記/资治通鉴60.html)|漢紀五十二|191|193|漢末道教諸張世系||漢獻帝3年至5年</v>
       </c>
     </row>
-    <row r="62" spans="1:9" x14ac:dyDescent="0.15">
+    <row r="62" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A62">
         <v>522</v>
       </c>
@@ -8232,7 +8276,7 @@
         <v>522|[卷61](5_筆記/资治通鉴61.html)|漢紀五十三|194|195|孫吳世系||漢獻帝6年至7年</v>
       </c>
     </row>
-    <row r="63" spans="1:9" x14ac:dyDescent="0.15">
+    <row r="63" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A63">
         <v>523</v>
       </c>
@@ -8265,7 +8309,7 @@
         <v>523|[卷62](5_筆記/资治通鉴62.html)|漢紀五十四|196|198|下邳陳氏世系、潁川陳氏世系|蔡邕漢樂四品|漢獻帝8年至10年</v>
       </c>
     </row>
-    <row r="64" spans="1:9" x14ac:dyDescent="0.15">
+    <row r="64" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A64">
         <v>524</v>
       </c>
@@ -8292,7 +8336,7 @@
         <v>524|[卷63](5_筆記/资治通鉴63.html)|漢紀五十五|199|200|||漢獻帝11年至12年</v>
       </c>
     </row>
-    <row r="65" spans="1:9" x14ac:dyDescent="0.15">
+    <row r="65" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A65">
         <v>525</v>
       </c>
@@ -8322,7 +8366,7 @@
         <v>525|[卷64](5_筆記/资治通鉴64.html)|漢紀五十六|201|205|遼東公孫世系||漢獻帝13年至17年</v>
       </c>
     </row>
-    <row r="66" spans="1:9" x14ac:dyDescent="0.15">
+    <row r="66" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A66">
         <v>526</v>
       </c>
@@ -8349,7 +8393,7 @@
         <v>526|[卷65](5_筆記/资治通鉴65.html)|漢紀五十七|206|208|||漢獻帝18年至20年</v>
       </c>
     </row>
-    <row r="67" spans="1:9" x14ac:dyDescent="0.15">
+    <row r="67" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A67">
         <v>527</v>
       </c>
@@ -8376,7 +8420,7 @@
         <v>527|[卷66](5_筆記/资治通鉴66.html)|漢紀五十八|209|213|||漢獻帝21年至25年</v>
       </c>
     </row>
-    <row r="68" spans="1:9" x14ac:dyDescent="0.15">
+    <row r="68" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A68">
         <v>528</v>
       </c>
@@ -8406,7 +8450,7 @@
         <v>528|[卷67](5_筆記/资治通鉴67.html)|漢紀五十九|214|216||孫十萬合肥之戰表|漢獻帝26年至28年</v>
       </c>
     </row>
-    <row r="69" spans="1:9" x14ac:dyDescent="0.15">
+    <row r="69" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A69">
         <v>529</v>
       </c>
@@ -8433,7 +8477,7 @@
         <v>529|[卷68](5_筆記/资治通鉴68.html)|漢紀六十|217|219|||漢獻帝29年至31年</v>
       </c>
     </row>
-    <row r="70" spans="1:9" x14ac:dyDescent="0.15">
+    <row r="70" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A70">
         <v>601</v>
       </c>
@@ -8460,7 +8504,7 @@
         <v>601|[卷69](5_筆記/资治通鉴69.html)|魏紀一|220|222|||曹丕至3年</v>
       </c>
     </row>
-    <row r="71" spans="1:9" x14ac:dyDescent="0.15">
+    <row r="71" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A71">
         <v>602</v>
       </c>
@@ -8490,7 +8534,7 @@
         <v>602|[卷70](5_筆記/资治通鉴70.html)|魏紀二|223|227||曹丕三次伐吳表、諸葛亮五次北伐表|曹丕4年至7年、曹叡至2年</v>
       </c>
     </row>
-    <row r="72" spans="1:9" x14ac:dyDescent="0.15">
+    <row r="72" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A72">
         <v>603</v>
       </c>
@@ -8517,7 +8561,7 @@
         <v>603|[卷71](5_筆記/资治通鉴71.html)|魏紀三|228|230|||曹叡3年至5年</v>
       </c>
     </row>
-    <row r="73" spans="1:9" x14ac:dyDescent="0.15">
+    <row r="73" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A73">
         <v>604</v>
       </c>
@@ -8547,7 +8591,7 @@
         <v>604|[卷72](5_筆記/资治通鉴72.html)|魏紀四|231|234||劉曄勸諫表|曹叡6年至9年</v>
       </c>
     </row>
-    <row r="74" spans="1:9" x14ac:dyDescent="0.15">
+    <row r="74" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A74">
         <v>605</v>
       </c>
@@ -8577,7 +8621,7 @@
         <v>605|[卷73](5_筆記/资治通鉴73.html)|魏紀五|235|237||曹叡後宮十二等爵位|曹叡10年至12年</v>
       </c>
     </row>
-    <row r="75" spans="1:9" x14ac:dyDescent="0.15">
+    <row r="75" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A75">
         <v>606</v>
       </c>
@@ -8607,7 +8651,7 @@
         <v>606|[卷74](5_筆記/资治通鉴74.html)|魏紀六|238|245|全氏世系圖、吳郡陸氏世系圖||曹叡13年至14年、曹芳至7年</v>
       </c>
     </row>
-    <row r="76" spans="1:9" x14ac:dyDescent="0.15">
+    <row r="76" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A76">
         <v>607</v>
       </c>
@@ -8640,7 +8684,7 @@
         <v>607|[卷75](5_筆記/资治通鉴75.html)|魏紀七|246|252|太山羊氏世系、太原王氏世系|姜維十一次北伐表、壽春三叛表|曹芳8年至14年</v>
       </c>
     </row>
-    <row r="77" spans="1:9" x14ac:dyDescent="0.15">
+    <row r="77" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A77">
         <v>608</v>
       </c>
@@ -8670,7 +8714,7 @@
         <v>608|[卷76](5_筆記/资治通鉴76.html)|魏紀八|253|255|琅邪諸葛世系||曹芳15年至16年、曹髦至2年</v>
       </c>
     </row>
-    <row r="78" spans="1:9" x14ac:dyDescent="0.15">
+    <row r="78" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A78">
         <v>609</v>
       </c>
@@ -8700,7 +8744,7 @@
         <v>609|[卷77](5_筆記/资治通鉴77.html)|魏紀九|256|261|孫權托孤亂政圖、琅邪王氏世系、琅邪太原王氏源流圖||曹髦3年至7年、曹奐至2年</v>
       </c>
     </row>
-    <row r="79" spans="1:9" x14ac:dyDescent="0.15">
+    <row r="79" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A79">
         <v>610</v>
       </c>
@@ -8730,7 +8774,7 @@
         <v>610|[卷78](5_筆記/资治通鉴78.html)|魏紀十|262|264|陳留阮氏世系、三卞皇后圖||曹奐3年至5年</v>
       </c>
     </row>
-    <row r="80" spans="1:9" x14ac:dyDescent="0.15">
+    <row r="80" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A80">
         <v>701</v>
       </c>
@@ -8757,7 +8801,7 @@
         <v>701|[卷79](5_筆記/资治通鉴79.html)|晉紀一|265|272|||曹奐6年至7年、司馬炎至7年</v>
       </c>
     </row>
-    <row r="81" spans="1:9" x14ac:dyDescent="0.15">
+    <row r="81" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A81">
         <v>702</v>
       </c>
@@ -8787,7 +8831,7 @@
         <v>702|[卷80](5_筆記/资治通鉴80.html)|晉紀二|273|279||諸王就國情況(西晉大小國)|司馬炎8年至14年</v>
       </c>
     </row>
-    <row r="82" spans="1:9" x14ac:dyDescent="0.15">
+    <row r="82" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A82">
         <v>703</v>
       </c>
@@ -8817,7 +8861,7 @@
         <v>703|[卷81](5_筆記/资治通鉴81.html)|晉紀三|280|288|弘農楊氏名人世系||司馬炎15年至23年</v>
       </c>
     </row>
-    <row r="83" spans="1:9" x14ac:dyDescent="0.15">
+    <row r="83" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A83">
         <v>704</v>
       </c>
@@ -8844,7 +8888,7 @@
         <v>704|[卷82](5_筆記/资治通鉴82.html)|晉紀四|289|298|||司馬炎24年至25年、晉惠帝至9年</v>
       </c>
     </row>
-    <row r="84" spans="1:9" x14ac:dyDescent="0.15">
+    <row r="84" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A84">
         <v>705</v>
       </c>
@@ -8871,7 +8915,7 @@
         <v>705|[卷83](5_筆記/资治通鉴83.html)|晉紀五|299|300|||晉惠帝10年至11年</v>
       </c>
     </row>
-    <row r="85" spans="1:9" x14ac:dyDescent="0.15">
+    <row r="85" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A85">
         <v>706</v>
       </c>
@@ -8898,7 +8942,7 @@
         <v>706|[卷84](5_筆記/资治通鉴84.html)|晉紀六|301|302|||晉惠帝12年、司馬倫、晉惠帝13年</v>
       </c>
     </row>
-    <row r="86" spans="1:9" x14ac:dyDescent="0.15">
+    <row r="86" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A86">
         <v>707</v>
       </c>
@@ -8928,7 +8972,7 @@
         <v>707|[卷85](5_筆記/资治通鉴85.html)|晉紀七|303|304||羊獻容廢立表|晉惠帝14年至15年</v>
       </c>
     </row>
-    <row r="87" spans="1:9" x14ac:dyDescent="0.15">
+    <row r="87" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A87">
         <v>708</v>
       </c>
@@ -8955,7 +8999,7 @@
         <v>708|[卷86](5_筆記/资治通鉴86.html)|晉紀八|305|308|||晉惠帝16年至18年、晉懷帝至2年</v>
       </c>
     </row>
-    <row r="88" spans="1:9" x14ac:dyDescent="0.15">
+    <row r="88" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A88">
         <v>709</v>
       </c>
@@ -8982,7 +9026,7 @@
         <v>709|[卷87](5_筆記/资治通鉴87.html)|晉紀九|309|311|||晉懷帝3年至5年</v>
       </c>
     </row>
-    <row r="89" spans="1:9" x14ac:dyDescent="0.15">
+    <row r="89" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A89">
         <v>710</v>
       </c>
@@ -9009,7 +9053,7 @@
         <v>710|[卷88](5_筆記/资治通鉴88.html)|晉紀十|312|313|||晉懷帝6年至7年、晉愍帝元年</v>
       </c>
     </row>
-    <row r="90" spans="1:9" x14ac:dyDescent="0.15">
+    <row r="90" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A90">
         <v>711</v>
       </c>
@@ -9036,31 +9080,34 @@
         <v>711|[卷89](5_筆記/资治通鉴89.html)|晉紀十一|314|316|||晉愍帝2年至4年</v>
       </c>
     </row>
-    <row r="91" spans="1:9" x14ac:dyDescent="0.15">
+    <row r="91" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A91">
         <v>801</v>
       </c>
-      <c r="B91" t="e">
+      <c r="B91" t="str">
         <f>VLOOKUP($A91,統計!$A:$G,2,)</f>
-        <v>#N/A</v>
+        <v>卷90</v>
       </c>
       <c r="C91" t="s">
         <v>286</v>
       </c>
-      <c r="D91" t="e">
+      <c r="D91">
         <f>VLOOKUP($A91,統計!$A:$G,6,)</f>
-        <v>#N/A</v>
-      </c>
-      <c r="E91" t="e">
+        <v>317</v>
+      </c>
+      <c r="E91">
         <f>VLOOKUP($A91,統計!$A:$G,7,)</f>
-        <v>#N/A</v>
-      </c>
-      <c r="I91" t="e">
+        <v>318</v>
+      </c>
+      <c r="H91" t="s">
+        <v>521</v>
+      </c>
+      <c r="I91" t="str">
         <f t="shared" si="1"/>
-        <v>#N/A</v>
-      </c>
-    </row>
-    <row r="92" spans="1:9" x14ac:dyDescent="0.15">
+        <v>801|[卷90](5_筆記/资治通鉴90.html)|晉紀十二|317|318|||晉元帝至2年</v>
+      </c>
+    </row>
+    <row r="92" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A92">
         <v>802</v>
       </c>
@@ -9084,7 +9131,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="93" spans="1:9" x14ac:dyDescent="0.15">
+    <row r="93" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A93">
         <v>803</v>
       </c>
@@ -9108,7 +9155,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="94" spans="1:9" x14ac:dyDescent="0.15">
+    <row r="94" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A94">
         <v>804</v>
       </c>
@@ -9132,7 +9179,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="95" spans="1:9" x14ac:dyDescent="0.15">
+    <row r="95" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A95">
         <v>805</v>
       </c>
@@ -9156,7 +9203,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="96" spans="1:9" x14ac:dyDescent="0.15">
+    <row r="96" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A96">
         <v>806</v>
       </c>
@@ -9180,7 +9227,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="97" spans="1:9" x14ac:dyDescent="0.15">
+    <row r="97" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A97">
         <v>807</v>
       </c>
@@ -9204,7 +9251,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="98" spans="1:9" x14ac:dyDescent="0.15">
+    <row r="98" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A98">
         <v>808</v>
       </c>
@@ -9228,7 +9275,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="99" spans="1:9" x14ac:dyDescent="0.15">
+    <row r="99" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A99">
         <v>809</v>
       </c>
@@ -9252,7 +9299,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="100" spans="1:9" x14ac:dyDescent="0.15">
+    <row r="100" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A100">
         <v>810</v>
       </c>
@@ -9276,7 +9323,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="101" spans="1:9" x14ac:dyDescent="0.15">
+    <row r="101" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A101">
         <v>811</v>
       </c>
@@ -9300,7 +9347,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="102" spans="1:9" x14ac:dyDescent="0.15">
+    <row r="102" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A102">
         <v>812</v>
       </c>
@@ -9324,7 +9371,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="103" spans="1:9" x14ac:dyDescent="0.15">
+    <row r="103" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A103">
         <v>813</v>
       </c>
@@ -9348,7 +9395,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="104" spans="1:9" x14ac:dyDescent="0.15">
+    <row r="104" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A104">
         <v>814</v>
       </c>
@@ -9372,7 +9419,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="105" spans="1:9" x14ac:dyDescent="0.15">
+    <row r="105" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A105">
         <v>815</v>
       </c>
@@ -9396,7 +9443,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="106" spans="1:9" x14ac:dyDescent="0.15">
+    <row r="106" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A106">
         <v>816</v>
       </c>
@@ -9420,7 +9467,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="107" spans="1:9" x14ac:dyDescent="0.15">
+    <row r="107" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A107">
         <v>817</v>
       </c>
@@ -9444,7 +9491,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="108" spans="1:9" x14ac:dyDescent="0.15">
+    <row r="108" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A108">
         <v>818</v>
       </c>
@@ -9468,7 +9515,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="109" spans="1:9" x14ac:dyDescent="0.15">
+    <row r="109" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A109">
         <v>819</v>
       </c>
@@ -9492,7 +9539,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="110" spans="1:9" x14ac:dyDescent="0.15">
+    <row r="110" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A110">
         <v>820</v>
       </c>
@@ -9516,7 +9563,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="111" spans="1:9" x14ac:dyDescent="0.15">
+    <row r="111" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A111">
         <v>821</v>
       </c>
@@ -9540,7 +9587,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="112" spans="1:9" x14ac:dyDescent="0.15">
+    <row r="112" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A112">
         <v>822</v>
       </c>
@@ -9564,7 +9611,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="113" spans="1:9" x14ac:dyDescent="0.15">
+    <row r="113" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A113">
         <v>823</v>
       </c>
@@ -9588,7 +9635,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="114" spans="1:9" x14ac:dyDescent="0.15">
+    <row r="114" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A114">
         <v>824</v>
       </c>
@@ -9612,7 +9659,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="115" spans="1:9" x14ac:dyDescent="0.15">
+    <row r="115" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A115">
         <v>825</v>
       </c>
@@ -9636,7 +9683,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="116" spans="1:9" x14ac:dyDescent="0.15">
+    <row r="116" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A116">
         <v>826</v>
       </c>
@@ -9660,7 +9707,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="117" spans="1:9" x14ac:dyDescent="0.15">
+    <row r="117" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A117">
         <v>827</v>
       </c>
@@ -9684,7 +9731,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="118" spans="1:9" x14ac:dyDescent="0.15">
+    <row r="118" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A118">
         <v>828</v>
       </c>
@@ -9708,7 +9755,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="119" spans="1:9" x14ac:dyDescent="0.15">
+    <row r="119" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A119">
         <v>829</v>
       </c>
@@ -9732,7 +9779,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="120" spans="1:9" x14ac:dyDescent="0.15">
+    <row r="120" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A120">
         <v>901</v>
       </c>
@@ -9756,7 +9803,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="121" spans="1:9" x14ac:dyDescent="0.15">
+    <row r="121" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A121">
         <v>902</v>
       </c>
@@ -9780,7 +9827,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="122" spans="1:9" x14ac:dyDescent="0.15">
+    <row r="122" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A122">
         <v>903</v>
       </c>
@@ -9804,7 +9851,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="123" spans="1:9" x14ac:dyDescent="0.15">
+    <row r="123" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A123">
         <v>904</v>
       </c>
@@ -9828,7 +9875,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="124" spans="1:9" x14ac:dyDescent="0.15">
+    <row r="124" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A124">
         <v>905</v>
       </c>
@@ -9852,7 +9899,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="125" spans="1:9" x14ac:dyDescent="0.15">
+    <row r="125" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A125">
         <v>906</v>
       </c>
@@ -9876,7 +9923,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="126" spans="1:9" x14ac:dyDescent="0.15">
+    <row r="126" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A126">
         <v>907</v>
       </c>
@@ -9900,7 +9947,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="127" spans="1:9" x14ac:dyDescent="0.15">
+    <row r="127" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A127">
         <v>908</v>
       </c>
@@ -9924,7 +9971,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="128" spans="1:9" x14ac:dyDescent="0.15">
+    <row r="128" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A128">
         <v>909</v>
       </c>
@@ -9948,7 +9995,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="129" spans="1:9" x14ac:dyDescent="0.15">
+    <row r="129" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A129">
         <v>910</v>
       </c>
@@ -9972,7 +10019,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="130" spans="1:9" x14ac:dyDescent="0.15">
+    <row r="130" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A130">
         <v>911</v>
       </c>
@@ -9996,7 +10043,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="131" spans="1:9" x14ac:dyDescent="0.15">
+    <row r="131" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A131">
         <v>912</v>
       </c>
@@ -10020,7 +10067,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="132" spans="1:9" x14ac:dyDescent="0.15">
+    <row r="132" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A132">
         <v>913</v>
       </c>
@@ -10044,7 +10091,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="133" spans="1:9" x14ac:dyDescent="0.15">
+    <row r="133" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A133">
         <v>914</v>
       </c>
@@ -10068,7 +10115,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="134" spans="1:9" x14ac:dyDescent="0.15">
+    <row r="134" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A134">
         <v>915</v>
       </c>
@@ -10092,7 +10139,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="135" spans="1:9" x14ac:dyDescent="0.15">
+    <row r="135" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A135">
         <v>916</v>
       </c>
@@ -10116,7 +10163,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="136" spans="1:9" x14ac:dyDescent="0.15">
+    <row r="136" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A136">
         <v>1001</v>
       </c>
@@ -10140,7 +10187,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="137" spans="1:9" x14ac:dyDescent="0.15">
+    <row r="137" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A137">
         <v>1002</v>
       </c>
@@ -10164,7 +10211,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="138" spans="1:9" x14ac:dyDescent="0.15">
+    <row r="138" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A138">
         <v>1003</v>
       </c>
@@ -10188,7 +10235,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="139" spans="1:9" x14ac:dyDescent="0.15">
+    <row r="139" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A139">
         <v>1004</v>
       </c>
@@ -10212,7 +10259,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="140" spans="1:9" x14ac:dyDescent="0.15">
+    <row r="140" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A140">
         <v>1005</v>
       </c>
@@ -10236,7 +10283,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="141" spans="1:9" x14ac:dyDescent="0.15">
+    <row r="141" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A141">
         <v>1006</v>
       </c>
@@ -10260,7 +10307,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="142" spans="1:9" x14ac:dyDescent="0.15">
+    <row r="142" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A142">
         <v>1007</v>
       </c>
@@ -10284,7 +10331,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="143" spans="1:9" x14ac:dyDescent="0.15">
+    <row r="143" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A143">
         <v>1008</v>
       </c>
@@ -10308,7 +10355,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="144" spans="1:9" x14ac:dyDescent="0.15">
+    <row r="144" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A144">
         <v>1009</v>
       </c>
@@ -10332,7 +10379,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="145" spans="1:9" x14ac:dyDescent="0.15">
+    <row r="145" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A145">
         <v>1010</v>
       </c>
@@ -10356,7 +10403,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="146" spans="1:9" x14ac:dyDescent="0.15">
+    <row r="146" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A146">
         <v>1101</v>
       </c>
@@ -10380,7 +10427,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="147" spans="1:9" x14ac:dyDescent="0.15">
+    <row r="147" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A147">
         <v>1102</v>
       </c>
@@ -10404,7 +10451,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="148" spans="1:9" x14ac:dyDescent="0.15">
+    <row r="148" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A148">
         <v>1103</v>
       </c>
@@ -10428,7 +10475,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="149" spans="1:9" x14ac:dyDescent="0.15">
+    <row r="149" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A149">
         <v>1104</v>
       </c>
@@ -10452,7 +10499,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="150" spans="1:9" x14ac:dyDescent="0.15">
+    <row r="150" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A150">
         <v>1105</v>
       </c>
@@ -10476,7 +10523,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="151" spans="1:9" x14ac:dyDescent="0.15">
+    <row r="151" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A151">
         <v>1106</v>
       </c>
@@ -10500,7 +10547,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="152" spans="1:9" x14ac:dyDescent="0.15">
+    <row r="152" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A152">
         <v>1107</v>
       </c>
@@ -10524,7 +10571,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="153" spans="1:9" x14ac:dyDescent="0.15">
+    <row r="153" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A153">
         <v>1108</v>
       </c>
@@ -10548,7 +10595,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="154" spans="1:9" x14ac:dyDescent="0.15">
+    <row r="154" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A154">
         <v>1109</v>
       </c>
@@ -10572,7 +10619,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="155" spans="1:9" x14ac:dyDescent="0.15">
+    <row r="155" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A155">
         <v>1110</v>
       </c>
@@ -10596,7 +10643,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="156" spans="1:9" x14ac:dyDescent="0.15">
+    <row r="156" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A156">
         <v>1111</v>
       </c>
@@ -10620,7 +10667,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="157" spans="1:9" x14ac:dyDescent="0.15">
+    <row r="157" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A157">
         <v>1112</v>
       </c>
@@ -10644,7 +10691,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="158" spans="1:9" x14ac:dyDescent="0.15">
+    <row r="158" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A158">
         <v>1113</v>
       </c>
@@ -10668,7 +10715,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="159" spans="1:9" x14ac:dyDescent="0.15">
+    <row r="159" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A159">
         <v>1114</v>
       </c>
@@ -10692,7 +10739,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="160" spans="1:9" x14ac:dyDescent="0.15">
+    <row r="160" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A160">
         <v>1115</v>
       </c>
@@ -10716,7 +10763,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="161" spans="1:9" x14ac:dyDescent="0.15">
+    <row r="161" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A161">
         <v>1116</v>
       </c>
@@ -10740,7 +10787,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="162" spans="1:9" x14ac:dyDescent="0.15">
+    <row r="162" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A162">
         <v>1117</v>
       </c>
@@ -10764,7 +10811,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="163" spans="1:9" x14ac:dyDescent="0.15">
+    <row r="163" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A163">
         <v>1118</v>
       </c>
@@ -10788,7 +10835,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="164" spans="1:9" x14ac:dyDescent="0.15">
+    <row r="164" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A164">
         <v>1119</v>
       </c>
@@ -10812,7 +10859,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="165" spans="1:9" x14ac:dyDescent="0.15">
+    <row r="165" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A165">
         <v>1120</v>
       </c>
@@ -10836,7 +10883,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="166" spans="1:9" x14ac:dyDescent="0.15">
+    <row r="166" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A166">
         <v>1121</v>
       </c>
@@ -10860,7 +10907,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="167" spans="1:9" x14ac:dyDescent="0.15">
+    <row r="167" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A167">
         <v>1122</v>
       </c>
@@ -10884,7 +10931,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="168" spans="1:9" x14ac:dyDescent="0.15">
+    <row r="168" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A168">
         <v>1201</v>
       </c>
@@ -10908,7 +10955,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="169" spans="1:9" x14ac:dyDescent="0.15">
+    <row r="169" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A169">
         <v>1202</v>
       </c>
@@ -10932,7 +10979,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="170" spans="1:9" x14ac:dyDescent="0.15">
+    <row r="170" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A170">
         <v>1203</v>
       </c>
@@ -10956,7 +11003,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="171" spans="1:9" x14ac:dyDescent="0.15">
+    <row r="171" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A171">
         <v>1204</v>
       </c>
@@ -10980,7 +11027,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="172" spans="1:9" x14ac:dyDescent="0.15">
+    <row r="172" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A172">
         <v>1205</v>
       </c>
@@ -11004,7 +11051,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="173" spans="1:9" x14ac:dyDescent="0.15">
+    <row r="173" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A173">
         <v>1206</v>
       </c>
@@ -11028,7 +11075,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="174" spans="1:9" x14ac:dyDescent="0.15">
+    <row r="174" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A174">
         <v>1207</v>
       </c>
@@ -11052,7 +11099,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="175" spans="1:9" x14ac:dyDescent="0.15">
+    <row r="175" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A175">
         <v>1208</v>
       </c>
@@ -11076,7 +11123,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="176" spans="1:9" x14ac:dyDescent="0.15">
+    <row r="176" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A176">
         <v>1209</v>
       </c>
@@ -11100,7 +11147,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="177" spans="1:9" x14ac:dyDescent="0.15">
+    <row r="177" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A177">
         <v>1210</v>
       </c>
@@ -11124,7 +11171,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="178" spans="1:9" x14ac:dyDescent="0.15">
+    <row r="178" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A178">
         <v>1301</v>
       </c>
@@ -11148,7 +11195,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="179" spans="1:9" x14ac:dyDescent="0.15">
+    <row r="179" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A179">
         <v>1302</v>
       </c>
@@ -11172,7 +11219,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="180" spans="1:9" x14ac:dyDescent="0.15">
+    <row r="180" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A180">
         <v>1303</v>
       </c>
@@ -11196,7 +11243,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="181" spans="1:9" x14ac:dyDescent="0.15">
+    <row r="181" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A181">
         <v>1304</v>
       </c>
@@ -11220,7 +11267,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="182" spans="1:9" x14ac:dyDescent="0.15">
+    <row r="182" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A182">
         <v>1305</v>
       </c>
@@ -11244,7 +11291,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="183" spans="1:9" x14ac:dyDescent="0.15">
+    <row r="183" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A183">
         <v>1306</v>
       </c>
@@ -11268,7 +11315,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="184" spans="1:9" x14ac:dyDescent="0.15">
+    <row r="184" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A184">
         <v>1307</v>
       </c>
@@ -11292,7 +11339,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="185" spans="1:9" x14ac:dyDescent="0.15">
+    <row r="185" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A185">
         <v>1308</v>
       </c>
@@ -11316,7 +11363,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="186" spans="1:9" x14ac:dyDescent="0.15">
+    <row r="186" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A186">
         <v>1401</v>
       </c>
@@ -11340,7 +11387,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="187" spans="1:9" x14ac:dyDescent="0.15">
+    <row r="187" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A187">
         <v>1402</v>
       </c>
@@ -11364,7 +11411,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="188" spans="1:9" x14ac:dyDescent="0.15">
+    <row r="188" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A188">
         <v>1403</v>
       </c>
@@ -11388,7 +11435,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="189" spans="1:9" x14ac:dyDescent="0.15">
+    <row r="189" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A189">
         <v>1404</v>
       </c>
@@ -11412,7 +11459,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="190" spans="1:9" x14ac:dyDescent="0.15">
+    <row r="190" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A190">
         <v>1405</v>
       </c>
@@ -11436,7 +11483,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="191" spans="1:9" x14ac:dyDescent="0.15">
+    <row r="191" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A191">
         <v>1406</v>
       </c>
@@ -11460,7 +11507,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="192" spans="1:9" x14ac:dyDescent="0.15">
+    <row r="192" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A192">
         <v>1407</v>
       </c>
@@ -11484,7 +11531,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="193" spans="1:9" x14ac:dyDescent="0.15">
+    <row r="193" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A193">
         <v>1408</v>
       </c>
@@ -11508,7 +11555,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="194" spans="1:9" x14ac:dyDescent="0.15">
+    <row r="194" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A194">
         <v>1409</v>
       </c>
@@ -11532,7 +11579,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="195" spans="1:9" x14ac:dyDescent="0.15">
+    <row r="195" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A195">
         <v>1410</v>
       </c>
@@ -11556,7 +11603,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="196" spans="1:9" x14ac:dyDescent="0.15">
+    <row r="196" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A196">
         <v>1411</v>
       </c>
@@ -11580,7 +11627,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="197" spans="1:9" x14ac:dyDescent="0.15">
+    <row r="197" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A197">
         <v>1412</v>
       </c>
@@ -11604,7 +11651,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="198" spans="1:9" x14ac:dyDescent="0.15">
+    <row r="198" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A198">
         <v>1413</v>
       </c>
@@ -11628,7 +11675,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="199" spans="1:9" x14ac:dyDescent="0.15">
+    <row r="199" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A199">
         <v>1414</v>
       </c>
@@ -11652,7 +11699,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="200" spans="1:9" x14ac:dyDescent="0.15">
+    <row r="200" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A200">
         <v>1415</v>
       </c>
@@ -11676,7 +11723,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="201" spans="1:9" x14ac:dyDescent="0.15">
+    <row r="201" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A201">
         <v>1416</v>
       </c>
@@ -11700,7 +11747,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="202" spans="1:9" x14ac:dyDescent="0.15">
+    <row r="202" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A202">
         <v>1417</v>
       </c>
@@ -11724,7 +11771,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="203" spans="1:9" x14ac:dyDescent="0.15">
+    <row r="203" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A203">
         <v>1418</v>
       </c>
@@ -11748,7 +11795,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="204" spans="1:9" x14ac:dyDescent="0.15">
+    <row r="204" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A204">
         <v>1419</v>
       </c>
@@ -11772,7 +11819,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="205" spans="1:9" x14ac:dyDescent="0.15">
+    <row r="205" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A205">
         <v>1420</v>
       </c>
@@ -11796,7 +11843,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="206" spans="1:9" x14ac:dyDescent="0.15">
+    <row r="206" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A206">
         <v>1421</v>
       </c>
@@ -11820,7 +11867,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="207" spans="1:9" x14ac:dyDescent="0.15">
+    <row r="207" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A207">
         <v>1422</v>
       </c>
@@ -11844,7 +11891,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="208" spans="1:9" x14ac:dyDescent="0.15">
+    <row r="208" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A208">
         <v>1423</v>
       </c>
@@ -11868,7 +11915,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="209" spans="1:9" x14ac:dyDescent="0.15">
+    <row r="209" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A209">
         <v>1424</v>
       </c>
@@ -11892,7 +11939,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="210" spans="1:9" x14ac:dyDescent="0.15">
+    <row r="210" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A210">
         <v>1425</v>
       </c>
@@ -11916,7 +11963,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="211" spans="1:9" x14ac:dyDescent="0.15">
+    <row r="211" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A211">
         <v>1426</v>
       </c>
@@ -11940,7 +11987,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="212" spans="1:9" x14ac:dyDescent="0.15">
+    <row r="212" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A212">
         <v>1427</v>
       </c>
@@ -11964,7 +12011,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="213" spans="1:9" x14ac:dyDescent="0.15">
+    <row r="213" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A213">
         <v>1428</v>
       </c>
@@ -11988,7 +12035,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="214" spans="1:9" x14ac:dyDescent="0.15">
+    <row r="214" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A214">
         <v>1429</v>
       </c>
@@ -12012,7 +12059,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="215" spans="1:9" x14ac:dyDescent="0.15">
+    <row r="215" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A215">
         <v>1430</v>
       </c>
@@ -12036,7 +12083,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="216" spans="1:9" x14ac:dyDescent="0.15">
+    <row r="216" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A216">
         <v>1431</v>
       </c>
@@ -12060,7 +12107,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="217" spans="1:9" x14ac:dyDescent="0.15">
+    <row r="217" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A217">
         <v>1432</v>
       </c>
@@ -12084,7 +12131,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="218" spans="1:9" x14ac:dyDescent="0.15">
+    <row r="218" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A218">
         <v>1433</v>
       </c>
@@ -12108,7 +12155,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="219" spans="1:9" x14ac:dyDescent="0.15">
+    <row r="219" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A219">
         <v>1434</v>
       </c>
@@ -12132,7 +12179,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="220" spans="1:9" x14ac:dyDescent="0.15">
+    <row r="220" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A220">
         <v>1435</v>
       </c>
@@ -12156,7 +12203,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="221" spans="1:9" x14ac:dyDescent="0.15">
+    <row r="221" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A221">
         <v>1436</v>
       </c>
@@ -12180,7 +12227,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="222" spans="1:9" x14ac:dyDescent="0.15">
+    <row r="222" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A222">
         <v>1437</v>
       </c>
@@ -12204,7 +12251,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="223" spans="1:9" x14ac:dyDescent="0.15">
+    <row r="223" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A223">
         <v>1438</v>
       </c>
@@ -12228,7 +12275,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="224" spans="1:9" x14ac:dyDescent="0.15">
+    <row r="224" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A224">
         <v>1439</v>
       </c>
@@ -12252,7 +12299,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="225" spans="1:9" x14ac:dyDescent="0.15">
+    <row r="225" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A225">
         <v>1440</v>
       </c>
@@ -12276,7 +12323,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="226" spans="1:9" x14ac:dyDescent="0.15">
+    <row r="226" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A226">
         <v>1441</v>
       </c>
@@ -12300,7 +12347,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="227" spans="1:9" x14ac:dyDescent="0.15">
+    <row r="227" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A227">
         <v>1442</v>
       </c>
@@ -12324,7 +12371,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="228" spans="1:9" x14ac:dyDescent="0.15">
+    <row r="228" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A228">
         <v>1443</v>
       </c>
@@ -12348,7 +12395,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="229" spans="1:9" x14ac:dyDescent="0.15">
+    <row r="229" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A229">
         <v>1444</v>
       </c>
@@ -12372,7 +12419,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="230" spans="1:9" x14ac:dyDescent="0.15">
+    <row r="230" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A230">
         <v>1445</v>
       </c>
@@ -12396,7 +12443,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="231" spans="1:9" x14ac:dyDescent="0.15">
+    <row r="231" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A231">
         <v>1446</v>
       </c>
@@ -12420,7 +12467,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="232" spans="1:9" x14ac:dyDescent="0.15">
+    <row r="232" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A232">
         <v>1447</v>
       </c>
@@ -12444,7 +12491,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="233" spans="1:9" x14ac:dyDescent="0.15">
+    <row r="233" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A233">
         <v>1448</v>
       </c>
@@ -12468,7 +12515,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="234" spans="1:9" x14ac:dyDescent="0.15">
+    <row r="234" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A234">
         <v>1449</v>
       </c>
@@ -12492,7 +12539,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="235" spans="1:9" x14ac:dyDescent="0.15">
+    <row r="235" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A235">
         <v>1450</v>
       </c>
@@ -12516,7 +12563,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="236" spans="1:9" x14ac:dyDescent="0.15">
+    <row r="236" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A236">
         <v>1451</v>
       </c>
@@ -12540,7 +12587,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="237" spans="1:9" x14ac:dyDescent="0.15">
+    <row r="237" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A237">
         <v>1452</v>
       </c>
@@ -12564,7 +12611,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="238" spans="1:9" x14ac:dyDescent="0.15">
+    <row r="238" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A238">
         <v>1453</v>
       </c>
@@ -12588,7 +12635,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="239" spans="1:9" x14ac:dyDescent="0.15">
+    <row r="239" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A239">
         <v>1454</v>
       </c>
@@ -12612,7 +12659,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="240" spans="1:9" x14ac:dyDescent="0.15">
+    <row r="240" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A240">
         <v>1455</v>
       </c>
@@ -12636,7 +12683,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="241" spans="1:9" x14ac:dyDescent="0.15">
+    <row r="241" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A241">
         <v>1456</v>
       </c>
@@ -12660,7 +12707,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="242" spans="1:9" x14ac:dyDescent="0.15">
+    <row r="242" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A242">
         <v>1457</v>
       </c>
@@ -12684,7 +12731,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="243" spans="1:9" x14ac:dyDescent="0.15">
+    <row r="243" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A243">
         <v>1458</v>
       </c>
@@ -12708,7 +12755,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="244" spans="1:9" x14ac:dyDescent="0.15">
+    <row r="244" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A244">
         <v>1459</v>
       </c>
@@ -12732,7 +12779,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="245" spans="1:9" x14ac:dyDescent="0.15">
+    <row r="245" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A245">
         <v>1460</v>
       </c>
@@ -12756,7 +12803,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="246" spans="1:9" x14ac:dyDescent="0.15">
+    <row r="246" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A246">
         <v>1461</v>
       </c>
@@ -12780,7 +12827,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="247" spans="1:9" x14ac:dyDescent="0.15">
+    <row r="247" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A247">
         <v>1462</v>
       </c>
@@ -12804,7 +12851,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="248" spans="1:9" x14ac:dyDescent="0.15">
+    <row r="248" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A248">
         <v>1463</v>
       </c>
@@ -12828,7 +12875,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="249" spans="1:9" x14ac:dyDescent="0.15">
+    <row r="249" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A249">
         <v>1464</v>
       </c>
@@ -12852,7 +12899,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="250" spans="1:9" x14ac:dyDescent="0.15">
+    <row r="250" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A250">
         <v>1465</v>
       </c>
@@ -12876,7 +12923,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="251" spans="1:9" x14ac:dyDescent="0.15">
+    <row r="251" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A251">
         <v>1466</v>
       </c>
@@ -12900,7 +12947,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="252" spans="1:9" x14ac:dyDescent="0.15">
+    <row r="252" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A252">
         <v>1467</v>
       </c>
@@ -12924,7 +12971,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="253" spans="1:9" x14ac:dyDescent="0.15">
+    <row r="253" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A253">
         <v>1468</v>
       </c>
@@ -12948,7 +12995,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="254" spans="1:9" x14ac:dyDescent="0.15">
+    <row r="254" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A254">
         <v>1469</v>
       </c>
@@ -12972,7 +13019,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="255" spans="1:9" x14ac:dyDescent="0.15">
+    <row r="255" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A255">
         <v>1470</v>
       </c>
@@ -12996,7 +13043,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="256" spans="1:9" x14ac:dyDescent="0.15">
+    <row r="256" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A256">
         <v>1471</v>
       </c>
@@ -13020,7 +13067,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="257" spans="1:9" x14ac:dyDescent="0.15">
+    <row r="257" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A257">
         <v>1472</v>
       </c>
@@ -13044,7 +13091,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="258" spans="1:9" x14ac:dyDescent="0.15">
+    <row r="258" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A258">
         <v>1473</v>
       </c>
@@ -13068,7 +13115,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="259" spans="1:9" x14ac:dyDescent="0.15">
+    <row r="259" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A259">
         <v>1474</v>
       </c>
@@ -13092,7 +13139,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="260" spans="1:9" x14ac:dyDescent="0.15">
+    <row r="260" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A260">
         <v>1475</v>
       </c>
@@ -13116,7 +13163,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="261" spans="1:9" x14ac:dyDescent="0.15">
+    <row r="261" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A261">
         <v>1476</v>
       </c>
@@ -13140,7 +13187,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="262" spans="1:9" x14ac:dyDescent="0.15">
+    <row r="262" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A262">
         <v>1477</v>
       </c>
@@ -13164,7 +13211,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="263" spans="1:9" x14ac:dyDescent="0.15">
+    <row r="263" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A263">
         <v>1478</v>
       </c>
@@ -13188,7 +13235,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="264" spans="1:9" x14ac:dyDescent="0.15">
+    <row r="264" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A264">
         <v>1479</v>
       </c>
@@ -13212,7 +13259,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="265" spans="1:9" x14ac:dyDescent="0.15">
+    <row r="265" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A265">
         <v>1480</v>
       </c>
@@ -13236,7 +13283,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="266" spans="1:9" x14ac:dyDescent="0.15">
+    <row r="266" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A266">
         <v>1481</v>
       </c>
@@ -13260,7 +13307,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="267" spans="1:9" x14ac:dyDescent="0.15">
+    <row r="267" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A267">
         <v>1501</v>
       </c>
@@ -13284,7 +13331,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="268" spans="1:9" x14ac:dyDescent="0.15">
+    <row r="268" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A268">
         <v>1502</v>
       </c>
@@ -13308,7 +13355,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="269" spans="1:9" x14ac:dyDescent="0.15">
+    <row r="269" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A269">
         <v>1503</v>
       </c>
@@ -13332,7 +13379,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="270" spans="1:9" x14ac:dyDescent="0.15">
+    <row r="270" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A270">
         <v>1504</v>
       </c>
@@ -13356,7 +13403,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="271" spans="1:9" x14ac:dyDescent="0.15">
+    <row r="271" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A271">
         <v>1505</v>
       </c>
@@ -13380,7 +13427,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="272" spans="1:9" x14ac:dyDescent="0.15">
+    <row r="272" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A272">
         <v>1506</v>
       </c>
@@ -13404,7 +13451,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="273" spans="1:9" x14ac:dyDescent="0.15">
+    <row r="273" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A273">
         <v>1601</v>
       </c>
@@ -13428,7 +13475,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="274" spans="1:9" x14ac:dyDescent="0.15">
+    <row r="274" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A274">
         <v>1602</v>
       </c>
@@ -13452,7 +13499,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="275" spans="1:9" x14ac:dyDescent="0.15">
+    <row r="275" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A275">
         <v>1603</v>
       </c>
@@ -13476,7 +13523,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="276" spans="1:9" x14ac:dyDescent="0.15">
+    <row r="276" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A276">
         <v>1604</v>
       </c>
@@ -13500,7 +13547,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="277" spans="1:9" x14ac:dyDescent="0.15">
+    <row r="277" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A277">
         <v>1605</v>
       </c>
@@ -13524,7 +13571,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="278" spans="1:9" x14ac:dyDescent="0.15">
+    <row r="278" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A278">
         <v>1606</v>
       </c>
@@ -13548,7 +13595,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="279" spans="1:9" x14ac:dyDescent="0.15">
+    <row r="279" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A279">
         <v>1607</v>
       </c>
@@ -13572,7 +13619,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="280" spans="1:9" x14ac:dyDescent="0.15">
+    <row r="280" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A280">
         <v>1608</v>
       </c>
@@ -13596,7 +13643,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="281" spans="1:9" x14ac:dyDescent="0.15">
+    <row r="281" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A281">
         <v>1701</v>
       </c>
@@ -13620,7 +13667,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="282" spans="1:9" x14ac:dyDescent="0.15">
+    <row r="282" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A282">
         <v>1702</v>
       </c>
@@ -13644,7 +13691,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="283" spans="1:9" x14ac:dyDescent="0.15">
+    <row r="283" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A283">
         <v>1703</v>
       </c>
@@ -13668,7 +13715,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="284" spans="1:9" x14ac:dyDescent="0.15">
+    <row r="284" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A284">
         <v>1704</v>
       </c>
@@ -13692,7 +13739,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="285" spans="1:9" x14ac:dyDescent="0.15">
+    <row r="285" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A285">
         <v>1705</v>
       </c>
@@ -13716,7 +13763,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="286" spans="1:9" x14ac:dyDescent="0.15">
+    <row r="286" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A286">
         <v>1706</v>
       </c>
@@ -13740,7 +13787,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="287" spans="1:9" x14ac:dyDescent="0.15">
+    <row r="287" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A287">
         <v>1801</v>
       </c>
@@ -13764,7 +13811,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="288" spans="1:9" x14ac:dyDescent="0.15">
+    <row r="288" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A288">
         <v>1802</v>
       </c>
@@ -13788,7 +13835,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="289" spans="1:9" x14ac:dyDescent="0.15">
+    <row r="289" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A289">
         <v>1803</v>
       </c>
@@ -13812,7 +13859,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="290" spans="1:9" x14ac:dyDescent="0.15">
+    <row r="290" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A290">
         <v>1804</v>
       </c>
@@ -13836,7 +13883,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="291" spans="1:9" x14ac:dyDescent="0.15">
+    <row r="291" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A291">
         <v>1901</v>
       </c>
@@ -13860,7 +13907,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="292" spans="1:9" x14ac:dyDescent="0.15">
+    <row r="292" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A292">
         <v>1902</v>
       </c>
@@ -13884,7 +13931,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="293" spans="1:9" x14ac:dyDescent="0.15">
+    <row r="293" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A293">
         <v>1903</v>
       </c>
@@ -13908,7 +13955,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="294" spans="1:9" x14ac:dyDescent="0.15">
+    <row r="294" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A294">
         <v>1904</v>
       </c>
@@ -13932,7 +13979,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="295" spans="1:9" x14ac:dyDescent="0.15">
+    <row r="295" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A295">
         <v>1905</v>
       </c>
@@ -13966,9 +14013,9 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <dimension ref="B1:Q14"/>
-  <sheetFormatPr defaultColWidth="8.625" defaultRowHeight="13.5" x14ac:dyDescent="0.15"/>
+  <sheetFormatPr defaultColWidth="8.6328125" defaultRowHeight="14" x14ac:dyDescent="0.25"/>
   <sheetData>
-    <row r="1" spans="2:17" x14ac:dyDescent="0.15">
+    <row r="1" spans="2:17" x14ac:dyDescent="0.25">
       <c r="B1" t="s">
         <v>491</v>
       </c>
@@ -13979,7 +14026,7 @@
         <v>493</v>
       </c>
     </row>
-    <row r="2" spans="2:17" x14ac:dyDescent="0.15">
+    <row r="2" spans="2:17" x14ac:dyDescent="0.25">
       <c r="B2">
         <v>268</v>
       </c>
@@ -14020,7 +14067,7 @@
         <v>6.8201193520886619E-2</v>
       </c>
     </row>
-    <row r="3" spans="2:17" x14ac:dyDescent="0.15">
+    <row r="3" spans="2:17" x14ac:dyDescent="0.25">
       <c r="C3">
         <v>1239</v>
       </c>
@@ -14028,7 +14075,7 @@
         <v>499</v>
       </c>
     </row>
-    <row r="4" spans="2:17" x14ac:dyDescent="0.15">
+    <row r="4" spans="2:17" x14ac:dyDescent="0.25">
       <c r="C4">
         <v>2175</v>
       </c>
@@ -14036,7 +14083,7 @@
         <v>500</v>
       </c>
     </row>
-    <row r="5" spans="2:17" x14ac:dyDescent="0.15">
+    <row r="5" spans="2:17" x14ac:dyDescent="0.25">
       <c r="C5">
         <v>2491</v>
       </c>
@@ -14059,7 +14106,7 @@
         <v>505</v>
       </c>
     </row>
-    <row r="6" spans="2:17" x14ac:dyDescent="0.15">
+    <row r="6" spans="2:17" x14ac:dyDescent="0.25">
       <c r="C6">
         <v>3732</v>
       </c>
@@ -14087,7 +14134,7 @@
         <v>5963.3518518518522</v>
       </c>
     </row>
-    <row r="7" spans="2:17" x14ac:dyDescent="0.15">
+    <row r="7" spans="2:17" x14ac:dyDescent="0.25">
       <c r="C7">
         <v>9612</v>
       </c>
@@ -14098,7 +14145,7 @@
         <v>507</v>
       </c>
     </row>
-    <row r="8" spans="2:17" x14ac:dyDescent="0.15">
+    <row r="8" spans="2:17" x14ac:dyDescent="0.25">
       <c r="G8" s="9">
         <f>C2/C7</f>
         <v>6.741573033707865E-2</v>
@@ -14113,7 +14160,7 @@
         <v>510</v>
       </c>
     </row>
-    <row r="9" spans="2:17" x14ac:dyDescent="0.15">
+    <row r="9" spans="2:17" x14ac:dyDescent="0.25">
       <c r="N9" t="s">
         <v>511</v>
       </c>
@@ -14129,7 +14176,7 @@
         <v>199</v>
       </c>
     </row>
-    <row r="10" spans="2:17" x14ac:dyDescent="0.15">
+    <row r="10" spans="2:17" x14ac:dyDescent="0.25">
       <c r="N10" t="s">
         <v>511</v>
       </c>
@@ -14145,7 +14192,7 @@
         <v>399</v>
       </c>
     </row>
-    <row r="11" spans="2:17" x14ac:dyDescent="0.15">
+    <row r="11" spans="2:17" x14ac:dyDescent="0.25">
       <c r="N11" t="s">
         <v>511</v>
       </c>
@@ -14161,7 +14208,7 @@
         <v>58799</v>
       </c>
     </row>
-    <row r="13" spans="2:17" x14ac:dyDescent="0.15">
+    <row r="13" spans="2:17" x14ac:dyDescent="0.25">
       <c r="N13" t="s">
         <v>512</v>
       </c>
@@ -14169,7 +14216,7 @@
         <v>200</v>
       </c>
     </row>
-    <row r="14" spans="2:17" x14ac:dyDescent="0.15">
+    <row r="14" spans="2:17" x14ac:dyDescent="0.25">
       <c r="N14" t="s">
         <v>513</v>
       </c>

--- a/5_筆記/閱讀數據.xlsx
+++ b/5_筆記/閱讀數據.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\self\study\zizhitongjian\5_筆記\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6ACF3720-862A-41EA-BB3A-6207F0770878}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{94315FB8-8059-4678-B4FA-7A69DA02ED9B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="38620" windowHeight="21220" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="5440" yWindow="5460" windowWidth="32960" windowHeight="15540" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="統計" sheetId="1" r:id="rId1"/>
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="528" uniqueCount="522">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="529" uniqueCount="523">
   <si>
     <t>索引號</t>
   </si>
@@ -1598,6 +1598,10 @@
   </si>
   <si>
     <t>晉元帝至2年</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>晉元帝3年至5年</t>
     <phoneticPr fontId="4" type="noConversion"/>
   </si>
 </sst>
@@ -1902,7 +1906,7 @@
             <c:strRef>
               <c:f>統計!$B$2:$B$115</c:f>
               <c:strCache>
-                <c:ptCount val="90"/>
+                <c:ptCount val="91"/>
                 <c:pt idx="0">
                   <c:v>卷1</c:v>
                 </c:pt>
@@ -2172,6 +2176,9 @@
                 </c:pt>
                 <c:pt idx="89">
                   <c:v>卷90</c:v>
+                </c:pt>
+                <c:pt idx="90">
+                  <c:v>卷91</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
@@ -2451,6 +2458,9 @@
                 </c:pt>
                 <c:pt idx="89">
                   <c:v>5.5</c:v>
+                </c:pt>
+                <c:pt idx="90">
+                  <c:v>4.666666666666667</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -3005,7 +3015,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:R91"/>
+  <dimension ref="A1:R92"/>
   <sheetFormatPr defaultColWidth="8.6328125" defaultRowHeight="14" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="7.7265625" customWidth="1"/>
@@ -3120,19 +3130,19 @@
       </c>
       <c r="O2">
         <f t="shared" ref="O2:O8" si="5">L2*$L$10</f>
-        <v>633.91111111111115</v>
+        <v>637.4065934065934</v>
       </c>
       <c r="P2" s="1">
         <f t="shared" ref="P2:P8" si="6">$C$2+O2</f>
-        <v>44652.911111111112</v>
+        <v>44656.406593406595</v>
       </c>
       <c r="Q2">
         <f t="shared" ref="Q2:Q8" si="7">(M2-$F$2)*$L$11</f>
-        <v>693.78588689311891</v>
+        <v>712.33483940537417</v>
       </c>
       <c r="R2" s="1">
         <f t="shared" ref="R2:R8" si="8">$C$2+Q2</f>
-        <v>44712.785886893122</v>
+        <v>44731.334839405376</v>
       </c>
     </row>
     <row r="3" spans="1:18" x14ac:dyDescent="0.25">
@@ -3183,19 +3193,19 @@
       </c>
       <c r="O3">
         <f t="shared" si="5"/>
-        <v>727.13333333333344</v>
+        <v>731.14285714285722</v>
       </c>
       <c r="P3" s="1">
         <f t="shared" si="6"/>
-        <v>44746.133333333331</v>
+        <v>44750.142857142855</v>
       </c>
       <c r="Q3">
         <f t="shared" si="7"/>
-        <v>760.60314726805814</v>
+        <v>780.93851575260112</v>
       </c>
       <c r="R3" s="1">
         <f t="shared" si="8"/>
-        <v>44779.603147268055</v>
+        <v>44799.938515752598</v>
       </c>
     </row>
     <row r="4" spans="1:18" x14ac:dyDescent="0.25">
@@ -3246,19 +3256,19 @@
       </c>
       <c r="O4">
         <f t="shared" si="5"/>
-        <v>1100.0222222222224</v>
+        <v>1106.0879120879122</v>
       </c>
       <c r="P4" s="1">
         <f t="shared" si="6"/>
-        <v>45119.022222222222</v>
+        <v>45125.087912087911</v>
       </c>
       <c r="Q4">
         <f t="shared" si="7"/>
-        <v>916.5100881429164</v>
+        <v>941.01376056279764</v>
       </c>
       <c r="R4" s="1">
         <f t="shared" si="8"/>
-        <v>44935.510088142917</v>
+        <v>44960.013760562797</v>
       </c>
     </row>
     <row r="5" spans="1:18" x14ac:dyDescent="0.25">
@@ -3309,19 +3319,19 @@
       </c>
       <c r="O5">
         <f t="shared" si="5"/>
-        <v>1640.7111111111112</v>
+        <v>1649.7582417582419</v>
       </c>
       <c r="P5" s="1">
         <f t="shared" si="6"/>
-        <v>45659.711111111108</v>
+        <v>45668.758241758245</v>
       </c>
       <c r="Q5">
         <f t="shared" si="7"/>
-        <v>1104.7120381989953</v>
+        <v>1134.2474489408205</v>
       </c>
       <c r="R5" s="1">
         <f t="shared" si="8"/>
-        <v>45123.712038198995</v>
+        <v>45153.24744894082</v>
       </c>
     </row>
     <row r="6" spans="1:18" x14ac:dyDescent="0.25">
@@ -3372,19 +3382,19 @@
       </c>
       <c r="O6">
         <f t="shared" si="5"/>
-        <v>2470.3888888888891</v>
+        <v>2484.0109890109893</v>
       </c>
       <c r="P6" s="1">
         <f t="shared" si="6"/>
-        <v>46489.388888888891</v>
+        <v>46503.010989010989</v>
       </c>
       <c r="Q6">
         <f t="shared" si="7"/>
-        <v>1458.843518186173</v>
+        <v>1497.8469335811237</v>
       </c>
       <c r="R6" s="1">
         <f t="shared" si="8"/>
-        <v>45477.843518186171</v>
+        <v>45516.846933581124</v>
       </c>
     </row>
     <row r="7" spans="1:18" x14ac:dyDescent="0.25">
@@ -3435,19 +3445,19 @@
       </c>
       <c r="O7">
         <f t="shared" si="5"/>
-        <v>2740.7333333333336</v>
+        <v>2755.8461538461538</v>
       </c>
       <c r="P7" s="1">
         <f t="shared" si="6"/>
-        <v>46759.733333333337</v>
+        <v>46774.846153846156</v>
       </c>
       <c r="Q7">
         <f t="shared" si="7"/>
-        <v>1516.7518105111203</v>
+        <v>1557.3034530820539</v>
       </c>
       <c r="R7" s="1">
         <f t="shared" si="8"/>
-        <v>45535.751810511123</v>
+        <v>45576.303453082051</v>
       </c>
     </row>
     <row r="8" spans="1:18" x14ac:dyDescent="0.25">
@@ -3498,19 +3508,19 @@
       </c>
       <c r="O8">
         <f t="shared" si="5"/>
-        <v>2740.7333333333336</v>
+        <v>2755.8461538461538</v>
       </c>
       <c r="P8" s="1">
         <f t="shared" si="6"/>
-        <v>46759.733333333337</v>
+        <v>46774.846153846156</v>
       </c>
       <c r="Q8">
         <f t="shared" si="7"/>
-        <v>1516.7518105111203</v>
+        <v>1557.3034530820539</v>
       </c>
       <c r="R8" s="1">
         <f t="shared" si="8"/>
-        <v>45535.751810511123</v>
+        <v>45576.303453082051</v>
       </c>
     </row>
     <row r="9" spans="1:18" x14ac:dyDescent="0.25">
@@ -3585,7 +3595,7 @@
       </c>
       <c r="L10">
         <f>AVERAGE(E:E)</f>
-        <v>9.3222222222222229</v>
+        <v>9.3736263736263741</v>
       </c>
     </row>
     <row r="11" spans="1:18" x14ac:dyDescent="0.25">
@@ -3626,7 +3636,7 @@
       </c>
       <c r="L11">
         <f>AVEDEV(I:I)</f>
-        <v>1.1136210062489871</v>
+        <v>1.1433946057871174</v>
       </c>
     </row>
     <row r="12" spans="1:18" x14ac:dyDescent="0.25">
@@ -5489,7 +5499,7 @@
         <v>526</v>
       </c>
       <c r="B66" t="str">
-        <f t="shared" ref="B66:B91" si="16">"卷"&amp;ROW(B65)</f>
+        <f t="shared" ref="B66:B92" si="16">"卷"&amp;ROW(B65)</f>
         <v>卷65</v>
       </c>
       <c r="C66" s="1">
@@ -6324,7 +6334,7 @@
         <v>卷89</v>
       </c>
       <c r="C90" s="1">
-        <f t="shared" ref="C90" si="40">D89+1</f>
+        <f t="shared" ref="C90:C92" si="40">D89+1</f>
         <v>44944</v>
       </c>
       <c r="D90" s="1">
@@ -6382,6 +6392,41 @@
       <c r="I91">
         <f t="shared" si="44"/>
         <v>5.5</v>
+      </c>
+    </row>
+    <row r="92" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A92">
+        <v>802</v>
+      </c>
+      <c r="B92" t="str">
+        <f t="shared" si="16"/>
+        <v>卷91</v>
+      </c>
+      <c r="C92" s="1">
+        <f t="shared" si="40"/>
+        <v>45030</v>
+      </c>
+      <c r="D92" s="1">
+        <v>45043</v>
+      </c>
+      <c r="E92">
+        <f t="shared" ref="E92" si="48">D92-C92+1</f>
+        <v>14</v>
+      </c>
+      <c r="F92">
+        <f t="shared" ref="F92" si="49">G91+1</f>
+        <v>319</v>
+      </c>
+      <c r="G92">
+        <v>321</v>
+      </c>
+      <c r="H92">
+        <f t="shared" ref="H92" si="50">IF(F92*G92&lt;0,ABS(F92)+ABS(G92),G92-F92+1)</f>
+        <v>3</v>
+      </c>
+      <c r="I92">
+        <f t="shared" ref="I92" si="51">E92/H92</f>
+        <v>4.666666666666667</v>
       </c>
     </row>
   </sheetData>
@@ -9111,24 +9156,27 @@
       <c r="A92">
         <v>802</v>
       </c>
-      <c r="B92" t="e">
+      <c r="B92" t="str">
         <f>VLOOKUP($A92,統計!$A:$G,2,)</f>
-        <v>#N/A</v>
+        <v>卷91</v>
       </c>
       <c r="C92" t="s">
         <v>287</v>
       </c>
-      <c r="D92" t="e">
+      <c r="D92">
         <f>VLOOKUP($A92,統計!$A:$G,6,)</f>
-        <v>#N/A</v>
-      </c>
-      <c r="E92" t="e">
+        <v>319</v>
+      </c>
+      <c r="E92">
         <f>VLOOKUP($A92,統計!$A:$G,7,)</f>
-        <v>#N/A</v>
-      </c>
-      <c r="I92" t="e">
+        <v>321</v>
+      </c>
+      <c r="H92" t="s">
+        <v>522</v>
+      </c>
+      <c r="I92" t="str">
         <f t="shared" si="1"/>
-        <v>#N/A</v>
+        <v>802|[卷91](5_筆記/资治通鉴91.html)|晉紀十三|319|321|||晉元帝3年至5年</v>
       </c>
     </row>
     <row r="93" spans="1:9" x14ac:dyDescent="0.25">

--- a/5_筆記/閱讀數據.xlsx
+++ b/5_筆記/閱讀數據.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="26227"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="26327"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\self\study\zizhitongjian\5_筆記\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{94315FB8-8059-4678-B4FA-7A69DA02ED9B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AC98C4AA-02E7-4AE0-97BC-7CD2F4DE48A7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="5440" yWindow="5460" windowWidth="32960" windowHeight="15540" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="38620" windowHeight="21220" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="統計" sheetId="1" r:id="rId1"/>
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="529" uniqueCount="523">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="531" uniqueCount="525">
   <si>
     <t>索引號</t>
   </si>
@@ -1602,6 +1602,13 @@
   </si>
   <si>
     <t>晉元帝3年至5年</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>晉元帝6年至7年、晉明帝元年</t>
+  </si>
+  <si>
+    <t>兩晉諸周氏世系</t>
     <phoneticPr fontId="4" type="noConversion"/>
   </si>
 </sst>
@@ -1906,7 +1913,7 @@
             <c:strRef>
               <c:f>統計!$B$2:$B$115</c:f>
               <c:strCache>
-                <c:ptCount val="91"/>
+                <c:ptCount val="92"/>
                 <c:pt idx="0">
                   <c:v>卷1</c:v>
                 </c:pt>
@@ -2179,6 +2186,9 @@
                 </c:pt>
                 <c:pt idx="90">
                   <c:v>卷91</c:v>
+                </c:pt>
+                <c:pt idx="91">
+                  <c:v>卷92</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
@@ -2461,6 +2471,9 @@
                 </c:pt>
                 <c:pt idx="90">
                   <c:v>4.666666666666667</c:v>
+                </c:pt>
+                <c:pt idx="91">
+                  <c:v>6</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -3015,7 +3028,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:R92"/>
+  <dimension ref="A1:R93"/>
   <sheetFormatPr defaultColWidth="8.6328125" defaultRowHeight="14" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="7.7265625" customWidth="1"/>
@@ -3130,19 +3143,19 @@
       </c>
       <c r="O2">
         <f t="shared" ref="O2:O8" si="5">L2*$L$10</f>
-        <v>637.4065934065934</v>
+        <v>639.3478260869565</v>
       </c>
       <c r="P2" s="1">
         <f t="shared" ref="P2:P8" si="6">$C$2+O2</f>
-        <v>44656.406593406595</v>
+        <v>44658.34782608696</v>
       </c>
       <c r="Q2">
         <f t="shared" ref="Q2:Q8" si="7">(M2-$F$2)*$L$11</f>
-        <v>712.33483940537417</v>
+        <v>741.89098059202263</v>
       </c>
       <c r="R2" s="1">
         <f t="shared" ref="R2:R8" si="8">$C$2+Q2</f>
-        <v>44731.334839405376</v>
+        <v>44760.890980592019</v>
       </c>
     </row>
     <row r="3" spans="1:18" x14ac:dyDescent="0.25">
@@ -3193,19 +3206,19 @@
       </c>
       <c r="O3">
         <f t="shared" si="5"/>
-        <v>731.14285714285722</v>
+        <v>733.36956521739137</v>
       </c>
       <c r="P3" s="1">
         <f t="shared" si="6"/>
-        <v>44750.142857142855</v>
+        <v>44752.369565217392</v>
       </c>
       <c r="Q3">
         <f t="shared" si="7"/>
-        <v>780.93851575260112</v>
+        <v>813.34115528788357</v>
       </c>
       <c r="R3" s="1">
         <f t="shared" si="8"/>
-        <v>44799.938515752598</v>
+        <v>44832.341155287882</v>
       </c>
     </row>
     <row r="4" spans="1:18" x14ac:dyDescent="0.25">
@@ -3256,19 +3269,19 @@
       </c>
       <c r="O4">
         <f t="shared" si="5"/>
-        <v>1106.0879120879122</v>
+        <v>1109.4565217391305</v>
       </c>
       <c r="P4" s="1">
         <f t="shared" si="6"/>
-        <v>45125.087912087911</v>
+        <v>45128.456521739128</v>
       </c>
       <c r="Q4">
         <f t="shared" si="7"/>
-        <v>941.01376056279764</v>
+        <v>980.05822957822579</v>
       </c>
       <c r="R4" s="1">
         <f t="shared" si="8"/>
-        <v>44960.013760562797</v>
+        <v>44999.058229578222</v>
       </c>
     </row>
     <row r="5" spans="1:18" x14ac:dyDescent="0.25">
@@ -3319,19 +3332,19 @@
       </c>
       <c r="O5">
         <f t="shared" si="5"/>
-        <v>1649.7582417582419</v>
+        <v>1654.7826086956522</v>
       </c>
       <c r="P5" s="1">
         <f t="shared" si="6"/>
-        <v>45668.758241758245</v>
+        <v>45673.782608695656</v>
       </c>
       <c r="Q5">
         <f t="shared" si="7"/>
-        <v>1134.2474489408205</v>
+        <v>1181.3095549715674</v>
       </c>
       <c r="R5" s="1">
         <f t="shared" si="8"/>
-        <v>45153.24744894082</v>
+        <v>45200.309554971565</v>
       </c>
     </row>
     <row r="6" spans="1:18" x14ac:dyDescent="0.25">
@@ -3382,19 +3395,19 @@
       </c>
       <c r="O6">
         <f t="shared" si="5"/>
-        <v>2484.0109890109893</v>
+        <v>2491.576086956522</v>
       </c>
       <c r="P6" s="1">
         <f t="shared" si="6"/>
-        <v>46503.010989010989</v>
+        <v>46510.57608695652</v>
       </c>
       <c r="Q6">
         <f t="shared" si="7"/>
-        <v>1497.8469335811237</v>
+        <v>1559.9954808596303</v>
       </c>
       <c r="R6" s="1">
         <f t="shared" si="8"/>
-        <v>45516.846933581124</v>
+        <v>45578.99548085963</v>
       </c>
     </row>
     <row r="7" spans="1:18" x14ac:dyDescent="0.25">
@@ -3445,19 +3458,19 @@
       </c>
       <c r="O7">
         <f t="shared" si="5"/>
-        <v>2755.8461538461538</v>
+        <v>2764.2391304347825</v>
       </c>
       <c r="P7" s="1">
         <f t="shared" si="6"/>
-        <v>46774.846153846156</v>
+        <v>46783.239130434784</v>
       </c>
       <c r="Q7">
         <f t="shared" si="7"/>
-        <v>1557.3034530820539</v>
+        <v>1621.9189655960431</v>
       </c>
       <c r="R7" s="1">
         <f t="shared" si="8"/>
-        <v>45576.303453082051</v>
+        <v>45640.918965596044</v>
       </c>
     </row>
     <row r="8" spans="1:18" x14ac:dyDescent="0.25">
@@ -3508,19 +3521,19 @@
       </c>
       <c r="O8">
         <f t="shared" si="5"/>
-        <v>2755.8461538461538</v>
+        <v>2764.2391304347825</v>
       </c>
       <c r="P8" s="1">
         <f t="shared" si="6"/>
-        <v>46774.846153846156</v>
+        <v>46783.239130434784</v>
       </c>
       <c r="Q8">
         <f t="shared" si="7"/>
-        <v>1557.3034530820539</v>
+        <v>1621.9189655960431</v>
       </c>
       <c r="R8" s="1">
         <f t="shared" si="8"/>
-        <v>45576.303453082051</v>
+        <v>45640.918965596044</v>
       </c>
     </row>
     <row r="9" spans="1:18" x14ac:dyDescent="0.25">
@@ -3595,7 +3608,7 @@
       </c>
       <c r="L10">
         <f>AVERAGE(E:E)</f>
-        <v>9.3736263736263741</v>
+        <v>9.4021739130434785</v>
       </c>
     </row>
     <row r="11" spans="1:18" x14ac:dyDescent="0.25">
@@ -3636,7 +3649,7 @@
       </c>
       <c r="L11">
         <f>AVEDEV(I:I)</f>
-        <v>1.1433946057871174</v>
+        <v>1.1908362449310155</v>
       </c>
     </row>
     <row r="12" spans="1:18" x14ac:dyDescent="0.25">
@@ -5499,7 +5512,7 @@
         <v>526</v>
       </c>
       <c r="B66" t="str">
-        <f t="shared" ref="B66:B92" si="16">"卷"&amp;ROW(B65)</f>
+        <f t="shared" ref="B66:B93" si="16">"卷"&amp;ROW(B65)</f>
         <v>卷65</v>
       </c>
       <c r="C66" s="1">
@@ -6427,6 +6440,41 @@
       <c r="I92">
         <f t="shared" ref="I92" si="51">E92/H92</f>
         <v>4.666666666666667</v>
+      </c>
+    </row>
+    <row r="93" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A93">
+        <v>803</v>
+      </c>
+      <c r="B93" t="str">
+        <f t="shared" si="16"/>
+        <v>卷92</v>
+      </c>
+      <c r="C93" s="1">
+        <f t="shared" ref="C93" si="52">D92+1</f>
+        <v>45044</v>
+      </c>
+      <c r="D93" s="1">
+        <v>45055</v>
+      </c>
+      <c r="E93">
+        <f t="shared" ref="E93" si="53">D93-C93+1</f>
+        <v>12</v>
+      </c>
+      <c r="F93">
+        <f t="shared" ref="F93" si="54">G92+1</f>
+        <v>322</v>
+      </c>
+      <c r="G93">
+        <v>323</v>
+      </c>
+      <c r="H93">
+        <f t="shared" ref="H93" si="55">IF(F93*G93&lt;0,ABS(F93)+ABS(G93),G93-F93+1)</f>
+        <v>2</v>
+      </c>
+      <c r="I93">
+        <f t="shared" ref="I93" si="56">E93/H93</f>
+        <v>6</v>
       </c>
     </row>
   </sheetData>
@@ -9183,24 +9231,30 @@
       <c r="A93">
         <v>803</v>
       </c>
-      <c r="B93" t="e">
+      <c r="B93" t="str">
         <f>VLOOKUP($A93,統計!$A:$G,2,)</f>
-        <v>#N/A</v>
+        <v>卷92</v>
       </c>
       <c r="C93" t="s">
         <v>288</v>
       </c>
-      <c r="D93" t="e">
+      <c r="D93">
         <f>VLOOKUP($A93,統計!$A:$G,6,)</f>
-        <v>#N/A</v>
-      </c>
-      <c r="E93" t="e">
+        <v>322</v>
+      </c>
+      <c r="E93">
         <f>VLOOKUP($A93,統計!$A:$G,7,)</f>
-        <v>#N/A</v>
-      </c>
-      <c r="I93" t="e">
+        <v>323</v>
+      </c>
+      <c r="F93" t="s">
+        <v>524</v>
+      </c>
+      <c r="H93" t="s">
+        <v>523</v>
+      </c>
+      <c r="I93" t="str">
         <f t="shared" si="1"/>
-        <v>#N/A</v>
+        <v>803|[卷92](5_筆記/资治通鉴92.html)|晉紀十四|322|323|兩晉諸周氏世系||晉元帝6年至7年、晉明帝元年</v>
       </c>
     </row>
     <row r="94" spans="1:9" x14ac:dyDescent="0.25">

--- a/5_筆記/閱讀數據.xlsx
+++ b/5_筆記/閱讀數據.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\self\study\zizhitongjian\5_筆記\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AC98C4AA-02E7-4AE0-97BC-7CD2F4DE48A7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D2879E27-31AB-4FE2-BBEA-E214ED1793EA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="38620" windowHeight="21220" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="531" uniqueCount="525">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="532" uniqueCount="526">
   <si>
     <t>索引號</t>
   </si>
@@ -1609,6 +1609,10 @@
   </si>
   <si>
     <t>兩晉諸周氏世系</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>晉明帝2年至3年、晉成帝至3年</t>
     <phoneticPr fontId="4" type="noConversion"/>
   </si>
 </sst>
@@ -1913,7 +1917,7 @@
             <c:strRef>
               <c:f>統計!$B$2:$B$115</c:f>
               <c:strCache>
-                <c:ptCount val="92"/>
+                <c:ptCount val="93"/>
                 <c:pt idx="0">
                   <c:v>卷1</c:v>
                 </c:pt>
@@ -2189,6 +2193,9 @@
                 </c:pt>
                 <c:pt idx="91">
                   <c:v>卷92</c:v>
+                </c:pt>
+                <c:pt idx="92">
+                  <c:v>卷93</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
@@ -2474,6 +2481,9 @@
                 </c:pt>
                 <c:pt idx="91">
                   <c:v>6</c:v>
+                </c:pt>
+                <c:pt idx="92">
+                  <c:v>4</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -3028,7 +3038,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:R93"/>
+  <dimension ref="A1:R94"/>
   <sheetFormatPr defaultColWidth="8.6328125" defaultRowHeight="14" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="7.7265625" customWidth="1"/>
@@ -3143,19 +3153,19 @@
       </c>
       <c r="O2">
         <f t="shared" ref="O2:O8" si="5">L2*$L$10</f>
-        <v>639.3478260869565</v>
+        <v>644.17204301075265</v>
       </c>
       <c r="P2" s="1">
         <f t="shared" ref="P2:P8" si="6">$C$2+O2</f>
-        <v>44658.34782608696</v>
+        <v>44663.172043010753</v>
       </c>
       <c r="Q2">
         <f t="shared" ref="Q2:Q8" si="7">(M2-$F$2)*$L$11</f>
-        <v>741.89098059202263</v>
+        <v>752.4423302515728</v>
       </c>
       <c r="R2" s="1">
         <f t="shared" ref="R2:R8" si="8">$C$2+Q2</f>
-        <v>44760.890980592019</v>
+        <v>44771.442330251572</v>
       </c>
     </row>
     <row r="3" spans="1:18" x14ac:dyDescent="0.25">
@@ -3206,19 +3216,19 @@
       </c>
       <c r="O3">
         <f t="shared" si="5"/>
-        <v>733.36956521739137</v>
+        <v>738.90322580645159</v>
       </c>
       <c r="P3" s="1">
         <f t="shared" si="6"/>
-        <v>44752.369565217392</v>
+        <v>44757.903225806454</v>
       </c>
       <c r="Q3">
         <f t="shared" si="7"/>
-        <v>813.34115528788357</v>
+        <v>824.90868629506292</v>
       </c>
       <c r="R3" s="1">
         <f t="shared" si="8"/>
-        <v>44832.341155287882</v>
+        <v>44843.908686295064</v>
       </c>
     </row>
     <row r="4" spans="1:18" x14ac:dyDescent="0.25">
@@ -3269,19 +3279,19 @@
       </c>
       <c r="O4">
         <f t="shared" si="5"/>
-        <v>1109.4565217391305</v>
+        <v>1117.8279569892472</v>
       </c>
       <c r="P4" s="1">
         <f t="shared" si="6"/>
-        <v>45128.456521739128</v>
+        <v>45136.827956989247</v>
       </c>
       <c r="Q4">
         <f t="shared" si="7"/>
-        <v>980.05822957822579</v>
+        <v>993.99685039654003</v>
       </c>
       <c r="R4" s="1">
         <f t="shared" si="8"/>
-        <v>44999.058229578222</v>
+        <v>45012.996850396543</v>
       </c>
     </row>
     <row r="5" spans="1:18" x14ac:dyDescent="0.25">
@@ -3332,19 +3342,19 @@
       </c>
       <c r="O5">
         <f t="shared" si="5"/>
-        <v>1654.7826086956522</v>
+        <v>1667.2688172043011</v>
       </c>
       <c r="P5" s="1">
         <f t="shared" si="6"/>
-        <v>45673.782608695656</v>
+        <v>45686.268817204298</v>
       </c>
       <c r="Q5">
         <f t="shared" si="7"/>
-        <v>1181.3095549715674</v>
+        <v>1198.1104199190372</v>
       </c>
       <c r="R5" s="1">
         <f t="shared" si="8"/>
-        <v>45200.309554971565</v>
+        <v>45217.110419919038</v>
       </c>
     </row>
     <row r="6" spans="1:18" x14ac:dyDescent="0.25">
@@ -3395,19 +3405,19 @@
       </c>
       <c r="O6">
         <f t="shared" si="5"/>
-        <v>2491.576086956522</v>
+        <v>2510.3763440860216</v>
       </c>
       <c r="P6" s="1">
         <f t="shared" si="6"/>
-        <v>46510.57608695652</v>
+        <v>46529.37634408602</v>
       </c>
       <c r="Q6">
         <f t="shared" si="7"/>
-        <v>1559.9954808596303</v>
+        <v>1582.1821069495352</v>
       </c>
       <c r="R6" s="1">
         <f t="shared" si="8"/>
-        <v>45578.99548085963</v>
+        <v>45601.182106949535</v>
       </c>
     </row>
     <row r="7" spans="1:18" x14ac:dyDescent="0.25">
@@ -3458,19 +3468,19 @@
       </c>
       <c r="O7">
         <f t="shared" si="5"/>
-        <v>2764.2391304347825</v>
+        <v>2785.0967741935483</v>
       </c>
       <c r="P7" s="1">
         <f t="shared" si="6"/>
-        <v>46783.239130434784</v>
+        <v>46804.096774193546</v>
       </c>
       <c r="Q7">
         <f t="shared" si="7"/>
-        <v>1621.9189655960431</v>
+        <v>1644.9862821872266</v>
       </c>
       <c r="R7" s="1">
         <f t="shared" si="8"/>
-        <v>45640.918965596044</v>
+        <v>45663.986282187223</v>
       </c>
     </row>
     <row r="8" spans="1:18" x14ac:dyDescent="0.25">
@@ -3521,19 +3531,19 @@
       </c>
       <c r="O8">
         <f t="shared" si="5"/>
-        <v>2764.2391304347825</v>
+        <v>2785.0967741935483</v>
       </c>
       <c r="P8" s="1">
         <f t="shared" si="6"/>
-        <v>46783.239130434784</v>
+        <v>46804.096774193546</v>
       </c>
       <c r="Q8">
         <f t="shared" si="7"/>
-        <v>1621.9189655960431</v>
+        <v>1644.9862821872266</v>
       </c>
       <c r="R8" s="1">
         <f t="shared" si="8"/>
-        <v>45640.918965596044</v>
+        <v>45663.986282187223</v>
       </c>
     </row>
     <row r="9" spans="1:18" x14ac:dyDescent="0.25">
@@ -3608,7 +3618,7 @@
       </c>
       <c r="L10">
         <f>AVERAGE(E:E)</f>
-        <v>9.4021739130434785</v>
+        <v>9.4731182795698921</v>
       </c>
     </row>
     <row r="11" spans="1:18" x14ac:dyDescent="0.25">
@@ -3649,7 +3659,7 @@
       </c>
       <c r="L11">
         <f>AVEDEV(I:I)</f>
-        <v>1.1908362449310155</v>
+        <v>1.2077726007248359</v>
       </c>
     </row>
     <row r="12" spans="1:18" x14ac:dyDescent="0.25">
@@ -5512,7 +5522,7 @@
         <v>526</v>
       </c>
       <c r="B66" t="str">
-        <f t="shared" ref="B66:B93" si="16">"卷"&amp;ROW(B65)</f>
+        <f t="shared" ref="B66:B94" si="16">"卷"&amp;ROW(B65)</f>
         <v>卷65</v>
       </c>
       <c r="C66" s="1">
@@ -6475,6 +6485,41 @@
       <c r="I93">
         <f t="shared" ref="I93" si="56">E93/H93</f>
         <v>6</v>
+      </c>
+    </row>
+    <row r="94" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A94">
+        <v>804</v>
+      </c>
+      <c r="B94" t="str">
+        <f t="shared" si="16"/>
+        <v>卷93</v>
+      </c>
+      <c r="C94" s="1">
+        <f t="shared" ref="C94" si="57">D93+1</f>
+        <v>45056</v>
+      </c>
+      <c r="D94" s="1">
+        <v>45071</v>
+      </c>
+      <c r="E94">
+        <f t="shared" ref="E94" si="58">D94-C94+1</f>
+        <v>16</v>
+      </c>
+      <c r="F94">
+        <f t="shared" ref="F94" si="59">G93+1</f>
+        <v>324</v>
+      </c>
+      <c r="G94">
+        <v>327</v>
+      </c>
+      <c r="H94">
+        <f t="shared" ref="H94" si="60">IF(F94*G94&lt;0,ABS(F94)+ABS(G94),G94-F94+1)</f>
+        <v>4</v>
+      </c>
+      <c r="I94">
+        <f t="shared" ref="I94" si="61">E94/H94</f>
+        <v>4</v>
       </c>
     </row>
   </sheetData>
@@ -9261,24 +9306,27 @@
       <c r="A94">
         <v>804</v>
       </c>
-      <c r="B94" t="e">
+      <c r="B94" t="str">
         <f>VLOOKUP($A94,統計!$A:$G,2,)</f>
-        <v>#N/A</v>
+        <v>卷93</v>
       </c>
       <c r="C94" t="s">
         <v>289</v>
       </c>
-      <c r="D94" t="e">
+      <c r="D94">
         <f>VLOOKUP($A94,統計!$A:$G,6,)</f>
-        <v>#N/A</v>
-      </c>
-      <c r="E94" t="e">
+        <v>324</v>
+      </c>
+      <c r="E94">
         <f>VLOOKUP($A94,統計!$A:$G,7,)</f>
-        <v>#N/A</v>
-      </c>
-      <c r="I94" t="e">
+        <v>327</v>
+      </c>
+      <c r="H94" t="s">
+        <v>525</v>
+      </c>
+      <c r="I94" t="str">
         <f t="shared" si="1"/>
-        <v>#N/A</v>
+        <v>804|[卷93](5_筆記/资治通鉴93.html)|晉紀十五|324|327|||晉明帝2年至3年、晉成帝至3年</v>
       </c>
     </row>
     <row r="95" spans="1:9" x14ac:dyDescent="0.25">

--- a/5_筆記/閱讀數據.xlsx
+++ b/5_筆記/閱讀數據.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\self\study\zizhitongjian\5_筆記\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D2879E27-31AB-4FE2-BBEA-E214ED1793EA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5588C885-706F-4CBF-8E14-E251747197EA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="38620" windowHeight="21220" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="532" uniqueCount="526">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="533" uniqueCount="527">
   <si>
     <t>索引號</t>
   </si>
@@ -1613,6 +1613,10 @@
   </si>
   <si>
     <t>晉明帝2年至3年、晉成帝至3年</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>晉成帝4年至7年</t>
     <phoneticPr fontId="4" type="noConversion"/>
   </si>
 </sst>
@@ -1917,7 +1921,7 @@
             <c:strRef>
               <c:f>統計!$B$2:$B$115</c:f>
               <c:strCache>
-                <c:ptCount val="93"/>
+                <c:ptCount val="94"/>
                 <c:pt idx="0">
                   <c:v>卷1</c:v>
                 </c:pt>
@@ -2196,6 +2200,9 @@
                 </c:pt>
                 <c:pt idx="92">
                   <c:v>卷93</c:v>
+                </c:pt>
+                <c:pt idx="93">
+                  <c:v>卷94</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
@@ -2483,6 +2490,9 @@
                   <c:v>6</c:v>
                 </c:pt>
                 <c:pt idx="92">
+                  <c:v>4</c:v>
+                </c:pt>
+                <c:pt idx="93">
                   <c:v>4</c:v>
                 </c:pt>
               </c:numCache>
@@ -3038,7 +3048,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:R94"/>
+  <dimension ref="A1:R95"/>
   <sheetFormatPr defaultColWidth="8.6328125" defaultRowHeight="14" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="7.7265625" customWidth="1"/>
@@ -3153,19 +3163,19 @@
       </c>
       <c r="O2">
         <f t="shared" ref="O2:O8" si="5">L2*$L$10</f>
-        <v>644.17204301075265</v>
+        <v>648.89361702127655</v>
       </c>
       <c r="P2" s="1">
         <f t="shared" ref="P2:P8" si="6">$C$2+O2</f>
-        <v>44663.172043010753</v>
+        <v>44667.893617021276</v>
       </c>
       <c r="Q2">
         <f t="shared" ref="Q2:Q8" si="7">(M2-$F$2)*$L$11</f>
-        <v>752.4423302515728</v>
+        <v>762.37914995029746</v>
       </c>
       <c r="R2" s="1">
         <f t="shared" ref="R2:R8" si="8">$C$2+Q2</f>
-        <v>44771.442330251572</v>
+        <v>44781.379149950299</v>
       </c>
     </row>
     <row r="3" spans="1:18" x14ac:dyDescent="0.25">
@@ -3216,19 +3226,19 @@
       </c>
       <c r="O3">
         <f t="shared" si="5"/>
-        <v>738.90322580645159</v>
+        <v>744.31914893617022</v>
       </c>
       <c r="P3" s="1">
         <f t="shared" si="6"/>
-        <v>44757.903225806454</v>
+        <v>44763.319148936171</v>
       </c>
       <c r="Q3">
         <f t="shared" si="7"/>
-        <v>824.90868629506292</v>
+        <v>835.80250307552672</v>
       </c>
       <c r="R3" s="1">
         <f t="shared" si="8"/>
-        <v>44843.908686295064</v>
+        <v>44854.802503075523</v>
       </c>
     </row>
     <row r="4" spans="1:18" x14ac:dyDescent="0.25">
@@ -3279,19 +3289,19 @@
       </c>
       <c r="O4">
         <f t="shared" si="5"/>
-        <v>1117.8279569892472</v>
+        <v>1126.0212765957447</v>
       </c>
       <c r="P4" s="1">
         <f t="shared" si="6"/>
-        <v>45136.827956989247</v>
+        <v>45145.021276595748</v>
       </c>
       <c r="Q4">
         <f t="shared" si="7"/>
-        <v>993.99685039654003</v>
+        <v>1007.1236603677285</v>
       </c>
       <c r="R4" s="1">
         <f t="shared" si="8"/>
-        <v>45012.996850396543</v>
+        <v>45026.123660367732</v>
       </c>
     </row>
     <row r="5" spans="1:18" x14ac:dyDescent="0.25">
@@ -3342,19 +3352,19 @@
       </c>
       <c r="O5">
         <f t="shared" si="5"/>
-        <v>1667.2688172043011</v>
+        <v>1679.4893617021276</v>
       </c>
       <c r="P5" s="1">
         <f t="shared" si="6"/>
-        <v>45686.268817204298</v>
+        <v>45698.48936170213</v>
       </c>
       <c r="Q5">
         <f t="shared" si="7"/>
-        <v>1198.1104199190372</v>
+        <v>1213.9327716704577</v>
       </c>
       <c r="R5" s="1">
         <f t="shared" si="8"/>
-        <v>45217.110419919038</v>
+        <v>45232.932771670457</v>
       </c>
     </row>
     <row r="6" spans="1:18" x14ac:dyDescent="0.25">
@@ -3405,19 +3415,19 @@
       </c>
       <c r="O6">
         <f t="shared" si="5"/>
-        <v>2510.3763440860216</v>
+        <v>2528.7765957446809</v>
       </c>
       <c r="P6" s="1">
         <f t="shared" si="6"/>
-        <v>46529.37634408602</v>
+        <v>46547.776595744683</v>
       </c>
       <c r="Q6">
         <f t="shared" si="7"/>
-        <v>1582.1821069495352</v>
+        <v>1603.076543234173</v>
       </c>
       <c r="R6" s="1">
         <f t="shared" si="8"/>
-        <v>45601.182106949535</v>
+        <v>45622.076543234172</v>
       </c>
     </row>
     <row r="7" spans="1:18" x14ac:dyDescent="0.25">
@@ -3468,19 +3478,19 @@
       </c>
       <c r="O7">
         <f t="shared" si="5"/>
-        <v>2785.0967741935483</v>
+        <v>2805.510638297872</v>
       </c>
       <c r="P7" s="1">
         <f t="shared" si="6"/>
-        <v>46804.096774193546</v>
+        <v>46824.51063829787</v>
       </c>
       <c r="Q7">
         <f t="shared" si="7"/>
-        <v>1644.9862821872266</v>
+        <v>1666.710115942705</v>
       </c>
       <c r="R7" s="1">
         <f t="shared" si="8"/>
-        <v>45663.986282187223</v>
+        <v>45685.710115942704</v>
       </c>
     </row>
     <row r="8" spans="1:18" x14ac:dyDescent="0.25">
@@ -3531,19 +3541,19 @@
       </c>
       <c r="O8">
         <f t="shared" si="5"/>
-        <v>2785.0967741935483</v>
+        <v>2805.510638297872</v>
       </c>
       <c r="P8" s="1">
         <f t="shared" si="6"/>
-        <v>46804.096774193546</v>
+        <v>46824.51063829787</v>
       </c>
       <c r="Q8">
         <f t="shared" si="7"/>
-        <v>1644.9862821872266</v>
+        <v>1666.710115942705</v>
       </c>
       <c r="R8" s="1">
         <f t="shared" si="8"/>
-        <v>45663.986282187223</v>
+        <v>45685.710115942704</v>
       </c>
     </row>
     <row r="9" spans="1:18" x14ac:dyDescent="0.25">
@@ -3618,7 +3628,7 @@
       </c>
       <c r="L10">
         <f>AVERAGE(E:E)</f>
-        <v>9.4731182795698921</v>
+        <v>9.5425531914893611</v>
       </c>
     </row>
     <row r="11" spans="1:18" x14ac:dyDescent="0.25">
@@ -3659,7 +3669,7 @@
       </c>
       <c r="L11">
         <f>AVEDEV(I:I)</f>
-        <v>1.2077726007248359</v>
+        <v>1.2237225520871549</v>
       </c>
     </row>
     <row r="12" spans="1:18" x14ac:dyDescent="0.25">
@@ -5522,7 +5532,7 @@
         <v>526</v>
       </c>
       <c r="B66" t="str">
-        <f t="shared" ref="B66:B94" si="16">"卷"&amp;ROW(B65)</f>
+        <f t="shared" ref="B66:B95" si="16">"卷"&amp;ROW(B65)</f>
         <v>卷65</v>
       </c>
       <c r="C66" s="1">
@@ -6519,6 +6529,41 @@
       </c>
       <c r="I94">
         <f t="shared" ref="I94" si="61">E94/H94</f>
+        <v>4</v>
+      </c>
+    </row>
+    <row r="95" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A95">
+        <v>805</v>
+      </c>
+      <c r="B95" t="str">
+        <f t="shared" si="16"/>
+        <v>卷94</v>
+      </c>
+      <c r="C95" s="1">
+        <f t="shared" ref="C95" si="62">D94+1</f>
+        <v>45072</v>
+      </c>
+      <c r="D95" s="1">
+        <v>45087</v>
+      </c>
+      <c r="E95">
+        <f t="shared" ref="E95" si="63">D95-C95+1</f>
+        <v>16</v>
+      </c>
+      <c r="F95">
+        <f t="shared" ref="F95" si="64">G94+1</f>
+        <v>328</v>
+      </c>
+      <c r="G95">
+        <v>331</v>
+      </c>
+      <c r="H95">
+        <f t="shared" ref="H95" si="65">IF(F95*G95&lt;0,ABS(F95)+ABS(G95),G95-F95+1)</f>
+        <v>4</v>
+      </c>
+      <c r="I95">
+        <f t="shared" ref="I95" si="66">E95/H95</f>
         <v>4</v>
       </c>
     </row>
@@ -9333,24 +9378,27 @@
       <c r="A95">
         <v>805</v>
       </c>
-      <c r="B95" t="e">
+      <c r="B95" t="str">
         <f>VLOOKUP($A95,統計!$A:$G,2,)</f>
-        <v>#N/A</v>
+        <v>卷94</v>
       </c>
       <c r="C95" t="s">
         <v>290</v>
       </c>
-      <c r="D95" t="e">
+      <c r="D95">
         <f>VLOOKUP($A95,統計!$A:$G,6,)</f>
-        <v>#N/A</v>
-      </c>
-      <c r="E95" t="e">
+        <v>328</v>
+      </c>
+      <c r="E95">
         <f>VLOOKUP($A95,統計!$A:$G,7,)</f>
-        <v>#N/A</v>
-      </c>
-      <c r="I95" t="e">
+        <v>331</v>
+      </c>
+      <c r="H95" t="s">
+        <v>526</v>
+      </c>
+      <c r="I95" t="str">
         <f t="shared" si="1"/>
-        <v>#N/A</v>
+        <v>805|[卷94](5_筆記/资治通鉴94.html)|晉紀十六|328|331|||晉成帝4年至7年</v>
       </c>
     </row>
     <row r="96" spans="1:9" x14ac:dyDescent="0.25">

--- a/5_筆記/閱讀數據.xlsx
+++ b/5_筆記/閱讀數據.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="26327"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="26501"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\self\study\zizhitongjian\5_筆記\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5588C885-706F-4CBF-8E14-E251747197EA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2D573459-EEA9-4704-8DA1-CBF3CBAC5DBC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="38620" windowHeight="21220" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="38620" windowHeight="21220" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="統計" sheetId="1" r:id="rId1"/>
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="533" uniqueCount="527">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="534" uniqueCount="528">
   <si>
     <t>索引號</t>
   </si>
@@ -1617,6 +1617,10 @@
   </si>
   <si>
     <t>晉成帝4年至7年</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>晉成帝8年至13年</t>
     <phoneticPr fontId="4" type="noConversion"/>
   </si>
 </sst>
@@ -1921,7 +1925,7 @@
             <c:strRef>
               <c:f>統計!$B$2:$B$115</c:f>
               <c:strCache>
-                <c:ptCount val="94"/>
+                <c:ptCount val="95"/>
                 <c:pt idx="0">
                   <c:v>卷1</c:v>
                 </c:pt>
@@ -2203,6 +2207,9 @@
                 </c:pt>
                 <c:pt idx="93">
                   <c:v>卷94</c:v>
+                </c:pt>
+                <c:pt idx="94">
+                  <c:v>卷95</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
@@ -2494,6 +2501,9 @@
                 </c:pt>
                 <c:pt idx="93">
                   <c:v>4</c:v>
+                </c:pt>
+                <c:pt idx="94">
+                  <c:v>2.8333333333333335</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -3048,7 +3058,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:R95"/>
+  <dimension ref="A1:R96"/>
   <sheetFormatPr defaultColWidth="8.6328125" defaultRowHeight="14" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="7.7265625" customWidth="1"/>
@@ -3163,19 +3173,19 @@
       </c>
       <c r="O2">
         <f t="shared" ref="O2:O8" si="5">L2*$L$10</f>
-        <v>648.89361702127655</v>
+        <v>654.23157894736846</v>
       </c>
       <c r="P2" s="1">
         <f t="shared" ref="P2:P8" si="6">$C$2+O2</f>
-        <v>44667.893617021276</v>
+        <v>44673.231578947365</v>
       </c>
       <c r="Q2">
         <f t="shared" ref="Q2:Q8" si="7">(M2-$F$2)*$L$11</f>
-        <v>762.37914995029746</v>
+        <v>761.90769605641435</v>
       </c>
       <c r="R2" s="1">
         <f t="shared" ref="R2:R8" si="8">$C$2+Q2</f>
-        <v>44781.379149950299</v>
+        <v>44780.907696056413</v>
       </c>
     </row>
     <row r="3" spans="1:18" x14ac:dyDescent="0.25">
@@ -3226,19 +3236,19 @@
       </c>
       <c r="O3">
         <f t="shared" si="5"/>
-        <v>744.31914893617022</v>
+        <v>750.44210526315794</v>
       </c>
       <c r="P3" s="1">
         <f t="shared" si="6"/>
-        <v>44763.319148936171</v>
+        <v>44769.442105263159</v>
       </c>
       <c r="Q3">
         <f t="shared" si="7"/>
-        <v>835.80250307552672</v>
+        <v>835.28564431224891</v>
       </c>
       <c r="R3" s="1">
         <f t="shared" si="8"/>
-        <v>44854.802503075523</v>
+        <v>44854.285644312251</v>
       </c>
     </row>
     <row r="4" spans="1:18" x14ac:dyDescent="0.25">
@@ -3289,19 +3299,19 @@
       </c>
       <c r="O4">
         <f t="shared" si="5"/>
-        <v>1126.0212765957447</v>
+        <v>1135.2842105263157</v>
       </c>
       <c r="P4" s="1">
         <f t="shared" si="6"/>
-        <v>45145.021276595748</v>
+        <v>45154.284210526319</v>
       </c>
       <c r="Q4">
         <f t="shared" si="7"/>
-        <v>1007.1236603677285</v>
+        <v>1006.5008569091959</v>
       </c>
       <c r="R4" s="1">
         <f t="shared" si="8"/>
-        <v>45026.123660367732</v>
+        <v>45025.500856909195</v>
       </c>
     </row>
     <row r="5" spans="1:18" x14ac:dyDescent="0.25">
@@ -3352,19 +3362,19 @@
       </c>
       <c r="O5">
         <f t="shared" si="5"/>
-        <v>1679.4893617021276</v>
+        <v>1693.3052631578948</v>
       </c>
       <c r="P5" s="1">
         <f t="shared" si="6"/>
-        <v>45698.48936170213</v>
+        <v>45712.305263157898</v>
       </c>
       <c r="Q5">
         <f t="shared" si="7"/>
-        <v>1213.9327716704577</v>
+        <v>1213.1820778297963</v>
       </c>
       <c r="R5" s="1">
         <f t="shared" si="8"/>
-        <v>45232.932771670457</v>
+        <v>45232.182077829799</v>
       </c>
     </row>
     <row r="6" spans="1:18" x14ac:dyDescent="0.25">
@@ -3415,19 +3425,19 @@
       </c>
       <c r="O6">
         <f t="shared" si="5"/>
-        <v>2528.7765957446809</v>
+        <v>2549.5789473684213</v>
       </c>
       <c r="P6" s="1">
         <f t="shared" si="6"/>
-        <v>46547.776595744683</v>
+        <v>46568.57894736842</v>
       </c>
       <c r="Q6">
         <f t="shared" si="7"/>
-        <v>1603.076543234173</v>
+        <v>1602.085203585719</v>
       </c>
       <c r="R6" s="1">
         <f t="shared" si="8"/>
-        <v>45622.076543234172</v>
+        <v>45621.085203585717</v>
       </c>
     </row>
     <row r="7" spans="1:18" x14ac:dyDescent="0.25">
@@ -3478,19 +3488,19 @@
       </c>
       <c r="O7">
         <f t="shared" si="5"/>
-        <v>2805.510638297872</v>
+        <v>2828.5894736842106</v>
       </c>
       <c r="P7" s="1">
         <f t="shared" si="6"/>
-        <v>46824.51063829787</v>
+        <v>46847.589473684209</v>
       </c>
       <c r="Q7">
         <f t="shared" si="7"/>
-        <v>1666.710115942705</v>
+        <v>1665.6794254074421</v>
       </c>
       <c r="R7" s="1">
         <f t="shared" si="8"/>
-        <v>45685.710115942704</v>
+        <v>45684.679425407441</v>
       </c>
     </row>
     <row r="8" spans="1:18" x14ac:dyDescent="0.25">
@@ -3541,19 +3551,19 @@
       </c>
       <c r="O8">
         <f t="shared" si="5"/>
-        <v>2805.510638297872</v>
+        <v>2828.5894736842106</v>
       </c>
       <c r="P8" s="1">
         <f t="shared" si="6"/>
-        <v>46824.51063829787</v>
+        <v>46847.589473684209</v>
       </c>
       <c r="Q8">
         <f t="shared" si="7"/>
-        <v>1666.710115942705</v>
+        <v>1665.6794254074421</v>
       </c>
       <c r="R8" s="1">
         <f t="shared" si="8"/>
-        <v>45685.710115942704</v>
+        <v>45684.679425407441</v>
       </c>
     </row>
     <row r="9" spans="1:18" x14ac:dyDescent="0.25">
@@ -3628,7 +3638,7 @@
       </c>
       <c r="L10">
         <f>AVERAGE(E:E)</f>
-        <v>9.5425531914893611</v>
+        <v>9.621052631578948</v>
       </c>
     </row>
     <row r="11" spans="1:18" x14ac:dyDescent="0.25">
@@ -3669,7 +3679,7 @@
       </c>
       <c r="L11">
         <f>AVEDEV(I:I)</f>
-        <v>1.2237225520871549</v>
+        <v>1.2229658042639076</v>
       </c>
     </row>
     <row r="12" spans="1:18" x14ac:dyDescent="0.25">
@@ -5532,7 +5542,7 @@
         <v>526</v>
       </c>
       <c r="B66" t="str">
-        <f t="shared" ref="B66:B95" si="16">"卷"&amp;ROW(B65)</f>
+        <f t="shared" ref="B66:B96" si="16">"卷"&amp;ROW(B65)</f>
         <v>卷65</v>
       </c>
       <c r="C66" s="1">
@@ -6565,6 +6575,40 @@
       <c r="I95">
         <f t="shared" ref="I95" si="66">E95/H95</f>
         <v>4</v>
+      </c>
+    </row>
+    <row r="96" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A96">
+        <v>806</v>
+      </c>
+      <c r="B96" t="str">
+        <f t="shared" si="16"/>
+        <v>卷95</v>
+      </c>
+      <c r="C96" s="1">
+        <v>45089</v>
+      </c>
+      <c r="D96" s="1">
+        <v>45105</v>
+      </c>
+      <c r="E96">
+        <f t="shared" ref="E96" si="67">D96-C96+1</f>
+        <v>17</v>
+      </c>
+      <c r="F96">
+        <f t="shared" ref="F96" si="68">G95+1</f>
+        <v>332</v>
+      </c>
+      <c r="G96">
+        <v>337</v>
+      </c>
+      <c r="H96">
+        <f t="shared" ref="H96" si="69">IF(F96*G96&lt;0,ABS(F96)+ABS(G96),G96-F96+1)</f>
+        <v>6</v>
+      </c>
+      <c r="I96">
+        <f t="shared" ref="I96" si="70">E96/H96</f>
+        <v>2.8333333333333335</v>
       </c>
     </row>
   </sheetData>
@@ -9405,24 +9449,27 @@
       <c r="A96">
         <v>806</v>
       </c>
-      <c r="B96" t="e">
+      <c r="B96" t="str">
         <f>VLOOKUP($A96,統計!$A:$G,2,)</f>
-        <v>#N/A</v>
+        <v>卷95</v>
       </c>
       <c r="C96" t="s">
         <v>291</v>
       </c>
-      <c r="D96" t="e">
+      <c r="D96">
         <f>VLOOKUP($A96,統計!$A:$G,6,)</f>
-        <v>#N/A</v>
-      </c>
-      <c r="E96" t="e">
+        <v>332</v>
+      </c>
+      <c r="E96">
         <f>VLOOKUP($A96,統計!$A:$G,7,)</f>
-        <v>#N/A</v>
-      </c>
-      <c r="I96" t="e">
+        <v>337</v>
+      </c>
+      <c r="H96" t="s">
+        <v>527</v>
+      </c>
+      <c r="I96" t="str">
         <f t="shared" si="1"/>
-        <v>#N/A</v>
+        <v>806|[卷95](5_筆記/资治通鉴95.html)|晉紀十七|332|337|||晉成帝8年至13年</v>
       </c>
     </row>
     <row r="97" spans="1:9" x14ac:dyDescent="0.25">

--- a/5_筆記/閱讀數據.xlsx
+++ b/5_筆記/閱讀數據.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="26501"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="26529"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\self\study\zizhitongjian\5_筆記\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2D573459-EEA9-4704-8DA1-CBF3CBAC5DBC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2604F92B-F06D-4522-8647-2AD92167EE7C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="38620" windowHeight="21220" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="5180" yWindow="6650" windowWidth="28810" windowHeight="13760" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="統計" sheetId="1" r:id="rId1"/>
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="534" uniqueCount="528">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="535" uniqueCount="529">
   <si>
     <t>索引號</t>
   </si>
@@ -1621,6 +1621,10 @@
   </si>
   <si>
     <t>晉成帝8年至13年</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>晉成帝14年至17年</t>
     <phoneticPr fontId="4" type="noConversion"/>
   </si>
 </sst>
@@ -1925,7 +1929,7 @@
             <c:strRef>
               <c:f>統計!$B$2:$B$115</c:f>
               <c:strCache>
-                <c:ptCount val="95"/>
+                <c:ptCount val="96"/>
                 <c:pt idx="0">
                   <c:v>卷1</c:v>
                 </c:pt>
@@ -2210,6 +2214,9 @@
                 </c:pt>
                 <c:pt idx="94">
                   <c:v>卷95</c:v>
+                </c:pt>
+                <c:pt idx="95">
+                  <c:v>卷96</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
@@ -2504,6 +2511,9 @@
                 </c:pt>
                 <c:pt idx="94">
                   <c:v>2.8333333333333335</c:v>
+                </c:pt>
+                <c:pt idx="95">
+                  <c:v>4.75</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -3058,7 +3068,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:R96"/>
+  <dimension ref="A1:R97"/>
   <sheetFormatPr defaultColWidth="8.6328125" defaultRowHeight="14" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="7.7265625" customWidth="1"/>
@@ -3173,19 +3183,19 @@
       </c>
       <c r="O2">
         <f t="shared" ref="O2:O8" si="5">L2*$L$10</f>
-        <v>654.23157894736846</v>
+        <v>660.875</v>
       </c>
       <c r="P2" s="1">
         <f t="shared" ref="P2:P8" si="6">$C$2+O2</f>
-        <v>44673.231578947365</v>
+        <v>44679.875</v>
       </c>
       <c r="Q2">
         <f t="shared" ref="Q2:Q8" si="7">(M2-$F$2)*$L$11</f>
-        <v>761.90769605641435</v>
+        <v>777.09742963586302</v>
       </c>
       <c r="R2" s="1">
         <f t="shared" ref="R2:R8" si="8">$C$2+Q2</f>
-        <v>44780.907696056413</v>
+        <v>44796.097429635862</v>
       </c>
     </row>
     <row r="3" spans="1:18" x14ac:dyDescent="0.25">
@@ -3236,19 +3246,19 @@
       </c>
       <c r="O3">
         <f t="shared" si="5"/>
-        <v>750.44210526315794</v>
+        <v>758.0625</v>
       </c>
       <c r="P3" s="1">
         <f t="shared" si="6"/>
-        <v>44769.442105263159</v>
+        <v>44777.0625</v>
       </c>
       <c r="Q3">
         <f t="shared" si="7"/>
-        <v>835.28564431224891</v>
+        <v>851.93827358153203</v>
       </c>
       <c r="R3" s="1">
         <f t="shared" si="8"/>
-        <v>44854.285644312251</v>
+        <v>44870.938273581531</v>
       </c>
     </row>
     <row r="4" spans="1:18" x14ac:dyDescent="0.25">
@@ -3299,19 +3309,19 @@
       </c>
       <c r="O4">
         <f t="shared" si="5"/>
-        <v>1135.2842105263157</v>
+        <v>1146.8125</v>
       </c>
       <c r="P4" s="1">
         <f t="shared" si="6"/>
-        <v>45154.284210526319</v>
+        <v>45165.8125</v>
       </c>
       <c r="Q4">
         <f t="shared" si="7"/>
-        <v>1006.5008569091959</v>
+        <v>1026.5669094547598</v>
       </c>
       <c r="R4" s="1">
         <f t="shared" si="8"/>
-        <v>45025.500856909195</v>
+        <v>45045.566909454763</v>
       </c>
     </row>
     <row r="5" spans="1:18" x14ac:dyDescent="0.25">
@@ -3362,19 +3372,19 @@
       </c>
       <c r="O5">
         <f t="shared" si="5"/>
-        <v>1693.3052631578948</v>
+        <v>1710.5</v>
       </c>
       <c r="P5" s="1">
         <f t="shared" si="6"/>
-        <v>45712.305263157898</v>
+        <v>45729.5</v>
       </c>
       <c r="Q5">
         <f t="shared" si="7"/>
-        <v>1213.1820778297963</v>
+        <v>1237.3686199017275</v>
       </c>
       <c r="R5" s="1">
         <f t="shared" si="8"/>
-        <v>45232.182077829799</v>
+        <v>45256.368619901725</v>
       </c>
     </row>
     <row r="6" spans="1:18" x14ac:dyDescent="0.25">
@@ -3425,19 +3435,19 @@
       </c>
       <c r="O6">
         <f t="shared" si="5"/>
-        <v>2549.5789473684213</v>
+        <v>2575.46875</v>
       </c>
       <c r="P6" s="1">
         <f t="shared" si="6"/>
-        <v>46568.57894736842</v>
+        <v>46594.46875</v>
       </c>
       <c r="Q6">
         <f t="shared" si="7"/>
-        <v>1602.085203585719</v>
+        <v>1634.025092813773</v>
       </c>
       <c r="R6" s="1">
         <f t="shared" si="8"/>
-        <v>45621.085203585717</v>
+        <v>45653.025092813776</v>
       </c>
     </row>
     <row r="7" spans="1:18" x14ac:dyDescent="0.25">
@@ -3488,19 +3498,19 @@
       </c>
       <c r="O7">
         <f t="shared" si="5"/>
-        <v>2828.5894736842106</v>
+        <v>2857.3125</v>
       </c>
       <c r="P7" s="1">
         <f t="shared" si="6"/>
-        <v>46847.589473684209</v>
+        <v>46876.3125</v>
       </c>
       <c r="Q7">
         <f t="shared" si="7"/>
-        <v>1665.6794254074421</v>
+        <v>1698.8871575666863</v>
       </c>
       <c r="R7" s="1">
         <f t="shared" si="8"/>
-        <v>45684.679425407441</v>
+        <v>45717.887157566685</v>
       </c>
     </row>
     <row r="8" spans="1:18" x14ac:dyDescent="0.25">
@@ -3551,19 +3561,19 @@
       </c>
       <c r="O8">
         <f t="shared" si="5"/>
-        <v>2828.5894736842106</v>
+        <v>2857.3125</v>
       </c>
       <c r="P8" s="1">
         <f t="shared" si="6"/>
-        <v>46847.589473684209</v>
+        <v>46876.3125</v>
       </c>
       <c r="Q8">
         <f t="shared" si="7"/>
-        <v>1665.6794254074421</v>
+        <v>1698.8871575666863</v>
       </c>
       <c r="R8" s="1">
         <f t="shared" si="8"/>
-        <v>45684.679425407441</v>
+        <v>45717.887157566685</v>
       </c>
     </row>
     <row r="9" spans="1:18" x14ac:dyDescent="0.25">
@@ -3638,7 +3648,7 @@
       </c>
       <c r="L10">
         <f>AVERAGE(E:E)</f>
-        <v>9.621052631578948</v>
+        <v>9.71875</v>
       </c>
     </row>
     <row r="11" spans="1:18" x14ac:dyDescent="0.25">
@@ -3679,7 +3689,7 @@
       </c>
       <c r="L11">
         <f>AVEDEV(I:I)</f>
-        <v>1.2229658042639076</v>
+        <v>1.2473473990944832</v>
       </c>
     </row>
     <row r="12" spans="1:18" x14ac:dyDescent="0.25">
@@ -5542,7 +5552,7 @@
         <v>526</v>
       </c>
       <c r="B66" t="str">
-        <f t="shared" ref="B66:B96" si="16">"卷"&amp;ROW(B65)</f>
+        <f t="shared" ref="B66:B97" si="16">"卷"&amp;ROW(B65)</f>
         <v>卷65</v>
       </c>
       <c r="C66" s="1">
@@ -6609,6 +6619,40 @@
       <c r="I96">
         <f t="shared" ref="I96" si="70">E96/H96</f>
         <v>2.8333333333333335</v>
+      </c>
+    </row>
+    <row r="97" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A97">
+        <v>807</v>
+      </c>
+      <c r="B97" t="str">
+        <f t="shared" si="16"/>
+        <v>卷96</v>
+      </c>
+      <c r="C97" s="1">
+        <v>45106</v>
+      </c>
+      <c r="D97" s="1">
+        <v>45124</v>
+      </c>
+      <c r="E97">
+        <f t="shared" ref="E97" si="71">D97-C97+1</f>
+        <v>19</v>
+      </c>
+      <c r="F97">
+        <f t="shared" ref="F97" si="72">G96+1</f>
+        <v>338</v>
+      </c>
+      <c r="G97">
+        <v>341</v>
+      </c>
+      <c r="H97">
+        <f t="shared" ref="H97" si="73">IF(F97*G97&lt;0,ABS(F97)+ABS(G97),G97-F97+1)</f>
+        <v>4</v>
+      </c>
+      <c r="I97">
+        <f t="shared" ref="I97" si="74">E97/H97</f>
+        <v>4.75</v>
       </c>
     </row>
   </sheetData>
@@ -9476,24 +9520,27 @@
       <c r="A97">
         <v>807</v>
       </c>
-      <c r="B97" t="e">
+      <c r="B97" t="str">
         <f>VLOOKUP($A97,統計!$A:$G,2,)</f>
-        <v>#N/A</v>
+        <v>卷96</v>
       </c>
       <c r="C97" t="s">
         <v>292</v>
       </c>
-      <c r="D97" t="e">
+      <c r="D97">
         <f>VLOOKUP($A97,統計!$A:$G,6,)</f>
-        <v>#N/A</v>
-      </c>
-      <c r="E97" t="e">
+        <v>338</v>
+      </c>
+      <c r="E97">
         <f>VLOOKUP($A97,統計!$A:$G,7,)</f>
-        <v>#N/A</v>
-      </c>
-      <c r="I97" t="e">
+        <v>341</v>
+      </c>
+      <c r="H97" t="s">
+        <v>528</v>
+      </c>
+      <c r="I97" t="str">
         <f t="shared" si="1"/>
-        <v>#N/A</v>
+        <v>807|[卷96](5_筆記/资治通鉴96.html)|晉紀十八|338|341|||晉成帝14年至17年</v>
       </c>
     </row>
     <row r="98" spans="1:9" x14ac:dyDescent="0.25">

--- a/5_筆記/閱讀數據.xlsx
+++ b/5_筆記/閱讀數據.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="26529"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="26626"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\self\study\zizhitongjian\5_筆記\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2604F92B-F06D-4522-8647-2AD92167EE7C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1C9167C3-2CAA-4BBF-857C-D595D8A5967D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="5180" yWindow="6650" windowWidth="28810" windowHeight="13760" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="19670" yWindow="5070" windowWidth="14380" windowHeight="13760" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="統計" sheetId="1" r:id="rId1"/>
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="535" uniqueCount="529">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="536" uniqueCount="530">
   <si>
     <t>索引號</t>
   </si>
@@ -1626,6 +1626,9 @@
   <si>
     <t>晉成帝14年至17年</t>
     <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>晉成帝18年、晉康帝共3年、晉穆帝至4年</t>
   </si>
 </sst>
 </file>
@@ -1929,7 +1932,7 @@
             <c:strRef>
               <c:f>統計!$B$2:$B$115</c:f>
               <c:strCache>
-                <c:ptCount val="96"/>
+                <c:ptCount val="97"/>
                 <c:pt idx="0">
                   <c:v>卷1</c:v>
                 </c:pt>
@@ -2217,6 +2220,9 @@
                 </c:pt>
                 <c:pt idx="95">
                   <c:v>卷96</c:v>
+                </c:pt>
+                <c:pt idx="96">
+                  <c:v>卷97</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
@@ -2514,6 +2520,9 @@
                 </c:pt>
                 <c:pt idx="95">
                   <c:v>4.75</c:v>
+                </c:pt>
+                <c:pt idx="96">
+                  <c:v>2.8333333333333335</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -3068,7 +3077,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:R97"/>
+  <dimension ref="A1:R98"/>
   <sheetFormatPr defaultColWidth="8.6328125" defaultRowHeight="14" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="7.7265625" customWidth="1"/>
@@ -3183,19 +3192,19 @@
       </c>
       <c r="O2">
         <f t="shared" ref="O2:O8" si="5">L2*$L$10</f>
-        <v>660.875</v>
+        <v>665.97938144329896</v>
       </c>
       <c r="P2" s="1">
         <f t="shared" ref="P2:P8" si="6">$C$2+O2</f>
-        <v>44679.875</v>
+        <v>44684.9793814433</v>
       </c>
       <c r="Q2">
         <f t="shared" ref="Q2:Q8" si="7">(M2-$F$2)*$L$11</f>
-        <v>777.09742963586302</v>
+        <v>776.01920496040213</v>
       </c>
       <c r="R2" s="1">
         <f t="shared" ref="R2:R8" si="8">$C$2+Q2</f>
-        <v>44796.097429635862</v>
+        <v>44795.019204960401</v>
       </c>
     </row>
     <row r="3" spans="1:18" x14ac:dyDescent="0.25">
@@ -3246,19 +3255,19 @@
       </c>
       <c r="O3">
         <f t="shared" si="5"/>
-        <v>758.0625</v>
+        <v>763.91752577319596</v>
       </c>
       <c r="P3" s="1">
         <f t="shared" si="6"/>
-        <v>44777.0625</v>
+        <v>44782.917525773199</v>
       </c>
       <c r="Q3">
         <f t="shared" si="7"/>
-        <v>851.93827358153203</v>
+        <v>850.75620704326593</v>
       </c>
       <c r="R3" s="1">
         <f t="shared" si="8"/>
-        <v>44870.938273581531</v>
+        <v>44869.756207043269</v>
       </c>
     </row>
     <row r="4" spans="1:18" x14ac:dyDescent="0.25">
@@ -3309,19 +3318,19 @@
       </c>
       <c r="O4">
         <f t="shared" si="5"/>
-        <v>1146.8125</v>
+        <v>1155.6701030927836</v>
       </c>
       <c r="P4" s="1">
         <f t="shared" si="6"/>
-        <v>45165.8125</v>
+        <v>45174.670103092787</v>
       </c>
       <c r="Q4">
         <f t="shared" si="7"/>
-        <v>1026.5669094547598</v>
+        <v>1025.1425452366148</v>
       </c>
       <c r="R4" s="1">
         <f t="shared" si="8"/>
-        <v>45045.566909454763</v>
+        <v>45044.142545236617</v>
       </c>
     </row>
     <row r="5" spans="1:18" x14ac:dyDescent="0.25">
@@ -3372,19 +3381,19 @@
       </c>
       <c r="O5">
         <f t="shared" si="5"/>
-        <v>1710.5</v>
+        <v>1723.7113402061857</v>
       </c>
       <c r="P5" s="1">
         <f t="shared" si="6"/>
-        <v>45729.5</v>
+        <v>45742.711340206188</v>
       </c>
       <c r="Q5">
         <f t="shared" si="7"/>
-        <v>1237.3686199017275</v>
+        <v>1235.6517677700144</v>
       </c>
       <c r="R5" s="1">
         <f t="shared" si="8"/>
-        <v>45256.368619901725</v>
+        <v>45254.651767770018</v>
       </c>
     </row>
     <row r="6" spans="1:18" x14ac:dyDescent="0.25">
@@ -3435,19 +3444,19 @@
       </c>
       <c r="O6">
         <f t="shared" si="5"/>
-        <v>2575.46875</v>
+        <v>2595.3608247422681</v>
       </c>
       <c r="P6" s="1">
         <f t="shared" si="6"/>
-        <v>46594.46875</v>
+        <v>46614.360824742267</v>
       </c>
       <c r="Q6">
         <f t="shared" si="7"/>
-        <v>1634.025092813773</v>
+        <v>1631.7578788091923</v>
       </c>
       <c r="R6" s="1">
         <f t="shared" si="8"/>
-        <v>45653.025092813776</v>
+        <v>45650.757878809192</v>
       </c>
     </row>
     <row r="7" spans="1:18" x14ac:dyDescent="0.25">
@@ -3498,19 +3507,19 @@
       </c>
       <c r="O7">
         <f t="shared" si="5"/>
-        <v>2857.3125</v>
+        <v>2879.3814432989693</v>
       </c>
       <c r="P7" s="1">
         <f t="shared" si="6"/>
-        <v>46876.3125</v>
+        <v>46898.381443298967</v>
       </c>
       <c r="Q7">
         <f t="shared" si="7"/>
-        <v>1698.8871575666863</v>
+        <v>1696.5299472810075</v>
       </c>
       <c r="R7" s="1">
         <f t="shared" si="8"/>
-        <v>45717.887157566685</v>
+        <v>45715.529947281007</v>
       </c>
     </row>
     <row r="8" spans="1:18" x14ac:dyDescent="0.25">
@@ -3561,19 +3570,19 @@
       </c>
       <c r="O8">
         <f t="shared" si="5"/>
-        <v>2857.3125</v>
+        <v>2879.3814432989693</v>
       </c>
       <c r="P8" s="1">
         <f t="shared" si="6"/>
-        <v>46876.3125</v>
+        <v>46898.381443298967</v>
       </c>
       <c r="Q8">
         <f t="shared" si="7"/>
-        <v>1698.8871575666863</v>
+        <v>1696.5299472810075</v>
       </c>
       <c r="R8" s="1">
         <f t="shared" si="8"/>
-        <v>45717.887157566685</v>
+        <v>45715.529947281007</v>
       </c>
     </row>
     <row r="9" spans="1:18" x14ac:dyDescent="0.25">
@@ -3648,7 +3657,7 @@
       </c>
       <c r="L10">
         <f>AVERAGE(E:E)</f>
-        <v>9.71875</v>
+        <v>9.7938144329896915</v>
       </c>
     </row>
     <row r="11" spans="1:18" x14ac:dyDescent="0.25">
@@ -3689,7 +3698,7 @@
       </c>
       <c r="L11">
         <f>AVEDEV(I:I)</f>
-        <v>1.2473473990944832</v>
+        <v>1.2456167013810628</v>
       </c>
     </row>
     <row r="12" spans="1:18" x14ac:dyDescent="0.25">
@@ -5552,7 +5561,7 @@
         <v>526</v>
       </c>
       <c r="B66" t="str">
-        <f t="shared" ref="B66:B97" si="16">"卷"&amp;ROW(B65)</f>
+        <f t="shared" ref="B66:B98" si="16">"卷"&amp;ROW(B65)</f>
         <v>卷65</v>
       </c>
       <c r="C66" s="1">
@@ -6653,6 +6662,41 @@
       <c r="I97">
         <f t="shared" ref="I97" si="74">E97/H97</f>
         <v>4.75</v>
+      </c>
+    </row>
+    <row r="98" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A98">
+        <v>808</v>
+      </c>
+      <c r="B98" t="str">
+        <f t="shared" si="16"/>
+        <v>卷97</v>
+      </c>
+      <c r="C98" s="1">
+        <f t="shared" ref="C98" si="75">D97+1</f>
+        <v>45125</v>
+      </c>
+      <c r="D98" s="1">
+        <v>45141</v>
+      </c>
+      <c r="E98">
+        <f t="shared" ref="E98" si="76">D98-C98+1</f>
+        <v>17</v>
+      </c>
+      <c r="F98">
+        <f t="shared" ref="F98" si="77">G97+1</f>
+        <v>342</v>
+      </c>
+      <c r="G98">
+        <v>347</v>
+      </c>
+      <c r="H98">
+        <f t="shared" ref="H98" si="78">IF(F98*G98&lt;0,ABS(F98)+ABS(G98),G98-F98+1)</f>
+        <v>6</v>
+      </c>
+      <c r="I98">
+        <f t="shared" ref="I98" si="79">E98/H98</f>
+        <v>2.8333333333333335</v>
       </c>
     </row>
   </sheetData>
@@ -9547,24 +9591,27 @@
       <c r="A98">
         <v>808</v>
       </c>
-      <c r="B98" t="e">
+      <c r="B98" t="str">
         <f>VLOOKUP($A98,統計!$A:$G,2,)</f>
-        <v>#N/A</v>
+        <v>卷97</v>
       </c>
       <c r="C98" t="s">
         <v>293</v>
       </c>
-      <c r="D98" t="e">
+      <c r="D98">
         <f>VLOOKUP($A98,統計!$A:$G,6,)</f>
-        <v>#N/A</v>
-      </c>
-      <c r="E98" t="e">
+        <v>342</v>
+      </c>
+      <c r="E98">
         <f>VLOOKUP($A98,統計!$A:$G,7,)</f>
-        <v>#N/A</v>
-      </c>
-      <c r="I98" t="e">
+        <v>347</v>
+      </c>
+      <c r="H98" t="s">
+        <v>529</v>
+      </c>
+      <c r="I98" t="str">
         <f t="shared" si="1"/>
-        <v>#N/A</v>
+        <v>808|[卷97](5_筆記/资治通鉴97.html)|晉紀十九|342|347|||晉成帝18年、晉康帝共3年、晉穆帝至4年</v>
       </c>
     </row>
     <row r="99" spans="1:9" x14ac:dyDescent="0.25">

--- a/5_筆記/閱讀數據.xlsx
+++ b/5_筆記/閱讀數據.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\self\study\zizhitongjian\5_筆記\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1C9167C3-2CAA-4BBF-857C-D595D8A5967D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2BAD9A28-D916-41EC-95E1-3A3E786F9E65}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="19670" yWindow="5070" windowWidth="14380" windowHeight="13760" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="38620" windowHeight="21220" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="統計" sheetId="1" r:id="rId1"/>
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="536" uniqueCount="530">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="539" uniqueCount="533">
   <si>
     <t>索引號</t>
   </si>
@@ -1629,6 +1629,17 @@
   </si>
   <si>
     <t>晉成帝18年、晉康帝共3年、晉穆帝至4年</t>
+  </si>
+  <si>
+    <t>晉穆帝5年至7年</t>
+  </si>
+  <si>
+    <t>石虎手刃重要家屬列表</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>淝水之戰前政權形勢圖</t>
+    <phoneticPr fontId="4" type="noConversion"/>
   </si>
 </sst>
 </file>
@@ -1932,7 +1943,7 @@
             <c:strRef>
               <c:f>統計!$B$2:$B$115</c:f>
               <c:strCache>
-                <c:ptCount val="97"/>
+                <c:ptCount val="98"/>
                 <c:pt idx="0">
                   <c:v>卷1</c:v>
                 </c:pt>
@@ -2223,6 +2234,9 @@
                 </c:pt>
                 <c:pt idx="96">
                   <c:v>卷97</c:v>
+                </c:pt>
+                <c:pt idx="97">
+                  <c:v>卷98</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
@@ -2523,6 +2537,9 @@
                 </c:pt>
                 <c:pt idx="96">
                   <c:v>2.8333333333333335</c:v>
+                </c:pt>
+                <c:pt idx="97">
+                  <c:v>5</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -3077,7 +3094,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:R98"/>
+  <dimension ref="A1:R99"/>
   <sheetFormatPr defaultColWidth="8.6328125" defaultRowHeight="14" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="7.7265625" customWidth="1"/>
@@ -3192,19 +3209,19 @@
       </c>
       <c r="O2">
         <f t="shared" ref="O2:O8" si="5">L2*$L$10</f>
-        <v>665.97938144329896</v>
+        <v>669.59183673469386</v>
       </c>
       <c r="P2" s="1">
         <f t="shared" ref="P2:P8" si="6">$C$2+O2</f>
-        <v>44684.9793814433</v>
+        <v>44688.591836734697</v>
       </c>
       <c r="Q2">
         <f t="shared" ref="Q2:Q8" si="7">(M2-$F$2)*$L$11</f>
-        <v>776.01920496040213</v>
+        <v>792.34349349480556</v>
       </c>
       <c r="R2" s="1">
         <f t="shared" ref="R2:R8" si="8">$C$2+Q2</f>
-        <v>44795.019204960401</v>
+        <v>44811.343493494809</v>
       </c>
     </row>
     <row r="3" spans="1:18" x14ac:dyDescent="0.25">
@@ -3255,19 +3272,19 @@
       </c>
       <c r="O3">
         <f t="shared" si="5"/>
-        <v>763.91752577319596</v>
+        <v>768.0612244897959</v>
       </c>
       <c r="P3" s="1">
         <f t="shared" si="6"/>
-        <v>44782.917525773199</v>
+        <v>44787.061224489793</v>
       </c>
       <c r="Q3">
         <f t="shared" si="7"/>
-        <v>850.75620704326593</v>
+        <v>868.65265819735498</v>
       </c>
       <c r="R3" s="1">
         <f t="shared" si="8"/>
-        <v>44869.756207043269</v>
+        <v>44887.652658197352</v>
       </c>
     </row>
     <row r="4" spans="1:18" x14ac:dyDescent="0.25">
@@ -3318,19 +3335,19 @@
       </c>
       <c r="O4">
         <f t="shared" si="5"/>
-        <v>1155.6701030927836</v>
+        <v>1161.9387755102041</v>
       </c>
       <c r="P4" s="1">
         <f t="shared" si="6"/>
-        <v>45174.670103092787</v>
+        <v>45180.938775510207</v>
       </c>
       <c r="Q4">
         <f t="shared" si="7"/>
-        <v>1025.1425452366148</v>
+        <v>1046.7073758366371</v>
       </c>
       <c r="R4" s="1">
         <f t="shared" si="8"/>
-        <v>45044.142545236617</v>
+        <v>45065.707375836639</v>
       </c>
     </row>
     <row r="5" spans="1:18" x14ac:dyDescent="0.25">
@@ -3381,19 +3398,19 @@
       </c>
       <c r="O5">
         <f t="shared" si="5"/>
-        <v>1723.7113402061857</v>
+        <v>1733.0612244897957</v>
       </c>
       <c r="P5" s="1">
         <f t="shared" si="6"/>
-        <v>45742.711340206188</v>
+        <v>45752.061224489793</v>
       </c>
       <c r="Q5">
         <f t="shared" si="7"/>
-        <v>1235.6517677700144</v>
+        <v>1261.6448564154848</v>
       </c>
       <c r="R5" s="1">
         <f t="shared" si="8"/>
-        <v>45254.651767770018</v>
+        <v>45280.644856415485</v>
       </c>
     </row>
     <row r="6" spans="1:18" x14ac:dyDescent="0.25">
@@ -3444,19 +3461,19 @@
       </c>
       <c r="O6">
         <f t="shared" si="5"/>
-        <v>2595.3608247422681</v>
+        <v>2609.4387755102039</v>
       </c>
       <c r="P6" s="1">
         <f t="shared" si="6"/>
-        <v>46614.360824742267</v>
+        <v>46628.438775510207</v>
       </c>
       <c r="Q6">
         <f t="shared" si="7"/>
-        <v>1631.7578788091923</v>
+        <v>1666.0834293389971</v>
       </c>
       <c r="R6" s="1">
         <f t="shared" si="8"/>
-        <v>45650.757878809192</v>
+        <v>45685.083429339</v>
       </c>
     </row>
     <row r="7" spans="1:18" x14ac:dyDescent="0.25">
@@ -3507,19 +3524,19 @@
       </c>
       <c r="O7">
         <f t="shared" si="5"/>
-        <v>2879.3814432989693</v>
+        <v>2895</v>
       </c>
       <c r="P7" s="1">
         <f t="shared" si="6"/>
-        <v>46898.381443298967</v>
+        <v>46914</v>
       </c>
       <c r="Q7">
         <f t="shared" si="7"/>
-        <v>1696.5299472810075</v>
+        <v>1732.2180387478734</v>
       </c>
       <c r="R7" s="1">
         <f t="shared" si="8"/>
-        <v>45715.529947281007</v>
+        <v>45751.218038747873</v>
       </c>
     </row>
     <row r="8" spans="1:18" x14ac:dyDescent="0.25">
@@ -3570,19 +3587,19 @@
       </c>
       <c r="O8">
         <f t="shared" si="5"/>
-        <v>2879.3814432989693</v>
+        <v>2895</v>
       </c>
       <c r="P8" s="1">
         <f t="shared" si="6"/>
-        <v>46898.381443298967</v>
+        <v>46914</v>
       </c>
       <c r="Q8">
         <f t="shared" si="7"/>
-        <v>1696.5299472810075</v>
+        <v>1732.2180387478734</v>
       </c>
       <c r="R8" s="1">
         <f t="shared" si="8"/>
-        <v>45715.529947281007</v>
+        <v>45751.218038747873</v>
       </c>
     </row>
     <row r="9" spans="1:18" x14ac:dyDescent="0.25">
@@ -3657,7 +3674,7 @@
       </c>
       <c r="L10">
         <f>AVERAGE(E:E)</f>
-        <v>9.7938144329896915</v>
+        <v>9.8469387755102034</v>
       </c>
     </row>
     <row r="11" spans="1:18" x14ac:dyDescent="0.25">
@@ -3698,7 +3715,7 @@
       </c>
       <c r="L11">
         <f>AVEDEV(I:I)</f>
-        <v>1.2456167013810628</v>
+        <v>1.2718194117091581</v>
       </c>
     </row>
     <row r="12" spans="1:18" x14ac:dyDescent="0.25">
@@ -5561,7 +5578,7 @@
         <v>526</v>
       </c>
       <c r="B66" t="str">
-        <f t="shared" ref="B66:B98" si="16">"卷"&amp;ROW(B65)</f>
+        <f t="shared" ref="B66:B99" si="16">"卷"&amp;ROW(B65)</f>
         <v>卷65</v>
       </c>
       <c r="C66" s="1">
@@ -6697,6 +6714,40 @@
       <c r="I98">
         <f t="shared" ref="I98" si="79">E98/H98</f>
         <v>2.8333333333333335</v>
+      </c>
+    </row>
+    <row r="99" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A99">
+        <v>809</v>
+      </c>
+      <c r="B99" t="str">
+        <f t="shared" si="16"/>
+        <v>卷98</v>
+      </c>
+      <c r="C99" s="1">
+        <v>45143</v>
+      </c>
+      <c r="D99" s="1">
+        <v>45157</v>
+      </c>
+      <c r="E99">
+        <f t="shared" ref="E99" si="80">D99-C99+1</f>
+        <v>15</v>
+      </c>
+      <c r="F99">
+        <f t="shared" ref="F99" si="81">G98+1</f>
+        <v>348</v>
+      </c>
+      <c r="G99">
+        <v>350</v>
+      </c>
+      <c r="H99">
+        <f t="shared" ref="H99" si="82">IF(F99*G99&lt;0,ABS(F99)+ABS(G99),G99-F99+1)</f>
+        <v>3</v>
+      </c>
+      <c r="I99">
+        <f t="shared" ref="I99" si="83">E99/H99</f>
+        <v>5</v>
       </c>
     </row>
   </sheetData>
@@ -9618,24 +9669,33 @@
       <c r="A99">
         <v>809</v>
       </c>
-      <c r="B99" t="e">
+      <c r="B99" t="str">
         <f>VLOOKUP($A99,統計!$A:$G,2,)</f>
-        <v>#N/A</v>
+        <v>卷98</v>
       </c>
       <c r="C99" t="s">
         <v>294</v>
       </c>
-      <c r="D99" t="e">
+      <c r="D99">
         <f>VLOOKUP($A99,統計!$A:$G,6,)</f>
-        <v>#N/A</v>
-      </c>
-      <c r="E99" t="e">
+        <v>348</v>
+      </c>
+      <c r="E99">
         <f>VLOOKUP($A99,統計!$A:$G,7,)</f>
-        <v>#N/A</v>
-      </c>
-      <c r="I99" t="e">
+        <v>350</v>
+      </c>
+      <c r="F99" t="s">
+        <v>532</v>
+      </c>
+      <c r="G99" t="s">
+        <v>531</v>
+      </c>
+      <c r="H99" t="s">
+        <v>530</v>
+      </c>
+      <c r="I99" t="str">
         <f t="shared" si="1"/>
-        <v>#N/A</v>
+        <v>809|[卷98](5_筆記/资治通鉴98.html)|晉紀二十|348|350|淝水之戰前政權形勢圖|石虎手刃重要家屬列表|晉穆帝5年至7年</v>
       </c>
     </row>
     <row r="100" spans="1:9" x14ac:dyDescent="0.25">

--- a/5_筆記/閱讀數據.xlsx
+++ b/5_筆記/閱讀數據.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="26626"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="26731"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\self\study\zizhitongjian\5_筆記\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2BAD9A28-D916-41EC-95E1-3A3E786F9E65}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{889F82DB-CE25-4FDA-82FC-7FE124AC96AB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="38620" windowHeight="21220" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="539" uniqueCount="533">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="540" uniqueCount="534">
   <si>
     <t>索引號</t>
   </si>
@@ -1639,6 +1639,10 @@
   </si>
   <si>
     <t>淝水之戰前政權形勢圖</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>晉穆帝8年至11年</t>
     <phoneticPr fontId="4" type="noConversion"/>
   </si>
 </sst>
@@ -1943,7 +1947,7 @@
             <c:strRef>
               <c:f>統計!$B$2:$B$115</c:f>
               <c:strCache>
-                <c:ptCount val="98"/>
+                <c:ptCount val="99"/>
                 <c:pt idx="0">
                   <c:v>卷1</c:v>
                 </c:pt>
@@ -2237,6 +2241,9 @@
                 </c:pt>
                 <c:pt idx="97">
                   <c:v>卷98</c:v>
+                </c:pt>
+                <c:pt idx="98">
+                  <c:v>卷99</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
@@ -2540,6 +2547,9 @@
                 </c:pt>
                 <c:pt idx="97">
                   <c:v>5</c:v>
+                </c:pt>
+                <c:pt idx="98">
+                  <c:v>3.75</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -3094,7 +3104,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:R99"/>
+  <dimension ref="A1:R100"/>
   <sheetFormatPr defaultColWidth="8.6328125" defaultRowHeight="14" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="7.7265625" customWidth="1"/>
@@ -3209,19 +3219,19 @@
       </c>
       <c r="O2">
         <f t="shared" ref="O2:O8" si="5">L2*$L$10</f>
-        <v>669.59183673469386</v>
+        <v>673.13131313131316</v>
       </c>
       <c r="P2" s="1">
         <f t="shared" ref="P2:P8" si="6">$C$2+O2</f>
-        <v>44688.591836734697</v>
+        <v>44692.131313131315</v>
       </c>
       <c r="Q2">
         <f t="shared" ref="Q2:Q8" si="7">(M2-$F$2)*$L$11</f>
-        <v>792.34349349480556</v>
+        <v>798.2384313987435</v>
       </c>
       <c r="R2" s="1">
         <f t="shared" ref="R2:R8" si="8">$C$2+Q2</f>
-        <v>44811.343493494809</v>
+        <v>44817.238431398742</v>
       </c>
     </row>
     <row r="3" spans="1:18" x14ac:dyDescent="0.25">
@@ -3272,19 +3282,19 @@
       </c>
       <c r="O3">
         <f t="shared" si="5"/>
-        <v>768.0612244897959</v>
+        <v>772.12121212121212</v>
       </c>
       <c r="P3" s="1">
         <f t="shared" si="6"/>
-        <v>44787.061224489793</v>
+        <v>44791.121212121216</v>
       </c>
       <c r="Q3">
         <f t="shared" si="7"/>
-        <v>868.65265819735498</v>
+        <v>875.11532687855834</v>
       </c>
       <c r="R3" s="1">
         <f t="shared" si="8"/>
-        <v>44887.652658197352</v>
+        <v>44894.115326878557</v>
       </c>
     </row>
     <row r="4" spans="1:18" x14ac:dyDescent="0.25">
@@ -3335,19 +3345,19 @@
       </c>
       <c r="O4">
         <f t="shared" si="5"/>
-        <v>1161.9387755102041</v>
+        <v>1168.0808080808081</v>
       </c>
       <c r="P4" s="1">
         <f t="shared" si="6"/>
-        <v>45180.938775510207</v>
+        <v>45187.080808080806</v>
       </c>
       <c r="Q4">
         <f t="shared" si="7"/>
-        <v>1046.7073758366371</v>
+        <v>1054.4947496647928</v>
       </c>
       <c r="R4" s="1">
         <f t="shared" si="8"/>
-        <v>45065.707375836639</v>
+        <v>45073.494749664795</v>
       </c>
     </row>
     <row r="5" spans="1:18" x14ac:dyDescent="0.25">
@@ -3398,19 +3408,19 @@
       </c>
       <c r="O5">
         <f t="shared" si="5"/>
-        <v>1733.0612244897957</v>
+        <v>1742.2222222222224</v>
       </c>
       <c r="P5" s="1">
         <f t="shared" si="6"/>
-        <v>45752.061224489793</v>
+        <v>45761.222222222219</v>
       </c>
       <c r="Q5">
         <f t="shared" si="7"/>
-        <v>1261.6448564154848</v>
+        <v>1271.0313385996044</v>
       </c>
       <c r="R5" s="1">
         <f t="shared" si="8"/>
-        <v>45280.644856415485</v>
+        <v>45290.031338599605</v>
       </c>
     </row>
     <row r="6" spans="1:18" x14ac:dyDescent="0.25">
@@ -3461,19 +3471,19 @@
       </c>
       <c r="O6">
         <f t="shared" si="5"/>
-        <v>2609.4387755102039</v>
+        <v>2623.2323232323233</v>
       </c>
       <c r="P6" s="1">
         <f t="shared" si="6"/>
-        <v>46628.438775510207</v>
+        <v>46642.232323232325</v>
       </c>
       <c r="Q6">
         <f t="shared" si="7"/>
-        <v>1666.0834293389971</v>
+        <v>1678.4788846426229</v>
       </c>
       <c r="R6" s="1">
         <f t="shared" si="8"/>
-        <v>45685.083429339</v>
+        <v>45697.478884642624</v>
       </c>
     </row>
     <row r="7" spans="1:18" x14ac:dyDescent="0.25">
@@ -3524,19 +3534,19 @@
       </c>
       <c r="O7">
         <f t="shared" si="5"/>
-        <v>2895</v>
+        <v>2910.3030303030305</v>
       </c>
       <c r="P7" s="1">
         <f t="shared" si="6"/>
-        <v>46914</v>
+        <v>46929.303030303032</v>
       </c>
       <c r="Q7">
         <f t="shared" si="7"/>
-        <v>1732.2180387478734</v>
+        <v>1745.1055273917957</v>
       </c>
       <c r="R7" s="1">
         <f t="shared" si="8"/>
-        <v>45751.218038747873</v>
+        <v>45764.105527391795</v>
       </c>
     </row>
     <row r="8" spans="1:18" x14ac:dyDescent="0.25">
@@ -3587,19 +3597,19 @@
       </c>
       <c r="O8">
         <f t="shared" si="5"/>
-        <v>2895</v>
+        <v>2910.3030303030305</v>
       </c>
       <c r="P8" s="1">
         <f t="shared" si="6"/>
-        <v>46914</v>
+        <v>46929.303030303032</v>
       </c>
       <c r="Q8">
         <f t="shared" si="7"/>
-        <v>1732.2180387478734</v>
+        <v>1745.1055273917957</v>
       </c>
       <c r="R8" s="1">
         <f t="shared" si="8"/>
-        <v>45751.218038747873</v>
+        <v>45764.105527391795</v>
       </c>
     </row>
     <row r="9" spans="1:18" x14ac:dyDescent="0.25">
@@ -3674,7 +3684,7 @@
       </c>
       <c r="L10">
         <f>AVERAGE(E:E)</f>
-        <v>9.8469387755102034</v>
+        <v>9.8989898989898997</v>
       </c>
     </row>
     <row r="11" spans="1:18" x14ac:dyDescent="0.25">
@@ -3715,7 +3725,7 @@
       </c>
       <c r="L11">
         <f>AVEDEV(I:I)</f>
-        <v>1.2718194117091581</v>
+        <v>1.2812815913302464</v>
       </c>
     </row>
     <row r="12" spans="1:18" x14ac:dyDescent="0.25">
@@ -5578,7 +5588,7 @@
         <v>526</v>
       </c>
       <c r="B66" t="str">
-        <f t="shared" ref="B66:B99" si="16">"卷"&amp;ROW(B65)</f>
+        <f t="shared" ref="B66:B100" si="16">"卷"&amp;ROW(B65)</f>
         <v>卷65</v>
       </c>
       <c r="C66" s="1">
@@ -6748,6 +6758,41 @@
       <c r="I99">
         <f t="shared" ref="I99" si="83">E99/H99</f>
         <v>5</v>
+      </c>
+    </row>
+    <row r="100" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A100">
+        <v>810</v>
+      </c>
+      <c r="B100" t="str">
+        <f t="shared" si="16"/>
+        <v>卷99</v>
+      </c>
+      <c r="C100" s="1">
+        <f>D99+1</f>
+        <v>45158</v>
+      </c>
+      <c r="D100" s="1">
+        <v>45172</v>
+      </c>
+      <c r="E100">
+        <f t="shared" ref="E100" si="84">D100-C100+1</f>
+        <v>15</v>
+      </c>
+      <c r="F100">
+        <f t="shared" ref="F100" si="85">G99+1</f>
+        <v>351</v>
+      </c>
+      <c r="G100">
+        <v>354</v>
+      </c>
+      <c r="H100">
+        <f t="shared" ref="H100" si="86">IF(F100*G100&lt;0,ABS(F100)+ABS(G100),G100-F100+1)</f>
+        <v>4</v>
+      </c>
+      <c r="I100">
+        <f t="shared" ref="I100" si="87">E100/H100</f>
+        <v>3.75</v>
       </c>
     </row>
   </sheetData>
@@ -9702,24 +9747,27 @@
       <c r="A100">
         <v>810</v>
       </c>
-      <c r="B100" t="e">
+      <c r="B100" t="str">
         <f>VLOOKUP($A100,統計!$A:$G,2,)</f>
-        <v>#N/A</v>
+        <v>卷99</v>
       </c>
       <c r="C100" t="s">
         <v>295</v>
       </c>
-      <c r="D100" t="e">
+      <c r="D100">
         <f>VLOOKUP($A100,統計!$A:$G,6,)</f>
-        <v>#N/A</v>
-      </c>
-      <c r="E100" t="e">
+        <v>351</v>
+      </c>
+      <c r="E100">
         <f>VLOOKUP($A100,統計!$A:$G,7,)</f>
-        <v>#N/A</v>
-      </c>
-      <c r="I100" t="e">
+        <v>354</v>
+      </c>
+      <c r="H100" t="s">
+        <v>533</v>
+      </c>
+      <c r="I100" t="str">
         <f t="shared" si="1"/>
-        <v>#N/A</v>
+        <v>810|[卷99](5_筆記/资治通鉴99.html)|晉紀二十一|351|354|||晉穆帝8年至11年</v>
       </c>
     </row>
     <row r="101" spans="1:9" x14ac:dyDescent="0.25">

--- a/5_筆記/閱讀數據.xlsx
+++ b/5_筆記/閱讀數據.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\self\study\zizhitongjian\5_筆記\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{889F82DB-CE25-4FDA-82FC-7FE124AC96AB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6EB42131-7B1B-44F9-9B0B-AB59C0C6DA23}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="38620" windowHeight="21220" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="540" uniqueCount="534">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="541" uniqueCount="535">
   <si>
     <t>索引號</t>
   </si>
@@ -1644,6 +1644,9 @@
   <si>
     <t>晉穆帝8年至11年</t>
     <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>晉穆帝12年至16年</t>
   </si>
 </sst>
 </file>
@@ -1947,7 +1950,7 @@
             <c:strRef>
               <c:f>統計!$B$2:$B$115</c:f>
               <c:strCache>
-                <c:ptCount val="99"/>
+                <c:ptCount val="100"/>
                 <c:pt idx="0">
                   <c:v>卷1</c:v>
                 </c:pt>
@@ -2244,6 +2247,9 @@
                 </c:pt>
                 <c:pt idx="98">
                   <c:v>卷99</c:v>
+                </c:pt>
+                <c:pt idx="99">
+                  <c:v>卷100</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
@@ -2550,6 +2556,9 @@
                 </c:pt>
                 <c:pt idx="98">
                   <c:v>3.75</c:v>
+                </c:pt>
+                <c:pt idx="99">
+                  <c:v>3</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -3104,7 +3113,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:R100"/>
+  <dimension ref="A1:R101"/>
   <sheetFormatPr defaultColWidth="8.6328125" defaultRowHeight="14" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="7.7265625" customWidth="1"/>
@@ -3219,19 +3228,19 @@
       </c>
       <c r="O2">
         <f t="shared" ref="O2:O8" si="5">L2*$L$10</f>
-        <v>673.13131313131316</v>
+        <v>676.59999999999991</v>
       </c>
       <c r="P2" s="1">
         <f t="shared" ref="P2:P8" si="6">$C$2+O2</f>
-        <v>44692.131313131315</v>
+        <v>44695.6</v>
       </c>
       <c r="Q2">
         <f t="shared" ref="Q2:Q8" si="7">(M2-$F$2)*$L$11</f>
-        <v>798.2384313987435</v>
+        <v>797.85293207540656</v>
       </c>
       <c r="R2" s="1">
         <f t="shared" ref="R2:R8" si="8">$C$2+Q2</f>
-        <v>44817.238431398742</v>
+        <v>44816.85293207541</v>
       </c>
     </row>
     <row r="3" spans="1:18" x14ac:dyDescent="0.25">
@@ -3282,19 +3291,19 @@
       </c>
       <c r="O3">
         <f t="shared" si="5"/>
-        <v>772.12121212121212</v>
+        <v>776.09999999999991</v>
       </c>
       <c r="P3" s="1">
         <f t="shared" si="6"/>
-        <v>44791.121212121216</v>
+        <v>44795.1</v>
       </c>
       <c r="Q3">
         <f t="shared" si="7"/>
-        <v>875.11532687855834</v>
+        <v>874.69270081461104</v>
       </c>
       <c r="R3" s="1">
         <f t="shared" si="8"/>
-        <v>44894.115326878557</v>
+        <v>44893.692700814609</v>
       </c>
     </row>
     <row r="4" spans="1:18" x14ac:dyDescent="0.25">
@@ -3345,19 +3354,19 @@
       </c>
       <c r="O4">
         <f t="shared" si="5"/>
-        <v>1168.0808080808081</v>
+        <v>1174.0999999999999</v>
       </c>
       <c r="P4" s="1">
         <f t="shared" si="6"/>
-        <v>45187.080808080806</v>
+        <v>45193.1</v>
       </c>
       <c r="Q4">
         <f t="shared" si="7"/>
-        <v>1054.4947496647928</v>
+        <v>1053.9854945394216</v>
       </c>
       <c r="R4" s="1">
         <f t="shared" si="8"/>
-        <v>45073.494749664795</v>
+        <v>45072.985494539418</v>
       </c>
     </row>
     <row r="5" spans="1:18" x14ac:dyDescent="0.25">
@@ -3408,19 +3417,19 @@
       </c>
       <c r="O5">
         <f t="shared" si="5"/>
-        <v>1742.2222222222224</v>
+        <v>1751.1999999999998</v>
       </c>
       <c r="P5" s="1">
         <f t="shared" si="6"/>
-        <v>45761.222222222219</v>
+        <v>45770.2</v>
       </c>
       <c r="Q5">
         <f t="shared" si="7"/>
-        <v>1271.0313385996044</v>
+        <v>1270.4175098215142</v>
       </c>
       <c r="R5" s="1">
         <f t="shared" si="8"/>
-        <v>45290.031338599605</v>
+        <v>45289.417509821513</v>
       </c>
     </row>
     <row r="6" spans="1:18" x14ac:dyDescent="0.25">
@@ -3471,19 +3480,19 @@
       </c>
       <c r="O6">
         <f t="shared" si="5"/>
-        <v>2623.2323232323233</v>
+        <v>2636.75</v>
       </c>
       <c r="P6" s="1">
         <f t="shared" si="6"/>
-        <v>46642.232323232325</v>
+        <v>46655.75</v>
       </c>
       <c r="Q6">
         <f t="shared" si="7"/>
-        <v>1678.4788846426229</v>
+        <v>1677.6682841392978</v>
       </c>
       <c r="R6" s="1">
         <f t="shared" si="8"/>
-        <v>45697.478884642624</v>
+        <v>45696.668284139298</v>
       </c>
     </row>
     <row r="7" spans="1:18" x14ac:dyDescent="0.25">
@@ -3534,19 +3543,19 @@
       </c>
       <c r="O7">
         <f t="shared" si="5"/>
-        <v>2910.3030303030305</v>
+        <v>2925.2999999999997</v>
       </c>
       <c r="P7" s="1">
         <f t="shared" si="6"/>
-        <v>46929.303030303032</v>
+        <v>46944.3</v>
       </c>
       <c r="Q7">
         <f t="shared" si="7"/>
-        <v>1745.1055273917957</v>
+        <v>1744.2627503799417</v>
       </c>
       <c r="R7" s="1">
         <f t="shared" si="8"/>
-        <v>45764.105527391795</v>
+        <v>45763.262750379945</v>
       </c>
     </row>
     <row r="8" spans="1:18" x14ac:dyDescent="0.25">
@@ -3597,19 +3606,19 @@
       </c>
       <c r="O8">
         <f t="shared" si="5"/>
-        <v>2910.3030303030305</v>
+        <v>2925.2999999999997</v>
       </c>
       <c r="P8" s="1">
         <f t="shared" si="6"/>
-        <v>46929.303030303032</v>
+        <v>46944.3</v>
       </c>
       <c r="Q8">
         <f t="shared" si="7"/>
-        <v>1745.1055273917957</v>
+        <v>1744.2627503799417</v>
       </c>
       <c r="R8" s="1">
         <f t="shared" si="8"/>
-        <v>45764.105527391795</v>
+        <v>45763.262750379945</v>
       </c>
     </row>
     <row r="9" spans="1:18" x14ac:dyDescent="0.25">
@@ -3684,7 +3693,7 @@
       </c>
       <c r="L10">
         <f>AVERAGE(E:E)</f>
-        <v>9.8989898989898997</v>
+        <v>9.9499999999999993</v>
       </c>
     </row>
     <row r="11" spans="1:18" x14ac:dyDescent="0.25">
@@ -3725,7 +3734,7 @@
       </c>
       <c r="L11">
         <f>AVEDEV(I:I)</f>
-        <v>1.2812815913302464</v>
+        <v>1.2806628123200747</v>
       </c>
     </row>
     <row r="12" spans="1:18" x14ac:dyDescent="0.25">
@@ -5588,7 +5597,7 @@
         <v>526</v>
       </c>
       <c r="B66" t="str">
-        <f t="shared" ref="B66:B100" si="16">"卷"&amp;ROW(B65)</f>
+        <f t="shared" ref="B66:B101" si="16">"卷"&amp;ROW(B65)</f>
         <v>卷65</v>
       </c>
       <c r="C66" s="1">
@@ -6793,6 +6802,41 @@
       <c r="I100">
         <f t="shared" ref="I100" si="87">E100/H100</f>
         <v>3.75</v>
+      </c>
+    </row>
+    <row r="101" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A101">
+        <v>811</v>
+      </c>
+      <c r="B101" t="str">
+        <f t="shared" si="16"/>
+        <v>卷100</v>
+      </c>
+      <c r="C101" s="1">
+        <f>D100+1</f>
+        <v>45173</v>
+      </c>
+      <c r="D101" s="1">
+        <v>45187</v>
+      </c>
+      <c r="E101">
+        <f t="shared" ref="E101" si="88">D101-C101+1</f>
+        <v>15</v>
+      </c>
+      <c r="F101">
+        <f t="shared" ref="F101" si="89">G100+1</f>
+        <v>355</v>
+      </c>
+      <c r="G101">
+        <v>359</v>
+      </c>
+      <c r="H101">
+        <f t="shared" ref="H101" si="90">IF(F101*G101&lt;0,ABS(F101)+ABS(G101),G101-F101+1)</f>
+        <v>5</v>
+      </c>
+      <c r="I101">
+        <f t="shared" ref="I101" si="91">E101/H101</f>
+        <v>3</v>
       </c>
     </row>
   </sheetData>
@@ -9774,24 +9818,27 @@
       <c r="A101">
         <v>811</v>
       </c>
-      <c r="B101" t="e">
+      <c r="B101" t="str">
         <f>VLOOKUP($A101,統計!$A:$G,2,)</f>
-        <v>#N/A</v>
+        <v>卷100</v>
       </c>
       <c r="C101" t="s">
         <v>296</v>
       </c>
-      <c r="D101" t="e">
+      <c r="D101">
         <f>VLOOKUP($A101,統計!$A:$G,6,)</f>
-        <v>#N/A</v>
-      </c>
-      <c r="E101" t="e">
+        <v>355</v>
+      </c>
+      <c r="E101">
         <f>VLOOKUP($A101,統計!$A:$G,7,)</f>
-        <v>#N/A</v>
-      </c>
-      <c r="I101" t="e">
+        <v>359</v>
+      </c>
+      <c r="H101" t="s">
+        <v>534</v>
+      </c>
+      <c r="I101" t="str">
         <f t="shared" si="1"/>
-        <v>#N/A</v>
+        <v>811|[卷100](5_筆記/资治通鉴100.html)|晉紀二十二|355|359|||晉穆帝12年至16年</v>
       </c>
     </row>
     <row r="102" spans="1:9" x14ac:dyDescent="0.25">

--- a/5_筆記/閱讀數據.xlsx
+++ b/5_筆記/閱讀數據.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="26731"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="26827"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\self\study\zizhitongjian\5_筆記\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6EB42131-7B1B-44F9-9B0B-AB59C0C6DA23}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1022AEE3-8B22-4B4B-810B-BD4B9B451E6D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="38620" windowHeight="21220" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="16180" yWindow="1680" windowWidth="13520" windowHeight="12050" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="統計" sheetId="1" r:id="rId1"/>
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="541" uniqueCount="535">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="542" uniqueCount="536">
   <si>
     <t>索引號</t>
   </si>
@@ -1647,6 +1647,10 @@
   </si>
   <si>
     <t>晉穆帝12年至16年</t>
+  </si>
+  <si>
+    <t>晉穆帝17年至18年、晉哀帝至5年、晉廢帝至4年</t>
+    <phoneticPr fontId="4" type="noConversion"/>
   </si>
 </sst>
 </file>
@@ -1950,7 +1954,7 @@
             <c:strRef>
               <c:f>統計!$B$2:$B$115</c:f>
               <c:strCache>
-                <c:ptCount val="100"/>
+                <c:ptCount val="101"/>
                 <c:pt idx="0">
                   <c:v>卷1</c:v>
                 </c:pt>
@@ -2250,6 +2254,9 @@
                 </c:pt>
                 <c:pt idx="99">
                   <c:v>卷100</c:v>
+                </c:pt>
+                <c:pt idx="100">
+                  <c:v>卷101</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
@@ -2559,6 +2566,9 @@
                 </c:pt>
                 <c:pt idx="99">
                   <c:v>3</c:v>
+                </c:pt>
+                <c:pt idx="100">
+                  <c:v>2.7777777777777777</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -3113,7 +3123,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:R101"/>
+  <dimension ref="A1:R102"/>
   <sheetFormatPr defaultColWidth="8.6328125" defaultRowHeight="14" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="7.7265625" customWidth="1"/>
@@ -3228,19 +3238,19 @@
       </c>
       <c r="O2">
         <f t="shared" ref="O2:O8" si="5">L2*$L$10</f>
-        <v>676.59999999999991</v>
+        <v>686.73267326732673</v>
       </c>
       <c r="P2" s="1">
         <f t="shared" ref="P2:P8" si="6">$C$2+O2</f>
-        <v>44695.6</v>
+        <v>44705.732673267325</v>
       </c>
       <c r="Q2">
         <f t="shared" ref="Q2:Q8" si="7">(M2-$F$2)*$L$11</f>
-        <v>797.85293207540656</v>
+        <v>795.61609404656724</v>
       </c>
       <c r="R2" s="1">
         <f t="shared" ref="R2:R8" si="8">$C$2+Q2</f>
-        <v>44816.85293207541</v>
+        <v>44814.616094046571</v>
       </c>
     </row>
     <row r="3" spans="1:18" x14ac:dyDescent="0.25">
@@ -3291,19 +3301,19 @@
       </c>
       <c r="O3">
         <f t="shared" si="5"/>
-        <v>776.09999999999991</v>
+        <v>787.7227722772277</v>
       </c>
       <c r="P3" s="1">
         <f t="shared" si="6"/>
-        <v>44795.1</v>
+        <v>44806.72277227723</v>
       </c>
       <c r="Q3">
         <f t="shared" si="7"/>
-        <v>874.69270081461104</v>
+        <v>872.2404369724004</v>
       </c>
       <c r="R3" s="1">
         <f t="shared" si="8"/>
-        <v>44893.692700814609</v>
+        <v>44891.240436972403</v>
       </c>
     </row>
     <row r="4" spans="1:18" x14ac:dyDescent="0.25">
@@ -3354,19 +3364,19 @@
       </c>
       <c r="O4">
         <f t="shared" si="5"/>
-        <v>1174.0999999999999</v>
+        <v>1191.6831683168316</v>
       </c>
       <c r="P4" s="1">
         <f t="shared" si="6"/>
-        <v>45193.1</v>
+        <v>45210.683168316835</v>
       </c>
       <c r="Q4">
         <f t="shared" si="7"/>
-        <v>1053.9854945394216</v>
+        <v>1051.0305704660111</v>
       </c>
       <c r="R4" s="1">
         <f t="shared" si="8"/>
-        <v>45072.985494539418</v>
+        <v>45070.030570466013</v>
       </c>
     </row>
     <row r="5" spans="1:18" x14ac:dyDescent="0.25">
@@ -3417,19 +3427,19 @@
       </c>
       <c r="O5">
         <f t="shared" si="5"/>
-        <v>1751.1999999999998</v>
+        <v>1777.4257425742574</v>
       </c>
       <c r="P5" s="1">
         <f t="shared" si="6"/>
-        <v>45770.2</v>
+        <v>45796.425742574254</v>
       </c>
       <c r="Q5">
         <f t="shared" si="7"/>
-        <v>1270.4175098215142</v>
+        <v>1266.8558030404411</v>
       </c>
       <c r="R5" s="1">
         <f t="shared" si="8"/>
-        <v>45289.417509821513</v>
+        <v>45285.855803040438</v>
       </c>
     </row>
     <row r="6" spans="1:18" x14ac:dyDescent="0.25">
@@ -3480,19 +3490,19 @@
       </c>
       <c r="O6">
         <f t="shared" si="5"/>
-        <v>2636.75</v>
+        <v>2676.2376237623762</v>
       </c>
       <c r="P6" s="1">
         <f t="shared" si="6"/>
-        <v>46655.75</v>
+        <v>46695.237623762376</v>
       </c>
       <c r="Q6">
         <f t="shared" si="7"/>
-        <v>1677.6682841392978</v>
+        <v>1672.9648205473566</v>
       </c>
       <c r="R6" s="1">
         <f t="shared" si="8"/>
-        <v>45696.668284139298</v>
+        <v>45691.964820547357</v>
       </c>
     </row>
     <row r="7" spans="1:18" x14ac:dyDescent="0.25">
@@ -3543,19 +3553,19 @@
       </c>
       <c r="O7">
         <f t="shared" si="5"/>
-        <v>2925.2999999999997</v>
+        <v>2969.1089108910892</v>
       </c>
       <c r="P7" s="1">
         <f t="shared" si="6"/>
-        <v>46944.3</v>
+        <v>46988.108910891089</v>
       </c>
       <c r="Q7">
         <f t="shared" si="7"/>
-        <v>1744.2627503799417</v>
+        <v>1739.3725844164119</v>
       </c>
       <c r="R7" s="1">
         <f t="shared" si="8"/>
-        <v>45763.262750379945</v>
+        <v>45758.372584416415</v>
       </c>
     </row>
     <row r="8" spans="1:18" x14ac:dyDescent="0.25">
@@ -3606,19 +3616,19 @@
       </c>
       <c r="O8">
         <f t="shared" si="5"/>
-        <v>2925.2999999999997</v>
+        <v>2969.1089108910892</v>
       </c>
       <c r="P8" s="1">
         <f t="shared" si="6"/>
-        <v>46944.3</v>
+        <v>46988.108910891089</v>
       </c>
       <c r="Q8">
         <f t="shared" si="7"/>
-        <v>1744.2627503799417</v>
+        <v>1739.3725844164119</v>
       </c>
       <c r="R8" s="1">
         <f t="shared" si="8"/>
-        <v>45763.262750379945</v>
+        <v>45758.372584416415</v>
       </c>
     </row>
     <row r="9" spans="1:18" x14ac:dyDescent="0.25">
@@ -3693,7 +3703,7 @@
       </c>
       <c r="L10">
         <f>AVERAGE(E:E)</f>
-        <v>9.9499999999999993</v>
+        <v>10.099009900990099</v>
       </c>
     </row>
     <row r="11" spans="1:18" x14ac:dyDescent="0.25">
@@ -3734,7 +3744,7 @@
       </c>
       <c r="L11">
         <f>AVEDEV(I:I)</f>
-        <v>1.2806628123200747</v>
+        <v>1.2770723820972187</v>
       </c>
     </row>
     <row r="12" spans="1:18" x14ac:dyDescent="0.25">
@@ -5597,7 +5607,7 @@
         <v>526</v>
       </c>
       <c r="B66" t="str">
-        <f t="shared" ref="B66:B101" si="16">"卷"&amp;ROW(B65)</f>
+        <f t="shared" ref="B66:B102" si="16">"卷"&amp;ROW(B65)</f>
         <v>卷65</v>
       </c>
       <c r="C66" s="1">
@@ -6837,6 +6847,41 @@
       <c r="I101">
         <f t="shared" ref="I101" si="91">E101/H101</f>
         <v>3</v>
+      </c>
+    </row>
+    <row r="102" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A102">
+        <v>812</v>
+      </c>
+      <c r="B102" t="str">
+        <f t="shared" si="16"/>
+        <v>卷101</v>
+      </c>
+      <c r="C102" s="1">
+        <f>D101+1</f>
+        <v>45188</v>
+      </c>
+      <c r="D102" s="1">
+        <v>45212</v>
+      </c>
+      <c r="E102">
+        <f t="shared" ref="E102" si="92">D102-C102+1</f>
+        <v>25</v>
+      </c>
+      <c r="F102">
+        <f t="shared" ref="F102" si="93">G101+1</f>
+        <v>360</v>
+      </c>
+      <c r="G102">
+        <v>368</v>
+      </c>
+      <c r="H102">
+        <f t="shared" ref="H102" si="94">IF(F102*G102&lt;0,ABS(F102)+ABS(G102),G102-F102+1)</f>
+        <v>9</v>
+      </c>
+      <c r="I102">
+        <f t="shared" ref="I102" si="95">E102/H102</f>
+        <v>2.7777777777777777</v>
       </c>
     </row>
   </sheetData>
@@ -9845,24 +9890,27 @@
       <c r="A102">
         <v>812</v>
       </c>
-      <c r="B102" t="e">
+      <c r="B102" t="str">
         <f>VLOOKUP($A102,統計!$A:$G,2,)</f>
-        <v>#N/A</v>
+        <v>卷101</v>
       </c>
       <c r="C102" t="s">
         <v>297</v>
       </c>
-      <c r="D102" t="e">
+      <c r="D102">
         <f>VLOOKUP($A102,統計!$A:$G,6,)</f>
-        <v>#N/A</v>
-      </c>
-      <c r="E102" t="e">
+        <v>360</v>
+      </c>
+      <c r="E102">
         <f>VLOOKUP($A102,統計!$A:$G,7,)</f>
-        <v>#N/A</v>
-      </c>
-      <c r="I102" t="e">
+        <v>368</v>
+      </c>
+      <c r="H102" t="s">
+        <v>535</v>
+      </c>
+      <c r="I102" t="str">
         <f t="shared" si="1"/>
-        <v>#N/A</v>
+        <v>812|[卷101](5_筆記/资治通鉴101.html)|晉紀二十三|360|368|||晉穆帝17年至18年、晉哀帝至5年、晉廢帝至4年</v>
       </c>
     </row>
     <row r="103" spans="1:9" x14ac:dyDescent="0.25">

--- a/5_筆記/閱讀數據.xlsx
+++ b/5_筆記/閱讀數據.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\self\study\zizhitongjian\5_筆記\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1022AEE3-8B22-4B4B-810B-BD4B9B451E6D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{14F074BA-B537-4A71-85D5-80095F81FF69}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="16180" yWindow="1680" windowWidth="13520" windowHeight="12050" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="38620" windowHeight="21220" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="統計" sheetId="1" r:id="rId1"/>
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="542" uniqueCount="536">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="543" uniqueCount="537">
   <si>
     <t>索引號</t>
   </si>
@@ -1650,6 +1650,10 @@
   </si>
   <si>
     <t>晉穆帝17年至18年、晉哀帝至5年、晉廢帝至4年</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>晉廢帝5年至6年</t>
     <phoneticPr fontId="4" type="noConversion"/>
   </si>
 </sst>
@@ -1954,7 +1958,7 @@
             <c:strRef>
               <c:f>統計!$B$2:$B$115</c:f>
               <c:strCache>
-                <c:ptCount val="101"/>
+                <c:ptCount val="102"/>
                 <c:pt idx="0">
                   <c:v>卷1</c:v>
                 </c:pt>
@@ -2257,6 +2261,9 @@
                 </c:pt>
                 <c:pt idx="100">
                   <c:v>卷101</c:v>
+                </c:pt>
+                <c:pt idx="101">
+                  <c:v>卷102</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
@@ -2569,6 +2576,9 @@
                 </c:pt>
                 <c:pt idx="100">
                   <c:v>2.7777777777777777</c:v>
+                </c:pt>
+                <c:pt idx="101">
+                  <c:v>7</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -3123,7 +3133,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:R102"/>
+  <dimension ref="A1:R103"/>
   <sheetFormatPr defaultColWidth="8.6328125" defaultRowHeight="14" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="7.7265625" customWidth="1"/>
@@ -3238,19 +3248,19 @@
       </c>
       <c r="O2">
         <f t="shared" ref="O2:O8" si="5">L2*$L$10</f>
-        <v>686.73267326732673</v>
+        <v>689.33333333333326</v>
       </c>
       <c r="P2" s="1">
         <f t="shared" ref="P2:P8" si="6">$C$2+O2</f>
-        <v>44705.732673267325</v>
+        <v>44708.333333333336</v>
       </c>
       <c r="Q2">
         <f t="shared" ref="Q2:Q8" si="7">(M2-$F$2)*$L$11</f>
-        <v>795.61609404656724</v>
+        <v>825.16976451211156</v>
       </c>
       <c r="R2" s="1">
         <f t="shared" ref="R2:R8" si="8">$C$2+Q2</f>
-        <v>44814.616094046571</v>
+        <v>44844.169764512109</v>
       </c>
     </row>
     <row r="3" spans="1:18" x14ac:dyDescent="0.25">
@@ -3301,19 +3311,19 @@
       </c>
       <c r="O3">
         <f t="shared" si="5"/>
-        <v>787.7227722772277</v>
+        <v>790.7058823529411</v>
       </c>
       <c r="P3" s="1">
         <f t="shared" si="6"/>
-        <v>44806.72277227723</v>
+        <v>44809.705882352944</v>
       </c>
       <c r="Q3">
         <f t="shared" si="7"/>
-        <v>872.2404369724004</v>
+        <v>904.64036783591041</v>
       </c>
       <c r="R3" s="1">
         <f t="shared" si="8"/>
-        <v>44891.240436972403</v>
+        <v>44923.640367835913</v>
       </c>
     </row>
     <row r="4" spans="1:18" x14ac:dyDescent="0.25">
@@ -3364,19 +3374,19 @@
       </c>
       <c r="O4">
         <f t="shared" si="5"/>
-        <v>1191.6831683168316</v>
+        <v>1196.1960784313726</v>
       </c>
       <c r="P4" s="1">
         <f t="shared" si="6"/>
-        <v>45210.683168316835</v>
+        <v>45215.196078431371</v>
       </c>
       <c r="Q4">
         <f t="shared" si="7"/>
-        <v>1051.0305704660111</v>
+        <v>1090.0717755914411</v>
       </c>
       <c r="R4" s="1">
         <f t="shared" si="8"/>
-        <v>45070.030570466013</v>
+        <v>45109.071775591437</v>
       </c>
     </row>
     <row r="5" spans="1:18" x14ac:dyDescent="0.25">
@@ -3427,19 +3437,19 @@
       </c>
       <c r="O5">
         <f t="shared" si="5"/>
-        <v>1777.4257425742574</v>
+        <v>1784.1568627450979</v>
       </c>
       <c r="P5" s="1">
         <f t="shared" si="6"/>
-        <v>45796.425742574254</v>
+        <v>45803.156862745098</v>
       </c>
       <c r="Q5">
         <f t="shared" si="7"/>
-        <v>1266.8558030404411</v>
+        <v>1313.9139749534745</v>
       </c>
       <c r="R5" s="1">
         <f t="shared" si="8"/>
-        <v>45285.855803040438</v>
+        <v>45332.913974953473</v>
       </c>
     </row>
     <row r="6" spans="1:18" x14ac:dyDescent="0.25">
@@ -3490,19 +3500,19 @@
       </c>
       <c r="O6">
         <f t="shared" si="5"/>
-        <v>2676.2376237623762</v>
+        <v>2686.3725490196075</v>
       </c>
       <c r="P6" s="1">
         <f t="shared" si="6"/>
-        <v>46695.237623762376</v>
+        <v>46705.372549019608</v>
       </c>
       <c r="Q6">
         <f t="shared" si="7"/>
-        <v>1672.9648205473566</v>
+        <v>1735.1081725696085</v>
       </c>
       <c r="R6" s="1">
         <f t="shared" si="8"/>
-        <v>45691.964820547357</v>
+        <v>45754.108172569606</v>
       </c>
     </row>
     <row r="7" spans="1:18" x14ac:dyDescent="0.25">
@@ -3553,19 +3563,19 @@
       </c>
       <c r="O7">
         <f t="shared" si="5"/>
-        <v>2969.1089108910892</v>
+        <v>2980.3529411764703</v>
       </c>
       <c r="P7" s="1">
         <f t="shared" si="6"/>
-        <v>46988.108910891089</v>
+        <v>46999.352941176468</v>
       </c>
       <c r="Q7">
         <f t="shared" si="7"/>
-        <v>1739.3725844164119</v>
+        <v>1803.9826954502344</v>
       </c>
       <c r="R7" s="1">
         <f t="shared" si="8"/>
-        <v>45758.372584416415</v>
+        <v>45822.982695450235</v>
       </c>
     </row>
     <row r="8" spans="1:18" x14ac:dyDescent="0.25">
@@ -3616,19 +3626,19 @@
       </c>
       <c r="O8">
         <f t="shared" si="5"/>
-        <v>2969.1089108910892</v>
+        <v>2980.3529411764703</v>
       </c>
       <c r="P8" s="1">
         <f t="shared" si="6"/>
-        <v>46988.108910891089</v>
+        <v>46999.352941176468</v>
       </c>
       <c r="Q8">
         <f t="shared" si="7"/>
-        <v>1739.3725844164119</v>
+        <v>1803.9826954502344</v>
       </c>
       <c r="R8" s="1">
         <f t="shared" si="8"/>
-        <v>45758.372584416415</v>
+        <v>45822.982695450235</v>
       </c>
     </row>
     <row r="9" spans="1:18" x14ac:dyDescent="0.25">
@@ -3703,7 +3713,7 @@
       </c>
       <c r="L10">
         <f>AVERAGE(E:E)</f>
-        <v>10.099009900990099</v>
+        <v>10.137254901960784</v>
       </c>
     </row>
     <row r="11" spans="1:18" x14ac:dyDescent="0.25">
@@ -3744,7 +3754,7 @@
       </c>
       <c r="L11">
         <f>AVEDEV(I:I)</f>
-        <v>1.2770723820972187</v>
+        <v>1.3245100553966478</v>
       </c>
     </row>
     <row r="12" spans="1:18" x14ac:dyDescent="0.25">
@@ -5607,7 +5617,7 @@
         <v>526</v>
       </c>
       <c r="B66" t="str">
-        <f t="shared" ref="B66:B102" si="16">"卷"&amp;ROW(B65)</f>
+        <f t="shared" ref="B66:B103" si="16">"卷"&amp;ROW(B65)</f>
         <v>卷65</v>
       </c>
       <c r="C66" s="1">
@@ -6882,6 +6892,41 @@
       <c r="I102">
         <f t="shared" ref="I102" si="95">E102/H102</f>
         <v>2.7777777777777777</v>
+      </c>
+    </row>
+    <row r="103" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A103">
+        <v>813</v>
+      </c>
+      <c r="B103" t="str">
+        <f t="shared" si="16"/>
+        <v>卷102</v>
+      </c>
+      <c r="C103" s="1">
+        <f>D102+1</f>
+        <v>45213</v>
+      </c>
+      <c r="D103" s="1">
+        <v>45226</v>
+      </c>
+      <c r="E103">
+        <f t="shared" ref="E103" si="96">D103-C103+1</f>
+        <v>14</v>
+      </c>
+      <c r="F103">
+        <f t="shared" ref="F103" si="97">G102+1</f>
+        <v>369</v>
+      </c>
+      <c r="G103">
+        <v>370</v>
+      </c>
+      <c r="H103">
+        <f t="shared" ref="H103" si="98">IF(F103*G103&lt;0,ABS(F103)+ABS(G103),G103-F103+1)</f>
+        <v>2</v>
+      </c>
+      <c r="I103">
+        <f t="shared" ref="I103" si="99">E103/H103</f>
+        <v>7</v>
       </c>
     </row>
   </sheetData>
@@ -9917,24 +9962,27 @@
       <c r="A103">
         <v>813</v>
       </c>
-      <c r="B103" t="e">
+      <c r="B103" t="str">
         <f>VLOOKUP($A103,統計!$A:$G,2,)</f>
-        <v>#N/A</v>
+        <v>卷102</v>
       </c>
       <c r="C103" t="s">
         <v>298</v>
       </c>
-      <c r="D103" t="e">
+      <c r="D103">
         <f>VLOOKUP($A103,統計!$A:$G,6,)</f>
-        <v>#N/A</v>
-      </c>
-      <c r="E103" t="e">
+        <v>369</v>
+      </c>
+      <c r="E103">
         <f>VLOOKUP($A103,統計!$A:$G,7,)</f>
-        <v>#N/A</v>
-      </c>
-      <c r="I103" t="e">
+        <v>370</v>
+      </c>
+      <c r="H103" t="s">
+        <v>536</v>
+      </c>
+      <c r="I103" t="str">
         <f t="shared" si="1"/>
-        <v>#N/A</v>
+        <v>813|[卷102](5_筆記/资治通鉴102.html)|晉紀二十四|369|370|||晉廢帝5年至6年</v>
       </c>
     </row>
     <row r="104" spans="1:9" x14ac:dyDescent="0.25">

--- a/5_筆記/閱讀數據.xlsx
+++ b/5_筆記/閱讀數據.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="26827"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="26924"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\self\study\zizhitongjian\5_筆記\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{14F074BA-B537-4A71-85D5-80095F81FF69}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1E8B7150-9489-43F1-ACFD-714DA0CD262F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="38620" windowHeight="21220" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="543" uniqueCount="537">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="544" uniqueCount="538">
   <si>
     <t>索引號</t>
   </si>
@@ -1654,6 +1654,10 @@
   </si>
   <si>
     <t>晉廢帝5年至6年</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>晉廢帝7年、晉簡文帝至2年、晉孝武帝至4年</t>
     <phoneticPr fontId="4" type="noConversion"/>
   </si>
 </sst>
@@ -1958,7 +1962,7 @@
             <c:strRef>
               <c:f>統計!$B$2:$B$115</c:f>
               <c:strCache>
-                <c:ptCount val="102"/>
+                <c:ptCount val="103"/>
                 <c:pt idx="0">
                   <c:v>卷1</c:v>
                 </c:pt>
@@ -2264,6 +2268,9 @@
                 </c:pt>
                 <c:pt idx="101">
                   <c:v>卷102</c:v>
+                </c:pt>
+                <c:pt idx="102">
+                  <c:v>卷103</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
@@ -2579,6 +2586,9 @@
                 </c:pt>
                 <c:pt idx="101">
                   <c:v>7</c:v>
+                </c:pt>
+                <c:pt idx="102">
+                  <c:v>3.4</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -3133,7 +3143,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:R103"/>
+  <dimension ref="A1:R104"/>
   <sheetFormatPr defaultColWidth="8.6328125" defaultRowHeight="14" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="7.7265625" customWidth="1"/>
@@ -3248,19 +3258,19 @@
       </c>
       <c r="O2">
         <f t="shared" ref="O2:O8" si="5">L2*$L$10</f>
-        <v>689.33333333333326</v>
+        <v>693.86407766990283</v>
       </c>
       <c r="P2" s="1">
         <f t="shared" ref="P2:P8" si="6">$C$2+O2</f>
-        <v>44708.333333333336</v>
+        <v>44712.864077669903</v>
       </c>
       <c r="Q2">
         <f t="shared" ref="Q2:Q8" si="7">(M2-$F$2)*$L$11</f>
-        <v>825.16976451211156</v>
+        <v>826.79422043538364</v>
       </c>
       <c r="R2" s="1">
         <f t="shared" ref="R2:R8" si="8">$C$2+Q2</f>
-        <v>44844.169764512109</v>
+        <v>44845.794220435382</v>
       </c>
     </row>
     <row r="3" spans="1:18" x14ac:dyDescent="0.25">
@@ -3311,19 +3321,19 @@
       </c>
       <c r="O3">
         <f t="shared" si="5"/>
-        <v>790.7058823529411</v>
+        <v>795.90291262135918</v>
       </c>
       <c r="P3" s="1">
         <f t="shared" si="6"/>
-        <v>44809.705882352944</v>
+        <v>44814.902912621357</v>
       </c>
       <c r="Q3">
         <f t="shared" si="7"/>
-        <v>904.64036783591041</v>
+        <v>906.42127216270796</v>
       </c>
       <c r="R3" s="1">
         <f t="shared" si="8"/>
-        <v>44923.640367835913</v>
+        <v>44925.421272162705</v>
       </c>
     </row>
     <row r="4" spans="1:18" x14ac:dyDescent="0.25">
@@ -3374,19 +3384,19 @@
       </c>
       <c r="O4">
         <f t="shared" si="5"/>
-        <v>1196.1960784313726</v>
+        <v>1204.0582524271845</v>
       </c>
       <c r="P4" s="1">
         <f t="shared" si="6"/>
-        <v>45215.196078431371</v>
+        <v>45223.058252427181</v>
       </c>
       <c r="Q4">
         <f t="shared" si="7"/>
-        <v>1090.0717755914411</v>
+        <v>1092.2177261931313</v>
       </c>
       <c r="R4" s="1">
         <f t="shared" si="8"/>
-        <v>45109.071775591437</v>
+        <v>45111.217726193128</v>
       </c>
     </row>
     <row r="5" spans="1:18" x14ac:dyDescent="0.25">
@@ -3437,19 +3447,19 @@
       </c>
       <c r="O5">
         <f t="shared" si="5"/>
-        <v>1784.1568627450979</v>
+        <v>1795.8834951456311</v>
       </c>
       <c r="P5" s="1">
         <f t="shared" si="6"/>
-        <v>45803.156862745098</v>
+        <v>45814.88349514563</v>
       </c>
       <c r="Q5">
         <f t="shared" si="7"/>
-        <v>1313.9139749534745</v>
+        <v>1316.5005885584278</v>
       </c>
       <c r="R5" s="1">
         <f t="shared" si="8"/>
-        <v>45332.913974953473</v>
+        <v>45335.500588558425</v>
       </c>
     </row>
     <row r="6" spans="1:18" x14ac:dyDescent="0.25">
@@ -3500,19 +3510,19 @@
       </c>
       <c r="O6">
         <f t="shared" si="5"/>
-        <v>2686.3725490196075</v>
+        <v>2704.029126213592</v>
       </c>
       <c r="P6" s="1">
         <f t="shared" si="6"/>
-        <v>46705.372549019608</v>
+        <v>46723.029126213594</v>
       </c>
       <c r="Q6">
         <f t="shared" si="7"/>
-        <v>1735.1081725696085</v>
+        <v>1738.5239627132464</v>
       </c>
       <c r="R6" s="1">
         <f t="shared" si="8"/>
-        <v>45754.108172569606</v>
+        <v>45757.523962713247</v>
       </c>
     </row>
     <row r="7" spans="1:18" x14ac:dyDescent="0.25">
@@ -3563,19 +3573,19 @@
       </c>
       <c r="O7">
         <f t="shared" si="5"/>
-        <v>2980.3529411764703</v>
+        <v>2999.9417475728155</v>
       </c>
       <c r="P7" s="1">
         <f t="shared" si="6"/>
-        <v>46999.352941176468</v>
+        <v>47018.941747572819</v>
       </c>
       <c r="Q7">
         <f t="shared" si="7"/>
-        <v>1803.9826954502344</v>
+        <v>1807.5340742102608</v>
       </c>
       <c r="R7" s="1">
         <f t="shared" si="8"/>
-        <v>45822.982695450235</v>
+        <v>45826.534074210263</v>
       </c>
     </row>
     <row r="8" spans="1:18" x14ac:dyDescent="0.25">
@@ -3626,19 +3636,19 @@
       </c>
       <c r="O8">
         <f t="shared" si="5"/>
-        <v>2980.3529411764703</v>
+        <v>2999.9417475728155</v>
       </c>
       <c r="P8" s="1">
         <f t="shared" si="6"/>
-        <v>46999.352941176468</v>
+        <v>47018.941747572819</v>
       </c>
       <c r="Q8">
         <f t="shared" si="7"/>
-        <v>1803.9826954502344</v>
+        <v>1807.5340742102608</v>
       </c>
       <c r="R8" s="1">
         <f t="shared" si="8"/>
-        <v>45822.982695450235</v>
+        <v>45826.534074210263</v>
       </c>
     </row>
     <row r="9" spans="1:18" x14ac:dyDescent="0.25">
@@ -3713,7 +3723,7 @@
       </c>
       <c r="L10">
         <f>AVERAGE(E:E)</f>
-        <v>10.137254901960784</v>
+        <v>10.203883495145631</v>
       </c>
     </row>
     <row r="11" spans="1:18" x14ac:dyDescent="0.25">
@@ -3754,7 +3764,7 @@
       </c>
       <c r="L11">
         <f>AVEDEV(I:I)</f>
-        <v>1.3245100553966478</v>
+        <v>1.3271175287887378</v>
       </c>
     </row>
     <row r="12" spans="1:18" x14ac:dyDescent="0.25">
@@ -5617,7 +5627,7 @@
         <v>526</v>
       </c>
       <c r="B66" t="str">
-        <f t="shared" ref="B66:B103" si="16">"卷"&amp;ROW(B65)</f>
+        <f t="shared" ref="B66:B104" si="16">"卷"&amp;ROW(B65)</f>
         <v>卷65</v>
       </c>
       <c r="C66" s="1">
@@ -6927,6 +6937,41 @@
       <c r="I103">
         <f t="shared" ref="I103" si="99">E103/H103</f>
         <v>7</v>
+      </c>
+    </row>
+    <row r="104" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A104">
+        <v>814</v>
+      </c>
+      <c r="B104" t="str">
+        <f t="shared" si="16"/>
+        <v>卷103</v>
+      </c>
+      <c r="C104" s="1">
+        <f>D103+1</f>
+        <v>45227</v>
+      </c>
+      <c r="D104" s="1">
+        <v>45243</v>
+      </c>
+      <c r="E104">
+        <f t="shared" ref="E104" si="100">D104-C104+1</f>
+        <v>17</v>
+      </c>
+      <c r="F104">
+        <f t="shared" ref="F104" si="101">G103+1</f>
+        <v>371</v>
+      </c>
+      <c r="G104">
+        <v>375</v>
+      </c>
+      <c r="H104">
+        <f t="shared" ref="H104" si="102">IF(F104*G104&lt;0,ABS(F104)+ABS(G104),G104-F104+1)</f>
+        <v>5</v>
+      </c>
+      <c r="I104">
+        <f t="shared" ref="I104" si="103">E104/H104</f>
+        <v>3.4</v>
       </c>
     </row>
   </sheetData>
@@ -9989,24 +10034,27 @@
       <c r="A104">
         <v>814</v>
       </c>
-      <c r="B104" t="e">
+      <c r="B104" t="str">
         <f>VLOOKUP($A104,統計!$A:$G,2,)</f>
-        <v>#N/A</v>
+        <v>卷103</v>
       </c>
       <c r="C104" t="s">
         <v>299</v>
       </c>
-      <c r="D104" t="e">
+      <c r="D104">
         <f>VLOOKUP($A104,統計!$A:$G,6,)</f>
-        <v>#N/A</v>
-      </c>
-      <c r="E104" t="e">
+        <v>371</v>
+      </c>
+      <c r="E104">
         <f>VLOOKUP($A104,統計!$A:$G,7,)</f>
-        <v>#N/A</v>
-      </c>
-      <c r="I104" t="e">
+        <v>375</v>
+      </c>
+      <c r="H104" t="s">
+        <v>537</v>
+      </c>
+      <c r="I104" t="str">
         <f t="shared" si="1"/>
-        <v>#N/A</v>
+        <v>814|[卷103](5_筆記/资治通鉴103.html)|晉紀二十五|371|375|||晉廢帝7年、晉簡文帝至2年、晉孝武帝至4年</v>
       </c>
     </row>
     <row r="105" spans="1:9" x14ac:dyDescent="0.25">

--- a/5_筆記/閱讀數據.xlsx
+++ b/5_筆記/閱讀數據.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\self\study\zizhitongjian\5_筆記\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1E8B7150-9489-43F1-ACFD-714DA0CD262F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CE21DD41-BA28-4FE6-BB9A-17B1AF6EB2D5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="38620" windowHeight="21220" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="544" uniqueCount="538">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="545" uniqueCount="539">
   <si>
     <t>索引號</t>
   </si>
@@ -1658,6 +1658,10 @@
   </si>
   <si>
     <t>晉廢帝7年、晉簡文帝至2年、晉孝武帝至4年</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>晉孝武帝5年至11年</t>
     <phoneticPr fontId="4" type="noConversion"/>
   </si>
 </sst>
@@ -1962,7 +1966,7 @@
             <c:strRef>
               <c:f>統計!$B$2:$B$115</c:f>
               <c:strCache>
-                <c:ptCount val="103"/>
+                <c:ptCount val="104"/>
                 <c:pt idx="0">
                   <c:v>卷1</c:v>
                 </c:pt>
@@ -2271,6 +2275,9 @@
                 </c:pt>
                 <c:pt idx="102">
                   <c:v>卷103</c:v>
+                </c:pt>
+                <c:pt idx="103">
+                  <c:v>卷104</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
@@ -2589,6 +2596,9 @@
                 </c:pt>
                 <c:pt idx="102">
                   <c:v>3.4</c:v>
+                </c:pt>
+                <c:pt idx="103">
+                  <c:v>2.2857142857142856</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -3143,7 +3153,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:R104"/>
+  <dimension ref="A1:R105"/>
   <sheetFormatPr defaultColWidth="8.6328125" defaultRowHeight="14" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="7.7265625" customWidth="1"/>
@@ -3258,19 +3268,19 @@
       </c>
       <c r="O2">
         <f t="shared" ref="O2:O8" si="5">L2*$L$10</f>
-        <v>693.86407766990283</v>
+        <v>697.65384615384619</v>
       </c>
       <c r="P2" s="1">
         <f t="shared" ref="P2:P8" si="6">$C$2+O2</f>
-        <v>44712.864077669903</v>
+        <v>44716.653846153844</v>
       </c>
       <c r="Q2">
         <f t="shared" ref="Q2:Q8" si="7">(M2-$F$2)*$L$11</f>
-        <v>826.79422043538364</v>
+        <v>820.116895267563</v>
       </c>
       <c r="R2" s="1">
         <f t="shared" ref="R2:R8" si="8">$C$2+Q2</f>
-        <v>44845.794220435382</v>
+        <v>44839.116895267565</v>
       </c>
     </row>
     <row r="3" spans="1:18" x14ac:dyDescent="0.25">
@@ -3321,19 +3331,19 @@
       </c>
       <c r="O3">
         <f t="shared" si="5"/>
-        <v>795.90291262135918</v>
+        <v>800.25</v>
       </c>
       <c r="P3" s="1">
         <f t="shared" si="6"/>
-        <v>44814.902912621357</v>
+        <v>44819.25</v>
       </c>
       <c r="Q3">
         <f t="shared" si="7"/>
-        <v>906.42127216270796</v>
+        <v>899.10086591933464</v>
       </c>
       <c r="R3" s="1">
         <f t="shared" si="8"/>
-        <v>44925.421272162705</v>
+        <v>44918.100865919332</v>
       </c>
     </row>
     <row r="4" spans="1:18" x14ac:dyDescent="0.25">
@@ -3384,19 +3394,19 @@
       </c>
       <c r="O4">
         <f t="shared" si="5"/>
-        <v>1204.0582524271845</v>
+        <v>1210.6346153846155</v>
       </c>
       <c r="P4" s="1">
         <f t="shared" si="6"/>
-        <v>45223.058252427181</v>
+        <v>45229.634615384617</v>
       </c>
       <c r="Q4">
         <f t="shared" si="7"/>
-        <v>1092.2177261931313</v>
+        <v>1083.3967974401353</v>
       </c>
       <c r="R4" s="1">
         <f t="shared" si="8"/>
-        <v>45111.217726193128</v>
+        <v>45102.396797440138</v>
       </c>
     </row>
     <row r="5" spans="1:18" x14ac:dyDescent="0.25">
@@ -3447,19 +3457,19 @@
       </c>
       <c r="O5">
         <f t="shared" si="5"/>
-        <v>1795.8834951456311</v>
+        <v>1805.6923076923078</v>
       </c>
       <c r="P5" s="1">
         <f t="shared" si="6"/>
-        <v>45814.88349514563</v>
+        <v>45824.692307692305</v>
       </c>
       <c r="Q5">
         <f t="shared" si="7"/>
-        <v>1316.5005885584278</v>
+        <v>1305.8683147759589</v>
       </c>
       <c r="R5" s="1">
         <f t="shared" si="8"/>
-        <v>45335.500588558425</v>
+        <v>45324.868314775958</v>
       </c>
     </row>
     <row r="6" spans="1:18" x14ac:dyDescent="0.25">
@@ -3510,19 +3520,19 @@
       </c>
       <c r="O6">
         <f t="shared" si="5"/>
-        <v>2704.029126213592</v>
+        <v>2718.7980769230771</v>
       </c>
       <c r="P6" s="1">
         <f t="shared" si="6"/>
-        <v>46723.029126213594</v>
+        <v>46737.798076923078</v>
       </c>
       <c r="Q6">
         <f t="shared" si="7"/>
-        <v>1738.5239627132464</v>
+        <v>1724.4833592303492</v>
       </c>
       <c r="R6" s="1">
         <f t="shared" si="8"/>
-        <v>45757.523962713247</v>
+        <v>45743.483359230348</v>
       </c>
     </row>
     <row r="7" spans="1:18" x14ac:dyDescent="0.25">
@@ -3573,19 +3583,19 @@
       </c>
       <c r="O7">
         <f t="shared" si="5"/>
-        <v>2999.9417475728155</v>
+        <v>3016.3269230769233</v>
       </c>
       <c r="P7" s="1">
         <f t="shared" si="6"/>
-        <v>47018.941747572819</v>
+        <v>47035.326923076922</v>
       </c>
       <c r="Q7">
         <f t="shared" si="7"/>
-        <v>1807.5340742102608</v>
+        <v>1792.936133795218</v>
       </c>
       <c r="R7" s="1">
         <f t="shared" si="8"/>
-        <v>45826.534074210263</v>
+        <v>45811.936133795221</v>
       </c>
     </row>
     <row r="8" spans="1:18" x14ac:dyDescent="0.25">
@@ -3636,19 +3646,19 @@
       </c>
       <c r="O8">
         <f t="shared" si="5"/>
-        <v>2999.9417475728155</v>
+        <v>3016.3269230769233</v>
       </c>
       <c r="P8" s="1">
         <f t="shared" si="6"/>
-        <v>47018.941747572819</v>
+        <v>47035.326923076922</v>
       </c>
       <c r="Q8">
         <f t="shared" si="7"/>
-        <v>1807.5340742102608</v>
+        <v>1792.936133795218</v>
       </c>
       <c r="R8" s="1">
         <f t="shared" si="8"/>
-        <v>45826.534074210263</v>
+        <v>45811.936133795221</v>
       </c>
     </row>
     <row r="9" spans="1:18" x14ac:dyDescent="0.25">
@@ -3723,7 +3733,7 @@
       </c>
       <c r="L10">
         <f>AVERAGE(E:E)</f>
-        <v>10.203883495145631</v>
+        <v>10.259615384615385</v>
       </c>
     </row>
     <row r="11" spans="1:18" x14ac:dyDescent="0.25">
@@ -3764,7 +3774,7 @@
       </c>
       <c r="L11">
         <f>AVEDEV(I:I)</f>
-        <v>1.3271175287887378</v>
+        <v>1.3163995108628619</v>
       </c>
     </row>
     <row r="12" spans="1:18" x14ac:dyDescent="0.25">
@@ -5627,7 +5637,7 @@
         <v>526</v>
       </c>
       <c r="B66" t="str">
-        <f t="shared" ref="B66:B104" si="16">"卷"&amp;ROW(B65)</f>
+        <f t="shared" ref="B66:B105" si="16">"卷"&amp;ROW(B65)</f>
         <v>卷65</v>
       </c>
       <c r="C66" s="1">
@@ -6972,6 +6982,40 @@
       <c r="I104">
         <f t="shared" ref="I104" si="103">E104/H104</f>
         <v>3.4</v>
+      </c>
+    </row>
+    <row r="105" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A105">
+        <v>815</v>
+      </c>
+      <c r="B105" t="str">
+        <f t="shared" si="16"/>
+        <v>卷104</v>
+      </c>
+      <c r="C105" s="1">
+        <v>45245</v>
+      </c>
+      <c r="D105" s="1">
+        <v>45260</v>
+      </c>
+      <c r="E105">
+        <f t="shared" ref="E105" si="104">D105-C105+1</f>
+        <v>16</v>
+      </c>
+      <c r="F105">
+        <f t="shared" ref="F105" si="105">G104+1</f>
+        <v>376</v>
+      </c>
+      <c r="G105">
+        <v>382</v>
+      </c>
+      <c r="H105">
+        <f t="shared" ref="H105" si="106">IF(F105*G105&lt;0,ABS(F105)+ABS(G105),G105-F105+1)</f>
+        <v>7</v>
+      </c>
+      <c r="I105">
+        <f t="shared" ref="I105" si="107">E105/H105</f>
+        <v>2.2857142857142856</v>
       </c>
     </row>
   </sheetData>
@@ -10061,24 +10105,27 @@
       <c r="A105">
         <v>815</v>
       </c>
-      <c r="B105" t="e">
+      <c r="B105" t="str">
         <f>VLOOKUP($A105,統計!$A:$G,2,)</f>
-        <v>#N/A</v>
+        <v>卷104</v>
       </c>
       <c r="C105" t="s">
         <v>300</v>
       </c>
-      <c r="D105" t="e">
+      <c r="D105">
         <f>VLOOKUP($A105,統計!$A:$G,6,)</f>
-        <v>#N/A</v>
-      </c>
-      <c r="E105" t="e">
+        <v>376</v>
+      </c>
+      <c r="E105">
         <f>VLOOKUP($A105,統計!$A:$G,7,)</f>
-        <v>#N/A</v>
-      </c>
-      <c r="I105" t="e">
+        <v>382</v>
+      </c>
+      <c r="H105" t="s">
+        <v>538</v>
+      </c>
+      <c r="I105" t="str">
         <f t="shared" si="1"/>
-        <v>#N/A</v>
+        <v>815|[卷104](5_筆記/资治通鉴104.html)|晉紀二十六|376|382|||晉孝武帝5年至11年</v>
       </c>
     </row>
     <row r="106" spans="1:9" x14ac:dyDescent="0.25">

--- a/5_筆記/閱讀數據.xlsx
+++ b/5_筆記/閱讀數據.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="26924"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="27029"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\self\study\zizhitongjian\5_筆記\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CE21DD41-BA28-4FE6-BB9A-17B1AF6EB2D5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2FE6DEFF-E7A1-4F58-9D65-59E78F5D7E67}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="38620" windowHeight="21220" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="545" uniqueCount="539">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="546" uniqueCount="540">
   <si>
     <t>索引號</t>
   </si>
@@ -1662,6 +1662,10 @@
   </si>
   <si>
     <t>晉孝武帝5年至11年</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>晉孝武帝12年至13年</t>
     <phoneticPr fontId="4" type="noConversion"/>
   </si>
 </sst>
@@ -1966,7 +1970,7 @@
             <c:strRef>
               <c:f>統計!$B$2:$B$115</c:f>
               <c:strCache>
-                <c:ptCount val="104"/>
+                <c:ptCount val="105"/>
                 <c:pt idx="0">
                   <c:v>卷1</c:v>
                 </c:pt>
@@ -2278,6 +2282,9 @@
                 </c:pt>
                 <c:pt idx="103">
                   <c:v>卷104</c:v>
+                </c:pt>
+                <c:pt idx="104">
+                  <c:v>卷105</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
@@ -2599,6 +2606,9 @@
                 </c:pt>
                 <c:pt idx="103">
                   <c:v>2.2857142857142856</c:v>
+                </c:pt>
+                <c:pt idx="104">
+                  <c:v>8.5</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -3153,7 +3163,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:R105"/>
+  <dimension ref="A1:R106"/>
   <sheetFormatPr defaultColWidth="8.6328125" defaultRowHeight="14" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="7.7265625" customWidth="1"/>
@@ -3268,19 +3278,19 @@
       </c>
       <c r="O2">
         <f t="shared" ref="O2:O8" si="5">L2*$L$10</f>
-        <v>697.65384615384619</v>
+        <v>702.01904761904768</v>
       </c>
       <c r="P2" s="1">
         <f t="shared" ref="P2:P8" si="6">$C$2+O2</f>
-        <v>44716.653846153844</v>
+        <v>44721.019047619047</v>
       </c>
       <c r="Q2">
         <f t="shared" ref="Q2:Q8" si="7">(M2-$F$2)*$L$11</f>
-        <v>820.116895267563</v>
+        <v>857.78846202530053</v>
       </c>
       <c r="R2" s="1">
         <f t="shared" ref="R2:R8" si="8">$C$2+Q2</f>
-        <v>44839.116895267565</v>
+        <v>44876.788462025303</v>
       </c>
     </row>
     <row r="3" spans="1:18" x14ac:dyDescent="0.25">
@@ -3331,19 +3341,19 @@
       </c>
       <c r="O3">
         <f t="shared" si="5"/>
-        <v>800.25</v>
+        <v>805.25714285714287</v>
       </c>
       <c r="P3" s="1">
         <f t="shared" si="6"/>
-        <v>44819.25</v>
+        <v>44824.257142857146</v>
       </c>
       <c r="Q3">
         <f t="shared" si="7"/>
-        <v>899.10086591933464</v>
+        <v>940.40051294266493</v>
       </c>
       <c r="R3" s="1">
         <f t="shared" si="8"/>
-        <v>44918.100865919332</v>
+        <v>44959.400512942666</v>
       </c>
     </row>
     <row r="4" spans="1:18" x14ac:dyDescent="0.25">
@@ -3394,19 +3404,19 @@
       </c>
       <c r="O4">
         <f t="shared" si="5"/>
-        <v>1210.6346153846155</v>
+        <v>1218.2095238095239</v>
       </c>
       <c r="P4" s="1">
         <f t="shared" si="6"/>
-        <v>45229.634615384617</v>
+        <v>45237.209523809521</v>
       </c>
       <c r="Q4">
         <f t="shared" si="7"/>
-        <v>1083.3967974401353</v>
+        <v>1133.1619650831819</v>
       </c>
       <c r="R4" s="1">
         <f t="shared" si="8"/>
-        <v>45102.396797440138</v>
+        <v>45152.161965083185</v>
       </c>
     </row>
     <row r="5" spans="1:18" x14ac:dyDescent="0.25">
@@ -3457,19 +3467,19 @@
       </c>
       <c r="O5">
         <f t="shared" si="5"/>
-        <v>1805.6923076923078</v>
+        <v>1816.9904761904763</v>
       </c>
       <c r="P5" s="1">
         <f t="shared" si="6"/>
-        <v>45824.692307692305</v>
+        <v>45835.990476190476</v>
       </c>
       <c r="Q5">
         <f t="shared" si="7"/>
-        <v>1305.8683147759589</v>
+        <v>1365.8525751670918</v>
       </c>
       <c r="R5" s="1">
         <f t="shared" si="8"/>
-        <v>45324.868314775958</v>
+        <v>45384.85257516709</v>
       </c>
     </row>
     <row r="6" spans="1:18" x14ac:dyDescent="0.25">
@@ -3520,19 +3530,19 @@
       </c>
       <c r="O6">
         <f t="shared" si="5"/>
-        <v>2718.7980769230771</v>
+        <v>2735.8095238095239</v>
       </c>
       <c r="P6" s="1">
         <f t="shared" si="6"/>
-        <v>46737.798076923078</v>
+        <v>46754.809523809527</v>
       </c>
       <c r="Q6">
         <f t="shared" si="7"/>
-        <v>1724.4833592303492</v>
+        <v>1803.6964450291232</v>
       </c>
       <c r="R6" s="1">
         <f t="shared" si="8"/>
-        <v>45743.483359230348</v>
+        <v>45822.69644502912</v>
       </c>
     </row>
     <row r="7" spans="1:18" x14ac:dyDescent="0.25">
@@ -3583,19 +3593,19 @@
       </c>
       <c r="O7">
         <f t="shared" si="5"/>
-        <v>3016.3269230769233</v>
+        <v>3035.2000000000003</v>
       </c>
       <c r="P7" s="1">
         <f t="shared" si="6"/>
-        <v>47035.326923076922</v>
+        <v>47054.2</v>
       </c>
       <c r="Q7">
         <f t="shared" si="7"/>
-        <v>1792.936133795218</v>
+        <v>1875.2935558241722</v>
       </c>
       <c r="R7" s="1">
         <f t="shared" si="8"/>
-        <v>45811.936133795221</v>
+        <v>45894.293555824173</v>
       </c>
     </row>
     <row r="8" spans="1:18" x14ac:dyDescent="0.25">
@@ -3646,19 +3656,19 @@
       </c>
       <c r="O8">
         <f t="shared" si="5"/>
-        <v>3016.3269230769233</v>
+        <v>3035.2000000000003</v>
       </c>
       <c r="P8" s="1">
         <f t="shared" si="6"/>
-        <v>47035.326923076922</v>
+        <v>47054.2</v>
       </c>
       <c r="Q8">
         <f t="shared" si="7"/>
-        <v>1792.936133795218</v>
+        <v>1875.2935558241722</v>
       </c>
       <c r="R8" s="1">
         <f t="shared" si="8"/>
-        <v>45811.936133795221</v>
+        <v>45894.293555824173</v>
       </c>
     </row>
     <row r="9" spans="1:18" x14ac:dyDescent="0.25">
@@ -3733,7 +3743,7 @@
       </c>
       <c r="L10">
         <f>AVERAGE(E:E)</f>
-        <v>10.259615384615385</v>
+        <v>10.323809523809524</v>
       </c>
     </row>
     <row r="11" spans="1:18" x14ac:dyDescent="0.25">
@@ -3774,7 +3784,7 @@
       </c>
       <c r="L11">
         <f>AVEDEV(I:I)</f>
-        <v>1.3163995108628619</v>
+        <v>1.376867515289407</v>
       </c>
     </row>
     <row r="12" spans="1:18" x14ac:dyDescent="0.25">
@@ -5637,7 +5647,7 @@
         <v>526</v>
       </c>
       <c r="B66" t="str">
-        <f t="shared" ref="B66:B105" si="16">"卷"&amp;ROW(B65)</f>
+        <f t="shared" ref="B66:B106" si="16">"卷"&amp;ROW(B65)</f>
         <v>卷65</v>
       </c>
       <c r="C66" s="1">
@@ -7016,6 +7026,41 @@
       <c r="I105">
         <f t="shared" ref="I105" si="107">E105/H105</f>
         <v>2.2857142857142856</v>
+      </c>
+    </row>
+    <row r="106" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A106">
+        <v>816</v>
+      </c>
+      <c r="B106" t="str">
+        <f t="shared" si="16"/>
+        <v>卷105</v>
+      </c>
+      <c r="C106" s="1">
+        <f>D105+1</f>
+        <v>45261</v>
+      </c>
+      <c r="D106" s="1">
+        <v>45277</v>
+      </c>
+      <c r="E106">
+        <f t="shared" ref="E106" si="108">D106-C106+1</f>
+        <v>17</v>
+      </c>
+      <c r="F106">
+        <f t="shared" ref="F106" si="109">G105+1</f>
+        <v>383</v>
+      </c>
+      <c r="G106">
+        <v>384</v>
+      </c>
+      <c r="H106">
+        <f t="shared" ref="H106" si="110">IF(F106*G106&lt;0,ABS(F106)+ABS(G106),G106-F106+1)</f>
+        <v>2</v>
+      </c>
+      <c r="I106">
+        <f t="shared" ref="I106" si="111">E106/H106</f>
+        <v>8.5</v>
       </c>
     </row>
   </sheetData>
@@ -10132,24 +10177,27 @@
       <c r="A106">
         <v>816</v>
       </c>
-      <c r="B106" t="e">
+      <c r="B106" t="str">
         <f>VLOOKUP($A106,統計!$A:$G,2,)</f>
-        <v>#N/A</v>
+        <v>卷105</v>
       </c>
       <c r="C106" t="s">
         <v>301</v>
       </c>
-      <c r="D106" t="e">
+      <c r="D106">
         <f>VLOOKUP($A106,統計!$A:$G,6,)</f>
-        <v>#N/A</v>
-      </c>
-      <c r="E106" t="e">
+        <v>383</v>
+      </c>
+      <c r="E106">
         <f>VLOOKUP($A106,統計!$A:$G,7,)</f>
-        <v>#N/A</v>
-      </c>
-      <c r="I106" t="e">
+        <v>384</v>
+      </c>
+      <c r="H106" t="s">
+        <v>539</v>
+      </c>
+      <c r="I106" t="str">
         <f t="shared" si="1"/>
-        <v>#N/A</v>
+        <v>816|[卷105](5_筆記/资治通鉴105.html)|晉紀二十七|383|384|||晉孝武帝12年至13年</v>
       </c>
     </row>
     <row r="107" spans="1:9" x14ac:dyDescent="0.25">

--- a/5_筆記/閱讀數據.xlsx
+++ b/5_筆記/閱讀數據.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\self\study\zizhitongjian\5_筆記\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2FE6DEFF-E7A1-4F58-9D65-59E78F5D7E67}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7414385B-5CF1-4C2F-82F6-E3CBCC9CCAF0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="38620" windowHeight="21220" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="546" uniqueCount="540">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="547" uniqueCount="541">
   <si>
     <t>索引號</t>
   </si>
@@ -1667,6 +1667,9 @@
   <si>
     <t>晉孝武帝12年至13年</t>
     <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>晉孝武帝14年至15年</t>
   </si>
 </sst>
 </file>
@@ -1970,7 +1973,7 @@
             <c:strRef>
               <c:f>統計!$B$2:$B$115</c:f>
               <c:strCache>
-                <c:ptCount val="105"/>
+                <c:ptCount val="106"/>
                 <c:pt idx="0">
                   <c:v>卷1</c:v>
                 </c:pt>
@@ -2285,6 +2288,9 @@
                 </c:pt>
                 <c:pt idx="104">
                   <c:v>卷105</c:v>
+                </c:pt>
+                <c:pt idx="105">
+                  <c:v>卷106</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
@@ -2609,6 +2615,9 @@
                 </c:pt>
                 <c:pt idx="104">
                   <c:v>8.5</c:v>
+                </c:pt>
+                <c:pt idx="105">
+                  <c:v>9.5</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -3163,7 +3172,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:R106"/>
+  <dimension ref="A1:R107"/>
   <sheetFormatPr defaultColWidth="8.6328125" defaultRowHeight="14" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="7.7265625" customWidth="1"/>
@@ -3278,19 +3287,19 @@
       </c>
       <c r="O2">
         <f t="shared" ref="O2:O8" si="5">L2*$L$10</f>
-        <v>702.01904761904768</v>
+        <v>707.58490566037733</v>
       </c>
       <c r="P2" s="1">
         <f t="shared" ref="P2:P8" si="6">$C$2+O2</f>
-        <v>44721.019047619047</v>
+        <v>44726.584905660377</v>
       </c>
       <c r="Q2">
         <f t="shared" ref="Q2:Q8" si="7">(M2-$F$2)*$L$11</f>
-        <v>857.78846202530053</v>
+        <v>900.88547956958951</v>
       </c>
       <c r="R2" s="1">
         <f t="shared" ref="R2:R8" si="8">$C$2+Q2</f>
-        <v>44876.788462025303</v>
+        <v>44919.885479569588</v>
       </c>
     </row>
     <row r="3" spans="1:18" x14ac:dyDescent="0.25">
@@ -3341,19 +3350,19 @@
       </c>
       <c r="O3">
         <f t="shared" si="5"/>
-        <v>805.25714285714287</v>
+        <v>811.64150943396226</v>
       </c>
       <c r="P3" s="1">
         <f t="shared" si="6"/>
-        <v>44824.257142857146</v>
+        <v>44830.641509433961</v>
       </c>
       <c r="Q3">
         <f t="shared" si="7"/>
-        <v>940.40051294266493</v>
+        <v>987.64812607709416</v>
       </c>
       <c r="R3" s="1">
         <f t="shared" si="8"/>
-        <v>44959.400512942666</v>
+        <v>45006.648126077096</v>
       </c>
     </row>
     <row r="4" spans="1:18" x14ac:dyDescent="0.25">
@@ -3404,19 +3413,19 @@
       </c>
       <c r="O4">
         <f t="shared" si="5"/>
-        <v>1218.2095238095239</v>
+        <v>1227.867924528302</v>
       </c>
       <c r="P4" s="1">
         <f t="shared" si="6"/>
-        <v>45237.209523809521</v>
+        <v>45246.867924528298</v>
       </c>
       <c r="Q4">
         <f t="shared" si="7"/>
-        <v>1133.1619650831819</v>
+        <v>1190.0943012612715</v>
       </c>
       <c r="R4" s="1">
         <f t="shared" si="8"/>
-        <v>45152.161965083185</v>
+        <v>45209.09430126127</v>
       </c>
     </row>
     <row r="5" spans="1:18" x14ac:dyDescent="0.25">
@@ -3467,19 +3476,19 @@
       </c>
       <c r="O5">
         <f t="shared" si="5"/>
-        <v>1816.9904761904763</v>
+        <v>1831.3962264150944</v>
       </c>
       <c r="P5" s="1">
         <f t="shared" si="6"/>
-        <v>45835.990476190476</v>
+        <v>45850.396226415098</v>
       </c>
       <c r="Q5">
         <f t="shared" si="7"/>
-        <v>1365.8525751670918</v>
+        <v>1434.4757555907429</v>
       </c>
       <c r="R5" s="1">
         <f t="shared" si="8"/>
-        <v>45384.85257516709</v>
+        <v>45453.475755590742</v>
       </c>
     </row>
     <row r="6" spans="1:18" x14ac:dyDescent="0.25">
@@ -3530,19 +3539,19 @@
       </c>
       <c r="O6">
         <f t="shared" si="5"/>
-        <v>2735.8095238095239</v>
+        <v>2757.5</v>
       </c>
       <c r="P6" s="1">
         <f t="shared" si="6"/>
-        <v>46754.809523809527</v>
+        <v>46776.5</v>
       </c>
       <c r="Q6">
         <f t="shared" si="7"/>
-        <v>1803.6964450291232</v>
+        <v>1894.3177820805172</v>
       </c>
       <c r="R6" s="1">
         <f t="shared" si="8"/>
-        <v>45822.69644502912</v>
+        <v>45913.317782080514</v>
       </c>
     </row>
     <row r="7" spans="1:18" x14ac:dyDescent="0.25">
@@ -3593,19 +3602,19 @@
       </c>
       <c r="O7">
         <f t="shared" si="5"/>
-        <v>3035.2000000000003</v>
+        <v>3059.2641509433961</v>
       </c>
       <c r="P7" s="1">
         <f t="shared" si="6"/>
-        <v>47054.2</v>
+        <v>47078.264150943396</v>
       </c>
       <c r="Q7">
         <f t="shared" si="7"/>
-        <v>1875.2935558241722</v>
+        <v>1969.5120757203547</v>
       </c>
       <c r="R7" s="1">
         <f t="shared" si="8"/>
-        <v>45894.293555824173</v>
+        <v>45988.512075720355</v>
       </c>
     </row>
     <row r="8" spans="1:18" x14ac:dyDescent="0.25">
@@ -3656,19 +3665,19 @@
       </c>
       <c r="O8">
         <f t="shared" si="5"/>
-        <v>3035.2000000000003</v>
+        <v>3059.2641509433961</v>
       </c>
       <c r="P8" s="1">
         <f t="shared" si="6"/>
-        <v>47054.2</v>
+        <v>47078.264150943396</v>
       </c>
       <c r="Q8">
         <f t="shared" si="7"/>
-        <v>1875.2935558241722</v>
+        <v>1969.5120757203547</v>
       </c>
       <c r="R8" s="1">
         <f t="shared" si="8"/>
-        <v>45894.293555824173</v>
+        <v>45988.512075720355</v>
       </c>
     </row>
     <row r="9" spans="1:18" x14ac:dyDescent="0.25">
@@ -3743,7 +3752,7 @@
       </c>
       <c r="L10">
         <f>AVERAGE(E:E)</f>
-        <v>10.323809523809524</v>
+        <v>10.40566037735849</v>
       </c>
     </row>
     <row r="11" spans="1:18" x14ac:dyDescent="0.25">
@@ -3784,7 +3793,7 @@
       </c>
       <c r="L11">
         <f>AVEDEV(I:I)</f>
-        <v>1.376867515289407</v>
+        <v>1.4460441084584101</v>
       </c>
     </row>
     <row r="12" spans="1:18" x14ac:dyDescent="0.25">
@@ -5647,7 +5656,7 @@
         <v>526</v>
       </c>
       <c r="B66" t="str">
-        <f t="shared" ref="B66:B106" si="16">"卷"&amp;ROW(B65)</f>
+        <f t="shared" ref="B66:B107" si="16">"卷"&amp;ROW(B65)</f>
         <v>卷65</v>
       </c>
       <c r="C66" s="1">
@@ -7061,6 +7070,40 @@
       <c r="I106">
         <f t="shared" ref="I106" si="111">E106/H106</f>
         <v>8.5</v>
+      </c>
+    </row>
+    <row r="107" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A107">
+        <v>817</v>
+      </c>
+      <c r="B107" t="str">
+        <f t="shared" si="16"/>
+        <v>卷106</v>
+      </c>
+      <c r="C107" s="1">
+        <v>45279</v>
+      </c>
+      <c r="D107" s="1">
+        <v>45297</v>
+      </c>
+      <c r="E107">
+        <f t="shared" ref="E107" si="112">D107-C107+1</f>
+        <v>19</v>
+      </c>
+      <c r="F107">
+        <f t="shared" ref="F107" si="113">G106+1</f>
+        <v>385</v>
+      </c>
+      <c r="G107">
+        <v>386</v>
+      </c>
+      <c r="H107">
+        <f t="shared" ref="H107" si="114">IF(F107*G107&lt;0,ABS(F107)+ABS(G107),G107-F107+1)</f>
+        <v>2</v>
+      </c>
+      <c r="I107">
+        <f t="shared" ref="I107" si="115">E107/H107</f>
+        <v>9.5</v>
       </c>
     </row>
   </sheetData>
@@ -10204,24 +10247,27 @@
       <c r="A107">
         <v>817</v>
       </c>
-      <c r="B107" t="e">
+      <c r="B107" t="str">
         <f>VLOOKUP($A107,統計!$A:$G,2,)</f>
-        <v>#N/A</v>
+        <v>卷106</v>
       </c>
       <c r="C107" t="s">
         <v>302</v>
       </c>
-      <c r="D107" t="e">
+      <c r="D107">
         <f>VLOOKUP($A107,統計!$A:$G,6,)</f>
-        <v>#N/A</v>
-      </c>
-      <c r="E107" t="e">
+        <v>385</v>
+      </c>
+      <c r="E107">
         <f>VLOOKUP($A107,統計!$A:$G,7,)</f>
-        <v>#N/A</v>
-      </c>
-      <c r="I107" t="e">
+        <v>386</v>
+      </c>
+      <c r="H107" t="s">
+        <v>540</v>
+      </c>
+      <c r="I107" t="str">
         <f t="shared" si="1"/>
-        <v>#N/A</v>
+        <v>817|[卷106](5_筆記/资治通鉴106.html)|晉紀二十八|385|386|||晉孝武帝14年至15年</v>
       </c>
     </row>
     <row r="108" spans="1:9" x14ac:dyDescent="0.25">

--- a/5_筆記/閱讀數據.xlsx
+++ b/5_筆記/閱讀數據.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="27029"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="27126"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\self\study\zizhitongjian\5_筆記\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7414385B-5CF1-4C2F-82F6-E3CBCC9CCAF0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3E87F890-2933-4E7E-A6AD-9F798C74CC70}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="38620" windowHeight="21220" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="547" uniqueCount="541">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="548" uniqueCount="542">
   <si>
     <t>索引號</t>
   </si>
@@ -1670,6 +1670,9 @@
   </si>
   <si>
     <t>晉孝武帝14年至15年</t>
+  </si>
+  <si>
+    <t>晉孝武帝16年至20年</t>
   </si>
 </sst>
 </file>
@@ -1973,7 +1976,7 @@
             <c:strRef>
               <c:f>統計!$B$2:$B$115</c:f>
               <c:strCache>
-                <c:ptCount val="106"/>
+                <c:ptCount val="107"/>
                 <c:pt idx="0">
                   <c:v>卷1</c:v>
                 </c:pt>
@@ -2291,6 +2294,9 @@
                 </c:pt>
                 <c:pt idx="105">
                   <c:v>卷106</c:v>
+                </c:pt>
+                <c:pt idx="106">
+                  <c:v>卷107</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
@@ -2618,6 +2624,9 @@
                 </c:pt>
                 <c:pt idx="105">
                   <c:v>9.5</c:v>
+                </c:pt>
+                <c:pt idx="106">
+                  <c:v>2.6</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -3172,7 +3181,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:R107"/>
+  <dimension ref="A1:R108"/>
   <sheetFormatPr defaultColWidth="8.6328125" defaultRowHeight="14" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="7.7265625" customWidth="1"/>
@@ -3287,19 +3296,19 @@
       </c>
       <c r="O2">
         <f t="shared" ref="O2:O8" si="5">L2*$L$10</f>
-        <v>707.58490566037733</v>
+        <v>709.23364485981313</v>
       </c>
       <c r="P2" s="1">
         <f t="shared" ref="P2:P8" si="6">$C$2+O2</f>
-        <v>44726.584905660377</v>
+        <v>44728.233644859814</v>
       </c>
       <c r="Q2">
         <f t="shared" ref="Q2:Q8" si="7">(M2-$F$2)*$L$11</f>
-        <v>900.88547956958951</v>
+        <v>894.92047367096529</v>
       </c>
       <c r="R2" s="1">
         <f t="shared" ref="R2:R8" si="8">$C$2+Q2</f>
-        <v>44919.885479569588</v>
+        <v>44913.920473670965</v>
       </c>
     </row>
     <row r="3" spans="1:18" x14ac:dyDescent="0.25">
@@ -3350,19 +3359,19 @@
       </c>
       <c r="O3">
         <f t="shared" si="5"/>
-        <v>811.64150943396226</v>
+        <v>813.53271028037386</v>
       </c>
       <c r="P3" s="1">
         <f t="shared" si="6"/>
-        <v>44830.641509433961</v>
+        <v>44832.532710280371</v>
       </c>
       <c r="Q3">
         <f t="shared" si="7"/>
-        <v>987.64812607709416</v>
+        <v>981.10864127972604</v>
       </c>
       <c r="R3" s="1">
         <f t="shared" si="8"/>
-        <v>45006.648126077096</v>
+        <v>45000.108641279723</v>
       </c>
     </row>
     <row r="4" spans="1:18" x14ac:dyDescent="0.25">
@@ -3413,19 +3422,19 @@
       </c>
       <c r="O4">
         <f t="shared" si="5"/>
-        <v>1227.867924528302</v>
+        <v>1230.7289719626169</v>
       </c>
       <c r="P4" s="1">
         <f t="shared" si="6"/>
-        <v>45246.867924528298</v>
+        <v>45249.728971962613</v>
       </c>
       <c r="Q4">
         <f t="shared" si="7"/>
-        <v>1190.0943012612715</v>
+        <v>1182.2143657001677</v>
       </c>
       <c r="R4" s="1">
         <f t="shared" si="8"/>
-        <v>45209.09430126127</v>
+        <v>45201.214365700165</v>
       </c>
     </row>
     <row r="5" spans="1:18" x14ac:dyDescent="0.25">
@@ -3476,19 +3485,19 @@
       </c>
       <c r="O5">
         <f t="shared" si="5"/>
-        <v>1831.3962264150944</v>
+        <v>1835.6635514018692</v>
       </c>
       <c r="P5" s="1">
         <f t="shared" si="6"/>
-        <v>45850.396226415098</v>
+        <v>45854.663551401871</v>
       </c>
       <c r="Q5">
         <f t="shared" si="7"/>
-        <v>1434.4757555907429</v>
+        <v>1424.9777044648436</v>
       </c>
       <c r="R5" s="1">
         <f t="shared" si="8"/>
-        <v>45453.475755590742</v>
+        <v>45443.977704464844</v>
       </c>
     </row>
     <row r="6" spans="1:18" x14ac:dyDescent="0.25">
@@ -3539,19 +3548,19 @@
       </c>
       <c r="O6">
         <f t="shared" si="5"/>
-        <v>2757.5</v>
+        <v>2763.9252336448599</v>
       </c>
       <c r="P6" s="1">
         <f t="shared" si="6"/>
-        <v>46776.5</v>
+        <v>46782.925233644863</v>
       </c>
       <c r="Q6">
         <f t="shared" si="7"/>
-        <v>1894.3177820805172</v>
+        <v>1881.7749927912753</v>
       </c>
       <c r="R6" s="1">
         <f t="shared" si="8"/>
-        <v>45913.317782080514</v>
+        <v>45900.774992791274</v>
       </c>
     </row>
     <row r="7" spans="1:18" x14ac:dyDescent="0.25">
@@ -3602,19 +3611,19 @@
       </c>
       <c r="O7">
         <f t="shared" si="5"/>
-        <v>3059.2641509433961</v>
+        <v>3066.3925233644864</v>
       </c>
       <c r="P7" s="1">
         <f t="shared" si="6"/>
-        <v>47078.264150943396</v>
+        <v>47085.392523364484</v>
       </c>
       <c r="Q7">
         <f t="shared" si="7"/>
-        <v>1969.5120757203547</v>
+        <v>1956.4714047188679</v>
       </c>
       <c r="R7" s="1">
         <f t="shared" si="8"/>
-        <v>45988.512075720355</v>
+        <v>45975.471404718868</v>
       </c>
     </row>
     <row r="8" spans="1:18" x14ac:dyDescent="0.25">
@@ -3665,19 +3674,19 @@
       </c>
       <c r="O8">
         <f t="shared" si="5"/>
-        <v>3059.2641509433961</v>
+        <v>3066.3925233644864</v>
       </c>
       <c r="P8" s="1">
         <f t="shared" si="6"/>
-        <v>47078.264150943396</v>
+        <v>47085.392523364484</v>
       </c>
       <c r="Q8">
         <f t="shared" si="7"/>
-        <v>1969.5120757203547</v>
+        <v>1956.4714047188679</v>
       </c>
       <c r="R8" s="1">
         <f t="shared" si="8"/>
-        <v>45988.512075720355</v>
+        <v>45975.471404718868</v>
       </c>
     </row>
     <row r="9" spans="1:18" x14ac:dyDescent="0.25">
@@ -3752,7 +3761,7 @@
       </c>
       <c r="L10">
         <f>AVERAGE(E:E)</f>
-        <v>10.40566037735849</v>
+        <v>10.429906542056075</v>
       </c>
     </row>
     <row r="11" spans="1:18" x14ac:dyDescent="0.25">
@@ -3793,7 +3802,7 @@
       </c>
       <c r="L11">
         <f>AVEDEV(I:I)</f>
-        <v>1.4460441084584101</v>
+        <v>1.4364694601460117</v>
       </c>
     </row>
     <row r="12" spans="1:18" x14ac:dyDescent="0.25">
@@ -5656,7 +5665,7 @@
         <v>526</v>
       </c>
       <c r="B66" t="str">
-        <f t="shared" ref="B66:B107" si="16">"卷"&amp;ROW(B65)</f>
+        <f t="shared" ref="B66:B108" si="16">"卷"&amp;ROW(B65)</f>
         <v>卷65</v>
       </c>
       <c r="C66" s="1">
@@ -7104,6 +7113,41 @@
       <c r="I107">
         <f t="shared" ref="I107" si="115">E107/H107</f>
         <v>9.5</v>
+      </c>
+    </row>
+    <row r="108" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A108">
+        <v>818</v>
+      </c>
+      <c r="B108" t="str">
+        <f t="shared" si="16"/>
+        <v>卷107</v>
+      </c>
+      <c r="C108" s="1">
+        <f>D107+1</f>
+        <v>45298</v>
+      </c>
+      <c r="D108" s="1">
+        <v>45310</v>
+      </c>
+      <c r="E108">
+        <f t="shared" ref="E108" si="116">D108-C108+1</f>
+        <v>13</v>
+      </c>
+      <c r="F108">
+        <f t="shared" ref="F108" si="117">G107+1</f>
+        <v>387</v>
+      </c>
+      <c r="G108">
+        <v>391</v>
+      </c>
+      <c r="H108">
+        <f t="shared" ref="H108" si="118">IF(F108*G108&lt;0,ABS(F108)+ABS(G108),G108-F108+1)</f>
+        <v>5</v>
+      </c>
+      <c r="I108">
+        <f t="shared" ref="I108" si="119">E108/H108</f>
+        <v>2.6</v>
       </c>
     </row>
   </sheetData>
@@ -10274,24 +10318,27 @@
       <c r="A108">
         <v>818</v>
       </c>
-      <c r="B108" t="e">
+      <c r="B108" t="str">
         <f>VLOOKUP($A108,統計!$A:$G,2,)</f>
-        <v>#N/A</v>
+        <v>卷107</v>
       </c>
       <c r="C108" t="s">
         <v>303</v>
       </c>
-      <c r="D108" t="e">
+      <c r="D108">
         <f>VLOOKUP($A108,統計!$A:$G,6,)</f>
-        <v>#N/A</v>
-      </c>
-      <c r="E108" t="e">
+        <v>387</v>
+      </c>
+      <c r="E108">
         <f>VLOOKUP($A108,統計!$A:$G,7,)</f>
-        <v>#N/A</v>
-      </c>
-      <c r="I108" t="e">
+        <v>391</v>
+      </c>
+      <c r="H108" t="s">
+        <v>541</v>
+      </c>
+      <c r="I108" t="str">
         <f t="shared" si="1"/>
-        <v>#N/A</v>
+        <v>818|[卷107](5_筆記/资治通鉴107.html)|晉紀二十九|387|391|||晉孝武帝16年至20年</v>
       </c>
     </row>
     <row r="109" spans="1:9" x14ac:dyDescent="0.25">

--- a/5_筆記/閱讀數據.xlsx
+++ b/5_筆記/閱讀數據.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\self\study\zizhitongjian\5_筆記\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3E87F890-2933-4E7E-A6AD-9F798C74CC70}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3FBC4EB7-5352-4AE3-99B2-E4B28475C434}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="38620" windowHeight="21220" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="548" uniqueCount="542">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="550" uniqueCount="544">
   <si>
     <t>索引號</t>
   </si>
@@ -1673,6 +1673,13 @@
   </si>
   <si>
     <t>晉孝武帝16年至20年</t>
+  </si>
+  <si>
+    <t>慕容段氏婚姻表</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>晉孝武帝21年至25年、晉安帝元年</t>
   </si>
 </sst>
 </file>
@@ -1976,7 +1983,7 @@
             <c:strRef>
               <c:f>統計!$B$2:$B$115</c:f>
               <c:strCache>
-                <c:ptCount val="107"/>
+                <c:ptCount val="108"/>
                 <c:pt idx="0">
                   <c:v>卷1</c:v>
                 </c:pt>
@@ -2297,6 +2304,9 @@
                 </c:pt>
                 <c:pt idx="106">
                   <c:v>卷107</c:v>
+                </c:pt>
+                <c:pt idx="107">
+                  <c:v>卷108</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
@@ -2626,6 +2636,9 @@
                   <c:v>9.5</c:v>
                 </c:pt>
                 <c:pt idx="106">
+                  <c:v>2.6</c:v>
+                </c:pt>
+                <c:pt idx="107">
                   <c:v>2.6</c:v>
                 </c:pt>
               </c:numCache>
@@ -3181,7 +3194,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:R108"/>
+  <dimension ref="A1:R109"/>
   <sheetFormatPr defaultColWidth="8.6328125" defaultRowHeight="14" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="7.7265625" customWidth="1"/>
@@ -3296,19 +3309,19 @@
       </c>
       <c r="O2">
         <f t="shared" ref="O2:O8" si="5">L2*$L$10</f>
-        <v>709.23364485981313</v>
+        <v>710.85185185185185</v>
       </c>
       <c r="P2" s="1">
         <f t="shared" ref="P2:P8" si="6">$C$2+O2</f>
-        <v>44728.233644859814</v>
+        <v>44729.851851851854</v>
       </c>
       <c r="Q2">
         <f t="shared" ref="Q2:Q8" si="7">(M2-$F$2)*$L$11</f>
-        <v>894.92047367096529</v>
+        <v>889.02089829165448</v>
       </c>
       <c r="R2" s="1">
         <f t="shared" ref="R2:R8" si="8">$C$2+Q2</f>
-        <v>44913.920473670965</v>
+        <v>44908.020898291652</v>
       </c>
     </row>
     <row r="3" spans="1:18" x14ac:dyDescent="0.25">
@@ -3359,19 +3372,19 @@
       </c>
       <c r="O3">
         <f t="shared" si="5"/>
-        <v>813.53271028037386</v>
+        <v>815.38888888888891</v>
       </c>
       <c r="P3" s="1">
         <f t="shared" si="6"/>
-        <v>44832.532710280371</v>
+        <v>44834.388888888891</v>
       </c>
       <c r="Q3">
         <f t="shared" si="7"/>
-        <v>981.10864127972604</v>
+        <v>974.64088849630821</v>
       </c>
       <c r="R3" s="1">
         <f t="shared" si="8"/>
-        <v>45000.108641279723</v>
+        <v>44993.640888496309</v>
       </c>
     </row>
     <row r="4" spans="1:18" x14ac:dyDescent="0.25">
@@ -3422,19 +3435,19 @@
       </c>
       <c r="O4">
         <f t="shared" si="5"/>
-        <v>1230.7289719626169</v>
+        <v>1233.5370370370372</v>
       </c>
       <c r="P4" s="1">
         <f t="shared" si="6"/>
-        <v>45249.728971962613</v>
+        <v>45252.537037037036</v>
       </c>
       <c r="Q4">
         <f t="shared" si="7"/>
-        <v>1182.2143657001677</v>
+        <v>1174.4208656405003</v>
       </c>
       <c r="R4" s="1">
         <f t="shared" si="8"/>
-        <v>45201.214365700165</v>
+        <v>45193.420865640503</v>
       </c>
     </row>
     <row r="5" spans="1:18" x14ac:dyDescent="0.25">
@@ -3485,19 +3498,19 @@
       </c>
       <c r="O5">
         <f t="shared" si="5"/>
-        <v>1835.6635514018692</v>
+        <v>1839.851851851852</v>
       </c>
       <c r="P5" s="1">
         <f t="shared" si="6"/>
-        <v>45854.663551401871</v>
+        <v>45858.851851851854</v>
       </c>
       <c r="Q5">
         <f t="shared" si="7"/>
-        <v>1424.9777044648436</v>
+        <v>1415.5838380502748</v>
       </c>
       <c r="R5" s="1">
         <f t="shared" si="8"/>
-        <v>45443.977704464844</v>
+        <v>45434.583838050276</v>
       </c>
     </row>
     <row r="6" spans="1:18" x14ac:dyDescent="0.25">
@@ -3548,19 +3561,19 @@
       </c>
       <c r="O6">
         <f t="shared" si="5"/>
-        <v>2763.9252336448599</v>
+        <v>2770.2314814814818</v>
       </c>
       <c r="P6" s="1">
         <f t="shared" si="6"/>
-        <v>46782.925233644863</v>
+        <v>46789.231481481482</v>
       </c>
       <c r="Q6">
         <f t="shared" si="7"/>
-        <v>1881.7749927912753</v>
+        <v>1869.3697861349397</v>
       </c>
       <c r="R6" s="1">
         <f t="shared" si="8"/>
-        <v>45900.774992791274</v>
+        <v>45888.369786134943</v>
       </c>
     </row>
     <row r="7" spans="1:18" x14ac:dyDescent="0.25">
@@ -3611,19 +3624,19 @@
       </c>
       <c r="O7">
         <f t="shared" si="5"/>
-        <v>3066.3925233644864</v>
+        <v>3073.3888888888891</v>
       </c>
       <c r="P7" s="1">
         <f t="shared" si="6"/>
-        <v>47085.392523364484</v>
+        <v>47092.388888888891</v>
       </c>
       <c r="Q7">
         <f t="shared" si="7"/>
-        <v>1956.4714047188679</v>
+        <v>1943.5737776456394</v>
       </c>
       <c r="R7" s="1">
         <f t="shared" si="8"/>
-        <v>45975.471404718868</v>
+        <v>45962.573777645637</v>
       </c>
     </row>
     <row r="8" spans="1:18" x14ac:dyDescent="0.25">
@@ -3674,19 +3687,19 @@
       </c>
       <c r="O8">
         <f t="shared" si="5"/>
-        <v>3066.3925233644864</v>
+        <v>3073.3888888888891</v>
       </c>
       <c r="P8" s="1">
         <f t="shared" si="6"/>
-        <v>47085.392523364484</v>
+        <v>47092.388888888891</v>
       </c>
       <c r="Q8">
         <f t="shared" si="7"/>
-        <v>1956.4714047188679</v>
+        <v>1943.5737776456394</v>
       </c>
       <c r="R8" s="1">
         <f t="shared" si="8"/>
-        <v>45975.471404718868</v>
+        <v>45962.573777645637</v>
       </c>
     </row>
     <row r="9" spans="1:18" x14ac:dyDescent="0.25">
@@ -3761,7 +3774,7 @@
       </c>
       <c r="L10">
         <f>AVERAGE(E:E)</f>
-        <v>10.429906542056075</v>
+        <v>10.453703703703704</v>
       </c>
     </row>
     <row r="11" spans="1:18" x14ac:dyDescent="0.25">
@@ -3802,7 +3815,7 @@
       </c>
       <c r="L11">
         <f>AVEDEV(I:I)</f>
-        <v>1.4364694601460117</v>
+        <v>1.4269998367442287</v>
       </c>
     </row>
     <row r="12" spans="1:18" x14ac:dyDescent="0.25">
@@ -5665,7 +5678,7 @@
         <v>526</v>
       </c>
       <c r="B66" t="str">
-        <f t="shared" ref="B66:B108" si="16">"卷"&amp;ROW(B65)</f>
+        <f t="shared" ref="B66:B109" si="16">"卷"&amp;ROW(B65)</f>
         <v>卷65</v>
       </c>
       <c r="C66" s="1">
@@ -7147,6 +7160,41 @@
       </c>
       <c r="I108">
         <f t="shared" ref="I108" si="119">E108/H108</f>
+        <v>2.6</v>
+      </c>
+    </row>
+    <row r="109" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A109">
+        <v>819</v>
+      </c>
+      <c r="B109" t="str">
+        <f t="shared" si="16"/>
+        <v>卷108</v>
+      </c>
+      <c r="C109" s="1">
+        <f>D108+1</f>
+        <v>45311</v>
+      </c>
+      <c r="D109" s="1">
+        <v>45323</v>
+      </c>
+      <c r="E109">
+        <f t="shared" ref="E109" si="120">D109-C109+1</f>
+        <v>13</v>
+      </c>
+      <c r="F109">
+        <f t="shared" ref="F109" si="121">G108+1</f>
+        <v>392</v>
+      </c>
+      <c r="G109">
+        <v>396</v>
+      </c>
+      <c r="H109">
+        <f t="shared" ref="H109" si="122">IF(F109*G109&lt;0,ABS(F109)+ABS(G109),G109-F109+1)</f>
+        <v>5</v>
+      </c>
+      <c r="I109">
+        <f t="shared" ref="I109" si="123">E109/H109</f>
         <v>2.6</v>
       </c>
     </row>
@@ -10345,24 +10393,30 @@
       <c r="A109">
         <v>819</v>
       </c>
-      <c r="B109" t="e">
+      <c r="B109" t="str">
         <f>VLOOKUP($A109,統計!$A:$G,2,)</f>
-        <v>#N/A</v>
+        <v>卷108</v>
       </c>
       <c r="C109" t="s">
         <v>304</v>
       </c>
-      <c r="D109" t="e">
+      <c r="D109">
         <f>VLOOKUP($A109,統計!$A:$G,6,)</f>
-        <v>#N/A</v>
-      </c>
-      <c r="E109" t="e">
+        <v>392</v>
+      </c>
+      <c r="E109">
         <f>VLOOKUP($A109,統計!$A:$G,7,)</f>
-        <v>#N/A</v>
-      </c>
-      <c r="I109" t="e">
+        <v>396</v>
+      </c>
+      <c r="G109" t="s">
+        <v>542</v>
+      </c>
+      <c r="H109" t="s">
+        <v>543</v>
+      </c>
+      <c r="I109" t="str">
         <f t="shared" si="1"/>
-        <v>#N/A</v>
+        <v>819|[卷108](5_筆記/资治通鉴108.html)|晉紀三十|392|396||慕容段氏婚姻表|晉孝武帝21年至25年、晉安帝元年</v>
       </c>
     </row>
     <row r="110" spans="1:9" x14ac:dyDescent="0.25">

--- a/5_筆記/閱讀數據.xlsx
+++ b/5_筆記/閱讀數據.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="27126"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="27231"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\self\study\zizhitongjian\5_筆記\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3FBC4EB7-5352-4AE3-99B2-E4B28475C434}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{58EEA477-C551-4FF2-9642-C6D66FE631FA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="38620" windowHeight="21220" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="480" yWindow="9100" windowWidth="25600" windowHeight="11470" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="統計" sheetId="1" r:id="rId1"/>
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="550" uniqueCount="544">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="552" uniqueCount="546">
   <si>
     <t>索引號</t>
   </si>
@@ -1680,6 +1680,14 @@
   </si>
   <si>
     <t>晉孝武帝21年至25年、晉安帝元年</t>
+  </si>
+  <si>
+    <t>晉安帝2年</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>晉安帝3年</t>
+    <phoneticPr fontId="4" type="noConversion"/>
   </si>
 </sst>
 </file>
@@ -1983,7 +1991,7 @@
             <c:strRef>
               <c:f>統計!$B$2:$B$115</c:f>
               <c:strCache>
-                <c:ptCount val="108"/>
+                <c:ptCount val="110"/>
                 <c:pt idx="0">
                   <c:v>卷1</c:v>
                 </c:pt>
@@ -2307,6 +2315,12 @@
                 </c:pt>
                 <c:pt idx="107">
                   <c:v>卷108</c:v>
+                </c:pt>
+                <c:pt idx="108">
+                  <c:v>卷109</c:v>
+                </c:pt>
+                <c:pt idx="109">
+                  <c:v>卷110</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
@@ -2640,6 +2654,12 @@
                 </c:pt>
                 <c:pt idx="107">
                   <c:v>2.6</c:v>
+                </c:pt>
+                <c:pt idx="108">
+                  <c:v>11</c:v>
+                </c:pt>
+                <c:pt idx="109">
+                  <c:v>3</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -3194,7 +3214,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:R109"/>
+  <dimension ref="A1:R111"/>
   <sheetFormatPr defaultColWidth="8.6328125" defaultRowHeight="14" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="7.7265625" customWidth="1"/>
@@ -3309,19 +3329,19 @@
       </c>
       <c r="O2">
         <f t="shared" ref="O2:O8" si="5">L2*$L$10</f>
-        <v>710.85185185185185</v>
+        <v>706.58181818181811</v>
       </c>
       <c r="P2" s="1">
         <f t="shared" ref="P2:P8" si="6">$C$2+O2</f>
-        <v>44729.851851851854</v>
+        <v>44725.581818181818</v>
       </c>
       <c r="Q2">
         <f t="shared" ref="Q2:Q8" si="7">(M2-$F$2)*$L$11</f>
-        <v>889.02089829165448</v>
+        <v>935.1598241774625</v>
       </c>
       <c r="R2" s="1">
         <f t="shared" ref="R2:R8" si="8">$C$2+Q2</f>
-        <v>44908.020898291652</v>
+        <v>44954.159824177463</v>
       </c>
     </row>
     <row r="3" spans="1:18" x14ac:dyDescent="0.25">
@@ -3372,19 +3392,19 @@
       </c>
       <c r="O3">
         <f t="shared" si="5"/>
-        <v>815.38888888888891</v>
+        <v>810.4909090909091</v>
       </c>
       <c r="P3" s="1">
         <f t="shared" si="6"/>
-        <v>44834.388888888891</v>
+        <v>44829.490909090906</v>
       </c>
       <c r="Q3">
         <f t="shared" si="7"/>
-        <v>974.64088849630821</v>
+        <v>1025.223370647202</v>
       </c>
       <c r="R3" s="1">
         <f t="shared" si="8"/>
-        <v>44993.640888496309</v>
+        <v>45044.223370647203</v>
       </c>
     </row>
     <row r="4" spans="1:18" x14ac:dyDescent="0.25">
@@ -3435,19 +3455,19 @@
       </c>
       <c r="O4">
         <f t="shared" si="5"/>
-        <v>1233.5370370370372</v>
+        <v>1226.1272727272726</v>
       </c>
       <c r="P4" s="1">
         <f t="shared" si="6"/>
-        <v>45252.537037037036</v>
+        <v>45245.127272727274</v>
       </c>
       <c r="Q4">
         <f t="shared" si="7"/>
-        <v>1174.4208656405003</v>
+        <v>1235.3716457432611</v>
       </c>
       <c r="R4" s="1">
         <f t="shared" si="8"/>
-        <v>45193.420865640503</v>
+        <v>45254.37164574326</v>
       </c>
     </row>
     <row r="5" spans="1:18" x14ac:dyDescent="0.25">
@@ -3498,19 +3518,19 @@
       </c>
       <c r="O5">
         <f t="shared" si="5"/>
-        <v>1839.851851851852</v>
+        <v>1828.8</v>
       </c>
       <c r="P5" s="1">
         <f t="shared" si="6"/>
-        <v>45858.851851851854</v>
+        <v>45847.8</v>
       </c>
       <c r="Q5">
         <f t="shared" si="7"/>
-        <v>1415.5838380502748</v>
+        <v>1489.0506349663608</v>
       </c>
       <c r="R5" s="1">
         <f t="shared" si="8"/>
-        <v>45434.583838050276</v>
+        <v>45508.050634966363</v>
       </c>
     </row>
     <row r="6" spans="1:18" x14ac:dyDescent="0.25">
@@ -3561,19 +3581,19 @@
       </c>
       <c r="O6">
         <f t="shared" si="5"/>
-        <v>2770.2314814814818</v>
+        <v>2753.590909090909</v>
       </c>
       <c r="P6" s="1">
         <f t="shared" si="6"/>
-        <v>46789.231481481482</v>
+        <v>46772.590909090912</v>
       </c>
       <c r="Q6">
         <f t="shared" si="7"/>
-        <v>1869.3697861349397</v>
+        <v>1966.3874312559806</v>
       </c>
       <c r="R6" s="1">
         <f t="shared" si="8"/>
-        <v>45888.369786134943</v>
+        <v>45985.387431255978</v>
       </c>
     </row>
     <row r="7" spans="1:18" x14ac:dyDescent="0.25">
@@ -3624,19 +3644,19 @@
       </c>
       <c r="O7">
         <f t="shared" si="5"/>
-        <v>3073.3888888888891</v>
+        <v>3054.9272727272728</v>
       </c>
       <c r="P7" s="1">
         <f t="shared" si="6"/>
-        <v>47092.388888888891</v>
+        <v>47073.927272727276</v>
       </c>
       <c r="Q7">
         <f t="shared" si="7"/>
-        <v>1943.5737776456394</v>
+        <v>2044.4425048630881</v>
       </c>
       <c r="R7" s="1">
         <f t="shared" si="8"/>
-        <v>45962.573777645637</v>
+        <v>46063.442504863087</v>
       </c>
     </row>
     <row r="8" spans="1:18" x14ac:dyDescent="0.25">
@@ -3687,19 +3707,19 @@
       </c>
       <c r="O8">
         <f t="shared" si="5"/>
-        <v>3073.3888888888891</v>
+        <v>3054.9272727272728</v>
       </c>
       <c r="P8" s="1">
         <f t="shared" si="6"/>
-        <v>47092.388888888891</v>
+        <v>47073.927272727276</v>
       </c>
       <c r="Q8">
         <f t="shared" si="7"/>
-        <v>1943.5737776456394</v>
+        <v>2044.4425048630881</v>
       </c>
       <c r="R8" s="1">
         <f t="shared" si="8"/>
-        <v>45962.573777645637</v>
+        <v>46063.442504863087</v>
       </c>
     </row>
     <row r="9" spans="1:18" x14ac:dyDescent="0.25">
@@ -3774,7 +3794,7 @@
       </c>
       <c r="L10">
         <f>AVERAGE(E:E)</f>
-        <v>10.453703703703704</v>
+        <v>10.390909090909091</v>
       </c>
     </row>
     <row r="11" spans="1:18" x14ac:dyDescent="0.25">
@@ -3815,7 +3835,7 @@
       </c>
       <c r="L11">
         <f>AVEDEV(I:I)</f>
-        <v>1.4269998367442287</v>
+        <v>1.5010591078289928</v>
       </c>
     </row>
     <row r="12" spans="1:18" x14ac:dyDescent="0.25">
@@ -5678,7 +5698,7 @@
         <v>526</v>
       </c>
       <c r="B66" t="str">
-        <f t="shared" ref="B66:B109" si="16">"卷"&amp;ROW(B65)</f>
+        <f t="shared" ref="B66:B111" si="16">"卷"&amp;ROW(B65)</f>
         <v>卷65</v>
       </c>
       <c r="C66" s="1">
@@ -7196,6 +7216,75 @@
       <c r="I109">
         <f t="shared" ref="I109" si="123">E109/H109</f>
         <v>2.6</v>
+      </c>
+    </row>
+    <row r="110" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A110">
+        <v>820</v>
+      </c>
+      <c r="B110" t="str">
+        <f t="shared" si="16"/>
+        <v>卷109</v>
+      </c>
+      <c r="C110" s="1">
+        <f>D109+1</f>
+        <v>45324</v>
+      </c>
+      <c r="D110" s="1">
+        <v>45334</v>
+      </c>
+      <c r="E110">
+        <f t="shared" ref="E110" si="124">D110-C110+1</f>
+        <v>11</v>
+      </c>
+      <c r="F110">
+        <f t="shared" ref="F110" si="125">G109+1</f>
+        <v>397</v>
+      </c>
+      <c r="G110">
+        <v>397</v>
+      </c>
+      <c r="H110">
+        <f t="shared" ref="H110" si="126">IF(F110*G110&lt;0,ABS(F110)+ABS(G110),G110-F110+1)</f>
+        <v>1</v>
+      </c>
+      <c r="I110">
+        <f t="shared" ref="I110" si="127">E110/H110</f>
+        <v>11</v>
+      </c>
+    </row>
+    <row r="111" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A111">
+        <v>821</v>
+      </c>
+      <c r="B111" t="str">
+        <f t="shared" si="16"/>
+        <v>卷110</v>
+      </c>
+      <c r="C111" s="1">
+        <v>45346</v>
+      </c>
+      <c r="D111" s="1">
+        <v>45348</v>
+      </c>
+      <c r="E111">
+        <f t="shared" ref="E111" si="128">D111-C111+1</f>
+        <v>3</v>
+      </c>
+      <c r="F111">
+        <f t="shared" ref="F111" si="129">G110+1</f>
+        <v>398</v>
+      </c>
+      <c r="G111">
+        <v>398</v>
+      </c>
+      <c r="H111">
+        <f t="shared" ref="H111" si="130">IF(F111*G111&lt;0,ABS(F111)+ABS(G111),G111-F111+1)</f>
+        <v>1</v>
+      </c>
+      <c r="I111">
+        <f t="shared" ref="I111" si="131">E111/H111</f>
+        <v>3</v>
       </c>
     </row>
   </sheetData>
@@ -10423,48 +10512,54 @@
       <c r="A110">
         <v>820</v>
       </c>
-      <c r="B110" t="e">
+      <c r="B110" t="str">
         <f>VLOOKUP($A110,統計!$A:$G,2,)</f>
-        <v>#N/A</v>
+        <v>卷109</v>
       </c>
       <c r="C110" t="s">
         <v>305</v>
       </c>
-      <c r="D110" t="e">
+      <c r="D110">
         <f>VLOOKUP($A110,統計!$A:$G,6,)</f>
-        <v>#N/A</v>
-      </c>
-      <c r="E110" t="e">
+        <v>397</v>
+      </c>
+      <c r="E110">
         <f>VLOOKUP($A110,統計!$A:$G,7,)</f>
-        <v>#N/A</v>
-      </c>
-      <c r="I110" t="e">
+        <v>397</v>
+      </c>
+      <c r="H110" t="s">
+        <v>544</v>
+      </c>
+      <c r="I110" t="str">
         <f t="shared" si="1"/>
-        <v>#N/A</v>
+        <v>820|[卷109](5_筆記/资治通鉴109.html)|晉紀三十一|397|397|||晉安帝2年</v>
       </c>
     </row>
     <row r="111" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A111">
         <v>821</v>
       </c>
-      <c r="B111" t="e">
+      <c r="B111" t="str">
         <f>VLOOKUP($A111,統計!$A:$G,2,)</f>
-        <v>#N/A</v>
+        <v>卷110</v>
       </c>
       <c r="C111" t="s">
         <v>306</v>
       </c>
-      <c r="D111" t="e">
+      <c r="D111">
         <f>VLOOKUP($A111,統計!$A:$G,6,)</f>
-        <v>#N/A</v>
-      </c>
-      <c r="E111" t="e">
+        <v>398</v>
+      </c>
+      <c r="E111">
         <f>VLOOKUP($A111,統計!$A:$G,7,)</f>
-        <v>#N/A</v>
-      </c>
-      <c r="I111" t="e">
+        <v>398</v>
+      </c>
+      <c r="H111" t="s">
+        <v>545</v>
+      </c>
+      <c r="I111" t="str">
         <f t="shared" si="1"/>
-        <v>#N/A</v>
+        <v>821|[卷110](5_筆記/资治通鉴110.html)|晉紀三十二|398|398|||晉安帝3年</v>
       </c>
     </row>
     <row r="112" spans="1:9" x14ac:dyDescent="0.25">

--- a/5_筆記/閱讀數據.xlsx
+++ b/5_筆記/閱讀數據.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\self\study\zizhitongjian\5_筆記\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{58EEA477-C551-4FF2-9642-C6D66FE631FA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E20E4BDB-789F-4D0C-9A61-D4EE9DCA7BAF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="480" yWindow="9100" windowWidth="25600" windowHeight="11470" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="480" yWindow="9100" windowWidth="25600" windowHeight="11470" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="統計" sheetId="1" r:id="rId1"/>
@@ -2659,7 +2659,7 @@
                   <c:v>11</c:v>
                 </c:pt>
                 <c:pt idx="109">
-                  <c:v>3</c:v>
+                  <c:v>7</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -3329,19 +3329,19 @@
       </c>
       <c r="O2">
         <f t="shared" ref="O2:O8" si="5">L2*$L$10</f>
-        <v>706.58181818181811</v>
+        <v>709.05454545454552</v>
       </c>
       <c r="P2" s="1">
         <f t="shared" ref="P2:P8" si="6">$C$2+O2</f>
-        <v>44725.581818181818</v>
+        <v>44728.054545454543</v>
       </c>
       <c r="Q2">
         <f t="shared" ref="Q2:Q8" si="7">(M2-$F$2)*$L$11</f>
-        <v>935.1598241774625</v>
+        <v>963.58098120225611</v>
       </c>
       <c r="R2" s="1">
         <f t="shared" ref="R2:R8" si="8">$C$2+Q2</f>
-        <v>44954.159824177463</v>
+        <v>44982.580981202256</v>
       </c>
     </row>
     <row r="3" spans="1:18" x14ac:dyDescent="0.25">
@@ -3392,19 +3392,19 @@
       </c>
       <c r="O3">
         <f t="shared" si="5"/>
-        <v>810.4909090909091</v>
+        <v>813.32727272727277</v>
       </c>
       <c r="P3" s="1">
         <f t="shared" si="6"/>
-        <v>44829.490909090906</v>
+        <v>44832.327272727271</v>
       </c>
       <c r="Q3">
         <f t="shared" si="7"/>
-        <v>1025.223370647202</v>
+        <v>1056.3817177546402</v>
       </c>
       <c r="R3" s="1">
         <f t="shared" si="8"/>
-        <v>45044.223370647203</v>
+        <v>45075.381717754637</v>
       </c>
     </row>
     <row r="4" spans="1:18" x14ac:dyDescent="0.25">
@@ -3455,19 +3455,19 @@
       </c>
       <c r="O4">
         <f t="shared" si="5"/>
-        <v>1226.1272727272726</v>
+        <v>1230.4181818181819</v>
       </c>
       <c r="P4" s="1">
         <f t="shared" si="6"/>
-        <v>45245.127272727274</v>
+        <v>45249.418181818182</v>
       </c>
       <c r="Q4">
         <f t="shared" si="7"/>
-        <v>1235.3716457432611</v>
+        <v>1272.9167697102034</v>
       </c>
       <c r="R4" s="1">
         <f t="shared" si="8"/>
-        <v>45254.37164574326</v>
+        <v>45291.916769710202</v>
       </c>
     </row>
     <row r="5" spans="1:18" x14ac:dyDescent="0.25">
@@ -3518,19 +3518,19 @@
       </c>
       <c r="O5">
         <f t="shared" si="5"/>
-        <v>1828.8</v>
+        <v>1835.2</v>
       </c>
       <c r="P5" s="1">
         <f t="shared" si="6"/>
-        <v>45847.8</v>
+        <v>45854.2</v>
       </c>
       <c r="Q5">
         <f t="shared" si="7"/>
-        <v>1489.0506349663608</v>
+        <v>1534.3055109994191</v>
       </c>
       <c r="R5" s="1">
         <f t="shared" si="8"/>
-        <v>45508.050634966363</v>
+        <v>45553.305510999417</v>
       </c>
     </row>
     <row r="6" spans="1:18" x14ac:dyDescent="0.25">
@@ -3581,19 +3581,19 @@
       </c>
       <c r="O6">
         <f t="shared" si="5"/>
-        <v>2753.590909090909</v>
+        <v>2763.227272727273</v>
       </c>
       <c r="P6" s="1">
         <f t="shared" si="6"/>
-        <v>46772.590909090912</v>
+        <v>46782.227272727272</v>
       </c>
       <c r="Q6">
         <f t="shared" si="7"/>
-        <v>1966.3874312559806</v>
+        <v>2026.1494147270553</v>
       </c>
       <c r="R6" s="1">
         <f t="shared" si="8"/>
-        <v>45985.387431255978</v>
+        <v>46045.149414727057</v>
       </c>
     </row>
     <row r="7" spans="1:18" x14ac:dyDescent="0.25">
@@ -3644,19 +3644,19 @@
       </c>
       <c r="O7">
         <f t="shared" si="5"/>
-        <v>3054.9272727272728</v>
+        <v>3065.6181818181822</v>
       </c>
       <c r="P7" s="1">
         <f t="shared" si="6"/>
-        <v>47073.927272727276</v>
+        <v>47084.618181818179</v>
       </c>
       <c r="Q7">
         <f t="shared" si="7"/>
-        <v>2044.4425048630881</v>
+        <v>2106.5767197391215</v>
       </c>
       <c r="R7" s="1">
         <f t="shared" si="8"/>
-        <v>46063.442504863087</v>
+        <v>46125.576719739125</v>
       </c>
     </row>
     <row r="8" spans="1:18" x14ac:dyDescent="0.25">
@@ -3707,19 +3707,19 @@
       </c>
       <c r="O8">
         <f t="shared" si="5"/>
-        <v>3054.9272727272728</v>
+        <v>3065.6181818181822</v>
       </c>
       <c r="P8" s="1">
         <f t="shared" si="6"/>
-        <v>47073.927272727276</v>
+        <v>47084.618181818179</v>
       </c>
       <c r="Q8">
         <f t="shared" si="7"/>
-        <v>2044.4425048630881</v>
+        <v>2106.5767197391215</v>
       </c>
       <c r="R8" s="1">
         <f t="shared" si="8"/>
-        <v>46063.442504863087</v>
+        <v>46125.576719739125</v>
       </c>
     </row>
     <row r="9" spans="1:18" x14ac:dyDescent="0.25">
@@ -3794,7 +3794,7 @@
       </c>
       <c r="L10">
         <f>AVERAGE(E:E)</f>
-        <v>10.390909090909091</v>
+        <v>10.427272727272728</v>
       </c>
     </row>
     <row r="11" spans="1:18" x14ac:dyDescent="0.25">
@@ -3835,7 +3835,7 @@
       </c>
       <c r="L11">
         <f>AVEDEV(I:I)</f>
-        <v>1.5010591078289928</v>
+        <v>1.5466789425397369</v>
       </c>
     </row>
     <row r="12" spans="1:18" x14ac:dyDescent="0.25">
@@ -7265,11 +7265,11 @@
         <v>45346</v>
       </c>
       <c r="D111" s="1">
-        <v>45348</v>
+        <v>45352</v>
       </c>
       <c r="E111">
         <f t="shared" ref="E111" si="128">D111-C111+1</f>
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="F111">
         <f t="shared" ref="F111" si="129">G110+1</f>
@@ -7284,7 +7284,7 @@
       </c>
       <c r="I111">
         <f t="shared" ref="I111" si="131">E111/H111</f>
-        <v>3</v>
+        <v>7</v>
       </c>
     </row>
   </sheetData>

--- a/5_筆記/閱讀數據.xlsx
+++ b/5_筆記/閱讀數據.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="27231"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="27328"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\self\study\zizhitongjian\5_筆記\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E20E4BDB-789F-4D0C-9A61-D4EE9DCA7BAF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FF761D4B-3C32-4EE2-ADB6-1CBE3314F53A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="480" yWindow="9100" windowWidth="25600" windowHeight="11470" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="38620" windowHeight="21220" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="統計" sheetId="1" r:id="rId1"/>
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="552" uniqueCount="546">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="553" uniqueCount="547">
   <si>
     <t>索引號</t>
   </si>
@@ -1687,6 +1687,10 @@
   </si>
   <si>
     <t>晉安帝3年</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>晉安帝4年至5年</t>
     <phoneticPr fontId="4" type="noConversion"/>
   </si>
 </sst>
@@ -1991,7 +1995,7 @@
             <c:strRef>
               <c:f>統計!$B$2:$B$115</c:f>
               <c:strCache>
-                <c:ptCount val="110"/>
+                <c:ptCount val="111"/>
                 <c:pt idx="0">
                   <c:v>卷1</c:v>
                 </c:pt>
@@ -2321,6 +2325,9 @@
                 </c:pt>
                 <c:pt idx="109">
                   <c:v>卷110</c:v>
+                </c:pt>
+                <c:pt idx="110">
+                  <c:v>卷111</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
@@ -2660,6 +2667,9 @@
                 </c:pt>
                 <c:pt idx="109">
                   <c:v>7</c:v>
+                </c:pt>
+                <c:pt idx="110">
+                  <c:v>6.5</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -3214,7 +3224,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:R111"/>
+  <dimension ref="A1:R112"/>
   <sheetFormatPr defaultColWidth="8.6328125" defaultRowHeight="14" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="7.7265625" customWidth="1"/>
@@ -3329,19 +3339,19 @@
       </c>
       <c r="O2">
         <f t="shared" ref="O2:O8" si="5">L2*$L$10</f>
-        <v>709.05454545454552</v>
+        <v>710.63063063063066</v>
       </c>
       <c r="P2" s="1">
         <f t="shared" ref="P2:P8" si="6">$C$2+O2</f>
-        <v>44728.054545454543</v>
+        <v>44729.630630630629</v>
       </c>
       <c r="Q2">
         <f t="shared" ref="Q2:Q8" si="7">(M2-$F$2)*$L$11</f>
-        <v>963.58098120225611</v>
+        <v>983.70884347825631</v>
       </c>
       <c r="R2" s="1">
         <f t="shared" ref="R2:R8" si="8">$C$2+Q2</f>
-        <v>44982.580981202256</v>
+        <v>45002.708843478256</v>
       </c>
     </row>
     <row r="3" spans="1:18" x14ac:dyDescent="0.25">
@@ -3392,19 +3402,19 @@
       </c>
       <c r="O3">
         <f t="shared" si="5"/>
-        <v>813.32727272727277</v>
+        <v>815.1351351351351</v>
       </c>
       <c r="P3" s="1">
         <f t="shared" si="6"/>
-        <v>44832.327272727271</v>
+        <v>44834.135135135133</v>
       </c>
       <c r="Q3">
         <f t="shared" si="7"/>
-        <v>1056.3817177546402</v>
+        <v>1078.4480579384415</v>
       </c>
       <c r="R3" s="1">
         <f t="shared" si="8"/>
-        <v>45075.381717754637</v>
+        <v>45097.44805793844</v>
       </c>
     </row>
     <row r="4" spans="1:18" x14ac:dyDescent="0.25">
@@ -3455,19 +3465,19 @@
       </c>
       <c r="O4">
         <f t="shared" si="5"/>
-        <v>1230.4181818181819</v>
+        <v>1233.1531531531532</v>
       </c>
       <c r="P4" s="1">
         <f t="shared" si="6"/>
-        <v>45249.418181818182</v>
+        <v>45252.153153153151</v>
       </c>
       <c r="Q4">
         <f t="shared" si="7"/>
-        <v>1272.9167697102034</v>
+        <v>1299.5062250122071</v>
       </c>
       <c r="R4" s="1">
         <f t="shared" si="8"/>
-        <v>45291.916769710202</v>
+        <v>45318.506225012206</v>
       </c>
     </row>
     <row r="5" spans="1:18" x14ac:dyDescent="0.25">
@@ -3518,19 +3528,19 @@
       </c>
       <c r="O5">
         <f t="shared" si="5"/>
-        <v>1835.2</v>
+        <v>1839.2792792792793</v>
       </c>
       <c r="P5" s="1">
         <f t="shared" si="6"/>
-        <v>45854.2</v>
+        <v>45858.279279279282</v>
       </c>
       <c r="Q5">
         <f t="shared" si="7"/>
-        <v>1534.3055109994191</v>
+        <v>1566.3550124083954</v>
       </c>
       <c r="R5" s="1">
         <f t="shared" si="8"/>
-        <v>45553.305510999417</v>
+        <v>45585.355012408392</v>
       </c>
     </row>
     <row r="6" spans="1:18" x14ac:dyDescent="0.25">
@@ -3581,19 +3591,19 @@
       </c>
       <c r="O6">
         <f t="shared" si="5"/>
-        <v>2763.227272727273</v>
+        <v>2769.3693693693695</v>
       </c>
       <c r="P6" s="1">
         <f t="shared" si="6"/>
-        <v>46782.227272727272</v>
+        <v>46788.369369369371</v>
       </c>
       <c r="Q6">
         <f t="shared" si="7"/>
-        <v>2026.1494147270553</v>
+        <v>2068.4728490473767</v>
       </c>
       <c r="R6" s="1">
         <f t="shared" si="8"/>
-        <v>46045.149414727057</v>
+        <v>46087.472849047379</v>
       </c>
     </row>
     <row r="7" spans="1:18" x14ac:dyDescent="0.25">
@@ -3644,19 +3654,19 @@
       </c>
       <c r="O7">
         <f t="shared" si="5"/>
-        <v>3065.6181818181822</v>
+        <v>3072.4324324324325</v>
       </c>
       <c r="P7" s="1">
         <f t="shared" si="6"/>
-        <v>47084.618181818179</v>
+        <v>47091.432432432433</v>
       </c>
       <c r="Q7">
         <f t="shared" si="7"/>
-        <v>2106.5767197391215</v>
+        <v>2150.5801682462043</v>
       </c>
       <c r="R7" s="1">
         <f t="shared" si="8"/>
-        <v>46125.576719739125</v>
+        <v>46169.580168246204</v>
       </c>
     </row>
     <row r="8" spans="1:18" x14ac:dyDescent="0.25">
@@ -3707,19 +3717,19 @@
       </c>
       <c r="O8">
         <f t="shared" si="5"/>
-        <v>3065.6181818181822</v>
+        <v>3072.4324324324325</v>
       </c>
       <c r="P8" s="1">
         <f t="shared" si="6"/>
-        <v>47084.618181818179</v>
+        <v>47091.432432432433</v>
       </c>
       <c r="Q8">
         <f t="shared" si="7"/>
-        <v>2106.5767197391215</v>
+        <v>2150.5801682462043</v>
       </c>
       <c r="R8" s="1">
         <f t="shared" si="8"/>
-        <v>46125.576719739125</v>
+        <v>46169.580168246204</v>
       </c>
     </row>
     <row r="9" spans="1:18" x14ac:dyDescent="0.25">
@@ -3794,7 +3804,7 @@
       </c>
       <c r="L10">
         <f>AVERAGE(E:E)</f>
-        <v>10.427272727272728</v>
+        <v>10.45045045045045</v>
       </c>
     </row>
     <row r="11" spans="1:18" x14ac:dyDescent="0.25">
@@ -3835,7 +3845,7 @@
       </c>
       <c r="L11">
         <f>AVEDEV(I:I)</f>
-        <v>1.5466789425397369</v>
+        <v>1.5789869076697534</v>
       </c>
     </row>
     <row r="12" spans="1:18" x14ac:dyDescent="0.25">
@@ -5698,7 +5708,7 @@
         <v>526</v>
       </c>
       <c r="B66" t="str">
-        <f t="shared" ref="B66:B111" si="16">"卷"&amp;ROW(B65)</f>
+        <f t="shared" ref="B66:B112" si="16">"卷"&amp;ROW(B65)</f>
         <v>卷65</v>
       </c>
       <c r="C66" s="1">
@@ -7285,6 +7295,40 @@
       <c r="I111">
         <f t="shared" ref="I111" si="131">E111/H111</f>
         <v>7</v>
+      </c>
+    </row>
+    <row r="112" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A112">
+        <v>822</v>
+      </c>
+      <c r="B112" t="str">
+        <f t="shared" si="16"/>
+        <v>卷111</v>
+      </c>
+      <c r="C112" s="1">
+        <v>45354</v>
+      </c>
+      <c r="D112" s="1">
+        <v>45366</v>
+      </c>
+      <c r="E112">
+        <f t="shared" ref="E112" si="132">D112-C112+1</f>
+        <v>13</v>
+      </c>
+      <c r="F112">
+        <f t="shared" ref="F112" si="133">G111+1</f>
+        <v>399</v>
+      </c>
+      <c r="G112">
+        <v>400</v>
+      </c>
+      <c r="H112">
+        <f t="shared" ref="H112" si="134">IF(F112*G112&lt;0,ABS(F112)+ABS(G112),G112-F112+1)</f>
+        <v>2</v>
+      </c>
+      <c r="I112">
+        <f t="shared" ref="I112" si="135">E112/H112</f>
+        <v>6.5</v>
       </c>
     </row>
   </sheetData>
@@ -10566,24 +10610,27 @@
       <c r="A112">
         <v>822</v>
       </c>
-      <c r="B112" t="e">
+      <c r="B112" t="str">
         <f>VLOOKUP($A112,統計!$A:$G,2,)</f>
-        <v>#N/A</v>
+        <v>卷111</v>
       </c>
       <c r="C112" t="s">
         <v>307</v>
       </c>
-      <c r="D112" t="e">
+      <c r="D112">
         <f>VLOOKUP($A112,統計!$A:$G,6,)</f>
-        <v>#N/A</v>
-      </c>
-      <c r="E112" t="e">
+        <v>399</v>
+      </c>
+      <c r="E112">
         <f>VLOOKUP($A112,統計!$A:$G,7,)</f>
-        <v>#N/A</v>
-      </c>
-      <c r="I112" t="e">
+        <v>400</v>
+      </c>
+      <c r="H112" t="s">
+        <v>546</v>
+      </c>
+      <c r="I112" t="str">
         <f t="shared" si="1"/>
-        <v>#N/A</v>
+        <v>822|[卷111](5_筆記/资治通鉴111.html)|晉紀三十三|399|400|||晉安帝4年至5年</v>
       </c>
     </row>
     <row r="113" spans="1:9" x14ac:dyDescent="0.25">
